--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Knowhow" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="293">
   <si>
     <t>No.</t>
   </si>
@@ -1585,12 +1585,84 @@
   <si>
     <t>Backtrace</t>
   </si>
+  <si>
+    <t>hàm print_backtrace</t>
+  </si>
+  <si>
+    <t>trace log lấy thông tin line, function, file.</t>
+  </si>
+  <si>
+    <t>backtrace có 2 kiểu :</t>
+  </si>
+  <si>
+    <t>backtrace</t>
+  </si>
+  <si>
+    <t>backtrace_symbol</t>
+  </si>
+  <si>
+    <t>lấy ra địa chỉ của hàm trong stack</t>
+  </si>
+  <si>
+    <t>#include &lt;execinfo.h&gt;</t>
+  </si>
+  <si>
+    <t>#include &lt;stdio.h&gt;</t>
+  </si>
+  <si>
+    <t>void print_backtrace() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    void *buffer[10];</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int nptrs = backtrace(buffer, 10);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    char **symbols = backtrace_symbols(buffer, nptrs);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    for (int i = 0; i &lt; nptrs; i++) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        printf("%s\n", symbols[i]);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    free(symbols);</t>
+  </si>
+  <si>
+    <t>}</t>
+  </si>
+  <si>
+    <t>// Thư viện của backtrace</t>
+  </si>
+  <si>
+    <t>Gmock</t>
+  </si>
+  <si>
+    <t>Các Segment trong C++</t>
+  </si>
+  <si>
+    <t>#8</t>
+  </si>
+  <si>
+    <t>#9</t>
+  </si>
+  <si>
+    <t>Multi threading C++</t>
+  </si>
+  <si>
+    <t>// Khai báo 1 mảng kiểu void, có 10 phần tử để lưu được 10 return address ( tại sao lại không dùng kiểu con trỏ khác ư ? Vì return address không có kiểu cố định như int, char, string,… nên dùng kiểu void thì sẽ hợp lý nhất)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1672,6 +1744,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1912,7 +1991,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -2019,6 +2098,9 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5554,6 +5636,239 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>546100</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangular Callout 1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7753350" y="2292350"/>
+          <a:ext cx="3321050" cy="711200"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -81254"/>
+            <a:gd name="adj2" fmla="val -48899"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Khai báo</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> hàm backtrace, có tác dụng là gán các return address vào mảng void buffer (tối đa 10 phần tử) và return số địa chỉ trả về gán vào biến "nptrs"</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>90380</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>117739</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Straight Arrow Connector 3"/>
+        <xdr:cNvCxnSpPr>
+          <a:endCxn id="2" idx="4"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="3930650" y="2300180"/>
+          <a:ext cx="2784739" cy="11220"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>565150</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>260350</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Rectangular Callout 5"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7772400" y="3073400"/>
+          <a:ext cx="3352800" cy="1123950"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -81063"/>
+            <a:gd name="adj2" fmla="val -79256"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Khai báo</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> 1 mảng các con trỏ trỏ vào con trỏ kiểu char "symbols" để gán vào đó tên các hàm, lấy thông in từ đối số truyền vào là mảng buffer[10] và mảng return address "nptrs". ( Không dùng string được đâu nhé, vì kiểu truyền vào của hàm backtrace là **char)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>133270</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>166477</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="Straight Arrow Connector 6"/>
+        <xdr:cNvCxnSpPr>
+          <a:endCxn id="6" idx="4"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5054600" y="2546350"/>
+          <a:ext cx="1676320" cy="198227"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -5823,19 +6138,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:K22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="5.7109375" customWidth="1"/>
-    <col min="3" max="3" width="37.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.42578125" customWidth="1"/>
+    <col min="2" max="2" width="5.7265625" customWidth="1"/>
+    <col min="3" max="3" width="37.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.453125" customWidth="1"/>
     <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7265625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="18.75">
+    <row r="2" spans="2:11" ht="18.5">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -5861,7 +6176,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:11" ht="45">
+    <row r="3" spans="2:11" ht="43.5">
       <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
@@ -6215,15 +6530,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:F103"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="3" max="3" width="12.28515625" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.26953125" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" customWidth="1"/>
+    <col min="5" max="5" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="18.75">
+    <row r="2" spans="2:6" ht="18.5">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -7365,13 +7680,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:G51"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="B1:G52"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="3" max="3" width="50.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="68.5703125" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" customWidth="1"/>
+    <col min="3" max="3" width="50.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.54296875" customWidth="1"/>
+    <col min="6" max="6" width="9.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6">
@@ -7379,7 +7694,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="2:6" ht="18.75">
+    <row r="2" spans="2:6" ht="18.5">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -8032,18 +8347,24 @@
       </c>
     </row>
     <row r="45" spans="2:6">
-      <c r="B45" s="5"/>
-      <c r="C45" s="6"/>
+      <c r="B45" s="5">
+        <v>6.1</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>269</v>
+      </c>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
-      <c r="F45" s="6"/>
+      <c r="F45" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="46" spans="2:6">
-      <c r="B46" s="5" t="s">
-        <v>267</v>
+      <c r="B46" s="5">
+        <v>6.2</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>191</v>
+        <v>270</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
@@ -8051,27 +8372,33 @@
     </row>
     <row r="47" spans="2:6">
       <c r="B47" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C47" s="6"/>
+        <v>267</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>191</v>
+      </c>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C48" s="6"/>
+        <v>289</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>287</v>
+      </c>
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
       <c r="F48" s="6"/>
     </row>
     <row r="49" spans="2:6">
       <c r="B49" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C49" s="6"/>
+        <v>290</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>288</v>
+      </c>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
       <c r="F49" s="6"/>
@@ -8080,7 +8407,9 @@
       <c r="B50" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C50" s="6"/>
+      <c r="C50" s="6" t="s">
+        <v>291</v>
+      </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
@@ -8093,6 +8422,15 @@
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
       <c r="F51" s="6"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -8136,6 +8474,7 @@
     <hyperlink ref="F42" location="'#5'!B74" display="Link"/>
     <hyperlink ref="F43" location="'#5'!B82" display="Link"/>
     <hyperlink ref="F44" location="'#6'!B2" display="Link"/>
+    <hyperlink ref="F45" location="'#6'!B2" display="Link"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId6"/>
@@ -8145,13 +8484,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J164"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" customWidth="1"/>
+    <col min="1" max="1" width="4.26953125" customWidth="1"/>
+    <col min="2" max="2" width="6.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75">
+    <row r="1" spans="1:3" ht="18.5">
       <c r="C1" s="41" t="s">
         <v>15</v>
       </c>
@@ -8408,14 +8747,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L61"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="3" max="3" width="10.42578125" customWidth="1"/>
-    <col min="4" max="4" width="5.28515625" customWidth="1"/>
-    <col min="5" max="5" width="48.85546875" customWidth="1"/>
+    <col min="3" max="3" width="10.453125" customWidth="1"/>
+    <col min="4" max="4" width="5.26953125" customWidth="1"/>
+    <col min="5" max="5" width="48.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75">
+    <row r="1" spans="1:10" ht="18.5">
       <c r="C1" s="41" t="s">
         <v>57</v>
       </c>
@@ -8446,13 +8785,13 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15.75" thickBot="1">
+    <row r="12" spans="1:10" ht="15" thickBot="1">
       <c r="C12" s="11" t="s">
         <v>63</v>
       </c>
       <c r="D12" s="11"/>
     </row>
-    <row r="13" spans="1:10" ht="15.75" thickBot="1">
+    <row r="13" spans="1:10" ht="15" thickBot="1">
       <c r="C13" s="53" t="s">
         <v>78</v>
       </c>
@@ -8469,7 +8808,7 @@
       <c r="H13" s="24"/>
       <c r="I13" s="25"/>
     </row>
-    <row r="14" spans="1:10" ht="15.75" thickBot="1">
+    <row r="14" spans="1:10" ht="15" thickBot="1">
       <c r="C14" s="54"/>
       <c r="D14" s="23" t="s">
         <v>65</v>
@@ -8511,7 +8850,7 @@
       <c r="H16" s="30"/>
       <c r="I16" s="31"/>
     </row>
-    <row r="17" spans="3:12" ht="15.75" thickBot="1">
+    <row r="17" spans="3:12" ht="15" thickBot="1">
       <c r="C17" s="55"/>
       <c r="D17" s="32"/>
       <c r="E17" s="33" t="s">
@@ -8522,7 +8861,7 @@
       <c r="H17" s="30"/>
       <c r="I17" s="31"/>
     </row>
-    <row r="18" spans="3:12" ht="15.75" thickBot="1">
+    <row r="18" spans="3:12" ht="15" thickBot="1">
       <c r="C18" s="37" t="s">
         <v>79</v>
       </c>
@@ -8542,7 +8881,7 @@
       <c r="K18" s="24"/>
       <c r="L18" s="25"/>
     </row>
-    <row r="19" spans="3:12" ht="15.75" thickBot="1">
+    <row r="19" spans="3:12" ht="15" thickBot="1">
       <c r="C19" s="53" t="s">
         <v>78</v>
       </c>
@@ -8562,7 +8901,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="3:12" ht="15.75" thickBot="1">
+    <row r="21" spans="3:12" ht="15" thickBot="1">
       <c r="C21" s="55"/>
       <c r="D21" s="32"/>
       <c r="E21" s="40" t="s">
@@ -8676,10 +9015,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:V102"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="13" max="13" width="4.85546875" customWidth="1"/>
+    <col min="13" max="13" width="4.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
@@ -9194,7 +9533,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D32"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" s="6" t="s">
@@ -9317,10 +9656,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:H90"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="4" max="4" width="13.5703125" customWidth="1"/>
-    <col min="7" max="7" width="9.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" customWidth="1"/>
+    <col min="7" max="7" width="9.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4">
@@ -9685,15 +10024,121 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="B2:Z19"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="4" max="4" width="15.90625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="2:2">
+    <row r="2" spans="2:26">
       <c r="B2" s="6" t="s">
         <v>268</v>
       </c>
     </row>
+    <row r="3" spans="2:26">
+      <c r="C3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="4" spans="2:26">
+      <c r="D4" t="s">
+        <v>272</v>
+      </c>
+      <c r="E4" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="5" spans="2:26">
+      <c r="D5" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="8" spans="2:26">
+      <c r="D8" s="57" t="s">
+        <v>275</v>
+      </c>
+      <c r="F8" s="58" t="s">
+        <v>286</v>
+      </c>
+      <c r="G8" s="58"/>
+      <c r="H8" s="58"/>
+    </row>
+    <row r="9" spans="2:26">
+      <c r="D9" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="11" spans="2:26">
+      <c r="D11" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="12" spans="2:26">
+      <c r="D12" s="56" t="s">
+        <v>278</v>
+      </c>
+      <c r="F12" s="58" t="s">
+        <v>292</v>
+      </c>
+      <c r="G12" s="58"/>
+      <c r="H12" s="58"/>
+      <c r="I12" s="58"/>
+      <c r="J12" s="58"/>
+      <c r="K12" s="58"/>
+      <c r="L12" s="58"/>
+      <c r="M12" s="58"/>
+      <c r="N12" s="58"/>
+      <c r="O12" s="58"/>
+      <c r="P12" s="58"/>
+      <c r="Q12" s="58"/>
+      <c r="R12" s="58"/>
+      <c r="S12" s="58"/>
+      <c r="T12" s="58"/>
+      <c r="U12" s="58"/>
+      <c r="V12" s="58"/>
+      <c r="W12" s="58"/>
+      <c r="X12" s="58"/>
+      <c r="Y12" s="58"/>
+      <c r="Z12" s="58"/>
+    </row>
+    <row r="13" spans="2:26">
+      <c r="D13" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="14" spans="2:26">
+      <c r="D14" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="15" spans="2:26">
+      <c r="D15" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="16" spans="2:26">
+      <c r="D16" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4">
+      <c r="D17" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="18" spans="4:4">
+      <c r="D18" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="19" spans="4:4">
+      <c r="D19" t="s">
+        <v>285</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Knowhow" sheetId="1" r:id="rId1"/>
@@ -16,6 +16,8 @@
     <sheet name="#4" sheetId="7" r:id="rId7"/>
     <sheet name="#5" sheetId="8" r:id="rId8"/>
     <sheet name="#6" sheetId="9" r:id="rId9"/>
+    <sheet name="#7" sheetId="10" r:id="rId10"/>
+    <sheet name="#8" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="425">
   <si>
     <t>No.</t>
   </si>
@@ -1323,9 +1325,6 @@
     <t>đọc manual của 1 lệnh chỉ định</t>
   </si>
   <si>
-    <t>Gtest</t>
-  </si>
-  <si>
     <t>ls</t>
   </si>
   <si>
@@ -1657,12 +1656,1160 @@
   <si>
     <t>// Khai báo 1 mảng kiểu void, có 10 phần tử để lưu được 10 return address ( tại sao lại không dùng kiểu con trỏ khác ư ? Vì return address không có kiểu cố định như int, char, string,… nên dùng kiểu void thì sẽ hợp lý nhất)</t>
   </si>
+  <si>
+    <t>lấy ra tên của các hàm gọi cho tới hàm này, đối số truyền vào là mảng các địa chỉ và số phần tử của mảng đó</t>
+  </si>
+  <si>
+    <t>printf("[LINE:%d]%s:%s [s_DefaultCopySetting.e_DisplayType:%d]\n",__LINE__,__FILE__,__FUNCTION__,         (int)OAPE_PanelDisplayType_Normal);</t>
+  </si>
+  <si>
+    <t>__LINE__</t>
+  </si>
+  <si>
+    <t>__FILE__</t>
+  </si>
+  <si>
+    <t>__FUNCTION__</t>
+  </si>
+  <si>
+    <t>Thông tin line</t>
+  </si>
+  <si>
+    <t>Thông tin file</t>
+  </si>
+  <si>
+    <t>Thông tin function</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (int)OAPE_PanelDisplayType_Normal</t>
+  </si>
+  <si>
+    <t>Tùy chọn thêm, ở ví dụ này là ép kiểu int và cho hiện giá trị của phương thức</t>
+  </si>
+  <si>
+    <t>Cmake</t>
+  </si>
+  <si>
+    <t>Con trỏ trỏ con trỏ</t>
+  </si>
+  <si>
+    <t>Gtest, Vector Gtest</t>
+  </si>
+  <si>
+    <t>Là 1 biến con trỏ trỏ đến 1 con trỏ khác</t>
+  </si>
+  <si>
+    <t>Tác dụng của nó:</t>
+  </si>
+  <si>
+    <t>Thay đổi trực tiếp biến con trỏ mà nó trỏ đến (bình thường hàm sẽ không thay đổi được con trỏ)</t>
+  </si>
+  <si>
+    <t>void allocate(int *p) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    p = new int(10); // chỉ thay đổi bản sao của con trỏ</t>
+  </si>
+  <si>
+    <t>int main() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int *ptr = nullptr;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    allocate(ptr);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // ptr vẫn là nullptr !!!</t>
+  </si>
+  <si>
+    <t>Case bình thường : hàm không thay đổi được con trỏ</t>
+  </si>
+  <si>
+    <t>Case có sử dụng con trỏ trỏ con trỏ</t>
+  </si>
+  <si>
+    <t>void allocate(int **p) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    *p = new int(10); // thay đổi con trỏ thật</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    allocate(&amp;ptr);   // truyền địa chỉ của ptr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    std::cout &lt;&lt; *ptr; // in ra 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    delete ptr;</t>
+  </si>
+  <si>
+    <t>#10</t>
+  </si>
+  <si>
+    <t>#11</t>
+  </si>
+  <si>
+    <t>#12</t>
+  </si>
+  <si>
+    <t>#13</t>
+  </si>
+  <si>
+    <t>Smart pointer C++</t>
+  </si>
+  <si>
+    <t>Làm việc với mảng các con trỏ</t>
+  </si>
+  <si>
+    <t>int main(int argc, char **argv) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    for (int i = 0; i &lt; argc; i++) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        std::cout &lt;&lt; argv[i] &lt;&lt; std::endl;</t>
+  </si>
+  <si>
+    <t>**argv là con trỏ trỏ tới phần tử đầu tiên của mảng các con trỏ kiểu char</t>
+  </si>
+  <si>
+    <t>khi sử dụng</t>
+  </si>
+  <si>
+    <t>argv[i]</t>
+  </si>
+  <si>
+    <t>argv[i][j]</t>
+  </si>
+  <si>
+    <t>lấy đc toàn bộ chuỗi đến ký tự cuối /0</t>
+  </si>
+  <si>
+    <t>lấy đc ký tự tại vị trí j của mảng thứ i</t>
+  </si>
+  <si>
+    <t>Khi cấp phát mảng 2 chiều</t>
+  </si>
+  <si>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>Chủ đề</t>
+  </si>
+  <si>
+    <t>Mục tiêu</t>
+  </si>
+  <si>
+    <t>Build system là gì?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hiểu vai trò của build system (biên dịch, liên kết, tạo executable) và tại sao CMake chỉ là </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>trình sinh build script</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> chứ không trực tiếp biên dịch.</t>
+    </r>
+  </si>
+  <si>
+    <t>Compiler &amp; Linker</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nắm khái niệm cơ bản về </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>gcc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>clang</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>msvc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, và cách </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>compile → link → run</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Makefile là gì (so sánh nhẹ với CMake)</t>
+  </si>
+  <si>
+    <t>Biết rằng CMake sinh ra để thay thế việc viết Makefile thủ công.</t>
+  </si>
+  <si>
+    <t>⚙️ II. Cấu trúc cơ bản của CMake</t>
+  </si>
+  <si>
+    <t>CMakeLists.txt là gì</t>
+  </si>
+  <si>
+    <t>File trung tâm của dự án CMake, dùng để mô tả cách build.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lệnh </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>cmake_minimum_required()</t>
+    </r>
+  </si>
+  <si>
+    <t>Khai báo version CMake tối thiểu.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lệnh </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>project()</t>
+    </r>
+  </si>
+  <si>
+    <t>Đặt tên project, ngôn ngữ, version.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lệnh </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>add_executable()</t>
+    </r>
+  </si>
+  <si>
+    <t>Tạo file chạy (binary) từ mã nguồn.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lệnh </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>add_library()</t>
+    </r>
+  </si>
+  <si>
+    <t>Tạo thư viện tĩnh (.a / .lib) hoặc động (.so / .dll).</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lệnh </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>target_link_libraries()</t>
+    </r>
+  </si>
+  <si>
+    <t>Liên kết thư viện vào executable hoặc thư viện khác.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lệnh </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>target_include_directories()</t>
+    </r>
+  </si>
+  <si>
+    <t>Chỉ định đường dẫn chứa file header.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lệnh </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>set()</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và biến trong CMake</t>
+    </r>
+  </si>
+  <si>
+    <t>Cách khai báo và sử dụng biến.</t>
+  </si>
+  <si>
+    <t>Cấu trúc thư mục CMake project chuẩn</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Biết cách chia </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>src/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>include/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>tests/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, v.v.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lệnh </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>add_subdirectory()</t>
+    </r>
+  </si>
+  <si>
+    <t>Gộp nhiều CMakeLists nhỏ vào một project lớn.</t>
+  </si>
+  <si>
+    <t>Cách include file header giữa các module</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sử dụng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>target_include_directories()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> đúng cách.</t>
+    </r>
+  </si>
+  <si>
+    <t>Tạo và link thư viện con (submodule)</t>
+  </si>
+  <si>
+    <t>Tách code thành thư viện riêng rồi link vào main.</t>
+  </si>
+  <si>
+    <r>
+      <t>Option và biến cấu hình (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>option()</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>set()</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Cho phép người dùng bật/tắt tính năng khi build (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>-DOPTION=ON</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Build type (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Debug</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Release</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, …)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sử dụng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>CMAKE_BUILD_TYPE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>CMAKE_SOURCE_DIR vs CMAKE_BINARY_DIR</t>
+  </si>
+  <si>
+    <t>Hiểu sự khác biệt giữa nơi chứa source và nơi build.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lệnh </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>message()</t>
+    </r>
+  </si>
+  <si>
+    <t>In thông tin debug khi chạy CMake.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lệnh </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>find_package()</t>
+    </r>
+  </si>
+  <si>
+    <t>Dò và import thư viện cài sẵn (Boost, OpenCV, GTest…).</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cách tự viết file </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>FindXXX.cmake</t>
+    </r>
+  </si>
+  <si>
+    <t>Nếu thư viện không có CMake config sẵn.</t>
+  </si>
+  <si>
+    <r>
+      <t>FetchContent</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> module</t>
+    </r>
+  </si>
+  <si>
+    <t>Tải và build thư viện từ Git trong lúc build.</t>
+  </si>
+  <si>
+    <r>
+      <t>target_link_libraries()</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> nâng cao</t>
+    </r>
+  </si>
+  <si>
+    <t>Phân biệt PUBLIC / PRIVATE / INTERFACE.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lệnh </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>enable_testing()</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>add_test()</t>
+    </r>
+  </si>
+  <si>
+    <t>Tích hợp unit test (thường với GoogleTest).</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lệnh </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>install()</t>
+    </r>
+  </si>
+  <si>
+    <t>Đóng gói, cài đặt file thực thi hoặc thư viện.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lệnh </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>include()</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>configure_file()</t>
+    </r>
+  </si>
+  <si>
+    <t>Tự động tạo file cấu hình khi build.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Generator expressions </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>$&lt;...&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>Điều kiện hóa build theo target.</t>
+  </si>
+  <si>
+    <r>
+      <t>Custom commands (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>add_custom_command</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>add_custom_target</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Chạy script hoặc lệnh tùy chỉnh trong quá trình build.</t>
+  </si>
+  <si>
+    <t>Cross-compiling (build cho nền tảng khác)</t>
+  </si>
+  <si>
+    <t>Build trên Windows nhưng xuất binary cho Linux hoặc ARM.</t>
+  </si>
+  <si>
+    <r>
+      <t>Export/Import target (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>install(EXPORT ...)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Tạo project dùng lại được như thư viện CMake.</t>
+  </si>
+  <si>
+    <t>CMake Presets (CMakePresets.json)</t>
+  </si>
+  <si>
+    <t>Lưu cấu hình build sẵn để chạy nhanh.</t>
+  </si>
+  <si>
+    <t>📘 VIII. Thực hành</t>
+  </si>
+  <si>
+    <t>Bài tập thực hành</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Build 1 file </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>main.cpp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> đơn giản</t>
+    </r>
+  </si>
+  <si>
+    <t>Nắm cấu trúc cơ bản.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Build project có nhiều file </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>.cpp</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>add_executable()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>target_include_directories()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Build và link thư viện con</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>add_library()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>target_link_libraries()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>find_package(GTest)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để test</t>
+    </r>
+  </si>
+  <si>
+    <t>Tích hợp unit test với GoogleTest.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>FetchContent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để tự tải thư viện ngoài</t>
+    </r>
+  </si>
+  <si>
+    <t>Build project hiện đại, không cần cài thủ công.</t>
+  </si>
+  <si>
+    <t>Viết CMake cho project lớn nhiều module</t>
+  </si>
+  <si>
+    <t>Tổng hợp toàn bộ kiến thức.</t>
+  </si>
+  <si>
+    <t>Các đầu mục học Cmake</t>
+  </si>
+  <si>
+    <t>📘 VII. Các chủ đề nâng cao (học sau khi vững cơ bản)</t>
+  </si>
+  <si>
+    <t>📘 VI. Test và cài đặt</t>
+  </si>
+  <si>
+    <t>📘 V. Làm việc với thư viện ngoài</t>
+  </si>
+  <si>
+    <t>📘 IV. Biến, Option, và cấu hình build</t>
+  </si>
+  <si>
+    <t>📘 III. Tổ chức project nhiều file, nhiều thư mục</t>
+  </si>
+  <si>
+    <t>📘 I. Kiến thức nền tảng cần hiểu trước</t>
+  </si>
+  <si>
+    <t>Ý hiểu của tôi</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="13">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1752,8 +2899,38 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1808,8 +2985,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -1986,12 +3169,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -2089,6 +3283,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2098,9 +3295,45 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -6138,19 +7371,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:K22"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="5.7265625" customWidth="1"/>
-    <col min="3" max="3" width="37.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.453125" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" customWidth="1"/>
+    <col min="3" max="3" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.42578125" customWidth="1"/>
     <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="18.5">
+    <row r="2" spans="2:11" ht="18.75">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -6176,7 +7409,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:11" ht="43.5">
+    <row r="3" spans="2:11" ht="45">
       <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
@@ -6527,18 +7760,915 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:Q30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="11" max="11" width="3.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:17">
+      <c r="B2" s="60" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="3" spans="2:17">
+      <c r="C3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17">
+      <c r="C4" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17">
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17">
+      <c r="D6" s="61" t="s">
+        <v>314</v>
+      </c>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="63"/>
+      <c r="L6" s="64" t="s">
+        <v>315</v>
+      </c>
+      <c r="M6" s="44"/>
+      <c r="N6" s="44"/>
+      <c r="O6" s="44"/>
+      <c r="P6" s="44"/>
+      <c r="Q6" s="44"/>
+    </row>
+    <row r="7" spans="2:17">
+      <c r="D7" s="62"/>
+      <c r="E7" s="62" t="s">
+        <v>308</v>
+      </c>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="62"/>
+      <c r="J7" s="62"/>
+      <c r="K7" s="63"/>
+      <c r="L7" s="44"/>
+      <c r="M7" s="44" t="s">
+        <v>316</v>
+      </c>
+      <c r="N7" s="44"/>
+      <c r="O7" s="44"/>
+      <c r="P7" s="44"/>
+      <c r="Q7" s="44"/>
+    </row>
+    <row r="8" spans="2:17">
+      <c r="D8" s="62"/>
+      <c r="E8" s="62" t="s">
+        <v>309</v>
+      </c>
+      <c r="F8" s="62"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="62"/>
+      <c r="K8" s="63"/>
+      <c r="L8" s="44"/>
+      <c r="M8" s="44" t="s">
+        <v>317</v>
+      </c>
+      <c r="N8" s="44"/>
+      <c r="O8" s="44"/>
+      <c r="P8" s="44"/>
+      <c r="Q8" s="44"/>
+    </row>
+    <row r="9" spans="2:17">
+      <c r="D9" s="62"/>
+      <c r="E9" s="62" t="s">
+        <v>284</v>
+      </c>
+      <c r="F9" s="62"/>
+      <c r="G9" s="62"/>
+      <c r="H9" s="62"/>
+      <c r="I9" s="62"/>
+      <c r="J9" s="62"/>
+      <c r="K9" s="63"/>
+      <c r="L9" s="44"/>
+      <c r="M9" s="44" t="s">
+        <v>284</v>
+      </c>
+      <c r="N9" s="44"/>
+      <c r="O9" s="44"/>
+      <c r="P9" s="44"/>
+      <c r="Q9" s="44"/>
+    </row>
+    <row r="10" spans="2:17">
+      <c r="D10" s="62"/>
+      <c r="E10" s="62"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="62"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="62"/>
+      <c r="J10" s="62"/>
+      <c r="K10" s="63"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="44"/>
+      <c r="N10" s="44"/>
+      <c r="O10" s="44"/>
+      <c r="P10" s="44"/>
+      <c r="Q10" s="44"/>
+    </row>
+    <row r="11" spans="2:17">
+      <c r="D11" s="62"/>
+      <c r="E11" s="62" t="s">
+        <v>310</v>
+      </c>
+      <c r="F11" s="62"/>
+      <c r="G11" s="62"/>
+      <c r="H11" s="62"/>
+      <c r="I11" s="62"/>
+      <c r="J11" s="62"/>
+      <c r="K11" s="63"/>
+      <c r="L11" s="44"/>
+      <c r="M11" s="44" t="s">
+        <v>310</v>
+      </c>
+      <c r="N11" s="44"/>
+      <c r="O11" s="44"/>
+      <c r="P11" s="44"/>
+      <c r="Q11" s="44"/>
+    </row>
+    <row r="12" spans="2:17">
+      <c r="D12" s="62"/>
+      <c r="E12" s="62" t="s">
+        <v>311</v>
+      </c>
+      <c r="F12" s="62"/>
+      <c r="G12" s="62"/>
+      <c r="H12" s="62"/>
+      <c r="I12" s="62"/>
+      <c r="J12" s="62"/>
+      <c r="K12" s="63"/>
+      <c r="L12" s="44"/>
+      <c r="M12" s="44" t="s">
+        <v>311</v>
+      </c>
+      <c r="N12" s="44"/>
+      <c r="O12" s="44"/>
+      <c r="P12" s="44"/>
+      <c r="Q12" s="44"/>
+    </row>
+    <row r="13" spans="2:17">
+      <c r="D13" s="62"/>
+      <c r="E13" s="62" t="s">
+        <v>312</v>
+      </c>
+      <c r="F13" s="62"/>
+      <c r="G13" s="62"/>
+      <c r="H13" s="62"/>
+      <c r="I13" s="62"/>
+      <c r="J13" s="62"/>
+      <c r="K13" s="63"/>
+      <c r="L13" s="44"/>
+      <c r="M13" s="44" t="s">
+        <v>318</v>
+      </c>
+      <c r="N13" s="44"/>
+      <c r="O13" s="44"/>
+      <c r="P13" s="44"/>
+      <c r="Q13" s="44"/>
+    </row>
+    <row r="14" spans="2:17">
+      <c r="D14" s="62"/>
+      <c r="E14" s="62" t="s">
+        <v>313</v>
+      </c>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="62"/>
+      <c r="J14" s="62"/>
+      <c r="K14" s="63"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="44" t="s">
+        <v>319</v>
+      </c>
+      <c r="N14" s="44"/>
+      <c r="O14" s="44"/>
+      <c r="P14" s="44"/>
+      <c r="Q14" s="44"/>
+    </row>
+    <row r="15" spans="2:17">
+      <c r="D15" s="62"/>
+      <c r="E15" s="62" t="s">
+        <v>284</v>
+      </c>
+      <c r="F15" s="62"/>
+      <c r="G15" s="62"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="62"/>
+      <c r="K15" s="63"/>
+      <c r="L15" s="44"/>
+      <c r="M15" s="44" t="s">
+        <v>320</v>
+      </c>
+      <c r="N15" s="44"/>
+      <c r="O15" s="44"/>
+      <c r="P15" s="44"/>
+      <c r="Q15" s="44"/>
+    </row>
+    <row r="16" spans="2:17">
+      <c r="D16" s="62"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="62"/>
+      <c r="G16" s="62"/>
+      <c r="H16" s="62"/>
+      <c r="I16" s="62"/>
+      <c r="J16" s="62"/>
+      <c r="K16" s="63"/>
+      <c r="L16" s="44"/>
+      <c r="M16" s="44" t="s">
+        <v>284</v>
+      </c>
+      <c r="N16" s="44"/>
+      <c r="O16" s="44"/>
+      <c r="P16" s="44"/>
+      <c r="Q16" s="44"/>
+    </row>
+    <row r="18" spans="3:8">
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="19" spans="3:8">
+      <c r="E19" s="65" t="s">
+        <v>327</v>
+      </c>
+      <c r="F19" s="65"/>
+      <c r="G19" s="65"/>
+      <c r="H19" s="65"/>
+    </row>
+    <row r="20" spans="3:8">
+      <c r="E20" s="65" t="s">
+        <v>328</v>
+      </c>
+      <c r="F20" s="65"/>
+      <c r="G20" s="65"/>
+      <c r="H20" s="65"/>
+    </row>
+    <row r="21" spans="3:8">
+      <c r="E21" s="65" t="s">
+        <v>329</v>
+      </c>
+      <c r="F21" s="65"/>
+      <c r="G21" s="65"/>
+      <c r="H21" s="65"/>
+    </row>
+    <row r="22" spans="3:8">
+      <c r="E22" s="65" t="s">
+        <v>282</v>
+      </c>
+      <c r="F22" s="65"/>
+      <c r="G22" s="65"/>
+      <c r="H22" s="65"/>
+    </row>
+    <row r="23" spans="3:8">
+      <c r="E23" s="65" t="s">
+        <v>284</v>
+      </c>
+      <c r="F23" s="65"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="65"/>
+    </row>
+    <row r="25" spans="3:8">
+      <c r="D25" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="26" spans="3:8">
+      <c r="D26" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="27" spans="3:8">
+      <c r="E27" t="s">
+        <v>332</v>
+      </c>
+      <c r="F27" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="28" spans="3:8">
+      <c r="E28" t="s">
+        <v>333</v>
+      </c>
+      <c r="F28" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="30" spans="3:8">
+      <c r="C30">
+        <v>3</v>
+      </c>
+      <c r="D30" t="s">
+        <v>336</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E76"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="4.42578125" customWidth="1"/>
+    <col min="3" max="3" width="39.7109375" customWidth="1"/>
+    <col min="4" max="4" width="50.85546875" customWidth="1"/>
+    <col min="5" max="5" width="44.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="28.5">
+      <c r="A1" s="71" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="23.25">
+      <c r="B2" s="66" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="B4" s="74" t="s">
+        <v>337</v>
+      </c>
+      <c r="C4" s="74" t="s">
+        <v>338</v>
+      </c>
+      <c r="D4" s="74" t="s">
+        <v>339</v>
+      </c>
+      <c r="E4" s="75" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="45">
+      <c r="B5" s="72">
+        <v>1</v>
+      </c>
+      <c r="C5" s="73" t="s">
+        <v>340</v>
+      </c>
+      <c r="D5" s="72" t="s">
+        <v>341</v>
+      </c>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" ht="30">
+      <c r="B6" s="72">
+        <v>2</v>
+      </c>
+      <c r="C6" s="73" t="s">
+        <v>342</v>
+      </c>
+      <c r="D6" s="72" t="s">
+        <v>343</v>
+      </c>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" ht="30">
+      <c r="B7" s="72">
+        <v>3</v>
+      </c>
+      <c r="C7" s="73" t="s">
+        <v>344</v>
+      </c>
+      <c r="D7" s="72" t="s">
+        <v>345</v>
+      </c>
+      <c r="E7" s="1"/>
+    </row>
+    <row r="10" spans="1:5" ht="23.25">
+      <c r="B10" s="66" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="B12" s="67" t="s">
+        <v>337</v>
+      </c>
+      <c r="C12" s="67" t="s">
+        <v>338</v>
+      </c>
+      <c r="D12" s="67" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="30">
+      <c r="B13" s="68">
+        <v>1</v>
+      </c>
+      <c r="C13" s="69" t="s">
+        <v>347</v>
+      </c>
+      <c r="D13" s="68" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="B14" s="68">
+        <v>2</v>
+      </c>
+      <c r="C14" s="69" t="s">
+        <v>349</v>
+      </c>
+      <c r="D14" s="68" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="B15" s="68">
+        <v>3</v>
+      </c>
+      <c r="C15" s="69" t="s">
+        <v>351</v>
+      </c>
+      <c r="D15" s="68" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="B16" s="68">
+        <v>4</v>
+      </c>
+      <c r="C16" s="69" t="s">
+        <v>353</v>
+      </c>
+      <c r="D16" s="68" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17" s="68">
+        <v>5</v>
+      </c>
+      <c r="C17" s="69" t="s">
+        <v>355</v>
+      </c>
+      <c r="D17" s="68" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="B18" s="68">
+        <v>6</v>
+      </c>
+      <c r="C18" s="69" t="s">
+        <v>357</v>
+      </c>
+      <c r="D18" s="68" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="B19" s="68">
+        <v>7</v>
+      </c>
+      <c r="C19" s="69" t="s">
+        <v>359</v>
+      </c>
+      <c r="D19" s="68" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4">
+      <c r="B20" s="68">
+        <v>8</v>
+      </c>
+      <c r="C20" s="69" t="s">
+        <v>361</v>
+      </c>
+      <c r="D20" s="68" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" ht="23.25">
+      <c r="B23" s="66" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4">
+      <c r="B25" s="67" t="s">
+        <v>337</v>
+      </c>
+      <c r="C25" s="67" t="s">
+        <v>338</v>
+      </c>
+      <c r="D25" s="67" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4">
+      <c r="B26" s="68">
+        <v>1</v>
+      </c>
+      <c r="C26" s="69" t="s">
+        <v>363</v>
+      </c>
+      <c r="D26" s="68" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4">
+      <c r="B27" s="68">
+        <v>2</v>
+      </c>
+      <c r="C27" s="69" t="s">
+        <v>365</v>
+      </c>
+      <c r="D27" s="68" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4">
+      <c r="B28" s="68">
+        <v>3</v>
+      </c>
+      <c r="C28" s="69" t="s">
+        <v>367</v>
+      </c>
+      <c r="D28" s="68" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4">
+      <c r="B29" s="68">
+        <v>4</v>
+      </c>
+      <c r="C29" s="69" t="s">
+        <v>369</v>
+      </c>
+      <c r="D29" s="68" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" ht="23.25">
+      <c r="B32" s="66" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="B34" s="67" t="s">
+        <v>337</v>
+      </c>
+      <c r="C34" s="67" t="s">
+        <v>338</v>
+      </c>
+      <c r="D34" s="67" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" ht="30">
+      <c r="B35" s="68">
+        <v>1</v>
+      </c>
+      <c r="C35" s="69" t="s">
+        <v>371</v>
+      </c>
+      <c r="D35" s="68" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="B36" s="68">
+        <v>2</v>
+      </c>
+      <c r="C36" s="69" t="s">
+        <v>373</v>
+      </c>
+      <c r="D36" s="68" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" ht="30">
+      <c r="B37" s="68">
+        <v>3</v>
+      </c>
+      <c r="C37" s="69" t="s">
+        <v>375</v>
+      </c>
+      <c r="D37" s="68" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4">
+      <c r="B38" s="68">
+        <v>4</v>
+      </c>
+      <c r="C38" s="69" t="s">
+        <v>377</v>
+      </c>
+      <c r="D38" s="68" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" ht="23.25">
+      <c r="B41" s="66" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4">
+      <c r="B43" s="67" t="s">
+        <v>337</v>
+      </c>
+      <c r="C43" s="67" t="s">
+        <v>338</v>
+      </c>
+      <c r="D43" s="67" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" ht="30">
+      <c r="B44" s="68">
+        <v>1</v>
+      </c>
+      <c r="C44" s="69" t="s">
+        <v>379</v>
+      </c>
+      <c r="D44" s="68" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4">
+      <c r="B45" s="68">
+        <v>2</v>
+      </c>
+      <c r="C45" s="69" t="s">
+        <v>381</v>
+      </c>
+      <c r="D45" s="68" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4">
+      <c r="B46" s="68">
+        <v>3</v>
+      </c>
+      <c r="C46" s="70" t="s">
+        <v>383</v>
+      </c>
+      <c r="D46" s="68" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4">
+      <c r="B47" s="68">
+        <v>4</v>
+      </c>
+      <c r="C47" s="70" t="s">
+        <v>385</v>
+      </c>
+      <c r="D47" s="68" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" ht="23.25">
+      <c r="B50" s="66" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4">
+      <c r="B52" s="67" t="s">
+        <v>337</v>
+      </c>
+      <c r="C52" s="67" t="s">
+        <v>338</v>
+      </c>
+      <c r="D52" s="67" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4">
+      <c r="B53" s="68">
+        <v>1</v>
+      </c>
+      <c r="C53" s="69" t="s">
+        <v>387</v>
+      </c>
+      <c r="D53" s="68" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4">
+      <c r="B54" s="68">
+        <v>2</v>
+      </c>
+      <c r="C54" s="69" t="s">
+        <v>389</v>
+      </c>
+      <c r="D54" s="68" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4">
+      <c r="B55" s="68">
+        <v>3</v>
+      </c>
+      <c r="C55" s="69" t="s">
+        <v>391</v>
+      </c>
+      <c r="D55" s="68" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4">
+      <c r="B56" s="68"/>
+    </row>
+    <row r="58" spans="2:4" ht="23.25">
+      <c r="B58" s="66" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4">
+      <c r="B60" s="67" t="s">
+        <v>337</v>
+      </c>
+      <c r="C60" s="67" t="s">
+        <v>338</v>
+      </c>
+      <c r="D60" s="67" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4">
+      <c r="B61" s="68">
+        <v>1</v>
+      </c>
+      <c r="C61" s="69" t="s">
+        <v>393</v>
+      </c>
+      <c r="D61" s="68" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4" ht="45">
+      <c r="B62" s="68">
+        <v>2</v>
+      </c>
+      <c r="C62" s="69" t="s">
+        <v>395</v>
+      </c>
+      <c r="D62" s="68" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4" ht="30">
+      <c r="B63" s="68">
+        <v>3</v>
+      </c>
+      <c r="C63" s="69" t="s">
+        <v>397</v>
+      </c>
+      <c r="D63" s="68" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4">
+      <c r="B64" s="68">
+        <v>4</v>
+      </c>
+      <c r="C64" s="69" t="s">
+        <v>399</v>
+      </c>
+      <c r="D64" s="68" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4">
+      <c r="B65" s="68">
+        <v>5</v>
+      </c>
+      <c r="C65" s="69" t="s">
+        <v>401</v>
+      </c>
+      <c r="D65" s="68" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" ht="23.25">
+      <c r="B68" s="66" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4">
+      <c r="B70" s="67" t="s">
+        <v>337</v>
+      </c>
+      <c r="C70" s="67" t="s">
+        <v>404</v>
+      </c>
+      <c r="D70" s="67" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4">
+      <c r="B71" s="68">
+        <v>1</v>
+      </c>
+      <c r="C71" s="68" t="s">
+        <v>405</v>
+      </c>
+      <c r="D71" s="68" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4">
+      <c r="B72" s="68">
+        <v>2</v>
+      </c>
+      <c r="C72" s="68" t="s">
+        <v>407</v>
+      </c>
+      <c r="D72" s="68" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4">
+      <c r="B73" s="68">
+        <v>3</v>
+      </c>
+      <c r="C73" s="68" t="s">
+        <v>409</v>
+      </c>
+      <c r="D73" s="68" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4">
+      <c r="B74" s="68">
+        <v>4</v>
+      </c>
+      <c r="C74" s="68" t="s">
+        <v>411</v>
+      </c>
+      <c r="D74" s="68" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4">
+      <c r="B75" s="68">
+        <v>5</v>
+      </c>
+      <c r="C75" s="68" t="s">
+        <v>413</v>
+      </c>
+      <c r="D75" s="68" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4">
+      <c r="B76" s="68">
+        <v>6</v>
+      </c>
+      <c r="C76" s="68" t="s">
+        <v>415</v>
+      </c>
+      <c r="D76" s="68" t="s">
+        <v>416</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:F103"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="12.26953125" customWidth="1"/>
-    <col min="4" max="4" width="13.54296875" customWidth="1"/>
-    <col min="5" max="5" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.1796875" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="18.5">
+    <row r="2" spans="2:6" ht="18.75">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -7680,13 +9810,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:G52"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="B1:G53"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="50.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="68.54296875" customWidth="1"/>
-    <col min="6" max="6" width="9.7265625" customWidth="1"/>
+    <col min="3" max="3" width="50.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6">
@@ -7694,7 +9824,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="2:6" ht="18.5">
+    <row r="2" spans="2:6" ht="18.75">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -8154,13 +10284,13 @@
         <v>5.2</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D32" s="42">
         <v>1</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F32" s="49" t="s">
         <v>14</v>
@@ -8171,7 +10301,7 @@
         <v>5.3</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D33" s="42">
         <v>1</v>
@@ -8186,7 +10316,7 @@
         <v>5.4</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D34" s="42">
         <v>1</v>
@@ -8201,7 +10331,7 @@
         <v>5.5</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D35" s="42">
         <v>1</v>
@@ -8216,7 +10346,7 @@
         <v>5.6</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D36" s="42">
         <v>1</v>
@@ -8231,7 +10361,7 @@
         <v>5.7</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D37" s="42">
         <v>1</v>
@@ -8246,13 +10376,13 @@
         <v>5.8</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D38" s="42">
         <v>1</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>121</v>
@@ -8263,7 +10393,7 @@
         <v>5.9</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D39" s="42">
         <v>1</v>
@@ -8275,10 +10405,10 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="52" t="s">
+        <v>237</v>
+      </c>
+      <c r="C40" s="6" t="s">
         <v>238</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>239</v>
       </c>
       <c r="D40" s="42">
         <v>1</v>
@@ -8290,10 +10420,10 @@
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="52" t="s">
+        <v>242</v>
+      </c>
+      <c r="C41" s="6" t="s">
         <v>243</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>244</v>
       </c>
       <c r="D41" s="42">
         <v>1</v>
@@ -8305,10 +10435,10 @@
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="52" t="s">
+        <v>248</v>
+      </c>
+      <c r="C42" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="D42" s="42">
         <v>1</v>
@@ -8320,10 +10450,10 @@
     </row>
     <row r="43" spans="2:6">
       <c r="B43" s="52" t="s">
+        <v>253</v>
+      </c>
+      <c r="C43" s="6" t="s">
         <v>254</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>255</v>
       </c>
       <c r="D43" s="42">
         <v>1</v>
@@ -8338,9 +10468,11 @@
         <v>12</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="D44" s="6"/>
+        <v>267</v>
+      </c>
+      <c r="D44" s="42">
+        <v>1</v>
+      </c>
       <c r="E44" s="6"/>
       <c r="F44" s="16" t="s">
         <v>14</v>
@@ -8351,9 +10483,11 @@
         <v>6.1</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="D45" s="6"/>
+        <v>268</v>
+      </c>
+      <c r="D45" s="42">
+        <v>1</v>
+      </c>
       <c r="E45" s="6"/>
       <c r="F45" s="16" t="s">
         <v>14</v>
@@ -8364,40 +10498,52 @@
         <v>6.2</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="D46" s="6"/>
+        <v>269</v>
+      </c>
+      <c r="D46" s="42">
+        <v>1</v>
+      </c>
       <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
+      <c r="F46" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="47" spans="2:6">
       <c r="B47" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D47" s="6"/>
+        <v>266</v>
+      </c>
+      <c r="C47" s="60" t="s">
+        <v>303</v>
+      </c>
+      <c r="D47" s="42">
+        <v>1</v>
+      </c>
       <c r="E47" s="6"/>
-      <c r="F47" s="6"/>
+      <c r="F47" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="D48" s="6"/>
+        <v>288</v>
+      </c>
+      <c r="C48" s="59" t="s">
+        <v>302</v>
+      </c>
+      <c r="D48" s="42">
+        <v>0</v>
+      </c>
       <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
+      <c r="F48" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="49" spans="2:6">
       <c r="B49" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
@@ -8405,10 +10551,10 @@
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="5" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
@@ -8416,21 +10562,36 @@
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C51" s="6"/>
+        <v>322</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>287</v>
+      </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
       <c r="F51" s="6"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C52" s="6"/>
+        <v>323</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>290</v>
+      </c>
       <c r="D52" s="6"/>
       <c r="E52" s="6"/>
       <c r="F52" s="6"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -8475,6 +10636,9 @@
     <hyperlink ref="F43" location="'#5'!B82" display="Link"/>
     <hyperlink ref="F44" location="'#6'!B2" display="Link"/>
     <hyperlink ref="F45" location="'#6'!B2" display="Link"/>
+    <hyperlink ref="F46" location="'#6'!B33" display="Link"/>
+    <hyperlink ref="F47" location="'#7'!B2" display="Link"/>
+    <hyperlink ref="F48" location="'#8'!A1" display="Link"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId6"/>
@@ -8484,13 +10648,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J164"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.26953125" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.5">
+    <row r="1" spans="1:3" ht="18.75">
       <c r="C1" s="41" t="s">
         <v>15</v>
       </c>
@@ -8747,14 +10911,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L61"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="10.453125" customWidth="1"/>
-    <col min="4" max="4" width="5.26953125" customWidth="1"/>
-    <col min="5" max="5" width="48.81640625" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" customWidth="1"/>
+    <col min="4" max="4" width="5.28515625" customWidth="1"/>
+    <col min="5" max="5" width="48.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.5">
+    <row r="1" spans="1:10" ht="18.75">
       <c r="C1" s="41" t="s">
         <v>57</v>
       </c>
@@ -8785,14 +10949,14 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15" thickBot="1">
+    <row r="12" spans="1:10" ht="15.75" thickBot="1">
       <c r="C12" s="11" t="s">
         <v>63</v>
       </c>
       <c r="D12" s="11"/>
     </row>
-    <row r="13" spans="1:10" ht="15" thickBot="1">
-      <c r="C13" s="53" t="s">
+    <row r="13" spans="1:10" ht="15.75" thickBot="1">
+      <c r="C13" s="56" t="s">
         <v>78</v>
       </c>
       <c r="D13" s="26" t="s">
@@ -8808,8 +10972,8 @@
       <c r="H13" s="24"/>
       <c r="I13" s="25"/>
     </row>
-    <row r="14" spans="1:10" ht="15" thickBot="1">
-      <c r="C14" s="54"/>
+    <row r="14" spans="1:10" ht="15.75" thickBot="1">
+      <c r="C14" s="57"/>
       <c r="D14" s="23" t="s">
         <v>65</v>
       </c>
@@ -8825,7 +10989,7 @@
       <c r="J14" s="25"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="C15" s="54"/>
+      <c r="C15" s="57"/>
       <c r="D15" s="26" t="s">
         <v>66</v>
       </c>
@@ -8840,7 +11004,7 @@
       <c r="I15" s="28"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="C16" s="54"/>
+      <c r="C16" s="57"/>
       <c r="D16" s="29"/>
       <c r="E16" s="30" t="s">
         <v>74</v>
@@ -8850,8 +11014,8 @@
       <c r="H16" s="30"/>
       <c r="I16" s="31"/>
     </row>
-    <row r="17" spans="3:12" ht="15" thickBot="1">
-      <c r="C17" s="55"/>
+    <row r="17" spans="3:12" ht="15.75" thickBot="1">
+      <c r="C17" s="58"/>
       <c r="D17" s="32"/>
       <c r="E17" s="33" t="s">
         <v>75</v>
@@ -8861,7 +11025,7 @@
       <c r="H17" s="30"/>
       <c r="I17" s="31"/>
     </row>
-    <row r="18" spans="3:12" ht="15" thickBot="1">
+    <row r="18" spans="3:12" ht="15.75" thickBot="1">
       <c r="C18" s="37" t="s">
         <v>79</v>
       </c>
@@ -8881,8 +11045,8 @@
       <c r="K18" s="24"/>
       <c r="L18" s="25"/>
     </row>
-    <row r="19" spans="3:12" ht="15" thickBot="1">
-      <c r="C19" s="53" t="s">
+    <row r="19" spans="3:12" ht="15.75" thickBot="1">
+      <c r="C19" s="56" t="s">
         <v>78</v>
       </c>
       <c r="D19" s="23" t="s">
@@ -8893,7 +11057,7 @@
       </c>
     </row>
     <row r="20" spans="3:12">
-      <c r="C20" s="54"/>
+      <c r="C20" s="57"/>
       <c r="D20" s="26" t="s">
         <v>82</v>
       </c>
@@ -8901,8 +11065,8 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="3:12" ht="15" thickBot="1">
-      <c r="C21" s="55"/>
+    <row r="21" spans="3:12" ht="15.75" thickBot="1">
+      <c r="C21" s="58"/>
       <c r="D21" s="32"/>
       <c r="E21" s="40" t="s">
         <v>84</v>
@@ -9015,10 +11179,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:V102"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="13" max="13" width="4.81640625" customWidth="1"/>
+    <col min="13" max="13" width="4.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
@@ -9533,7 +11697,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D32"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" s="6" t="s">
@@ -9656,111 +11820,111 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:H90"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="13.54296875" customWidth="1"/>
-    <col min="7" max="7" width="9.453125" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="2:4">
       <c r="C3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="2:4">
       <c r="C5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6" spans="2:4">
       <c r="C6" s="17" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="2:4">
       <c r="C7" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>197</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="8" spans="2:4">
       <c r="C8" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="D8" t="s">
         <v>199</v>
-      </c>
-      <c r="D8" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="9" spans="2:4">
       <c r="C9" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="D9" t="s">
         <v>201</v>
-      </c>
-      <c r="D9" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="13" spans="2:4">
       <c r="B13" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14" spans="2:4">
       <c r="C14" s="22" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" spans="2:4">
       <c r="C16" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17" spans="2:4">
       <c r="C17" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="D17" t="s">
         <v>206</v>
-      </c>
-      <c r="D17" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="18" spans="2:4">
       <c r="C18" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="D18" t="s">
         <v>208</v>
-      </c>
-      <c r="D18" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="21" spans="2:4">
       <c r="B21" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22" spans="2:4">
       <c r="C22" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="24" spans="2:4">
       <c r="C24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25" spans="2:4">
       <c r="C25" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="D25" t="s">
         <v>211</v>
-      </c>
-      <c r="D25" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="26" spans="2:4">
@@ -9768,146 +11932,146 @@
     </row>
     <row r="28" spans="2:4">
       <c r="B28" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="29" spans="2:4">
       <c r="C29" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="31" spans="2:4">
       <c r="C31" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="32" spans="2:4">
       <c r="C32" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="D32" t="s">
         <v>215</v>
-      </c>
-      <c r="D32" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="36" spans="2:6">
       <c r="C36" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="37" spans="2:6">
       <c r="C37" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="39" spans="2:6">
       <c r="C39" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="40" spans="2:6">
       <c r="C40" s="17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D40" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="43" spans="2:6">
       <c r="B43" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="44" spans="2:6">
       <c r="C44" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="46" spans="2:6">
       <c r="C46" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="47" spans="2:6">
       <c r="C47" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="E47" t="s">
         <v>224</v>
-      </c>
-      <c r="E47" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="48" spans="2:6">
       <c r="C48" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="F48" t="s">
         <v>226</v>
-      </c>
-      <c r="F48" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="49" spans="2:6">
       <c r="C49" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="F49" t="s">
         <v>228</v>
-      </c>
-      <c r="F49" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="53" spans="2:6">
       <c r="C53" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="55" spans="2:6">
       <c r="C55" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="C56" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="E56" t="s">
         <v>234</v>
-      </c>
-      <c r="E56" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="57" spans="2:6">
       <c r="C57" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="E57" t="s">
         <v>236</v>
-      </c>
-      <c r="E57" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="61" spans="2:6">
       <c r="C61" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="63" spans="2:6">
       <c r="C63" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="64" spans="2:6">
       <c r="C64" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="E64" t="s">
         <v>241</v>
-      </c>
-      <c r="E64" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="65" spans="2:8">
@@ -9915,106 +12079,106 @@
     </row>
     <row r="67" spans="2:8">
       <c r="B67" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C67" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="68" spans="2:8">
       <c r="C68" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="70" spans="2:8">
       <c r="C70" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="71" spans="2:8">
       <c r="C71" s="17" t="s">
+        <v>245</v>
+      </c>
+      <c r="E71" t="s">
         <v>246</v>
-      </c>
-      <c r="E71" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="74" spans="2:8">
       <c r="B74" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="75" spans="2:8">
       <c r="C75" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="77" spans="2:8">
       <c r="C77" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="78" spans="2:8">
       <c r="C78" t="s">
+        <v>251</v>
+      </c>
+      <c r="H78" t="s">
         <v>252</v>
-      </c>
-      <c r="H78" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="82" spans="2:5">
       <c r="B82" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="83" spans="2:5">
       <c r="C83" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="85" spans="2:5">
       <c r="C85" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="86" spans="2:5">
       <c r="C86" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="E86" t="s">
         <v>257</v>
-      </c>
-      <c r="E86" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="87" spans="2:5">
       <c r="C87" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="E87" t="s">
         <v>261</v>
-      </c>
-      <c r="E87" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="88" spans="2:5">
       <c r="C88" s="17" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E88" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="89" spans="2:5">
       <c r="C89" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="E89" t="s">
         <v>259</v>
-      </c>
-      <c r="E89" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="90" spans="2:5">
       <c r="C90" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="E90" t="s">
         <v>263</v>
-      </c>
-      <c r="E90" t="s">
-        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -10024,121 +12188,166 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:Z19"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="B2:Z40"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:26">
       <c r="B2" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="2:26">
       <c r="C3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="2:26">
       <c r="D4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="2:26">
       <c r="D5" t="s">
-        <v>273</v>
+        <v>272</v>
+      </c>
+      <c r="E5" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="8" spans="2:26">
-      <c r="D8" s="57" t="s">
-        <v>275</v>
-      </c>
-      <c r="F8" s="58" t="s">
-        <v>286</v>
-      </c>
-      <c r="G8" s="58"/>
-      <c r="H8" s="58"/>
+      <c r="D8" s="54" t="s">
+        <v>274</v>
+      </c>
+      <c r="F8" s="55" t="s">
+        <v>285</v>
+      </c>
+      <c r="G8" s="55"/>
+      <c r="H8" s="55"/>
     </row>
     <row r="9" spans="2:26">
       <c r="D9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="2:26">
       <c r="D11" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="12" spans="2:26">
+      <c r="D12" s="53" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="12" spans="2:26">
-      <c r="D12" s="56" t="s">
-        <v>278</v>
-      </c>
-      <c r="F12" s="58" t="s">
-        <v>292</v>
-      </c>
-      <c r="G12" s="58"/>
-      <c r="H12" s="58"/>
-      <c r="I12" s="58"/>
-      <c r="J12" s="58"/>
-      <c r="K12" s="58"/>
-      <c r="L12" s="58"/>
-      <c r="M12" s="58"/>
-      <c r="N12" s="58"/>
-      <c r="O12" s="58"/>
-      <c r="P12" s="58"/>
-      <c r="Q12" s="58"/>
-      <c r="R12" s="58"/>
-      <c r="S12" s="58"/>
-      <c r="T12" s="58"/>
-      <c r="U12" s="58"/>
-      <c r="V12" s="58"/>
-      <c r="W12" s="58"/>
-      <c r="X12" s="58"/>
-      <c r="Y12" s="58"/>
-      <c r="Z12" s="58"/>
+      <c r="F12" s="55" t="s">
+        <v>291</v>
+      </c>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="55"/>
+      <c r="K12" s="55"/>
+      <c r="L12" s="55"/>
+      <c r="M12" s="55"/>
+      <c r="N12" s="55"/>
+      <c r="O12" s="55"/>
+      <c r="P12" s="55"/>
+      <c r="Q12" s="55"/>
+      <c r="R12" s="55"/>
+      <c r="S12" s="55"/>
+      <c r="T12" s="55"/>
+      <c r="U12" s="55"/>
+      <c r="V12" s="55"/>
+      <c r="W12" s="55"/>
+      <c r="X12" s="55"/>
+      <c r="Y12" s="55"/>
+      <c r="Z12" s="55"/>
     </row>
     <row r="13" spans="2:26">
       <c r="D13" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="2:26">
       <c r="D14" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="2:26">
       <c r="D15" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="2:26">
       <c r="D16" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>285</v>
+        <v>284</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7">
+      <c r="B33" s="6" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
+      <c r="C35" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7">
+      <c r="D37" t="s">
+        <v>294</v>
+      </c>
+      <c r="E37" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7">
+      <c r="D38" t="s">
+        <v>295</v>
+      </c>
+      <c r="E38" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7">
+      <c r="D39" t="s">
+        <v>296</v>
+      </c>
+      <c r="E39" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7">
+      <c r="D40" t="s">
+        <v>300</v>
+      </c>
+      <c r="G40" t="s">
+        <v>301</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -18,6 +18,7 @@
     <sheet name="#6" sheetId="9" r:id="rId9"/>
     <sheet name="#7" sheetId="10" r:id="rId10"/>
     <sheet name="#8" sheetId="11" r:id="rId11"/>
+    <sheet name="Sheet1" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="450">
   <si>
     <t>No.</t>
   </si>
@@ -1990,9 +1991,6 @@
     </r>
   </si>
   <si>
-    <t>Tạo thư viện tĩnh (.a / .lib) hoặc động (.so / .dll).</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Lệnh </t>
     </r>
@@ -2803,13 +2801,550 @@
   </si>
   <si>
     <t>Ý hiểu của tôi</t>
+  </si>
+  <si>
+    <t>Build system là hệ thống build các file ".cpp" thành file ".o" hoặc ".obj" rồi liên kết chúng lại với nhau để tạo thành file thực thi. ( ví dụ liên kết với nhau tạo thành file ".exe")</t>
+  </si>
+  <si>
+    <t>Compile : Build file từ mã nguồn C++ thành mã máy ".o" , ".obj" (compiler phổ biến : g++, clang++, ...)
+Link : Trình linker ghép các file .o lại với nhau và ghép cả thư viện hệ thống (như iostream) lại để tạo thành file .exe , .out
+Run : Hệ điều hành chạy file .exe đó</t>
+  </si>
+  <si>
+    <t>CMake sinh ra để thay thế việc viết Makefile thủ công</t>
+  </si>
+  <si>
+    <t>Đây là file trung tâm của dự án, dùng để mô tả cách build</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cấu hình version cmake tối thiểu. VD : 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cmake_minimum_required(VERSION 3.10)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Đặt tên để gọi trong src, nên đặt giống tên folder và execute để dễ quản lý. VD :
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>project(HelloCMake)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Build src chỉ định và tạo file execute để chạy src đó. VD : 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>add_executable(HelloCMake src/main.cpp)</t>
+    </r>
+  </si>
+  <si>
+    <t>Kiểu</t>
+  </si>
+  <si>
+    <t>Cách tạo trong CMake</t>
+  </si>
+  <si>
+    <t>File sinh ra</t>
+  </si>
+  <si>
+    <t>Khi nào dùng</t>
+  </si>
+  <si>
+    <t>Static library</t>
+  </si>
+  <si>
+    <t>add_library(mylib STATIC src/mylib.cpp)</t>
+  </si>
+  <si>
+    <r>
+      <t>.a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Linux/macOS), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>.lib</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Windows)</t>
+    </r>
+  </si>
+  <si>
+    <t>Khi muốn nhúng code thư viện vào chương trình (compile-time)</t>
+  </si>
+  <si>
+    <t>Shared/Dynamic library</t>
+  </si>
+  <si>
+    <t>add_library(mylib SHARED src/mylib.cpp)</t>
+  </si>
+  <si>
+    <r>
+      <t>.so</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Linux), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>.dll</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Windows), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>.dylib</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (macOS)</t>
+    </r>
+  </si>
+  <si>
+    <t>Khi muốn chia sẻ thư viện (runtime load)</t>
+  </si>
+  <si>
+    <t>Object library</t>
+  </si>
+  <si>
+    <t>add_library(mylib OBJECT src/mylib.cpp)</t>
+  </si>
+  <si>
+    <r>
+      <t>.obj</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hoặc </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>.o</t>
+    </r>
+  </si>
+  <si>
+    <t>Khi cần tái sử dụng đối tượng biên dịch trước khi link</t>
+  </si>
+  <si>
+    <t>Tạo thư viện tĩnh (.a / .lib) hoặc động (.so / .dll) hoặc thư viện mở ( .o / .obj)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Build exe và liên kết thư viện vào file đó. 
+Cấu trúc : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>add_library( &lt;tên đối tượng thư viện&gt; &lt;STATIC/SHARED/OBJECT(kiểu thư viện)&gt; &lt;đường dẫn tới file ".cpp"&gt; )</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+VD :
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">add_library(mylib </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>STATIC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> src/include/mylib.cpp)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : add thư viện tĩnh vào exe, nếu sửa thư viện là phải build lại toàn bộ
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">add_library(mylib </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SHARED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> src/include/mylib.cpp)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : add thư viện động (DLL : Dynamic Linked Library), nếu sửa thư viện thì chỉ cần build lại thư viện là exe chạy với xử lý khác
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">add_library(mylib </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OBJECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> src/include/mylib.cpp)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : add thư viện mở cho dự án lớn, chưa build thư viện với exe, nếu sửa thư viện thì phải build lại thư viện đối tượng</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sau khi </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>add_library</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> xong thì phải liên kết nó vào execute hoặc liên kết thư viện vào thư viện khác. Cấu trúc : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>target_link_libraries(&lt;tên đối tượng(phải là execute hoặc thư viện khác&gt; &lt;PRIVATE/PUBLIC/INTERFACE(kiểu liên kết)&gt; &lt;đối tượng liên kết tới&gt;)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+VD :
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">target_link_libraries(MyApp </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PRIVATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> mylib)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : liên kết kiểu private, các thư viện khác link tới MyApp không sử dụng đc define của mylib
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">target_link_libraries(MyApp </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PUBLIC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> mylib)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : liên kết kiểu public, các thư viện khác và target đều dùng được define của mylib
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">target_link_libraries(MyApp </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>INTERFACE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> mylib)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : liên kết kiểu interface, target không thể sử dụng được define, nhưng các thư viện link tới target thì dùng được define của thư viện được link</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2929,8 +3464,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2988,6 +3530,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3185,7 +3733,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -3286,15 +3834,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3333,6 +3872,27 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7769,7 +8329,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17">
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="57" t="s">
         <v>303</v>
       </c>
     </row>
@@ -7792,17 +8352,17 @@
       </c>
     </row>
     <row r="6" spans="2:17">
-      <c r="D6" s="61" t="s">
+      <c r="D6" s="58" t="s">
         <v>314</v>
       </c>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="63"/>
-      <c r="L6" s="64" t="s">
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="60"/>
+      <c r="L6" s="61" t="s">
         <v>315</v>
       </c>
       <c r="M6" s="44"/>
@@ -7812,16 +8372,16 @@
       <c r="Q6" s="44"/>
     </row>
     <row r="7" spans="2:17">
-      <c r="D7" s="62"/>
-      <c r="E7" s="62" t="s">
+      <c r="D7" s="59"/>
+      <c r="E7" s="59" t="s">
         <v>308</v>
       </c>
-      <c r="F7" s="62"/>
-      <c r="G7" s="62"/>
-      <c r="H7" s="62"/>
-      <c r="I7" s="62"/>
-      <c r="J7" s="62"/>
-      <c r="K7" s="63"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="59"/>
+      <c r="K7" s="60"/>
       <c r="L7" s="44"/>
       <c r="M7" s="44" t="s">
         <v>316</v>
@@ -7832,16 +8392,16 @@
       <c r="Q7" s="44"/>
     </row>
     <row r="8" spans="2:17">
-      <c r="D8" s="62"/>
-      <c r="E8" s="62" t="s">
+      <c r="D8" s="59"/>
+      <c r="E8" s="59" t="s">
         <v>309</v>
       </c>
-      <c r="F8" s="62"/>
-      <c r="G8" s="62"/>
-      <c r="H8" s="62"/>
-      <c r="I8" s="62"/>
-      <c r="J8" s="62"/>
-      <c r="K8" s="63"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="59"/>
+      <c r="K8" s="60"/>
       <c r="L8" s="44"/>
       <c r="M8" s="44" t="s">
         <v>317</v>
@@ -7852,16 +8412,16 @@
       <c r="Q8" s="44"/>
     </row>
     <row r="9" spans="2:17">
-      <c r="D9" s="62"/>
-      <c r="E9" s="62" t="s">
+      <c r="D9" s="59"/>
+      <c r="E9" s="59" t="s">
         <v>284</v>
       </c>
-      <c r="F9" s="62"/>
-      <c r="G9" s="62"/>
-      <c r="H9" s="62"/>
-      <c r="I9" s="62"/>
-      <c r="J9" s="62"/>
-      <c r="K9" s="63"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="59"/>
+      <c r="J9" s="59"/>
+      <c r="K9" s="60"/>
       <c r="L9" s="44"/>
       <c r="M9" s="44" t="s">
         <v>284</v>
@@ -7872,14 +8432,14 @@
       <c r="Q9" s="44"/>
     </row>
     <row r="10" spans="2:17">
-      <c r="D10" s="62"/>
-      <c r="E10" s="62"/>
-      <c r="F10" s="62"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="62"/>
-      <c r="I10" s="62"/>
-      <c r="J10" s="62"/>
-      <c r="K10" s="63"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="59"/>
+      <c r="K10" s="60"/>
       <c r="L10" s="44"/>
       <c r="M10" s="44"/>
       <c r="N10" s="44"/>
@@ -7888,16 +8448,16 @@
       <c r="Q10" s="44"/>
     </row>
     <row r="11" spans="2:17">
-      <c r="D11" s="62"/>
-      <c r="E11" s="62" t="s">
+      <c r="D11" s="59"/>
+      <c r="E11" s="59" t="s">
         <v>310</v>
       </c>
-      <c r="F11" s="62"/>
-      <c r="G11" s="62"/>
-      <c r="H11" s="62"/>
-      <c r="I11" s="62"/>
-      <c r="J11" s="62"/>
-      <c r="K11" s="63"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="59"/>
+      <c r="J11" s="59"/>
+      <c r="K11" s="60"/>
       <c r="L11" s="44"/>
       <c r="M11" s="44" t="s">
         <v>310</v>
@@ -7908,16 +8468,16 @@
       <c r="Q11" s="44"/>
     </row>
     <row r="12" spans="2:17">
-      <c r="D12" s="62"/>
-      <c r="E12" s="62" t="s">
+      <c r="D12" s="59"/>
+      <c r="E12" s="59" t="s">
         <v>311</v>
       </c>
-      <c r="F12" s="62"/>
-      <c r="G12" s="62"/>
-      <c r="H12" s="62"/>
-      <c r="I12" s="62"/>
-      <c r="J12" s="62"/>
-      <c r="K12" s="63"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+      <c r="J12" s="59"/>
+      <c r="K12" s="60"/>
       <c r="L12" s="44"/>
       <c r="M12" s="44" t="s">
         <v>311</v>
@@ -7928,16 +8488,16 @@
       <c r="Q12" s="44"/>
     </row>
     <row r="13" spans="2:17">
-      <c r="D13" s="62"/>
-      <c r="E13" s="62" t="s">
+      <c r="D13" s="59"/>
+      <c r="E13" s="59" t="s">
         <v>312</v>
       </c>
-      <c r="F13" s="62"/>
-      <c r="G13" s="62"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="62"/>
-      <c r="J13" s="62"/>
-      <c r="K13" s="63"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="59"/>
+      <c r="I13" s="59"/>
+      <c r="J13" s="59"/>
+      <c r="K13" s="60"/>
       <c r="L13" s="44"/>
       <c r="M13" s="44" t="s">
         <v>318</v>
@@ -7948,16 +8508,16 @@
       <c r="Q13" s="44"/>
     </row>
     <row r="14" spans="2:17">
-      <c r="D14" s="62"/>
-      <c r="E14" s="62" t="s">
+      <c r="D14" s="59"/>
+      <c r="E14" s="59" t="s">
         <v>313</v>
       </c>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="62"/>
-      <c r="J14" s="62"/>
-      <c r="K14" s="63"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="59"/>
+      <c r="H14" s="59"/>
+      <c r="I14" s="59"/>
+      <c r="J14" s="59"/>
+      <c r="K14" s="60"/>
       <c r="L14" s="44"/>
       <c r="M14" s="44" t="s">
         <v>319</v>
@@ -7968,16 +8528,16 @@
       <c r="Q14" s="44"/>
     </row>
     <row r="15" spans="2:17">
-      <c r="D15" s="62"/>
-      <c r="E15" s="62" t="s">
+      <c r="D15" s="59"/>
+      <c r="E15" s="59" t="s">
         <v>284</v>
       </c>
-      <c r="F15" s="62"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="62"/>
-      <c r="I15" s="62"/>
-      <c r="J15" s="62"/>
-      <c r="K15" s="63"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="59"/>
+      <c r="H15" s="59"/>
+      <c r="I15" s="59"/>
+      <c r="J15" s="59"/>
+      <c r="K15" s="60"/>
       <c r="L15" s="44"/>
       <c r="M15" s="44" t="s">
         <v>320</v>
@@ -7988,14 +8548,14 @@
       <c r="Q15" s="44"/>
     </row>
     <row r="16" spans="2:17">
-      <c r="D16" s="62"/>
-      <c r="E16" s="62"/>
-      <c r="F16" s="62"/>
-      <c r="G16" s="62"/>
-      <c r="H16" s="62"/>
-      <c r="I16" s="62"/>
-      <c r="J16" s="62"/>
-      <c r="K16" s="63"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="59"/>
+      <c r="I16" s="59"/>
+      <c r="J16" s="59"/>
+      <c r="K16" s="60"/>
       <c r="L16" s="44"/>
       <c r="M16" s="44" t="s">
         <v>284</v>
@@ -8014,44 +8574,44 @@
       </c>
     </row>
     <row r="19" spans="3:8">
-      <c r="E19" s="65" t="s">
+      <c r="E19" s="62" t="s">
         <v>327</v>
       </c>
-      <c r="F19" s="65"/>
-      <c r="G19" s="65"/>
-      <c r="H19" s="65"/>
+      <c r="F19" s="62"/>
+      <c r="G19" s="62"/>
+      <c r="H19" s="62"/>
     </row>
     <row r="20" spans="3:8">
-      <c r="E20" s="65" t="s">
+      <c r="E20" s="62" t="s">
         <v>328</v>
       </c>
-      <c r="F20" s="65"/>
-      <c r="G20" s="65"/>
-      <c r="H20" s="65"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="62"/>
+      <c r="H20" s="62"/>
     </row>
     <row r="21" spans="3:8">
-      <c r="E21" s="65" t="s">
+      <c r="E21" s="62" t="s">
         <v>329</v>
       </c>
-      <c r="F21" s="65"/>
-      <c r="G21" s="65"/>
-      <c r="H21" s="65"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="62"/>
+      <c r="H21" s="62"/>
     </row>
     <row r="22" spans="3:8">
-      <c r="E22" s="65" t="s">
+      <c r="E22" s="62" t="s">
         <v>282</v>
       </c>
-      <c r="F22" s="65"/>
-      <c r="G22" s="65"/>
-      <c r="H22" s="65"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="62"/>
     </row>
     <row r="23" spans="3:8">
-      <c r="E23" s="65" t="s">
+      <c r="E23" s="62" t="s">
         <v>284</v>
       </c>
-      <c r="F23" s="65"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="65"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="62"/>
+      <c r="H23" s="62"/>
     </row>
     <row r="25" spans="3:8">
       <c r="D25" t="s">
@@ -8100,556 +8660,655 @@
     <col min="2" max="2" width="4.42578125" customWidth="1"/>
     <col min="3" max="3" width="39.7109375" customWidth="1"/>
     <col min="4" max="4" width="50.85546875" customWidth="1"/>
-    <col min="5" max="5" width="44.140625" customWidth="1"/>
+    <col min="5" max="5" width="75.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.5">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="68" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="23.25">
+      <c r="B2" s="63" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="B4" s="71" t="s">
+        <v>337</v>
+      </c>
+      <c r="C4" s="71" t="s">
+        <v>338</v>
+      </c>
+      <c r="D4" s="71" t="s">
+        <v>339</v>
+      </c>
+      <c r="E4" s="72" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="45">
+      <c r="B5" s="69">
+        <v>1</v>
+      </c>
+      <c r="C5" s="70" t="s">
+        <v>340</v>
+      </c>
+      <c r="D5" s="69" t="s">
+        <v>341</v>
+      </c>
+      <c r="E5" s="69" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="81" customHeight="1">
+      <c r="B6" s="69">
+        <v>2</v>
+      </c>
+      <c r="C6" s="70" t="s">
+        <v>342</v>
+      </c>
+      <c r="D6" s="69" t="s">
+        <v>343</v>
+      </c>
+      <c r="E6" s="69" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="30">
+      <c r="B7" s="69">
+        <v>3</v>
+      </c>
+      <c r="C7" s="70" t="s">
+        <v>344</v>
+      </c>
+      <c r="D7" s="69" t="s">
+        <v>345</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="23.25">
+      <c r="B10" s="63" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="B12" s="73" t="s">
+        <v>337</v>
+      </c>
+      <c r="C12" s="73" t="s">
+        <v>338</v>
+      </c>
+      <c r="D12" s="73" t="s">
+        <v>339</v>
+      </c>
+      <c r="E12" s="74" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="30">
+      <c r="B13" s="69">
+        <v>1</v>
+      </c>
+      <c r="C13" s="70" t="s">
+        <v>347</v>
+      </c>
+      <c r="D13" s="69" t="s">
+        <v>348</v>
+      </c>
+      <c r="E13" s="69" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="30">
+      <c r="B14" s="69">
+        <v>2</v>
+      </c>
+      <c r="C14" s="70" t="s">
+        <v>349</v>
+      </c>
+      <c r="D14" s="69" t="s">
+        <v>350</v>
+      </c>
+      <c r="E14" s="69" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="30">
+      <c r="B15" s="69">
+        <v>3</v>
+      </c>
+      <c r="C15" s="70" t="s">
+        <v>351</v>
+      </c>
+      <c r="D15" s="69" t="s">
+        <v>352</v>
+      </c>
+      <c r="E15" s="69" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="30">
+      <c r="B16" s="69">
+        <v>4</v>
+      </c>
+      <c r="C16" s="70" t="s">
+        <v>353</v>
+      </c>
+      <c r="D16" s="69" t="s">
+        <v>354</v>
+      </c>
+      <c r="E16" s="78" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="165">
+      <c r="B17" s="69">
+        <v>5</v>
+      </c>
+      <c r="C17" s="70" t="s">
+        <v>355</v>
+      </c>
+      <c r="D17" s="69" t="s">
+        <v>447</v>
+      </c>
+      <c r="E17" s="78" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="180">
+      <c r="B18" s="69">
+        <v>6</v>
+      </c>
+      <c r="C18" s="70" t="s">
+        <v>356</v>
+      </c>
+      <c r="D18" s="69" t="s">
+        <v>357</v>
+      </c>
+      <c r="E18" s="78" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
+      <c r="B19" s="69">
+        <v>7</v>
+      </c>
+      <c r="C19" s="70" t="s">
+        <v>358</v>
+      </c>
+      <c r="D19" s="69" t="s">
+        <v>359</v>
+      </c>
+      <c r="E19" s="1"/>
+    </row>
+    <row r="20" spans="2:5">
+      <c r="B20" s="69">
+        <v>8</v>
+      </c>
+      <c r="C20" s="70" t="s">
+        <v>360</v>
+      </c>
+      <c r="D20" s="69" t="s">
+        <v>361</v>
+      </c>
+      <c r="E20" s="1"/>
+    </row>
+    <row r="23" spans="2:5" ht="23.25">
+      <c r="B23" s="63" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5">
+      <c r="B25" s="64" t="s">
+        <v>337</v>
+      </c>
+      <c r="C25" s="64" t="s">
+        <v>338</v>
+      </c>
+      <c r="D25" s="64" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5">
+      <c r="B26" s="65">
+        <v>1</v>
+      </c>
+      <c r="C26" s="66" t="s">
+        <v>362</v>
+      </c>
+      <c r="D26" s="65" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5">
+      <c r="B27" s="65">
+        <v>2</v>
+      </c>
+      <c r="C27" s="66" t="s">
+        <v>364</v>
+      </c>
+      <c r="D27" s="65" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5">
+      <c r="B28" s="65">
+        <v>3</v>
+      </c>
+      <c r="C28" s="66" t="s">
+        <v>366</v>
+      </c>
+      <c r="D28" s="65" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5">
+      <c r="B29" s="65">
+        <v>4</v>
+      </c>
+      <c r="C29" s="66" t="s">
+        <v>368</v>
+      </c>
+      <c r="D29" s="65" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" ht="23.25">
+      <c r="B32" s="63" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="B34" s="64" t="s">
+        <v>337</v>
+      </c>
+      <c r="C34" s="64" t="s">
+        <v>338</v>
+      </c>
+      <c r="D34" s="64" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" ht="30">
+      <c r="B35" s="65">
+        <v>1</v>
+      </c>
+      <c r="C35" s="66" t="s">
+        <v>370</v>
+      </c>
+      <c r="D35" s="65" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="B36" s="65">
+        <v>2</v>
+      </c>
+      <c r="C36" s="66" t="s">
+        <v>372</v>
+      </c>
+      <c r="D36" s="65" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" ht="30">
+      <c r="B37" s="65">
+        <v>3</v>
+      </c>
+      <c r="C37" s="66" t="s">
+        <v>374</v>
+      </c>
+      <c r="D37" s="65" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4">
+      <c r="B38" s="65">
+        <v>4</v>
+      </c>
+      <c r="C38" s="66" t="s">
+        <v>376</v>
+      </c>
+      <c r="D38" s="65" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" ht="23.25">
+      <c r="B41" s="63" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4">
+      <c r="B43" s="64" t="s">
+        <v>337</v>
+      </c>
+      <c r="C43" s="64" t="s">
+        <v>338</v>
+      </c>
+      <c r="D43" s="64" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" ht="30">
+      <c r="B44" s="65">
+        <v>1</v>
+      </c>
+      <c r="C44" s="66" t="s">
+        <v>378</v>
+      </c>
+      <c r="D44" s="65" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4">
+      <c r="B45" s="65">
+        <v>2</v>
+      </c>
+      <c r="C45" s="66" t="s">
+        <v>380</v>
+      </c>
+      <c r="D45" s="65" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4">
+      <c r="B46" s="65">
+        <v>3</v>
+      </c>
+      <c r="C46" s="67" t="s">
+        <v>382</v>
+      </c>
+      <c r="D46" s="65" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4">
+      <c r="B47" s="65">
+        <v>4</v>
+      </c>
+      <c r="C47" s="67" t="s">
+        <v>384</v>
+      </c>
+      <c r="D47" s="65" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" ht="23.25">
+      <c r="B50" s="63" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4">
+      <c r="B52" s="64" t="s">
+        <v>337</v>
+      </c>
+      <c r="C52" s="64" t="s">
+        <v>338</v>
+      </c>
+      <c r="D52" s="64" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4">
+      <c r="B53" s="65">
+        <v>1</v>
+      </c>
+      <c r="C53" s="66" t="s">
+        <v>386</v>
+      </c>
+      <c r="D53" s="65" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4">
+      <c r="B54" s="65">
+        <v>2</v>
+      </c>
+      <c r="C54" s="66" t="s">
+        <v>388</v>
+      </c>
+      <c r="D54" s="65" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4">
+      <c r="B55" s="65">
+        <v>3</v>
+      </c>
+      <c r="C55" s="66" t="s">
+        <v>390</v>
+      </c>
+      <c r="D55" s="65" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4">
+      <c r="B56" s="65"/>
+    </row>
+    <row r="58" spans="2:4" ht="23.25">
+      <c r="B58" s="63" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="23.25">
-      <c r="B2" s="66" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="B4" s="74" t="s">
+    <row r="60" spans="2:4">
+      <c r="B60" s="64" t="s">
         <v>337</v>
       </c>
-      <c r="C4" s="74" t="s">
+      <c r="C60" s="64" t="s">
         <v>338</v>
       </c>
-      <c r="D4" s="74" t="s">
+      <c r="D60" s="64" t="s">
         <v>339</v>
       </c>
-      <c r="E4" s="75" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="45">
-      <c r="B5" s="72">
+    </row>
+    <row r="61" spans="2:4">
+      <c r="B61" s="65">
         <v>1</v>
       </c>
-      <c r="C5" s="73" t="s">
-        <v>340</v>
-      </c>
-      <c r="D5" s="72" t="s">
-        <v>341</v>
-      </c>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="1:5" ht="30">
-      <c r="B6" s="72">
+      <c r="C61" s="66" t="s">
+        <v>392</v>
+      </c>
+      <c r="D61" s="65" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4" ht="45">
+      <c r="B62" s="65">
         <v>2</v>
       </c>
-      <c r="C6" s="73" t="s">
-        <v>342</v>
-      </c>
-      <c r="D6" s="72" t="s">
-        <v>343</v>
-      </c>
-      <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="1:5" ht="30">
-      <c r="B7" s="72">
+      <c r="C62" s="66" t="s">
+        <v>394</v>
+      </c>
+      <c r="D62" s="65" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4" ht="30">
+      <c r="B63" s="65">
         <v>3</v>
       </c>
-      <c r="C7" s="73" t="s">
-        <v>344</v>
-      </c>
-      <c r="D7" s="72" t="s">
-        <v>345</v>
-      </c>
-      <c r="E7" s="1"/>
-    </row>
-    <row r="10" spans="1:5" ht="23.25">
-      <c r="B10" s="66" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="B12" s="67" t="s">
+      <c r="C63" s="66" t="s">
+        <v>396</v>
+      </c>
+      <c r="D63" s="65" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4">
+      <c r="B64" s="65">
+        <v>4</v>
+      </c>
+      <c r="C64" s="66" t="s">
+        <v>398</v>
+      </c>
+      <c r="D64" s="65" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4">
+      <c r="B65" s="65">
+        <v>5</v>
+      </c>
+      <c r="C65" s="66" t="s">
+        <v>400</v>
+      </c>
+      <c r="D65" s="65" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" ht="23.25">
+      <c r="B68" s="63" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4">
+      <c r="B70" s="64" t="s">
         <v>337</v>
       </c>
-      <c r="C12" s="67" t="s">
-        <v>338</v>
-      </c>
-      <c r="D12" s="67" t="s">
+      <c r="C70" s="64" t="s">
+        <v>403</v>
+      </c>
+      <c r="D70" s="64" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="30">
-      <c r="B13" s="68">
+    <row r="71" spans="2:4">
+      <c r="B71" s="65">
         <v>1</v>
       </c>
-      <c r="C13" s="69" t="s">
-        <v>347</v>
-      </c>
-      <c r="D13" s="68" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="B14" s="68">
+      <c r="C71" s="65" t="s">
+        <v>404</v>
+      </c>
+      <c r="D71" s="65" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4">
+      <c r="B72" s="65">
         <v>2</v>
       </c>
-      <c r="C14" s="69" t="s">
-        <v>349</v>
-      </c>
-      <c r="D14" s="68" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="B15" s="68">
+      <c r="C72" s="65" t="s">
+        <v>406</v>
+      </c>
+      <c r="D72" s="65" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4">
+      <c r="B73" s="65">
         <v>3</v>
       </c>
-      <c r="C15" s="69" t="s">
-        <v>351</v>
-      </c>
-      <c r="D15" s="68" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="B16" s="68">
+      <c r="C73" s="65" t="s">
+        <v>408</v>
+      </c>
+      <c r="D73" s="65" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4">
+      <c r="B74" s="65">
         <v>4</v>
       </c>
-      <c r="C16" s="69" t="s">
-        <v>353</v>
-      </c>
-      <c r="D16" s="68" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4">
-      <c r="B17" s="68">
+      <c r="C74" s="65" t="s">
+        <v>410</v>
+      </c>
+      <c r="D74" s="65" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4">
+      <c r="B75" s="65">
         <v>5</v>
       </c>
-      <c r="C17" s="69" t="s">
-        <v>355</v>
-      </c>
-      <c r="D17" s="68" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4">
-      <c r="B18" s="68">
+      <c r="C75" s="65" t="s">
+        <v>412</v>
+      </c>
+      <c r="D75" s="65" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4">
+      <c r="B76" s="65">
         <v>6</v>
       </c>
-      <c r="C18" s="69" t="s">
-        <v>357</v>
-      </c>
-      <c r="D18" s="68" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4">
-      <c r="B19" s="68">
-        <v>7</v>
-      </c>
-      <c r="C19" s="69" t="s">
-        <v>359</v>
-      </c>
-      <c r="D19" s="68" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4">
-      <c r="B20" s="68">
-        <v>8</v>
-      </c>
-      <c r="C20" s="69" t="s">
-        <v>361</v>
-      </c>
-      <c r="D20" s="68" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" ht="23.25">
-      <c r="B23" s="66" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4">
-      <c r="B25" s="67" t="s">
-        <v>337</v>
-      </c>
-      <c r="C25" s="67" t="s">
-        <v>338</v>
-      </c>
-      <c r="D25" s="67" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4">
-      <c r="B26" s="68">
-        <v>1</v>
-      </c>
-      <c r="C26" s="69" t="s">
-        <v>363</v>
-      </c>
-      <c r="D26" s="68" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4">
-      <c r="B27" s="68">
-        <v>2</v>
-      </c>
-      <c r="C27" s="69" t="s">
-        <v>365</v>
-      </c>
-      <c r="D27" s="68" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4">
-      <c r="B28" s="68">
-        <v>3</v>
-      </c>
-      <c r="C28" s="69" t="s">
-        <v>367</v>
-      </c>
-      <c r="D28" s="68" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4">
-      <c r="B29" s="68">
-        <v>4</v>
-      </c>
-      <c r="C29" s="69" t="s">
-        <v>369</v>
-      </c>
-      <c r="D29" s="68" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" ht="23.25">
-      <c r="B32" s="66" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4">
-      <c r="B34" s="67" t="s">
-        <v>337</v>
-      </c>
-      <c r="C34" s="67" t="s">
-        <v>338</v>
-      </c>
-      <c r="D34" s="67" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" ht="30">
-      <c r="B35" s="68">
-        <v>1</v>
-      </c>
-      <c r="C35" s="69" t="s">
-        <v>371</v>
-      </c>
-      <c r="D35" s="68" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4">
-      <c r="B36" s="68">
-        <v>2</v>
-      </c>
-      <c r="C36" s="69" t="s">
-        <v>373</v>
-      </c>
-      <c r="D36" s="68" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4" ht="30">
-      <c r="B37" s="68">
-        <v>3</v>
-      </c>
-      <c r="C37" s="69" t="s">
-        <v>375</v>
-      </c>
-      <c r="D37" s="68" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4">
-      <c r="B38" s="68">
-        <v>4</v>
-      </c>
-      <c r="C38" s="69" t="s">
-        <v>377</v>
-      </c>
-      <c r="D38" s="68" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4" ht="23.25">
-      <c r="B41" s="66" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4">
-      <c r="B43" s="67" t="s">
-        <v>337</v>
-      </c>
-      <c r="C43" s="67" t="s">
-        <v>338</v>
-      </c>
-      <c r="D43" s="67" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4" ht="30">
-      <c r="B44" s="68">
-        <v>1</v>
-      </c>
-      <c r="C44" s="69" t="s">
-        <v>379</v>
-      </c>
-      <c r="D44" s="68" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4">
-      <c r="B45" s="68">
-        <v>2</v>
-      </c>
-      <c r="C45" s="69" t="s">
-        <v>381</v>
-      </c>
-      <c r="D45" s="68" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="46" spans="2:4">
-      <c r="B46" s="68">
-        <v>3</v>
-      </c>
-      <c r="C46" s="70" t="s">
-        <v>383</v>
-      </c>
-      <c r="D46" s="68" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="47" spans="2:4">
-      <c r="B47" s="68">
-        <v>4</v>
-      </c>
-      <c r="C47" s="70" t="s">
-        <v>385</v>
-      </c>
-      <c r="D47" s="68" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="50" spans="2:4" ht="23.25">
-      <c r="B50" s="66" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="52" spans="2:4">
-      <c r="B52" s="67" t="s">
-        <v>337</v>
-      </c>
-      <c r="C52" s="67" t="s">
-        <v>338</v>
-      </c>
-      <c r="D52" s="67" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="53" spans="2:4">
-      <c r="B53" s="68">
-        <v>1</v>
-      </c>
-      <c r="C53" s="69" t="s">
-        <v>387</v>
-      </c>
-      <c r="D53" s="68" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="54" spans="2:4">
-      <c r="B54" s="68">
-        <v>2</v>
-      </c>
-      <c r="C54" s="69" t="s">
-        <v>389</v>
-      </c>
-      <c r="D54" s="68" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="55" spans="2:4">
-      <c r="B55" s="68">
-        <v>3</v>
-      </c>
-      <c r="C55" s="69" t="s">
-        <v>391</v>
-      </c>
-      <c r="D55" s="68" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="56" spans="2:4">
-      <c r="B56" s="68"/>
-    </row>
-    <row r="58" spans="2:4" ht="23.25">
-      <c r="B58" s="66" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="60" spans="2:4">
-      <c r="B60" s="67" t="s">
-        <v>337</v>
-      </c>
-      <c r="C60" s="67" t="s">
-        <v>338</v>
-      </c>
-      <c r="D60" s="67" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="61" spans="2:4">
-      <c r="B61" s="68">
-        <v>1</v>
-      </c>
-      <c r="C61" s="69" t="s">
-        <v>393</v>
-      </c>
-      <c r="D61" s="68" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="62" spans="2:4" ht="45">
-      <c r="B62" s="68">
-        <v>2</v>
-      </c>
-      <c r="C62" s="69" t="s">
-        <v>395</v>
-      </c>
-      <c r="D62" s="68" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="63" spans="2:4" ht="30">
-      <c r="B63" s="68">
-        <v>3</v>
-      </c>
-      <c r="C63" s="69" t="s">
-        <v>397</v>
-      </c>
-      <c r="D63" s="68" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="64" spans="2:4">
-      <c r="B64" s="68">
-        <v>4</v>
-      </c>
-      <c r="C64" s="69" t="s">
-        <v>399</v>
-      </c>
-      <c r="D64" s="68" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="65" spans="2:4">
-      <c r="B65" s="68">
-        <v>5</v>
-      </c>
-      <c r="C65" s="69" t="s">
-        <v>401</v>
-      </c>
-      <c r="D65" s="68" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="68" spans="2:4" ht="23.25">
-      <c r="B68" s="66" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="70" spans="2:4">
-      <c r="B70" s="67" t="s">
-        <v>337</v>
-      </c>
-      <c r="C70" s="67" t="s">
-        <v>404</v>
-      </c>
-      <c r="D70" s="67" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="71" spans="2:4">
-      <c r="B71" s="68">
-        <v>1</v>
-      </c>
-      <c r="C71" s="68" t="s">
-        <v>405</v>
-      </c>
-      <c r="D71" s="68" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="72" spans="2:4">
-      <c r="B72" s="68">
-        <v>2</v>
-      </c>
-      <c r="C72" s="68" t="s">
-        <v>407</v>
-      </c>
-      <c r="D72" s="68" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="73" spans="2:4">
-      <c r="B73" s="68">
-        <v>3</v>
-      </c>
-      <c r="C73" s="68" t="s">
-        <v>409</v>
-      </c>
-      <c r="D73" s="68" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="74" spans="2:4">
-      <c r="B74" s="68">
-        <v>4</v>
-      </c>
-      <c r="C74" s="68" t="s">
-        <v>411</v>
-      </c>
-      <c r="D74" s="68" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="75" spans="2:4">
-      <c r="B75" s="68">
-        <v>5</v>
-      </c>
-      <c r="C75" s="68" t="s">
-        <v>413</v>
-      </c>
-      <c r="D75" s="68" t="s">
+      <c r="C76" s="65" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="76" spans="2:4">
-      <c r="B76" s="68">
-        <v>6</v>
-      </c>
-      <c r="C76" s="68" t="s">
+      <c r="D76" s="65" t="s">
         <v>415</v>
       </c>
-      <c r="D76" s="68" t="s">
-        <v>416</v>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="D2:G5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="4" max="9" width="36" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="4:7">
+      <c r="D2" s="64" t="s">
+        <v>431</v>
+      </c>
+      <c r="E2" s="64" t="s">
+        <v>432</v>
+      </c>
+      <c r="F2" s="64" t="s">
+        <v>433</v>
+      </c>
+      <c r="G2" s="64" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="3" spans="4:7" ht="30">
+      <c r="D3" s="66" t="s">
+        <v>435</v>
+      </c>
+      <c r="E3" s="79" t="s">
+        <v>436</v>
+      </c>
+      <c r="F3" s="79" t="s">
+        <v>437</v>
+      </c>
+      <c r="G3" s="65" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="4" spans="4:7" ht="30">
+      <c r="D4" s="66" t="s">
+        <v>439</v>
+      </c>
+      <c r="E4" s="79" t="s">
+        <v>440</v>
+      </c>
+      <c r="F4" s="79" t="s">
+        <v>441</v>
+      </c>
+      <c r="G4" s="65" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="5" spans="4:7" ht="30">
+      <c r="D5" s="66" t="s">
+        <v>443</v>
+      </c>
+      <c r="E5" s="79" t="s">
+        <v>444</v>
+      </c>
+      <c r="F5" s="79" t="s">
+        <v>445</v>
+      </c>
+      <c r="G5" s="65" t="s">
+        <v>446</v>
       </c>
     </row>
   </sheetData>
@@ -10512,7 +11171,7 @@
       <c r="B47" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="C47" s="60" t="s">
+      <c r="C47" s="57" t="s">
         <v>303</v>
       </c>
       <c r="D47" s="42">
@@ -10527,7 +11186,7 @@
       <c r="B48" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="C48" s="59" t="s">
+      <c r="C48" s="56" t="s">
         <v>302</v>
       </c>
       <c r="D48" s="42">
@@ -10956,7 +11615,7 @@
       <c r="D12" s="11"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" thickBot="1">
-      <c r="C13" s="56" t="s">
+      <c r="C13" s="75" t="s">
         <v>78</v>
       </c>
       <c r="D13" s="26" t="s">
@@ -10973,7 +11632,7 @@
       <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:10" ht="15.75" thickBot="1">
-      <c r="C14" s="57"/>
+      <c r="C14" s="76"/>
       <c r="D14" s="23" t="s">
         <v>65</v>
       </c>
@@ -10989,7 +11648,7 @@
       <c r="J14" s="25"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="C15" s="57"/>
+      <c r="C15" s="76"/>
       <c r="D15" s="26" t="s">
         <v>66</v>
       </c>
@@ -11004,7 +11663,7 @@
       <c r="I15" s="28"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="C16" s="57"/>
+      <c r="C16" s="76"/>
       <c r="D16" s="29"/>
       <c r="E16" s="30" t="s">
         <v>74</v>
@@ -11015,7 +11674,7 @@
       <c r="I16" s="31"/>
     </row>
     <row r="17" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C17" s="58"/>
+      <c r="C17" s="77"/>
       <c r="D17" s="32"/>
       <c r="E17" s="33" t="s">
         <v>75</v>
@@ -11046,7 +11705,7 @@
       <c r="L18" s="25"/>
     </row>
     <row r="19" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C19" s="56" t="s">
+      <c r="C19" s="75" t="s">
         <v>78</v>
       </c>
       <c r="D19" s="23" t="s">
@@ -11057,7 +11716,7 @@
       </c>
     </row>
     <row r="20" spans="3:12">
-      <c r="C20" s="57"/>
+      <c r="C20" s="76"/>
       <c r="D20" s="26" t="s">
         <v>82</v>
       </c>
@@ -11066,7 +11725,7 @@
       </c>
     </row>
     <row r="21" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C21" s="58"/>
+      <c r="C21" s="77"/>
       <c r="D21" s="32"/>
       <c r="E21" s="40" t="s">
         <v>84</v>

--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -18,7 +18,6 @@
     <sheet name="#6" sheetId="9" r:id="rId9"/>
     <sheet name="#7" sheetId="10" r:id="rId10"/>
     <sheet name="#8" sheetId="11" r:id="rId11"/>
-    <sheet name="Sheet1" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="437">
   <si>
     <t>No.</t>
   </si>
@@ -2865,152 +2864,6 @@
     </r>
   </si>
   <si>
-    <t>Kiểu</t>
-  </si>
-  <si>
-    <t>Cách tạo trong CMake</t>
-  </si>
-  <si>
-    <t>File sinh ra</t>
-  </si>
-  <si>
-    <t>Khi nào dùng</t>
-  </si>
-  <si>
-    <t>Static library</t>
-  </si>
-  <si>
-    <t>add_library(mylib STATIC src/mylib.cpp)</t>
-  </si>
-  <si>
-    <r>
-      <t>.a</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (Linux/macOS), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>.lib</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (Windows)</t>
-    </r>
-  </si>
-  <si>
-    <t>Khi muốn nhúng code thư viện vào chương trình (compile-time)</t>
-  </si>
-  <si>
-    <t>Shared/Dynamic library</t>
-  </si>
-  <si>
-    <t>add_library(mylib SHARED src/mylib.cpp)</t>
-  </si>
-  <si>
-    <r>
-      <t>.so</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (Linux), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>.dll</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (Windows), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>.dylib</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (macOS)</t>
-    </r>
-  </si>
-  <si>
-    <t>Khi muốn chia sẻ thư viện (runtime load)</t>
-  </si>
-  <si>
-    <t>Object library</t>
-  </si>
-  <si>
-    <t>add_library(mylib OBJECT src/mylib.cpp)</t>
-  </si>
-  <si>
-    <r>
-      <t>.obj</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> hoặc </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>.o</t>
-    </r>
-  </si>
-  <si>
-    <t>Khi cần tái sử dụng đối tượng biên dịch trước khi link</t>
-  </si>
-  <si>
     <t>Tạo thư viện tĩnh (.a / .lib) hoặc động (.so / .dll) hoặc thư viện mở ( .o / .obj)</t>
   </si>
   <si>
@@ -3337,6 +3190,447 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> : liên kết kiểu interface, target không thể sử dụng được define, nhưng các thư viện link tới target thì dùng được define của thư viện được link</t>
+    </r>
+  </si>
+  <si>
+    <t>Atomic</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lệnh include đường dẫn của file ".h" vào execution. Cấu trúc : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">target_include_directories(&lt;target&gt; &lt;INTERFACE|PUBLIC|PRIVATE&gt; [path...])
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>VD :</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>target_include_directories(MyApp</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> PRIVATE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> include)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Chỉ target MyApp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> thấy được include
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">target_include_directories(MyApp </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PUBLIC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> include)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> :</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> MyApp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tất cả target link</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> đến MyApp đều thấy include
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">target_include_directories(MyApp </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>INTERFACE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> include)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : MyApp không thấy được mà chỉ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tất cả target link</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> đến MyApp thấy include</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lệnh </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>set()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> là công cụ chính để tạo và gán giá trị cho các biến. Cấu trúc :
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>set(&lt;tên_biến&gt; &lt;giá_trị&gt;)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> . Sau đó sử dụng cú pháp sau để gọi biến : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${...}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> . VD : 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">set(MY_NAME "HoangAnh") </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">sau đó có thể gọi message : message("My name is: ${MY_NAME}")
+VD#2 :
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>set(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SOURCES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> main.cpp rc/app.cpp src/utils.cpp) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">sau đó có thể add rất gọn : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>add_executable(MyApp ${</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SOURCES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>})</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> thay vì phải dùng lệnh rất dài như sau : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>add_executable(MyApp main.cpp rc/app.cpp src/utils.cpp)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
     </r>
   </si>
 </sst>
@@ -3733,7 +4027,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -3879,6 +4173,9 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3887,12 +4184,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -8800,7 +9091,7 @@
       <c r="D16" s="69" t="s">
         <v>354</v>
       </c>
-      <c r="E16" s="78" t="s">
+      <c r="E16" s="75" t="s">
         <v>430</v>
       </c>
     </row>
@@ -8812,10 +9103,10 @@
         <v>355</v>
       </c>
       <c r="D17" s="69" t="s">
-        <v>447</v>
-      </c>
-      <c r="E17" s="78" t="s">
-        <v>448</v>
+        <v>431</v>
+      </c>
+      <c r="E17" s="75" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="180">
@@ -8828,11 +9119,11 @@
       <c r="D18" s="69" t="s">
         <v>357</v>
       </c>
-      <c r="E18" s="78" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5">
+      <c r="E18" s="75" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="135">
       <c r="B19" s="69">
         <v>7</v>
       </c>
@@ -8842,9 +9133,11 @@
       <c r="D19" s="69" t="s">
         <v>359</v>
       </c>
-      <c r="E19" s="1"/>
-    </row>
-    <row r="20" spans="2:5">
+      <c r="E19" s="75" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" ht="135">
       <c r="B20" s="69">
         <v>8</v>
       </c>
@@ -8854,7 +9147,9 @@
       <c r="D20" s="69" t="s">
         <v>361</v>
       </c>
-      <c r="E20" s="1"/>
+      <c r="E20" s="75" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="23" spans="2:5" ht="23.25">
       <c r="B23" s="63" t="s">
@@ -8862,59 +9157,66 @@
       </c>
     </row>
     <row r="25" spans="2:5">
-      <c r="B25" s="64" t="s">
+      <c r="B25" s="73" t="s">
         <v>337</v>
       </c>
-      <c r="C25" s="64" t="s">
+      <c r="C25" s="73" t="s">
         <v>338</v>
       </c>
-      <c r="D25" s="64" t="s">
+      <c r="D25" s="73" t="s">
         <v>339</v>
       </c>
+      <c r="E25" s="74" t="s">
+        <v>423</v>
+      </c>
     </row>
     <row r="26" spans="2:5">
-      <c r="B26" s="65">
+      <c r="B26" s="69">
         <v>1</v>
       </c>
-      <c r="C26" s="66" t="s">
+      <c r="C26" s="70" t="s">
         <v>362</v>
       </c>
-      <c r="D26" s="65" t="s">
+      <c r="D26" s="69" t="s">
         <v>363</v>
       </c>
+      <c r="E26" s="1"/>
     </row>
     <row r="27" spans="2:5">
-      <c r="B27" s="65">
+      <c r="B27" s="69">
         <v>2</v>
       </c>
-      <c r="C27" s="66" t="s">
+      <c r="C27" s="70" t="s">
         <v>364</v>
       </c>
-      <c r="D27" s="65" t="s">
+      <c r="D27" s="69" t="s">
         <v>365</v>
       </c>
+      <c r="E27" s="1"/>
     </row>
     <row r="28" spans="2:5">
-      <c r="B28" s="65">
+      <c r="B28" s="69">
         <v>3</v>
       </c>
-      <c r="C28" s="66" t="s">
+      <c r="C28" s="70" t="s">
         <v>366</v>
       </c>
-      <c r="D28" s="65" t="s">
+      <c r="D28" s="69" t="s">
         <v>367</v>
       </c>
+      <c r="E28" s="1"/>
     </row>
     <row r="29" spans="2:5">
-      <c r="B29" s="65">
+      <c r="B29" s="69">
         <v>4</v>
       </c>
-      <c r="C29" s="66" t="s">
+      <c r="C29" s="70" t="s">
         <v>368</v>
       </c>
-      <c r="D29" s="65" t="s">
+      <c r="D29" s="69" t="s">
         <v>369</v>
       </c>
+      <c r="E29" s="1"/>
     </row>
     <row r="32" spans="2:5" ht="23.25">
       <c r="B32" s="63" t="s">
@@ -9244,75 +9546,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="D2:G5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="4" max="9" width="36" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="4:7">
-      <c r="D2" s="64" t="s">
-        <v>431</v>
-      </c>
-      <c r="E2" s="64" t="s">
-        <v>432</v>
-      </c>
-      <c r="F2" s="64" t="s">
-        <v>433</v>
-      </c>
-      <c r="G2" s="64" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="3" spans="4:7" ht="30">
-      <c r="D3" s="66" t="s">
-        <v>435</v>
-      </c>
-      <c r="E3" s="79" t="s">
-        <v>436</v>
-      </c>
-      <c r="F3" s="79" t="s">
-        <v>437</v>
-      </c>
-      <c r="G3" s="65" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="4" spans="4:7" ht="30">
-      <c r="D4" s="66" t="s">
-        <v>439</v>
-      </c>
-      <c r="E4" s="79" t="s">
-        <v>440</v>
-      </c>
-      <c r="F4" s="79" t="s">
-        <v>441</v>
-      </c>
-      <c r="G4" s="65" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="5" spans="4:7" ht="30">
-      <c r="D5" s="66" t="s">
-        <v>443</v>
-      </c>
-      <c r="E5" s="79" t="s">
-        <v>444</v>
-      </c>
-      <c r="F5" s="79" t="s">
-        <v>445</v>
-      </c>
-      <c r="G5" s="65" t="s">
-        <v>446</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -10469,7 +10702,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:G53"/>
+  <dimension ref="B1:G54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="50.140625" bestFit="1" customWidth="1"/>
@@ -11242,15 +11475,24 @@
       <c r="F52" s="6"/>
     </row>
     <row r="53" spans="2:6">
-      <c r="B53" s="5" t="s">
-        <v>324</v>
-      </c>
+      <c r="B53" s="5"/>
       <c r="C53" s="6" t="s">
-        <v>325</v>
+        <v>434</v>
       </c>
       <c r="D53" s="6"/>
       <c r="E53" s="6"/>
       <c r="F53" s="6"/>
+    </row>
+    <row r="54" spans="2:6">
+      <c r="B54" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -11615,7 +11857,7 @@
       <c r="D12" s="11"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" thickBot="1">
-      <c r="C13" s="75" t="s">
+      <c r="C13" s="76" t="s">
         <v>78</v>
       </c>
       <c r="D13" s="26" t="s">
@@ -11632,7 +11874,7 @@
       <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:10" ht="15.75" thickBot="1">
-      <c r="C14" s="76"/>
+      <c r="C14" s="77"/>
       <c r="D14" s="23" t="s">
         <v>65</v>
       </c>
@@ -11648,7 +11890,7 @@
       <c r="J14" s="25"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="C15" s="76"/>
+      <c r="C15" s="77"/>
       <c r="D15" s="26" t="s">
         <v>66</v>
       </c>
@@ -11663,7 +11905,7 @@
       <c r="I15" s="28"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="C16" s="76"/>
+      <c r="C16" s="77"/>
       <c r="D16" s="29"/>
       <c r="E16" s="30" t="s">
         <v>74</v>
@@ -11674,7 +11916,7 @@
       <c r="I16" s="31"/>
     </row>
     <row r="17" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C17" s="77"/>
+      <c r="C17" s="78"/>
       <c r="D17" s="32"/>
       <c r="E17" s="33" t="s">
         <v>75</v>
@@ -11705,7 +11947,7 @@
       <c r="L18" s="25"/>
     </row>
     <row r="19" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C19" s="75" t="s">
+      <c r="C19" s="76" t="s">
         <v>78</v>
       </c>
       <c r="D19" s="23" t="s">
@@ -11716,7 +11958,7 @@
       </c>
     </row>
     <row r="20" spans="3:12">
-      <c r="C20" s="76"/>
+      <c r="C20" s="77"/>
       <c r="D20" s="26" t="s">
         <v>82</v>
       </c>
@@ -11725,7 +11967,7 @@
       </c>
     </row>
     <row r="21" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C21" s="77"/>
+      <c r="C21" s="78"/>
       <c r="D21" s="32"/>
       <c r="E21" s="40" t="s">
         <v>84</v>

--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="10"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Knowhow" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="#6" sheetId="9" r:id="rId9"/>
     <sheet name="#7" sheetId="10" r:id="rId10"/>
     <sheet name="#8" sheetId="11" r:id="rId11"/>
+    <sheet name="#14" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="503">
   <si>
     <t>No.</t>
   </si>
@@ -1640,9 +1641,6 @@
   </si>
   <si>
     <t>Gmock</t>
-  </si>
-  <si>
-    <t>Các Segment trong C++</t>
   </si>
   <si>
     <t>#8</t>
@@ -3632,6 +3630,276 @@
       <t xml:space="preserve">
 </t>
     </r>
+  </si>
+  <si>
+    <t>#14</t>
+  </si>
+  <si>
+    <t>Các thuật toán sort phổ biến trong C++. Triển khai minh họa.</t>
+  </si>
+  <si>
+    <t>https://chatgpt.com/share/690b291c-d088-8002-b37a-10bb5da410ce</t>
+  </si>
+  <si>
+    <t>What is the difference between ++i and i++</t>
+  </si>
+  <si>
+    <t>Các Segment trong C++ ( Data Segment)</t>
+  </si>
+  <si>
+    <t>RAII là gì (Resource Acquisition Is Initialization)</t>
+  </si>
+  <si>
+    <t>Điều gì xảy ra khi double delete, cách phòng tránh ?</t>
+  </si>
+  <si>
+    <t>Cách phòng tránh</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Khi delete 1 con trỏ, nó trở thành </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dangling pointer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Nếu delete 1 con trỏ 2 lần , sẽ xảy ra hiện tượng "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Undefined Behavior</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">" vì </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hệ thống quản lý bộ nhớ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> không cho phép giải phóng 1 con trỏ đã giải phóng rồi</t>
+    </r>
+  </si>
+  <si>
+    <t>Cấp phát động trong C và C++</t>
+  </si>
+  <si>
+    <t>Cách 1</t>
+  </si>
+  <si>
+    <t>Cách 2</t>
+  </si>
+  <si>
+    <t>Sau khi delete con trỏ, set nó về nullptr, vì xóa nullptr là hợp lệ</t>
+  </si>
+  <si>
+    <t>Sử dụng unique pointer</t>
+  </si>
+  <si>
+    <t>* Rất khó để phát hiện 1 biến con trỏ có đang là dangling pointer không, vì vậy, hãy chủ động phòng tránh bằng cách set nullptr hoặc dùng unique ptr luôn</t>
+  </si>
+  <si>
+    <t>#15</t>
+  </si>
+  <si>
+    <t>#16</t>
+  </si>
+  <si>
+    <t>Ôn lại OOP</t>
+  </si>
+  <si>
+    <t>Sự khác biệt giữa virtual, pure virtual và override</t>
+  </si>
+  <si>
+    <t>What happens if a base class destructor is not virtual?</t>
+  </si>
+  <si>
+    <t>Can constructors be virtual?</t>
+  </si>
+  <si>
+    <t>What is slicing in C++?</t>
+  </si>
+  <si>
+    <t>#17</t>
+  </si>
+  <si>
+    <t>C++ hiện đại</t>
+  </si>
+  <si>
+    <t>Phân biệt rvalue và lvalue ? What are rvalue references (&amp;&amp;) used for?</t>
+  </si>
+  <si>
+    <t>What is the difference between emplace_back() and push_back()?</t>
+  </si>
+  <si>
+    <t>What is a lambda function in C++?</t>
+  </si>
+  <si>
+    <t>#18</t>
+  </si>
+  <si>
+    <t>Containers (vector, list, map, set, queue, stack, …)</t>
+  </si>
+  <si>
+    <t>Algorithms (sort(), find(), count(), max_element(), …)</t>
+  </si>
+  <si>
+    <t>STL (Standard Template Library) &amp; Algorithms</t>
+  </si>
+  <si>
+    <t>Khác biệt giữa compile-time polymorphism ( đa hình lúc biên dịch) và runtime polymorphism ( đa hình lúc chạy).</t>
+  </si>
+  <si>
+    <t>Over loading, Over riding</t>
+  </si>
+  <si>
+    <t>#19</t>
+  </si>
+  <si>
+    <t>Làm thế nào để tránh Memory leak ( và các tool tránh)</t>
+  </si>
+  <si>
+    <t>https://chatgpt.com/share/690b28bd-0994-8002-8476-6d34821ba602</t>
+  </si>
+  <si>
+    <t>#20</t>
+  </si>
+  <si>
+    <t>#21</t>
+  </si>
+  <si>
+    <t>#23</t>
+  </si>
+  <si>
+    <t>https://chatgpt.com/share/690b2878-1980-8002-a972-852d53b05b6d</t>
+  </si>
+  <si>
+    <t>#24</t>
+  </si>
+  <si>
+    <t>Design Pattern phổ biến</t>
+  </si>
+  <si>
+    <t>What is the purpose of std::move()?, Move constructor và move assignment operation ? move semantics ? perfect forwarding ?</t>
+  </si>
+  <si>
+    <t>Khi bạn phải xử lý bug khó tái hiện (intermittent bug) trong hệ thống multi-threaded, bạn sẽ làm gì?</t>
+  </si>
+  <si>
+    <t>https://chatgpt.com/share/690b2849-8930-8002-8e74-c83657de06f5</t>
+  </si>
+  <si>
+    <t>Xem thêm</t>
+  </si>
+  <si>
+    <t>#n</t>
+  </si>
+  <si>
+    <t>Access modifiers : Private, Public, Protected</t>
+  </si>
+  <si>
+    <t>#25</t>
+  </si>
+  <si>
+    <t>Module mày làm gì (CSRC, OpenAPI) ? Đóng vai trò thế nào trong dự án, triển khai theo mô hình nào ?</t>
+  </si>
+  <si>
+    <t>#26</t>
+  </si>
+  <si>
+    <t>Struct vs Union</t>
+  </si>
+  <si>
+    <t>Function pointer</t>
+  </si>
+  <si>
+    <t>Quản lý memory như nào cho hiệu quả</t>
+  </si>
+  <si>
+    <t>Khác nhau giữa C và C++, Data alignment and padding of struct/class in cpp</t>
+  </si>
+  <si>
+    <t>-dangerous of using gets()
+- char src[] = ""Sample Test"";
+char dst[10];
+strcpy(dst, src)</t>
+  </si>
+  <si>
+    <t>File anh Thư</t>
+  </si>
+  <si>
+    <t>What is a template in C++? 
+- class template khác class thường ntn khi compile</t>
+  </si>
+  <si>
+    <t>How do vectors differ from arrays in C++?</t>
+  </si>
+  <si>
+    <t>Unordered_map, map, set, priority_queue, list, …</t>
+  </si>
+  <si>
+    <t>How to loop through map, vector</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Casting in cpp
+- static_cast
+- dynamic_cast
+- reinterpret_cast</t>
+  </si>
+  <si>
+    <t>#27</t>
+  </si>
+  <si>
+    <t>#28</t>
+  </si>
+  <si>
+    <t>#29</t>
+  </si>
+  <si>
+    <t>#30</t>
+  </si>
+  <si>
+    <t>#31</t>
   </si>
 </sst>
 </file>
@@ -4027,7 +4295,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -4176,6 +4444,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4184,6 +4456,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -8621,17 +8899,17 @@
   <sheetData>
     <row r="2" spans="2:17">
       <c r="B2" s="57" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3" spans="2:17">
       <c r="C3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="2:17">
       <c r="C4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" spans="2:17">
@@ -8639,12 +8917,12 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" spans="2:17">
       <c r="D6" s="58" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E6" s="59"/>
       <c r="F6" s="59"/>
@@ -8654,7 +8932,7 @@
       <c r="J6" s="59"/>
       <c r="K6" s="60"/>
       <c r="L6" s="61" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="M6" s="44"/>
       <c r="N6" s="44"/>
@@ -8665,7 +8943,7 @@
     <row r="7" spans="2:17">
       <c r="D7" s="59"/>
       <c r="E7" s="59" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F7" s="59"/>
       <c r="G7" s="59"/>
@@ -8675,7 +8953,7 @@
       <c r="K7" s="60"/>
       <c r="L7" s="44"/>
       <c r="M7" s="44" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="N7" s="44"/>
       <c r="O7" s="44"/>
@@ -8685,7 +8963,7 @@
     <row r="8" spans="2:17">
       <c r="D8" s="59"/>
       <c r="E8" s="59" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F8" s="59"/>
       <c r="G8" s="59"/>
@@ -8695,7 +8973,7 @@
       <c r="K8" s="60"/>
       <c r="L8" s="44"/>
       <c r="M8" s="44" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="N8" s="44"/>
       <c r="O8" s="44"/>
@@ -8741,7 +9019,7 @@
     <row r="11" spans="2:17">
       <c r="D11" s="59"/>
       <c r="E11" s="59" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F11" s="59"/>
       <c r="G11" s="59"/>
@@ -8751,7 +9029,7 @@
       <c r="K11" s="60"/>
       <c r="L11" s="44"/>
       <c r="M11" s="44" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="N11" s="44"/>
       <c r="O11" s="44"/>
@@ -8761,7 +9039,7 @@
     <row r="12" spans="2:17">
       <c r="D12" s="59"/>
       <c r="E12" s="59" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F12" s="59"/>
       <c r="G12" s="59"/>
@@ -8771,7 +9049,7 @@
       <c r="K12" s="60"/>
       <c r="L12" s="44"/>
       <c r="M12" s="44" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="N12" s="44"/>
       <c r="O12" s="44"/>
@@ -8781,7 +9059,7 @@
     <row r="13" spans="2:17">
       <c r="D13" s="59"/>
       <c r="E13" s="59" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F13" s="59"/>
       <c r="G13" s="59"/>
@@ -8791,7 +9069,7 @@
       <c r="K13" s="60"/>
       <c r="L13" s="44"/>
       <c r="M13" s="44" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="N13" s="44"/>
       <c r="O13" s="44"/>
@@ -8801,7 +9079,7 @@
     <row r="14" spans="2:17">
       <c r="D14" s="59"/>
       <c r="E14" s="59" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F14" s="59"/>
       <c r="G14" s="59"/>
@@ -8811,7 +9089,7 @@
       <c r="K14" s="60"/>
       <c r="L14" s="44"/>
       <c r="M14" s="44" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N14" s="44"/>
       <c r="O14" s="44"/>
@@ -8831,7 +9109,7 @@
       <c r="K15" s="60"/>
       <c r="L15" s="44"/>
       <c r="M15" s="44" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="N15" s="44"/>
       <c r="O15" s="44"/>
@@ -8861,12 +9139,12 @@
         <v>2</v>
       </c>
       <c r="D18" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="19" spans="3:8">
       <c r="E19" s="62" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F19" s="62"/>
       <c r="G19" s="62"/>
@@ -8874,7 +9152,7 @@
     </row>
     <row r="20" spans="3:8">
       <c r="E20" s="62" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F20" s="62"/>
       <c r="G20" s="62"/>
@@ -8882,7 +9160,7 @@
     </row>
     <row r="21" spans="3:8">
       <c r="E21" s="62" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F21" s="62"/>
       <c r="G21" s="62"/>
@@ -8906,28 +9184,28 @@
     </row>
     <row r="25" spans="3:8">
       <c r="D25" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="26" spans="3:8">
       <c r="D26" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="27" spans="3:8">
       <c r="E27" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F27" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="28" spans="3:8">
       <c r="E28" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F28" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="30" spans="3:8">
@@ -8935,7 +9213,7 @@
         <v>3</v>
       </c>
       <c r="D30" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -8956,26 +9234,26 @@
   <sheetData>
     <row r="1" spans="1:5" ht="28.5">
       <c r="A1" s="68" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="23.25">
       <c r="B2" s="63" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="B4" s="71" t="s">
+        <v>336</v>
+      </c>
+      <c r="C4" s="71" t="s">
         <v>337</v>
       </c>
-      <c r="C4" s="71" t="s">
+      <c r="D4" s="71" t="s">
         <v>338</v>
       </c>
-      <c r="D4" s="71" t="s">
-        <v>339</v>
-      </c>
       <c r="E4" s="72" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="45">
@@ -8983,13 +9261,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="70" t="s">
+        <v>339</v>
+      </c>
+      <c r="D5" s="69" t="s">
         <v>340</v>
       </c>
-      <c r="D5" s="69" t="s">
-        <v>341</v>
-      </c>
       <c r="E5" s="69" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="81" customHeight="1">
@@ -8997,13 +9275,13 @@
         <v>2</v>
       </c>
       <c r="C6" s="70" t="s">
+        <v>341</v>
+      </c>
+      <c r="D6" s="69" t="s">
         <v>342</v>
       </c>
-      <c r="D6" s="69" t="s">
-        <v>343</v>
-      </c>
       <c r="E6" s="69" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="30">
@@ -9011,32 +9289,32 @@
         <v>3</v>
       </c>
       <c r="C7" s="70" t="s">
+        <v>343</v>
+      </c>
+      <c r="D7" s="69" t="s">
         <v>344</v>
       </c>
-      <c r="D7" s="69" t="s">
-        <v>345</v>
-      </c>
       <c r="E7" s="5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="23.25">
       <c r="B10" s="63" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="B12" s="73" t="s">
+        <v>336</v>
+      </c>
+      <c r="C12" s="73" t="s">
         <v>337</v>
       </c>
-      <c r="C12" s="73" t="s">
+      <c r="D12" s="73" t="s">
         <v>338</v>
       </c>
-      <c r="D12" s="73" t="s">
-        <v>339</v>
-      </c>
       <c r="E12" s="74" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="30">
@@ -9044,13 +9322,13 @@
         <v>1</v>
       </c>
       <c r="C13" s="70" t="s">
+        <v>346</v>
+      </c>
+      <c r="D13" s="69" t="s">
         <v>347</v>
       </c>
-      <c r="D13" s="69" t="s">
-        <v>348</v>
-      </c>
       <c r="E13" s="69" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="30">
@@ -9058,13 +9336,13 @@
         <v>2</v>
       </c>
       <c r="C14" s="70" t="s">
+        <v>348</v>
+      </c>
+      <c r="D14" s="69" t="s">
         <v>349</v>
       </c>
-      <c r="D14" s="69" t="s">
-        <v>350</v>
-      </c>
       <c r="E14" s="69" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="30">
@@ -9072,13 +9350,13 @@
         <v>3</v>
       </c>
       <c r="C15" s="70" t="s">
+        <v>350</v>
+      </c>
+      <c r="D15" s="69" t="s">
         <v>351</v>
       </c>
-      <c r="D15" s="69" t="s">
-        <v>352</v>
-      </c>
       <c r="E15" s="69" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="30">
@@ -9086,13 +9364,13 @@
         <v>4</v>
       </c>
       <c r="C16" s="70" t="s">
+        <v>352</v>
+      </c>
+      <c r="D16" s="69" t="s">
         <v>353</v>
       </c>
-      <c r="D16" s="69" t="s">
-        <v>354</v>
-      </c>
       <c r="E16" s="75" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="165">
@@ -9100,13 +9378,13 @@
         <v>5</v>
       </c>
       <c r="C17" s="70" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D17" s="69" t="s">
+        <v>430</v>
+      </c>
+      <c r="E17" s="75" t="s">
         <v>431</v>
-      </c>
-      <c r="E17" s="75" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="180">
@@ -9114,13 +9392,13 @@
         <v>6</v>
       </c>
       <c r="C18" s="70" t="s">
+        <v>355</v>
+      </c>
+      <c r="D18" s="69" t="s">
         <v>356</v>
       </c>
-      <c r="D18" s="69" t="s">
-        <v>357</v>
-      </c>
       <c r="E18" s="75" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="135">
@@ -9128,13 +9406,13 @@
         <v>7</v>
       </c>
       <c r="C19" s="70" t="s">
+        <v>357</v>
+      </c>
+      <c r="D19" s="69" t="s">
         <v>358</v>
       </c>
-      <c r="D19" s="69" t="s">
-        <v>359</v>
-      </c>
       <c r="E19" s="75" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="135">
@@ -9142,32 +9420,32 @@
         <v>8</v>
       </c>
       <c r="C20" s="70" t="s">
+        <v>359</v>
+      </c>
+      <c r="D20" s="69" t="s">
         <v>360</v>
       </c>
-      <c r="D20" s="69" t="s">
-        <v>361</v>
-      </c>
       <c r="E20" s="75" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="23.25">
       <c r="B23" s="63" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="25" spans="2:5">
       <c r="B25" s="73" t="s">
+        <v>336</v>
+      </c>
+      <c r="C25" s="73" t="s">
         <v>337</v>
       </c>
-      <c r="C25" s="73" t="s">
+      <c r="D25" s="73" t="s">
         <v>338</v>
       </c>
-      <c r="D25" s="73" t="s">
-        <v>339</v>
-      </c>
       <c r="E25" s="74" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="26" spans="2:5">
@@ -9175,10 +9453,10 @@
         <v>1</v>
       </c>
       <c r="C26" s="70" t="s">
+        <v>361</v>
+      </c>
+      <c r="D26" s="69" t="s">
         <v>362</v>
-      </c>
-      <c r="D26" s="69" t="s">
-        <v>363</v>
       </c>
       <c r="E26" s="1"/>
     </row>
@@ -9187,10 +9465,10 @@
         <v>2</v>
       </c>
       <c r="C27" s="70" t="s">
+        <v>363</v>
+      </c>
+      <c r="D27" s="69" t="s">
         <v>364</v>
-      </c>
-      <c r="D27" s="69" t="s">
-        <v>365</v>
       </c>
       <c r="E27" s="1"/>
     </row>
@@ -9199,10 +9477,10 @@
         <v>3</v>
       </c>
       <c r="C28" s="70" t="s">
+        <v>365</v>
+      </c>
+      <c r="D28" s="69" t="s">
         <v>366</v>
-      </c>
-      <c r="D28" s="69" t="s">
-        <v>367</v>
       </c>
       <c r="E28" s="1"/>
     </row>
@@ -9211,27 +9489,27 @@
         <v>4</v>
       </c>
       <c r="C29" s="70" t="s">
+        <v>367</v>
+      </c>
+      <c r="D29" s="69" t="s">
         <v>368</v>
-      </c>
-      <c r="D29" s="69" t="s">
-        <v>369</v>
       </c>
       <c r="E29" s="1"/>
     </row>
     <row r="32" spans="2:5" ht="23.25">
       <c r="B32" s="63" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="64" t="s">
+        <v>336</v>
+      </c>
+      <c r="C34" s="64" t="s">
         <v>337</v>
       </c>
-      <c r="C34" s="64" t="s">
+      <c r="D34" s="64" t="s">
         <v>338</v>
-      </c>
-      <c r="D34" s="64" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="35" spans="2:4" ht="30">
@@ -9239,10 +9517,10 @@
         <v>1</v>
       </c>
       <c r="C35" s="66" t="s">
+        <v>369</v>
+      </c>
+      <c r="D35" s="65" t="s">
         <v>370</v>
-      </c>
-      <c r="D35" s="65" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="36" spans="2:4">
@@ -9250,10 +9528,10 @@
         <v>2</v>
       </c>
       <c r="C36" s="66" t="s">
+        <v>371</v>
+      </c>
+      <c r="D36" s="65" t="s">
         <v>372</v>
-      </c>
-      <c r="D36" s="65" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="37" spans="2:4" ht="30">
@@ -9261,10 +9539,10 @@
         <v>3</v>
       </c>
       <c r="C37" s="66" t="s">
+        <v>373</v>
+      </c>
+      <c r="D37" s="65" t="s">
         <v>374</v>
-      </c>
-      <c r="D37" s="65" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="38" spans="2:4">
@@ -9272,26 +9550,26 @@
         <v>4</v>
       </c>
       <c r="C38" s="66" t="s">
+        <v>375</v>
+      </c>
+      <c r="D38" s="65" t="s">
         <v>376</v>
-      </c>
-      <c r="D38" s="65" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="41" spans="2:4" ht="23.25">
       <c r="B41" s="63" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="64" t="s">
+        <v>336</v>
+      </c>
+      <c r="C43" s="64" t="s">
         <v>337</v>
       </c>
-      <c r="C43" s="64" t="s">
+      <c r="D43" s="64" t="s">
         <v>338</v>
-      </c>
-      <c r="D43" s="64" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="44" spans="2:4" ht="30">
@@ -9299,10 +9577,10 @@
         <v>1</v>
       </c>
       <c r="C44" s="66" t="s">
+        <v>377</v>
+      </c>
+      <c r="D44" s="65" t="s">
         <v>378</v>
-      </c>
-      <c r="D44" s="65" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="45" spans="2:4">
@@ -9310,10 +9588,10 @@
         <v>2</v>
       </c>
       <c r="C45" s="66" t="s">
+        <v>379</v>
+      </c>
+      <c r="D45" s="65" t="s">
         <v>380</v>
-      </c>
-      <c r="D45" s="65" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="46" spans="2:4">
@@ -9321,10 +9599,10 @@
         <v>3</v>
       </c>
       <c r="C46" s="67" t="s">
+        <v>381</v>
+      </c>
+      <c r="D46" s="65" t="s">
         <v>382</v>
-      </c>
-      <c r="D46" s="65" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="47" spans="2:4">
@@ -9332,26 +9610,26 @@
         <v>4</v>
       </c>
       <c r="C47" s="67" t="s">
+        <v>383</v>
+      </c>
+      <c r="D47" s="65" t="s">
         <v>384</v>
-      </c>
-      <c r="D47" s="65" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="50" spans="2:4" ht="23.25">
       <c r="B50" s="63" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="52" spans="2:4">
       <c r="B52" s="64" t="s">
+        <v>336</v>
+      </c>
+      <c r="C52" s="64" t="s">
         <v>337</v>
       </c>
-      <c r="C52" s="64" t="s">
+      <c r="D52" s="64" t="s">
         <v>338</v>
-      </c>
-      <c r="D52" s="64" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="53" spans="2:4">
@@ -9359,10 +9637,10 @@
         <v>1</v>
       </c>
       <c r="C53" s="66" t="s">
+        <v>385</v>
+      </c>
+      <c r="D53" s="65" t="s">
         <v>386</v>
-      </c>
-      <c r="D53" s="65" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="54" spans="2:4">
@@ -9370,10 +9648,10 @@
         <v>2</v>
       </c>
       <c r="C54" s="66" t="s">
+        <v>387</v>
+      </c>
+      <c r="D54" s="65" t="s">
         <v>388</v>
-      </c>
-      <c r="D54" s="65" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="55" spans="2:4">
@@ -9381,10 +9659,10 @@
         <v>3</v>
       </c>
       <c r="C55" s="66" t="s">
+        <v>389</v>
+      </c>
+      <c r="D55" s="65" t="s">
         <v>390</v>
-      </c>
-      <c r="D55" s="65" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="56" spans="2:4">
@@ -9392,18 +9670,18 @@
     </row>
     <row r="58" spans="2:4" ht="23.25">
       <c r="B58" s="63" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="60" spans="2:4">
       <c r="B60" s="64" t="s">
+        <v>336</v>
+      </c>
+      <c r="C60" s="64" t="s">
         <v>337</v>
       </c>
-      <c r="C60" s="64" t="s">
+      <c r="D60" s="64" t="s">
         <v>338</v>
-      </c>
-      <c r="D60" s="64" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="61" spans="2:4">
@@ -9411,10 +9689,10 @@
         <v>1</v>
       </c>
       <c r="C61" s="66" t="s">
+        <v>391</v>
+      </c>
+      <c r="D61" s="65" t="s">
         <v>392</v>
-      </c>
-      <c r="D61" s="65" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="62" spans="2:4" ht="45">
@@ -9422,10 +9700,10 @@
         <v>2</v>
       </c>
       <c r="C62" s="66" t="s">
+        <v>393</v>
+      </c>
+      <c r="D62" s="65" t="s">
         <v>394</v>
-      </c>
-      <c r="D62" s="65" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="63" spans="2:4" ht="30">
@@ -9433,10 +9711,10 @@
         <v>3</v>
       </c>
       <c r="C63" s="66" t="s">
+        <v>395</v>
+      </c>
+      <c r="D63" s="65" t="s">
         <v>396</v>
-      </c>
-      <c r="D63" s="65" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="64" spans="2:4">
@@ -9444,10 +9722,10 @@
         <v>4</v>
       </c>
       <c r="C64" s="66" t="s">
+        <v>397</v>
+      </c>
+      <c r="D64" s="65" t="s">
         <v>398</v>
-      </c>
-      <c r="D64" s="65" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="65" spans="2:4">
@@ -9455,26 +9733,26 @@
         <v>5</v>
       </c>
       <c r="C65" s="66" t="s">
+        <v>399</v>
+      </c>
+      <c r="D65" s="65" t="s">
         <v>400</v>
-      </c>
-      <c r="D65" s="65" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="68" spans="2:4" ht="23.25">
       <c r="B68" s="63" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="70" spans="2:4">
       <c r="B70" s="64" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C70" s="64" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D70" s="64" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="71" spans="2:4">
@@ -9482,10 +9760,10 @@
         <v>1</v>
       </c>
       <c r="C71" s="65" t="s">
+        <v>403</v>
+      </c>
+      <c r="D71" s="65" t="s">
         <v>404</v>
-      </c>
-      <c r="D71" s="65" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="72" spans="2:4">
@@ -9493,10 +9771,10 @@
         <v>2</v>
       </c>
       <c r="C72" s="65" t="s">
+        <v>405</v>
+      </c>
+      <c r="D72" s="65" t="s">
         <v>406</v>
-      </c>
-      <c r="D72" s="65" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="73" spans="2:4">
@@ -9504,10 +9782,10 @@
         <v>3</v>
       </c>
       <c r="C73" s="65" t="s">
+        <v>407</v>
+      </c>
+      <c r="D73" s="65" t="s">
         <v>408</v>
-      </c>
-      <c r="D73" s="65" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="74" spans="2:4">
@@ -9515,10 +9793,10 @@
         <v>4</v>
       </c>
       <c r="C74" s="65" t="s">
+        <v>409</v>
+      </c>
+      <c r="D74" s="65" t="s">
         <v>410</v>
-      </c>
-      <c r="D74" s="65" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="75" spans="2:4">
@@ -9526,10 +9804,10 @@
         <v>5</v>
       </c>
       <c r="C75" s="65" t="s">
+        <v>411</v>
+      </c>
+      <c r="D75" s="65" t="s">
         <v>412</v>
-      </c>
-      <c r="D75" s="65" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="76" spans="2:4">
@@ -9537,10 +9815,57 @@
         <v>6</v>
       </c>
       <c r="C76" s="65" t="s">
+        <v>413</v>
+      </c>
+      <c r="D76" s="65" t="s">
         <v>414</v>
       </c>
-      <c r="D76" s="65" t="s">
-        <v>415</v>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:D7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2" spans="2:4">
+      <c r="B2" s="6" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4">
+      <c r="C3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="C4" s="76" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
+      <c r="B5" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
+      <c r="C6" t="s">
+        <v>446</v>
+      </c>
+      <c r="D6" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4">
+      <c r="C7" t="s">
+        <v>447</v>
+      </c>
+      <c r="D7" t="s">
+        <v>449</v>
       </c>
     </row>
   </sheetData>
@@ -10702,7 +11027,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:G54"/>
+  <dimension ref="B1:G90"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="50.140625" bestFit="1" customWidth="1"/>
@@ -11050,7 +11375,9 @@
       <c r="C23" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="D23" s="6"/>
+      <c r="D23" s="42">
+        <v>1</v>
+      </c>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
     </row>
@@ -11405,7 +11732,7 @@
         <v>266</v>
       </c>
       <c r="C47" s="57" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D47" s="42">
         <v>1</v>
@@ -11417,13 +11744,13 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C48" s="56" t="s">
-        <v>302</v>
-      </c>
-      <c r="D48" s="42">
-        <v>0</v>
+        <v>301</v>
+      </c>
+      <c r="D48" s="51">
+        <v>0.8</v>
       </c>
       <c r="E48" s="6"/>
       <c r="F48" s="16" t="s">
@@ -11432,10 +11759,10 @@
     </row>
     <row r="49" spans="2:6">
       <c r="B49" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
@@ -11443,7 +11770,7 @@
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>286</v>
@@ -11452,32 +11779,36 @@
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
     </row>
-    <row r="51" spans="2:6">
+    <row r="51" spans="2:6" ht="30">
       <c r="B51" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>287</v>
+        <v>321</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>437</v>
       </c>
       <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
+      <c r="E51" s="16" t="s">
+        <v>438</v>
+      </c>
       <c r="F51" s="6"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>290</v>
+        <v>439</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="6"/>
       <c r="F52" s="6"/>
     </row>
     <row r="53" spans="2:6">
-      <c r="B53" s="5"/>
+      <c r="B53" s="5" t="s">
+        <v>323</v>
+      </c>
       <c r="C53" s="6" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="D53" s="6"/>
       <c r="E53" s="6"/>
@@ -11485,14 +11816,426 @@
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="D54" s="42">
+        <v>1</v>
+      </c>
+      <c r="E54" s="6"/>
+      <c r="F54" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6">
+      <c r="B55" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="6"/>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="D56" s="6"/>
+      <c r="E56" s="16" t="s">
+        <v>471</v>
+      </c>
+      <c r="F56" s="6"/>
+    </row>
+    <row r="57" spans="2:6">
+      <c r="B57" s="5">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="D57" s="6"/>
+      <c r="E57" s="16"/>
+      <c r="F57" s="6"/>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="5">
+        <v>16.2</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="6"/>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="5">
+        <v>16.3</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="6"/>
+    </row>
+    <row r="60" spans="2:6">
+      <c r="B60" s="5">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6"/>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="5">
+        <v>16.5</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="6"/>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="5">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="6"/>
+    </row>
+    <row r="63" spans="2:6" ht="40.5" customHeight="1">
+      <c r="B63" s="5">
+        <v>16.7</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="6"/>
+    </row>
+    <row r="64" spans="2:6">
+      <c r="B64" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="6"/>
+    </row>
+    <row r="65" spans="2:6" ht="30">
+      <c r="B65" s="5">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="C65" s="81" t="s">
+        <v>490</v>
+      </c>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="6"/>
+    </row>
+    <row r="66" spans="2:6" ht="30">
+      <c r="B66" s="5">
+        <v>17.2</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D66" s="6"/>
+      <c r="E66" s="6"/>
+      <c r="F66" s="6"/>
+    </row>
+    <row r="67" spans="2:6" ht="50.25" customHeight="1">
+      <c r="B67" s="5">
+        <v>17.3</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="D67" s="6"/>
+      <c r="E67" s="16" t="s">
+        <v>471</v>
+      </c>
+      <c r="F67" s="6"/>
+    </row>
+    <row r="68" spans="2:6" ht="30">
+      <c r="B68" s="5">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="D68" s="6"/>
+      <c r="E68" s="6"/>
+      <c r="F68" s="6"/>
+    </row>
+    <row r="69" spans="2:6">
+      <c r="B69" s="5">
+        <v>17.5</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
+    </row>
+    <row r="70" spans="2:6">
+      <c r="B70" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="D70" s="6"/>
+      <c r="E70" s="6"/>
+      <c r="F70" s="6"/>
+    </row>
+    <row r="71" spans="2:6">
+      <c r="B71" s="5">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="D71" s="6"/>
+      <c r="E71" s="6"/>
+      <c r="F71" s="6"/>
+    </row>
+    <row r="72" spans="2:6">
+      <c r="B72" s="5">
+        <v>18.2</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="D72" s="6"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="6"/>
+    </row>
+    <row r="73" spans="2:6">
+      <c r="B73" s="5">
+        <v>18.3</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="D73" s="6"/>
+      <c r="E73" s="6"/>
+      <c r="F73" s="6"/>
+    </row>
+    <row r="74" spans="2:6">
+      <c r="B74" s="5">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="6"/>
+    </row>
+    <row r="75" spans="2:6">
+      <c r="B75" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="D75" s="6"/>
+      <c r="E75" s="6"/>
+      <c r="F75" s="6"/>
+    </row>
+    <row r="76" spans="2:6">
+      <c r="B76" s="5">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="D76" s="6"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="6"/>
+    </row>
+    <row r="77" spans="2:6">
+      <c r="B77" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="D77" s="6"/>
+      <c r="E77" s="6"/>
+      <c r="F77" s="6"/>
+    </row>
+    <row r="78" spans="2:6">
+      <c r="B78" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="D78" s="6"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="6"/>
+    </row>
+    <row r="79" spans="2:6">
+      <c r="B79" s="5">
+        <v>21.1</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="D79" s="6"/>
+      <c r="E79" s="6"/>
+      <c r="F79" s="6"/>
+    </row>
+    <row r="80" spans="2:6" ht="30">
+      <c r="B80" s="5">
+        <v>21.2</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="D80" s="6"/>
+      <c r="E80" s="6"/>
+      <c r="F80" s="6"/>
+    </row>
+    <row r="81" spans="2:6">
+      <c r="B81" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="C81" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="C54" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6"/>
-      <c r="F54" s="6"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="16" t="s">
+        <v>475</v>
+      </c>
+      <c r="F81" s="6"/>
+    </row>
+    <row r="82" spans="2:6">
+      <c r="B82" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="D82" s="6"/>
+      <c r="E82" s="16" t="s">
+        <v>475</v>
+      </c>
+      <c r="F82" s="6"/>
+    </row>
+    <row r="83" spans="2:6">
+      <c r="B83" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="D83" s="6"/>
+      <c r="E83" s="16"/>
+      <c r="F83" s="6"/>
+    </row>
+    <row r="84" spans="2:6">
+      <c r="B84" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="D84" s="6"/>
+      <c r="E84" s="16"/>
+      <c r="F84" s="6"/>
+    </row>
+    <row r="85" spans="2:6" ht="60">
+      <c r="B85" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="C85" s="82" t="s">
+        <v>491</v>
+      </c>
+      <c r="D85" s="6"/>
+      <c r="E85" s="16" t="s">
+        <v>492</v>
+      </c>
+      <c r="F85" s="6"/>
+    </row>
+    <row r="86" spans="2:6" ht="30">
+      <c r="B86" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>493</v>
+      </c>
+      <c r="D86" s="6"/>
+      <c r="E86" s="16"/>
+      <c r="F86" s="6"/>
+    </row>
+    <row r="87" spans="2:6">
+      <c r="B87" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="D87" s="6"/>
+      <c r="E87" s="16"/>
+      <c r="F87" s="6"/>
+    </row>
+    <row r="88" spans="2:6" ht="60">
+      <c r="B88" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="D88" s="6"/>
+      <c r="E88" s="16"/>
+      <c r="F88" s="6"/>
+    </row>
+    <row r="89" spans="2:6" ht="30">
+      <c r="B89" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="D89" s="6"/>
+      <c r="E89" s="16"/>
+      <c r="F89" s="6"/>
+    </row>
+    <row r="90" spans="2:6">
+      <c r="B90" s="77" t="s">
+        <v>482</v>
+      </c>
+      <c r="C90" s="57" t="s">
+        <v>481</v>
+      </c>
+      <c r="D90" s="1"/>
+      <c r="E90" s="49" t="s">
+        <v>480</v>
+      </c>
+      <c r="F90" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -11540,9 +12283,16 @@
     <hyperlink ref="F46" location="'#6'!B33" display="Link"/>
     <hyperlink ref="F47" location="'#7'!B2" display="Link"/>
     <hyperlink ref="F48" location="'#8'!A1" display="Link"/>
+    <hyperlink ref="E51" r:id="rId6"/>
+    <hyperlink ref="F54" location="'#14'!B2" display="Link"/>
+    <hyperlink ref="E56" r:id="rId7"/>
+    <hyperlink ref="E67" r:id="rId8"/>
+    <hyperlink ref="E81" r:id="rId9"/>
+    <hyperlink ref="E82" r:id="rId10"/>
+    <hyperlink ref="E90" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId6"/>
+  <pageSetup orientation="portrait" r:id="rId12"/>
 </worksheet>
 </file>
 
@@ -11857,7 +12607,7 @@
       <c r="D12" s="11"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" thickBot="1">
-      <c r="C13" s="76" t="s">
+      <c r="C13" s="78" t="s">
         <v>78</v>
       </c>
       <c r="D13" s="26" t="s">
@@ -11874,7 +12624,7 @@
       <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:10" ht="15.75" thickBot="1">
-      <c r="C14" s="77"/>
+      <c r="C14" s="79"/>
       <c r="D14" s="23" t="s">
         <v>65</v>
       </c>
@@ -11890,7 +12640,7 @@
       <c r="J14" s="25"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="C15" s="77"/>
+      <c r="C15" s="79"/>
       <c r="D15" s="26" t="s">
         <v>66</v>
       </c>
@@ -11905,7 +12655,7 @@
       <c r="I15" s="28"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="C16" s="77"/>
+      <c r="C16" s="79"/>
       <c r="D16" s="29"/>
       <c r="E16" s="30" t="s">
         <v>74</v>
@@ -11916,7 +12666,7 @@
       <c r="I16" s="31"/>
     </row>
     <row r="17" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C17" s="78"/>
+      <c r="C17" s="80"/>
       <c r="D17" s="32"/>
       <c r="E17" s="33" t="s">
         <v>75</v>
@@ -11947,7 +12697,7 @@
       <c r="L18" s="25"/>
     </row>
     <row r="19" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C19" s="76" t="s">
+      <c r="C19" s="78" t="s">
         <v>78</v>
       </c>
       <c r="D19" s="23" t="s">
@@ -11958,7 +12708,7 @@
       </c>
     </row>
     <row r="20" spans="3:12">
-      <c r="C20" s="77"/>
+      <c r="C20" s="79"/>
       <c r="D20" s="26" t="s">
         <v>82</v>
       </c>
@@ -11967,7 +12717,7 @@
       </c>
     </row>
     <row r="21" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C21" s="78"/>
+      <c r="C21" s="80"/>
       <c r="D21" s="32"/>
       <c r="E21" s="40" t="s">
         <v>84</v>
@@ -13118,7 +13868,7 @@
         <v>272</v>
       </c>
       <c r="E5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8" spans="2:26">
@@ -13146,7 +13896,7 @@
         <v>277</v>
       </c>
       <c r="F12" s="55" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G12" s="55"/>
       <c r="H12" s="55"/>
@@ -13211,39 +13961,39 @@
     </row>
     <row r="35" spans="2:7">
       <c r="C35" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="37" spans="2:7">
       <c r="D37" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E37" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="38" spans="2:7">
       <c r="D38" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E38" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="39" spans="2:7">
       <c r="D39" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E39" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="40" spans="2:7">
       <c r="D40" t="s">
+        <v>299</v>
+      </c>
+      <c r="G40" t="s">
         <v>300</v>
-      </c>
-      <c r="G40" t="s">
-        <v>301</v>
       </c>
     </row>
   </sheetData>

--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="Knowhow" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,8 @@
     <sheet name="#6" sheetId="9" r:id="rId9"/>
     <sheet name="#7" sheetId="10" r:id="rId10"/>
     <sheet name="#8" sheetId="11" r:id="rId11"/>
-    <sheet name="#14" sheetId="12" r:id="rId12"/>
+    <sheet name="#9" sheetId="13" r:id="rId12"/>
+    <sheet name="#14" sheetId="12" r:id="rId13"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="509">
   <si>
     <t>No.</t>
   </si>
@@ -3900,6 +3901,24 @@
   </si>
   <si>
     <t>#31</t>
+  </si>
+  <si>
+    <t>1 Framework để hỗ trợ việc Unit test dễ dàng hơn</t>
+  </si>
+  <si>
+    <t>Khi test cần lưu ý, phân rõ ràng thư mục ra</t>
+  </si>
+  <si>
+    <t>/test</t>
+  </si>
+  <si>
+    <t>thư mục để test</t>
+  </si>
+  <si>
+    <t>/src</t>
+  </si>
+  <si>
+    <t>thư mục để src</t>
   </si>
 </sst>
 </file>
@@ -4448,6 +4467,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4456,12 +4481,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -9829,6 +9848,47 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:E7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2" spans="2:5">
+      <c r="B2" s="6" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5">
+      <c r="C3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5">
+      <c r="C5" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5">
+      <c r="D6" t="s">
+        <v>505</v>
+      </c>
+      <c r="E6" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5">
+      <c r="D7" t="s">
+        <v>507</v>
+      </c>
+      <c r="E7" t="s">
+        <v>508</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -11764,9 +11824,13 @@
       <c r="C49" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="D49" s="6"/>
+      <c r="D49" s="42">
+        <v>0</v>
+      </c>
       <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
+      <c r="F49" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="5" t="s">
@@ -11775,7 +11839,9 @@
       <c r="C50" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="D50" s="6"/>
+      <c r="D50" s="51">
+        <v>0</v>
+      </c>
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
     </row>
@@ -11945,7 +12011,7 @@
       <c r="B65" s="5">
         <v>17.100000000000001</v>
       </c>
-      <c r="C65" s="81" t="s">
+      <c r="C65" s="78" t="s">
         <v>490</v>
       </c>
       <c r="D65" s="6"/>
@@ -12171,7 +12237,7 @@
       <c r="B85" s="5" t="s">
         <v>498</v>
       </c>
-      <c r="C85" s="82" t="s">
+      <c r="C85" s="79" t="s">
         <v>491</v>
       </c>
       <c r="D85" s="6"/>
@@ -12290,6 +12356,7 @@
     <hyperlink ref="E81" r:id="rId9"/>
     <hyperlink ref="E82" r:id="rId10"/>
     <hyperlink ref="E90" r:id="rId11"/>
+    <hyperlink ref="F49" location="'#9'!B2" display="Link"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId12"/>
@@ -12607,7 +12674,7 @@
       <c r="D12" s="11"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" thickBot="1">
-      <c r="C13" s="78" t="s">
+      <c r="C13" s="80" t="s">
         <v>78</v>
       </c>
       <c r="D13" s="26" t="s">
@@ -12624,7 +12691,7 @@
       <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:10" ht="15.75" thickBot="1">
-      <c r="C14" s="79"/>
+      <c r="C14" s="81"/>
       <c r="D14" s="23" t="s">
         <v>65</v>
       </c>
@@ -12640,7 +12707,7 @@
       <c r="J14" s="25"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="C15" s="79"/>
+      <c r="C15" s="81"/>
       <c r="D15" s="26" t="s">
         <v>66</v>
       </c>
@@ -12655,7 +12722,7 @@
       <c r="I15" s="28"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="C16" s="79"/>
+      <c r="C16" s="81"/>
       <c r="D16" s="29"/>
       <c r="E16" s="30" t="s">
         <v>74</v>
@@ -12666,7 +12733,7 @@
       <c r="I16" s="31"/>
     </row>
     <row r="17" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C17" s="80"/>
+      <c r="C17" s="82"/>
       <c r="D17" s="32"/>
       <c r="E17" s="33" t="s">
         <v>75</v>
@@ -12697,7 +12764,7 @@
       <c r="L18" s="25"/>
     </row>
     <row r="19" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C19" s="78" t="s">
+      <c r="C19" s="80" t="s">
         <v>78</v>
       </c>
       <c r="D19" s="23" t="s">
@@ -12708,7 +12775,7 @@
       </c>
     </row>
     <row r="20" spans="3:12">
-      <c r="C20" s="79"/>
+      <c r="C20" s="81"/>
       <c r="D20" s="26" t="s">
         <v>82</v>
       </c>
@@ -12717,7 +12784,7 @@
       </c>
     </row>
     <row r="21" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C21" s="80"/>
+      <c r="C21" s="82"/>
       <c r="D21" s="32"/>
       <c r="E21" s="40" t="s">
         <v>84</v>

--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="11"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Knowhow" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,9 @@
     <sheet name="#7" sheetId="10" r:id="rId10"/>
     <sheet name="#8" sheetId="11" r:id="rId11"/>
     <sheet name="#9" sheetId="13" r:id="rId12"/>
-    <sheet name="#14" sheetId="12" r:id="rId13"/>
+    <sheet name="#12" sheetId="14" r:id="rId13"/>
+    <sheet name="#14" sheetId="12" r:id="rId14"/>
+    <sheet name="#16" sheetId="15" r:id="rId15"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="540">
   <si>
     <t>No.</t>
   </si>
@@ -3642,9 +3644,6 @@
     <t>https://chatgpt.com/share/690b291c-d088-8002-b37a-10bb5da410ce</t>
   </si>
   <si>
-    <t>What is the difference between ++i and i++</t>
-  </si>
-  <si>
     <t>Các Segment trong C++ ( Data Segment)</t>
   </si>
   <si>
@@ -3720,9 +3719,6 @@
       </rPr>
       <t xml:space="preserve"> không cho phép giải phóng 1 con trỏ đã giải phóng rồi</t>
     </r>
-  </si>
-  <si>
-    <t>Cấp phát động trong C và C++</t>
   </si>
   <si>
     <t>Cách 1</t>
@@ -3919,6 +3915,275 @@
   </si>
   <si>
     <t>thư mục để src</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Gtest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> có thể </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>kết hợp với Cmake</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để thuận tiện trong việc build hơn. Khi add_executable thì sẽ add file test.cpp và unit test sẽ tự động chạy hàm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>main của nó</t>
+    </r>
+  </si>
+  <si>
+    <t>Sử dụng Gcovr để gen ra file HTML check xem đã cover được bao nhiêu phần trăm code</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">*khi sửa 1 function của 1 file 10000 line, recommend là </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tạo riêng 1 file .cpp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> chỉ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>chứa function đó</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để kết quả gen HTML </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>coverage là 100%</t>
+    </r>
+  </si>
+  <si>
+    <t>Điền triển khai qua VDI trên cty vào đây</t>
+  </si>
+  <si>
+    <t>Sự khác biệt giữa ++i và i++</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Tiền </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tố</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Hậu </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tố</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>++</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>++</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i</t>
+    </r>
+  </si>
+  <si>
+    <t>Tăng sau khi dùng</t>
+  </si>
+  <si>
+    <t>Tăng trước khi dùng</t>
+  </si>
+  <si>
+    <t>Cấp phát động trong C và C++ (new và malloc)</t>
+  </si>
+  <si>
+    <t>Ví dụ :</t>
+  </si>
+  <si>
+    <t>#include &lt;iostream&gt;</t>
+  </si>
+  <si>
+    <t>int main()</t>
+  </si>
+  <si>
+    <t>{</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int i = 5;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int j = 5;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int a,b;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    a = i++;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    b = ++j;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    std::cout&lt;&lt;a&lt;&lt;" sau khi i++ va "&lt;&lt;i&lt;&lt;std::endl;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    std::cout&lt;&lt;b&lt;&lt;" sau khi ++i va "&lt;&lt;j;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return 0;</t>
+  </si>
+  <si>
+    <t>OUTPUT :</t>
+  </si>
+  <si>
+    <t>a = 5</t>
+  </si>
+  <si>
+    <t>b = 6</t>
+  </si>
+  <si>
+    <t>Private</t>
+  </si>
+  <si>
+    <t>Public</t>
+  </si>
+  <si>
+    <t>Protected</t>
+  </si>
+  <si>
+    <t>Có thể truy cập từ ngoài class</t>
+  </si>
+  <si>
+    <t>Chỉ truy cập được các thuộc tính, phương thức trong chính class đó. (kể cả trong hệ thống kế thừa thì class kế thừa cũng không thể lấy ra dùng được)</t>
+  </si>
+  <si>
+    <t>Không thể truy cập từ bên ngoài class, chỉ có thể truy cập từ class thuộc hệ thống kế thừa</t>
   </si>
 </sst>
 </file>
@@ -4314,7 +4579,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -4482,6 +4747,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -8519,19 +8785,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:K22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="5.7109375" customWidth="1"/>
-    <col min="3" max="3" width="37.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.42578125" customWidth="1"/>
+    <col min="2" max="2" width="5.7265625" customWidth="1"/>
+    <col min="3" max="3" width="37.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.453125" customWidth="1"/>
     <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7265625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="18.75">
+    <row r="2" spans="2:11" ht="18.5">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -8557,7 +8823,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:11" ht="45">
+    <row r="3" spans="2:11" ht="43.5">
       <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
@@ -8911,9 +9177,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Q30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="11" max="11" width="3.7109375" customWidth="1"/>
+    <col min="11" max="11" width="3.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:17">
@@ -9243,12 +9509,12 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E76"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="4.42578125" customWidth="1"/>
-    <col min="3" max="3" width="39.7109375" customWidth="1"/>
-    <col min="4" max="4" width="50.85546875" customWidth="1"/>
-    <col min="5" max="5" width="75.42578125" customWidth="1"/>
+    <col min="2" max="2" width="4.453125" customWidth="1"/>
+    <col min="3" max="3" width="39.7265625" customWidth="1"/>
+    <col min="4" max="4" width="50.81640625" customWidth="1"/>
+    <col min="5" max="5" width="75.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.5">
@@ -9256,7 +9522,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="23.25">
+    <row r="2" spans="1:5" ht="23.5">
       <c r="B2" s="63" t="s">
         <v>421</v>
       </c>
@@ -9275,7 +9541,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="45">
+    <row r="5" spans="1:5" ht="43.5">
       <c r="B5" s="69">
         <v>1</v>
       </c>
@@ -9303,7 +9569,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5" ht="29">
       <c r="B7" s="69">
         <v>3</v>
       </c>
@@ -9317,7 +9583,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="23.25">
+    <row r="10" spans="1:5" ht="23.5">
       <c r="B10" s="63" t="s">
         <v>345</v>
       </c>
@@ -9336,7 +9602,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="30">
+    <row r="13" spans="1:5">
       <c r="B13" s="69">
         <v>1</v>
       </c>
@@ -9350,7 +9616,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="30">
+    <row r="14" spans="1:5" ht="29">
       <c r="B14" s="69">
         <v>2</v>
       </c>
@@ -9364,7 +9630,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="30">
+    <row r="15" spans="1:5" ht="29">
       <c r="B15" s="69">
         <v>3</v>
       </c>
@@ -9378,7 +9644,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30">
+    <row r="16" spans="1:5" ht="29">
       <c r="B16" s="69">
         <v>4</v>
       </c>
@@ -9392,7 +9658,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="165">
+    <row r="17" spans="2:5" ht="145">
       <c r="B17" s="69">
         <v>5</v>
       </c>
@@ -9406,7 +9672,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="180">
+    <row r="18" spans="2:5" ht="159.5">
       <c r="B18" s="69">
         <v>6</v>
       </c>
@@ -9420,7 +9686,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="135">
+    <row r="19" spans="2:5" ht="130.5">
       <c r="B19" s="69">
         <v>7</v>
       </c>
@@ -9434,7 +9700,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="135">
+    <row r="20" spans="2:5" ht="130.5">
       <c r="B20" s="69">
         <v>8</v>
       </c>
@@ -9448,7 +9714,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="23" spans="2:5" ht="23.25">
+    <row r="23" spans="2:5" ht="23.5">
       <c r="B23" s="63" t="s">
         <v>420</v>
       </c>
@@ -9515,7 +9781,7 @@
       </c>
       <c r="E29" s="1"/>
     </row>
-    <row r="32" spans="2:5" ht="23.25">
+    <row r="32" spans="2:5" ht="23.5">
       <c r="B32" s="63" t="s">
         <v>419</v>
       </c>
@@ -9531,7 +9797,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="35" spans="2:4" ht="30">
+    <row r="35" spans="2:4" ht="29">
       <c r="B35" s="65">
         <v>1</v>
       </c>
@@ -9553,7 +9819,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="37" spans="2:4" ht="30">
+    <row r="37" spans="2:4">
       <c r="B37" s="65">
         <v>3</v>
       </c>
@@ -9575,7 +9841,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="41" spans="2:4" ht="23.25">
+    <row r="41" spans="2:4" ht="23.5">
       <c r="B41" s="63" t="s">
         <v>418</v>
       </c>
@@ -9591,7 +9857,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="44" spans="2:4" ht="30">
+    <row r="44" spans="2:4">
       <c r="B44" s="65">
         <v>1</v>
       </c>
@@ -9635,7 +9901,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="50" spans="2:4" ht="23.25">
+    <row r="50" spans="2:4" ht="23.5">
       <c r="B50" s="63" t="s">
         <v>417</v>
       </c>
@@ -9687,7 +9953,7 @@
     <row r="56" spans="2:4">
       <c r="B56" s="65"/>
     </row>
-    <row r="58" spans="2:4" ht="23.25">
+    <row r="58" spans="2:4" ht="23.5">
       <c r="B58" s="63" t="s">
         <v>416</v>
       </c>
@@ -9714,7 +9980,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="62" spans="2:4" ht="45">
+    <row r="62" spans="2:4" ht="29">
       <c r="B62" s="65">
         <v>2</v>
       </c>
@@ -9725,7 +9991,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="63" spans="2:4" ht="30">
+    <row r="63" spans="2:4" ht="29">
       <c r="B63" s="65">
         <v>3</v>
       </c>
@@ -9758,7 +10024,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="68" spans="2:4" ht="23.25">
+    <row r="68" spans="2:4" ht="23.5">
       <c r="B68" s="63" t="s">
         <v>401</v>
       </c>
@@ -9848,8 +10114,8 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:E7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="B2:E14"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -9858,28 +10124,166 @@
     </row>
     <row r="3" spans="2:5">
       <c r="C3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="5" spans="2:5">
       <c r="C5" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="D6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E6" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="D7" t="s">
+        <v>505</v>
+      </c>
+      <c r="E7" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5">
+      <c r="C9" t="s">
         <v>507</v>
       </c>
-      <c r="E7" t="s">
+    </row>
+    <row r="11" spans="2:5">
+      <c r="C11" t="s">
         <v>508</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5">
+      <c r="D12" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5">
+      <c r="C14" t="s">
+        <v>510</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:E25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="2" spans="2:5">
+      <c r="B2" s="6" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5">
+      <c r="C3" t="s">
+        <v>514</v>
+      </c>
+      <c r="D3" t="s">
+        <v>513</v>
+      </c>
+      <c r="E3" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5">
+      <c r="C4" s="83" t="s">
+        <v>515</v>
+      </c>
+      <c r="D4" t="s">
+        <v>512</v>
+      </c>
+      <c r="E4" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5">
+      <c r="C7" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
+      <c r="C8" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5">
+      <c r="C10" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5">
+      <c r="C11" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5">
+      <c r="C12" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5">
+      <c r="C13" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5">
+      <c r="C14" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5">
+      <c r="C15" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5">
+      <c r="C16" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3">
+      <c r="C20" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3">
+      <c r="C21" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="23" spans="3:3">
+      <c r="C23" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3">
+      <c r="C24" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="25" spans="3:3">
+      <c r="C25" t="s">
+        <v>533</v>
       </c>
     </row>
   </sheetData>
@@ -9887,45 +10291,45 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="3" spans="2:4">
       <c r="C3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="C4" s="76" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="5" spans="2:4">
       <c r="B5" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="6" spans="2:4">
       <c r="C6" t="s">
+        <v>444</v>
+      </c>
+      <c r="D6" t="s">
         <v>446</v>
-      </c>
-      <c r="D6" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="7" spans="2:4">
       <c r="C7" t="s">
+        <v>445</v>
+      </c>
+      <c r="D7" t="s">
         <v>447</v>
-      </c>
-      <c r="D7" t="s">
-        <v>449</v>
       </c>
     </row>
   </sheetData>
@@ -9934,18 +10338,57 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:D5"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="2" spans="2:4">
+      <c r="B2" s="6" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4">
+      <c r="C3" t="s">
+        <v>534</v>
+      </c>
+      <c r="D3" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="C4" t="s">
+        <v>535</v>
+      </c>
+      <c r="D4" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
+      <c r="C5" t="s">
+        <v>536</v>
+      </c>
+      <c r="D5" t="s">
+        <v>539</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:F103"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="3" max="3" width="12.28515625" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.26953125" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" customWidth="1"/>
+    <col min="5" max="5" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="18.75">
+    <row r="2" spans="2:6" ht="18.5">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -11088,12 +11531,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:G90"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="3" max="3" width="50.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="68.5703125" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" customWidth="1"/>
+    <col min="3" max="3" width="50.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.54296875" customWidth="1"/>
+    <col min="6" max="6" width="9.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6">
@@ -11101,7 +11544,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="2:6" ht="18.75">
+    <row r="2" spans="2:6" ht="18.5">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -11824,8 +12267,8 @@
       <c r="C49" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="D49" s="42">
-        <v>0</v>
+      <c r="D49" s="51">
+        <v>0.8</v>
       </c>
       <c r="E49" s="6"/>
       <c r="F49" s="16" t="s">
@@ -11845,7 +12288,7 @@
       <c r="E50" s="6"/>
       <c r="F50" s="6"/>
     </row>
-    <row r="51" spans="2:6" ht="30">
+    <row r="51" spans="2:6" ht="29">
       <c r="B51" s="5" t="s">
         <v>321</v>
       </c>
@@ -11863,18 +12306,22 @@
         <v>322</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>439</v>
-      </c>
-      <c r="D52" s="6"/>
+        <v>511</v>
+      </c>
+      <c r="D52" s="42">
+        <v>1</v>
+      </c>
       <c r="E52" s="6"/>
-      <c r="F52" s="6"/>
+      <c r="F52" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="5" t="s">
         <v>323</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D53" s="6"/>
       <c r="E53" s="6"/>
@@ -11885,7 +12332,7 @@
         <v>436</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D54" s="42">
         <v>1</v>
@@ -11897,10 +12344,10 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>445</v>
+        <v>518</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="6"/>
@@ -11908,14 +12355,14 @@
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="5" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D56" s="6"/>
       <c r="E56" s="16" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F56" s="6"/>
     </row>
@@ -11924,18 +12371,22 @@
         <v>16.100000000000001</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>483</v>
-      </c>
-      <c r="D57" s="6"/>
+        <v>481</v>
+      </c>
+      <c r="D57" s="42">
+        <v>1</v>
+      </c>
       <c r="E57" s="16"/>
-      <c r="F57" s="6"/>
+      <c r="F57" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="5">
         <v>16.2</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="6"/>
@@ -11946,7 +12397,7 @@
         <v>16.3</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D59" s="6"/>
       <c r="E59" s="6"/>
@@ -11957,7 +12408,7 @@
         <v>16.399999999999999</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D60" s="6"/>
       <c r="E60" s="6"/>
@@ -11968,7 +12419,7 @@
         <v>16.5</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
@@ -11979,7 +12430,7 @@
         <v>16.600000000000001</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D62" s="6"/>
       <c r="E62" s="6"/>
@@ -11990,7 +12441,7 @@
         <v>16.7</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
@@ -11998,32 +12449,32 @@
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="5" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>
     </row>
-    <row r="65" spans="2:6" ht="30">
+    <row r="65" spans="2:6" ht="29">
       <c r="B65" s="5">
         <v>17.100000000000001</v>
       </c>
       <c r="C65" s="78" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D65" s="6"/>
       <c r="E65" s="6"/>
       <c r="F65" s="6"/>
     </row>
-    <row r="66" spans="2:6" ht="30">
+    <row r="66" spans="2:6" ht="29">
       <c r="B66" s="5">
         <v>17.2</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D66" s="6"/>
       <c r="E66" s="6"/>
@@ -12034,20 +12485,20 @@
         <v>17.3</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="D67" s="6"/>
       <c r="E67" s="16" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F67" s="6"/>
     </row>
-    <row r="68" spans="2:6" ht="30">
+    <row r="68" spans="2:6" ht="29">
       <c r="B68" s="5">
         <v>17.399999999999999</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
@@ -12058,7 +12509,7 @@
         <v>17.5</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D69" s="6"/>
       <c r="E69" s="6"/>
@@ -12066,10 +12517,10 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="5" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D70" s="6"/>
       <c r="E70" s="6"/>
@@ -12080,7 +12531,7 @@
         <v>18.100000000000001</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D71" s="6"/>
       <c r="E71" s="6"/>
@@ -12091,7 +12542,7 @@
         <v>18.2</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D72" s="6"/>
       <c r="E72" s="6"/>
@@ -12102,7 +12553,7 @@
         <v>18.3</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D73" s="6"/>
       <c r="E73" s="6"/>
@@ -12113,7 +12564,7 @@
         <v>18.399999999999999</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D74" s="6"/>
       <c r="E74" s="6"/>
@@ -12121,10 +12572,10 @@
     </row>
     <row r="75" spans="2:6">
       <c r="B75" s="5" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D75" s="6"/>
       <c r="E75" s="6"/>
@@ -12135,7 +12586,7 @@
         <v>19.100000000000001</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D76" s="6"/>
       <c r="E76" s="6"/>
@@ -12143,10 +12594,10 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="5" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D77" s="6"/>
       <c r="E77" s="6"/>
@@ -12154,7 +12605,7 @@
     </row>
     <row r="78" spans="2:6">
       <c r="B78" s="5" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>289</v>
@@ -12174,12 +12625,12 @@
       <c r="E79" s="6"/>
       <c r="F79" s="6"/>
     </row>
-    <row r="80" spans="2:6" ht="30">
+    <row r="80" spans="2:6" ht="29">
       <c r="B80" s="5">
         <v>21.2</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D80" s="6"/>
       <c r="E80" s="6"/>
@@ -12187,36 +12638,36 @@
     </row>
     <row r="81" spans="2:6">
       <c r="B81" s="5" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>324</v>
       </c>
       <c r="D81" s="6"/>
       <c r="E81" s="16" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F81" s="6"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="5" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D82" s="6"/>
       <c r="E82" s="16" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F82" s="6"/>
     </row>
     <row r="83" spans="2:6">
       <c r="B83" s="5" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D83" s="6"/>
       <c r="E83" s="16"/>
@@ -12224,34 +12675,34 @@
     </row>
     <row r="84" spans="2:6">
       <c r="B84" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="C84" s="6" t="s">
         <v>486</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>488</v>
       </c>
       <c r="D84" s="6"/>
       <c r="E84" s="16"/>
       <c r="F84" s="6"/>
     </row>
-    <row r="85" spans="2:6" ht="60">
+    <row r="85" spans="2:6" ht="58">
       <c r="B85" s="5" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C85" s="79" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D85" s="6"/>
       <c r="E85" s="16" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F85" s="6"/>
     </row>
-    <row r="86" spans="2:6" ht="30">
+    <row r="86" spans="2:6" ht="29">
       <c r="B86" s="5" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D86" s="6"/>
       <c r="E86" s="16"/>
@@ -12259,32 +12710,32 @@
     </row>
     <row r="87" spans="2:6">
       <c r="B87" s="5" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D87" s="6"/>
       <c r="E87" s="16"/>
       <c r="F87" s="6"/>
     </row>
-    <row r="88" spans="2:6" ht="60">
+    <row r="88" spans="2:6" ht="58">
       <c r="B88" s="5" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D88" s="6"/>
       <c r="E88" s="16"/>
       <c r="F88" s="6"/>
     </row>
-    <row r="89" spans="2:6" ht="30">
+    <row r="89" spans="2:6" ht="29">
       <c r="B89" s="5" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D89" s="6"/>
       <c r="E89" s="16"/>
@@ -12292,14 +12743,14 @@
     </row>
     <row r="90" spans="2:6">
       <c r="B90" s="77" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C90" s="57" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D90" s="1"/>
       <c r="E90" s="49" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F90" s="1"/>
     </row>
@@ -12357,6 +12808,8 @@
     <hyperlink ref="E82" r:id="rId10"/>
     <hyperlink ref="E90" r:id="rId11"/>
     <hyperlink ref="F49" location="'#9'!B2" display="Link"/>
+    <hyperlink ref="F52" location="'#12'!B2" display="Link"/>
+    <hyperlink ref="F57" location="'#16'!B2" display="Link"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId12"/>
@@ -12366,13 +12819,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J164"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" customWidth="1"/>
+    <col min="1" max="1" width="4.26953125" customWidth="1"/>
+    <col min="2" max="2" width="6.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75">
+    <row r="1" spans="1:3" ht="18.5">
       <c r="C1" s="41" t="s">
         <v>15</v>
       </c>
@@ -12629,14 +13082,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L61"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="3" max="3" width="10.42578125" customWidth="1"/>
-    <col min="4" max="4" width="5.28515625" customWidth="1"/>
-    <col min="5" max="5" width="48.85546875" customWidth="1"/>
+    <col min="3" max="3" width="10.453125" customWidth="1"/>
+    <col min="4" max="4" width="5.26953125" customWidth="1"/>
+    <col min="5" max="5" width="48.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75">
+    <row r="1" spans="1:10" ht="18.5">
       <c r="C1" s="41" t="s">
         <v>57</v>
       </c>
@@ -12667,13 +13120,13 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15.75" thickBot="1">
+    <row r="12" spans="1:10" ht="15" thickBot="1">
       <c r="C12" s="11" t="s">
         <v>63</v>
       </c>
       <c r="D12" s="11"/>
     </row>
-    <row r="13" spans="1:10" ht="15.75" thickBot="1">
+    <row r="13" spans="1:10" ht="15" thickBot="1">
       <c r="C13" s="80" t="s">
         <v>78</v>
       </c>
@@ -12690,7 +13143,7 @@
       <c r="H13" s="24"/>
       <c r="I13" s="25"/>
     </row>
-    <row r="14" spans="1:10" ht="15.75" thickBot="1">
+    <row r="14" spans="1:10" ht="15" thickBot="1">
       <c r="C14" s="81"/>
       <c r="D14" s="23" t="s">
         <v>65</v>
@@ -12732,7 +13185,7 @@
       <c r="H16" s="30"/>
       <c r="I16" s="31"/>
     </row>
-    <row r="17" spans="3:12" ht="15.75" thickBot="1">
+    <row r="17" spans="3:12" ht="15" thickBot="1">
       <c r="C17" s="82"/>
       <c r="D17" s="32"/>
       <c r="E17" s="33" t="s">
@@ -12743,7 +13196,7 @@
       <c r="H17" s="30"/>
       <c r="I17" s="31"/>
     </row>
-    <row r="18" spans="3:12" ht="15.75" thickBot="1">
+    <row r="18" spans="3:12" ht="15" thickBot="1">
       <c r="C18" s="37" t="s">
         <v>79</v>
       </c>
@@ -12763,7 +13216,7 @@
       <c r="K18" s="24"/>
       <c r="L18" s="25"/>
     </row>
-    <row r="19" spans="3:12" ht="15.75" thickBot="1">
+    <row r="19" spans="3:12" ht="15" thickBot="1">
       <c r="C19" s="80" t="s">
         <v>78</v>
       </c>
@@ -12783,7 +13236,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="3:12" ht="15.75" thickBot="1">
+    <row r="21" spans="3:12" ht="15" thickBot="1">
       <c r="C21" s="82"/>
       <c r="D21" s="32"/>
       <c r="E21" s="40" t="s">
@@ -12897,10 +13350,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:V102"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="13" max="13" width="4.85546875" customWidth="1"/>
+    <col min="13" max="13" width="4.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
@@ -13415,7 +13868,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D32"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" s="6" t="s">
@@ -13538,10 +13991,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:H90"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="4" max="4" width="13.5703125" customWidth="1"/>
-    <col min="7" max="7" width="9.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" customWidth="1"/>
+    <col min="7" max="7" width="9.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4">
@@ -13907,9 +14360,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Z40"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="4" max="4" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:26">

--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" firstSheet="1" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="3" activeTab="16"/>
   </bookViews>
   <sheets>
     <sheet name="Knowhow" sheetId="1" r:id="rId1"/>
@@ -19,9 +19,11 @@
     <sheet name="#7" sheetId="10" r:id="rId10"/>
     <sheet name="#8" sheetId="11" r:id="rId11"/>
     <sheet name="#9" sheetId="13" r:id="rId12"/>
-    <sheet name="#12" sheetId="14" r:id="rId13"/>
-    <sheet name="#14" sheetId="12" r:id="rId14"/>
-    <sheet name="#16" sheetId="15" r:id="rId15"/>
+    <sheet name="#10" sheetId="16" r:id="rId13"/>
+    <sheet name="#12" sheetId="14" r:id="rId14"/>
+    <sheet name="#13" sheetId="17" r:id="rId15"/>
+    <sheet name="#14" sheetId="12" r:id="rId16"/>
+    <sheet name="#16" sheetId="15" r:id="rId17"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="601">
   <si>
     <t>No.</t>
   </si>
@@ -1641,9 +1643,6 @@
   </si>
   <si>
     <t>// Thư viện của backtrace</t>
-  </si>
-  <si>
-    <t>Gmock</t>
   </si>
   <si>
     <t>#8</t>
@@ -4027,9 +4026,6 @@
     </r>
   </si>
   <si>
-    <t>Điền triển khai qua VDI trên cty vào đây</t>
-  </si>
-  <si>
     <t>Sự khác biệt giữa ++i và i++</t>
   </si>
   <si>
@@ -4184,13 +4180,976 @@
   </si>
   <si>
     <t>Không thể truy cập từ bên ngoài class, chỉ có thể truy cập từ class thuộc hệ thống kế thừa</t>
+  </si>
+  <si>
+    <t>Cấu trúc 1 folder Gtest tích hợp Cmake</t>
+  </si>
+  <si>
+    <t>my_project/</t>
+  </si>
+  <si>
+    <t>│   └── mylib/</t>
+  </si>
+  <si>
+    <t>│       ├── include/</t>
+  </si>
+  <si>
+    <t>│       │   └── mylib/</t>
+  </si>
+  <si>
+    <t>│       │       └── math_util.h</t>
+  </si>
+  <si>
+    <t>│       └── src/</t>
+  </si>
+  <si>
+    <t>│           └── math_util.cpp</t>
+  </si>
+  <si>
+    <t>│   └── test_math_util.cpp</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">│   ├── </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CMakeLists.txt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">        # build library/app</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">│   ├── </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CMakeLists.txt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">        # build tests</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">├── </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CMakeLists.txt</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">├── </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCC00FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>src</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">├── </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCC00FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tests</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/</t>
+    </r>
+  </si>
+  <si>
+    <t>└── third_party/              # (tuỳ chọn) ví dụ thêm Gcovr để gen HTML xem độ bao phủ</t>
+  </si>
+  <si>
+    <r>
+      <t>#include</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"gtest/gtest.h"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#include</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"mylib.h"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>TEST</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(AddTest, HandlesPositiveInput) {</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>EXPECT_EQ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>add</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>EXPECT_EQ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>add</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>TEST</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(AddTest, HandlesNegativeInput) {</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>EXPECT_EQ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>add</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>EXPECT_EQ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>add</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <t>Cấu trúc file test của gtest</t>
+  </si>
+  <si>
+    <t>Gtest, Vector Gtest (Gmock)</t>
+  </si>
+  <si>
+    <t>Kết hợp Gtest, Cmake, Gcovr</t>
+  </si>
+  <si>
+    <t>// include thư viện của Gtest</t>
+  </si>
+  <si>
+    <t>// include thư viện cần test</t>
+  </si>
+  <si>
+    <t>Hàm TEST ( Truyền vào 2 đối số có thể đặt tên theo ý thích : TestSuiteName, TestName)</t>
+  </si>
+  <si>
+    <t>// EXPECT_EQ (val1 , val2) : hàm phổ biến nhất, để so sánh 2 giá trị với nhau</t>
+  </si>
+  <si>
+    <t>Nếu có nhiều File test, có thể viết tập trung chạy hết các test ở hàm main() - file main.cpp như sau :</t>
+  </si>
+  <si>
+    <t>#include &lt;gtest/gtest.h&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ::testing::InitGoogleTest(&amp;argc, argv);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return RUN_ALL_TESTS(); // chạy tất cả các TEST() đã định nghĩa</t>
+  </si>
+  <si>
+    <t>Hoặc nếu có Cmake rồi thì không cần viết lại nữa, chỉ cần add lệnh :</t>
+  </si>
+  <si>
+    <t>add_executable(MyTests test_add.cpp)</t>
+  </si>
+  <si>
+    <t>target_link_libraries(MyTests PRIVATE gtest_main)</t>
+  </si>
+  <si>
+    <t>Cách add Gtest vào Cmake</t>
+  </si>
+  <si>
+    <r>
+      <t>add_subdirectory</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(external/googletest/googletest-1.15.0)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>enable_testing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>()</t>
+    </r>
+  </si>
+  <si>
+    <t>Đầu file CmakeLists.txt viết</t>
+  </si>
+  <si>
+    <r>
+      <t>target_link_libraries</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(tests PRIVATE add gtest_main)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>include</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(GoogleTest)</t>
+    </r>
+  </si>
+  <si>
+    <t>gtest_discover_tests(tests)</t>
+  </si>
+  <si>
+    <t>Cuối file CmakeLists.txt viết</t>
+  </si>
+  <si>
+    <t>Cop Gtest về và giải nén, để vào folder tương ứng</t>
+  </si>
+  <si>
+    <t>Cách add Gcovr vào Gtest, Cmake</t>
+  </si>
+  <si>
+    <t>Để run</t>
+  </si>
+  <si>
+    <t>Ctrl+Shift+P</t>
+  </si>
+  <si>
+    <t>Cmake: Build</t>
+  </si>
+  <si>
+    <t>Cmake: Run without debugging</t>
+  </si>
+  <si>
+    <t>Cài Gcovr vào máy bằng Python</t>
+  </si>
+  <si>
+    <t>Điền thêm nội dung như sau vào file CmakeLists.txt</t>
+  </si>
+  <si>
+    <r>
+      <t>option</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">(CODE_COVERAGE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Enable coverage reporting"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ON</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>if</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">(CODE_COVERAGE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>AND</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> CMAKE_CXX_COMPILER_ID </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>MATCHES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"GNU|Clang"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>    message</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">(STATUS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"&gt;&gt; Code coverage enabled"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>    add_compile_options</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(--coverage -O0 -g)</t>
+    </r>
+  </si>
+  <si>
+    <t>    add_link_options(--coverage)</t>
+  </si>
+  <si>
+    <r>
+      <t>endif</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>()</t>
+    </r>
+  </si>
+  <si>
+    <t>cmake --build build</t>
+  </si>
+  <si>
+    <t>cd build</t>
+  </si>
+  <si>
+    <t>ctest</t>
+  </si>
+  <si>
+    <t>gcovr -r .. --html --html-details -o coverage.html</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4317,8 +5276,38 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFCCCCCC"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFCE9178"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFDCDCAA"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFB5CEA8"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFD4D4D4"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4382,6 +5371,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4579,7 +5592,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -4738,6 +5751,30 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4747,7 +5784,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -8521,6 +9557,99 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>86157</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>9683</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6743700" y="4400550"/>
+          <a:ext cx="3096057" cy="1133633"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Straight Arrow Connector 3"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6057900" y="4486275"/>
+          <a:ext cx="790575" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -8785,19 +9914,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:K22"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="5.7265625" customWidth="1"/>
-    <col min="3" max="3" width="37.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.453125" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" customWidth="1"/>
+    <col min="3" max="3" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.42578125" customWidth="1"/>
     <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="18.5">
+    <row r="2" spans="2:11" ht="18.75">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -8823,7 +9952,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:11" ht="43.5">
+    <row r="3" spans="2:11" ht="45">
       <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
@@ -9177,24 +10306,24 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Q30"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="11" max="11" width="3.7265625" customWidth="1"/>
+    <col min="11" max="11" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:17">
       <c r="B2" s="57" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" spans="2:17">
       <c r="C3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="2:17">
       <c r="C4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="2:17">
@@ -9202,12 +10331,12 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" spans="2:17">
       <c r="D6" s="58" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E6" s="59"/>
       <c r="F6" s="59"/>
@@ -9217,7 +10346,7 @@
       <c r="J6" s="59"/>
       <c r="K6" s="60"/>
       <c r="L6" s="61" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="M6" s="44"/>
       <c r="N6" s="44"/>
@@ -9228,7 +10357,7 @@
     <row r="7" spans="2:17">
       <c r="D7" s="59"/>
       <c r="E7" s="59" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F7" s="59"/>
       <c r="G7" s="59"/>
@@ -9238,7 +10367,7 @@
       <c r="K7" s="60"/>
       <c r="L7" s="44"/>
       <c r="M7" s="44" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="N7" s="44"/>
       <c r="O7" s="44"/>
@@ -9248,7 +10377,7 @@
     <row r="8" spans="2:17">
       <c r="D8" s="59"/>
       <c r="E8" s="59" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F8" s="59"/>
       <c r="G8" s="59"/>
@@ -9258,7 +10387,7 @@
       <c r="K8" s="60"/>
       <c r="L8" s="44"/>
       <c r="M8" s="44" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="N8" s="44"/>
       <c r="O8" s="44"/>
@@ -9304,7 +10433,7 @@
     <row r="11" spans="2:17">
       <c r="D11" s="59"/>
       <c r="E11" s="59" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F11" s="59"/>
       <c r="G11" s="59"/>
@@ -9314,7 +10443,7 @@
       <c r="K11" s="60"/>
       <c r="L11" s="44"/>
       <c r="M11" s="44" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="N11" s="44"/>
       <c r="O11" s="44"/>
@@ -9324,7 +10453,7 @@
     <row r="12" spans="2:17">
       <c r="D12" s="59"/>
       <c r="E12" s="59" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F12" s="59"/>
       <c r="G12" s="59"/>
@@ -9334,7 +10463,7 @@
       <c r="K12" s="60"/>
       <c r="L12" s="44"/>
       <c r="M12" s="44" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="N12" s="44"/>
       <c r="O12" s="44"/>
@@ -9344,7 +10473,7 @@
     <row r="13" spans="2:17">
       <c r="D13" s="59"/>
       <c r="E13" s="59" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F13" s="59"/>
       <c r="G13" s="59"/>
@@ -9354,7 +10483,7 @@
       <c r="K13" s="60"/>
       <c r="L13" s="44"/>
       <c r="M13" s="44" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="N13" s="44"/>
       <c r="O13" s="44"/>
@@ -9364,7 +10493,7 @@
     <row r="14" spans="2:17">
       <c r="D14" s="59"/>
       <c r="E14" s="59" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F14" s="59"/>
       <c r="G14" s="59"/>
@@ -9374,7 +10503,7 @@
       <c r="K14" s="60"/>
       <c r="L14" s="44"/>
       <c r="M14" s="44" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="N14" s="44"/>
       <c r="O14" s="44"/>
@@ -9394,7 +10523,7 @@
       <c r="K15" s="60"/>
       <c r="L15" s="44"/>
       <c r="M15" s="44" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N15" s="44"/>
       <c r="O15" s="44"/>
@@ -9424,12 +10553,12 @@
         <v>2</v>
       </c>
       <c r="D18" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="19" spans="3:8">
       <c r="E19" s="62" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F19" s="62"/>
       <c r="G19" s="62"/>
@@ -9437,7 +10566,7 @@
     </row>
     <row r="20" spans="3:8">
       <c r="E20" s="62" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F20" s="62"/>
       <c r="G20" s="62"/>
@@ -9445,7 +10574,7 @@
     </row>
     <row r="21" spans="3:8">
       <c r="E21" s="62" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F21" s="62"/>
       <c r="G21" s="62"/>
@@ -9469,28 +10598,28 @@
     </row>
     <row r="25" spans="3:8">
       <c r="D25" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="26" spans="3:8">
       <c r="D26" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="27" spans="3:8">
       <c r="E27" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F27" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="28" spans="3:8">
       <c r="E28" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F28" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="30" spans="3:8">
@@ -9498,7 +10627,7 @@
         <v>3</v>
       </c>
       <c r="D30" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -9509,50 +10638,50 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E76"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="4.453125" customWidth="1"/>
-    <col min="3" max="3" width="39.7265625" customWidth="1"/>
-    <col min="4" max="4" width="50.81640625" customWidth="1"/>
-    <col min="5" max="5" width="75.453125" customWidth="1"/>
+    <col min="2" max="2" width="4.42578125" customWidth="1"/>
+    <col min="3" max="3" width="39.7109375" customWidth="1"/>
+    <col min="4" max="4" width="50.85546875" customWidth="1"/>
+    <col min="5" max="5" width="75.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.5">
       <c r="A1" s="68" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="23.5">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="23.25">
       <c r="B2" s="63" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="B4" s="71" t="s">
+        <v>335</v>
+      </c>
+      <c r="C4" s="71" t="s">
         <v>336</v>
       </c>
-      <c r="C4" s="71" t="s">
+      <c r="D4" s="71" t="s">
         <v>337</v>
       </c>
-      <c r="D4" s="71" t="s">
-        <v>338</v>
-      </c>
       <c r="E4" s="72" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="43.5">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="45">
       <c r="B5" s="69">
         <v>1</v>
       </c>
       <c r="C5" s="70" t="s">
+        <v>338</v>
+      </c>
+      <c r="D5" s="69" t="s">
         <v>339</v>
       </c>
-      <c r="D5" s="69" t="s">
-        <v>340</v>
-      </c>
       <c r="E5" s="69" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="81" customHeight="1">
@@ -9560,177 +10689,177 @@
         <v>2</v>
       </c>
       <c r="C6" s="70" t="s">
+        <v>340</v>
+      </c>
+      <c r="D6" s="69" t="s">
         <v>341</v>
       </c>
-      <c r="D6" s="69" t="s">
-        <v>342</v>
-      </c>
       <c r="E6" s="69" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="29">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="30">
       <c r="B7" s="69">
         <v>3</v>
       </c>
       <c r="C7" s="70" t="s">
+        <v>342</v>
+      </c>
+      <c r="D7" s="69" t="s">
         <v>343</v>
       </c>
-      <c r="D7" s="69" t="s">
+      <c r="E7" s="5" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="23.25">
+      <c r="B10" s="63" t="s">
         <v>344</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="23.5">
-      <c r="B10" s="63" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="B12" s="73" t="s">
+        <v>335</v>
+      </c>
+      <c r="C12" s="73" t="s">
         <v>336</v>
       </c>
-      <c r="C12" s="73" t="s">
+      <c r="D12" s="73" t="s">
         <v>337</v>
       </c>
-      <c r="D12" s="73" t="s">
-        <v>338</v>
-      </c>
       <c r="E12" s="74" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="30">
       <c r="B13" s="69">
         <v>1</v>
       </c>
       <c r="C13" s="70" t="s">
+        <v>345</v>
+      </c>
+      <c r="D13" s="69" t="s">
         <v>346</v>
       </c>
-      <c r="D13" s="69" t="s">
-        <v>347</v>
-      </c>
       <c r="E13" s="69" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="29">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="30">
       <c r="B14" s="69">
         <v>2</v>
       </c>
       <c r="C14" s="70" t="s">
+        <v>347</v>
+      </c>
+      <c r="D14" s="69" t="s">
         <v>348</v>
       </c>
-      <c r="D14" s="69" t="s">
-        <v>349</v>
-      </c>
       <c r="E14" s="69" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="29">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="30">
       <c r="B15" s="69">
         <v>3</v>
       </c>
       <c r="C15" s="70" t="s">
+        <v>349</v>
+      </c>
+      <c r="D15" s="69" t="s">
         <v>350</v>
       </c>
-      <c r="D15" s="69" t="s">
-        <v>351</v>
-      </c>
       <c r="E15" s="69" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="29">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="30">
       <c r="B16" s="69">
         <v>4</v>
       </c>
       <c r="C16" s="70" t="s">
+        <v>351</v>
+      </c>
+      <c r="D16" s="69" t="s">
         <v>352</v>
       </c>
-      <c r="D16" s="69" t="s">
-        <v>353</v>
-      </c>
       <c r="E16" s="75" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" ht="145">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="165">
       <c r="B17" s="69">
         <v>5</v>
       </c>
       <c r="C17" s="70" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D17" s="69" t="s">
+        <v>429</v>
+      </c>
+      <c r="E17" s="75" t="s">
         <v>430</v>
       </c>
-      <c r="E17" s="75" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" ht="159.5">
+    </row>
+    <row r="18" spans="2:5" ht="180">
       <c r="B18" s="69">
         <v>6</v>
       </c>
       <c r="C18" s="70" t="s">
+        <v>354</v>
+      </c>
+      <c r="D18" s="69" t="s">
         <v>355</v>
       </c>
-      <c r="D18" s="69" t="s">
-        <v>356</v>
-      </c>
       <c r="E18" s="75" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" ht="130.5">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="135">
       <c r="B19" s="69">
         <v>7</v>
       </c>
       <c r="C19" s="70" t="s">
+        <v>356</v>
+      </c>
+      <c r="D19" s="69" t="s">
         <v>357</v>
       </c>
-      <c r="D19" s="69" t="s">
-        <v>358</v>
-      </c>
       <c r="E19" s="75" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" ht="130.5">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" ht="135">
       <c r="B20" s="69">
         <v>8</v>
       </c>
       <c r="C20" s="70" t="s">
+        <v>358</v>
+      </c>
+      <c r="D20" s="69" t="s">
         <v>359</v>
       </c>
-      <c r="D20" s="69" t="s">
-        <v>360</v>
-      </c>
       <c r="E20" s="75" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" ht="23.5">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" ht="23.25">
       <c r="B23" s="63" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="25" spans="2:5">
       <c r="B25" s="73" t="s">
+        <v>335</v>
+      </c>
+      <c r="C25" s="73" t="s">
         <v>336</v>
       </c>
-      <c r="C25" s="73" t="s">
+      <c r="D25" s="73" t="s">
         <v>337</v>
       </c>
-      <c r="D25" s="73" t="s">
-        <v>338</v>
-      </c>
       <c r="E25" s="74" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="26" spans="2:5">
@@ -9738,10 +10867,10 @@
         <v>1</v>
       </c>
       <c r="C26" s="70" t="s">
+        <v>360</v>
+      </c>
+      <c r="D26" s="69" t="s">
         <v>361</v>
-      </c>
-      <c r="D26" s="69" t="s">
-        <v>362</v>
       </c>
       <c r="E26" s="1"/>
     </row>
@@ -9750,10 +10879,10 @@
         <v>2</v>
       </c>
       <c r="C27" s="70" t="s">
+        <v>362</v>
+      </c>
+      <c r="D27" s="69" t="s">
         <v>363</v>
-      </c>
-      <c r="D27" s="69" t="s">
-        <v>364</v>
       </c>
       <c r="E27" s="1"/>
     </row>
@@ -9762,10 +10891,10 @@
         <v>3</v>
       </c>
       <c r="C28" s="70" t="s">
+        <v>364</v>
+      </c>
+      <c r="D28" s="69" t="s">
         <v>365</v>
-      </c>
-      <c r="D28" s="69" t="s">
-        <v>366</v>
       </c>
       <c r="E28" s="1"/>
     </row>
@@ -9774,38 +10903,38 @@
         <v>4</v>
       </c>
       <c r="C29" s="70" t="s">
+        <v>366</v>
+      </c>
+      <c r="D29" s="69" t="s">
         <v>367</v>
       </c>
-      <c r="D29" s="69" t="s">
-        <v>368</v>
-      </c>
       <c r="E29" s="1"/>
     </row>
-    <row r="32" spans="2:5" ht="23.5">
+    <row r="32" spans="2:5" ht="23.25">
       <c r="B32" s="63" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="64" t="s">
+        <v>335</v>
+      </c>
+      <c r="C34" s="64" t="s">
         <v>336</v>
       </c>
-      <c r="C34" s="64" t="s">
+      <c r="D34" s="64" t="s">
         <v>337</v>
       </c>
-      <c r="D34" s="64" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" ht="29">
+    </row>
+    <row r="35" spans="2:4" ht="30">
       <c r="B35" s="65">
         <v>1</v>
       </c>
       <c r="C35" s="66" t="s">
+        <v>368</v>
+      </c>
+      <c r="D35" s="65" t="s">
         <v>369</v>
-      </c>
-      <c r="D35" s="65" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="36" spans="2:4">
@@ -9813,21 +10942,21 @@
         <v>2</v>
       </c>
       <c r="C36" s="66" t="s">
+        <v>370</v>
+      </c>
+      <c r="D36" s="65" t="s">
         <v>371</v>
       </c>
-      <c r="D36" s="65" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4">
+    </row>
+    <row r="37" spans="2:4" ht="30">
       <c r="B37" s="65">
         <v>3</v>
       </c>
       <c r="C37" s="66" t="s">
+        <v>372</v>
+      </c>
+      <c r="D37" s="65" t="s">
         <v>373</v>
-      </c>
-      <c r="D37" s="65" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="38" spans="2:4">
@@ -9835,37 +10964,37 @@
         <v>4</v>
       </c>
       <c r="C38" s="66" t="s">
+        <v>374</v>
+      </c>
+      <c r="D38" s="65" t="s">
         <v>375</v>
       </c>
-      <c r="D38" s="65" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4" ht="23.5">
+    </row>
+    <row r="41" spans="2:4" ht="23.25">
       <c r="B41" s="63" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="64" t="s">
+        <v>335</v>
+      </c>
+      <c r="C43" s="64" t="s">
         <v>336</v>
       </c>
-      <c r="C43" s="64" t="s">
+      <c r="D43" s="64" t="s">
         <v>337</v>
       </c>
-      <c r="D43" s="64" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4">
+    </row>
+    <row r="44" spans="2:4" ht="30">
       <c r="B44" s="65">
         <v>1</v>
       </c>
       <c r="C44" s="66" t="s">
+        <v>376</v>
+      </c>
+      <c r="D44" s="65" t="s">
         <v>377</v>
-      </c>
-      <c r="D44" s="65" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="45" spans="2:4">
@@ -9873,10 +11002,10 @@
         <v>2</v>
       </c>
       <c r="C45" s="66" t="s">
+        <v>378</v>
+      </c>
+      <c r="D45" s="65" t="s">
         <v>379</v>
-      </c>
-      <c r="D45" s="65" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="46" spans="2:4">
@@ -9884,10 +11013,10 @@
         <v>3</v>
       </c>
       <c r="C46" s="67" t="s">
+        <v>380</v>
+      </c>
+      <c r="D46" s="65" t="s">
         <v>381</v>
-      </c>
-      <c r="D46" s="65" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="47" spans="2:4">
@@ -9895,26 +11024,26 @@
         <v>4</v>
       </c>
       <c r="C47" s="67" t="s">
+        <v>382</v>
+      </c>
+      <c r="D47" s="65" t="s">
         <v>383</v>
       </c>
-      <c r="D47" s="65" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="50" spans="2:4" ht="23.5">
+    </row>
+    <row r="50" spans="2:4" ht="23.25">
       <c r="B50" s="63" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="52" spans="2:4">
       <c r="B52" s="64" t="s">
+        <v>335</v>
+      </c>
+      <c r="C52" s="64" t="s">
         <v>336</v>
       </c>
-      <c r="C52" s="64" t="s">
+      <c r="D52" s="64" t="s">
         <v>337</v>
-      </c>
-      <c r="D52" s="64" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="53" spans="2:4">
@@ -9922,10 +11051,10 @@
         <v>1</v>
       </c>
       <c r="C53" s="66" t="s">
+        <v>384</v>
+      </c>
+      <c r="D53" s="65" t="s">
         <v>385</v>
-      </c>
-      <c r="D53" s="65" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="54" spans="2:4">
@@ -9933,10 +11062,10 @@
         <v>2</v>
       </c>
       <c r="C54" s="66" t="s">
+        <v>386</v>
+      </c>
+      <c r="D54" s="65" t="s">
         <v>387</v>
-      </c>
-      <c r="D54" s="65" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="55" spans="2:4">
@@ -9944,29 +11073,29 @@
         <v>3</v>
       </c>
       <c r="C55" s="66" t="s">
+        <v>388</v>
+      </c>
+      <c r="D55" s="65" t="s">
         <v>389</v>
-      </c>
-      <c r="D55" s="65" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="56" spans="2:4">
       <c r="B56" s="65"/>
     </row>
-    <row r="58" spans="2:4" ht="23.5">
+    <row r="58" spans="2:4" ht="23.25">
       <c r="B58" s="63" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="60" spans="2:4">
       <c r="B60" s="64" t="s">
+        <v>335</v>
+      </c>
+      <c r="C60" s="64" t="s">
         <v>336</v>
       </c>
-      <c r="C60" s="64" t="s">
+      <c r="D60" s="64" t="s">
         <v>337</v>
-      </c>
-      <c r="D60" s="64" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="61" spans="2:4">
@@ -9974,32 +11103,32 @@
         <v>1</v>
       </c>
       <c r="C61" s="66" t="s">
+        <v>390</v>
+      </c>
+      <c r="D61" s="65" t="s">
         <v>391</v>
       </c>
-      <c r="D61" s="65" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="62" spans="2:4" ht="29">
+    </row>
+    <row r="62" spans="2:4" ht="45">
       <c r="B62" s="65">
         <v>2</v>
       </c>
       <c r="C62" s="66" t="s">
+        <v>392</v>
+      </c>
+      <c r="D62" s="65" t="s">
         <v>393</v>
       </c>
-      <c r="D62" s="65" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="63" spans="2:4" ht="29">
+    </row>
+    <row r="63" spans="2:4" ht="30">
       <c r="B63" s="65">
         <v>3</v>
       </c>
       <c r="C63" s="66" t="s">
+        <v>394</v>
+      </c>
+      <c r="D63" s="65" t="s">
         <v>395</v>
-      </c>
-      <c r="D63" s="65" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="64" spans="2:4">
@@ -10007,10 +11136,10 @@
         <v>4</v>
       </c>
       <c r="C64" s="66" t="s">
+        <v>396</v>
+      </c>
+      <c r="D64" s="65" t="s">
         <v>397</v>
-      </c>
-      <c r="D64" s="65" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="65" spans="2:4">
@@ -10018,26 +11147,26 @@
         <v>5</v>
       </c>
       <c r="C65" s="66" t="s">
+        <v>398</v>
+      </c>
+      <c r="D65" s="65" t="s">
         <v>399</v>
       </c>
-      <c r="D65" s="65" t="s">
+    </row>
+    <row r="68" spans="2:4" ht="23.25">
+      <c r="B68" s="63" t="s">
         <v>400</v>
-      </c>
-    </row>
-    <row r="68" spans="2:4" ht="23.5">
-      <c r="B68" s="63" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="70" spans="2:4">
       <c r="B70" s="64" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C70" s="64" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D70" s="64" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="71" spans="2:4">
@@ -10045,10 +11174,10 @@
         <v>1</v>
       </c>
       <c r="C71" s="65" t="s">
+        <v>402</v>
+      </c>
+      <c r="D71" s="65" t="s">
         <v>403</v>
-      </c>
-      <c r="D71" s="65" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="72" spans="2:4">
@@ -10056,10 +11185,10 @@
         <v>2</v>
       </c>
       <c r="C72" s="65" t="s">
+        <v>404</v>
+      </c>
+      <c r="D72" s="65" t="s">
         <v>405</v>
-      </c>
-      <c r="D72" s="65" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="73" spans="2:4">
@@ -10067,10 +11196,10 @@
         <v>3</v>
       </c>
       <c r="C73" s="65" t="s">
+        <v>406</v>
+      </c>
+      <c r="D73" s="65" t="s">
         <v>407</v>
-      </c>
-      <c r="D73" s="65" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="74" spans="2:4">
@@ -10078,10 +11207,10 @@
         <v>4</v>
       </c>
       <c r="C74" s="65" t="s">
+        <v>408</v>
+      </c>
+      <c r="D74" s="65" t="s">
         <v>409</v>
-      </c>
-      <c r="D74" s="65" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="75" spans="2:4">
@@ -10089,10 +11218,10 @@
         <v>5</v>
       </c>
       <c r="C75" s="65" t="s">
+        <v>410</v>
+      </c>
+      <c r="D75" s="65" t="s">
         <v>411</v>
-      </c>
-      <c r="D75" s="65" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="76" spans="2:4">
@@ -10100,10 +11229,10 @@
         <v>6</v>
       </c>
       <c r="C76" s="65" t="s">
+        <v>412</v>
+      </c>
+      <c r="D76" s="65" t="s">
         <v>413</v>
-      </c>
-      <c r="D76" s="65" t="s">
-        <v>414</v>
       </c>
     </row>
   </sheetData>
@@ -10114,156 +11243,735 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:E14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="B2:S38"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3" spans="2:5">
       <c r="C3" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5" spans="2:5">
       <c r="C5" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="D6" t="s">
+        <v>502</v>
+      </c>
+      <c r="E6" t="s">
         <v>503</v>
-      </c>
-      <c r="E6" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="D7" t="s">
+        <v>504</v>
+      </c>
+      <c r="E7" t="s">
         <v>505</v>
-      </c>
-      <c r="E7" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="C9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="C11" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="D12" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5">
-      <c r="C14" t="s">
-        <v>510</v>
-      </c>
+        <v>508</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5">
+      <c r="C15" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="17" spans="3:19">
+      <c r="D17" s="83" t="s">
+        <v>553</v>
+      </c>
+      <c r="E17" s="87"/>
+      <c r="F17" s="87"/>
+      <c r="G17" s="87"/>
+      <c r="H17" s="87"/>
+      <c r="I17" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19">
+      <c r="D18" s="83" t="s">
+        <v>554</v>
+      </c>
+      <c r="E18" s="87"/>
+      <c r="F18" s="87"/>
+      <c r="G18" s="87"/>
+      <c r="H18" s="87"/>
+      <c r="I18" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19">
+      <c r="D19" s="84"/>
+      <c r="E19" s="87"/>
+      <c r="F19" s="87"/>
+      <c r="G19" s="87"/>
+      <c r="H19" s="87"/>
+    </row>
+    <row r="20" spans="3:19">
+      <c r="D20" s="85" t="s">
+        <v>555</v>
+      </c>
+      <c r="E20" s="87"/>
+      <c r="F20" s="87"/>
+      <c r="G20" s="87"/>
+      <c r="H20" s="87"/>
+      <c r="I20" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19">
+      <c r="D21" s="86" t="s">
+        <v>556</v>
+      </c>
+      <c r="E21" s="87"/>
+      <c r="F21" s="87"/>
+      <c r="G21" s="87"/>
+      <c r="H21" s="87"/>
+      <c r="I21" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19">
+      <c r="D22" s="86" t="s">
+        <v>557</v>
+      </c>
+      <c r="E22" s="87"/>
+      <c r="F22" s="87"/>
+      <c r="G22" s="87"/>
+      <c r="H22" s="87"/>
+    </row>
+    <row r="23" spans="3:19">
+      <c r="D23" s="86" t="s">
+        <v>284</v>
+      </c>
+      <c r="E23" s="87"/>
+      <c r="F23" s="87"/>
+      <c r="G23" s="87"/>
+      <c r="H23" s="87"/>
+    </row>
+    <row r="24" spans="3:19">
+      <c r="D24" s="84"/>
+      <c r="E24" s="87"/>
+      <c r="F24" s="87"/>
+      <c r="G24" s="87"/>
+      <c r="H24" s="87"/>
+    </row>
+    <row r="25" spans="3:19">
+      <c r="D25" s="85" t="s">
+        <v>558</v>
+      </c>
+      <c r="E25" s="87"/>
+      <c r="F25" s="87"/>
+      <c r="G25" s="87"/>
+      <c r="H25" s="87"/>
+    </row>
+    <row r="26" spans="3:19">
+      <c r="D26" s="86" t="s">
+        <v>559</v>
+      </c>
+      <c r="E26" s="87"/>
+      <c r="F26" s="87"/>
+      <c r="G26" s="87"/>
+      <c r="H26" s="87"/>
+    </row>
+    <row r="27" spans="3:19">
+      <c r="D27" s="86" t="s">
+        <v>560</v>
+      </c>
+      <c r="E27" s="87"/>
+      <c r="F27" s="87"/>
+      <c r="G27" s="87"/>
+      <c r="H27" s="87"/>
+    </row>
+    <row r="28" spans="3:19">
+      <c r="D28" s="86" t="s">
+        <v>284</v>
+      </c>
+      <c r="E28" s="87"/>
+      <c r="F28" s="87"/>
+      <c r="G28" s="87"/>
+      <c r="H28" s="87"/>
+    </row>
+    <row r="31" spans="3:19">
+      <c r="C31" s="88" t="s">
+        <v>568</v>
+      </c>
+      <c r="D31" s="88"/>
+      <c r="E31" s="88"/>
+      <c r="F31" s="88"/>
+      <c r="G31" s="88"/>
+      <c r="H31" s="88"/>
+      <c r="I31" s="88"/>
+      <c r="J31" s="88"/>
+      <c r="K31" s="88"/>
+      <c r="L31" s="88"/>
+      <c r="M31" s="89" t="s">
+        <v>572</v>
+      </c>
+      <c r="N31" s="89"/>
+      <c r="O31" s="89"/>
+      <c r="P31" s="89"/>
+      <c r="Q31" s="89"/>
+      <c r="R31" s="89"/>
+      <c r="S31" s="89"/>
+    </row>
+    <row r="32" spans="3:19">
+      <c r="C32" s="88"/>
+      <c r="D32" s="88"/>
+      <c r="E32" s="88"/>
+      <c r="F32" s="88"/>
+      <c r="G32" s="88"/>
+      <c r="H32" s="88"/>
+      <c r="I32" s="88"/>
+      <c r="J32" s="88"/>
+      <c r="K32" s="88"/>
+      <c r="L32" s="88"/>
+      <c r="M32" s="89"/>
+      <c r="N32" s="89"/>
+      <c r="O32" s="89"/>
+      <c r="P32" s="89"/>
+      <c r="Q32" s="89"/>
+      <c r="R32" s="89"/>
+      <c r="S32" s="89"/>
+    </row>
+    <row r="33" spans="3:19">
+      <c r="C33" s="88"/>
+      <c r="D33" s="88" t="s">
+        <v>569</v>
+      </c>
+      <c r="E33" s="88"/>
+      <c r="F33" s="88"/>
+      <c r="G33" s="88"/>
+      <c r="H33" s="88"/>
+      <c r="I33" s="88"/>
+      <c r="J33" s="88"/>
+      <c r="K33" s="88"/>
+      <c r="L33" s="88"/>
+      <c r="M33" s="89" t="s">
+        <v>573</v>
+      </c>
+      <c r="N33" s="89"/>
+      <c r="O33" s="89"/>
+      <c r="P33" s="89"/>
+      <c r="Q33" s="89"/>
+      <c r="R33" s="89"/>
+      <c r="S33" s="89"/>
+    </row>
+    <row r="34" spans="3:19">
+      <c r="C34" s="88"/>
+      <c r="D34" s="88"/>
+      <c r="E34" s="88"/>
+      <c r="F34" s="88"/>
+      <c r="G34" s="88"/>
+      <c r="H34" s="88"/>
+      <c r="I34" s="88"/>
+      <c r="J34" s="88"/>
+      <c r="K34" s="88"/>
+      <c r="L34" s="88"/>
+      <c r="M34" s="89" t="s">
+        <v>574</v>
+      </c>
+      <c r="N34" s="89"/>
+      <c r="O34" s="89"/>
+      <c r="P34" s="89"/>
+      <c r="Q34" s="89"/>
+      <c r="R34" s="89"/>
+      <c r="S34" s="89"/>
+    </row>
+    <row r="35" spans="3:19">
+      <c r="C35" s="88"/>
+      <c r="D35" s="88" t="s">
+        <v>325</v>
+      </c>
+      <c r="E35" s="88"/>
+      <c r="F35" s="88"/>
+      <c r="G35" s="88"/>
+      <c r="H35" s="88"/>
+      <c r="I35" s="88"/>
+      <c r="J35" s="88"/>
+      <c r="K35" s="88"/>
+      <c r="L35" s="88"/>
+      <c r="M35" s="89"/>
+      <c r="N35" s="89"/>
+      <c r="O35" s="89"/>
+      <c r="P35" s="89"/>
+      <c r="Q35" s="89"/>
+      <c r="R35" s="89"/>
+      <c r="S35" s="89"/>
+    </row>
+    <row r="36" spans="3:19">
+      <c r="C36" s="88"/>
+      <c r="D36" s="88" t="s">
+        <v>570</v>
+      </c>
+      <c r="E36" s="88"/>
+      <c r="F36" s="88"/>
+      <c r="G36" s="88"/>
+      <c r="H36" s="88"/>
+      <c r="I36" s="88"/>
+      <c r="J36" s="88"/>
+      <c r="K36" s="88"/>
+      <c r="L36" s="88"/>
+    </row>
+    <row r="37" spans="3:19">
+      <c r="C37" s="88"/>
+      <c r="D37" s="88" t="s">
+        <v>571</v>
+      </c>
+      <c r="E37" s="88"/>
+      <c r="F37" s="88"/>
+      <c r="G37" s="88"/>
+      <c r="H37" s="88"/>
+      <c r="I37" s="88"/>
+      <c r="J37" s="88"/>
+      <c r="K37" s="88"/>
+      <c r="L37" s="88"/>
+    </row>
+    <row r="38" spans="3:19">
+      <c r="C38" s="88"/>
+      <c r="D38" s="88" t="s">
+        <v>284</v>
+      </c>
+      <c r="E38" s="88"/>
+      <c r="F38" s="88"/>
+      <c r="G38" s="88"/>
+      <c r="H38" s="88"/>
+      <c r="I38" s="88"/>
+      <c r="J38" s="88"/>
+      <c r="K38" s="88"/>
+      <c r="L38" s="88"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:E25"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="B2:M57"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
-        <v>511</v>
+        <v>563</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5">
+      <c r="C4" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5">
+      <c r="D6" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5">
+      <c r="D7" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
+      <c r="D8" t="s">
+        <v>550</v>
+      </c>
+      <c r="E8" s="80"/>
+    </row>
+    <row r="9" spans="2:5">
+      <c r="D9" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5">
+      <c r="D10" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5">
+      <c r="D11" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5">
+      <c r="D12" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5">
+      <c r="D13" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5">
+      <c r="D14" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5">
+      <c r="D15" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5">
+      <c r="D16" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="17" spans="3:12">
+      <c r="D17" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="18" spans="3:12">
+      <c r="D18" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="19" spans="3:12">
+      <c r="D19" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="22" spans="3:12">
+      <c r="C22" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="23" spans="3:12">
+      <c r="D23" t="s">
+        <v>578</v>
+      </c>
+      <c r="L23" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="24" spans="3:12">
+      <c r="D24" s="81" t="s">
+        <v>576</v>
+      </c>
+      <c r="E24" s="90"/>
+      <c r="F24" s="90"/>
+      <c r="G24" s="90"/>
+      <c r="H24" s="90"/>
+      <c r="I24" s="90"/>
+      <c r="J24" s="90"/>
+    </row>
+    <row r="25" spans="3:12">
+      <c r="D25" s="81" t="s">
+        <v>577</v>
+      </c>
+      <c r="E25" s="90"/>
+      <c r="F25" s="90"/>
+      <c r="G25" s="90"/>
+      <c r="H25" s="90"/>
+      <c r="I25" s="90"/>
+      <c r="J25" s="90"/>
+    </row>
+    <row r="27" spans="3:12">
+      <c r="D27" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="28" spans="3:12">
+      <c r="D28" s="81" t="s">
+        <v>579</v>
+      </c>
+      <c r="E28" s="90"/>
+      <c r="F28" s="90"/>
+      <c r="G28" s="90"/>
+      <c r="H28" s="90"/>
+      <c r="I28" s="90"/>
+      <c r="J28" s="90"/>
+    </row>
+    <row r="29" spans="3:12">
+      <c r="D29" s="81" t="s">
+        <v>580</v>
+      </c>
+      <c r="E29" s="90"/>
+      <c r="F29" s="90"/>
+      <c r="G29" s="90"/>
+      <c r="H29" s="90"/>
+      <c r="I29" s="90"/>
+      <c r="J29" s="90"/>
+    </row>
+    <row r="30" spans="3:12">
+      <c r="D30" s="82" t="s">
+        <v>581</v>
+      </c>
+      <c r="E30" s="90"/>
+      <c r="F30" s="90"/>
+      <c r="G30" s="90"/>
+      <c r="H30" s="90"/>
+      <c r="I30" s="90"/>
+      <c r="J30" s="90"/>
+    </row>
+    <row r="33" spans="3:13">
+      <c r="D33" s="91" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="34" spans="3:13">
+      <c r="E34" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="35" spans="3:13">
+      <c r="F35" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="36" spans="3:13">
+      <c r="F36" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="39" spans="3:13">
+      <c r="C39" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="41" spans="3:13">
+      <c r="D41" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="43" spans="3:13">
+      <c r="D43" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="44" spans="3:13">
+      <c r="E44" s="81" t="s">
+        <v>591</v>
+      </c>
+      <c r="F44" s="90"/>
+      <c r="G44" s="90"/>
+      <c r="H44" s="90"/>
+      <c r="I44" s="90"/>
+      <c r="J44" s="90"/>
+      <c r="K44" s="90"/>
+      <c r="L44" s="90"/>
+      <c r="M44" s="90"/>
+    </row>
+    <row r="45" spans="3:13">
+      <c r="E45" s="82"/>
+      <c r="F45" s="90"/>
+      <c r="G45" s="90"/>
+      <c r="H45" s="90"/>
+      <c r="I45" s="90"/>
+      <c r="J45" s="90"/>
+      <c r="K45" s="90"/>
+      <c r="L45" s="90"/>
+      <c r="M45" s="90"/>
+    </row>
+    <row r="46" spans="3:13">
+      <c r="E46" s="81" t="s">
+        <v>592</v>
+      </c>
+      <c r="F46" s="90"/>
+      <c r="G46" s="90"/>
+      <c r="H46" s="90"/>
+      <c r="I46" s="90"/>
+      <c r="J46" s="90"/>
+      <c r="K46" s="90"/>
+      <c r="L46" s="90"/>
+      <c r="M46" s="90"/>
+    </row>
+    <row r="47" spans="3:13">
+      <c r="E47" s="81" t="s">
+        <v>593</v>
+      </c>
+      <c r="F47" s="90"/>
+      <c r="G47" s="90"/>
+      <c r="H47" s="90"/>
+      <c r="I47" s="90"/>
+      <c r="J47" s="90"/>
+      <c r="K47" s="90"/>
+      <c r="L47" s="90"/>
+      <c r="M47" s="90"/>
+    </row>
+    <row r="48" spans="3:13">
+      <c r="E48" s="81" t="s">
+        <v>594</v>
+      </c>
+      <c r="F48" s="90"/>
+      <c r="G48" s="90"/>
+      <c r="H48" s="90"/>
+      <c r="I48" s="90"/>
+      <c r="J48" s="90"/>
+      <c r="K48" s="90"/>
+      <c r="L48" s="90"/>
+      <c r="M48" s="90"/>
+    </row>
+    <row r="49" spans="4:13">
+      <c r="E49" s="82" t="s">
+        <v>595</v>
+      </c>
+      <c r="F49" s="90"/>
+      <c r="G49" s="90"/>
+      <c r="H49" s="90"/>
+      <c r="I49" s="90"/>
+      <c r="J49" s="90"/>
+      <c r="K49" s="90"/>
+      <c r="L49" s="90"/>
+      <c r="M49" s="90"/>
+    </row>
+    <row r="50" spans="4:13">
+      <c r="E50" s="81" t="s">
+        <v>596</v>
+      </c>
+      <c r="F50" s="90"/>
+      <c r="G50" s="90"/>
+      <c r="H50" s="90"/>
+      <c r="I50" s="90"/>
+      <c r="J50" s="90"/>
+      <c r="K50" s="90"/>
+      <c r="L50" s="90"/>
+      <c r="M50" s="90"/>
+    </row>
+    <row r="53" spans="4:13">
+      <c r="D53" s="91" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="54" spans="4:13">
+      <c r="E54" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="55" spans="4:13">
+      <c r="E55" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="56" spans="4:13">
+      <c r="E56" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="57" spans="4:13">
+      <c r="E57" t="s">
+        <v>600</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:E25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2" spans="2:5">
+      <c r="B2" s="6" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="3" spans="2:5">
       <c r="C3" t="s">
+        <v>512</v>
+      </c>
+      <c r="D3" t="s">
+        <v>511</v>
+      </c>
+      <c r="E3" t="s">
         <v>514</v>
       </c>
-      <c r="D3" t="s">
+    </row>
+    <row r="4" spans="2:5">
+      <c r="C4" s="80" t="s">
         <v>513</v>
       </c>
-      <c r="E3" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5">
-      <c r="C4" s="83" t="s">
+      <c r="D4" t="s">
+        <v>510</v>
+      </c>
+      <c r="E4" t="s">
         <v>515</v>
-      </c>
-      <c r="D4" t="s">
-        <v>512</v>
-      </c>
-      <c r="E4" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="C7" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="C8" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="C10" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="C11" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="C12" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="C13" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="C14" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="C15" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="C16" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="17" spans="3:3">
       <c r="C17" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="18" spans="3:3">
       <c r="C18" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="20" spans="3:3">
       <c r="C20" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="21" spans="3:3">
@@ -10273,17 +11981,17 @@
     </row>
     <row r="23" spans="3:3">
       <c r="C23" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="24" spans="3:3">
       <c r="C24" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="25" spans="3:3">
       <c r="C25" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
   </sheetData>
@@ -10291,45 +11999,60 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2" spans="2:2">
+      <c r="B2" s="6" t="s">
+        <v>439</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="3" spans="2:4">
       <c r="C3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="C4" s="76" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="5" spans="2:4">
       <c r="B5" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="6" spans="2:4">
       <c r="C6" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="7" spans="2:4">
       <c r="C7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D7" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
   </sheetData>
@@ -10338,38 +12061,43 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:D5"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="B2:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="3" spans="2:4">
       <c r="C3" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D3" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="C4" t="s">
+        <v>533</v>
+      </c>
+      <c r="D4" t="s">
         <v>535</v>
-      </c>
-      <c r="D4" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="5" spans="2:4">
       <c r="C5" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D5" t="s">
-        <v>539</v>
+        <v>537</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
+      <c r="B10" s="6" t="s">
+        <v>465</v>
       </c>
     </row>
   </sheetData>
@@ -10380,15 +12108,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:F103"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="12.26953125" customWidth="1"/>
-    <col min="4" max="4" width="13.54296875" customWidth="1"/>
-    <col min="5" max="5" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.1796875" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="18.5">
+    <row r="2" spans="2:6" ht="18.75">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -11531,12 +13259,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:G90"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="50.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="68.54296875" customWidth="1"/>
-    <col min="6" max="6" width="9.7265625" customWidth="1"/>
+    <col min="3" max="3" width="50.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6">
@@ -11544,7 +13272,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="2:6" ht="18.5">
+    <row r="2" spans="2:6" ht="18.75">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -12235,7 +13963,7 @@
         <v>266</v>
       </c>
       <c r="C47" s="57" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D47" s="42">
         <v>1</v>
@@ -12247,10 +13975,10 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C48" s="56" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D48" s="51">
         <v>0.8</v>
@@ -12262,13 +13990,13 @@
     </row>
     <row r="49" spans="2:6">
       <c r="B49" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>303</v>
+        <v>562</v>
       </c>
       <c r="D49" s="51">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E49" s="6"/>
       <c r="F49" s="16" t="s">
@@ -12277,36 +14005,38 @@
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="D50" s="42">
+        <v>1</v>
+      </c>
+      <c r="E50" s="6"/>
+      <c r="F50" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" ht="30">
+      <c r="B51" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="C50" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="D50" s="51">
-        <v>0</v>
-      </c>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-    </row>
-    <row r="51" spans="2:6" ht="29">
-      <c r="B51" s="5" t="s">
-        <v>321</v>
-      </c>
       <c r="C51" s="7" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="16" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F51" s="6"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D52" s="42">
         <v>1</v>
@@ -12318,21 +14048,23 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D53" s="6"/>
       <c r="E53" s="6"/>
-      <c r="F53" s="6"/>
+      <c r="F53" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="5" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D54" s="42">
         <v>1</v>
@@ -12344,10 +14076,10 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="5" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="6"/>
@@ -12355,14 +14087,14 @@
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="C56" s="6" t="s">
         <v>450</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>451</v>
       </c>
       <c r="D56" s="6"/>
       <c r="E56" s="16" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F56" s="6"/>
     </row>
@@ -12371,7 +14103,7 @@
         <v>16.100000000000001</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D57" s="42">
         <v>1</v>
@@ -12386,18 +14118,20 @@
         <v>16.2</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="6"/>
-      <c r="F58" s="6"/>
+      <c r="F58" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="5">
         <v>16.3</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D59" s="6"/>
       <c r="E59" s="6"/>
@@ -12408,7 +14142,7 @@
         <v>16.399999999999999</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D60" s="6"/>
       <c r="E60" s="6"/>
@@ -12419,7 +14153,7 @@
         <v>16.5</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
@@ -12430,7 +14164,7 @@
         <v>16.600000000000001</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D62" s="6"/>
       <c r="E62" s="6"/>
@@ -12441,7 +14175,7 @@
         <v>16.7</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
@@ -12449,32 +14183,32 @@
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="C64" s="6" t="s">
         <v>456</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>457</v>
       </c>
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>
     </row>
-    <row r="65" spans="2:6" ht="29">
+    <row r="65" spans="2:6" ht="30">
       <c r="B65" s="5">
         <v>17.100000000000001</v>
       </c>
       <c r="C65" s="78" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D65" s="6"/>
       <c r="E65" s="6"/>
       <c r="F65" s="6"/>
     </row>
-    <row r="66" spans="2:6" ht="29">
+    <row r="66" spans="2:6" ht="30">
       <c r="B66" s="5">
         <v>17.2</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D66" s="6"/>
       <c r="E66" s="6"/>
@@ -12485,20 +14219,20 @@
         <v>17.3</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D67" s="6"/>
       <c r="E67" s="16" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F67" s="6"/>
     </row>
-    <row r="68" spans="2:6" ht="29">
+    <row r="68" spans="2:6" ht="30">
       <c r="B68" s="5">
         <v>17.399999999999999</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
@@ -12509,7 +14243,7 @@
         <v>17.5</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D69" s="6"/>
       <c r="E69" s="6"/>
@@ -12517,10 +14251,10 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="5" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D70" s="6"/>
       <c r="E70" s="6"/>
@@ -12531,7 +14265,7 @@
         <v>18.100000000000001</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D71" s="6"/>
       <c r="E71" s="6"/>
@@ -12542,7 +14276,7 @@
         <v>18.2</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D72" s="6"/>
       <c r="E72" s="6"/>
@@ -12553,7 +14287,7 @@
         <v>18.3</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D73" s="6"/>
       <c r="E73" s="6"/>
@@ -12564,7 +14298,7 @@
         <v>18.399999999999999</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D74" s="6"/>
       <c r="E74" s="6"/>
@@ -12572,10 +14306,10 @@
     </row>
     <row r="75" spans="2:6">
       <c r="B75" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="C75" s="6" t="s">
         <v>467</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>468</v>
       </c>
       <c r="D75" s="6"/>
       <c r="E75" s="6"/>
@@ -12586,7 +14320,7 @@
         <v>19.100000000000001</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D76" s="6"/>
       <c r="E76" s="6"/>
@@ -12594,10 +14328,10 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="5" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D77" s="6"/>
       <c r="E77" s="6"/>
@@ -12605,10 +14339,10 @@
     </row>
     <row r="78" spans="2:6">
       <c r="B78" s="5" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D78" s="6"/>
       <c r="E78" s="6"/>
@@ -12619,18 +14353,18 @@
         <v>21.1</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D79" s="6"/>
       <c r="E79" s="6"/>
       <c r="F79" s="6"/>
     </row>
-    <row r="80" spans="2:6" ht="29">
+    <row r="80" spans="2:6" ht="30">
       <c r="B80" s="5">
         <v>21.2</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D80" s="6"/>
       <c r="E80" s="6"/>
@@ -12638,36 +14372,36 @@
     </row>
     <row r="81" spans="2:6">
       <c r="B81" s="5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D81" s="6"/>
       <c r="E81" s="16" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F81" s="6"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="C82" s="6" t="s">
         <v>474</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>475</v>
       </c>
       <c r="D82" s="6"/>
       <c r="E82" s="16" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F82" s="6"/>
     </row>
     <row r="83" spans="2:6">
       <c r="B83" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D83" s="6"/>
       <c r="E83" s="16"/>
@@ -12675,34 +14409,34 @@
     </row>
     <row r="84" spans="2:6">
       <c r="B84" s="5" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D84" s="6"/>
       <c r="E84" s="16"/>
       <c r="F84" s="6"/>
     </row>
-    <row r="85" spans="2:6" ht="58">
+    <row r="85" spans="2:6" ht="60">
       <c r="B85" s="5" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C85" s="79" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D85" s="6"/>
       <c r="E85" s="16" t="s">
+        <v>489</v>
+      </c>
+      <c r="F85" s="6"/>
+    </row>
+    <row r="86" spans="2:6" ht="30">
+      <c r="B86" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="C86" s="7" t="s">
         <v>490</v>
-      </c>
-      <c r="F85" s="6"/>
-    </row>
-    <row r="86" spans="2:6" ht="29">
-      <c r="B86" s="5" t="s">
-        <v>497</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>491</v>
       </c>
       <c r="D86" s="6"/>
       <c r="E86" s="16"/>
@@ -12710,32 +14444,32 @@
     </row>
     <row r="87" spans="2:6">
       <c r="B87" s="5" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D87" s="6"/>
       <c r="E87" s="16"/>
       <c r="F87" s="6"/>
     </row>
-    <row r="88" spans="2:6" ht="58">
+    <row r="88" spans="2:6" ht="60">
       <c r="B88" s="5" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D88" s="6"/>
       <c r="E88" s="16"/>
       <c r="F88" s="6"/>
     </row>
-    <row r="89" spans="2:6" ht="29">
+    <row r="89" spans="2:6" ht="30">
       <c r="B89" s="5" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D89" s="6"/>
       <c r="E89" s="16"/>
@@ -12743,14 +14477,14 @@
     </row>
     <row r="90" spans="2:6">
       <c r="B90" s="77" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C90" s="57" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D90" s="1"/>
       <c r="E90" s="49" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F90" s="1"/>
     </row>
@@ -12810,6 +14544,9 @@
     <hyperlink ref="F49" location="'#9'!B2" display="Link"/>
     <hyperlink ref="F52" location="'#12'!B2" display="Link"/>
     <hyperlink ref="F57" location="'#16'!B2" display="Link"/>
+    <hyperlink ref="F50" location="'#10'!B2" display="Link"/>
+    <hyperlink ref="F53" location="'#13'!B2" display="Link"/>
+    <hyperlink ref="F58" location="'#16'!B10" display="Link"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId12"/>
@@ -12819,13 +14556,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J164"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.26953125" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.5">
+    <row r="1" spans="1:3" ht="18.75">
       <c r="C1" s="41" t="s">
         <v>15</v>
       </c>
@@ -13082,14 +14819,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L61"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="10.453125" customWidth="1"/>
-    <col min="4" max="4" width="5.26953125" customWidth="1"/>
-    <col min="5" max="5" width="48.81640625" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" customWidth="1"/>
+    <col min="4" max="4" width="5.28515625" customWidth="1"/>
+    <col min="5" max="5" width="48.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.5">
+    <row r="1" spans="1:10" ht="18.75">
       <c r="C1" s="41" t="s">
         <v>57</v>
       </c>
@@ -13120,14 +14857,14 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15" thickBot="1">
+    <row r="12" spans="1:10" ht="15.75" thickBot="1">
       <c r="C12" s="11" t="s">
         <v>63</v>
       </c>
       <c r="D12" s="11"/>
     </row>
-    <row r="13" spans="1:10" ht="15" thickBot="1">
-      <c r="C13" s="80" t="s">
+    <row r="13" spans="1:10" ht="15.75" thickBot="1">
+      <c r="C13" s="92" t="s">
         <v>78</v>
       </c>
       <c r="D13" s="26" t="s">
@@ -13143,8 +14880,8 @@
       <c r="H13" s="24"/>
       <c r="I13" s="25"/>
     </row>
-    <row r="14" spans="1:10" ht="15" thickBot="1">
-      <c r="C14" s="81"/>
+    <row r="14" spans="1:10" ht="15.75" thickBot="1">
+      <c r="C14" s="93"/>
       <c r="D14" s="23" t="s">
         <v>65</v>
       </c>
@@ -13160,7 +14897,7 @@
       <c r="J14" s="25"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="C15" s="81"/>
+      <c r="C15" s="93"/>
       <c r="D15" s="26" t="s">
         <v>66</v>
       </c>
@@ -13175,7 +14912,7 @@
       <c r="I15" s="28"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="C16" s="81"/>
+      <c r="C16" s="93"/>
       <c r="D16" s="29"/>
       <c r="E16" s="30" t="s">
         <v>74</v>
@@ -13185,8 +14922,8 @@
       <c r="H16" s="30"/>
       <c r="I16" s="31"/>
     </row>
-    <row r="17" spans="3:12" ht="15" thickBot="1">
-      <c r="C17" s="82"/>
+    <row r="17" spans="3:12" ht="15.75" thickBot="1">
+      <c r="C17" s="94"/>
       <c r="D17" s="32"/>
       <c r="E17" s="33" t="s">
         <v>75</v>
@@ -13196,7 +14933,7 @@
       <c r="H17" s="30"/>
       <c r="I17" s="31"/>
     </row>
-    <row r="18" spans="3:12" ht="15" thickBot="1">
+    <row r="18" spans="3:12" ht="15.75" thickBot="1">
       <c r="C18" s="37" t="s">
         <v>79</v>
       </c>
@@ -13216,8 +14953,8 @@
       <c r="K18" s="24"/>
       <c r="L18" s="25"/>
     </row>
-    <row r="19" spans="3:12" ht="15" thickBot="1">
-      <c r="C19" s="80" t="s">
+    <row r="19" spans="3:12" ht="15.75" thickBot="1">
+      <c r="C19" s="92" t="s">
         <v>78</v>
       </c>
       <c r="D19" s="23" t="s">
@@ -13228,7 +14965,7 @@
       </c>
     </row>
     <row r="20" spans="3:12">
-      <c r="C20" s="81"/>
+      <c r="C20" s="93"/>
       <c r="D20" s="26" t="s">
         <v>82</v>
       </c>
@@ -13236,8 +14973,8 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="3:12" ht="15" thickBot="1">
-      <c r="C21" s="82"/>
+    <row r="21" spans="3:12" ht="15.75" thickBot="1">
+      <c r="C21" s="94"/>
       <c r="D21" s="32"/>
       <c r="E21" s="40" t="s">
         <v>84</v>
@@ -13350,10 +15087,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:V102"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="13" max="13" width="4.81640625" customWidth="1"/>
+    <col min="13" max="13" width="4.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
@@ -13868,7 +15605,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D32"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" s="6" t="s">
@@ -13991,10 +15728,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:H90"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="13.54296875" customWidth="1"/>
-    <col min="7" max="7" width="9.453125" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4">
@@ -14360,9 +16097,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Z40"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="17.1796875" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:26">
@@ -14388,7 +16125,7 @@
         <v>272</v>
       </c>
       <c r="E5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8" spans="2:26">
@@ -14416,7 +16153,7 @@
         <v>277</v>
       </c>
       <c r="F12" s="55" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G12" s="55"/>
       <c r="H12" s="55"/>
@@ -14481,39 +16218,39 @@
     </row>
     <row r="35" spans="2:7">
       <c r="C35" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="37" spans="2:7">
       <c r="D37" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E37" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="38" spans="2:7">
       <c r="D38" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E38" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="39" spans="2:7">
       <c r="D39" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E39" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="40" spans="2:7">
       <c r="D40" t="s">
+        <v>298</v>
+      </c>
+      <c r="G40" t="s">
         <v>299</v>
-      </c>
-      <c r="G40" t="s">
-        <v>300</v>
       </c>
     </row>
   </sheetData>

--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="3" activeTab="16"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Knowhow" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="610">
   <si>
     <t>No.</t>
   </si>
@@ -5143,6 +5143,95 @@
   </si>
   <si>
     <t>gcovr -r .. --html --html-details -o coverage.html</t>
+  </si>
+  <si>
+    <t>Tùy vào đối số truyền vào hàm mà chương trình sẽ ngầm hiểu là hàm đang được dùng theo cách nào</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Overloading</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : Nạp chồng hàm, là cơ chế trong C++ cho phép nhiều cách xử lý khác nhau cho cùng 1 tên hàm. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Overriding </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Ghi đè hàm, là cơ chế trong C++ mà khi kết hợp với phương thức virtual cho phép hàm cùng tên</t>
+    </r>
+  </si>
+  <si>
+    <t>trong class con, mặc dù có cùng tham số, đối số truyền vào, kiểu trả về nhưng có xử lý khác so với hàm cùng tên trong class cha</t>
+  </si>
+  <si>
+    <t>Khâu hoạt động</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Thời điểm quyết định : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Compile-time</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Thời điểm quyết định : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Runtime</t>
+    </r>
+  </si>
+  <si>
+    <t>Mục đích : Tăng tính linh hoạt cho code</t>
+  </si>
+  <si>
+    <t>Mục đích : Thay đổi hành vi của class cha</t>
   </si>
 </sst>
 </file>
@@ -9914,19 +10003,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:K22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="5.7109375" customWidth="1"/>
-    <col min="3" max="3" width="37.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.42578125" customWidth="1"/>
+    <col min="2" max="2" width="5.7265625" customWidth="1"/>
+    <col min="3" max="3" width="37.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.453125" customWidth="1"/>
     <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7265625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="18.75">
+    <row r="2" spans="2:11" ht="18.5">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -9952,7 +10041,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:11" ht="45">
+    <row r="3" spans="2:11" ht="43.5">
       <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
@@ -10306,9 +10395,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Q30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="11" max="11" width="3.7109375" customWidth="1"/>
+    <col min="11" max="11" width="3.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:17">
@@ -10638,12 +10727,12 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E76"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="4.42578125" customWidth="1"/>
-    <col min="3" max="3" width="39.7109375" customWidth="1"/>
-    <col min="4" max="4" width="50.85546875" customWidth="1"/>
-    <col min="5" max="5" width="75.42578125" customWidth="1"/>
+    <col min="2" max="2" width="4.453125" customWidth="1"/>
+    <col min="3" max="3" width="39.7265625" customWidth="1"/>
+    <col min="4" max="4" width="50.81640625" customWidth="1"/>
+    <col min="5" max="5" width="75.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.5">
@@ -10651,7 +10740,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="23.25">
+    <row r="2" spans="1:5" ht="23.5">
       <c r="B2" s="63" t="s">
         <v>420</v>
       </c>
@@ -10670,7 +10759,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="45">
+    <row r="5" spans="1:5" ht="43.5">
       <c r="B5" s="69">
         <v>1</v>
       </c>
@@ -10698,7 +10787,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5" ht="29">
       <c r="B7" s="69">
         <v>3</v>
       </c>
@@ -10712,7 +10801,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="23.25">
+    <row r="10" spans="1:5" ht="23.5">
       <c r="B10" s="63" t="s">
         <v>344</v>
       </c>
@@ -10731,7 +10820,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="30">
+    <row r="13" spans="1:5">
       <c r="B13" s="69">
         <v>1</v>
       </c>
@@ -10745,7 +10834,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="30">
+    <row r="14" spans="1:5" ht="29">
       <c r="B14" s="69">
         <v>2</v>
       </c>
@@ -10759,7 +10848,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="30">
+    <row r="15" spans="1:5" ht="29">
       <c r="B15" s="69">
         <v>3</v>
       </c>
@@ -10773,7 +10862,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30">
+    <row r="16" spans="1:5" ht="29">
       <c r="B16" s="69">
         <v>4</v>
       </c>
@@ -10787,7 +10876,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="165">
+    <row r="17" spans="2:5" ht="145">
       <c r="B17" s="69">
         <v>5</v>
       </c>
@@ -10801,7 +10890,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="180">
+    <row r="18" spans="2:5" ht="159.5">
       <c r="B18" s="69">
         <v>6</v>
       </c>
@@ -10815,7 +10904,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="135">
+    <row r="19" spans="2:5" ht="130.5">
       <c r="B19" s="69">
         <v>7</v>
       </c>
@@ -10829,7 +10918,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="135">
+    <row r="20" spans="2:5" ht="130.5">
       <c r="B20" s="69">
         <v>8</v>
       </c>
@@ -10843,7 +10932,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="23" spans="2:5" ht="23.25">
+    <row r="23" spans="2:5" ht="23.5">
       <c r="B23" s="63" t="s">
         <v>419</v>
       </c>
@@ -10910,7 +10999,7 @@
       </c>
       <c r="E29" s="1"/>
     </row>
-    <row r="32" spans="2:5" ht="23.25">
+    <row r="32" spans="2:5" ht="23.5">
       <c r="B32" s="63" t="s">
         <v>418</v>
       </c>
@@ -10926,7 +11015,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="35" spans="2:4" ht="30">
+    <row r="35" spans="2:4" ht="29">
       <c r="B35" s="65">
         <v>1</v>
       </c>
@@ -10948,7 +11037,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="37" spans="2:4" ht="30">
+    <row r="37" spans="2:4">
       <c r="B37" s="65">
         <v>3</v>
       </c>
@@ -10970,7 +11059,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="41" spans="2:4" ht="23.25">
+    <row r="41" spans="2:4" ht="23.5">
       <c r="B41" s="63" t="s">
         <v>417</v>
       </c>
@@ -10986,7 +11075,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="44" spans="2:4" ht="30">
+    <row r="44" spans="2:4">
       <c r="B44" s="65">
         <v>1</v>
       </c>
@@ -11030,7 +11119,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="50" spans="2:4" ht="23.25">
+    <row r="50" spans="2:4" ht="23.5">
       <c r="B50" s="63" t="s">
         <v>416</v>
       </c>
@@ -11082,7 +11171,7 @@
     <row r="56" spans="2:4">
       <c r="B56" s="65"/>
     </row>
-    <row r="58" spans="2:4" ht="23.25">
+    <row r="58" spans="2:4" ht="23.5">
       <c r="B58" s="63" t="s">
         <v>415</v>
       </c>
@@ -11109,7 +11198,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="62" spans="2:4" ht="45">
+    <row r="62" spans="2:4" ht="29">
       <c r="B62" s="65">
         <v>2</v>
       </c>
@@ -11120,7 +11209,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="63" spans="2:4" ht="30">
+    <row r="63" spans="2:4" ht="29">
       <c r="B63" s="65">
         <v>3</v>
       </c>
@@ -11153,7 +11242,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="68" spans="2:4" ht="23.25">
+    <row r="68" spans="2:4" ht="23.5">
       <c r="B68" s="63" t="s">
         <v>400</v>
       </c>
@@ -11244,7 +11333,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:S38"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -11571,7 +11660,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:M57"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -11885,7 +11974,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -12002,7 +12091,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:2">
       <c r="B2" s="6" t="s">
@@ -12017,7 +12106,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
@@ -12063,8 +12152,8 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:D10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="B2:D20"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
@@ -12100,23 +12189,69 @@
         <v>465</v>
       </c>
     </row>
+    <row r="11" spans="2:4">
+      <c r="C11" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4">
+      <c r="C12" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4">
+      <c r="C13" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4">
+      <c r="C14" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4">
+      <c r="C16" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3">
+      <c r="C20" t="s">
+        <v>609</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:F103"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="3" max="3" width="12.28515625" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.26953125" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" customWidth="1"/>
+    <col min="5" max="5" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="18.75">
+    <row r="2" spans="2:6" ht="18.5">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -13259,12 +13394,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:G90"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="3" max="3" width="50.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="68.5703125" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" customWidth="1"/>
+    <col min="3" max="3" width="50.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.54296875" customWidth="1"/>
+    <col min="6" max="6" width="9.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6">
@@ -13272,7 +13407,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="2:6" ht="18.75">
+    <row r="2" spans="2:6" ht="18.5">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -14018,7 +14153,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="2:6" ht="30">
+    <row r="51" spans="2:6" ht="29">
       <c r="B51" s="5" t="s">
         <v>320</v>
       </c>
@@ -14120,7 +14255,9 @@
       <c r="C58" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="D58" s="6"/>
+      <c r="D58" s="42">
+        <v>1</v>
+      </c>
       <c r="E58" s="6"/>
       <c r="F58" s="16" t="s">
         <v>14</v>
@@ -14192,7 +14329,7 @@
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>
     </row>
-    <row r="65" spans="2:6" ht="30">
+    <row r="65" spans="2:6" ht="29">
       <c r="B65" s="5">
         <v>17.100000000000001</v>
       </c>
@@ -14203,7 +14340,7 @@
       <c r="E65" s="6"/>
       <c r="F65" s="6"/>
     </row>
-    <row r="66" spans="2:6" ht="30">
+    <row r="66" spans="2:6" ht="29">
       <c r="B66" s="5">
         <v>17.2</v>
       </c>
@@ -14227,7 +14364,7 @@
       </c>
       <c r="F67" s="6"/>
     </row>
-    <row r="68" spans="2:6" ht="30">
+    <row r="68" spans="2:6" ht="29">
       <c r="B68" s="5">
         <v>17.399999999999999</v>
       </c>
@@ -14359,7 +14496,7 @@
       <c r="E79" s="6"/>
       <c r="F79" s="6"/>
     </row>
-    <row r="80" spans="2:6" ht="30">
+    <row r="80" spans="2:6" ht="29">
       <c r="B80" s="5">
         <v>21.2</v>
       </c>
@@ -14418,7 +14555,7 @@
       <c r="E84" s="16"/>
       <c r="F84" s="6"/>
     </row>
-    <row r="85" spans="2:6" ht="60">
+    <row r="85" spans="2:6" ht="58">
       <c r="B85" s="5" t="s">
         <v>495</v>
       </c>
@@ -14431,7 +14568,7 @@
       </c>
       <c r="F85" s="6"/>
     </row>
-    <row r="86" spans="2:6" ht="30">
+    <row r="86" spans="2:6" ht="29">
       <c r="B86" s="5" t="s">
         <v>496</v>
       </c>
@@ -14453,7 +14590,7 @@
       <c r="E87" s="16"/>
       <c r="F87" s="6"/>
     </row>
-    <row r="88" spans="2:6" ht="60">
+    <row r="88" spans="2:6" ht="58">
       <c r="B88" s="5" t="s">
         <v>498</v>
       </c>
@@ -14464,7 +14601,7 @@
       <c r="E88" s="16"/>
       <c r="F88" s="6"/>
     </row>
-    <row r="89" spans="2:6" ht="30">
+    <row r="89" spans="2:6" ht="29">
       <c r="B89" s="5" t="s">
         <v>499</v>
       </c>
@@ -14556,13 +14693,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J164"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" customWidth="1"/>
+    <col min="1" max="1" width="4.26953125" customWidth="1"/>
+    <col min="2" max="2" width="6.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75">
+    <row r="1" spans="1:3" ht="18.5">
       <c r="C1" s="41" t="s">
         <v>15</v>
       </c>
@@ -14819,14 +14956,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L61"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="3" max="3" width="10.42578125" customWidth="1"/>
-    <col min="4" max="4" width="5.28515625" customWidth="1"/>
-    <col min="5" max="5" width="48.85546875" customWidth="1"/>
+    <col min="3" max="3" width="10.453125" customWidth="1"/>
+    <col min="4" max="4" width="5.26953125" customWidth="1"/>
+    <col min="5" max="5" width="48.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75">
+    <row r="1" spans="1:10" ht="18.5">
       <c r="C1" s="41" t="s">
         <v>57</v>
       </c>
@@ -14857,13 +14994,13 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15.75" thickBot="1">
+    <row r="12" spans="1:10" ht="15" thickBot="1">
       <c r="C12" s="11" t="s">
         <v>63</v>
       </c>
       <c r="D12" s="11"/>
     </row>
-    <row r="13" spans="1:10" ht="15.75" thickBot="1">
+    <row r="13" spans="1:10" ht="15" thickBot="1">
       <c r="C13" s="92" t="s">
         <v>78</v>
       </c>
@@ -14880,7 +15017,7 @@
       <c r="H13" s="24"/>
       <c r="I13" s="25"/>
     </row>
-    <row r="14" spans="1:10" ht="15.75" thickBot="1">
+    <row r="14" spans="1:10" ht="15" thickBot="1">
       <c r="C14" s="93"/>
       <c r="D14" s="23" t="s">
         <v>65</v>
@@ -14922,7 +15059,7 @@
       <c r="H16" s="30"/>
       <c r="I16" s="31"/>
     </row>
-    <row r="17" spans="3:12" ht="15.75" thickBot="1">
+    <row r="17" spans="3:12" ht="15" thickBot="1">
       <c r="C17" s="94"/>
       <c r="D17" s="32"/>
       <c r="E17" s="33" t="s">
@@ -14933,7 +15070,7 @@
       <c r="H17" s="30"/>
       <c r="I17" s="31"/>
     </row>
-    <row r="18" spans="3:12" ht="15.75" thickBot="1">
+    <row r="18" spans="3:12" ht="15" thickBot="1">
       <c r="C18" s="37" t="s">
         <v>79</v>
       </c>
@@ -14953,7 +15090,7 @@
       <c r="K18" s="24"/>
       <c r="L18" s="25"/>
     </row>
-    <row r="19" spans="3:12" ht="15.75" thickBot="1">
+    <row r="19" spans="3:12" ht="15" thickBot="1">
       <c r="C19" s="92" t="s">
         <v>78</v>
       </c>
@@ -14973,7 +15110,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="3:12" ht="15.75" thickBot="1">
+    <row r="21" spans="3:12" ht="15" thickBot="1">
       <c r="C21" s="94"/>
       <c r="D21" s="32"/>
       <c r="E21" s="40" t="s">
@@ -15087,10 +15224,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:V102"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="13" max="13" width="4.85546875" customWidth="1"/>
+    <col min="13" max="13" width="4.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
@@ -15605,7 +15742,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D32"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" s="6" t="s">
@@ -15728,10 +15865,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:H90"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="4" max="4" width="13.5703125" customWidth="1"/>
-    <col min="7" max="7" width="9.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" customWidth="1"/>
+    <col min="7" max="7" width="9.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4">
@@ -16097,9 +16234,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Z40"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="4" max="4" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:26">

--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" firstSheet="2" activeTab="16"/>
   </bookViews>
   <sheets>
     <sheet name="Knowhow" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,8 @@
     <sheet name="#12" sheetId="14" r:id="rId14"/>
     <sheet name="#13" sheetId="17" r:id="rId15"/>
     <sheet name="#14" sheetId="12" r:id="rId16"/>
-    <sheet name="#16" sheetId="15" r:id="rId17"/>
+    <sheet name="#15" sheetId="18" r:id="rId17"/>
+    <sheet name="#16" sheetId="15" r:id="rId18"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="699">
   <si>
     <t>No.</t>
   </si>
@@ -3745,15 +3746,6 @@
   </si>
   <si>
     <t>Sự khác biệt giữa virtual, pure virtual và override</t>
-  </si>
-  <si>
-    <t>What happens if a base class destructor is not virtual?</t>
-  </si>
-  <si>
-    <t>Can constructors be virtual?</t>
-  </si>
-  <si>
-    <t>What is slicing in C++?</t>
   </si>
   <si>
     <t>#17</t>
@@ -4116,9 +4108,6 @@
     <t>Tăng trước khi dùng</t>
   </si>
   <si>
-    <t>Cấp phát động trong C và C++ (new và malloc)</t>
-  </si>
-  <si>
     <t>Ví dụ :</t>
   </si>
   <si>
@@ -5232,13 +5221,1420 @@
   </si>
   <si>
     <t>Mục đích : Thay đổi hành vi của class cha</t>
+  </si>
+  <si>
+    <t>Virture :</t>
+  </si>
+  <si>
+    <t>Cho phép hàm trong lớp cơ sở được ghi đè bởi hàm trong lớp dẫn xuất (khi kết hợp với override). Nếu không có</t>
+  </si>
+  <si>
+    <t>virture, tại thời điểm compile-time, chương trình sẽ chạy theo con trỏ trỏ đến hàm của lớp cơ sở. Nếu virture,</t>
+  </si>
+  <si>
+    <t>chương trình sẽ trỏ đến đúng đối tượng hàm chỉ định của lớp dẫn xuất</t>
+  </si>
+  <si>
+    <t>Chú ý : Virture được viết ở hàm cơ sở, để chỉ ra rằng nó có thể mang hình thái khác ở lớp dẫn xuất</t>
+  </si>
+  <si>
+    <t>Pure Virtual :</t>
+  </si>
+  <si>
+    <t>Được khai báo trong lớp cơ sở, nó là hàm ảo thuần túy, để bắt buộc chương trình phải mang triển khai phương</t>
+  </si>
+  <si>
+    <t>thức ở lớp dẫn xuất và không thể chạy trực tiếp hàm ở lớp cơ sở.</t>
+  </si>
+  <si>
+    <t>class Animal{</t>
+  </si>
+  <si>
+    <t>};</t>
+  </si>
+  <si>
+    <t>class Cat{</t>
+  </si>
+  <si>
+    <t>virture void sound() = 0</t>
+  </si>
+  <si>
+    <t>void sound(){ printf("Meow");}</t>
+  </si>
+  <si>
+    <t>virture void sound() { printf("Make sound");}</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">*class có </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>toàn bộ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> function là pure virture function được gọi là </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>interface class</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*class có</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ít nhất 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> pure virtual function được gọi là class trừu tượng ( </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>abstract class</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Ví dụ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        cout &lt;&lt; "Woof!\n";</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>void speak() override {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> // Compiler kiểm tra có override hợp lệ không</t>
+    </r>
+  </si>
+  <si>
+    <t>Hàm constructor có thể trở thành virtual không ?</t>
+  </si>
+  <si>
+    <t>Điều gì sẽ xảy ra khi hàm hủy (destructor) của class base không phải là virtual ?</t>
+  </si>
+  <si>
+    <t>Slicing trong C++ là gì? Khi khai báo class dẫn xuất theo kiểu cấp phát động, kiểu con trỏ cha, thì những phương thức, thuộc tính mới của class con có chỗ để chứa trong con trỏ đó không ? Cơ chế là gì ? Tại sao ?</t>
+  </si>
+  <si>
+    <t>Sẽ gây rò rỉ bộ nhớ (Memory Leak) khi thực hiện xóa class con.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">dẫn đến </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rò rỉ bộ nhớ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và rủi ro lỗi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>undefined behavior</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Khi xóa đối tượng đó, chương trình chỉ gọi đến </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>destructor tương ứng với kiểu con trỏ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, dẫn đến </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>destructor của lớp deliveried không được gọi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Cách làm đúng và an toàn : thêm virtual vào cho hàm hủy của class cơ sở, khi gọi hàm hủy, chương trình sẽ gọi từ destructor của </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>class dẫn xuất -&gt; class cơ sở</t>
+    </r>
+  </si>
+  <si>
+    <t>class Base {</t>
+  </si>
+  <si>
+    <t>public:</t>
+  </si>
+  <si>
+    <t>class Derived : public Base {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ~Derived() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    virtual ~Base() {</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>KHÔNG THỂ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, và </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>C++ cấm hoàn toàn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> việc khai báo constructor là virtual.</t>
+    </r>
+  </si>
+  <si>
+    <t>nếu gọi vào virtual constructor -&gt; chương trình sẽ tra vtable pointer -&gt; Không có do constructor chưa thực thi xong -&gt; Vòng lặp luẩn quẩn</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Lý do là </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>để gọi 1 virtual function</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> thì </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cần vtable pointer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, mà </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>vtable chỉ được khởi tạo khi constructor của đối tượng thực thi xong</t>
+    </r>
+  </si>
+  <si>
+    <t>sử dụng nó nữa, hệ thống sẽ tự động clean up đối tượng đó để tránh các vấn đề về bộ nhớ, lãng phí tài nguyên</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cơ chế hoạt động</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> của RAII</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Constructor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : Cấp phát tài nguyên lúc khởi tạo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>RAII là gì (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Resource Acquisition Is Initialization</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Destructor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : Dọn dẹp sạch tài nguyên khi đối tượng ra khỏi scope</t>
+    </r>
+  </si>
+  <si>
+    <t>Một số mô hình RAII trong C++</t>
+  </si>
+  <si>
+    <t>Bộ nhớ động :</t>
+  </si>
+  <si>
+    <t>File</t>
+  </si>
+  <si>
+    <t>Tự đóng file khi bị hủy</t>
+  </si>
+  <si>
+    <t>Mutex</t>
+  </si>
+  <si>
+    <t>std::fstream :</t>
+  </si>
+  <si>
+    <t>std::unique_ptr , std::shared_ptr, std::vector : Tự động giải phóng khi hết scope</t>
+  </si>
+  <si>
+    <t>std::lock_guard, std::unique_lock : tự động unlock khi scope kết thúc</t>
+  </si>
+  <si>
+    <r>
+      <t>Khái niệm : Dịch ra là "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Tài nguyên được cấp phát lúc khởi tạo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">". Tức là nếu </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>gói gọn tài nguyên trong 1 object</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, khi không </t>
+    </r>
+  </si>
+  <si>
+    <t>Cấp phát động trong C và C++</t>
+  </si>
+  <si>
+    <t>Cấp phát động trong C và C++
+Trong C : malloc(), calloc(), realloc(), free()
+Trong C++ : new()</t>
+  </si>
+  <si>
+    <t>Trong C :</t>
+  </si>
+  <si>
+    <t>malloc()</t>
+  </si>
+  <si>
+    <t>calloc()</t>
+  </si>
+  <si>
+    <t>realloc()</t>
+  </si>
+  <si>
+    <t>Cú pháp :</t>
+  </si>
+  <si>
+    <r>
+      <t>int* arr = (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>int*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>malloc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>n *</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sizeof(int))</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>int*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : malloc sẽ trả về kiểu void* nên cần ép kiểu cho nó</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : thường thì biến số n không cố định sẽ được nhân với </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sizeof</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(kiểu kích thước) để cấp phát kích thước mong muốn</t>
+    </r>
+  </si>
+  <si>
+    <t>Khi khởi tạo, các giá trị ban đầu là rác</t>
+  </si>
+  <si>
+    <t>Giống hệt malloc về cách dùng, chỉ khác là thay vì truyền vào tổng byte thì truyền vào số phần tử và kích thước. Giá trị khởi tạo ban đầu cho các phần tử được set = 0</t>
+  </si>
+  <si>
+    <r>
+      <t>int* arr = (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>int*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>calloc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(element_num </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>n ,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> size_each </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Q</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>int*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : calloc sẽ trả về kiểu void* nên cần ép kiểu cho nó</t>
+    </r>
+  </si>
+  <si>
+    <t>size của dữ liệu = n*Q</t>
+  </si>
+  <si>
+    <t>* Dùng calloc để tránh quên khởi tạo giá trị ban đầu cho dữ liệu, hoặc muốn ban đầu tất cả = 0</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dùng để </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>thay đổi kích thước</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (tăng hoặc giảm) 1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>con trỏ đã được cấp phát động</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bằng malloc(), calloc(), realloc() và </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>không làm thay đổi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> các phần tử cũ trong con trỏ đó</t>
+    </r>
+  </si>
+  <si>
+    <t>Có 2 trường hợp khi dùng realloc() :</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Mở rộng tại chỗ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> khi vẫn còn </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>đủ chỗ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> trong vùng nhớ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nếu </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>vùng nhớ không đủ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, realloc sẽ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>copy toàn bộ phần tử cũ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sang </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>vùng nhớ mới</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> có </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>đủ không gian</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để mở rộng, rồi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>giải phóng vùng nhớ cũ.</t>
+    </r>
+  </si>
+  <si>
+    <t>int *arr = (int*)malloc(3 * sizeof(int));</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>arr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>int*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>realloc</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>arr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5 * sizeof(int)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">// đối số của realloc ( </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>đối tượng con trỏ cần thay đổi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dung lượng sau khi thay đổi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> )</t>
+    </r>
+  </si>
+  <si>
+    <t>free(ptr)</t>
+  </si>
+  <si>
+    <t>Cách dùng đúng</t>
+  </si>
+  <si>
+    <t>free(ptr);</t>
+  </si>
+  <si>
+    <t>ptr = NULL;</t>
+  </si>
+  <si>
+    <r>
+      <t>Bản chất là delete con trỏ ptr, nhưng lúc này nếu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> gọi lại </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>biến</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ptr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> thì nó đang là </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dangling pointer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, sẽ dẫn đến lỗi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>undefined behavior</t>
+    </r>
+  </si>
+  <si>
+    <t>Trong C++ :</t>
+  </si>
+  <si>
+    <t>new() và delete</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Được sinh ra để </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cấp phát động cho class</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vì </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>malloc không có cơ chế hỗ trợ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> cho </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>contructor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>destructor</t>
+    </r>
+  </si>
+  <si>
+    <t>new()</t>
+  </si>
+  <si>
+    <t>cú pháp :</t>
+  </si>
+  <si>
+    <t>khai báo biến :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">khai báo mảng : </t>
+  </si>
+  <si>
+    <t>khai báo class :</t>
+  </si>
+  <si>
+    <t>int* p = new int(10);</t>
+  </si>
+  <si>
+    <t>int* arr = new int[3];</t>
+  </si>
+  <si>
+    <t>// cấp phát 1 mảng có 3 phần tử</t>
+  </si>
+  <si>
+    <t>// cấp phát động 1 biến int mang giá trị 10</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Printer* p = new Printer( </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>đối số của constructor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>copy constructor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) ;</t>
+    </r>
+  </si>
+  <si>
+    <t>delete()</t>
+  </si>
+  <si>
+    <t>clear biến :</t>
+  </si>
+  <si>
+    <t>delete p;</t>
+  </si>
+  <si>
+    <t>delete arr[];</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5394,6 +6790,20 @@
       <color rgb="FFD4D4D4"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="16">
@@ -5681,7 +7091,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -5873,6 +7283,9 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -11342,72 +12755,72 @@
     </row>
     <row r="3" spans="2:5">
       <c r="C3" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="5" spans="2:5">
       <c r="C5" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="D6" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="E6" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="D7" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="E7" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="C9" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="C11" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="D12" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="C15" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
     </row>
     <row r="17" spans="3:19">
       <c r="D17" s="83" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="E17" s="87"/>
       <c r="F17" s="87"/>
       <c r="G17" s="87"/>
       <c r="H17" s="87"/>
       <c r="I17" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
     </row>
     <row r="18" spans="3:19">
       <c r="D18" s="83" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="E18" s="87"/>
       <c r="F18" s="87"/>
       <c r="G18" s="87"/>
       <c r="H18" s="87"/>
       <c r="I18" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
     </row>
     <row r="19" spans="3:19">
@@ -11419,31 +12832,31 @@
     </row>
     <row r="20" spans="3:19">
       <c r="D20" s="85" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="E20" s="87"/>
       <c r="F20" s="87"/>
       <c r="G20" s="87"/>
       <c r="H20" s="87"/>
       <c r="I20" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
     </row>
     <row r="21" spans="3:19">
       <c r="D21" s="86" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="E21" s="87"/>
       <c r="F21" s="87"/>
       <c r="G21" s="87"/>
       <c r="H21" s="87"/>
       <c r="I21" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
     </row>
     <row r="22" spans="3:19">
       <c r="D22" s="86" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="E22" s="87"/>
       <c r="F22" s="87"/>
@@ -11468,7 +12881,7 @@
     </row>
     <row r="25" spans="3:19">
       <c r="D25" s="85" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="E25" s="87"/>
       <c r="F25" s="87"/>
@@ -11477,7 +12890,7 @@
     </row>
     <row r="26" spans="3:19">
       <c r="D26" s="86" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="E26" s="87"/>
       <c r="F26" s="87"/>
@@ -11486,7 +12899,7 @@
     </row>
     <row r="27" spans="3:19">
       <c r="D27" s="86" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="E27" s="87"/>
       <c r="F27" s="87"/>
@@ -11504,7 +12917,7 @@
     </row>
     <row r="31" spans="3:19">
       <c r="C31" s="88" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="D31" s="88"/>
       <c r="E31" s="88"/>
@@ -11516,7 +12929,7 @@
       <c r="K31" s="88"/>
       <c r="L31" s="88"/>
       <c r="M31" s="89" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="N31" s="89"/>
       <c r="O31" s="89"/>
@@ -11547,7 +12960,7 @@
     <row r="33" spans="3:19">
       <c r="C33" s="88"/>
       <c r="D33" s="88" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="E33" s="88"/>
       <c r="F33" s="88"/>
@@ -11558,7 +12971,7 @@
       <c r="K33" s="88"/>
       <c r="L33" s="88"/>
       <c r="M33" s="89" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="N33" s="89"/>
       <c r="O33" s="89"/>
@@ -11579,7 +12992,7 @@
       <c r="K34" s="88"/>
       <c r="L34" s="88"/>
       <c r="M34" s="89" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="N34" s="89"/>
       <c r="O34" s="89"/>
@@ -11612,7 +13025,7 @@
     <row r="36" spans="3:19">
       <c r="C36" s="88"/>
       <c r="D36" s="88" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="E36" s="88"/>
       <c r="F36" s="88"/>
@@ -11626,7 +13039,7 @@
     <row r="37" spans="3:19">
       <c r="C37" s="88"/>
       <c r="D37" s="88" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="E37" s="88"/>
       <c r="F37" s="88"/>
@@ -11664,101 +13077,101 @@
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="C4" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="D6" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="D7" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="D8" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="E8" s="80"/>
     </row>
     <row r="9" spans="2:5">
       <c r="D9" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="D10" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="D11" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="D12" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="D13" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="D14" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="D15" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="D16" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
     </row>
     <row r="17" spans="3:12">
       <c r="D17" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
     </row>
     <row r="18" spans="3:12">
       <c r="D18" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
     </row>
     <row r="19" spans="3:12">
       <c r="D19" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="22" spans="3:12">
       <c r="C22" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
     </row>
     <row r="23" spans="3:12">
       <c r="D23" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="L23" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
     </row>
     <row r="24" spans="3:12">
       <c r="D24" s="81" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="E24" s="90"/>
       <c r="F24" s="90"/>
@@ -11769,7 +13182,7 @@
     </row>
     <row r="25" spans="3:12">
       <c r="D25" s="81" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="E25" s="90"/>
       <c r="F25" s="90"/>
@@ -11780,12 +13193,12 @@
     </row>
     <row r="27" spans="3:12">
       <c r="D27" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
     </row>
     <row r="28" spans="3:12">
       <c r="D28" s="81" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="E28" s="90"/>
       <c r="F28" s="90"/>
@@ -11796,7 +13209,7 @@
     </row>
     <row r="29" spans="3:12">
       <c r="D29" s="81" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="E29" s="90"/>
       <c r="F29" s="90"/>
@@ -11807,7 +13220,7 @@
     </row>
     <row r="30" spans="3:12">
       <c r="D30" s="82" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="E30" s="90"/>
       <c r="F30" s="90"/>
@@ -11818,42 +13231,42 @@
     </row>
     <row r="33" spans="3:13">
       <c r="D33" s="91" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="34" spans="3:13">
       <c r="E34" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
     </row>
     <row r="35" spans="3:13">
       <c r="F35" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
     </row>
     <row r="36" spans="3:13">
       <c r="F36" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
     </row>
     <row r="39" spans="3:13">
       <c r="C39" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
     </row>
     <row r="41" spans="3:13">
       <c r="D41" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="43" spans="3:13">
       <c r="D43" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
     </row>
     <row r="44" spans="3:13">
       <c r="E44" s="81" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="F44" s="90"/>
       <c r="G44" s="90"/>
@@ -11877,7 +13290,7 @@
     </row>
     <row r="46" spans="3:13">
       <c r="E46" s="81" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="F46" s="90"/>
       <c r="G46" s="90"/>
@@ -11890,7 +13303,7 @@
     </row>
     <row r="47" spans="3:13">
       <c r="E47" s="81" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="F47" s="90"/>
       <c r="G47" s="90"/>
@@ -11903,7 +13316,7 @@
     </row>
     <row r="48" spans="3:13">
       <c r="E48" s="81" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="F48" s="90"/>
       <c r="G48" s="90"/>
@@ -11916,7 +13329,7 @@
     </row>
     <row r="49" spans="4:13">
       <c r="E49" s="82" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="F49" s="90"/>
       <c r="G49" s="90"/>
@@ -11929,7 +13342,7 @@
     </row>
     <row r="50" spans="4:13">
       <c r="E50" s="81" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="F50" s="90"/>
       <c r="G50" s="90"/>
@@ -11942,27 +13355,27 @@
     </row>
     <row r="53" spans="4:13">
       <c r="D53" s="91" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="54" spans="4:13">
       <c r="E54" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="55" spans="4:13">
       <c r="E55" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
     </row>
     <row r="56" spans="4:13">
       <c r="E56" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
     </row>
     <row r="57" spans="4:13">
       <c r="E57" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
     </row>
   </sheetData>
@@ -11978,89 +13391,89 @@
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="3" spans="2:5">
       <c r="C3" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="D3" t="s">
+        <v>508</v>
+      </c>
+      <c r="E3" t="s">
         <v>511</v>
-      </c>
-      <c r="E3" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="C4" s="80" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="D4" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="E4" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="C7" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="C8" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="C10" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="C11" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="C12" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="C13" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="C14" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="C15" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="C16" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
     </row>
     <row r="17" spans="3:3">
       <c r="C17" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
     </row>
     <row r="18" spans="3:3">
       <c r="C18" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
     </row>
     <row r="20" spans="3:3">
       <c r="C20" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="21" spans="3:3">
@@ -12070,17 +13483,17 @@
     </row>
     <row r="23" spans="3:3">
       <c r="C23" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
     </row>
     <row r="24" spans="3:3">
       <c r="C24" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
     </row>
     <row r="25" spans="3:3">
       <c r="C25" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
     </row>
   </sheetData>
@@ -12090,12 +13503,75 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2"/>
+  <dimension ref="B2:E16"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="2" spans="2:2">
+    <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
-        <v>439</v>
+        <v>643</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5">
+      <c r="C3" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5">
+      <c r="C4" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5">
+      <c r="C6" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5">
+      <c r="D7" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
+      <c r="D8" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5">
+      <c r="C10" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5">
+      <c r="C11" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5">
+      <c r="D12" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5">
+      <c r="C13" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5">
+      <c r="D14" t="s">
+        <v>650</v>
+      </c>
+      <c r="E14" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5">
+      <c r="C15" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5">
+      <c r="D16" t="s">
+        <v>652</v>
       </c>
     </row>
   </sheetData>
@@ -12152,86 +13628,565 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:D20"/>
+  <dimension ref="B2:I48"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
-        <v>480</v>
+        <v>654</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" ht="18.5">
+      <c r="C3" s="96" t="s">
+        <v>656</v>
+      </c>
+      <c r="D3" s="97"/>
+    </row>
+    <row r="5" spans="2:4">
+      <c r="C5" t="s">
+        <v>657</v>
+      </c>
+      <c r="D5" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
+      <c r="D6" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4">
+      <c r="D7" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="D8" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4">
+      <c r="D9" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4">
+      <c r="C11" t="s">
+        <v>658</v>
+      </c>
+      <c r="D11" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4">
+      <c r="D12" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4">
+      <c r="D13" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4">
+      <c r="D14" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4">
+      <c r="D15" s="95" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4">
+      <c r="D16" s="76" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5">
+      <c r="C17" t="s">
+        <v>659</v>
+      </c>
+      <c r="D17" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="18" spans="3:5">
+      <c r="D18" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="19" spans="3:5">
+      <c r="E19" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="20" spans="3:5">
+      <c r="E20" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="21" spans="3:5">
+      <c r="D21" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="22" spans="3:5">
+      <c r="D22" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="23" spans="3:5">
+      <c r="D23" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="24" spans="3:5">
+      <c r="D24" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="26" spans="3:5">
+      <c r="C26" t="s">
+        <v>677</v>
+      </c>
+      <c r="D26" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="27" spans="3:5">
+      <c r="D27" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="28" spans="3:5">
+      <c r="E28" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="29" spans="3:5">
+      <c r="E29" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" ht="18.5">
+      <c r="C33" s="96" t="s">
+        <v>682</v>
+      </c>
+      <c r="D33" s="97"/>
+    </row>
+    <row r="35" spans="3:9">
+      <c r="C35" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9">
+      <c r="D36" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="38" spans="3:9">
+      <c r="D38" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="39" spans="3:9">
+      <c r="E39" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="40" spans="3:9">
+      <c r="E40" t="s">
+        <v>687</v>
+      </c>
+      <c r="G40" t="s">
+        <v>690</v>
+      </c>
+      <c r="I40" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="41" spans="3:9">
+      <c r="E41" t="s">
+        <v>688</v>
+      </c>
+      <c r="G41" t="s">
+        <v>691</v>
+      </c>
+      <c r="I41" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="42" spans="3:9">
+      <c r="E42" t="s">
+        <v>689</v>
+      </c>
+      <c r="G42" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="44" spans="3:9">
+      <c r="D44" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="45" spans="3:9">
+      <c r="E45" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="46" spans="3:9">
+      <c r="E46" t="s">
+        <v>696</v>
+      </c>
+      <c r="G46" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="47" spans="3:9">
+      <c r="E47" t="s">
+        <v>688</v>
+      </c>
+      <c r="G47" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="48" spans="3:9">
+      <c r="E48" t="s">
+        <v>689</v>
+      </c>
+      <c r="G48" t="s">
+        <v>697</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:E85"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="2" spans="2:4">
+      <c r="B2" s="6" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="3" spans="2:4">
       <c r="C3" t="s">
+        <v>528</v>
+      </c>
+      <c r="D3" t="s">
         <v>532</v>
-      </c>
-      <c r="D3" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="C4" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="D4" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
     </row>
     <row r="5" spans="2:4">
       <c r="C5" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="D5" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
     </row>
     <row r="10" spans="2:4">
       <c r="B10" s="6" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="11" spans="2:4">
       <c r="C11" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
     </row>
     <row r="12" spans="2:4">
       <c r="C12" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
     </row>
     <row r="13" spans="2:4">
       <c r="C13" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
     </row>
     <row r="14" spans="2:4">
       <c r="C14" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
     </row>
     <row r="16" spans="2:4">
       <c r="C16" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="C17" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5">
+      <c r="C18" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
+      <c r="C19" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="17" spans="3:3">
-      <c r="C17" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="18" spans="3:3">
-      <c r="C18" t="s">
+    <row r="20" spans="2:5">
+      <c r="C20" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="19" spans="3:3">
-      <c r="C19" t="s">
+    <row r="22" spans="2:5">
+      <c r="D22" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5">
+      <c r="E23" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5">
+      <c r="E24" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5">
+      <c r="E25" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5">
+      <c r="B28" s="6" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5">
+      <c r="C29" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5">
+      <c r="D30" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="20" spans="3:3">
-      <c r="C20" t="s">
+    <row r="31" spans="2:5">
+      <c r="D31" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5">
+      <c r="D32" t="s">
         <v>609</v>
+      </c>
+    </row>
+    <row r="34" spans="3:5">
+      <c r="D34" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="36" spans="3:5">
+      <c r="D36" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="37" spans="3:5">
+      <c r="E37" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="38" spans="3:5">
+      <c r="E38" s="17" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="39" spans="3:5">
+      <c r="E39" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="41" spans="3:5">
+      <c r="E41" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="42" spans="3:5">
+      <c r="E42" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="43" spans="3:5">
+      <c r="E43" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="45" spans="3:5">
+      <c r="C45" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="46" spans="3:5">
+      <c r="D46" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="47" spans="3:5">
+      <c r="D47" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5">
+      <c r="D49" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5">
+      <c r="E50" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5">
+      <c r="E51" s="17" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5">
+      <c r="E52" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5">
+      <c r="E54" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5">
+      <c r="E55" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5">
+      <c r="E56" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5">
+      <c r="D58" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5">
+      <c r="D59" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5">
+      <c r="B62" s="6" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5">
+      <c r="C63" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5">
+      <c r="C64" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="65" spans="3:4">
+      <c r="C65" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="67" spans="3:4">
+      <c r="C67" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="69" spans="3:4">
+      <c r="D69" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="70" spans="3:4">
+      <c r="D70" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="71" spans="3:4">
+      <c r="D71" s="17" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="72" spans="3:4">
+      <c r="D72" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="73" spans="3:4">
+      <c r="D73" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="75" spans="3:4">
+      <c r="D75" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="76" spans="3:4">
+      <c r="D76" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="77" spans="3:4">
+      <c r="D77" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="78" spans="3:4">
+      <c r="D78" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="79" spans="3:4">
+      <c r="D79" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3">
+      <c r="B82" s="6" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3">
+      <c r="C83" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3">
+      <c r="C84" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="85" spans="2:3">
+      <c r="C85" t="s">
+        <v>638</v>
       </c>
     </row>
   </sheetData>
@@ -14128,7 +16083,7 @@
         <v>287</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="D49" s="51">
         <v>0.9</v>
@@ -14143,7 +16098,7 @@
         <v>319</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="D50" s="42">
         <v>1</v>
@@ -14171,7 +16126,7 @@
         <v>321</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D52" s="42">
         <v>1</v>
@@ -14188,7 +16143,9 @@
       <c r="C53" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="D53" s="6"/>
+      <c r="D53" s="42">
+        <v>1</v>
+      </c>
       <c r="E53" s="6"/>
       <c r="F53" s="16" t="s">
         <v>14</v>
@@ -14209,16 +16166,20 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" ht="43.5">
       <c r="B55" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="C55" s="6" t="s">
-        <v>516</v>
-      </c>
-      <c r="D55" s="6"/>
+      <c r="C55" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="D55" s="51">
+        <v>0.5</v>
+      </c>
       <c r="E55" s="6"/>
-      <c r="F55" s="6"/>
+      <c r="F55" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="5" t="s">
@@ -14227,9 +16188,11 @@
       <c r="C56" s="6" t="s">
         <v>450</v>
       </c>
-      <c r="D56" s="6"/>
+      <c r="D56" s="42">
+        <v>0.5</v>
+      </c>
       <c r="E56" s="16" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="F56" s="6"/>
     </row>
@@ -14238,7 +16201,7 @@
         <v>16.100000000000001</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D57" s="42">
         <v>1</v>
@@ -14253,7 +16216,7 @@
         <v>16.2</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D58" s="42">
         <v>1</v>
@@ -14270,38 +16233,50 @@
       <c r="C59" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="D59" s="6"/>
+      <c r="D59" s="42">
+        <v>1</v>
+      </c>
       <c r="E59" s="6"/>
-      <c r="F59" s="6"/>
-    </row>
-    <row r="60" spans="2:6">
+      <c r="F59" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" ht="29">
       <c r="B60" s="5">
         <v>16.399999999999999</v>
       </c>
-      <c r="C60" s="6" t="s">
-        <v>452</v>
-      </c>
-      <c r="D60" s="6"/>
+      <c r="C60" s="7" t="s">
+        <v>626</v>
+      </c>
+      <c r="D60" s="42">
+        <v>1</v>
+      </c>
       <c r="E60" s="6"/>
-      <c r="F60" s="6"/>
+      <c r="F60" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="5">
         <v>16.5</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>453</v>
-      </c>
-      <c r="D61" s="6"/>
+        <v>625</v>
+      </c>
+      <c r="D61" s="42">
+        <v>1</v>
+      </c>
       <c r="E61" s="6"/>
-      <c r="F61" s="6"/>
-    </row>
-    <row r="62" spans="2:6">
+      <c r="F61" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6" ht="58">
       <c r="B62" s="5">
         <v>16.600000000000001</v>
       </c>
-      <c r="C62" s="6" t="s">
-        <v>454</v>
+      <c r="C62" s="7" t="s">
+        <v>627</v>
       </c>
       <c r="D62" s="6"/>
       <c r="E62" s="6"/>
@@ -14312,7 +16287,7 @@
         <v>16.7</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
@@ -14320,10 +16295,10 @@
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="5" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
@@ -14334,7 +16309,7 @@
         <v>17.100000000000001</v>
       </c>
       <c r="C65" s="78" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="D65" s="6"/>
       <c r="E65" s="6"/>
@@ -14345,7 +16320,7 @@
         <v>17.2</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D66" s="6"/>
       <c r="E66" s="6"/>
@@ -14356,11 +16331,11 @@
         <v>17.3</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="D67" s="6"/>
       <c r="E67" s="16" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="F67" s="6"/>
     </row>
@@ -14369,7 +16344,7 @@
         <v>17.399999999999999</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
@@ -14380,7 +16355,7 @@
         <v>17.5</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="D69" s="6"/>
       <c r="E69" s="6"/>
@@ -14388,10 +16363,10 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="C70" s="6" t="s">
         <v>460</v>
-      </c>
-      <c r="C70" s="6" t="s">
-        <v>463</v>
       </c>
       <c r="D70" s="6"/>
       <c r="E70" s="6"/>
@@ -14402,7 +16377,7 @@
         <v>18.100000000000001</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D71" s="6"/>
       <c r="E71" s="6"/>
@@ -14413,7 +16388,7 @@
         <v>18.2</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="D72" s="6"/>
       <c r="E72" s="6"/>
@@ -14424,7 +16399,7 @@
         <v>18.3</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="D73" s="6"/>
       <c r="E73" s="6"/>
@@ -14435,7 +16410,7 @@
         <v>18.399999999999999</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="D74" s="6"/>
       <c r="E74" s="6"/>
@@ -14443,10 +16418,10 @@
     </row>
     <row r="75" spans="2:6">
       <c r="B75" s="5" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D75" s="6"/>
       <c r="E75" s="6"/>
@@ -14457,7 +16432,7 @@
         <v>19.100000000000001</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D76" s="6"/>
       <c r="E76" s="6"/>
@@ -14465,7 +16440,7 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="5" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>438</v>
@@ -14476,7 +16451,7 @@
     </row>
     <row r="78" spans="2:6">
       <c r="B78" s="5" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>288</v>
@@ -14501,7 +16476,7 @@
         <v>21.2</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D80" s="6"/>
       <c r="E80" s="6"/>
@@ -14509,36 +16484,36 @@
     </row>
     <row r="81" spans="2:6">
       <c r="B81" s="5" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>323</v>
       </c>
       <c r="D81" s="6"/>
       <c r="E81" s="16" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="F81" s="6"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="5" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D82" s="6"/>
       <c r="E82" s="16" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="F82" s="6"/>
     </row>
     <row r="83" spans="2:6">
       <c r="B83" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="C83" s="6" t="s">
         <v>481</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>484</v>
       </c>
       <c r="D83" s="6"/>
       <c r="E83" s="16"/>
@@ -14546,10 +16521,10 @@
     </row>
     <row r="84" spans="2:6">
       <c r="B84" s="5" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D84" s="6"/>
       <c r="E84" s="16"/>
@@ -14557,23 +16532,23 @@
     </row>
     <row r="85" spans="2:6" ht="58">
       <c r="B85" s="5" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C85" s="79" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D85" s="6"/>
       <c r="E85" s="16" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="F85" s="6"/>
     </row>
     <row r="86" spans="2:6" ht="29">
       <c r="B86" s="5" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="D86" s="6"/>
       <c r="E86" s="16"/>
@@ -14581,10 +16556,10 @@
     </row>
     <row r="87" spans="2:6">
       <c r="B87" s="5" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D87" s="6"/>
       <c r="E87" s="16"/>
@@ -14592,10 +16567,10 @@
     </row>
     <row r="88" spans="2:6" ht="58">
       <c r="B88" s="5" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D88" s="6"/>
       <c r="E88" s="16"/>
@@ -14603,10 +16578,10 @@
     </row>
     <row r="89" spans="2:6" ht="29">
       <c r="B89" s="5" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="D89" s="6"/>
       <c r="E89" s="16"/>
@@ -14614,14 +16589,14 @@
     </row>
     <row r="90" spans="2:6">
       <c r="B90" s="77" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C90" s="57" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="D90" s="1"/>
       <c r="E90" s="49" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="F90" s="1"/>
     </row>
@@ -14684,6 +16659,10 @@
     <hyperlink ref="F50" location="'#10'!B2" display="Link"/>
     <hyperlink ref="F53" location="'#13'!B2" display="Link"/>
     <hyperlink ref="F58" location="'#16'!B10" display="Link"/>
+    <hyperlink ref="F59" location="'#16'!B28" display="Link"/>
+    <hyperlink ref="F60" location="'#16'!B62" display="Link"/>
+    <hyperlink ref="F61" location="'#16'!B82" display="Link"/>
+    <hyperlink ref="F55" location="'#15'!B2" display="Link"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId12"/>

--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" firstSheet="2" activeTab="16"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Knowhow" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="710">
   <si>
     <t>No.</t>
   </si>
@@ -6628,6 +6628,41 @@
   </si>
   <si>
     <t>delete arr[];</t>
+  </si>
+  <si>
+    <t>Object Slicing (cắt lát đối tượng)</t>
+  </si>
+  <si>
+    <t>thì những phương thức/thuộc tính riêng của lớp dẫn xuất sẽ bị cắt bỏ, chỉ hoạt động như là lớp cơ sở</t>
+  </si>
+  <si>
+    <t>Khái niệm : Khi gán 1 biến/đối tượng của lớp cơ sở = biến/đối tượng của lớp dẫn xuất mà không thông qua con trỏ</t>
+  </si>
+  <si>
+    <t>Base b = d ;</t>
+  </si>
+  <si>
+    <t>Delivered d ;</t>
+  </si>
+  <si>
+    <t>Cách phòng tránh : Khai báo kiểu con trỏ lớp cơ sở, nó sẽ chỉ quản lý địa chỉ</t>
+  </si>
+  <si>
+    <t>Base* b = new Delivered();</t>
+  </si>
+  <si>
+    <t>Note : 
+Đa hình lúc biên dịch : Overloading
+Đa hình lúc chạy : Overriding</t>
+  </si>
+  <si>
+    <t>Về câu hỏi thì, do chỉ khai báo con trỏ để có địa chỉ quản lý thôi, nên sẽ không ảnh hưởng đến thuộc tính riêng của lớp dẫn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">xuât nhé. Thêm vào đó, đoạn sau " = new Delivered()" cho ta thấy rằng đây là cấp phát động, cung cấp vùng nhớ để </t>
+  </si>
+  <si>
+    <t>chứa được Delivered rồi.</t>
   </si>
 </sst>
 </file>
@@ -6898,7 +6933,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -7086,12 +7121,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -7274,6 +7318,9 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7283,9 +7330,12 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -11416,19 +11466,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:K22"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="5.7265625" customWidth="1"/>
-    <col min="3" max="3" width="37.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.453125" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" customWidth="1"/>
+    <col min="3" max="3" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.42578125" customWidth="1"/>
     <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="18.5">
+    <row r="2" spans="2:11" ht="18.75">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -11454,7 +11504,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:11" ht="43.5">
+    <row r="3" spans="2:11" ht="45">
       <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
@@ -11808,9 +11858,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Q30"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="11" max="11" width="3.7265625" customWidth="1"/>
+    <col min="11" max="11" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:17">
@@ -12140,12 +12190,12 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E76"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="4.453125" customWidth="1"/>
-    <col min="3" max="3" width="39.7265625" customWidth="1"/>
-    <col min="4" max="4" width="50.81640625" customWidth="1"/>
-    <col min="5" max="5" width="75.453125" customWidth="1"/>
+    <col min="2" max="2" width="4.42578125" customWidth="1"/>
+    <col min="3" max="3" width="39.7109375" customWidth="1"/>
+    <col min="4" max="4" width="50.85546875" customWidth="1"/>
+    <col min="5" max="5" width="75.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.5">
@@ -12153,7 +12203,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="23.5">
+    <row r="2" spans="1:5" ht="23.25">
       <c r="B2" s="63" t="s">
         <v>420</v>
       </c>
@@ -12172,7 +12222,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="43.5">
+    <row r="5" spans="1:5" ht="45">
       <c r="B5" s="69">
         <v>1</v>
       </c>
@@ -12200,7 +12250,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="29">
+    <row r="7" spans="1:5" ht="30">
       <c r="B7" s="69">
         <v>3</v>
       </c>
@@ -12214,7 +12264,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="23.5">
+    <row r="10" spans="1:5" ht="23.25">
       <c r="B10" s="63" t="s">
         <v>344</v>
       </c>
@@ -12233,7 +12283,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" ht="30">
       <c r="B13" s="69">
         <v>1</v>
       </c>
@@ -12247,7 +12297,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="29">
+    <row r="14" spans="1:5" ht="30">
       <c r="B14" s="69">
         <v>2</v>
       </c>
@@ -12261,7 +12311,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="29">
+    <row r="15" spans="1:5" ht="30">
       <c r="B15" s="69">
         <v>3</v>
       </c>
@@ -12275,7 +12325,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="29">
+    <row r="16" spans="1:5" ht="30">
       <c r="B16" s="69">
         <v>4</v>
       </c>
@@ -12289,7 +12339,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="145">
+    <row r="17" spans="2:5" ht="165">
       <c r="B17" s="69">
         <v>5</v>
       </c>
@@ -12303,7 +12353,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="159.5">
+    <row r="18" spans="2:5" ht="180">
       <c r="B18" s="69">
         <v>6</v>
       </c>
@@ -12317,7 +12367,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="130.5">
+    <row r="19" spans="2:5" ht="135">
       <c r="B19" s="69">
         <v>7</v>
       </c>
@@ -12331,7 +12381,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="130.5">
+    <row r="20" spans="2:5" ht="135">
       <c r="B20" s="69">
         <v>8</v>
       </c>
@@ -12345,7 +12395,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="23" spans="2:5" ht="23.5">
+    <row r="23" spans="2:5" ht="23.25">
       <c r="B23" s="63" t="s">
         <v>419</v>
       </c>
@@ -12412,7 +12462,7 @@
       </c>
       <c r="E29" s="1"/>
     </row>
-    <row r="32" spans="2:5" ht="23.5">
+    <row r="32" spans="2:5" ht="23.25">
       <c r="B32" s="63" t="s">
         <v>418</v>
       </c>
@@ -12428,7 +12478,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="35" spans="2:4" ht="29">
+    <row r="35" spans="2:4" ht="30">
       <c r="B35" s="65">
         <v>1</v>
       </c>
@@ -12450,7 +12500,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="37" spans="2:4">
+    <row r="37" spans="2:4" ht="30">
       <c r="B37" s="65">
         <v>3</v>
       </c>
@@ -12472,7 +12522,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="41" spans="2:4" ht="23.5">
+    <row r="41" spans="2:4" ht="23.25">
       <c r="B41" s="63" t="s">
         <v>417</v>
       </c>
@@ -12488,7 +12538,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="44" spans="2:4">
+    <row r="44" spans="2:4" ht="30">
       <c r="B44" s="65">
         <v>1</v>
       </c>
@@ -12532,7 +12582,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="50" spans="2:4" ht="23.5">
+    <row r="50" spans="2:4" ht="23.25">
       <c r="B50" s="63" t="s">
         <v>416</v>
       </c>
@@ -12584,7 +12634,7 @@
     <row r="56" spans="2:4">
       <c r="B56" s="65"/>
     </row>
-    <row r="58" spans="2:4" ht="23.5">
+    <row r="58" spans="2:4" ht="23.25">
       <c r="B58" s="63" t="s">
         <v>415</v>
       </c>
@@ -12611,7 +12661,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="62" spans="2:4" ht="29">
+    <row r="62" spans="2:4" ht="45">
       <c r="B62" s="65">
         <v>2</v>
       </c>
@@ -12622,7 +12672,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="63" spans="2:4" ht="29">
+    <row r="63" spans="2:4" ht="30">
       <c r="B63" s="65">
         <v>3</v>
       </c>
@@ -12655,7 +12705,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="68" spans="2:4" ht="23.5">
+    <row r="68" spans="2:4" ht="23.25">
       <c r="B68" s="63" t="s">
         <v>400</v>
       </c>
@@ -12746,7 +12796,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:S38"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -13073,7 +13123,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:M57"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -13387,7 +13437,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E25"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -13504,7 +13554,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E16"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -13582,7 +13632,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
@@ -13629,18 +13679,18 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I48"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="18.5">
-      <c r="C3" s="96" t="s">
+    <row r="3" spans="2:4" ht="18.75">
+      <c r="C3" s="93" t="s">
         <v>656</v>
       </c>
-      <c r="D3" s="97"/>
+      <c r="D3" s="94"/>
     </row>
     <row r="5" spans="2:4">
       <c r="C5" t="s">
@@ -13694,7 +13744,7 @@
       </c>
     </row>
     <row r="15" spans="2:4">
-      <c r="D15" s="95" t="s">
+      <c r="D15" s="92" t="s">
         <v>668</v>
       </c>
     </row>
@@ -13769,11 +13819,11 @@
         <v>680</v>
       </c>
     </row>
-    <row r="33" spans="3:9" ht="18.5">
-      <c r="C33" s="96" t="s">
+    <row r="33" spans="3:9" ht="18.75">
+      <c r="C33" s="93" t="s">
         <v>682</v>
       </c>
-      <c r="D33" s="97"/>
+      <c r="D33" s="94"/>
     </row>
     <row r="35" spans="3:9">
       <c r="C35" t="s">
@@ -13867,8 +13917,8 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:E85"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="B2:I101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
@@ -14169,44 +14219,109 @@
         <v>615</v>
       </c>
     </row>
-    <row r="82" spans="2:3">
+    <row r="82" spans="2:9">
       <c r="B82" s="6" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="83" spans="2:3">
+    <row r="83" spans="2:9">
       <c r="C83" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="84" spans="2:3">
+    <row r="84" spans="2:9">
       <c r="C84" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="85" spans="2:3">
+    <row r="85" spans="2:9">
       <c r="C85" t="s">
         <v>638</v>
       </c>
     </row>
+    <row r="89" spans="2:9" ht="54" customHeight="1">
+      <c r="B89" s="98" t="s">
+        <v>627</v>
+      </c>
+      <c r="C89" s="99"/>
+      <c r="D89" s="99"/>
+      <c r="E89" s="99"/>
+      <c r="F89" s="99"/>
+      <c r="G89" s="99"/>
+      <c r="H89" s="99"/>
+      <c r="I89" s="99"/>
+    </row>
+    <row r="91" spans="2:9">
+      <c r="B91" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="92" spans="2:9">
+      <c r="C92" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9">
+      <c r="C93" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="94" spans="2:9">
+      <c r="D94" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="95" spans="2:9">
+      <c r="D95" s="17" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="96" spans="2:9">
+      <c r="C96" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="97" spans="3:4">
+      <c r="D97" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="99" spans="3:4">
+      <c r="C99" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="100" spans="3:4">
+      <c r="C100" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="101" spans="3:4">
+      <c r="C101" t="s">
+        <v>709</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B89:I89"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:F103"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="12.26953125" customWidth="1"/>
-    <col min="4" max="4" width="13.54296875" customWidth="1"/>
-    <col min="5" max="5" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.1796875" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="18.5">
+    <row r="2" spans="2:6" ht="18.75">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -15349,12 +15464,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:G90"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="50.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="68.54296875" customWidth="1"/>
-    <col min="6" max="6" width="9.7265625" customWidth="1"/>
+    <col min="3" max="3" width="50.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6">
@@ -15362,7 +15477,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="2:6" ht="18.5">
+    <row r="2" spans="2:6" ht="18.75">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -16108,7 +16223,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="2:6" ht="29">
+    <row r="51" spans="2:6" ht="30">
       <c r="B51" s="5" t="s">
         <v>320</v>
       </c>
@@ -16166,15 +16281,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="2:6" ht="43.5">
+    <row r="55" spans="2:6" ht="45">
       <c r="B55" s="5" t="s">
         <v>448</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>655</v>
       </c>
-      <c r="D55" s="51">
-        <v>0.5</v>
+      <c r="D55" s="42">
+        <v>1</v>
       </c>
       <c r="E55" s="6"/>
       <c r="F55" s="16" t="s">
@@ -16189,7 +16304,7 @@
         <v>450</v>
       </c>
       <c r="D56" s="42">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E56" s="16" t="s">
         <v>465</v>
@@ -16241,7 +16356,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="2:6" ht="29">
+    <row r="60" spans="2:6" ht="30">
       <c r="B60" s="5">
         <v>16.399999999999999</v>
       </c>
@@ -16271,27 +16386,37 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="58">
+    <row r="62" spans="2:6" ht="60">
       <c r="B62" s="5">
         <v>16.600000000000001</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>627</v>
       </c>
-      <c r="D62" s="6"/>
+      <c r="D62" s="42">
+        <v>1</v>
+      </c>
       <c r="E62" s="6"/>
-      <c r="F62" s="6"/>
-    </row>
-    <row r="63" spans="2:6" ht="40.5" customHeight="1">
+      <c r="F62" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6" ht="43.5" customHeight="1">
       <c r="B63" s="5">
         <v>16.7</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6"/>
-      <c r="F63" s="6"/>
+      <c r="D63" s="42">
+        <v>1</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>706</v>
+      </c>
+      <c r="F63" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="5" t="s">
@@ -16304,7 +16429,7 @@
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>
     </row>
-    <row r="65" spans="2:6" ht="29">
+    <row r="65" spans="2:6" ht="30">
       <c r="B65" s="5">
         <v>17.100000000000001</v>
       </c>
@@ -16315,7 +16440,7 @@
       <c r="E65" s="6"/>
       <c r="F65" s="6"/>
     </row>
-    <row r="66" spans="2:6" ht="29">
+    <row r="66" spans="2:6" ht="30">
       <c r="B66" s="5">
         <v>17.2</v>
       </c>
@@ -16339,7 +16464,7 @@
       </c>
       <c r="F67" s="6"/>
     </row>
-    <row r="68" spans="2:6" ht="29">
+    <row r="68" spans="2:6" ht="30">
       <c r="B68" s="5">
         <v>17.399999999999999</v>
       </c>
@@ -16471,7 +16596,7 @@
       <c r="E79" s="6"/>
       <c r="F79" s="6"/>
     </row>
-    <row r="80" spans="2:6" ht="29">
+    <row r="80" spans="2:6" ht="30">
       <c r="B80" s="5">
         <v>21.2</v>
       </c>
@@ -16530,7 +16655,7 @@
       <c r="E84" s="16"/>
       <c r="F84" s="6"/>
     </row>
-    <row r="85" spans="2:6" ht="58">
+    <row r="85" spans="2:6" ht="60">
       <c r="B85" s="5" t="s">
         <v>492</v>
       </c>
@@ -16543,7 +16668,7 @@
       </c>
       <c r="F85" s="6"/>
     </row>
-    <row r="86" spans="2:6" ht="29">
+    <row r="86" spans="2:6" ht="30">
       <c r="B86" s="5" t="s">
         <v>493</v>
       </c>
@@ -16565,7 +16690,7 @@
       <c r="E87" s="16"/>
       <c r="F87" s="6"/>
     </row>
-    <row r="88" spans="2:6" ht="58">
+    <row r="88" spans="2:6" ht="60">
       <c r="B88" s="5" t="s">
         <v>495</v>
       </c>
@@ -16576,7 +16701,7 @@
       <c r="E88" s="16"/>
       <c r="F88" s="6"/>
     </row>
-    <row r="89" spans="2:6" ht="29">
+    <row r="89" spans="2:6" ht="30">
       <c r="B89" s="5" t="s">
         <v>496</v>
       </c>
@@ -16663,6 +16788,8 @@
     <hyperlink ref="F60" location="'#16'!B62" display="Link"/>
     <hyperlink ref="F61" location="'#16'!B82" display="Link"/>
     <hyperlink ref="F55" location="'#15'!B2" display="Link"/>
+    <hyperlink ref="F62" location="'#16'!B89" display="Link"/>
+    <hyperlink ref="F63" location="'#16'!B10" display="Link"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId12"/>
@@ -16672,13 +16799,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J164"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.26953125" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.5">
+    <row r="1" spans="1:3" ht="18.75">
       <c r="C1" s="41" t="s">
         <v>15</v>
       </c>
@@ -16935,14 +17062,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L61"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="10.453125" customWidth="1"/>
-    <col min="4" max="4" width="5.26953125" customWidth="1"/>
-    <col min="5" max="5" width="48.81640625" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" customWidth="1"/>
+    <col min="4" max="4" width="5.28515625" customWidth="1"/>
+    <col min="5" max="5" width="48.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.5">
+    <row r="1" spans="1:10" ht="18.75">
       <c r="C1" s="41" t="s">
         <v>57</v>
       </c>
@@ -16973,14 +17100,14 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15" thickBot="1">
+    <row r="12" spans="1:10" ht="15.75" thickBot="1">
       <c r="C12" s="11" t="s">
         <v>63</v>
       </c>
       <c r="D12" s="11"/>
     </row>
-    <row r="13" spans="1:10" ht="15" thickBot="1">
-      <c r="C13" s="92" t="s">
+    <row r="13" spans="1:10" ht="15.75" thickBot="1">
+      <c r="C13" s="95" t="s">
         <v>78</v>
       </c>
       <c r="D13" s="26" t="s">
@@ -16996,8 +17123,8 @@
       <c r="H13" s="24"/>
       <c r="I13" s="25"/>
     </row>
-    <row r="14" spans="1:10" ht="15" thickBot="1">
-      <c r="C14" s="93"/>
+    <row r="14" spans="1:10" ht="15.75" thickBot="1">
+      <c r="C14" s="96"/>
       <c r="D14" s="23" t="s">
         <v>65</v>
       </c>
@@ -17013,7 +17140,7 @@
       <c r="J14" s="25"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="C15" s="93"/>
+      <c r="C15" s="96"/>
       <c r="D15" s="26" t="s">
         <v>66</v>
       </c>
@@ -17028,7 +17155,7 @@
       <c r="I15" s="28"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="C16" s="93"/>
+      <c r="C16" s="96"/>
       <c r="D16" s="29"/>
       <c r="E16" s="30" t="s">
         <v>74</v>
@@ -17038,8 +17165,8 @@
       <c r="H16" s="30"/>
       <c r="I16" s="31"/>
     </row>
-    <row r="17" spans="3:12" ht="15" thickBot="1">
-      <c r="C17" s="94"/>
+    <row r="17" spans="3:12" ht="15.75" thickBot="1">
+      <c r="C17" s="97"/>
       <c r="D17" s="32"/>
       <c r="E17" s="33" t="s">
         <v>75</v>
@@ -17049,7 +17176,7 @@
       <c r="H17" s="30"/>
       <c r="I17" s="31"/>
     </row>
-    <row r="18" spans="3:12" ht="15" thickBot="1">
+    <row r="18" spans="3:12" ht="15.75" thickBot="1">
       <c r="C18" s="37" t="s">
         <v>79</v>
       </c>
@@ -17069,8 +17196,8 @@
       <c r="K18" s="24"/>
       <c r="L18" s="25"/>
     </row>
-    <row r="19" spans="3:12" ht="15" thickBot="1">
-      <c r="C19" s="92" t="s">
+    <row r="19" spans="3:12" ht="15.75" thickBot="1">
+      <c r="C19" s="95" t="s">
         <v>78</v>
       </c>
       <c r="D19" s="23" t="s">
@@ -17081,7 +17208,7 @@
       </c>
     </row>
     <row r="20" spans="3:12">
-      <c r="C20" s="93"/>
+      <c r="C20" s="96"/>
       <c r="D20" s="26" t="s">
         <v>82</v>
       </c>
@@ -17089,8 +17216,8 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="3:12" ht="15" thickBot="1">
-      <c r="C21" s="94"/>
+    <row r="21" spans="3:12" ht="15.75" thickBot="1">
+      <c r="C21" s="97"/>
       <c r="D21" s="32"/>
       <c r="E21" s="40" t="s">
         <v>84</v>
@@ -17203,10 +17330,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:V102"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="13" max="13" width="4.81640625" customWidth="1"/>
+    <col min="13" max="13" width="4.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
@@ -17721,7 +17848,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D32"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" s="6" t="s">
@@ -17844,10 +17971,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:H90"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="13.54296875" customWidth="1"/>
-    <col min="7" max="7" width="9.453125" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4">
@@ -18213,9 +18340,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Z40"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="17.1796875" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:26">

--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="4" activeTab="18"/>
   </bookViews>
   <sheets>
     <sheet name="Knowhow" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <sheet name="#14" sheetId="12" r:id="rId16"/>
     <sheet name="#15" sheetId="18" r:id="rId17"/>
     <sheet name="#16" sheetId="15" r:id="rId18"/>
+    <sheet name="#31" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="718">
   <si>
     <t>No.</t>
   </si>
@@ -6663,6 +6664,30 @@
   </si>
   <si>
     <t>chứa được Delivered rồi.</t>
+  </si>
+  <si>
+    <t>OpenAPI : Module của tôi đóng vai trò là module trung gian, cung cấp thông tin của máy in cho UI, App nội bộ, App và Web bên ngoài.</t>
+  </si>
+  <si>
+    <t>Thông tin cung cấp là các API tạo message dưới dạng XML</t>
+  </si>
+  <si>
+    <t>Nó chính là mô hình client-server trong đó :</t>
+  </si>
+  <si>
+    <t>Server</t>
+  </si>
+  <si>
+    <t>OpenAPI</t>
+  </si>
+  <si>
+    <t>Client</t>
+  </si>
+  <si>
+    <t>&lt;-------------------------(Message XML)----------------&gt;</t>
+  </si>
+  <si>
+    <t>Internal App, UI, External App, Web</t>
   </si>
 </sst>
 </file>
@@ -6841,7 +6866,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6932,8 +6957,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="18">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -7130,12 +7167,100 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -7336,6 +7461,14 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -14310,6 +14443,61 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:O9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2" spans="2:15">
+      <c r="B2" s="6" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15">
+      <c r="C4" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15">
+      <c r="C5" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15">
+      <c r="C6" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15">
+      <c r="F8" s="104" t="s">
+        <v>713</v>
+      </c>
+      <c r="L8" s="105" t="s">
+        <v>715</v>
+      </c>
+      <c r="M8" s="106"/>
+      <c r="N8" s="106"/>
+      <c r="O8" s="107"/>
+    </row>
+    <row r="9" spans="2:15">
+      <c r="F9" s="100" t="s">
+        <v>714</v>
+      </c>
+      <c r="G9" t="s">
+        <v>716</v>
+      </c>
+      <c r="L9" s="101" t="s">
+        <v>717</v>
+      </c>
+      <c r="M9" s="102"/>
+      <c r="N9" s="102"/>
+      <c r="O9" s="103"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:F103"/>
@@ -16708,9 +16896,13 @@
       <c r="C89" s="7" t="s">
         <v>479</v>
       </c>
-      <c r="D89" s="6"/>
+      <c r="D89" s="42">
+        <v>0</v>
+      </c>
       <c r="E89" s="16"/>
-      <c r="F89" s="6"/>
+      <c r="F89" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="90" spans="2:6">
       <c r="B90" s="77" t="s">
@@ -16790,6 +16982,7 @@
     <hyperlink ref="F55" location="'#15'!B2" display="Link"/>
     <hyperlink ref="F62" location="'#16'!B89" display="Link"/>
     <hyperlink ref="F63" location="'#16'!B10" display="Link"/>
+    <hyperlink ref="F89" location="'#31'!B2" display="Link"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId12"/>

--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -25,7 +25,8 @@
     <sheet name="#14" sheetId="12" r:id="rId16"/>
     <sheet name="#15" sheetId="18" r:id="rId17"/>
     <sheet name="#16" sheetId="15" r:id="rId18"/>
-    <sheet name="#31" sheetId="19" r:id="rId19"/>
+    <sheet name="#24" sheetId="20" r:id="rId19"/>
+    <sheet name="#31" sheetId="19" r:id="rId20"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="738">
   <si>
     <t>No.</t>
   </si>
@@ -3639,9 +3640,6 @@
     <t>#14</t>
   </si>
   <si>
-    <t>Các thuật toán sort phổ biến trong C++. Triển khai minh họa.</t>
-  </si>
-  <si>
     <t>https://chatgpt.com/share/690b291c-d088-8002-b37a-10bb5da410ce</t>
   </si>
   <si>
@@ -3804,9 +3802,6 @@
   </si>
   <si>
     <t>#24</t>
-  </si>
-  <si>
-    <t>Design Pattern phổ biến</t>
   </si>
   <si>
     <t>What is the purpose of std::move()?, Move constructor và move assignment operation ? move semantics ? perfect forwarding ?</t>
@@ -6688,13 +6683,750 @@
   </si>
   <si>
     <t>Internal App, UI, External App, Web</t>
+  </si>
+  <si>
+    <t>Các thuật toán sort phổ biến trong C++. Phải viết đc hết.</t>
+  </si>
+  <si>
+    <t>Server : luôn lắng nghe yêu cầu</t>
+  </si>
+  <si>
+    <t>Client : Máy khách, gửi request và nhận phản hồi respone</t>
+  </si>
+  <si>
+    <t>Nhận msg từ App</t>
+  </si>
+  <si>
+    <t>Tạo thread = _beginthread</t>
+  </si>
+  <si>
+    <t>quản lý race condition là công việc của module thread</t>
+  </si>
+  <si>
+    <t>bằng lock_guard(mutex)</t>
+  </si>
+  <si>
+    <t>XML Parse ( sử dụng thư viện XML)</t>
+  </si>
+  <si>
+    <r>
+      <t>class</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>singleton</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>static</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>singleton</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&amp;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>getInstance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>static</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>singleton</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>instance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC586C0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>return</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>instance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <t>private:</t>
+  </si>
+  <si>
+    <r>
+      <t>singleton</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(){</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>std</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>cout</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Singleton Created"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>singleton</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>singleton</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&amp;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ins</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>delete</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>singleton</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&amp;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>operator=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>singleton</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&amp;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ins</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>delete</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>main</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>singleton</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&amp;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>singleton</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>getInstance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>singleton</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&amp;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>singleton</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>getInstance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>return</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <t>Design Pattern : 
+Phải triển khai được singleton và Observer</t>
+  </si>
+  <si>
+    <t>singleton</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6865,8 +7597,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF4EC9B0"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6969,8 +7707,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="26">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -7255,12 +7999,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -7446,6 +8199,14 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7461,14 +8222,43 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -11335,6 +12125,61 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Arrow Connector 2"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2257425" y="3152775"/>
+          <a:ext cx="2628900" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -12938,72 +13783,72 @@
     </row>
     <row r="3" spans="2:5">
       <c r="C3" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="5" spans="2:5">
       <c r="C5" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="D6" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E6" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="D7" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E7" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="C9" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="C11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="D12" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="C15" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="17" spans="3:19">
       <c r="D17" s="83" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E17" s="87"/>
       <c r="F17" s="87"/>
       <c r="G17" s="87"/>
       <c r="H17" s="87"/>
       <c r="I17" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="18" spans="3:19">
       <c r="D18" s="83" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="E18" s="87"/>
       <c r="F18" s="87"/>
       <c r="G18" s="87"/>
       <c r="H18" s="87"/>
       <c r="I18" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="19" spans="3:19">
@@ -13015,31 +13860,31 @@
     </row>
     <row r="20" spans="3:19">
       <c r="D20" s="85" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E20" s="87"/>
       <c r="F20" s="87"/>
       <c r="G20" s="87"/>
       <c r="H20" s="87"/>
       <c r="I20" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="21" spans="3:19">
       <c r="D21" s="86" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E21" s="87"/>
       <c r="F21" s="87"/>
       <c r="G21" s="87"/>
       <c r="H21" s="87"/>
       <c r="I21" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="22" spans="3:19">
       <c r="D22" s="86" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E22" s="87"/>
       <c r="F22" s="87"/>
@@ -13064,7 +13909,7 @@
     </row>
     <row r="25" spans="3:19">
       <c r="D25" s="85" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E25" s="87"/>
       <c r="F25" s="87"/>
@@ -13073,7 +13918,7 @@
     </row>
     <row r="26" spans="3:19">
       <c r="D26" s="86" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="E26" s="87"/>
       <c r="F26" s="87"/>
@@ -13082,7 +13927,7 @@
     </row>
     <row r="27" spans="3:19">
       <c r="D27" s="86" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="E27" s="87"/>
       <c r="F27" s="87"/>
@@ -13100,7 +13945,7 @@
     </row>
     <row r="31" spans="3:19">
       <c r="C31" s="88" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="D31" s="88"/>
       <c r="E31" s="88"/>
@@ -13112,7 +13957,7 @@
       <c r="K31" s="88"/>
       <c r="L31" s="88"/>
       <c r="M31" s="89" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="N31" s="89"/>
       <c r="O31" s="89"/>
@@ -13143,7 +13988,7 @@
     <row r="33" spans="3:19">
       <c r="C33" s="88"/>
       <c r="D33" s="88" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E33" s="88"/>
       <c r="F33" s="88"/>
@@ -13154,7 +13999,7 @@
       <c r="K33" s="88"/>
       <c r="L33" s="88"/>
       <c r="M33" s="89" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="N33" s="89"/>
       <c r="O33" s="89"/>
@@ -13175,7 +14020,7 @@
       <c r="K34" s="88"/>
       <c r="L34" s="88"/>
       <c r="M34" s="89" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="N34" s="89"/>
       <c r="O34" s="89"/>
@@ -13208,7 +14053,7 @@
     <row r="36" spans="3:19">
       <c r="C36" s="88"/>
       <c r="D36" s="88" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E36" s="88"/>
       <c r="F36" s="88"/>
@@ -13222,7 +14067,7 @@
     <row r="37" spans="3:19">
       <c r="C37" s="88"/>
       <c r="D37" s="88" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E37" s="88"/>
       <c r="F37" s="88"/>
@@ -13260,101 +14105,101 @@
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="C4" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="D6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="D7" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="D8" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="E8" s="80"/>
     </row>
     <row r="9" spans="2:5">
       <c r="D9" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="D10" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="D11" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="D12" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="D13" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="D14" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="D15" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="D16" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="17" spans="3:12">
       <c r="D17" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="18" spans="3:12">
       <c r="D18" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="19" spans="3:12">
       <c r="D19" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="22" spans="3:12">
       <c r="C22" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="23" spans="3:12">
       <c r="D23" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="L23" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="24" spans="3:12">
       <c r="D24" s="81" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E24" s="90"/>
       <c r="F24" s="90"/>
@@ -13365,7 +14210,7 @@
     </row>
     <row r="25" spans="3:12">
       <c r="D25" s="81" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E25" s="90"/>
       <c r="F25" s="90"/>
@@ -13376,12 +14221,12 @@
     </row>
     <row r="27" spans="3:12">
       <c r="D27" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="28" spans="3:12">
       <c r="D28" s="81" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E28" s="90"/>
       <c r="F28" s="90"/>
@@ -13392,7 +14237,7 @@
     </row>
     <row r="29" spans="3:12">
       <c r="D29" s="81" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E29" s="90"/>
       <c r="F29" s="90"/>
@@ -13403,7 +14248,7 @@
     </row>
     <row r="30" spans="3:12">
       <c r="D30" s="82" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E30" s="90"/>
       <c r="F30" s="90"/>
@@ -13414,42 +14259,42 @@
     </row>
     <row r="33" spans="3:13">
       <c r="D33" s="91" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="34" spans="3:13">
       <c r="E34" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="35" spans="3:13">
       <c r="F35" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="36" spans="3:13">
       <c r="F36" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="39" spans="3:13">
       <c r="C39" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="41" spans="3:13">
       <c r="D41" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="43" spans="3:13">
       <c r="D43" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="44" spans="3:13">
       <c r="E44" s="81" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="F44" s="90"/>
       <c r="G44" s="90"/>
@@ -13473,7 +14318,7 @@
     </row>
     <row r="46" spans="3:13">
       <c r="E46" s="81" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="F46" s="90"/>
       <c r="G46" s="90"/>
@@ -13486,7 +14331,7 @@
     </row>
     <row r="47" spans="3:13">
       <c r="E47" s="81" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="F47" s="90"/>
       <c r="G47" s="90"/>
@@ -13499,7 +14344,7 @@
     </row>
     <row r="48" spans="3:13">
       <c r="E48" s="81" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="F48" s="90"/>
       <c r="G48" s="90"/>
@@ -13512,7 +14357,7 @@
     </row>
     <row r="49" spans="4:13">
       <c r="E49" s="82" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="F49" s="90"/>
       <c r="G49" s="90"/>
@@ -13525,7 +14370,7 @@
     </row>
     <row r="50" spans="4:13">
       <c r="E50" s="81" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="F50" s="90"/>
       <c r="G50" s="90"/>
@@ -13538,27 +14383,27 @@
     </row>
     <row r="53" spans="4:13">
       <c r="D53" s="91" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="54" spans="4:13">
       <c r="E54" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="55" spans="4:13">
       <c r="E55" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="56" spans="4:13">
       <c r="E56" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="57" spans="4:13">
       <c r="E57" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
   </sheetData>
@@ -13574,89 +14419,89 @@
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="3" spans="2:5">
       <c r="C3" t="s">
+        <v>507</v>
+      </c>
+      <c r="D3" t="s">
+        <v>506</v>
+      </c>
+      <c r="E3" t="s">
         <v>509</v>
-      </c>
-      <c r="D3" t="s">
-        <v>508</v>
-      </c>
-      <c r="E3" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="C4" s="80" t="s">
+        <v>508</v>
+      </c>
+      <c r="D4" t="s">
+        <v>505</v>
+      </c>
+      <c r="E4" t="s">
         <v>510</v>
-      </c>
-      <c r="D4" t="s">
-        <v>507</v>
-      </c>
-      <c r="E4" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="C7" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="C8" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="C10" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="C11" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="C12" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="C13" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="C14" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="C15" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="C16" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="17" spans="3:3">
       <c r="C17" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="18" spans="3:3">
       <c r="C18" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="20" spans="3:3">
       <c r="C20" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="21" spans="3:3">
@@ -13666,17 +14511,17 @@
     </row>
     <row r="23" spans="3:3">
       <c r="C23" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="24" spans="3:3">
       <c r="C24" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="25" spans="3:3">
       <c r="C25" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>
@@ -13691,70 +14536,70 @@
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="3" spans="2:5">
       <c r="C3" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="C4" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="C6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="D7" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="D8" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="C10" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="C11" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="D12" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="C13" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="D14" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E14" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="C15" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="D16" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
   </sheetData>
@@ -13769,38 +14614,38 @@
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="3" spans="2:4">
       <c r="C3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="C4" s="76" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="5" spans="2:4">
       <c r="B5" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="6" spans="2:4">
       <c r="C6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D6" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="7" spans="2:4">
       <c r="C7" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
   </sheetData>
@@ -13816,230 +14661,230 @@
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="3" spans="2:4" ht="18.75">
       <c r="C3" s="93" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D3" s="94"/>
     </row>
     <row r="5" spans="2:4">
       <c r="C5" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D5" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="6" spans="2:4">
       <c r="D6" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="7" spans="2:4">
       <c r="D7" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8" spans="2:4">
       <c r="D8" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="9" spans="2:4">
       <c r="D9" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="11" spans="2:4">
       <c r="C11" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D11" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
     </row>
     <row r="12" spans="2:4">
       <c r="D12" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="13" spans="2:4">
       <c r="D13" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="14" spans="2:4">
       <c r="D14" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="15" spans="2:4">
       <c r="D15" s="92" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="16" spans="2:4">
       <c r="D16" s="76" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="17" spans="3:5">
       <c r="C17" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D17" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="18" spans="3:5">
       <c r="D18" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="19" spans="3:5">
       <c r="E19" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="20" spans="3:5">
       <c r="E20" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="21" spans="3:5">
       <c r="D21" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="22" spans="3:5">
       <c r="D22" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="23" spans="3:5">
       <c r="D23" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
     </row>
     <row r="24" spans="3:5">
       <c r="D24" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="26" spans="3:5">
       <c r="C26" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D26" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
     </row>
     <row r="27" spans="3:5">
       <c r="D27" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
     </row>
     <row r="28" spans="3:5">
       <c r="E28" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
     </row>
     <row r="29" spans="3:5">
       <c r="E29" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="33" spans="3:9" ht="18.75">
       <c r="C33" s="93" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="D33" s="94"/>
     </row>
     <row r="35" spans="3:9">
       <c r="C35" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="36" spans="3:9">
       <c r="D36" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="38" spans="3:9">
       <c r="D38" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
     </row>
     <row r="39" spans="3:9">
       <c r="E39" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="40" spans="3:9">
       <c r="E40" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="G40" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="I40" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="41" spans="3:9">
       <c r="E41" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="G41" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="I41" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="42" spans="3:9">
       <c r="E42" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="G42" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="44" spans="3:9">
       <c r="D44" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="45" spans="3:9">
       <c r="E45" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="46" spans="3:9">
       <c r="E46" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="G46" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="47" spans="3:9">
       <c r="E47" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="G47" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="48" spans="3:9">
       <c r="E48" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="G48" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
   </sheetData>
@@ -14055,96 +14900,96 @@
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="3" spans="2:4">
       <c r="C3" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="C4" t="s">
+        <v>527</v>
+      </c>
+      <c r="D4" t="s">
         <v>529</v>
-      </c>
-      <c r="D4" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="5" spans="2:4">
       <c r="C5" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="D5" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="10" spans="2:4">
       <c r="B10" s="6" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="11" spans="2:4">
       <c r="C11" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="12" spans="2:4">
       <c r="C12" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="13" spans="2:4">
       <c r="C13" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="14" spans="2:4">
       <c r="C14" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="16" spans="2:4">
       <c r="C16" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="17" spans="2:5">
       <c r="C17" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="18" spans="2:5">
       <c r="C18" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="19" spans="2:5">
       <c r="C19" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="20" spans="2:5">
       <c r="C20" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="22" spans="2:5">
       <c r="D22" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="23" spans="2:5">
       <c r="E23" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="24" spans="2:5">
       <c r="E24" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="25" spans="2:5">
@@ -14154,167 +14999,167 @@
     </row>
     <row r="28" spans="2:5">
       <c r="B28" s="6" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="29" spans="2:5">
       <c r="C29" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="30" spans="2:5">
       <c r="D30" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="31" spans="2:5">
       <c r="D31" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="32" spans="2:5">
       <c r="D32" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="34" spans="3:5">
       <c r="D34" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="36" spans="3:5">
       <c r="D36" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="37" spans="3:5">
       <c r="E37" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="38" spans="3:5">
       <c r="E38" s="17" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="39" spans="3:5">
       <c r="E39" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="41" spans="3:5">
       <c r="E41" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="42" spans="3:5">
       <c r="E42" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="43" spans="3:5">
       <c r="E43" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="45" spans="3:5">
       <c r="C45" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="46" spans="3:5">
       <c r="D46" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="47" spans="3:5">
       <c r="D47" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="49" spans="2:5">
       <c r="D49" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="50" spans="2:5">
       <c r="E50" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="51" spans="2:5">
       <c r="E51" s="17" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="52" spans="2:5">
       <c r="E52" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="54" spans="2:5">
       <c r="E54" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="55" spans="2:5">
       <c r="E55" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="56" spans="2:5">
       <c r="E56" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="58" spans="2:5">
       <c r="D58" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="59" spans="2:5">
       <c r="D59" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="62" spans="2:5">
       <c r="B62" s="6" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="63" spans="2:5">
       <c r="C63" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="64" spans="2:5">
       <c r="C64" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="65" spans="3:4">
       <c r="C65" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="67" spans="3:4">
       <c r="C67" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="69" spans="3:4">
       <c r="D69" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="70" spans="3:4">
       <c r="D70" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="71" spans="3:4">
       <c r="D71" s="17" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="72" spans="3:4">
@@ -14324,22 +15169,22 @@
     </row>
     <row r="73" spans="3:4">
       <c r="D73" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="75" spans="3:4">
       <c r="D75" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="76" spans="3:4">
       <c r="D76" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="77" spans="3:4">
       <c r="D77" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="78" spans="3:4">
@@ -14349,89 +15194,89 @@
     </row>
     <row r="79" spans="3:4">
       <c r="D79" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="82" spans="2:9">
       <c r="B82" s="6" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="83" spans="2:9">
       <c r="C83" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="84" spans="2:9">
       <c r="C84" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="85" spans="2:9">
       <c r="C85" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="89" spans="2:9" ht="54" customHeight="1">
-      <c r="B89" s="98" t="s">
-        <v>627</v>
-      </c>
-      <c r="C89" s="99"/>
-      <c r="D89" s="99"/>
-      <c r="E89" s="99"/>
-      <c r="F89" s="99"/>
-      <c r="G89" s="99"/>
-      <c r="H89" s="99"/>
-      <c r="I89" s="99"/>
+      <c r="B89" s="106" t="s">
+        <v>625</v>
+      </c>
+      <c r="C89" s="107"/>
+      <c r="D89" s="107"/>
+      <c r="E89" s="107"/>
+      <c r="F89" s="107"/>
+      <c r="G89" s="107"/>
+      <c r="H89" s="107"/>
+      <c r="I89" s="107"/>
     </row>
     <row r="91" spans="2:9">
       <c r="B91" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="92" spans="2:9">
       <c r="C92" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="93" spans="2:9">
       <c r="C93" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="94" spans="2:9">
       <c r="D94" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
     </row>
     <row r="95" spans="2:9">
       <c r="D95" s="17" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="96" spans="2:9">
       <c r="C96" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="97" spans="3:4">
       <c r="D97" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="99" spans="3:4">
       <c r="C99" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="100" spans="3:4">
       <c r="C100" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="101" spans="3:4">
       <c r="C101" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
     </row>
   </sheetData>
@@ -14445,56 +15290,265 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:O9"/>
+  <dimension ref="B2:J23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="2:15">
-      <c r="B2" s="6" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="4" spans="2:15">
-      <c r="C4" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="5" spans="2:15">
-      <c r="C5" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15">
-      <c r="C6" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="8" spans="2:15">
-      <c r="F8" s="104" t="s">
-        <v>713</v>
-      </c>
-      <c r="L8" s="105" t="s">
-        <v>715</v>
-      </c>
-      <c r="M8" s="106"/>
-      <c r="N8" s="106"/>
-      <c r="O8" s="107"/>
-    </row>
-    <row r="9" spans="2:15">
-      <c r="F9" s="100" t="s">
-        <v>714</v>
-      </c>
-      <c r="G9" t="s">
-        <v>716</v>
-      </c>
-      <c r="L9" s="101" t="s">
-        <v>717</v>
-      </c>
-      <c r="M9" s="102"/>
-      <c r="N9" s="102"/>
-      <c r="O9" s="103"/>
+    <row r="2" spans="2:10">
+      <c r="B2" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10">
+      <c r="C3" s="114" t="s">
+        <v>724</v>
+      </c>
+      <c r="D3" s="115"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="115"/>
+      <c r="H3" s="115"/>
+      <c r="I3" s="115"/>
+      <c r="J3" s="115"/>
+    </row>
+    <row r="4" spans="2:10">
+      <c r="C4" s="116" t="s">
+        <v>514</v>
+      </c>
+      <c r="D4" s="115"/>
+      <c r="E4" s="115"/>
+      <c r="F4" s="115"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="115"/>
+    </row>
+    <row r="5" spans="2:10">
+      <c r="C5" s="114" t="s">
+        <v>631</v>
+      </c>
+      <c r="D5" s="115"/>
+      <c r="E5" s="115"/>
+      <c r="F5" s="115"/>
+      <c r="G5" s="115"/>
+      <c r="H5" s="115"/>
+      <c r="I5" s="115"/>
+      <c r="J5" s="115"/>
+    </row>
+    <row r="6" spans="2:10">
+      <c r="C6" s="114" t="s">
+        <v>725</v>
+      </c>
+      <c r="D6" s="115"/>
+      <c r="E6" s="115"/>
+      <c r="F6" s="115"/>
+      <c r="G6" s="115"/>
+      <c r="H6" s="115"/>
+      <c r="I6" s="115"/>
+      <c r="J6" s="115"/>
+    </row>
+    <row r="7" spans="2:10">
+      <c r="C7" s="116" t="s">
+        <v>514</v>
+      </c>
+      <c r="D7" s="115"/>
+      <c r="E7" s="115"/>
+      <c r="F7" s="115"/>
+      <c r="G7" s="115"/>
+      <c r="H7" s="115"/>
+      <c r="I7" s="115"/>
+      <c r="J7" s="115"/>
+    </row>
+    <row r="8" spans="2:10">
+      <c r="C8" s="116" t="s">
+        <v>726</v>
+      </c>
+      <c r="D8" s="115"/>
+      <c r="E8" s="115"/>
+      <c r="F8" s="115"/>
+      <c r="G8" s="115"/>
+      <c r="H8" s="115"/>
+      <c r="I8" s="115"/>
+      <c r="J8" s="115"/>
+    </row>
+    <row r="9" spans="2:10">
+      <c r="C9" s="116" t="s">
+        <v>727</v>
+      </c>
+      <c r="D9" s="115"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="115"/>
+      <c r="H9" s="115"/>
+      <c r="I9" s="115"/>
+      <c r="J9" s="115"/>
+    </row>
+    <row r="10" spans="2:10">
+      <c r="C10" s="116" t="s">
+        <v>284</v>
+      </c>
+      <c r="D10" s="115"/>
+      <c r="E10" s="115"/>
+      <c r="F10" s="115"/>
+      <c r="G10" s="115"/>
+      <c r="H10" s="115"/>
+      <c r="I10" s="115"/>
+      <c r="J10" s="115"/>
+    </row>
+    <row r="11" spans="2:10">
+      <c r="C11" s="114" t="s">
+        <v>728</v>
+      </c>
+      <c r="D11" s="115"/>
+      <c r="E11" s="115"/>
+      <c r="F11" s="115"/>
+      <c r="G11" s="115"/>
+      <c r="H11" s="115"/>
+      <c r="I11" s="115"/>
+      <c r="J11" s="115"/>
+    </row>
+    <row r="12" spans="2:10">
+      <c r="C12" s="117" t="s">
+        <v>729</v>
+      </c>
+      <c r="D12" s="115"/>
+      <c r="E12" s="115"/>
+      <c r="F12" s="115"/>
+      <c r="G12" s="115"/>
+      <c r="H12" s="115"/>
+      <c r="I12" s="115"/>
+      <c r="J12" s="115"/>
+    </row>
+    <row r="13" spans="2:10">
+      <c r="C13" s="117" t="s">
+        <v>730</v>
+      </c>
+      <c r="D13" s="115"/>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="115"/>
+      <c r="H13" s="115"/>
+      <c r="I13" s="115"/>
+      <c r="J13" s="115"/>
+    </row>
+    <row r="14" spans="2:10">
+      <c r="C14" s="118" t="s">
+        <v>731</v>
+      </c>
+      <c r="D14" s="115"/>
+      <c r="E14" s="115"/>
+      <c r="F14" s="115"/>
+      <c r="G14" s="115"/>
+      <c r="H14" s="115"/>
+      <c r="I14" s="115"/>
+      <c r="J14" s="115"/>
+    </row>
+    <row r="15" spans="2:10">
+      <c r="C15" s="116" t="s">
+        <v>613</v>
+      </c>
+      <c r="D15" s="115"/>
+      <c r="E15" s="115"/>
+      <c r="F15" s="115"/>
+      <c r="G15" s="115"/>
+      <c r="H15" s="115"/>
+      <c r="I15" s="115"/>
+      <c r="J15" s="115"/>
+    </row>
+    <row r="16" spans="2:10">
+      <c r="C16" s="119"/>
+      <c r="D16" s="115"/>
+      <c r="E16" s="115"/>
+      <c r="F16" s="115"/>
+      <c r="G16" s="115"/>
+      <c r="H16" s="115"/>
+      <c r="I16" s="115"/>
+      <c r="J16" s="115"/>
+    </row>
+    <row r="17" spans="3:10">
+      <c r="C17" s="114" t="s">
+        <v>732</v>
+      </c>
+      <c r="D17" s="115"/>
+      <c r="E17" s="115"/>
+      <c r="F17" s="115"/>
+      <c r="G17" s="115"/>
+      <c r="H17" s="115"/>
+      <c r="I17" s="115"/>
+      <c r="J17" s="115"/>
+    </row>
+    <row r="18" spans="3:10">
+      <c r="C18" s="116" t="s">
+        <v>514</v>
+      </c>
+      <c r="D18" s="115"/>
+      <c r="E18" s="115"/>
+      <c r="F18" s="115"/>
+      <c r="G18" s="115"/>
+      <c r="H18" s="115"/>
+      <c r="I18" s="115"/>
+      <c r="J18" s="115"/>
+    </row>
+    <row r="19" spans="3:10">
+      <c r="C19" s="118" t="s">
+        <v>733</v>
+      </c>
+      <c r="D19" s="115"/>
+      <c r="E19" s="115"/>
+      <c r="F19" s="115"/>
+      <c r="G19" s="115"/>
+      <c r="H19" s="115"/>
+      <c r="I19" s="115"/>
+      <c r="J19" s="115"/>
+    </row>
+    <row r="20" spans="3:10">
+      <c r="C20" s="118" t="s">
+        <v>734</v>
+      </c>
+      <c r="D20" s="115"/>
+      <c r="E20" s="115"/>
+      <c r="F20" s="115"/>
+      <c r="G20" s="115"/>
+      <c r="H20" s="115"/>
+      <c r="I20" s="115"/>
+      <c r="J20" s="115"/>
+    </row>
+    <row r="21" spans="3:10">
+      <c r="C21" s="120" t="s">
+        <v>735</v>
+      </c>
+      <c r="D21" s="115"/>
+      <c r="E21" s="115"/>
+      <c r="F21" s="115"/>
+      <c r="G21" s="115"/>
+      <c r="H21" s="115"/>
+      <c r="I21" s="115"/>
+      <c r="J21" s="115"/>
+    </row>
+    <row r="22" spans="3:10">
+      <c r="C22" s="116" t="s">
+        <v>284</v>
+      </c>
+      <c r="D22" s="115"/>
+      <c r="E22" s="115"/>
+      <c r="F22" s="115"/>
+      <c r="G22" s="115"/>
+      <c r="H22" s="115"/>
+      <c r="I22" s="115"/>
+      <c r="J22" s="115"/>
+    </row>
+    <row r="23" spans="3:10">
+      <c r="C23" s="115"/>
+      <c r="D23" s="115"/>
+      <c r="E23" s="115"/>
+      <c r="F23" s="115"/>
+      <c r="G23" s="115"/>
+      <c r="H23" s="115"/>
+      <c r="I23" s="115"/>
+      <c r="J23" s="115"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -15649,6 +16703,103 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:O20"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2" spans="2:15">
+      <c r="B2" s="6" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15">
+      <c r="C4" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15">
+      <c r="C5" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15">
+      <c r="C6" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15">
+      <c r="F8" s="99" t="s">
+        <v>711</v>
+      </c>
+      <c r="L8" s="100" t="s">
+        <v>713</v>
+      </c>
+      <c r="M8" s="101"/>
+      <c r="N8" s="101"/>
+      <c r="O8" s="102"/>
+    </row>
+    <row r="9" spans="2:15">
+      <c r="F9" s="95" t="s">
+        <v>712</v>
+      </c>
+      <c r="G9" t="s">
+        <v>714</v>
+      </c>
+      <c r="L9" s="96" t="s">
+        <v>715</v>
+      </c>
+      <c r="M9" s="97"/>
+      <c r="N9" s="97"/>
+      <c r="O9" s="98"/>
+    </row>
+    <row r="11" spans="2:15">
+      <c r="E11" t="s">
+        <v>717</v>
+      </c>
+      <c r="L11" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15">
+      <c r="D16" t="s">
+        <v>719</v>
+      </c>
+      <c r="I16" s="108" t="s">
+        <v>723</v>
+      </c>
+      <c r="J16" s="109"/>
+    </row>
+    <row r="17" spans="3:10" ht="15" customHeight="1">
+      <c r="I17" s="110"/>
+      <c r="J17" s="111"/>
+    </row>
+    <row r="18" spans="3:10">
+      <c r="D18" t="s">
+        <v>720</v>
+      </c>
+      <c r="I18" s="112"/>
+      <c r="J18" s="113"/>
+    </row>
+    <row r="19" spans="3:10">
+      <c r="C19" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="20" spans="3:10">
+      <c r="D20" t="s">
+        <v>722</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="I16:J18"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:G90"/>
@@ -16386,7 +17537,7 @@
         <v>287</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="D49" s="51">
         <v>0.9</v>
@@ -16401,7 +17552,7 @@
         <v>319</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="D50" s="42">
         <v>1</v>
@@ -16416,11 +17567,11 @@
         <v>320</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>436</v>
+        <v>716</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="16" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F51" s="6"/>
     </row>
@@ -16429,7 +17580,7 @@
         <v>321</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D52" s="42">
         <v>1</v>
@@ -16444,7 +17595,7 @@
         <v>322</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D53" s="42">
         <v>1</v>
@@ -16459,7 +17610,7 @@
         <v>435</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D54" s="42">
         <v>1</v>
@@ -16471,10 +17622,10 @@
     </row>
     <row r="55" spans="2:6" ht="45">
       <c r="B55" s="5" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D55" s="42">
         <v>1</v>
@@ -16486,16 +17637,16 @@
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="C56" s="6" t="s">
         <v>449</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>450</v>
       </c>
       <c r="D56" s="42">
         <v>1</v>
       </c>
       <c r="E56" s="16" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F56" s="6"/>
     </row>
@@ -16504,7 +17655,7 @@
         <v>16.100000000000001</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D57" s="42">
         <v>1</v>
@@ -16519,7 +17670,7 @@
         <v>16.2</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D58" s="42">
         <v>1</v>
@@ -16534,7 +17685,7 @@
         <v>16.3</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D59" s="42">
         <v>1</v>
@@ -16549,7 +17700,7 @@
         <v>16.399999999999999</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D60" s="42">
         <v>1</v>
@@ -16564,7 +17715,7 @@
         <v>16.5</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="D61" s="42">
         <v>1</v>
@@ -16579,7 +17730,7 @@
         <v>16.600000000000001</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D62" s="42">
         <v>1</v>
@@ -16594,13 +17745,13 @@
         <v>16.7</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D63" s="42">
         <v>1</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="F63" s="16" t="s">
         <v>14</v>
@@ -16608,10 +17759,10 @@
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="C64" s="6" t="s">
         <v>452</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>453</v>
       </c>
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
@@ -16622,7 +17773,7 @@
         <v>17.100000000000001</v>
       </c>
       <c r="C65" s="78" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D65" s="6"/>
       <c r="E65" s="6"/>
@@ -16633,7 +17784,7 @@
         <v>17.2</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D66" s="6"/>
       <c r="E66" s="6"/>
@@ -16644,11 +17795,11 @@
         <v>17.3</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D67" s="6"/>
       <c r="E67" s="16" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F67" s="6"/>
     </row>
@@ -16657,7 +17808,7 @@
         <v>17.399999999999999</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
@@ -16668,7 +17819,7 @@
         <v>17.5</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D69" s="6"/>
       <c r="E69" s="6"/>
@@ -16676,10 +17827,10 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="5" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D70" s="6"/>
       <c r="E70" s="6"/>
@@ -16690,7 +17841,7 @@
         <v>18.100000000000001</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D71" s="6"/>
       <c r="E71" s="6"/>
@@ -16701,7 +17852,7 @@
         <v>18.2</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D72" s="6"/>
       <c r="E72" s="6"/>
@@ -16712,7 +17863,7 @@
         <v>18.3</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D73" s="6"/>
       <c r="E73" s="6"/>
@@ -16723,7 +17874,7 @@
         <v>18.399999999999999</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D74" s="6"/>
       <c r="E74" s="6"/>
@@ -16731,10 +17882,10 @@
     </row>
     <row r="75" spans="2:6">
       <c r="B75" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="C75" s="6" t="s">
         <v>463</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>464</v>
       </c>
       <c r="D75" s="6"/>
       <c r="E75" s="6"/>
@@ -16745,7 +17896,7 @@
         <v>19.100000000000001</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D76" s="6"/>
       <c r="E76" s="6"/>
@@ -16753,10 +17904,10 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="5" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D77" s="6"/>
       <c r="E77" s="6"/>
@@ -16764,7 +17915,7 @@
     </row>
     <row r="78" spans="2:6">
       <c r="B78" s="5" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>288</v>
@@ -16789,7 +17940,7 @@
         <v>21.2</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D80" s="6"/>
       <c r="E80" s="6"/>
@@ -16797,36 +17948,38 @@
     </row>
     <row r="81" spans="2:6">
       <c r="B81" s="5" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>323</v>
       </c>
       <c r="D81" s="6"/>
       <c r="E81" s="16" t="s">
+        <v>468</v>
+      </c>
+      <c r="F81" s="6"/>
+    </row>
+    <row r="82" spans="2:6" ht="30">
+      <c r="B82" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="F81" s="6"/>
-    </row>
-    <row r="82" spans="2:6">
-      <c r="B82" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>471</v>
+      <c r="C82" s="7" t="s">
+        <v>736</v>
       </c>
       <c r="D82" s="6"/>
       <c r="E82" s="16" t="s">
-        <v>469</v>
-      </c>
-      <c r="F82" s="6"/>
+        <v>468</v>
+      </c>
+      <c r="F82" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="83" spans="2:6">
       <c r="B83" s="5" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D83" s="6"/>
       <c r="E83" s="16"/>
@@ -16834,10 +17987,10 @@
     </row>
     <row r="84" spans="2:6">
       <c r="B84" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="C84" s="6" t="s">
         <v>480</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>482</v>
       </c>
       <c r="D84" s="6"/>
       <c r="E84" s="16"/>
@@ -16845,23 +17998,23 @@
     </row>
     <row r="85" spans="2:6" ht="60">
       <c r="B85" s="5" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C85" s="79" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D85" s="6"/>
       <c r="E85" s="16" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="F85" s="6"/>
     </row>
     <row r="86" spans="2:6" ht="30">
       <c r="B86" s="5" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D86" s="6"/>
       <c r="E86" s="16"/>
@@ -16869,10 +18022,10 @@
     </row>
     <row r="87" spans="2:6">
       <c r="B87" s="5" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D87" s="6"/>
       <c r="E87" s="16"/>
@@ -16880,10 +18033,10 @@
     </row>
     <row r="88" spans="2:6" ht="60">
       <c r="B88" s="5" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D88" s="6"/>
       <c r="E88" s="16"/>
@@ -16891,10 +18044,10 @@
     </row>
     <row r="89" spans="2:6" ht="30">
       <c r="B89" s="5" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D89" s="42">
         <v>0</v>
@@ -16906,14 +18059,14 @@
     </row>
     <row r="90" spans="2:6">
       <c r="B90" s="77" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C90" s="57" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D90" s="1"/>
       <c r="E90" s="49" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F90" s="1"/>
     </row>
@@ -16983,6 +18136,7 @@
     <hyperlink ref="F62" location="'#16'!B89" display="Link"/>
     <hyperlink ref="F63" location="'#16'!B10" display="Link"/>
     <hyperlink ref="F89" location="'#31'!B2" display="Link"/>
+    <hyperlink ref="F82" location="'#24'!B2" display="Link"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId12"/>
@@ -17300,7 +18454,7 @@
       <c r="D12" s="11"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" thickBot="1">
-      <c r="C13" s="95" t="s">
+      <c r="C13" s="103" t="s">
         <v>78</v>
       </c>
       <c r="D13" s="26" t="s">
@@ -17317,7 +18471,7 @@
       <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:10" ht="15.75" thickBot="1">
-      <c r="C14" s="96"/>
+      <c r="C14" s="104"/>
       <c r="D14" s="23" t="s">
         <v>65</v>
       </c>
@@ -17333,7 +18487,7 @@
       <c r="J14" s="25"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="C15" s="96"/>
+      <c r="C15" s="104"/>
       <c r="D15" s="26" t="s">
         <v>66</v>
       </c>
@@ -17348,7 +18502,7 @@
       <c r="I15" s="28"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="C16" s="96"/>
+      <c r="C16" s="104"/>
       <c r="D16" s="29"/>
       <c r="E16" s="30" t="s">
         <v>74</v>
@@ -17359,7 +18513,7 @@
       <c r="I16" s="31"/>
     </row>
     <row r="17" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C17" s="97"/>
+      <c r="C17" s="105"/>
       <c r="D17" s="32"/>
       <c r="E17" s="33" t="s">
         <v>75</v>
@@ -17390,7 +18544,7 @@
       <c r="L18" s="25"/>
     </row>
     <row r="19" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C19" s="95" t="s">
+      <c r="C19" s="103" t="s">
         <v>78</v>
       </c>
       <c r="D19" s="23" t="s">
@@ -17401,7 +18555,7 @@
       </c>
     </row>
     <row r="20" spans="3:12">
-      <c r="C20" s="96"/>
+      <c r="C20" s="104"/>
       <c r="D20" s="26" t="s">
         <v>82</v>
       </c>
@@ -17410,7 +18564,7 @@
       </c>
     </row>
     <row r="21" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C21" s="97"/>
+      <c r="C21" s="105"/>
       <c r="D21" s="32"/>
       <c r="E21" s="40" t="s">
         <v>84</v>

--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="4" activeTab="18"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Knowhow" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1032" uniqueCount="782">
   <si>
     <t>No.</t>
   </si>
@@ -7420,6 +7420,2729 @@
   </si>
   <si>
     <t>singleton</t>
+  </si>
+  <si>
+    <r>
+      <t>#include</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;iostream&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#include</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;string&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#include</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;vector&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>#include</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;algorithm&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>class</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>IObserver</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>~IObserver</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>default</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>virtual</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>void</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>update</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>std</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>string</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>msg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>virtual</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>void</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>boFollow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">() </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>class</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>subject</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>std</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>string</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>message</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>std</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>vector</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>IObserver</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>*&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>observerList</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>void</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>add</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>IObserver</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ins</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>observerList</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>push_back</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ins</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>void</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>remove</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>IObserver</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ins</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>observerList</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>erase</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>std</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>remove</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>observerList</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>begin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>observerList</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>end</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ins</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">) , </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>observerList</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>end</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>());</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>void</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>notify</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC586C0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>for</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>auto</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ins</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>observerList</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>    {</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ins</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>-&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>update</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>message</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <t>    }</t>
+  </si>
+  <si>
+    <r>
+      <t>void</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>createMsg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>std</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>string</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>msg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>message</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>msg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">; </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>notify</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>class</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>concreteObserver</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>public</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>IObserver</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>std</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>string</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>subject</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>sub</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>concreteObserver</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>std</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>string</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ten</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>subject</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>subj</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ten</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>sub</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>subj</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>sub</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>-&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>add</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>this</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>void</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>boFollow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">() </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>override</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>sub</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>-&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>remove</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>this</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>std</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>cout</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Da xoa Mr."</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>std</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>endl</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>void</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>update</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>std</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>string</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>msg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>override</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>std</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>cout</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Mr."</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>" da nhan duoc thong bao : "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>msg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>std</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>endl</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>subject</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Bantin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC586C0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>new</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>subject</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>IObserver</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC586C0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>new</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>concreteObserver</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Anh"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Bantin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>IObserver</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC586C0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>new</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>concreteObserver</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Khang"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Bantin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>IObserver</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC586C0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>new</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>concreteObserver</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Phat"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Bantin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Bantin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>-&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>createMsg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Xin chao khach VIP"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>-&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>boFollow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Bantin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>-&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>createMsg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Xin chao khach #2"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>-&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>boFollow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Bantin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>-&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>createMsg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Xin chao Dad"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <t>Observer</t>
+  </si>
+  <si>
+    <t>observer</t>
   </si>
 </sst>
 </file>
@@ -8013,7 +10736,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -8207,6 +10930,25 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -8240,23 +10982,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -15218,16 +17944,16 @@
       </c>
     </row>
     <row r="89" spans="2:9" ht="54" customHeight="1">
-      <c r="B89" s="106" t="s">
+      <c r="B89" s="113" t="s">
         <v>625</v>
       </c>
-      <c r="C89" s="107"/>
-      <c r="D89" s="107"/>
-      <c r="E89" s="107"/>
-      <c r="F89" s="107"/>
-      <c r="G89" s="107"/>
-      <c r="H89" s="107"/>
-      <c r="I89" s="107"/>
+      <c r="C89" s="114"/>
+      <c r="D89" s="114"/>
+      <c r="E89" s="114"/>
+      <c r="F89" s="114"/>
+      <c r="G89" s="114"/>
+      <c r="H89" s="114"/>
+      <c r="I89" s="114"/>
     </row>
     <row r="91" spans="2:9">
       <c r="B91" t="s">
@@ -15290,7 +18016,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:J23"/>
+  <dimension ref="B2:Q108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:10">
@@ -15299,252 +18025,1793 @@
       </c>
     </row>
     <row r="3" spans="2:10">
-      <c r="C3" s="114" t="s">
+      <c r="C3" s="103" t="s">
         <v>724</v>
       </c>
-      <c r="D3" s="115"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="115"/>
-      <c r="G3" s="115"/>
-      <c r="H3" s="115"/>
-      <c r="I3" s="115"/>
-      <c r="J3" s="115"/>
+      <c r="D3" s="104"/>
+      <c r="E3" s="104"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="104"/>
+      <c r="H3" s="104"/>
+      <c r="I3" s="104"/>
+      <c r="J3" s="104"/>
     </row>
     <row r="4" spans="2:10">
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="105" t="s">
         <v>514</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115"/>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115"/>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115"/>
-      <c r="J4" s="115"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="104"/>
     </row>
     <row r="5" spans="2:10">
-      <c r="C5" s="114" t="s">
+      <c r="C5" s="103" t="s">
         <v>631</v>
       </c>
-      <c r="D5" s="115"/>
-      <c r="E5" s="115"/>
-      <c r="F5" s="115"/>
-      <c r="G5" s="115"/>
-      <c r="H5" s="115"/>
-      <c r="I5" s="115"/>
-      <c r="J5" s="115"/>
+      <c r="D5" s="104"/>
+      <c r="E5" s="104"/>
+      <c r="F5" s="104"/>
+      <c r="G5" s="104"/>
+      <c r="H5" s="104"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="104"/>
     </row>
     <row r="6" spans="2:10">
-      <c r="C6" s="114" t="s">
+      <c r="C6" s="103" t="s">
         <v>725</v>
       </c>
-      <c r="D6" s="115"/>
-      <c r="E6" s="115"/>
-      <c r="F6" s="115"/>
-      <c r="G6" s="115"/>
-      <c r="H6" s="115"/>
-      <c r="I6" s="115"/>
-      <c r="J6" s="115"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="104"/>
+      <c r="F6" s="104"/>
+      <c r="G6" s="104"/>
+      <c r="H6" s="104"/>
+      <c r="I6" s="104"/>
+      <c r="J6" s="104"/>
     </row>
     <row r="7" spans="2:10">
-      <c r="C7" s="116" t="s">
+      <c r="C7" s="105" t="s">
         <v>514</v>
       </c>
-      <c r="D7" s="115"/>
-      <c r="E7" s="115"/>
-      <c r="F7" s="115"/>
-      <c r="G7" s="115"/>
-      <c r="H7" s="115"/>
-      <c r="I7" s="115"/>
-      <c r="J7" s="115"/>
+      <c r="D7" s="104"/>
+      <c r="E7" s="104"/>
+      <c r="F7" s="104"/>
+      <c r="G7" s="104"/>
+      <c r="H7" s="104"/>
+      <c r="I7" s="104"/>
+      <c r="J7" s="104"/>
     </row>
     <row r="8" spans="2:10">
-      <c r="C8" s="116" t="s">
+      <c r="C8" s="105" t="s">
         <v>726</v>
       </c>
-      <c r="D8" s="115"/>
-      <c r="E8" s="115"/>
-      <c r="F8" s="115"/>
-      <c r="G8" s="115"/>
-      <c r="H8" s="115"/>
-      <c r="I8" s="115"/>
-      <c r="J8" s="115"/>
+      <c r="D8" s="104"/>
+      <c r="E8" s="104"/>
+      <c r="F8" s="104"/>
+      <c r="G8" s="104"/>
+      <c r="H8" s="104"/>
+      <c r="I8" s="104"/>
+      <c r="J8" s="104"/>
     </row>
     <row r="9" spans="2:10">
-      <c r="C9" s="116" t="s">
+      <c r="C9" s="105" t="s">
         <v>727</v>
       </c>
-      <c r="D9" s="115"/>
-      <c r="E9" s="115"/>
-      <c r="F9" s="115"/>
-      <c r="G9" s="115"/>
-      <c r="H9" s="115"/>
-      <c r="I9" s="115"/>
-      <c r="J9" s="115"/>
+      <c r="D9" s="104"/>
+      <c r="E9" s="104"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="104"/>
+      <c r="H9" s="104"/>
+      <c r="I9" s="104"/>
+      <c r="J9" s="104"/>
     </row>
     <row r="10" spans="2:10">
-      <c r="C10" s="116" t="s">
+      <c r="C10" s="105" t="s">
         <v>284</v>
       </c>
-      <c r="D10" s="115"/>
-      <c r="E10" s="115"/>
-      <c r="F10" s="115"/>
-      <c r="G10" s="115"/>
-      <c r="H10" s="115"/>
-      <c r="I10" s="115"/>
-      <c r="J10" s="115"/>
+      <c r="D10" s="104"/>
+      <c r="E10" s="104"/>
+      <c r="F10" s="104"/>
+      <c r="G10" s="104"/>
+      <c r="H10" s="104"/>
+      <c r="I10" s="104"/>
+      <c r="J10" s="104"/>
     </row>
     <row r="11" spans="2:10">
-      <c r="C11" s="114" t="s">
+      <c r="C11" s="103" t="s">
         <v>728</v>
       </c>
-      <c r="D11" s="115"/>
-      <c r="E11" s="115"/>
-      <c r="F11" s="115"/>
-      <c r="G11" s="115"/>
-      <c r="H11" s="115"/>
-      <c r="I11" s="115"/>
-      <c r="J11" s="115"/>
+      <c r="D11" s="104"/>
+      <c r="E11" s="104"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="104"/>
+      <c r="H11" s="104"/>
+      <c r="I11" s="104"/>
+      <c r="J11" s="104"/>
     </row>
     <row r="12" spans="2:10">
-      <c r="C12" s="117" t="s">
+      <c r="C12" s="106" t="s">
         <v>729</v>
       </c>
-      <c r="D12" s="115"/>
-      <c r="E12" s="115"/>
-      <c r="F12" s="115"/>
-      <c r="G12" s="115"/>
-      <c r="H12" s="115"/>
-      <c r="I12" s="115"/>
-      <c r="J12" s="115"/>
+      <c r="D12" s="104"/>
+      <c r="E12" s="104"/>
+      <c r="F12" s="104"/>
+      <c r="G12" s="104"/>
+      <c r="H12" s="104"/>
+      <c r="I12" s="104"/>
+      <c r="J12" s="104"/>
     </row>
     <row r="13" spans="2:10">
-      <c r="C13" s="117" t="s">
+      <c r="C13" s="106" t="s">
         <v>730</v>
       </c>
-      <c r="D13" s="115"/>
-      <c r="E13" s="115"/>
-      <c r="F13" s="115"/>
-      <c r="G13" s="115"/>
-      <c r="H13" s="115"/>
-      <c r="I13" s="115"/>
-      <c r="J13" s="115"/>
+      <c r="D13" s="104"/>
+      <c r="E13" s="104"/>
+      <c r="F13" s="104"/>
+      <c r="G13" s="104"/>
+      <c r="H13" s="104"/>
+      <c r="I13" s="104"/>
+      <c r="J13" s="104"/>
     </row>
     <row r="14" spans="2:10">
-      <c r="C14" s="118" t="s">
+      <c r="C14" s="107" t="s">
         <v>731</v>
       </c>
-      <c r="D14" s="115"/>
-      <c r="E14" s="115"/>
-      <c r="F14" s="115"/>
-      <c r="G14" s="115"/>
-      <c r="H14" s="115"/>
-      <c r="I14" s="115"/>
-      <c r="J14" s="115"/>
+      <c r="D14" s="104"/>
+      <c r="E14" s="104"/>
+      <c r="F14" s="104"/>
+      <c r="G14" s="104"/>
+      <c r="H14" s="104"/>
+      <c r="I14" s="104"/>
+      <c r="J14" s="104"/>
     </row>
     <row r="15" spans="2:10">
-      <c r="C15" s="116" t="s">
+      <c r="C15" s="105" t="s">
         <v>613</v>
       </c>
-      <c r="D15" s="115"/>
-      <c r="E15" s="115"/>
-      <c r="F15" s="115"/>
-      <c r="G15" s="115"/>
-      <c r="H15" s="115"/>
-      <c r="I15" s="115"/>
-      <c r="J15" s="115"/>
+      <c r="D15" s="104"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="104"/>
+      <c r="G15" s="104"/>
+      <c r="H15" s="104"/>
+      <c r="I15" s="104"/>
+      <c r="J15" s="104"/>
     </row>
     <row r="16" spans="2:10">
-      <c r="C16" s="119"/>
-      <c r="D16" s="115"/>
-      <c r="E16" s="115"/>
-      <c r="F16" s="115"/>
-      <c r="G16" s="115"/>
-      <c r="H16" s="115"/>
-      <c r="I16" s="115"/>
-      <c r="J16" s="115"/>
-    </row>
-    <row r="17" spans="3:10">
-      <c r="C17" s="114" t="s">
+      <c r="C16" s="108"/>
+      <c r="D16" s="104"/>
+      <c r="E16" s="104"/>
+      <c r="F16" s="104"/>
+      <c r="G16" s="104"/>
+      <c r="H16" s="104"/>
+      <c r="I16" s="104"/>
+      <c r="J16" s="104"/>
+    </row>
+    <row r="17" spans="2:17">
+      <c r="C17" s="103" t="s">
         <v>732</v>
       </c>
-      <c r="D17" s="115"/>
-      <c r="E17" s="115"/>
-      <c r="F17" s="115"/>
-      <c r="G17" s="115"/>
-      <c r="H17" s="115"/>
-      <c r="I17" s="115"/>
-      <c r="J17" s="115"/>
-    </row>
-    <row r="18" spans="3:10">
-      <c r="C18" s="116" t="s">
+      <c r="D17" s="104"/>
+      <c r="E17" s="104"/>
+      <c r="F17" s="104"/>
+      <c r="G17" s="104"/>
+      <c r="H17" s="104"/>
+      <c r="I17" s="104"/>
+      <c r="J17" s="104"/>
+    </row>
+    <row r="18" spans="2:17">
+      <c r="C18" s="105" t="s">
         <v>514</v>
       </c>
-      <c r="D18" s="115"/>
-      <c r="E18" s="115"/>
-      <c r="F18" s="115"/>
-      <c r="G18" s="115"/>
-      <c r="H18" s="115"/>
-      <c r="I18" s="115"/>
-      <c r="J18" s="115"/>
-    </row>
-    <row r="19" spans="3:10">
-      <c r="C19" s="118" t="s">
+      <c r="D18" s="104"/>
+      <c r="E18" s="104"/>
+      <c r="F18" s="104"/>
+      <c r="G18" s="104"/>
+      <c r="H18" s="104"/>
+      <c r="I18" s="104"/>
+      <c r="J18" s="104"/>
+    </row>
+    <row r="19" spans="2:17">
+      <c r="C19" s="107" t="s">
         <v>733</v>
       </c>
-      <c r="D19" s="115"/>
-      <c r="E19" s="115"/>
-      <c r="F19" s="115"/>
-      <c r="G19" s="115"/>
-      <c r="H19" s="115"/>
-      <c r="I19" s="115"/>
-      <c r="J19" s="115"/>
-    </row>
-    <row r="20" spans="3:10">
-      <c r="C20" s="118" t="s">
+      <c r="D19" s="104"/>
+      <c r="E19" s="104"/>
+      <c r="F19" s="104"/>
+      <c r="G19" s="104"/>
+      <c r="H19" s="104"/>
+      <c r="I19" s="104"/>
+      <c r="J19" s="104"/>
+    </row>
+    <row r="20" spans="2:17">
+      <c r="C20" s="107" t="s">
         <v>734</v>
       </c>
-      <c r="D20" s="115"/>
-      <c r="E20" s="115"/>
-      <c r="F20" s="115"/>
-      <c r="G20" s="115"/>
-      <c r="H20" s="115"/>
-      <c r="I20" s="115"/>
-      <c r="J20" s="115"/>
-    </row>
-    <row r="21" spans="3:10">
-      <c r="C21" s="120" t="s">
+      <c r="D20" s="104"/>
+      <c r="E20" s="104"/>
+      <c r="F20" s="104"/>
+      <c r="G20" s="104"/>
+      <c r="H20" s="104"/>
+      <c r="I20" s="104"/>
+      <c r="J20" s="104"/>
+    </row>
+    <row r="21" spans="2:17">
+      <c r="C21" s="109" t="s">
         <v>735</v>
       </c>
-      <c r="D21" s="115"/>
-      <c r="E21" s="115"/>
-      <c r="F21" s="115"/>
-      <c r="G21" s="115"/>
-      <c r="H21" s="115"/>
-      <c r="I21" s="115"/>
-      <c r="J21" s="115"/>
-    </row>
-    <row r="22" spans="3:10">
-      <c r="C22" s="116" t="s">
+      <c r="D21" s="104"/>
+      <c r="E21" s="104"/>
+      <c r="F21" s="104"/>
+      <c r="G21" s="104"/>
+      <c r="H21" s="104"/>
+      <c r="I21" s="104"/>
+      <c r="J21" s="104"/>
+    </row>
+    <row r="22" spans="2:17">
+      <c r="C22" s="105" t="s">
         <v>284</v>
       </c>
-      <c r="D22" s="115"/>
-      <c r="E22" s="115"/>
-      <c r="F22" s="115"/>
-      <c r="G22" s="115"/>
-      <c r="H22" s="115"/>
-      <c r="I22" s="115"/>
-      <c r="J22" s="115"/>
-    </row>
-    <row r="23" spans="3:10">
-      <c r="C23" s="115"/>
-      <c r="D23" s="115"/>
-      <c r="E23" s="115"/>
-      <c r="F23" s="115"/>
-      <c r="G23" s="115"/>
-      <c r="H23" s="115"/>
-      <c r="I23" s="115"/>
-      <c r="J23" s="115"/>
+      <c r="D22" s="104"/>
+      <c r="E22" s="104"/>
+      <c r="F22" s="104"/>
+      <c r="G22" s="104"/>
+      <c r="H22" s="104"/>
+      <c r="I22" s="104"/>
+      <c r="J22" s="104"/>
+    </row>
+    <row r="23" spans="2:17">
+      <c r="C23" s="104"/>
+      <c r="D23" s="104"/>
+      <c r="E23" s="104"/>
+      <c r="F23" s="104"/>
+      <c r="G23" s="104"/>
+      <c r="H23" s="104"/>
+      <c r="I23" s="104"/>
+      <c r="J23" s="104"/>
+    </row>
+    <row r="26" spans="2:17">
+      <c r="B26" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17">
+      <c r="C27" s="109" t="s">
+        <v>738</v>
+      </c>
+      <c r="D27" s="104"/>
+      <c r="E27" s="104"/>
+      <c r="F27" s="104"/>
+      <c r="G27" s="104"/>
+      <c r="H27" s="104"/>
+      <c r="I27" s="104"/>
+      <c r="J27" s="104"/>
+      <c r="K27" s="104"/>
+      <c r="L27" s="104"/>
+      <c r="M27" s="104"/>
+      <c r="N27" s="104"/>
+      <c r="O27" s="104"/>
+      <c r="P27" s="104"/>
+      <c r="Q27" s="104"/>
+    </row>
+    <row r="28" spans="2:17">
+      <c r="C28" s="109" t="s">
+        <v>739</v>
+      </c>
+      <c r="D28" s="104"/>
+      <c r="E28" s="104"/>
+      <c r="F28" s="104"/>
+      <c r="G28" s="104"/>
+      <c r="H28" s="104"/>
+      <c r="I28" s="104"/>
+      <c r="J28" s="104"/>
+      <c r="K28" s="104"/>
+      <c r="L28" s="104"/>
+      <c r="M28" s="104"/>
+      <c r="N28" s="104"/>
+      <c r="O28" s="104"/>
+      <c r="P28" s="104"/>
+      <c r="Q28" s="104"/>
+    </row>
+    <row r="29" spans="2:17">
+      <c r="C29" s="109" t="s">
+        <v>740</v>
+      </c>
+      <c r="D29" s="104"/>
+      <c r="E29" s="104"/>
+      <c r="F29" s="104"/>
+      <c r="G29" s="104"/>
+      <c r="H29" s="104"/>
+      <c r="I29" s="104"/>
+      <c r="J29" s="104"/>
+      <c r="K29" s="104"/>
+      <c r="L29" s="104"/>
+      <c r="M29" s="104"/>
+      <c r="N29" s="104"/>
+      <c r="O29" s="104"/>
+      <c r="P29" s="104"/>
+      <c r="Q29" s="104"/>
+    </row>
+    <row r="30" spans="2:17">
+      <c r="C30" s="109" t="s">
+        <v>741</v>
+      </c>
+      <c r="D30" s="104"/>
+      <c r="E30" s="104"/>
+      <c r="F30" s="104"/>
+      <c r="G30" s="104"/>
+      <c r="H30" s="104"/>
+      <c r="I30" s="104"/>
+      <c r="J30" s="104"/>
+      <c r="K30" s="104"/>
+      <c r="L30" s="104"/>
+      <c r="M30" s="104"/>
+      <c r="N30" s="104"/>
+      <c r="O30" s="104"/>
+      <c r="P30" s="104"/>
+      <c r="Q30" s="104"/>
+    </row>
+    <row r="31" spans="2:17">
+      <c r="C31" s="108"/>
+      <c r="D31" s="104"/>
+      <c r="E31" s="104"/>
+      <c r="F31" s="104"/>
+      <c r="G31" s="104"/>
+      <c r="H31" s="104"/>
+      <c r="I31" s="104"/>
+      <c r="J31" s="104"/>
+      <c r="K31" s="104"/>
+      <c r="L31" s="104"/>
+      <c r="M31" s="104"/>
+      <c r="N31" s="104"/>
+      <c r="O31" s="104"/>
+      <c r="P31" s="104"/>
+      <c r="Q31" s="104"/>
+    </row>
+    <row r="32" spans="2:17">
+      <c r="C32" s="103" t="s">
+        <v>742</v>
+      </c>
+      <c r="D32" s="104"/>
+      <c r="E32" s="104"/>
+      <c r="F32" s="104"/>
+      <c r="G32" s="104"/>
+      <c r="H32" s="104"/>
+      <c r="I32" s="104"/>
+      <c r="J32" s="104"/>
+      <c r="K32" s="104"/>
+      <c r="L32" s="104"/>
+      <c r="M32" s="104"/>
+      <c r="N32" s="104"/>
+      <c r="O32" s="104"/>
+      <c r="P32" s="104"/>
+      <c r="Q32" s="104"/>
+    </row>
+    <row r="33" spans="3:17">
+      <c r="C33" s="105" t="s">
+        <v>514</v>
+      </c>
+      <c r="D33" s="104"/>
+      <c r="E33" s="104"/>
+      <c r="F33" s="104"/>
+      <c r="G33" s="104"/>
+      <c r="H33" s="104"/>
+      <c r="I33" s="104"/>
+      <c r="J33" s="104"/>
+      <c r="K33" s="104"/>
+      <c r="L33" s="104"/>
+      <c r="M33" s="104"/>
+      <c r="N33" s="104"/>
+      <c r="O33" s="104"/>
+      <c r="P33" s="104"/>
+      <c r="Q33" s="104"/>
+    </row>
+    <row r="34" spans="3:17">
+      <c r="C34" s="103" t="s">
+        <v>631</v>
+      </c>
+      <c r="D34" s="104"/>
+      <c r="E34" s="104"/>
+      <c r="F34" s="104"/>
+      <c r="G34" s="104"/>
+      <c r="H34" s="104"/>
+      <c r="I34" s="104"/>
+      <c r="J34" s="104"/>
+      <c r="K34" s="104"/>
+      <c r="L34" s="104"/>
+      <c r="M34" s="104"/>
+      <c r="N34" s="104"/>
+      <c r="O34" s="104"/>
+      <c r="P34" s="104"/>
+      <c r="Q34" s="104"/>
+    </row>
+    <row r="35" spans="3:17">
+      <c r="C35" s="106" t="s">
+        <v>743</v>
+      </c>
+      <c r="D35" s="104"/>
+      <c r="E35" s="104"/>
+      <c r="F35" s="104"/>
+      <c r="G35" s="104"/>
+      <c r="H35" s="104"/>
+      <c r="I35" s="104"/>
+      <c r="J35" s="104"/>
+      <c r="K35" s="104"/>
+      <c r="L35" s="104"/>
+      <c r="M35" s="104"/>
+      <c r="N35" s="104"/>
+      <c r="O35" s="104"/>
+      <c r="P35" s="104"/>
+      <c r="Q35" s="104"/>
+    </row>
+    <row r="36" spans="3:17">
+      <c r="C36" s="103" t="s">
+        <v>744</v>
+      </c>
+      <c r="D36" s="104"/>
+      <c r="E36" s="104"/>
+      <c r="F36" s="104"/>
+      <c r="G36" s="104"/>
+      <c r="H36" s="104"/>
+      <c r="I36" s="104"/>
+      <c r="J36" s="104"/>
+      <c r="K36" s="104"/>
+      <c r="L36" s="104"/>
+      <c r="M36" s="104"/>
+      <c r="N36" s="104"/>
+      <c r="O36" s="104"/>
+      <c r="P36" s="104"/>
+      <c r="Q36" s="104"/>
+    </row>
+    <row r="37" spans="3:17">
+      <c r="C37" s="103" t="s">
+        <v>745</v>
+      </c>
+      <c r="D37" s="104"/>
+      <c r="E37" s="104"/>
+      <c r="F37" s="104"/>
+      <c r="G37" s="104"/>
+      <c r="H37" s="104"/>
+      <c r="I37" s="104"/>
+      <c r="J37" s="104"/>
+      <c r="K37" s="104"/>
+      <c r="L37" s="104"/>
+      <c r="M37" s="104"/>
+      <c r="N37" s="104"/>
+      <c r="O37" s="104"/>
+      <c r="P37" s="104"/>
+      <c r="Q37" s="104"/>
+    </row>
+    <row r="38" spans="3:17">
+      <c r="C38" s="105" t="s">
+        <v>613</v>
+      </c>
+      <c r="D38" s="104"/>
+      <c r="E38" s="104"/>
+      <c r="F38" s="104"/>
+      <c r="G38" s="104"/>
+      <c r="H38" s="104"/>
+      <c r="I38" s="104"/>
+      <c r="J38" s="104"/>
+      <c r="K38" s="104"/>
+      <c r="L38" s="104"/>
+      <c r="M38" s="104"/>
+      <c r="N38" s="104"/>
+      <c r="O38" s="104"/>
+      <c r="P38" s="104"/>
+      <c r="Q38" s="104"/>
+    </row>
+    <row r="39" spans="3:17">
+      <c r="C39" s="108"/>
+      <c r="D39" s="104"/>
+      <c r="E39" s="104"/>
+      <c r="F39" s="104"/>
+      <c r="G39" s="104"/>
+      <c r="H39" s="104"/>
+      <c r="I39" s="104"/>
+      <c r="J39" s="104"/>
+      <c r="K39" s="104"/>
+      <c r="L39" s="104"/>
+      <c r="M39" s="104"/>
+      <c r="N39" s="104"/>
+      <c r="O39" s="104"/>
+      <c r="P39" s="104"/>
+      <c r="Q39" s="104"/>
+    </row>
+    <row r="40" spans="3:17">
+      <c r="C40" s="103" t="s">
+        <v>746</v>
+      </c>
+      <c r="D40" s="104"/>
+      <c r="E40" s="104"/>
+      <c r="F40" s="104"/>
+      <c r="G40" s="104"/>
+      <c r="H40" s="104"/>
+      <c r="I40" s="104"/>
+      <c r="J40" s="104"/>
+      <c r="K40" s="104"/>
+      <c r="L40" s="104"/>
+      <c r="M40" s="104"/>
+      <c r="N40" s="104"/>
+      <c r="O40" s="104"/>
+      <c r="P40" s="104"/>
+      <c r="Q40" s="104"/>
+    </row>
+    <row r="41" spans="3:17">
+      <c r="C41" s="105" t="s">
+        <v>514</v>
+      </c>
+      <c r="D41" s="104"/>
+      <c r="E41" s="104"/>
+      <c r="F41" s="104"/>
+      <c r="G41" s="104"/>
+      <c r="H41" s="104"/>
+      <c r="I41" s="104"/>
+      <c r="J41" s="104"/>
+      <c r="K41" s="104"/>
+      <c r="L41" s="104"/>
+      <c r="M41" s="104"/>
+      <c r="N41" s="104"/>
+      <c r="O41" s="104"/>
+      <c r="P41" s="104"/>
+      <c r="Q41" s="104"/>
+    </row>
+    <row r="42" spans="3:17">
+      <c r="C42" s="103" t="s">
+        <v>728</v>
+      </c>
+      <c r="D42" s="104"/>
+      <c r="E42" s="104"/>
+      <c r="F42" s="104"/>
+      <c r="G42" s="104"/>
+      <c r="H42" s="104"/>
+      <c r="I42" s="104"/>
+      <c r="J42" s="104"/>
+      <c r="K42" s="104"/>
+      <c r="L42" s="104"/>
+      <c r="M42" s="104"/>
+      <c r="N42" s="104"/>
+      <c r="O42" s="104"/>
+      <c r="P42" s="104"/>
+      <c r="Q42" s="104"/>
+    </row>
+    <row r="43" spans="3:17">
+      <c r="C43" s="107" t="s">
+        <v>747</v>
+      </c>
+      <c r="D43" s="104"/>
+      <c r="E43" s="104"/>
+      <c r="F43" s="104"/>
+      <c r="G43" s="104"/>
+      <c r="H43" s="104"/>
+      <c r="I43" s="104"/>
+      <c r="J43" s="104"/>
+      <c r="K43" s="104"/>
+      <c r="L43" s="104"/>
+      <c r="M43" s="104"/>
+      <c r="N43" s="104"/>
+      <c r="O43" s="104"/>
+      <c r="P43" s="104"/>
+      <c r="Q43" s="104"/>
+    </row>
+    <row r="44" spans="3:17">
+      <c r="C44" s="107" t="s">
+        <v>748</v>
+      </c>
+      <c r="D44" s="104"/>
+      <c r="E44" s="104"/>
+      <c r="F44" s="104"/>
+      <c r="G44" s="104"/>
+      <c r="H44" s="104"/>
+      <c r="I44" s="104"/>
+      <c r="J44" s="104"/>
+      <c r="K44" s="104"/>
+      <c r="L44" s="104"/>
+      <c r="M44" s="104"/>
+      <c r="N44" s="104"/>
+      <c r="O44" s="104"/>
+      <c r="P44" s="104"/>
+      <c r="Q44" s="104"/>
+    </row>
+    <row r="45" spans="3:17">
+      <c r="C45" s="103" t="s">
+        <v>631</v>
+      </c>
+      <c r="D45" s="104"/>
+      <c r="E45" s="104"/>
+      <c r="F45" s="104"/>
+      <c r="G45" s="104"/>
+      <c r="H45" s="104"/>
+      <c r="I45" s="104"/>
+      <c r="J45" s="104"/>
+      <c r="K45" s="104"/>
+      <c r="L45" s="104"/>
+      <c r="M45" s="104"/>
+      <c r="N45" s="104"/>
+      <c r="O45" s="104"/>
+      <c r="P45" s="104"/>
+      <c r="Q45" s="104"/>
+    </row>
+    <row r="46" spans="3:17">
+      <c r="C46" s="103" t="s">
+        <v>749</v>
+      </c>
+      <c r="D46" s="104"/>
+      <c r="E46" s="104"/>
+      <c r="F46" s="104"/>
+      <c r="G46" s="104"/>
+      <c r="H46" s="104"/>
+      <c r="I46" s="104"/>
+      <c r="J46" s="104"/>
+      <c r="K46" s="104"/>
+      <c r="L46" s="104"/>
+      <c r="M46" s="104"/>
+      <c r="N46" s="104"/>
+      <c r="O46" s="104"/>
+      <c r="P46" s="104"/>
+      <c r="Q46" s="104"/>
+    </row>
+    <row r="47" spans="3:17">
+      <c r="C47" s="105" t="s">
+        <v>514</v>
+      </c>
+      <c r="D47" s="104"/>
+      <c r="E47" s="104"/>
+      <c r="F47" s="104"/>
+      <c r="G47" s="104"/>
+      <c r="H47" s="104"/>
+      <c r="I47" s="104"/>
+      <c r="J47" s="104"/>
+      <c r="K47" s="104"/>
+      <c r="L47" s="104"/>
+      <c r="M47" s="104"/>
+      <c r="N47" s="104"/>
+      <c r="O47" s="104"/>
+      <c r="P47" s="104"/>
+      <c r="Q47" s="104"/>
+    </row>
+    <row r="48" spans="3:17">
+      <c r="C48" s="121" t="s">
+        <v>750</v>
+      </c>
+      <c r="D48" s="104"/>
+      <c r="E48" s="104"/>
+      <c r="F48" s="104"/>
+      <c r="G48" s="104"/>
+      <c r="H48" s="104"/>
+      <c r="I48" s="104"/>
+      <c r="J48" s="104"/>
+      <c r="K48" s="104"/>
+      <c r="L48" s="104"/>
+      <c r="M48" s="104"/>
+      <c r="N48" s="104"/>
+      <c r="O48" s="104"/>
+      <c r="P48" s="104"/>
+      <c r="Q48" s="104"/>
+    </row>
+    <row r="49" spans="3:17">
+      <c r="C49" s="105" t="s">
+        <v>284</v>
+      </c>
+      <c r="D49" s="104"/>
+      <c r="E49" s="104"/>
+      <c r="F49" s="104"/>
+      <c r="G49" s="104"/>
+      <c r="H49" s="104"/>
+      <c r="I49" s="104"/>
+      <c r="J49" s="104"/>
+      <c r="K49" s="104"/>
+      <c r="L49" s="104"/>
+      <c r="M49" s="104"/>
+      <c r="N49" s="104"/>
+      <c r="O49" s="104"/>
+      <c r="P49" s="104"/>
+      <c r="Q49" s="104"/>
+    </row>
+    <row r="50" spans="3:17">
+      <c r="C50" s="103" t="s">
+        <v>751</v>
+      </c>
+      <c r="D50" s="104"/>
+      <c r="E50" s="104"/>
+      <c r="F50" s="104"/>
+      <c r="G50" s="104"/>
+      <c r="H50" s="104"/>
+      <c r="I50" s="104"/>
+      <c r="J50" s="104"/>
+      <c r="K50" s="104"/>
+      <c r="L50" s="104"/>
+      <c r="M50" s="104"/>
+      <c r="N50" s="104"/>
+      <c r="O50" s="104"/>
+      <c r="P50" s="104"/>
+      <c r="Q50" s="104"/>
+    </row>
+    <row r="51" spans="3:17">
+      <c r="C51" s="105" t="s">
+        <v>514</v>
+      </c>
+      <c r="D51" s="104"/>
+      <c r="E51" s="104"/>
+      <c r="F51" s="104"/>
+      <c r="G51" s="104"/>
+      <c r="H51" s="104"/>
+      <c r="I51" s="104"/>
+      <c r="J51" s="104"/>
+      <c r="K51" s="104"/>
+      <c r="L51" s="104"/>
+      <c r="M51" s="104"/>
+      <c r="N51" s="104"/>
+      <c r="O51" s="104"/>
+      <c r="P51" s="104"/>
+      <c r="Q51" s="104"/>
+    </row>
+    <row r="52" spans="3:17">
+      <c r="C52" s="121" t="s">
+        <v>752</v>
+      </c>
+      <c r="D52" s="104"/>
+      <c r="E52" s="104"/>
+      <c r="F52" s="104"/>
+      <c r="G52" s="104"/>
+      <c r="H52" s="104"/>
+      <c r="I52" s="104"/>
+      <c r="J52" s="104"/>
+      <c r="K52" s="104"/>
+      <c r="L52" s="104"/>
+      <c r="M52" s="104"/>
+      <c r="N52" s="104"/>
+      <c r="O52" s="104"/>
+      <c r="P52" s="104"/>
+      <c r="Q52" s="104"/>
+    </row>
+    <row r="53" spans="3:17">
+      <c r="C53" s="105" t="s">
+        <v>284</v>
+      </c>
+      <c r="D53" s="104"/>
+      <c r="E53" s="104"/>
+      <c r="F53" s="104"/>
+      <c r="G53" s="104"/>
+      <c r="H53" s="104"/>
+      <c r="I53" s="104"/>
+      <c r="J53" s="104"/>
+      <c r="K53" s="104"/>
+      <c r="L53" s="104"/>
+      <c r="M53" s="104"/>
+      <c r="N53" s="104"/>
+      <c r="O53" s="104"/>
+      <c r="P53" s="104"/>
+      <c r="Q53" s="104"/>
+    </row>
+    <row r="54" spans="3:17">
+      <c r="C54" s="103" t="s">
+        <v>753</v>
+      </c>
+      <c r="D54" s="104"/>
+      <c r="E54" s="104"/>
+      <c r="F54" s="104"/>
+      <c r="G54" s="104"/>
+      <c r="H54" s="104"/>
+      <c r="I54" s="104"/>
+      <c r="J54" s="104"/>
+      <c r="K54" s="104"/>
+      <c r="L54" s="104"/>
+      <c r="M54" s="104"/>
+      <c r="N54" s="104"/>
+      <c r="O54" s="104"/>
+      <c r="P54" s="104"/>
+      <c r="Q54" s="104"/>
+    </row>
+    <row r="55" spans="3:17">
+      <c r="C55" s="105" t="s">
+        <v>514</v>
+      </c>
+      <c r="D55" s="104"/>
+      <c r="E55" s="104"/>
+      <c r="F55" s="104"/>
+      <c r="G55" s="104"/>
+      <c r="H55" s="104"/>
+      <c r="I55" s="104"/>
+      <c r="J55" s="104"/>
+      <c r="K55" s="104"/>
+      <c r="L55" s="104"/>
+      <c r="M55" s="104"/>
+      <c r="N55" s="104"/>
+      <c r="O55" s="104"/>
+      <c r="P55" s="104"/>
+      <c r="Q55" s="104"/>
+    </row>
+    <row r="56" spans="3:17">
+      <c r="C56" s="105" t="s">
+        <v>754</v>
+      </c>
+      <c r="D56" s="104"/>
+      <c r="E56" s="104"/>
+      <c r="F56" s="104"/>
+      <c r="G56" s="104"/>
+      <c r="H56" s="104"/>
+      <c r="I56" s="104"/>
+      <c r="J56" s="104"/>
+      <c r="K56" s="104"/>
+      <c r="L56" s="104"/>
+      <c r="M56" s="104"/>
+      <c r="N56" s="104"/>
+      <c r="O56" s="104"/>
+      <c r="P56" s="104"/>
+      <c r="Q56" s="104"/>
+    </row>
+    <row r="57" spans="3:17">
+      <c r="C57" s="105" t="s">
+        <v>755</v>
+      </c>
+      <c r="D57" s="104"/>
+      <c r="E57" s="104"/>
+      <c r="F57" s="104"/>
+      <c r="G57" s="104"/>
+      <c r="H57" s="104"/>
+      <c r="I57" s="104"/>
+      <c r="J57" s="104"/>
+      <c r="K57" s="104"/>
+      <c r="L57" s="104"/>
+      <c r="M57" s="104"/>
+      <c r="N57" s="104"/>
+      <c r="O57" s="104"/>
+      <c r="P57" s="104"/>
+      <c r="Q57" s="104"/>
+    </row>
+    <row r="58" spans="3:17">
+      <c r="C58" s="105" t="s">
+        <v>756</v>
+      </c>
+      <c r="D58" s="104"/>
+      <c r="E58" s="104"/>
+      <c r="F58" s="104"/>
+      <c r="G58" s="104"/>
+      <c r="H58" s="104"/>
+      <c r="I58" s="104"/>
+      <c r="J58" s="104"/>
+      <c r="K58" s="104"/>
+      <c r="L58" s="104"/>
+      <c r="M58" s="104"/>
+      <c r="N58" s="104"/>
+      <c r="O58" s="104"/>
+      <c r="P58" s="104"/>
+      <c r="Q58" s="104"/>
+    </row>
+    <row r="59" spans="3:17">
+      <c r="C59" s="105" t="s">
+        <v>757</v>
+      </c>
+      <c r="D59" s="104"/>
+      <c r="E59" s="104"/>
+      <c r="F59" s="104"/>
+      <c r="G59" s="104"/>
+      <c r="H59" s="104"/>
+      <c r="I59" s="104"/>
+      <c r="J59" s="104"/>
+      <c r="K59" s="104"/>
+      <c r="L59" s="104"/>
+      <c r="M59" s="104"/>
+      <c r="N59" s="104"/>
+      <c r="O59" s="104"/>
+      <c r="P59" s="104"/>
+      <c r="Q59" s="104"/>
+    </row>
+    <row r="60" spans="3:17">
+      <c r="C60" s="105" t="s">
+        <v>284</v>
+      </c>
+      <c r="D60" s="104"/>
+      <c r="E60" s="104"/>
+      <c r="F60" s="104"/>
+      <c r="G60" s="104"/>
+      <c r="H60" s="104"/>
+      <c r="I60" s="104"/>
+      <c r="J60" s="104"/>
+      <c r="K60" s="104"/>
+      <c r="L60" s="104"/>
+      <c r="M60" s="104"/>
+      <c r="N60" s="104"/>
+      <c r="O60" s="104"/>
+      <c r="P60" s="104"/>
+      <c r="Q60" s="104"/>
+    </row>
+    <row r="61" spans="3:17">
+      <c r="C61" s="103" t="s">
+        <v>758</v>
+      </c>
+      <c r="D61" s="104"/>
+      <c r="E61" s="104"/>
+      <c r="F61" s="104"/>
+      <c r="G61" s="104"/>
+      <c r="H61" s="104"/>
+      <c r="I61" s="104"/>
+      <c r="J61" s="104"/>
+      <c r="K61" s="104"/>
+      <c r="L61" s="104"/>
+      <c r="M61" s="104"/>
+      <c r="N61" s="104"/>
+      <c r="O61" s="104"/>
+      <c r="P61" s="104"/>
+      <c r="Q61" s="104"/>
+    </row>
+    <row r="62" spans="3:17">
+      <c r="C62" s="105" t="s">
+        <v>514</v>
+      </c>
+      <c r="D62" s="104"/>
+      <c r="E62" s="104"/>
+      <c r="F62" s="104"/>
+      <c r="G62" s="104"/>
+      <c r="H62" s="104"/>
+      <c r="I62" s="104"/>
+      <c r="J62" s="104"/>
+      <c r="K62" s="104"/>
+      <c r="L62" s="104"/>
+      <c r="M62" s="104"/>
+      <c r="N62" s="104"/>
+      <c r="O62" s="104"/>
+      <c r="P62" s="104"/>
+      <c r="Q62" s="104"/>
+    </row>
+    <row r="63" spans="3:17">
+      <c r="C63" s="121" t="s">
+        <v>759</v>
+      </c>
+      <c r="D63" s="104"/>
+      <c r="E63" s="104"/>
+      <c r="F63" s="104"/>
+      <c r="G63" s="104"/>
+      <c r="H63" s="104"/>
+      <c r="I63" s="104"/>
+      <c r="J63" s="104"/>
+      <c r="K63" s="104"/>
+      <c r="L63" s="104"/>
+      <c r="M63" s="104"/>
+      <c r="N63" s="104"/>
+      <c r="O63" s="104"/>
+      <c r="P63" s="104"/>
+      <c r="Q63" s="104"/>
+    </row>
+    <row r="64" spans="3:17">
+      <c r="C64" s="106" t="s">
+        <v>760</v>
+      </c>
+      <c r="D64" s="104"/>
+      <c r="E64" s="104"/>
+      <c r="F64" s="104"/>
+      <c r="G64" s="104"/>
+      <c r="H64" s="104"/>
+      <c r="I64" s="104"/>
+      <c r="J64" s="104"/>
+      <c r="K64" s="104"/>
+      <c r="L64" s="104"/>
+      <c r="M64" s="104"/>
+      <c r="N64" s="104"/>
+      <c r="O64" s="104"/>
+      <c r="P64" s="104"/>
+      <c r="Q64" s="104"/>
+    </row>
+    <row r="65" spans="3:17">
+      <c r="C65" s="105" t="s">
+        <v>284</v>
+      </c>
+      <c r="D65" s="104"/>
+      <c r="E65" s="104"/>
+      <c r="F65" s="104"/>
+      <c r="G65" s="104"/>
+      <c r="H65" s="104"/>
+      <c r="I65" s="104"/>
+      <c r="J65" s="104"/>
+      <c r="K65" s="104"/>
+      <c r="L65" s="104"/>
+      <c r="M65" s="104"/>
+      <c r="N65" s="104"/>
+      <c r="O65" s="104"/>
+      <c r="P65" s="104"/>
+      <c r="Q65" s="104"/>
+    </row>
+    <row r="66" spans="3:17">
+      <c r="C66" s="105" t="s">
+        <v>613</v>
+      </c>
+      <c r="D66" s="104"/>
+      <c r="E66" s="104"/>
+      <c r="F66" s="104"/>
+      <c r="G66" s="104"/>
+      <c r="H66" s="104"/>
+      <c r="I66" s="104"/>
+      <c r="J66" s="104"/>
+      <c r="K66" s="104"/>
+      <c r="L66" s="104"/>
+      <c r="M66" s="104"/>
+      <c r="N66" s="104"/>
+      <c r="O66" s="104"/>
+      <c r="P66" s="104"/>
+      <c r="Q66" s="104"/>
+    </row>
+    <row r="67" spans="3:17">
+      <c r="C67" s="108"/>
+      <c r="D67" s="104"/>
+      <c r="E67" s="104"/>
+      <c r="F67" s="104"/>
+      <c r="G67" s="104"/>
+      <c r="H67" s="104"/>
+      <c r="I67" s="104"/>
+      <c r="J67" s="104"/>
+      <c r="K67" s="104"/>
+      <c r="L67" s="104"/>
+      <c r="M67" s="104"/>
+      <c r="N67" s="104"/>
+      <c r="O67" s="104"/>
+      <c r="P67" s="104"/>
+      <c r="Q67" s="104"/>
+    </row>
+    <row r="68" spans="3:17">
+      <c r="C68" s="103" t="s">
+        <v>761</v>
+      </c>
+      <c r="D68" s="104"/>
+      <c r="E68" s="104"/>
+      <c r="F68" s="104"/>
+      <c r="G68" s="104"/>
+      <c r="H68" s="104"/>
+      <c r="I68" s="104"/>
+      <c r="J68" s="104"/>
+      <c r="K68" s="104"/>
+      <c r="L68" s="104"/>
+      <c r="M68" s="104"/>
+      <c r="N68" s="104"/>
+      <c r="O68" s="104"/>
+      <c r="P68" s="104"/>
+      <c r="Q68" s="104"/>
+    </row>
+    <row r="69" spans="3:17">
+      <c r="C69" s="105" t="s">
+        <v>514</v>
+      </c>
+      <c r="D69" s="104"/>
+      <c r="E69" s="104"/>
+      <c r="F69" s="104"/>
+      <c r="G69" s="104"/>
+      <c r="H69" s="104"/>
+      <c r="I69" s="104"/>
+      <c r="J69" s="104"/>
+      <c r="K69" s="104"/>
+      <c r="L69" s="104"/>
+      <c r="M69" s="104"/>
+      <c r="N69" s="104"/>
+      <c r="O69" s="104"/>
+      <c r="P69" s="104"/>
+      <c r="Q69" s="104"/>
+    </row>
+    <row r="70" spans="3:17">
+      <c r="C70" s="103" t="s">
+        <v>728</v>
+      </c>
+      <c r="D70" s="104"/>
+      <c r="E70" s="104"/>
+      <c r="F70" s="104"/>
+      <c r="G70" s="104"/>
+      <c r="H70" s="104"/>
+      <c r="I70" s="104"/>
+      <c r="J70" s="104"/>
+      <c r="K70" s="104"/>
+      <c r="L70" s="104"/>
+      <c r="M70" s="104"/>
+      <c r="N70" s="104"/>
+      <c r="O70" s="104"/>
+      <c r="P70" s="104"/>
+      <c r="Q70" s="104"/>
+    </row>
+    <row r="71" spans="3:17">
+      <c r="C71" s="107" t="s">
+        <v>762</v>
+      </c>
+      <c r="D71" s="104"/>
+      <c r="E71" s="104"/>
+      <c r="F71" s="104"/>
+      <c r="G71" s="104"/>
+      <c r="H71" s="104"/>
+      <c r="I71" s="104"/>
+      <c r="J71" s="104"/>
+      <c r="K71" s="104"/>
+      <c r="L71" s="104"/>
+      <c r="M71" s="104"/>
+      <c r="N71" s="104"/>
+      <c r="O71" s="104"/>
+      <c r="P71" s="104"/>
+      <c r="Q71" s="104"/>
+    </row>
+    <row r="72" spans="3:17">
+      <c r="C72" s="107" t="s">
+        <v>763</v>
+      </c>
+      <c r="D72" s="104"/>
+      <c r="E72" s="104"/>
+      <c r="F72" s="104"/>
+      <c r="G72" s="104"/>
+      <c r="H72" s="104"/>
+      <c r="I72" s="104"/>
+      <c r="J72" s="104"/>
+      <c r="K72" s="104"/>
+      <c r="L72" s="104"/>
+      <c r="M72" s="104"/>
+      <c r="N72" s="104"/>
+      <c r="O72" s="104"/>
+      <c r="P72" s="104"/>
+      <c r="Q72" s="104"/>
+    </row>
+    <row r="73" spans="3:17">
+      <c r="C73" s="103" t="s">
+        <v>631</v>
+      </c>
+      <c r="D73" s="104"/>
+      <c r="E73" s="104"/>
+      <c r="F73" s="104"/>
+      <c r="G73" s="104"/>
+      <c r="H73" s="104"/>
+      <c r="I73" s="104"/>
+      <c r="J73" s="104"/>
+      <c r="K73" s="104"/>
+      <c r="L73" s="104"/>
+      <c r="M73" s="104"/>
+      <c r="N73" s="104"/>
+      <c r="O73" s="104"/>
+      <c r="P73" s="104"/>
+      <c r="Q73" s="104"/>
+    </row>
+    <row r="74" spans="3:17">
+      <c r="C74" s="106" t="s">
+        <v>764</v>
+      </c>
+      <c r="D74" s="104"/>
+      <c r="E74" s="104"/>
+      <c r="F74" s="104"/>
+      <c r="G74" s="104"/>
+      <c r="H74" s="104"/>
+      <c r="I74" s="104"/>
+      <c r="J74" s="104"/>
+      <c r="K74" s="104"/>
+      <c r="L74" s="104"/>
+      <c r="M74" s="104"/>
+      <c r="N74" s="104"/>
+      <c r="O74" s="104"/>
+      <c r="P74" s="104"/>
+      <c r="Q74" s="104"/>
+    </row>
+    <row r="75" spans="3:17">
+      <c r="C75" s="105" t="s">
+        <v>514</v>
+      </c>
+      <c r="D75" s="104"/>
+      <c r="E75" s="104"/>
+      <c r="F75" s="104"/>
+      <c r="G75" s="104"/>
+      <c r="H75" s="104"/>
+      <c r="I75" s="104"/>
+      <c r="J75" s="104"/>
+      <c r="K75" s="104"/>
+      <c r="L75" s="104"/>
+      <c r="M75" s="104"/>
+      <c r="N75" s="104"/>
+      <c r="O75" s="104"/>
+      <c r="P75" s="104"/>
+      <c r="Q75" s="104"/>
+    </row>
+    <row r="76" spans="3:17">
+      <c r="C76" s="121" t="s">
+        <v>765</v>
+      </c>
+      <c r="D76" s="104"/>
+      <c r="E76" s="104"/>
+      <c r="F76" s="104"/>
+      <c r="G76" s="104"/>
+      <c r="H76" s="104"/>
+      <c r="I76" s="104"/>
+      <c r="J76" s="104"/>
+      <c r="K76" s="104"/>
+      <c r="L76" s="104"/>
+      <c r="M76" s="104"/>
+      <c r="N76" s="104"/>
+      <c r="O76" s="104"/>
+      <c r="P76" s="104"/>
+      <c r="Q76" s="104"/>
+    </row>
+    <row r="77" spans="3:17">
+      <c r="C77" s="105" t="s">
+        <v>284</v>
+      </c>
+      <c r="D77" s="104"/>
+      <c r="E77" s="104"/>
+      <c r="F77" s="104"/>
+      <c r="G77" s="104"/>
+      <c r="H77" s="104"/>
+      <c r="I77" s="104"/>
+      <c r="J77" s="104"/>
+      <c r="K77" s="104"/>
+      <c r="L77" s="104"/>
+      <c r="M77" s="104"/>
+      <c r="N77" s="104"/>
+      <c r="O77" s="104"/>
+      <c r="P77" s="104"/>
+      <c r="Q77" s="104"/>
+    </row>
+    <row r="78" spans="3:17">
+      <c r="C78" s="108"/>
+      <c r="D78" s="104"/>
+      <c r="E78" s="104"/>
+      <c r="F78" s="104"/>
+      <c r="G78" s="104"/>
+      <c r="H78" s="104"/>
+      <c r="I78" s="104"/>
+      <c r="J78" s="104"/>
+      <c r="K78" s="104"/>
+      <c r="L78" s="104"/>
+      <c r="M78" s="104"/>
+      <c r="N78" s="104"/>
+      <c r="O78" s="104"/>
+      <c r="P78" s="104"/>
+      <c r="Q78" s="104"/>
+    </row>
+    <row r="79" spans="3:17">
+      <c r="C79" s="103" t="s">
+        <v>766</v>
+      </c>
+      <c r="D79" s="104"/>
+      <c r="E79" s="104"/>
+      <c r="F79" s="104"/>
+      <c r="G79" s="104"/>
+      <c r="H79" s="104"/>
+      <c r="I79" s="104"/>
+      <c r="J79" s="104"/>
+      <c r="K79" s="104"/>
+      <c r="L79" s="104"/>
+      <c r="M79" s="104"/>
+      <c r="N79" s="104"/>
+      <c r="O79" s="104"/>
+      <c r="P79" s="104"/>
+      <c r="Q79" s="104"/>
+    </row>
+    <row r="80" spans="3:17">
+      <c r="C80" s="105" t="s">
+        <v>514</v>
+      </c>
+      <c r="D80" s="104"/>
+      <c r="E80" s="104"/>
+      <c r="F80" s="104"/>
+      <c r="G80" s="104"/>
+      <c r="H80" s="104"/>
+      <c r="I80" s="104"/>
+      <c r="J80" s="104"/>
+      <c r="K80" s="104"/>
+      <c r="L80" s="104"/>
+      <c r="M80" s="104"/>
+      <c r="N80" s="104"/>
+      <c r="O80" s="104"/>
+      <c r="P80" s="104"/>
+      <c r="Q80" s="104"/>
+    </row>
+    <row r="81" spans="3:17">
+      <c r="C81" s="121" t="s">
+        <v>767</v>
+      </c>
+      <c r="D81" s="104"/>
+      <c r="E81" s="104"/>
+      <c r="F81" s="104"/>
+      <c r="G81" s="104"/>
+      <c r="H81" s="104"/>
+      <c r="I81" s="104"/>
+      <c r="J81" s="104"/>
+      <c r="K81" s="104"/>
+      <c r="L81" s="104"/>
+      <c r="M81" s="104"/>
+      <c r="N81" s="104"/>
+      <c r="O81" s="104"/>
+      <c r="P81" s="104"/>
+      <c r="Q81" s="104"/>
+    </row>
+    <row r="82" spans="3:17">
+      <c r="C82" s="107" t="s">
+        <v>768</v>
+      </c>
+      <c r="D82" s="104"/>
+      <c r="E82" s="104"/>
+      <c r="F82" s="104"/>
+      <c r="G82" s="104"/>
+      <c r="H82" s="104"/>
+      <c r="I82" s="104"/>
+      <c r="J82" s="104"/>
+      <c r="K82" s="104"/>
+      <c r="L82" s="104"/>
+      <c r="M82" s="104"/>
+      <c r="N82" s="104"/>
+      <c r="O82" s="104"/>
+      <c r="P82" s="104"/>
+      <c r="Q82" s="104"/>
+    </row>
+    <row r="83" spans="3:17">
+      <c r="C83" s="105" t="s">
+        <v>284</v>
+      </c>
+      <c r="D83" s="104"/>
+      <c r="E83" s="104"/>
+      <c r="F83" s="104"/>
+      <c r="G83" s="104"/>
+      <c r="H83" s="104"/>
+      <c r="I83" s="104"/>
+      <c r="J83" s="104"/>
+      <c r="K83" s="104"/>
+      <c r="L83" s="104"/>
+      <c r="M83" s="104"/>
+      <c r="N83" s="104"/>
+      <c r="O83" s="104"/>
+      <c r="P83" s="104"/>
+      <c r="Q83" s="104"/>
+    </row>
+    <row r="84" spans="3:17">
+      <c r="C84" s="108"/>
+      <c r="D84" s="104"/>
+      <c r="E84" s="104"/>
+      <c r="F84" s="104"/>
+      <c r="G84" s="104"/>
+      <c r="H84" s="104"/>
+      <c r="I84" s="104"/>
+      <c r="J84" s="104"/>
+      <c r="K84" s="104"/>
+      <c r="L84" s="104"/>
+      <c r="M84" s="104"/>
+      <c r="N84" s="104"/>
+      <c r="O84" s="104"/>
+      <c r="P84" s="104"/>
+      <c r="Q84" s="104"/>
+    </row>
+    <row r="85" spans="3:17">
+      <c r="C85" s="103" t="s">
+        <v>769</v>
+      </c>
+      <c r="D85" s="104"/>
+      <c r="E85" s="104"/>
+      <c r="F85" s="104"/>
+      <c r="G85" s="104"/>
+      <c r="H85" s="104"/>
+      <c r="I85" s="104"/>
+      <c r="J85" s="104"/>
+      <c r="K85" s="104"/>
+      <c r="L85" s="104"/>
+      <c r="M85" s="104"/>
+      <c r="N85" s="104"/>
+      <c r="O85" s="104"/>
+      <c r="P85" s="104"/>
+      <c r="Q85" s="104"/>
+    </row>
+    <row r="86" spans="3:17">
+      <c r="C86" s="105" t="s">
+        <v>514</v>
+      </c>
+      <c r="D86" s="104"/>
+      <c r="E86" s="104"/>
+      <c r="F86" s="104"/>
+      <c r="G86" s="104"/>
+      <c r="H86" s="104"/>
+      <c r="I86" s="104"/>
+      <c r="J86" s="104"/>
+      <c r="K86" s="104"/>
+      <c r="L86" s="104"/>
+      <c r="M86" s="104"/>
+      <c r="N86" s="104"/>
+      <c r="O86" s="104"/>
+      <c r="P86" s="104"/>
+      <c r="Q86" s="104"/>
+    </row>
+    <row r="87" spans="3:17">
+      <c r="C87" s="107" t="s">
+        <v>770</v>
+      </c>
+      <c r="D87" s="104"/>
+      <c r="E87" s="104"/>
+      <c r="F87" s="104"/>
+      <c r="G87" s="104"/>
+      <c r="H87" s="104"/>
+      <c r="I87" s="104"/>
+      <c r="J87" s="104"/>
+      <c r="K87" s="104"/>
+      <c r="L87" s="104"/>
+      <c r="M87" s="104"/>
+      <c r="N87" s="104"/>
+      <c r="O87" s="104"/>
+      <c r="P87" s="104"/>
+      <c r="Q87" s="104"/>
+    </row>
+    <row r="88" spans="3:17">
+      <c r="C88" s="105" t="s">
+        <v>284</v>
+      </c>
+      <c r="D88" s="104"/>
+      <c r="E88" s="104"/>
+      <c r="F88" s="104"/>
+      <c r="G88" s="104"/>
+      <c r="H88" s="104"/>
+      <c r="I88" s="104"/>
+      <c r="J88" s="104"/>
+      <c r="K88" s="104"/>
+      <c r="L88" s="104"/>
+      <c r="M88" s="104"/>
+      <c r="N88" s="104"/>
+      <c r="O88" s="104"/>
+      <c r="P88" s="104"/>
+      <c r="Q88" s="104"/>
+    </row>
+    <row r="89" spans="3:17">
+      <c r="C89" s="108"/>
+      <c r="D89" s="104"/>
+      <c r="E89" s="104"/>
+      <c r="F89" s="104"/>
+      <c r="G89" s="104"/>
+      <c r="H89" s="104"/>
+      <c r="I89" s="104"/>
+      <c r="J89" s="104"/>
+      <c r="K89" s="104"/>
+      <c r="L89" s="104"/>
+      <c r="M89" s="104"/>
+      <c r="N89" s="104"/>
+      <c r="O89" s="104"/>
+      <c r="P89" s="104"/>
+      <c r="Q89" s="104"/>
+    </row>
+    <row r="90" spans="3:17">
+      <c r="C90" s="105" t="s">
+        <v>613</v>
+      </c>
+      <c r="D90" s="104"/>
+      <c r="E90" s="104"/>
+      <c r="F90" s="104"/>
+      <c r="G90" s="104"/>
+      <c r="H90" s="104"/>
+      <c r="I90" s="104"/>
+      <c r="J90" s="104"/>
+      <c r="K90" s="104"/>
+      <c r="L90" s="104"/>
+      <c r="M90" s="104"/>
+      <c r="N90" s="104"/>
+      <c r="O90" s="104"/>
+      <c r="P90" s="104"/>
+      <c r="Q90" s="104"/>
+    </row>
+    <row r="91" spans="3:17">
+      <c r="C91" s="108"/>
+      <c r="D91" s="104"/>
+      <c r="E91" s="104"/>
+      <c r="F91" s="104"/>
+      <c r="G91" s="104"/>
+      <c r="H91" s="104"/>
+      <c r="I91" s="104"/>
+      <c r="J91" s="104"/>
+      <c r="K91" s="104"/>
+      <c r="L91" s="104"/>
+      <c r="M91" s="104"/>
+      <c r="N91" s="104"/>
+      <c r="O91" s="104"/>
+      <c r="P91" s="104"/>
+      <c r="Q91" s="104"/>
+    </row>
+    <row r="92" spans="3:17">
+      <c r="C92" s="103" t="s">
+        <v>732</v>
+      </c>
+      <c r="D92" s="104"/>
+      <c r="E92" s="104"/>
+      <c r="F92" s="104"/>
+      <c r="G92" s="104"/>
+      <c r="H92" s="104"/>
+      <c r="I92" s="104"/>
+      <c r="J92" s="104"/>
+      <c r="K92" s="104"/>
+      <c r="L92" s="104"/>
+      <c r="M92" s="104"/>
+      <c r="N92" s="104"/>
+      <c r="O92" s="104"/>
+      <c r="P92" s="104"/>
+      <c r="Q92" s="104"/>
+    </row>
+    <row r="93" spans="3:17">
+      <c r="C93" s="105" t="s">
+        <v>514</v>
+      </c>
+      <c r="D93" s="104"/>
+      <c r="E93" s="104"/>
+      <c r="F93" s="104"/>
+      <c r="G93" s="104"/>
+      <c r="H93" s="104"/>
+      <c r="I93" s="104"/>
+      <c r="J93" s="104"/>
+      <c r="K93" s="104"/>
+      <c r="L93" s="104"/>
+      <c r="M93" s="104"/>
+      <c r="N93" s="104"/>
+      <c r="O93" s="104"/>
+      <c r="P93" s="104"/>
+      <c r="Q93" s="104"/>
+    </row>
+    <row r="94" spans="3:17">
+      <c r="C94" s="107" t="s">
+        <v>771</v>
+      </c>
+      <c r="D94" s="104"/>
+      <c r="E94" s="104"/>
+      <c r="F94" s="104"/>
+      <c r="G94" s="104"/>
+      <c r="H94" s="104"/>
+      <c r="I94" s="104"/>
+      <c r="J94" s="104"/>
+      <c r="K94" s="104"/>
+      <c r="L94" s="104"/>
+      <c r="M94" s="104"/>
+      <c r="N94" s="104"/>
+      <c r="O94" s="104"/>
+      <c r="P94" s="104"/>
+      <c r="Q94" s="104"/>
+    </row>
+    <row r="95" spans="3:17">
+      <c r="C95" s="107" t="s">
+        <v>772</v>
+      </c>
+      <c r="D95" s="104"/>
+      <c r="E95" s="104"/>
+      <c r="F95" s="104"/>
+      <c r="G95" s="104"/>
+      <c r="H95" s="104"/>
+      <c r="I95" s="104"/>
+      <c r="J95" s="104"/>
+      <c r="K95" s="104"/>
+      <c r="L95" s="104"/>
+      <c r="M95" s="104"/>
+      <c r="N95" s="104"/>
+      <c r="O95" s="104"/>
+      <c r="P95" s="104"/>
+      <c r="Q95" s="104"/>
+    </row>
+    <row r="96" spans="3:17">
+      <c r="C96" s="107" t="s">
+        <v>773</v>
+      </c>
+      <c r="D96" s="104"/>
+      <c r="E96" s="104"/>
+      <c r="F96" s="104"/>
+      <c r="G96" s="104"/>
+      <c r="H96" s="104"/>
+      <c r="I96" s="104"/>
+      <c r="J96" s="104"/>
+      <c r="K96" s="104"/>
+      <c r="L96" s="104"/>
+      <c r="M96" s="104"/>
+      <c r="N96" s="104"/>
+      <c r="O96" s="104"/>
+      <c r="P96" s="104"/>
+      <c r="Q96" s="104"/>
+    </row>
+    <row r="97" spans="3:17">
+      <c r="C97" s="107" t="s">
+        <v>774</v>
+      </c>
+      <c r="D97" s="104"/>
+      <c r="E97" s="104"/>
+      <c r="F97" s="104"/>
+      <c r="G97" s="104"/>
+      <c r="H97" s="104"/>
+      <c r="I97" s="104"/>
+      <c r="J97" s="104"/>
+      <c r="K97" s="104"/>
+      <c r="L97" s="104"/>
+      <c r="M97" s="104"/>
+      <c r="N97" s="104"/>
+      <c r="O97" s="104"/>
+      <c r="P97" s="104"/>
+      <c r="Q97" s="104"/>
+    </row>
+    <row r="98" spans="3:17">
+      <c r="C98" s="108"/>
+      <c r="D98" s="104"/>
+      <c r="E98" s="104"/>
+      <c r="F98" s="104"/>
+      <c r="G98" s="104"/>
+      <c r="H98" s="104"/>
+      <c r="I98" s="104"/>
+      <c r="J98" s="104"/>
+      <c r="K98" s="104"/>
+      <c r="L98" s="104"/>
+      <c r="M98" s="104"/>
+      <c r="N98" s="104"/>
+      <c r="O98" s="104"/>
+      <c r="P98" s="104"/>
+      <c r="Q98" s="104"/>
+    </row>
+    <row r="99" spans="3:17">
+      <c r="C99" s="121" t="s">
+        <v>775</v>
+      </c>
+      <c r="D99" s="104"/>
+      <c r="E99" s="104"/>
+      <c r="F99" s="104"/>
+      <c r="G99" s="104"/>
+      <c r="H99" s="104"/>
+      <c r="I99" s="104"/>
+      <c r="J99" s="104"/>
+      <c r="K99" s="104"/>
+      <c r="L99" s="104"/>
+      <c r="M99" s="104"/>
+      <c r="N99" s="104"/>
+      <c r="O99" s="104"/>
+      <c r="P99" s="104"/>
+      <c r="Q99" s="104"/>
+    </row>
+    <row r="100" spans="3:17">
+      <c r="C100" s="121" t="s">
+        <v>776</v>
+      </c>
+      <c r="D100" s="104"/>
+      <c r="E100" s="104"/>
+      <c r="F100" s="104"/>
+      <c r="G100" s="104"/>
+      <c r="H100" s="104"/>
+      <c r="I100" s="104"/>
+      <c r="J100" s="104"/>
+      <c r="K100" s="104"/>
+      <c r="L100" s="104"/>
+      <c r="M100" s="104"/>
+      <c r="N100" s="104"/>
+      <c r="O100" s="104"/>
+      <c r="P100" s="104"/>
+      <c r="Q100" s="104"/>
+    </row>
+    <row r="101" spans="3:17">
+      <c r="C101" s="108"/>
+      <c r="D101" s="104"/>
+      <c r="E101" s="104"/>
+      <c r="F101" s="104"/>
+      <c r="G101" s="104"/>
+      <c r="H101" s="104"/>
+      <c r="I101" s="104"/>
+      <c r="J101" s="104"/>
+      <c r="K101" s="104"/>
+      <c r="L101" s="104"/>
+      <c r="M101" s="104"/>
+      <c r="N101" s="104"/>
+      <c r="O101" s="104"/>
+      <c r="P101" s="104"/>
+      <c r="Q101" s="104"/>
+    </row>
+    <row r="102" spans="3:17">
+      <c r="C102" s="121" t="s">
+        <v>777</v>
+      </c>
+      <c r="D102" s="104"/>
+      <c r="E102" s="104"/>
+      <c r="F102" s="104"/>
+      <c r="G102" s="104"/>
+      <c r="H102" s="104"/>
+      <c r="I102" s="104"/>
+      <c r="J102" s="104"/>
+      <c r="K102" s="104"/>
+      <c r="L102" s="104"/>
+      <c r="M102" s="104"/>
+      <c r="N102" s="104"/>
+      <c r="O102" s="104"/>
+      <c r="P102" s="104"/>
+      <c r="Q102" s="104"/>
+    </row>
+    <row r="103" spans="3:17">
+      <c r="C103" s="121" t="s">
+        <v>778</v>
+      </c>
+      <c r="D103" s="104"/>
+      <c r="E103" s="104"/>
+      <c r="F103" s="104"/>
+      <c r="G103" s="104"/>
+      <c r="H103" s="104"/>
+      <c r="I103" s="104"/>
+      <c r="J103" s="104"/>
+      <c r="K103" s="104"/>
+      <c r="L103" s="104"/>
+      <c r="M103" s="104"/>
+      <c r="N103" s="104"/>
+      <c r="O103" s="104"/>
+      <c r="P103" s="104"/>
+      <c r="Q103" s="104"/>
+    </row>
+    <row r="104" spans="3:17">
+      <c r="C104" s="108"/>
+      <c r="D104" s="104"/>
+      <c r="E104" s="104"/>
+      <c r="F104" s="104"/>
+      <c r="G104" s="104"/>
+      <c r="H104" s="104"/>
+      <c r="I104" s="104"/>
+      <c r="J104" s="104"/>
+      <c r="K104" s="104"/>
+      <c r="L104" s="104"/>
+      <c r="M104" s="104"/>
+      <c r="N104" s="104"/>
+      <c r="O104" s="104"/>
+      <c r="P104" s="104"/>
+      <c r="Q104" s="104"/>
+    </row>
+    <row r="105" spans="3:17">
+      <c r="C105" s="121" t="s">
+        <v>779</v>
+      </c>
+      <c r="D105" s="104"/>
+      <c r="E105" s="104"/>
+      <c r="F105" s="104"/>
+      <c r="G105" s="104"/>
+      <c r="H105" s="104"/>
+      <c r="I105" s="104"/>
+      <c r="J105" s="104"/>
+      <c r="K105" s="104"/>
+      <c r="L105" s="104"/>
+      <c r="M105" s="104"/>
+      <c r="N105" s="104"/>
+      <c r="O105" s="104"/>
+      <c r="P105" s="104"/>
+      <c r="Q105" s="104"/>
+    </row>
+    <row r="106" spans="3:17">
+      <c r="C106" s="108"/>
+      <c r="D106" s="104"/>
+      <c r="E106" s="104"/>
+      <c r="F106" s="104"/>
+      <c r="G106" s="104"/>
+      <c r="H106" s="104"/>
+      <c r="I106" s="104"/>
+      <c r="J106" s="104"/>
+      <c r="K106" s="104"/>
+      <c r="L106" s="104"/>
+      <c r="M106" s="104"/>
+      <c r="N106" s="104"/>
+      <c r="O106" s="104"/>
+      <c r="P106" s="104"/>
+      <c r="Q106" s="104"/>
+    </row>
+    <row r="107" spans="3:17">
+      <c r="C107" s="109" t="s">
+        <v>735</v>
+      </c>
+      <c r="D107" s="104"/>
+      <c r="E107" s="104"/>
+      <c r="F107" s="104"/>
+      <c r="G107" s="104"/>
+      <c r="H107" s="104"/>
+      <c r="I107" s="104"/>
+      <c r="J107" s="104"/>
+      <c r="K107" s="104"/>
+      <c r="L107" s="104"/>
+      <c r="M107" s="104"/>
+      <c r="N107" s="104"/>
+      <c r="O107" s="104"/>
+      <c r="P107" s="104"/>
+      <c r="Q107" s="104"/>
+    </row>
+    <row r="108" spans="3:17">
+      <c r="C108" s="105" t="s">
+        <v>284</v>
+      </c>
+      <c r="D108" s="104"/>
+      <c r="E108" s="104"/>
+      <c r="F108" s="104"/>
+      <c r="G108" s="104"/>
+      <c r="H108" s="104"/>
+      <c r="I108" s="104"/>
+      <c r="J108" s="104"/>
+      <c r="K108" s="104"/>
+      <c r="L108" s="104"/>
+      <c r="M108" s="104"/>
+      <c r="N108" s="104"/>
+      <c r="O108" s="104"/>
+      <c r="P108" s="104"/>
+      <c r="Q108" s="104"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16765,21 +21032,21 @@
       <c r="D16" t="s">
         <v>719</v>
       </c>
-      <c r="I16" s="108" t="s">
+      <c r="I16" s="115" t="s">
         <v>723</v>
       </c>
-      <c r="J16" s="109"/>
+      <c r="J16" s="116"/>
     </row>
     <row r="17" spans="3:10" ht="15" customHeight="1">
-      <c r="I17" s="110"/>
-      <c r="J17" s="111"/>
+      <c r="I17" s="117"/>
+      <c r="J17" s="118"/>
     </row>
     <row r="18" spans="3:10">
       <c r="D18" t="s">
         <v>720</v>
       </c>
-      <c r="I18" s="112"/>
-      <c r="J18" s="113"/>
+      <c r="I18" s="119"/>
+      <c r="J18" s="120"/>
     </row>
     <row r="19" spans="3:10">
       <c r="C19" t="s">
@@ -16802,7 +21069,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:G90"/>
+  <dimension ref="B1:G92"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="50.140625" bestFit="1" customWidth="1"/>
@@ -17946,7 +22213,7 @@
       <c r="E80" s="6"/>
       <c r="F80" s="6"/>
     </row>
-    <row r="81" spans="2:6">
+    <row r="81" spans="2:7">
       <c r="B81" s="5" t="s">
         <v>467</v>
       </c>
@@ -17959,116 +22226,147 @@
       </c>
       <c r="F81" s="6"/>
     </row>
-    <row r="82" spans="2:6" ht="30">
+    <row r="82" spans="2:7" ht="30">
       <c r="B82" s="5" t="s">
         <v>469</v>
       </c>
       <c r="C82" s="7" t="s">
         <v>736</v>
       </c>
-      <c r="D82" s="6"/>
+      <c r="D82" s="42">
+        <v>1</v>
+      </c>
       <c r="E82" s="16" t="s">
         <v>468</v>
       </c>
-      <c r="F82" s="16" t="s">
+      <c r="F82" s="16"/>
+    </row>
+    <row r="83" spans="2:7">
+      <c r="B83" s="5">
+        <v>24.1</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>737</v>
+      </c>
+      <c r="D83" s="42">
+        <v>1</v>
+      </c>
+      <c r="E83" s="16"/>
+      <c r="F83" s="16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="83" spans="2:6">
-      <c r="B83" s="5" t="s">
+    <row r="84" spans="2:7">
+      <c r="B84" s="5">
+        <v>24.2</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>781</v>
+      </c>
+      <c r="D84" s="42">
+        <v>1</v>
+      </c>
+      <c r="E84" s="16"/>
+      <c r="F84" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G84" s="48"/>
+    </row>
+    <row r="85" spans="2:7">
+      <c r="B85" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="C83" s="6" t="s">
+      <c r="C85" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D83" s="6"/>
-      <c r="E83" s="16"/>
-      <c r="F83" s="6"/>
-    </row>
-    <row r="84" spans="2:6">
-      <c r="B84" s="5" t="s">
+      <c r="D85" s="6"/>
+      <c r="E85" s="16"/>
+      <c r="F85" s="6"/>
+    </row>
+    <row r="86" spans="2:7">
+      <c r="B86" s="5" t="s">
         <v>478</v>
       </c>
-      <c r="C84" s="6" t="s">
+      <c r="C86" s="6" t="s">
         <v>480</v>
-      </c>
-      <c r="D84" s="6"/>
-      <c r="E84" s="16"/>
-      <c r="F84" s="6"/>
-    </row>
-    <row r="85" spans="2:6" ht="60">
-      <c r="B85" s="5" t="s">
-        <v>490</v>
-      </c>
-      <c r="C85" s="79" t="s">
-        <v>483</v>
-      </c>
-      <c r="D85" s="6"/>
-      <c r="E85" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="F85" s="6"/>
-    </row>
-    <row r="86" spans="2:6" ht="30">
-      <c r="B86" s="5" t="s">
-        <v>491</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>485</v>
       </c>
       <c r="D86" s="6"/>
       <c r="E86" s="16"/>
       <c r="F86" s="6"/>
     </row>
-    <row r="87" spans="2:6">
+    <row r="87" spans="2:7" ht="60">
       <c r="B87" s="5" t="s">
-        <v>492</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>486</v>
+        <v>490</v>
+      </c>
+      <c r="C87" s="79" t="s">
+        <v>483</v>
       </c>
       <c r="D87" s="6"/>
-      <c r="E87" s="16"/>
+      <c r="E87" s="16" t="s">
+        <v>484</v>
+      </c>
       <c r="F87" s="6"/>
     </row>
-    <row r="88" spans="2:6" ht="60">
+    <row r="88" spans="2:7" ht="30">
       <c r="B88" s="5" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D88" s="6"/>
       <c r="E88" s="16"/>
       <c r="F88" s="6"/>
     </row>
-    <row r="89" spans="2:6" ht="30">
+    <row r="89" spans="2:7">
       <c r="B89" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="D89" s="6"/>
+      <c r="E89" s="16"/>
+      <c r="F89" s="6"/>
+    </row>
+    <row r="90" spans="2:7" ht="60">
+      <c r="B90" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="D90" s="6"/>
+      <c r="E90" s="16"/>
+      <c r="F90" s="6"/>
+    </row>
+    <row r="91" spans="2:7" ht="30">
+      <c r="B91" s="5" t="s">
         <v>494</v>
       </c>
-      <c r="C89" s="7" t="s">
+      <c r="C91" s="7" t="s">
         <v>477</v>
       </c>
-      <c r="D89" s="42">
+      <c r="D91" s="42">
         <v>0</v>
       </c>
-      <c r="E89" s="16"/>
-      <c r="F89" s="16" t="s">
+      <c r="E91" s="16"/>
+      <c r="F91" s="16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="90" spans="2:6">
-      <c r="B90" s="77" t="s">
+    <row r="92" spans="2:7">
+      <c r="B92" s="77" t="s">
         <v>474</v>
       </c>
-      <c r="C90" s="57" t="s">
+      <c r="C92" s="57" t="s">
         <v>473</v>
       </c>
-      <c r="D90" s="1"/>
-      <c r="E90" s="49" t="s">
+      <c r="D92" s="1"/>
+      <c r="E92" s="49" t="s">
         <v>472</v>
       </c>
-      <c r="F90" s="1"/>
+      <c r="F92" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -18122,7 +22420,7 @@
     <hyperlink ref="E67" r:id="rId8"/>
     <hyperlink ref="E81" r:id="rId9"/>
     <hyperlink ref="E82" r:id="rId10"/>
-    <hyperlink ref="E90" r:id="rId11"/>
+    <hyperlink ref="E92" r:id="rId11"/>
     <hyperlink ref="F49" location="'#9'!B2" display="Link"/>
     <hyperlink ref="F52" location="'#12'!B2" display="Link"/>
     <hyperlink ref="F57" location="'#16'!B2" display="Link"/>
@@ -18135,8 +22433,10 @@
     <hyperlink ref="F55" location="'#15'!B2" display="Link"/>
     <hyperlink ref="F62" location="'#16'!B89" display="Link"/>
     <hyperlink ref="F63" location="'#16'!B10" display="Link"/>
-    <hyperlink ref="F89" location="'#31'!B2" display="Link"/>
-    <hyperlink ref="F82" location="'#24'!B2" display="Link"/>
+    <hyperlink ref="F91" location="'#31'!B2" display="Link"/>
+    <hyperlink ref="F83" location="'#24'!B2" display="Link"/>
+    <hyperlink ref="F84" location="'#24'!B2" display="Link"/>
+    <hyperlink ref="F84:G84" location="'#24'!B26" display="Link"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId12"/>
@@ -18454,7 +22754,7 @@
       <c r="D12" s="11"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" thickBot="1">
-      <c r="C13" s="103" t="s">
+      <c r="C13" s="110" t="s">
         <v>78</v>
       </c>
       <c r="D13" s="26" t="s">
@@ -18471,7 +22771,7 @@
       <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:10" ht="15.75" thickBot="1">
-      <c r="C14" s="104"/>
+      <c r="C14" s="111"/>
       <c r="D14" s="23" t="s">
         <v>65</v>
       </c>
@@ -18487,7 +22787,7 @@
       <c r="J14" s="25"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="C15" s="104"/>
+      <c r="C15" s="111"/>
       <c r="D15" s="26" t="s">
         <v>66</v>
       </c>
@@ -18502,7 +22802,7 @@
       <c r="I15" s="28"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="C16" s="104"/>
+      <c r="C16" s="111"/>
       <c r="D16" s="29"/>
       <c r="E16" s="30" t="s">
         <v>74</v>
@@ -18513,7 +22813,7 @@
       <c r="I16" s="31"/>
     </row>
     <row r="17" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C17" s="105"/>
+      <c r="C17" s="112"/>
       <c r="D17" s="32"/>
       <c r="E17" s="33" t="s">
         <v>75</v>
@@ -18544,7 +22844,7 @@
       <c r="L18" s="25"/>
     </row>
     <row r="19" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C19" s="103" t="s">
+      <c r="C19" s="110" t="s">
         <v>78</v>
       </c>
       <c r="D19" s="23" t="s">
@@ -18555,7 +22855,7 @@
       </c>
     </row>
     <row r="20" spans="3:12">
-      <c r="C20" s="104"/>
+      <c r="C20" s="111"/>
       <c r="D20" s="26" t="s">
         <v>82</v>
       </c>
@@ -18564,7 +22864,7 @@
       </c>
     </row>
     <row r="21" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C21" s="105"/>
+      <c r="C21" s="112"/>
       <c r="D21" s="32"/>
       <c r="E21" s="40" t="s">
         <v>84</v>

--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -25,8 +25,12 @@
     <sheet name="#14" sheetId="12" r:id="rId16"/>
     <sheet name="#15" sheetId="18" r:id="rId17"/>
     <sheet name="#16" sheetId="15" r:id="rId18"/>
-    <sheet name="#24" sheetId="20" r:id="rId19"/>
-    <sheet name="#31" sheetId="19" r:id="rId20"/>
+    <sheet name="#19" sheetId="22" r:id="rId19"/>
+    <sheet name="#24" sheetId="20" r:id="rId20"/>
+    <sheet name="#25" sheetId="21" r:id="rId21"/>
+    <sheet name="#29" sheetId="23" r:id="rId22"/>
+    <sheet name="#30" sheetId="24" r:id="rId23"/>
+    <sheet name="#31" sheetId="19" r:id="rId24"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -38,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1032" uniqueCount="782">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="816">
   <si>
     <t>No.</t>
   </si>
@@ -3783,9 +3787,6 @@
     <t>#19</t>
   </si>
   <si>
-    <t>Làm thế nào để tránh Memory leak ( và các tool tránh)</t>
-  </si>
-  <si>
     <t>https://chatgpt.com/share/690b28bd-0994-8002-8476-6d34821ba602</t>
   </si>
   <si>
@@ -3852,10 +3853,6 @@
     <t>File anh Thư</t>
   </si>
   <si>
-    <t>What is a template in C++? 
-- class template khác class thường ntn khi compile</t>
-  </si>
-  <si>
     <t>How do vectors differ from arrays in C++?</t>
   </si>
   <si>
@@ -3863,12 +3860,6 @@
   </si>
   <si>
     <t>How to loop through map, vector</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Casting in cpp
-- static_cast
-- dynamic_cast
-- reinterpret_cast</t>
   </si>
   <si>
     <t>#27</t>
@@ -10143,6 +10134,155 @@
   </si>
   <si>
     <t>observer</t>
+  </si>
+  <si>
+    <t>#32</t>
+  </si>
+  <si>
+    <t>Cách sử dụng erase, remove</t>
+  </si>
+  <si>
+    <t>What is a template in C++? 
+- class template khác class thường ntn khi compile
+- function template</t>
+  </si>
+  <si>
+    <t>Struct :</t>
+  </si>
+  <si>
+    <t>Cung cấp tài nguyên cho từng biến của nó. Vì vậy, tổng kích thước của struct = tổng kích thước của các biến trong struct</t>
+  </si>
+  <si>
+    <t>Union :</t>
+  </si>
+  <si>
+    <t>union chỉ cấp kích thước của biến lớn nhất. Khi dùng biến nào trong union thì replace biến cũ đi và ghi đè biến cần dùng lên tài nguyên.</t>
+  </si>
+  <si>
+    <t>Một biến phải được đặt tại địa chỉ chia hết cho kích thước truy cập của nó.</t>
+  </si>
+  <si>
+    <t>Alignment (căn lề dữ liệu) là quy tắc bắt buộc trong hầu hết CPU:</t>
+  </si>
+  <si>
+    <t>Padding là các byte rỗng compiler chèn vào để đảm bảo alignment của từng biến.</t>
+  </si>
+  <si>
+    <t>VD :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int </t>
+  </si>
+  <si>
+    <t>alignment = 4</t>
+  </si>
+  <si>
+    <t>char</t>
+  </si>
+  <si>
+    <t>alignment = 1</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>alignment = 32</t>
+  </si>
+  <si>
+    <t>Vì sao phải dùng quy tắc alignment : vì CPU đọc dữ liệu theo từng word (word là đơn vị dữ liệu mà CPU có thể xử lý trong 1 lần)</t>
+  </si>
+  <si>
+    <t>nếu biến ở vị trí lấp lửng, CPU phải đọc 2 word rồi ghép lại dẫn đến làm giảm hiệu suất, ngoài ra còn dễ crash khi thay đổi môi trường</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Một đối tượng </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>có nhiều thuộc tính</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> cùng tồn tại</t>
+    </r>
+  </si>
+  <si>
+    <t>Muốn gom nhiều biến vào một khối logic</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Muốn nhóm nhiều loại dữ liệu mà </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>không chia sẻ chung bộ nhớ</t>
+    </r>
+  </si>
+  <si>
+    <t>Khi nào dùng :</t>
+  </si>
+  <si>
+    <t>Muốn model hóa dữ liệu (OOP hoặc DATA)</t>
+  </si>
+  <si>
+    <t>Làm variant type (kiểu dữ liệu thay đổi)</t>
+  </si>
+  <si>
+    <t>Muốn tối ưu bộ nhớ</t>
+  </si>
+  <si>
+    <t>Dùng RAII để tự tạo tài nguyên và dọn dẹp khi ra khỏi scope (vector, smart ptr,…)</t>
+  </si>
+  <si>
+    <t>Linux</t>
+  </si>
+  <si>
+    <t>Các công cụ kiểm tra memory leak</t>
+  </si>
+  <si>
+    <t>valgrind --leak-check=full ./main</t>
+  </si>
+  <si>
+    <t>g++ -g main.cpp -o main</t>
+  </si>
+  <si>
+    <t>Nếu sử dụng con trỏ thô, sau khi dùng xong phải delete và set null. Trước khi dùng 1 con trỏ cần kiểm tra điều kiện null</t>
+  </si>
+  <si>
+    <t>static_cast</t>
+  </si>
+  <si>
+    <t>dynamic_cast</t>
+  </si>
+  <si>
+    <t>reinterpret_cast</t>
+  </si>
+  <si>
+    <t>Làm thế nào để tránh Memory leak ( và tool tránh Valgrind)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Casting in cpp</t>
   </si>
 </sst>
 </file>
@@ -10949,6 +11089,9 @@
     <xf numFmtId="0" fontId="6" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -10981,9 +11124,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -16509,72 +16649,72 @@
     </row>
     <row r="3" spans="2:5">
       <c r="C3" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="5" spans="2:5">
       <c r="C5" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="D6" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="E6" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="D7" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="E7" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="C9" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="C11" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="D12" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="C15" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="17" spans="3:19">
       <c r="D17" s="83" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="E17" s="87"/>
       <c r="F17" s="87"/>
       <c r="G17" s="87"/>
       <c r="H17" s="87"/>
       <c r="I17" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="18" spans="3:19">
       <c r="D18" s="83" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="E18" s="87"/>
       <c r="F18" s="87"/>
       <c r="G18" s="87"/>
       <c r="H18" s="87"/>
       <c r="I18" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="19" spans="3:19">
@@ -16586,31 +16726,31 @@
     </row>
     <row r="20" spans="3:19">
       <c r="D20" s="85" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="E20" s="87"/>
       <c r="F20" s="87"/>
       <c r="G20" s="87"/>
       <c r="H20" s="87"/>
       <c r="I20" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="21" spans="3:19">
       <c r="D21" s="86" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="E21" s="87"/>
       <c r="F21" s="87"/>
       <c r="G21" s="87"/>
       <c r="H21" s="87"/>
       <c r="I21" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="22" spans="3:19">
       <c r="D22" s="86" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="E22" s="87"/>
       <c r="F22" s="87"/>
@@ -16635,7 +16775,7 @@
     </row>
     <row r="25" spans="3:19">
       <c r="D25" s="85" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="E25" s="87"/>
       <c r="F25" s="87"/>
@@ -16644,7 +16784,7 @@
     </row>
     <row r="26" spans="3:19">
       <c r="D26" s="86" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="E26" s="87"/>
       <c r="F26" s="87"/>
@@ -16653,7 +16793,7 @@
     </row>
     <row r="27" spans="3:19">
       <c r="D27" s="86" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="E27" s="87"/>
       <c r="F27" s="87"/>
@@ -16671,7 +16811,7 @@
     </row>
     <row r="31" spans="3:19">
       <c r="C31" s="88" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="D31" s="88"/>
       <c r="E31" s="88"/>
@@ -16683,7 +16823,7 @@
       <c r="K31" s="88"/>
       <c r="L31" s="88"/>
       <c r="M31" s="89" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="N31" s="89"/>
       <c r="O31" s="89"/>
@@ -16714,7 +16854,7 @@
     <row r="33" spans="3:19">
       <c r="C33" s="88"/>
       <c r="D33" s="88" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="E33" s="88"/>
       <c r="F33" s="88"/>
@@ -16725,7 +16865,7 @@
       <c r="K33" s="88"/>
       <c r="L33" s="88"/>
       <c r="M33" s="89" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="N33" s="89"/>
       <c r="O33" s="89"/>
@@ -16746,7 +16886,7 @@
       <c r="K34" s="88"/>
       <c r="L34" s="88"/>
       <c r="M34" s="89" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="N34" s="89"/>
       <c r="O34" s="89"/>
@@ -16779,7 +16919,7 @@
     <row r="36" spans="3:19">
       <c r="C36" s="88"/>
       <c r="D36" s="88" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="E36" s="88"/>
       <c r="F36" s="88"/>
@@ -16793,7 +16933,7 @@
     <row r="37" spans="3:19">
       <c r="C37" s="88"/>
       <c r="D37" s="88" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="E37" s="88"/>
       <c r="F37" s="88"/>
@@ -16831,101 +16971,101 @@
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="C4" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="D6" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="D7" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="D8" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="E8" s="80"/>
     </row>
     <row r="9" spans="2:5">
       <c r="D9" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="D10" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="D11" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="D12" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="D13" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="D14" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="D15" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="D16" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="17" spans="3:12">
       <c r="D17" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="18" spans="3:12">
       <c r="D18" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="19" spans="3:12">
       <c r="D19" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="22" spans="3:12">
       <c r="C22" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="23" spans="3:12">
       <c r="D23" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="L23" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="24" spans="3:12">
       <c r="D24" s="81" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="E24" s="90"/>
       <c r="F24" s="90"/>
@@ -16936,7 +17076,7 @@
     </row>
     <row r="25" spans="3:12">
       <c r="D25" s="81" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="E25" s="90"/>
       <c r="F25" s="90"/>
@@ -16947,12 +17087,12 @@
     </row>
     <row r="27" spans="3:12">
       <c r="D27" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="28" spans="3:12">
       <c r="D28" s="81" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="E28" s="90"/>
       <c r="F28" s="90"/>
@@ -16963,7 +17103,7 @@
     </row>
     <row r="29" spans="3:12">
       <c r="D29" s="81" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="E29" s="90"/>
       <c r="F29" s="90"/>
@@ -16974,7 +17114,7 @@
     </row>
     <row r="30" spans="3:12">
       <c r="D30" s="82" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="E30" s="90"/>
       <c r="F30" s="90"/>
@@ -16985,42 +17125,42 @@
     </row>
     <row r="33" spans="3:13">
       <c r="D33" s="91" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="34" spans="3:13">
       <c r="E34" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="35" spans="3:13">
       <c r="F35" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="36" spans="3:13">
       <c r="F36" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="39" spans="3:13">
       <c r="C39" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="41" spans="3:13">
       <c r="D41" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="43" spans="3:13">
       <c r="D43" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="44" spans="3:13">
       <c r="E44" s="81" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="F44" s="90"/>
       <c r="G44" s="90"/>
@@ -17044,7 +17184,7 @@
     </row>
     <row r="46" spans="3:13">
       <c r="E46" s="81" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="F46" s="90"/>
       <c r="G46" s="90"/>
@@ -17057,7 +17197,7 @@
     </row>
     <row r="47" spans="3:13">
       <c r="E47" s="81" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="F47" s="90"/>
       <c r="G47" s="90"/>
@@ -17070,7 +17210,7 @@
     </row>
     <row r="48" spans="3:13">
       <c r="E48" s="81" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="F48" s="90"/>
       <c r="G48" s="90"/>
@@ -17083,7 +17223,7 @@
     </row>
     <row r="49" spans="4:13">
       <c r="E49" s="82" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="F49" s="90"/>
       <c r="G49" s="90"/>
@@ -17096,7 +17236,7 @@
     </row>
     <row r="50" spans="4:13">
       <c r="E50" s="81" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="F50" s="90"/>
       <c r="G50" s="90"/>
@@ -17109,27 +17249,27 @@
     </row>
     <row r="53" spans="4:13">
       <c r="D53" s="91" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="54" spans="4:13">
       <c r="E54" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="55" spans="4:13">
       <c r="E55" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="56" spans="4:13">
       <c r="E56" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="57" spans="4:13">
       <c r="E57" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
     </row>
   </sheetData>
@@ -17145,89 +17285,89 @@
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="3" spans="2:5">
       <c r="C3" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="D3" t="s">
+        <v>503</v>
+      </c>
+      <c r="E3" t="s">
         <v>506</v>
-      </c>
-      <c r="E3" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="C4" s="80" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D4" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E4" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="C7" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="C8" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="C10" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="C11" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="C12" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="C13" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="C14" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="C15" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="C16" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="17" spans="3:3">
       <c r="C17" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="18" spans="3:3">
       <c r="C18" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="20" spans="3:3">
       <c r="C20" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="21" spans="3:3">
@@ -17237,17 +17377,17 @@
     </row>
     <row r="23" spans="3:3">
       <c r="C23" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="24" spans="3:3">
       <c r="C24" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
     </row>
     <row r="25" spans="3:3">
       <c r="C25" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
@@ -17262,70 +17402,70 @@
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
     </row>
     <row r="3" spans="2:5">
       <c r="C3" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="C4" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="C6" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="D7" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="D8" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="C10" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="C11" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="D12" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="C13" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="D14" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="E14" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="C15" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="D16" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
   </sheetData>
@@ -17387,230 +17527,230 @@
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
     </row>
     <row r="3" spans="2:4" ht="18.75">
       <c r="C3" s="93" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="D3" s="94"/>
     </row>
     <row r="5" spans="2:4">
       <c r="C5" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="D5" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
     </row>
     <row r="6" spans="2:4">
       <c r="D6" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
     </row>
     <row r="7" spans="2:4">
       <c r="D7" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
     </row>
     <row r="8" spans="2:4">
       <c r="D8" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="9" spans="2:4">
       <c r="D9" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="11" spans="2:4">
       <c r="C11" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="D11" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="12" spans="2:4">
       <c r="D12" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
     </row>
     <row r="13" spans="2:4">
       <c r="D13" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
     </row>
     <row r="14" spans="2:4">
       <c r="D14" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
     </row>
     <row r="15" spans="2:4">
       <c r="D15" s="92" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="16" spans="2:4">
       <c r="D16" s="76" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
     </row>
     <row r="17" spans="3:5">
       <c r="C17" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="D17" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="18" spans="3:5">
       <c r="D18" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="19" spans="3:5">
       <c r="E19" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
     </row>
     <row r="20" spans="3:5">
       <c r="E20" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
     </row>
     <row r="21" spans="3:5">
       <c r="D21" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
     </row>
     <row r="22" spans="3:5">
       <c r="D22" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
     </row>
     <row r="23" spans="3:5">
       <c r="D23" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
     </row>
     <row r="24" spans="3:5">
       <c r="D24" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
     </row>
     <row r="26" spans="3:5">
       <c r="C26" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="D26" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
     </row>
     <row r="27" spans="3:5">
       <c r="D27" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
     </row>
     <row r="28" spans="3:5">
       <c r="E28" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
     </row>
     <row r="29" spans="3:5">
       <c r="E29" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
     </row>
     <row r="33" spans="3:9" ht="18.75">
       <c r="C33" s="93" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D33" s="94"/>
     </row>
     <row r="35" spans="3:9">
       <c r="C35" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
     </row>
     <row r="36" spans="3:9">
       <c r="D36" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
     </row>
     <row r="38" spans="3:9">
       <c r="D38" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
     </row>
     <row r="39" spans="3:9">
       <c r="E39" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="40" spans="3:9">
       <c r="E40" t="s">
+        <v>682</v>
+      </c>
+      <c r="G40" t="s">
         <v>685</v>
       </c>
-      <c r="G40" t="s">
+      <c r="I40" t="s">
         <v>688</v>
-      </c>
-      <c r="I40" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="41" spans="3:9">
       <c r="E41" t="s">
+        <v>683</v>
+      </c>
+      <c r="G41" t="s">
         <v>686</v>
       </c>
-      <c r="G41" t="s">
-        <v>689</v>
-      </c>
       <c r="I41" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="42" spans="3:9">
       <c r="E42" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="G42" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
     </row>
     <row r="44" spans="3:9">
       <c r="D44" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="45" spans="3:9">
       <c r="E45" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="46" spans="3:9">
       <c r="E46" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="G46" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
     </row>
     <row r="47" spans="3:9">
       <c r="E47" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="G47" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
     </row>
     <row r="48" spans="3:9">
       <c r="E48" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="G48" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
     </row>
   </sheetData>
@@ -17626,31 +17766,31 @@
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="3" spans="2:4">
       <c r="C3" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D3" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="C4" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="D4" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="5" spans="2:4">
       <c r="C5" t="s">
+        <v>525</v>
+      </c>
+      <c r="D5" t="s">
         <v>528</v>
-      </c>
-      <c r="D5" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="10" spans="2:4">
@@ -17660,62 +17800,62 @@
     </row>
     <row r="11" spans="2:4">
       <c r="C11" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="12" spans="2:4">
       <c r="C12" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="13" spans="2:4">
       <c r="C13" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
     </row>
     <row r="14" spans="2:4">
       <c r="C14" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="16" spans="2:4">
       <c r="C16" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
     </row>
     <row r="17" spans="2:5">
       <c r="C17" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="18" spans="2:5">
       <c r="C18" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="19" spans="2:5">
       <c r="C19" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="20" spans="2:5">
       <c r="C20" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="22" spans="2:5">
       <c r="D22" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="23" spans="2:5">
       <c r="E23" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="24" spans="2:5">
       <c r="E24" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="25" spans="2:5">
@@ -17730,162 +17870,162 @@
     </row>
     <row r="29" spans="2:5">
       <c r="C29" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="30" spans="2:5">
       <c r="D30" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="31" spans="2:5">
       <c r="D31" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="32" spans="2:5">
       <c r="D32" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="34" spans="3:5">
       <c r="D34" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="36" spans="3:5">
       <c r="D36" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="37" spans="3:5">
       <c r="E37" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="38" spans="3:5">
       <c r="E38" s="17" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="39" spans="3:5">
       <c r="E39" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="41" spans="3:5">
       <c r="E41" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="42" spans="3:5">
       <c r="E42" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="43" spans="3:5">
       <c r="E43" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="45" spans="3:5">
       <c r="C45" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="46" spans="3:5">
       <c r="D46" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="47" spans="3:5">
       <c r="D47" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="49" spans="2:5">
       <c r="D49" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="50" spans="2:5">
       <c r="E50" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="51" spans="2:5">
       <c r="E51" s="17" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="52" spans="2:5">
       <c r="E52" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="54" spans="2:5">
       <c r="E54" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="55" spans="2:5">
       <c r="E55" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="56" spans="2:5">
       <c r="E56" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="58" spans="2:5">
       <c r="D58" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
     <row r="59" spans="2:5">
       <c r="D59" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
     </row>
     <row r="62" spans="2:5">
       <c r="B62" s="6" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="63" spans="2:5">
       <c r="C63" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="64" spans="2:5">
       <c r="C64" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
     </row>
     <row r="65" spans="3:4">
       <c r="C65" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="67" spans="3:4">
       <c r="C67" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="69" spans="3:4">
       <c r="D69" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
     </row>
     <row r="70" spans="3:4">
       <c r="D70" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="71" spans="3:4">
       <c r="D71" s="17" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="72" spans="3:4">
@@ -17895,22 +18035,22 @@
     </row>
     <row r="73" spans="3:4">
       <c r="D73" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="75" spans="3:4">
       <c r="D75" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
     </row>
     <row r="76" spans="3:4">
       <c r="D76" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="77" spans="3:4">
       <c r="D77" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
     </row>
     <row r="78" spans="3:4">
@@ -17920,89 +18060,89 @@
     </row>
     <row r="79" spans="3:4">
       <c r="D79" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="82" spans="2:9">
       <c r="B82" s="6" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="83" spans="2:9">
       <c r="C83" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
     </row>
     <row r="84" spans="2:9">
       <c r="C84" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
     </row>
     <row r="85" spans="2:9">
       <c r="C85" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="89" spans="2:9" ht="54" customHeight="1">
-      <c r="B89" s="113" t="s">
-        <v>625</v>
-      </c>
-      <c r="C89" s="114"/>
-      <c r="D89" s="114"/>
-      <c r="E89" s="114"/>
-      <c r="F89" s="114"/>
-      <c r="G89" s="114"/>
-      <c r="H89" s="114"/>
-      <c r="I89" s="114"/>
+      <c r="B89" s="114" t="s">
+        <v>622</v>
+      </c>
+      <c r="C89" s="115"/>
+      <c r="D89" s="115"/>
+      <c r="E89" s="115"/>
+      <c r="F89" s="115"/>
+      <c r="G89" s="115"/>
+      <c r="H89" s="115"/>
+      <c r="I89" s="115"/>
     </row>
     <row r="91" spans="2:9">
       <c r="B91" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
     </row>
     <row r="92" spans="2:9">
       <c r="C92" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
     </row>
     <row r="93" spans="2:9">
       <c r="C93" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
     </row>
     <row r="94" spans="2:9">
       <c r="D94" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
     </row>
     <row r="95" spans="2:9">
       <c r="D95" s="17" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
     </row>
     <row r="96" spans="2:9">
       <c r="C96" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
     </row>
     <row r="97" spans="3:4">
       <c r="D97" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
     </row>
     <row r="99" spans="3:4">
       <c r="C99" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
     </row>
     <row r="100" spans="3:4">
       <c r="C100" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
     </row>
     <row r="101" spans="3:4">
       <c r="C101" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
     </row>
   </sheetData>
@@ -18016,1806 +18156,46 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:Q108"/>
+  <dimension ref="B2:D9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="2:10">
-      <c r="B2" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10">
-      <c r="C3" s="103" t="s">
-        <v>724</v>
-      </c>
-      <c r="D3" s="104"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="104"/>
-      <c r="I3" s="104"/>
-      <c r="J3" s="104"/>
-    </row>
-    <row r="4" spans="2:10">
-      <c r="C4" s="105" t="s">
-        <v>514</v>
-      </c>
-      <c r="D4" s="104"/>
-      <c r="E4" s="104"/>
-      <c r="F4" s="104"/>
-      <c r="G4" s="104"/>
-      <c r="H4" s="104"/>
-      <c r="I4" s="104"/>
-      <c r="J4" s="104"/>
-    </row>
-    <row r="5" spans="2:10">
-      <c r="C5" s="103" t="s">
-        <v>631</v>
-      </c>
-      <c r="D5" s="104"/>
-      <c r="E5" s="104"/>
-      <c r="F5" s="104"/>
-      <c r="G5" s="104"/>
-      <c r="H5" s="104"/>
-      <c r="I5" s="104"/>
-      <c r="J5" s="104"/>
-    </row>
-    <row r="6" spans="2:10">
-      <c r="C6" s="103" t="s">
-        <v>725</v>
-      </c>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
-      <c r="F6" s="104"/>
-      <c r="G6" s="104"/>
-      <c r="H6" s="104"/>
-      <c r="I6" s="104"/>
-      <c r="J6" s="104"/>
-    </row>
-    <row r="7" spans="2:10">
-      <c r="C7" s="105" t="s">
-        <v>514</v>
-      </c>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
-      <c r="F7" s="104"/>
-      <c r="G7" s="104"/>
-      <c r="H7" s="104"/>
-      <c r="I7" s="104"/>
-      <c r="J7" s="104"/>
-    </row>
-    <row r="8" spans="2:10">
-      <c r="C8" s="105" t="s">
-        <v>726</v>
-      </c>
-      <c r="D8" s="104"/>
-      <c r="E8" s="104"/>
-      <c r="F8" s="104"/>
-      <c r="G8" s="104"/>
-      <c r="H8" s="104"/>
-      <c r="I8" s="104"/>
-      <c r="J8" s="104"/>
-    </row>
-    <row r="9" spans="2:10">
-      <c r="C9" s="105" t="s">
-        <v>727</v>
-      </c>
-      <c r="D9" s="104"/>
-      <c r="E9" s="104"/>
-      <c r="F9" s="104"/>
-      <c r="G9" s="104"/>
-      <c r="H9" s="104"/>
-      <c r="I9" s="104"/>
-      <c r="J9" s="104"/>
-    </row>
-    <row r="10" spans="2:10">
-      <c r="C10" s="105" t="s">
-        <v>284</v>
-      </c>
-      <c r="D10" s="104"/>
-      <c r="E10" s="104"/>
-      <c r="F10" s="104"/>
-      <c r="G10" s="104"/>
-      <c r="H10" s="104"/>
-      <c r="I10" s="104"/>
-      <c r="J10" s="104"/>
-    </row>
-    <row r="11" spans="2:10">
-      <c r="C11" s="103" t="s">
-        <v>728</v>
-      </c>
-      <c r="D11" s="104"/>
-      <c r="E11" s="104"/>
-      <c r="F11" s="104"/>
-      <c r="G11" s="104"/>
-      <c r="H11" s="104"/>
-      <c r="I11" s="104"/>
-      <c r="J11" s="104"/>
-    </row>
-    <row r="12" spans="2:10">
-      <c r="C12" s="106" t="s">
-        <v>729</v>
-      </c>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="104"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="104"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="104"/>
-    </row>
-    <row r="13" spans="2:10">
-      <c r="C13" s="106" t="s">
-        <v>730</v>
-      </c>
-      <c r="D13" s="104"/>
-      <c r="E13" s="104"/>
-      <c r="F13" s="104"/>
-      <c r="G13" s="104"/>
-      <c r="H13" s="104"/>
-      <c r="I13" s="104"/>
-      <c r="J13" s="104"/>
-    </row>
-    <row r="14" spans="2:10">
-      <c r="C14" s="107" t="s">
-        <v>731</v>
-      </c>
-      <c r="D14" s="104"/>
-      <c r="E14" s="104"/>
-      <c r="F14" s="104"/>
-      <c r="G14" s="104"/>
-      <c r="H14" s="104"/>
-      <c r="I14" s="104"/>
-      <c r="J14" s="104"/>
-    </row>
-    <row r="15" spans="2:10">
-      <c r="C15" s="105" t="s">
-        <v>613</v>
-      </c>
-      <c r="D15" s="104"/>
-      <c r="E15" s="104"/>
-      <c r="F15" s="104"/>
-      <c r="G15" s="104"/>
-      <c r="H15" s="104"/>
-      <c r="I15" s="104"/>
-      <c r="J15" s="104"/>
-    </row>
-    <row r="16" spans="2:10">
-      <c r="C16" s="108"/>
-      <c r="D16" s="104"/>
-      <c r="E16" s="104"/>
-      <c r="F16" s="104"/>
-      <c r="G16" s="104"/>
-      <c r="H16" s="104"/>
-      <c r="I16" s="104"/>
-      <c r="J16" s="104"/>
-    </row>
-    <row r="17" spans="2:17">
-      <c r="C17" s="103" t="s">
-        <v>732</v>
-      </c>
-      <c r="D17" s="104"/>
-      <c r="E17" s="104"/>
-      <c r="F17" s="104"/>
-      <c r="G17" s="104"/>
-      <c r="H17" s="104"/>
-      <c r="I17" s="104"/>
-      <c r="J17" s="104"/>
-    </row>
-    <row r="18" spans="2:17">
-      <c r="C18" s="105" t="s">
-        <v>514</v>
-      </c>
-      <c r="D18" s="104"/>
-      <c r="E18" s="104"/>
-      <c r="F18" s="104"/>
-      <c r="G18" s="104"/>
-      <c r="H18" s="104"/>
-      <c r="I18" s="104"/>
-      <c r="J18" s="104"/>
-    </row>
-    <row r="19" spans="2:17">
-      <c r="C19" s="107" t="s">
-        <v>733</v>
-      </c>
-      <c r="D19" s="104"/>
-      <c r="E19" s="104"/>
-      <c r="F19" s="104"/>
-      <c r="G19" s="104"/>
-      <c r="H19" s="104"/>
-      <c r="I19" s="104"/>
-      <c r="J19" s="104"/>
-    </row>
-    <row r="20" spans="2:17">
-      <c r="C20" s="107" t="s">
-        <v>734</v>
-      </c>
-      <c r="D20" s="104"/>
-      <c r="E20" s="104"/>
-      <c r="F20" s="104"/>
-      <c r="G20" s="104"/>
-      <c r="H20" s="104"/>
-      <c r="I20" s="104"/>
-      <c r="J20" s="104"/>
-    </row>
-    <row r="21" spans="2:17">
-      <c r="C21" s="109" t="s">
-        <v>735</v>
-      </c>
-      <c r="D21" s="104"/>
-      <c r="E21" s="104"/>
-      <c r="F21" s="104"/>
-      <c r="G21" s="104"/>
-      <c r="H21" s="104"/>
-      <c r="I21" s="104"/>
-      <c r="J21" s="104"/>
-    </row>
-    <row r="22" spans="2:17">
-      <c r="C22" s="105" t="s">
-        <v>284</v>
-      </c>
-      <c r="D22" s="104"/>
-      <c r="E22" s="104"/>
-      <c r="F22" s="104"/>
-      <c r="G22" s="104"/>
-      <c r="H22" s="104"/>
-      <c r="I22" s="104"/>
-      <c r="J22" s="104"/>
-    </row>
-    <row r="23" spans="2:17">
-      <c r="C23" s="104"/>
-      <c r="D23" s="104"/>
-      <c r="E23" s="104"/>
-      <c r="F23" s="104"/>
-      <c r="G23" s="104"/>
-      <c r="H23" s="104"/>
-      <c r="I23" s="104"/>
-      <c r="J23" s="104"/>
-    </row>
-    <row r="26" spans="2:17">
-      <c r="B26" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="27" spans="2:17">
-      <c r="C27" s="109" t="s">
-        <v>738</v>
-      </c>
-      <c r="D27" s="104"/>
-      <c r="E27" s="104"/>
-      <c r="F27" s="104"/>
-      <c r="G27" s="104"/>
-      <c r="H27" s="104"/>
-      <c r="I27" s="104"/>
-      <c r="J27" s="104"/>
-      <c r="K27" s="104"/>
-      <c r="L27" s="104"/>
-      <c r="M27" s="104"/>
-      <c r="N27" s="104"/>
-      <c r="O27" s="104"/>
-      <c r="P27" s="104"/>
-      <c r="Q27" s="104"/>
-    </row>
-    <row r="28" spans="2:17">
-      <c r="C28" s="109" t="s">
-        <v>739</v>
-      </c>
-      <c r="D28" s="104"/>
-      <c r="E28" s="104"/>
-      <c r="F28" s="104"/>
-      <c r="G28" s="104"/>
-      <c r="H28" s="104"/>
-      <c r="I28" s="104"/>
-      <c r="J28" s="104"/>
-      <c r="K28" s="104"/>
-      <c r="L28" s="104"/>
-      <c r="M28" s="104"/>
-      <c r="N28" s="104"/>
-      <c r="O28" s="104"/>
-      <c r="P28" s="104"/>
-      <c r="Q28" s="104"/>
-    </row>
-    <row r="29" spans="2:17">
-      <c r="C29" s="109" t="s">
-        <v>740</v>
-      </c>
-      <c r="D29" s="104"/>
-      <c r="E29" s="104"/>
-      <c r="F29" s="104"/>
-      <c r="G29" s="104"/>
-      <c r="H29" s="104"/>
-      <c r="I29" s="104"/>
-      <c r="J29" s="104"/>
-      <c r="K29" s="104"/>
-      <c r="L29" s="104"/>
-      <c r="M29" s="104"/>
-      <c r="N29" s="104"/>
-      <c r="O29" s="104"/>
-      <c r="P29" s="104"/>
-      <c r="Q29" s="104"/>
-    </row>
-    <row r="30" spans="2:17">
-      <c r="C30" s="109" t="s">
-        <v>741</v>
-      </c>
-      <c r="D30" s="104"/>
-      <c r="E30" s="104"/>
-      <c r="F30" s="104"/>
-      <c r="G30" s="104"/>
-      <c r="H30" s="104"/>
-      <c r="I30" s="104"/>
-      <c r="J30" s="104"/>
-      <c r="K30" s="104"/>
-      <c r="L30" s="104"/>
-      <c r="M30" s="104"/>
-      <c r="N30" s="104"/>
-      <c r="O30" s="104"/>
-      <c r="P30" s="104"/>
-      <c r="Q30" s="104"/>
-    </row>
-    <row r="31" spans="2:17">
-      <c r="C31" s="108"/>
-      <c r="D31" s="104"/>
-      <c r="E31" s="104"/>
-      <c r="F31" s="104"/>
-      <c r="G31" s="104"/>
-      <c r="H31" s="104"/>
-      <c r="I31" s="104"/>
-      <c r="J31" s="104"/>
-      <c r="K31" s="104"/>
-      <c r="L31" s="104"/>
-      <c r="M31" s="104"/>
-      <c r="N31" s="104"/>
-      <c r="O31" s="104"/>
-      <c r="P31" s="104"/>
-      <c r="Q31" s="104"/>
-    </row>
-    <row r="32" spans="2:17">
-      <c r="C32" s="103" t="s">
-        <v>742</v>
-      </c>
-      <c r="D32" s="104"/>
-      <c r="E32" s="104"/>
-      <c r="F32" s="104"/>
-      <c r="G32" s="104"/>
-      <c r="H32" s="104"/>
-      <c r="I32" s="104"/>
-      <c r="J32" s="104"/>
-      <c r="K32" s="104"/>
-      <c r="L32" s="104"/>
-      <c r="M32" s="104"/>
-      <c r="N32" s="104"/>
-      <c r="O32" s="104"/>
-      <c r="P32" s="104"/>
-      <c r="Q32" s="104"/>
-    </row>
-    <row r="33" spans="3:17">
-      <c r="C33" s="105" t="s">
-        <v>514</v>
-      </c>
-      <c r="D33" s="104"/>
-      <c r="E33" s="104"/>
-      <c r="F33" s="104"/>
-      <c r="G33" s="104"/>
-      <c r="H33" s="104"/>
-      <c r="I33" s="104"/>
-      <c r="J33" s="104"/>
-      <c r="K33" s="104"/>
-      <c r="L33" s="104"/>
-      <c r="M33" s="104"/>
-      <c r="N33" s="104"/>
-      <c r="O33" s="104"/>
-      <c r="P33" s="104"/>
-      <c r="Q33" s="104"/>
-    </row>
-    <row r="34" spans="3:17">
-      <c r="C34" s="103" t="s">
-        <v>631</v>
-      </c>
-      <c r="D34" s="104"/>
-      <c r="E34" s="104"/>
-      <c r="F34" s="104"/>
-      <c r="G34" s="104"/>
-      <c r="H34" s="104"/>
-      <c r="I34" s="104"/>
-      <c r="J34" s="104"/>
-      <c r="K34" s="104"/>
-      <c r="L34" s="104"/>
-      <c r="M34" s="104"/>
-      <c r="N34" s="104"/>
-      <c r="O34" s="104"/>
-      <c r="P34" s="104"/>
-      <c r="Q34" s="104"/>
-    </row>
-    <row r="35" spans="3:17">
-      <c r="C35" s="106" t="s">
-        <v>743</v>
-      </c>
-      <c r="D35" s="104"/>
-      <c r="E35" s="104"/>
-      <c r="F35" s="104"/>
-      <c r="G35" s="104"/>
-      <c r="H35" s="104"/>
-      <c r="I35" s="104"/>
-      <c r="J35" s="104"/>
-      <c r="K35" s="104"/>
-      <c r="L35" s="104"/>
-      <c r="M35" s="104"/>
-      <c r="N35" s="104"/>
-      <c r="O35" s="104"/>
-      <c r="P35" s="104"/>
-      <c r="Q35" s="104"/>
-    </row>
-    <row r="36" spans="3:17">
-      <c r="C36" s="103" t="s">
-        <v>744</v>
-      </c>
-      <c r="D36" s="104"/>
-      <c r="E36" s="104"/>
-      <c r="F36" s="104"/>
-      <c r="G36" s="104"/>
-      <c r="H36" s="104"/>
-      <c r="I36" s="104"/>
-      <c r="J36" s="104"/>
-      <c r="K36" s="104"/>
-      <c r="L36" s="104"/>
-      <c r="M36" s="104"/>
-      <c r="N36" s="104"/>
-      <c r="O36" s="104"/>
-      <c r="P36" s="104"/>
-      <c r="Q36" s="104"/>
-    </row>
-    <row r="37" spans="3:17">
-      <c r="C37" s="103" t="s">
-        <v>745</v>
-      </c>
-      <c r="D37" s="104"/>
-      <c r="E37" s="104"/>
-      <c r="F37" s="104"/>
-      <c r="G37" s="104"/>
-      <c r="H37" s="104"/>
-      <c r="I37" s="104"/>
-      <c r="J37" s="104"/>
-      <c r="K37" s="104"/>
-      <c r="L37" s="104"/>
-      <c r="M37" s="104"/>
-      <c r="N37" s="104"/>
-      <c r="O37" s="104"/>
-      <c r="P37" s="104"/>
-      <c r="Q37" s="104"/>
-    </row>
-    <row r="38" spans="3:17">
-      <c r="C38" s="105" t="s">
-        <v>613</v>
-      </c>
-      <c r="D38" s="104"/>
-      <c r="E38" s="104"/>
-      <c r="F38" s="104"/>
-      <c r="G38" s="104"/>
-      <c r="H38" s="104"/>
-      <c r="I38" s="104"/>
-      <c r="J38" s="104"/>
-      <c r="K38" s="104"/>
-      <c r="L38" s="104"/>
-      <c r="M38" s="104"/>
-      <c r="N38" s="104"/>
-      <c r="O38" s="104"/>
-      <c r="P38" s="104"/>
-      <c r="Q38" s="104"/>
-    </row>
-    <row r="39" spans="3:17">
-      <c r="C39" s="108"/>
-      <c r="D39" s="104"/>
-      <c r="E39" s="104"/>
-      <c r="F39" s="104"/>
-      <c r="G39" s="104"/>
-      <c r="H39" s="104"/>
-      <c r="I39" s="104"/>
-      <c r="J39" s="104"/>
-      <c r="K39" s="104"/>
-      <c r="L39" s="104"/>
-      <c r="M39" s="104"/>
-      <c r="N39" s="104"/>
-      <c r="O39" s="104"/>
-      <c r="P39" s="104"/>
-      <c r="Q39" s="104"/>
-    </row>
-    <row r="40" spans="3:17">
-      <c r="C40" s="103" t="s">
-        <v>746</v>
-      </c>
-      <c r="D40" s="104"/>
-      <c r="E40" s="104"/>
-      <c r="F40" s="104"/>
-      <c r="G40" s="104"/>
-      <c r="H40" s="104"/>
-      <c r="I40" s="104"/>
-      <c r="J40" s="104"/>
-      <c r="K40" s="104"/>
-      <c r="L40" s="104"/>
-      <c r="M40" s="104"/>
-      <c r="N40" s="104"/>
-      <c r="O40" s="104"/>
-      <c r="P40" s="104"/>
-      <c r="Q40" s="104"/>
-    </row>
-    <row r="41" spans="3:17">
-      <c r="C41" s="105" t="s">
-        <v>514</v>
-      </c>
-      <c r="D41" s="104"/>
-      <c r="E41" s="104"/>
-      <c r="F41" s="104"/>
-      <c r="G41" s="104"/>
-      <c r="H41" s="104"/>
-      <c r="I41" s="104"/>
-      <c r="J41" s="104"/>
-      <c r="K41" s="104"/>
-      <c r="L41" s="104"/>
-      <c r="M41" s="104"/>
-      <c r="N41" s="104"/>
-      <c r="O41" s="104"/>
-      <c r="P41" s="104"/>
-      <c r="Q41" s="104"/>
-    </row>
-    <row r="42" spans="3:17">
-      <c r="C42" s="103" t="s">
-        <v>728</v>
-      </c>
-      <c r="D42" s="104"/>
-      <c r="E42" s="104"/>
-      <c r="F42" s="104"/>
-      <c r="G42" s="104"/>
-      <c r="H42" s="104"/>
-      <c r="I42" s="104"/>
-      <c r="J42" s="104"/>
-      <c r="K42" s="104"/>
-      <c r="L42" s="104"/>
-      <c r="M42" s="104"/>
-      <c r="N42" s="104"/>
-      <c r="O42" s="104"/>
-      <c r="P42" s="104"/>
-      <c r="Q42" s="104"/>
-    </row>
-    <row r="43" spans="3:17">
-      <c r="C43" s="107" t="s">
-        <v>747</v>
-      </c>
-      <c r="D43" s="104"/>
-      <c r="E43" s="104"/>
-      <c r="F43" s="104"/>
-      <c r="G43" s="104"/>
-      <c r="H43" s="104"/>
-      <c r="I43" s="104"/>
-      <c r="J43" s="104"/>
-      <c r="K43" s="104"/>
-      <c r="L43" s="104"/>
-      <c r="M43" s="104"/>
-      <c r="N43" s="104"/>
-      <c r="O43" s="104"/>
-      <c r="P43" s="104"/>
-      <c r="Q43" s="104"/>
-    </row>
-    <row r="44" spans="3:17">
-      <c r="C44" s="107" t="s">
-        <v>748</v>
-      </c>
-      <c r="D44" s="104"/>
-      <c r="E44" s="104"/>
-      <c r="F44" s="104"/>
-      <c r="G44" s="104"/>
-      <c r="H44" s="104"/>
-      <c r="I44" s="104"/>
-      <c r="J44" s="104"/>
-      <c r="K44" s="104"/>
-      <c r="L44" s="104"/>
-      <c r="M44" s="104"/>
-      <c r="N44" s="104"/>
-      <c r="O44" s="104"/>
-      <c r="P44" s="104"/>
-      <c r="Q44" s="104"/>
-    </row>
-    <row r="45" spans="3:17">
-      <c r="C45" s="103" t="s">
-        <v>631</v>
-      </c>
-      <c r="D45" s="104"/>
-      <c r="E45" s="104"/>
-      <c r="F45" s="104"/>
-      <c r="G45" s="104"/>
-      <c r="H45" s="104"/>
-      <c r="I45" s="104"/>
-      <c r="J45" s="104"/>
-      <c r="K45" s="104"/>
-      <c r="L45" s="104"/>
-      <c r="M45" s="104"/>
-      <c r="N45" s="104"/>
-      <c r="O45" s="104"/>
-      <c r="P45" s="104"/>
-      <c r="Q45" s="104"/>
-    </row>
-    <row r="46" spans="3:17">
-      <c r="C46" s="103" t="s">
-        <v>749</v>
-      </c>
-      <c r="D46" s="104"/>
-      <c r="E46" s="104"/>
-      <c r="F46" s="104"/>
-      <c r="G46" s="104"/>
-      <c r="H46" s="104"/>
-      <c r="I46" s="104"/>
-      <c r="J46" s="104"/>
-      <c r="K46" s="104"/>
-      <c r="L46" s="104"/>
-      <c r="M46" s="104"/>
-      <c r="N46" s="104"/>
-      <c r="O46" s="104"/>
-      <c r="P46" s="104"/>
-      <c r="Q46" s="104"/>
-    </row>
-    <row r="47" spans="3:17">
-      <c r="C47" s="105" t="s">
-        <v>514</v>
-      </c>
-      <c r="D47" s="104"/>
-      <c r="E47" s="104"/>
-      <c r="F47" s="104"/>
-      <c r="G47" s="104"/>
-      <c r="H47" s="104"/>
-      <c r="I47" s="104"/>
-      <c r="J47" s="104"/>
-      <c r="K47" s="104"/>
-      <c r="L47" s="104"/>
-      <c r="M47" s="104"/>
-      <c r="N47" s="104"/>
-      <c r="O47" s="104"/>
-      <c r="P47" s="104"/>
-      <c r="Q47" s="104"/>
-    </row>
-    <row r="48" spans="3:17">
-      <c r="C48" s="121" t="s">
-        <v>750</v>
-      </c>
-      <c r="D48" s="104"/>
-      <c r="E48" s="104"/>
-      <c r="F48" s="104"/>
-      <c r="G48" s="104"/>
-      <c r="H48" s="104"/>
-      <c r="I48" s="104"/>
-      <c r="J48" s="104"/>
-      <c r="K48" s="104"/>
-      <c r="L48" s="104"/>
-      <c r="M48" s="104"/>
-      <c r="N48" s="104"/>
-      <c r="O48" s="104"/>
-      <c r="P48" s="104"/>
-      <c r="Q48" s="104"/>
-    </row>
-    <row r="49" spans="3:17">
-      <c r="C49" s="105" t="s">
-        <v>284</v>
-      </c>
-      <c r="D49" s="104"/>
-      <c r="E49" s="104"/>
-      <c r="F49" s="104"/>
-      <c r="G49" s="104"/>
-      <c r="H49" s="104"/>
-      <c r="I49" s="104"/>
-      <c r="J49" s="104"/>
-      <c r="K49" s="104"/>
-      <c r="L49" s="104"/>
-      <c r="M49" s="104"/>
-      <c r="N49" s="104"/>
-      <c r="O49" s="104"/>
-      <c r="P49" s="104"/>
-      <c r="Q49" s="104"/>
-    </row>
-    <row r="50" spans="3:17">
-      <c r="C50" s="103" t="s">
-        <v>751</v>
-      </c>
-      <c r="D50" s="104"/>
-      <c r="E50" s="104"/>
-      <c r="F50" s="104"/>
-      <c r="G50" s="104"/>
-      <c r="H50" s="104"/>
-      <c r="I50" s="104"/>
-      <c r="J50" s="104"/>
-      <c r="K50" s="104"/>
-      <c r="L50" s="104"/>
-      <c r="M50" s="104"/>
-      <c r="N50" s="104"/>
-      <c r="O50" s="104"/>
-      <c r="P50" s="104"/>
-      <c r="Q50" s="104"/>
-    </row>
-    <row r="51" spans="3:17">
-      <c r="C51" s="105" t="s">
-        <v>514</v>
-      </c>
-      <c r="D51" s="104"/>
-      <c r="E51" s="104"/>
-      <c r="F51" s="104"/>
-      <c r="G51" s="104"/>
-      <c r="H51" s="104"/>
-      <c r="I51" s="104"/>
-      <c r="J51" s="104"/>
-      <c r="K51" s="104"/>
-      <c r="L51" s="104"/>
-      <c r="M51" s="104"/>
-      <c r="N51" s="104"/>
-      <c r="O51" s="104"/>
-      <c r="P51" s="104"/>
-      <c r="Q51" s="104"/>
-    </row>
-    <row r="52" spans="3:17">
-      <c r="C52" s="121" t="s">
-        <v>752</v>
-      </c>
-      <c r="D52" s="104"/>
-      <c r="E52" s="104"/>
-      <c r="F52" s="104"/>
-      <c r="G52" s="104"/>
-      <c r="H52" s="104"/>
-      <c r="I52" s="104"/>
-      <c r="J52" s="104"/>
-      <c r="K52" s="104"/>
-      <c r="L52" s="104"/>
-      <c r="M52" s="104"/>
-      <c r="N52" s="104"/>
-      <c r="O52" s="104"/>
-      <c r="P52" s="104"/>
-      <c r="Q52" s="104"/>
-    </row>
-    <row r="53" spans="3:17">
-      <c r="C53" s="105" t="s">
-        <v>284</v>
-      </c>
-      <c r="D53" s="104"/>
-      <c r="E53" s="104"/>
-      <c r="F53" s="104"/>
-      <c r="G53" s="104"/>
-      <c r="H53" s="104"/>
-      <c r="I53" s="104"/>
-      <c r="J53" s="104"/>
-      <c r="K53" s="104"/>
-      <c r="L53" s="104"/>
-      <c r="M53" s="104"/>
-      <c r="N53" s="104"/>
-      <c r="O53" s="104"/>
-      <c r="P53" s="104"/>
-      <c r="Q53" s="104"/>
-    </row>
-    <row r="54" spans="3:17">
-      <c r="C54" s="103" t="s">
-        <v>753</v>
-      </c>
-      <c r="D54" s="104"/>
-      <c r="E54" s="104"/>
-      <c r="F54" s="104"/>
-      <c r="G54" s="104"/>
-      <c r="H54" s="104"/>
-      <c r="I54" s="104"/>
-      <c r="J54" s="104"/>
-      <c r="K54" s="104"/>
-      <c r="L54" s="104"/>
-      <c r="M54" s="104"/>
-      <c r="N54" s="104"/>
-      <c r="O54" s="104"/>
-      <c r="P54" s="104"/>
-      <c r="Q54" s="104"/>
-    </row>
-    <row r="55" spans="3:17">
-      <c r="C55" s="105" t="s">
-        <v>514</v>
-      </c>
-      <c r="D55" s="104"/>
-      <c r="E55" s="104"/>
-      <c r="F55" s="104"/>
-      <c r="G55" s="104"/>
-      <c r="H55" s="104"/>
-      <c r="I55" s="104"/>
-      <c r="J55" s="104"/>
-      <c r="K55" s="104"/>
-      <c r="L55" s="104"/>
-      <c r="M55" s="104"/>
-      <c r="N55" s="104"/>
-      <c r="O55" s="104"/>
-      <c r="P55" s="104"/>
-      <c r="Q55" s="104"/>
-    </row>
-    <row r="56" spans="3:17">
-      <c r="C56" s="105" t="s">
-        <v>754</v>
-      </c>
-      <c r="D56" s="104"/>
-      <c r="E56" s="104"/>
-      <c r="F56" s="104"/>
-      <c r="G56" s="104"/>
-      <c r="H56" s="104"/>
-      <c r="I56" s="104"/>
-      <c r="J56" s="104"/>
-      <c r="K56" s="104"/>
-      <c r="L56" s="104"/>
-      <c r="M56" s="104"/>
-      <c r="N56" s="104"/>
-      <c r="O56" s="104"/>
-      <c r="P56" s="104"/>
-      <c r="Q56" s="104"/>
-    </row>
-    <row r="57" spans="3:17">
-      <c r="C57" s="105" t="s">
-        <v>755</v>
-      </c>
-      <c r="D57" s="104"/>
-      <c r="E57" s="104"/>
-      <c r="F57" s="104"/>
-      <c r="G57" s="104"/>
-      <c r="H57" s="104"/>
-      <c r="I57" s="104"/>
-      <c r="J57" s="104"/>
-      <c r="K57" s="104"/>
-      <c r="L57" s="104"/>
-      <c r="M57" s="104"/>
-      <c r="N57" s="104"/>
-      <c r="O57" s="104"/>
-      <c r="P57" s="104"/>
-      <c r="Q57" s="104"/>
-    </row>
-    <row r="58" spans="3:17">
-      <c r="C58" s="105" t="s">
-        <v>756</v>
-      </c>
-      <c r="D58" s="104"/>
-      <c r="E58" s="104"/>
-      <c r="F58" s="104"/>
-      <c r="G58" s="104"/>
-      <c r="H58" s="104"/>
-      <c r="I58" s="104"/>
-      <c r="J58" s="104"/>
-      <c r="K58" s="104"/>
-      <c r="L58" s="104"/>
-      <c r="M58" s="104"/>
-      <c r="N58" s="104"/>
-      <c r="O58" s="104"/>
-      <c r="P58" s="104"/>
-      <c r="Q58" s="104"/>
-    </row>
-    <row r="59" spans="3:17">
-      <c r="C59" s="105" t="s">
-        <v>757</v>
-      </c>
-      <c r="D59" s="104"/>
-      <c r="E59" s="104"/>
-      <c r="F59" s="104"/>
-      <c r="G59" s="104"/>
-      <c r="H59" s="104"/>
-      <c r="I59" s="104"/>
-      <c r="J59" s="104"/>
-      <c r="K59" s="104"/>
-      <c r="L59" s="104"/>
-      <c r="M59" s="104"/>
-      <c r="N59" s="104"/>
-      <c r="O59" s="104"/>
-      <c r="P59" s="104"/>
-      <c r="Q59" s="104"/>
-    </row>
-    <row r="60" spans="3:17">
-      <c r="C60" s="105" t="s">
-        <v>284</v>
-      </c>
-      <c r="D60" s="104"/>
-      <c r="E60" s="104"/>
-      <c r="F60" s="104"/>
-      <c r="G60" s="104"/>
-      <c r="H60" s="104"/>
-      <c r="I60" s="104"/>
-      <c r="J60" s="104"/>
-      <c r="K60" s="104"/>
-      <c r="L60" s="104"/>
-      <c r="M60" s="104"/>
-      <c r="N60" s="104"/>
-      <c r="O60" s="104"/>
-      <c r="P60" s="104"/>
-      <c r="Q60" s="104"/>
-    </row>
-    <row r="61" spans="3:17">
-      <c r="C61" s="103" t="s">
-        <v>758</v>
-      </c>
-      <c r="D61" s="104"/>
-      <c r="E61" s="104"/>
-      <c r="F61" s="104"/>
-      <c r="G61" s="104"/>
-      <c r="H61" s="104"/>
-      <c r="I61" s="104"/>
-      <c r="J61" s="104"/>
-      <c r="K61" s="104"/>
-      <c r="L61" s="104"/>
-      <c r="M61" s="104"/>
-      <c r="N61" s="104"/>
-      <c r="O61" s="104"/>
-      <c r="P61" s="104"/>
-      <c r="Q61" s="104"/>
-    </row>
-    <row r="62" spans="3:17">
-      <c r="C62" s="105" t="s">
-        <v>514</v>
-      </c>
-      <c r="D62" s="104"/>
-      <c r="E62" s="104"/>
-      <c r="F62" s="104"/>
-      <c r="G62" s="104"/>
-      <c r="H62" s="104"/>
-      <c r="I62" s="104"/>
-      <c r="J62" s="104"/>
-      <c r="K62" s="104"/>
-      <c r="L62" s="104"/>
-      <c r="M62" s="104"/>
-      <c r="N62" s="104"/>
-      <c r="O62" s="104"/>
-      <c r="P62" s="104"/>
-      <c r="Q62" s="104"/>
-    </row>
-    <row r="63" spans="3:17">
-      <c r="C63" s="121" t="s">
-        <v>759</v>
-      </c>
-      <c r="D63" s="104"/>
-      <c r="E63" s="104"/>
-      <c r="F63" s="104"/>
-      <c r="G63" s="104"/>
-      <c r="H63" s="104"/>
-      <c r="I63" s="104"/>
-      <c r="J63" s="104"/>
-      <c r="K63" s="104"/>
-      <c r="L63" s="104"/>
-      <c r="M63" s="104"/>
-      <c r="N63" s="104"/>
-      <c r="O63" s="104"/>
-      <c r="P63" s="104"/>
-      <c r="Q63" s="104"/>
-    </row>
-    <row r="64" spans="3:17">
-      <c r="C64" s="106" t="s">
-        <v>760</v>
-      </c>
-      <c r="D64" s="104"/>
-      <c r="E64" s="104"/>
-      <c r="F64" s="104"/>
-      <c r="G64" s="104"/>
-      <c r="H64" s="104"/>
-      <c r="I64" s="104"/>
-      <c r="J64" s="104"/>
-      <c r="K64" s="104"/>
-      <c r="L64" s="104"/>
-      <c r="M64" s="104"/>
-      <c r="N64" s="104"/>
-      <c r="O64" s="104"/>
-      <c r="P64" s="104"/>
-      <c r="Q64" s="104"/>
-    </row>
-    <row r="65" spans="3:17">
-      <c r="C65" s="105" t="s">
-        <v>284</v>
-      </c>
-      <c r="D65" s="104"/>
-      <c r="E65" s="104"/>
-      <c r="F65" s="104"/>
-      <c r="G65" s="104"/>
-      <c r="H65" s="104"/>
-      <c r="I65" s="104"/>
-      <c r="J65" s="104"/>
-      <c r="K65" s="104"/>
-      <c r="L65" s="104"/>
-      <c r="M65" s="104"/>
-      <c r="N65" s="104"/>
-      <c r="O65" s="104"/>
-      <c r="P65" s="104"/>
-      <c r="Q65" s="104"/>
-    </row>
-    <row r="66" spans="3:17">
-      <c r="C66" s="105" t="s">
-        <v>613</v>
-      </c>
-      <c r="D66" s="104"/>
-      <c r="E66" s="104"/>
-      <c r="F66" s="104"/>
-      <c r="G66" s="104"/>
-      <c r="H66" s="104"/>
-      <c r="I66" s="104"/>
-      <c r="J66" s="104"/>
-      <c r="K66" s="104"/>
-      <c r="L66" s="104"/>
-      <c r="M66" s="104"/>
-      <c r="N66" s="104"/>
-      <c r="O66" s="104"/>
-      <c r="P66" s="104"/>
-      <c r="Q66" s="104"/>
-    </row>
-    <row r="67" spans="3:17">
-      <c r="C67" s="108"/>
-      <c r="D67" s="104"/>
-      <c r="E67" s="104"/>
-      <c r="F67" s="104"/>
-      <c r="G67" s="104"/>
-      <c r="H67" s="104"/>
-      <c r="I67" s="104"/>
-      <c r="J67" s="104"/>
-      <c r="K67" s="104"/>
-      <c r="L67" s="104"/>
-      <c r="M67" s="104"/>
-      <c r="N67" s="104"/>
-      <c r="O67" s="104"/>
-      <c r="P67" s="104"/>
-      <c r="Q67" s="104"/>
-    </row>
-    <row r="68" spans="3:17">
-      <c r="C68" s="103" t="s">
-        <v>761</v>
-      </c>
-      <c r="D68" s="104"/>
-      <c r="E68" s="104"/>
-      <c r="F68" s="104"/>
-      <c r="G68" s="104"/>
-      <c r="H68" s="104"/>
-      <c r="I68" s="104"/>
-      <c r="J68" s="104"/>
-      <c r="K68" s="104"/>
-      <c r="L68" s="104"/>
-      <c r="M68" s="104"/>
-      <c r="N68" s="104"/>
-      <c r="O68" s="104"/>
-      <c r="P68" s="104"/>
-      <c r="Q68" s="104"/>
-    </row>
-    <row r="69" spans="3:17">
-      <c r="C69" s="105" t="s">
-        <v>514</v>
-      </c>
-      <c r="D69" s="104"/>
-      <c r="E69" s="104"/>
-      <c r="F69" s="104"/>
-      <c r="G69" s="104"/>
-      <c r="H69" s="104"/>
-      <c r="I69" s="104"/>
-      <c r="J69" s="104"/>
-      <c r="K69" s="104"/>
-      <c r="L69" s="104"/>
-      <c r="M69" s="104"/>
-      <c r="N69" s="104"/>
-      <c r="O69" s="104"/>
-      <c r="P69" s="104"/>
-      <c r="Q69" s="104"/>
-    </row>
-    <row r="70" spans="3:17">
-      <c r="C70" s="103" t="s">
-        <v>728</v>
-      </c>
-      <c r="D70" s="104"/>
-      <c r="E70" s="104"/>
-      <c r="F70" s="104"/>
-      <c r="G70" s="104"/>
-      <c r="H70" s="104"/>
-      <c r="I70" s="104"/>
-      <c r="J70" s="104"/>
-      <c r="K70" s="104"/>
-      <c r="L70" s="104"/>
-      <c r="M70" s="104"/>
-      <c r="N70" s="104"/>
-      <c r="O70" s="104"/>
-      <c r="P70" s="104"/>
-      <c r="Q70" s="104"/>
-    </row>
-    <row r="71" spans="3:17">
-      <c r="C71" s="107" t="s">
-        <v>762</v>
-      </c>
-      <c r="D71" s="104"/>
-      <c r="E71" s="104"/>
-      <c r="F71" s="104"/>
-      <c r="G71" s="104"/>
-      <c r="H71" s="104"/>
-      <c r="I71" s="104"/>
-      <c r="J71" s="104"/>
-      <c r="K71" s="104"/>
-      <c r="L71" s="104"/>
-      <c r="M71" s="104"/>
-      <c r="N71" s="104"/>
-      <c r="O71" s="104"/>
-      <c r="P71" s="104"/>
-      <c r="Q71" s="104"/>
-    </row>
-    <row r="72" spans="3:17">
-      <c r="C72" s="107" t="s">
-        <v>763</v>
-      </c>
-      <c r="D72" s="104"/>
-      <c r="E72" s="104"/>
-      <c r="F72" s="104"/>
-      <c r="G72" s="104"/>
-      <c r="H72" s="104"/>
-      <c r="I72" s="104"/>
-      <c r="J72" s="104"/>
-      <c r="K72" s="104"/>
-      <c r="L72" s="104"/>
-      <c r="M72" s="104"/>
-      <c r="N72" s="104"/>
-      <c r="O72" s="104"/>
-      <c r="P72" s="104"/>
-      <c r="Q72" s="104"/>
-    </row>
-    <row r="73" spans="3:17">
-      <c r="C73" s="103" t="s">
-        <v>631</v>
-      </c>
-      <c r="D73" s="104"/>
-      <c r="E73" s="104"/>
-      <c r="F73" s="104"/>
-      <c r="G73" s="104"/>
-      <c r="H73" s="104"/>
-      <c r="I73" s="104"/>
-      <c r="J73" s="104"/>
-      <c r="K73" s="104"/>
-      <c r="L73" s="104"/>
-      <c r="M73" s="104"/>
-      <c r="N73" s="104"/>
-      <c r="O73" s="104"/>
-      <c r="P73" s="104"/>
-      <c r="Q73" s="104"/>
-    </row>
-    <row r="74" spans="3:17">
-      <c r="C74" s="106" t="s">
-        <v>764</v>
-      </c>
-      <c r="D74" s="104"/>
-      <c r="E74" s="104"/>
-      <c r="F74" s="104"/>
-      <c r="G74" s="104"/>
-      <c r="H74" s="104"/>
-      <c r="I74" s="104"/>
-      <c r="J74" s="104"/>
-      <c r="K74" s="104"/>
-      <c r="L74" s="104"/>
-      <c r="M74" s="104"/>
-      <c r="N74" s="104"/>
-      <c r="O74" s="104"/>
-      <c r="P74" s="104"/>
-      <c r="Q74" s="104"/>
-    </row>
-    <row r="75" spans="3:17">
-      <c r="C75" s="105" t="s">
-        <v>514</v>
-      </c>
-      <c r="D75" s="104"/>
-      <c r="E75" s="104"/>
-      <c r="F75" s="104"/>
-      <c r="G75" s="104"/>
-      <c r="H75" s="104"/>
-      <c r="I75" s="104"/>
-      <c r="J75" s="104"/>
-      <c r="K75" s="104"/>
-      <c r="L75" s="104"/>
-      <c r="M75" s="104"/>
-      <c r="N75" s="104"/>
-      <c r="O75" s="104"/>
-      <c r="P75" s="104"/>
-      <c r="Q75" s="104"/>
-    </row>
-    <row r="76" spans="3:17">
-      <c r="C76" s="121" t="s">
-        <v>765</v>
-      </c>
-      <c r="D76" s="104"/>
-      <c r="E76" s="104"/>
-      <c r="F76" s="104"/>
-      <c r="G76" s="104"/>
-      <c r="H76" s="104"/>
-      <c r="I76" s="104"/>
-      <c r="J76" s="104"/>
-      <c r="K76" s="104"/>
-      <c r="L76" s="104"/>
-      <c r="M76" s="104"/>
-      <c r="N76" s="104"/>
-      <c r="O76" s="104"/>
-      <c r="P76" s="104"/>
-      <c r="Q76" s="104"/>
-    </row>
-    <row r="77" spans="3:17">
-      <c r="C77" s="105" t="s">
-        <v>284</v>
-      </c>
-      <c r="D77" s="104"/>
-      <c r="E77" s="104"/>
-      <c r="F77" s="104"/>
-      <c r="G77" s="104"/>
-      <c r="H77" s="104"/>
-      <c r="I77" s="104"/>
-      <c r="J77" s="104"/>
-      <c r="K77" s="104"/>
-      <c r="L77" s="104"/>
-      <c r="M77" s="104"/>
-      <c r="N77" s="104"/>
-      <c r="O77" s="104"/>
-      <c r="P77" s="104"/>
-      <c r="Q77" s="104"/>
-    </row>
-    <row r="78" spans="3:17">
-      <c r="C78" s="108"/>
-      <c r="D78" s="104"/>
-      <c r="E78" s="104"/>
-      <c r="F78" s="104"/>
-      <c r="G78" s="104"/>
-      <c r="H78" s="104"/>
-      <c r="I78" s="104"/>
-      <c r="J78" s="104"/>
-      <c r="K78" s="104"/>
-      <c r="L78" s="104"/>
-      <c r="M78" s="104"/>
-      <c r="N78" s="104"/>
-      <c r="O78" s="104"/>
-      <c r="P78" s="104"/>
-      <c r="Q78" s="104"/>
-    </row>
-    <row r="79" spans="3:17">
-      <c r="C79" s="103" t="s">
-        <v>766</v>
-      </c>
-      <c r="D79" s="104"/>
-      <c r="E79" s="104"/>
-      <c r="F79" s="104"/>
-      <c r="G79" s="104"/>
-      <c r="H79" s="104"/>
-      <c r="I79" s="104"/>
-      <c r="J79" s="104"/>
-      <c r="K79" s="104"/>
-      <c r="L79" s="104"/>
-      <c r="M79" s="104"/>
-      <c r="N79" s="104"/>
-      <c r="O79" s="104"/>
-      <c r="P79" s="104"/>
-      <c r="Q79" s="104"/>
-    </row>
-    <row r="80" spans="3:17">
-      <c r="C80" s="105" t="s">
-        <v>514</v>
-      </c>
-      <c r="D80" s="104"/>
-      <c r="E80" s="104"/>
-      <c r="F80" s="104"/>
-      <c r="G80" s="104"/>
-      <c r="H80" s="104"/>
-      <c r="I80" s="104"/>
-      <c r="J80" s="104"/>
-      <c r="K80" s="104"/>
-      <c r="L80" s="104"/>
-      <c r="M80" s="104"/>
-      <c r="N80" s="104"/>
-      <c r="O80" s="104"/>
-      <c r="P80" s="104"/>
-      <c r="Q80" s="104"/>
-    </row>
-    <row r="81" spans="3:17">
-      <c r="C81" s="121" t="s">
-        <v>767</v>
-      </c>
-      <c r="D81" s="104"/>
-      <c r="E81" s="104"/>
-      <c r="F81" s="104"/>
-      <c r="G81" s="104"/>
-      <c r="H81" s="104"/>
-      <c r="I81" s="104"/>
-      <c r="J81" s="104"/>
-      <c r="K81" s="104"/>
-      <c r="L81" s="104"/>
-      <c r="M81" s="104"/>
-      <c r="N81" s="104"/>
-      <c r="O81" s="104"/>
-      <c r="P81" s="104"/>
-      <c r="Q81" s="104"/>
-    </row>
-    <row r="82" spans="3:17">
-      <c r="C82" s="107" t="s">
-        <v>768</v>
-      </c>
-      <c r="D82" s="104"/>
-      <c r="E82" s="104"/>
-      <c r="F82" s="104"/>
-      <c r="G82" s="104"/>
-      <c r="H82" s="104"/>
-      <c r="I82" s="104"/>
-      <c r="J82" s="104"/>
-      <c r="K82" s="104"/>
-      <c r="L82" s="104"/>
-      <c r="M82" s="104"/>
-      <c r="N82" s="104"/>
-      <c r="O82" s="104"/>
-      <c r="P82" s="104"/>
-      <c r="Q82" s="104"/>
-    </row>
-    <row r="83" spans="3:17">
-      <c r="C83" s="105" t="s">
-        <v>284</v>
-      </c>
-      <c r="D83" s="104"/>
-      <c r="E83" s="104"/>
-      <c r="F83" s="104"/>
-      <c r="G83" s="104"/>
-      <c r="H83" s="104"/>
-      <c r="I83" s="104"/>
-      <c r="J83" s="104"/>
-      <c r="K83" s="104"/>
-      <c r="L83" s="104"/>
-      <c r="M83" s="104"/>
-      <c r="N83" s="104"/>
-      <c r="O83" s="104"/>
-      <c r="P83" s="104"/>
-      <c r="Q83" s="104"/>
-    </row>
-    <row r="84" spans="3:17">
-      <c r="C84" s="108"/>
-      <c r="D84" s="104"/>
-      <c r="E84" s="104"/>
-      <c r="F84" s="104"/>
-      <c r="G84" s="104"/>
-      <c r="H84" s="104"/>
-      <c r="I84" s="104"/>
-      <c r="J84" s="104"/>
-      <c r="K84" s="104"/>
-      <c r="L84" s="104"/>
-      <c r="M84" s="104"/>
-      <c r="N84" s="104"/>
-      <c r="O84" s="104"/>
-      <c r="P84" s="104"/>
-      <c r="Q84" s="104"/>
-    </row>
-    <row r="85" spans="3:17">
-      <c r="C85" s="103" t="s">
-        <v>769</v>
-      </c>
-      <c r="D85" s="104"/>
-      <c r="E85" s="104"/>
-      <c r="F85" s="104"/>
-      <c r="G85" s="104"/>
-      <c r="H85" s="104"/>
-      <c r="I85" s="104"/>
-      <c r="J85" s="104"/>
-      <c r="K85" s="104"/>
-      <c r="L85" s="104"/>
-      <c r="M85" s="104"/>
-      <c r="N85" s="104"/>
-      <c r="O85" s="104"/>
-      <c r="P85" s="104"/>
-      <c r="Q85" s="104"/>
-    </row>
-    <row r="86" spans="3:17">
-      <c r="C86" s="105" t="s">
-        <v>514</v>
-      </c>
-      <c r="D86" s="104"/>
-      <c r="E86" s="104"/>
-      <c r="F86" s="104"/>
-      <c r="G86" s="104"/>
-      <c r="H86" s="104"/>
-      <c r="I86" s="104"/>
-      <c r="J86" s="104"/>
-      <c r="K86" s="104"/>
-      <c r="L86" s="104"/>
-      <c r="M86" s="104"/>
-      <c r="N86" s="104"/>
-      <c r="O86" s="104"/>
-      <c r="P86" s="104"/>
-      <c r="Q86" s="104"/>
-    </row>
-    <row r="87" spans="3:17">
-      <c r="C87" s="107" t="s">
-        <v>770</v>
-      </c>
-      <c r="D87" s="104"/>
-      <c r="E87" s="104"/>
-      <c r="F87" s="104"/>
-      <c r="G87" s="104"/>
-      <c r="H87" s="104"/>
-      <c r="I87" s="104"/>
-      <c r="J87" s="104"/>
-      <c r="K87" s="104"/>
-      <c r="L87" s="104"/>
-      <c r="M87" s="104"/>
-      <c r="N87" s="104"/>
-      <c r="O87" s="104"/>
-      <c r="P87" s="104"/>
-      <c r="Q87" s="104"/>
-    </row>
-    <row r="88" spans="3:17">
-      <c r="C88" s="105" t="s">
-        <v>284</v>
-      </c>
-      <c r="D88" s="104"/>
-      <c r="E88" s="104"/>
-      <c r="F88" s="104"/>
-      <c r="G88" s="104"/>
-      <c r="H88" s="104"/>
-      <c r="I88" s="104"/>
-      <c r="J88" s="104"/>
-      <c r="K88" s="104"/>
-      <c r="L88" s="104"/>
-      <c r="M88" s="104"/>
-      <c r="N88" s="104"/>
-      <c r="O88" s="104"/>
-      <c r="P88" s="104"/>
-      <c r="Q88" s="104"/>
-    </row>
-    <row r="89" spans="3:17">
-      <c r="C89" s="108"/>
-      <c r="D89" s="104"/>
-      <c r="E89" s="104"/>
-      <c r="F89" s="104"/>
-      <c r="G89" s="104"/>
-      <c r="H89" s="104"/>
-      <c r="I89" s="104"/>
-      <c r="J89" s="104"/>
-      <c r="K89" s="104"/>
-      <c r="L89" s="104"/>
-      <c r="M89" s="104"/>
-      <c r="N89" s="104"/>
-      <c r="O89" s="104"/>
-      <c r="P89" s="104"/>
-      <c r="Q89" s="104"/>
-    </row>
-    <row r="90" spans="3:17">
-      <c r="C90" s="105" t="s">
-        <v>613</v>
-      </c>
-      <c r="D90" s="104"/>
-      <c r="E90" s="104"/>
-      <c r="F90" s="104"/>
-      <c r="G90" s="104"/>
-      <c r="H90" s="104"/>
-      <c r="I90" s="104"/>
-      <c r="J90" s="104"/>
-      <c r="K90" s="104"/>
-      <c r="L90" s="104"/>
-      <c r="M90" s="104"/>
-      <c r="N90" s="104"/>
-      <c r="O90" s="104"/>
-      <c r="P90" s="104"/>
-      <c r="Q90" s="104"/>
-    </row>
-    <row r="91" spans="3:17">
-      <c r="C91" s="108"/>
-      <c r="D91" s="104"/>
-      <c r="E91" s="104"/>
-      <c r="F91" s="104"/>
-      <c r="G91" s="104"/>
-      <c r="H91" s="104"/>
-      <c r="I91" s="104"/>
-      <c r="J91" s="104"/>
-      <c r="K91" s="104"/>
-      <c r="L91" s="104"/>
-      <c r="M91" s="104"/>
-      <c r="N91" s="104"/>
-      <c r="O91" s="104"/>
-      <c r="P91" s="104"/>
-      <c r="Q91" s="104"/>
-    </row>
-    <row r="92" spans="3:17">
-      <c r="C92" s="103" t="s">
-        <v>732</v>
-      </c>
-      <c r="D92" s="104"/>
-      <c r="E92" s="104"/>
-      <c r="F92" s="104"/>
-      <c r="G92" s="104"/>
-      <c r="H92" s="104"/>
-      <c r="I92" s="104"/>
-      <c r="J92" s="104"/>
-      <c r="K92" s="104"/>
-      <c r="L92" s="104"/>
-      <c r="M92" s="104"/>
-      <c r="N92" s="104"/>
-      <c r="O92" s="104"/>
-      <c r="P92" s="104"/>
-      <c r="Q92" s="104"/>
-    </row>
-    <row r="93" spans="3:17">
-      <c r="C93" s="105" t="s">
-        <v>514</v>
-      </c>
-      <c r="D93" s="104"/>
-      <c r="E93" s="104"/>
-      <c r="F93" s="104"/>
-      <c r="G93" s="104"/>
-      <c r="H93" s="104"/>
-      <c r="I93" s="104"/>
-      <c r="J93" s="104"/>
-      <c r="K93" s="104"/>
-      <c r="L93" s="104"/>
-      <c r="M93" s="104"/>
-      <c r="N93" s="104"/>
-      <c r="O93" s="104"/>
-      <c r="P93" s="104"/>
-      <c r="Q93" s="104"/>
-    </row>
-    <row r="94" spans="3:17">
-      <c r="C94" s="107" t="s">
-        <v>771</v>
-      </c>
-      <c r="D94" s="104"/>
-      <c r="E94" s="104"/>
-      <c r="F94" s="104"/>
-      <c r="G94" s="104"/>
-      <c r="H94" s="104"/>
-      <c r="I94" s="104"/>
-      <c r="J94" s="104"/>
-      <c r="K94" s="104"/>
-      <c r="L94" s="104"/>
-      <c r="M94" s="104"/>
-      <c r="N94" s="104"/>
-      <c r="O94" s="104"/>
-      <c r="P94" s="104"/>
-      <c r="Q94" s="104"/>
-    </row>
-    <row r="95" spans="3:17">
-      <c r="C95" s="107" t="s">
-        <v>772</v>
-      </c>
-      <c r="D95" s="104"/>
-      <c r="E95" s="104"/>
-      <c r="F95" s="104"/>
-      <c r="G95" s="104"/>
-      <c r="H95" s="104"/>
-      <c r="I95" s="104"/>
-      <c r="J95" s="104"/>
-      <c r="K95" s="104"/>
-      <c r="L95" s="104"/>
-      <c r="M95" s="104"/>
-      <c r="N95" s="104"/>
-      <c r="O95" s="104"/>
-      <c r="P95" s="104"/>
-      <c r="Q95" s="104"/>
-    </row>
-    <row r="96" spans="3:17">
-      <c r="C96" s="107" t="s">
-        <v>773</v>
-      </c>
-      <c r="D96" s="104"/>
-      <c r="E96" s="104"/>
-      <c r="F96" s="104"/>
-      <c r="G96" s="104"/>
-      <c r="H96" s="104"/>
-      <c r="I96" s="104"/>
-      <c r="J96" s="104"/>
-      <c r="K96" s="104"/>
-      <c r="L96" s="104"/>
-      <c r="M96" s="104"/>
-      <c r="N96" s="104"/>
-      <c r="O96" s="104"/>
-      <c r="P96" s="104"/>
-      <c r="Q96" s="104"/>
-    </row>
-    <row r="97" spans="3:17">
-      <c r="C97" s="107" t="s">
-        <v>774</v>
-      </c>
-      <c r="D97" s="104"/>
-      <c r="E97" s="104"/>
-      <c r="F97" s="104"/>
-      <c r="G97" s="104"/>
-      <c r="H97" s="104"/>
-      <c r="I97" s="104"/>
-      <c r="J97" s="104"/>
-      <c r="K97" s="104"/>
-      <c r="L97" s="104"/>
-      <c r="M97" s="104"/>
-      <c r="N97" s="104"/>
-      <c r="O97" s="104"/>
-      <c r="P97" s="104"/>
-      <c r="Q97" s="104"/>
-    </row>
-    <row r="98" spans="3:17">
-      <c r="C98" s="108"/>
-      <c r="D98" s="104"/>
-      <c r="E98" s="104"/>
-      <c r="F98" s="104"/>
-      <c r="G98" s="104"/>
-      <c r="H98" s="104"/>
-      <c r="I98" s="104"/>
-      <c r="J98" s="104"/>
-      <c r="K98" s="104"/>
-      <c r="L98" s="104"/>
-      <c r="M98" s="104"/>
-      <c r="N98" s="104"/>
-      <c r="O98" s="104"/>
-      <c r="P98" s="104"/>
-      <c r="Q98" s="104"/>
-    </row>
-    <row r="99" spans="3:17">
-      <c r="C99" s="121" t="s">
-        <v>775</v>
-      </c>
-      <c r="D99" s="104"/>
-      <c r="E99" s="104"/>
-      <c r="F99" s="104"/>
-      <c r="G99" s="104"/>
-      <c r="H99" s="104"/>
-      <c r="I99" s="104"/>
-      <c r="J99" s="104"/>
-      <c r="K99" s="104"/>
-      <c r="L99" s="104"/>
-      <c r="M99" s="104"/>
-      <c r="N99" s="104"/>
-      <c r="O99" s="104"/>
-      <c r="P99" s="104"/>
-      <c r="Q99" s="104"/>
-    </row>
-    <row r="100" spans="3:17">
-      <c r="C100" s="121" t="s">
-        <v>776</v>
-      </c>
-      <c r="D100" s="104"/>
-      <c r="E100" s="104"/>
-      <c r="F100" s="104"/>
-      <c r="G100" s="104"/>
-      <c r="H100" s="104"/>
-      <c r="I100" s="104"/>
-      <c r="J100" s="104"/>
-      <c r="K100" s="104"/>
-      <c r="L100" s="104"/>
-      <c r="M100" s="104"/>
-      <c r="N100" s="104"/>
-      <c r="O100" s="104"/>
-      <c r="P100" s="104"/>
-      <c r="Q100" s="104"/>
-    </row>
-    <row r="101" spans="3:17">
-      <c r="C101" s="108"/>
-      <c r="D101" s="104"/>
-      <c r="E101" s="104"/>
-      <c r="F101" s="104"/>
-      <c r="G101" s="104"/>
-      <c r="H101" s="104"/>
-      <c r="I101" s="104"/>
-      <c r="J101" s="104"/>
-      <c r="K101" s="104"/>
-      <c r="L101" s="104"/>
-      <c r="M101" s="104"/>
-      <c r="N101" s="104"/>
-      <c r="O101" s="104"/>
-      <c r="P101" s="104"/>
-      <c r="Q101" s="104"/>
-    </row>
-    <row r="102" spans="3:17">
-      <c r="C102" s="121" t="s">
-        <v>777</v>
-      </c>
-      <c r="D102" s="104"/>
-      <c r="E102" s="104"/>
-      <c r="F102" s="104"/>
-      <c r="G102" s="104"/>
-      <c r="H102" s="104"/>
-      <c r="I102" s="104"/>
-      <c r="J102" s="104"/>
-      <c r="K102" s="104"/>
-      <c r="L102" s="104"/>
-      <c r="M102" s="104"/>
-      <c r="N102" s="104"/>
-      <c r="O102" s="104"/>
-      <c r="P102" s="104"/>
-      <c r="Q102" s="104"/>
-    </row>
-    <row r="103" spans="3:17">
-      <c r="C103" s="121" t="s">
-        <v>778</v>
-      </c>
-      <c r="D103" s="104"/>
-      <c r="E103" s="104"/>
-      <c r="F103" s="104"/>
-      <c r="G103" s="104"/>
-      <c r="H103" s="104"/>
-      <c r="I103" s="104"/>
-      <c r="J103" s="104"/>
-      <c r="K103" s="104"/>
-      <c r="L103" s="104"/>
-      <c r="M103" s="104"/>
-      <c r="N103" s="104"/>
-      <c r="O103" s="104"/>
-      <c r="P103" s="104"/>
-      <c r="Q103" s="104"/>
-    </row>
-    <row r="104" spans="3:17">
-      <c r="C104" s="108"/>
-      <c r="D104" s="104"/>
-      <c r="E104" s="104"/>
-      <c r="F104" s="104"/>
-      <c r="G104" s="104"/>
-      <c r="H104" s="104"/>
-      <c r="I104" s="104"/>
-      <c r="J104" s="104"/>
-      <c r="K104" s="104"/>
-      <c r="L104" s="104"/>
-      <c r="M104" s="104"/>
-      <c r="N104" s="104"/>
-      <c r="O104" s="104"/>
-      <c r="P104" s="104"/>
-      <c r="Q104" s="104"/>
-    </row>
-    <row r="105" spans="3:17">
-      <c r="C105" s="121" t="s">
-        <v>779</v>
-      </c>
-      <c r="D105" s="104"/>
-      <c r="E105" s="104"/>
-      <c r="F105" s="104"/>
-      <c r="G105" s="104"/>
-      <c r="H105" s="104"/>
-      <c r="I105" s="104"/>
-      <c r="J105" s="104"/>
-      <c r="K105" s="104"/>
-      <c r="L105" s="104"/>
-      <c r="M105" s="104"/>
-      <c r="N105" s="104"/>
-      <c r="O105" s="104"/>
-      <c r="P105" s="104"/>
-      <c r="Q105" s="104"/>
-    </row>
-    <row r="106" spans="3:17">
-      <c r="C106" s="108"/>
-      <c r="D106" s="104"/>
-      <c r="E106" s="104"/>
-      <c r="F106" s="104"/>
-      <c r="G106" s="104"/>
-      <c r="H106" s="104"/>
-      <c r="I106" s="104"/>
-      <c r="J106" s="104"/>
-      <c r="K106" s="104"/>
-      <c r="L106" s="104"/>
-      <c r="M106" s="104"/>
-      <c r="N106" s="104"/>
-      <c r="O106" s="104"/>
-      <c r="P106" s="104"/>
-      <c r="Q106" s="104"/>
-    </row>
-    <row r="107" spans="3:17">
-      <c r="C107" s="109" t="s">
-        <v>735</v>
-      </c>
-      <c r="D107" s="104"/>
-      <c r="E107" s="104"/>
-      <c r="F107" s="104"/>
-      <c r="G107" s="104"/>
-      <c r="H107" s="104"/>
-      <c r="I107" s="104"/>
-      <c r="J107" s="104"/>
-      <c r="K107" s="104"/>
-      <c r="L107" s="104"/>
-      <c r="M107" s="104"/>
-      <c r="N107" s="104"/>
-      <c r="O107" s="104"/>
-      <c r="P107" s="104"/>
-      <c r="Q107" s="104"/>
-    </row>
-    <row r="108" spans="3:17">
-      <c r="C108" s="105" t="s">
-        <v>284</v>
-      </c>
-      <c r="D108" s="104"/>
-      <c r="E108" s="104"/>
-      <c r="F108" s="104"/>
-      <c r="G108" s="104"/>
-      <c r="H108" s="104"/>
-      <c r="I108" s="104"/>
-      <c r="J108" s="104"/>
-      <c r="K108" s="104"/>
-      <c r="L108" s="104"/>
-      <c r="M108" s="104"/>
-      <c r="N108" s="104"/>
-      <c r="O108" s="104"/>
-      <c r="P108" s="104"/>
-      <c r="Q108" s="104"/>
+    <row r="2" spans="2:4">
+      <c r="B2" s="6" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4">
+      <c r="C3" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="C4" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
+      <c r="C6" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4">
+      <c r="C7" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="D8" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4">
+      <c r="D9" t="s">
+        <v>808</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -20972,35 +19352,1999 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:Q108"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2" spans="2:10">
+      <c r="B2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10">
+      <c r="C3" s="103" t="s">
+        <v>721</v>
+      </c>
+      <c r="D3" s="104"/>
+      <c r="E3" s="104"/>
+      <c r="F3" s="104"/>
+      <c r="G3" s="104"/>
+      <c r="H3" s="104"/>
+      <c r="I3" s="104"/>
+      <c r="J3" s="104"/>
+    </row>
+    <row r="4" spans="2:10">
+      <c r="C4" s="105" t="s">
+        <v>511</v>
+      </c>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
+      <c r="F4" s="104"/>
+      <c r="G4" s="104"/>
+      <c r="H4" s="104"/>
+      <c r="I4" s="104"/>
+      <c r="J4" s="104"/>
+    </row>
+    <row r="5" spans="2:10">
+      <c r="C5" s="103" t="s">
+        <v>628</v>
+      </c>
+      <c r="D5" s="104"/>
+      <c r="E5" s="104"/>
+      <c r="F5" s="104"/>
+      <c r="G5" s="104"/>
+      <c r="H5" s="104"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="104"/>
+    </row>
+    <row r="6" spans="2:10">
+      <c r="C6" s="103" t="s">
+        <v>722</v>
+      </c>
+      <c r="D6" s="104"/>
+      <c r="E6" s="104"/>
+      <c r="F6" s="104"/>
+      <c r="G6" s="104"/>
+      <c r="H6" s="104"/>
+      <c r="I6" s="104"/>
+      <c r="J6" s="104"/>
+    </row>
+    <row r="7" spans="2:10">
+      <c r="C7" s="105" t="s">
+        <v>511</v>
+      </c>
+      <c r="D7" s="104"/>
+      <c r="E7" s="104"/>
+      <c r="F7" s="104"/>
+      <c r="G7" s="104"/>
+      <c r="H7" s="104"/>
+      <c r="I7" s="104"/>
+      <c r="J7" s="104"/>
+    </row>
+    <row r="8" spans="2:10">
+      <c r="C8" s="105" t="s">
+        <v>723</v>
+      </c>
+      <c r="D8" s="104"/>
+      <c r="E8" s="104"/>
+      <c r="F8" s="104"/>
+      <c r="G8" s="104"/>
+      <c r="H8" s="104"/>
+      <c r="I8" s="104"/>
+      <c r="J8" s="104"/>
+    </row>
+    <row r="9" spans="2:10">
+      <c r="C9" s="105" t="s">
+        <v>724</v>
+      </c>
+      <c r="D9" s="104"/>
+      <c r="E9" s="104"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="104"/>
+      <c r="H9" s="104"/>
+      <c r="I9" s="104"/>
+      <c r="J9" s="104"/>
+    </row>
+    <row r="10" spans="2:10">
+      <c r="C10" s="105" t="s">
+        <v>284</v>
+      </c>
+      <c r="D10" s="104"/>
+      <c r="E10" s="104"/>
+      <c r="F10" s="104"/>
+      <c r="G10" s="104"/>
+      <c r="H10" s="104"/>
+      <c r="I10" s="104"/>
+      <c r="J10" s="104"/>
+    </row>
+    <row r="11" spans="2:10">
+      <c r="C11" s="103" t="s">
+        <v>725</v>
+      </c>
+      <c r="D11" s="104"/>
+      <c r="E11" s="104"/>
+      <c r="F11" s="104"/>
+      <c r="G11" s="104"/>
+      <c r="H11" s="104"/>
+      <c r="I11" s="104"/>
+      <c r="J11" s="104"/>
+    </row>
+    <row r="12" spans="2:10">
+      <c r="C12" s="106" t="s">
+        <v>726</v>
+      </c>
+      <c r="D12" s="104"/>
+      <c r="E12" s="104"/>
+      <c r="F12" s="104"/>
+      <c r="G12" s="104"/>
+      <c r="H12" s="104"/>
+      <c r="I12" s="104"/>
+      <c r="J12" s="104"/>
+    </row>
+    <row r="13" spans="2:10">
+      <c r="C13" s="106" t="s">
+        <v>727</v>
+      </c>
+      <c r="D13" s="104"/>
+      <c r="E13" s="104"/>
+      <c r="F13" s="104"/>
+      <c r="G13" s="104"/>
+      <c r="H13" s="104"/>
+      <c r="I13" s="104"/>
+      <c r="J13" s="104"/>
+    </row>
+    <row r="14" spans="2:10">
+      <c r="C14" s="107" t="s">
+        <v>728</v>
+      </c>
+      <c r="D14" s="104"/>
+      <c r="E14" s="104"/>
+      <c r="F14" s="104"/>
+      <c r="G14" s="104"/>
+      <c r="H14" s="104"/>
+      <c r="I14" s="104"/>
+      <c r="J14" s="104"/>
+    </row>
+    <row r="15" spans="2:10">
+      <c r="C15" s="105" t="s">
+        <v>610</v>
+      </c>
+      <c r="D15" s="104"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="104"/>
+      <c r="G15" s="104"/>
+      <c r="H15" s="104"/>
+      <c r="I15" s="104"/>
+      <c r="J15" s="104"/>
+    </row>
+    <row r="16" spans="2:10">
+      <c r="C16" s="108"/>
+      <c r="D16" s="104"/>
+      <c r="E16" s="104"/>
+      <c r="F16" s="104"/>
+      <c r="G16" s="104"/>
+      <c r="H16" s="104"/>
+      <c r="I16" s="104"/>
+      <c r="J16" s="104"/>
+    </row>
+    <row r="17" spans="2:17">
+      <c r="C17" s="103" t="s">
+        <v>729</v>
+      </c>
+      <c r="D17" s="104"/>
+      <c r="E17" s="104"/>
+      <c r="F17" s="104"/>
+      <c r="G17" s="104"/>
+      <c r="H17" s="104"/>
+      <c r="I17" s="104"/>
+      <c r="J17" s="104"/>
+    </row>
+    <row r="18" spans="2:17">
+      <c r="C18" s="105" t="s">
+        <v>511</v>
+      </c>
+      <c r="D18" s="104"/>
+      <c r="E18" s="104"/>
+      <c r="F18" s="104"/>
+      <c r="G18" s="104"/>
+      <c r="H18" s="104"/>
+      <c r="I18" s="104"/>
+      <c r="J18" s="104"/>
+    </row>
+    <row r="19" spans="2:17">
+      <c r="C19" s="107" t="s">
+        <v>730</v>
+      </c>
+      <c r="D19" s="104"/>
+      <c r="E19" s="104"/>
+      <c r="F19" s="104"/>
+      <c r="G19" s="104"/>
+      <c r="H19" s="104"/>
+      <c r="I19" s="104"/>
+      <c r="J19" s="104"/>
+    </row>
+    <row r="20" spans="2:17">
+      <c r="C20" s="107" t="s">
+        <v>731</v>
+      </c>
+      <c r="D20" s="104"/>
+      <c r="E20" s="104"/>
+      <c r="F20" s="104"/>
+      <c r="G20" s="104"/>
+      <c r="H20" s="104"/>
+      <c r="I20" s="104"/>
+      <c r="J20" s="104"/>
+    </row>
+    <row r="21" spans="2:17">
+      <c r="C21" s="109" t="s">
+        <v>732</v>
+      </c>
+      <c r="D21" s="104"/>
+      <c r="E21" s="104"/>
+      <c r="F21" s="104"/>
+      <c r="G21" s="104"/>
+      <c r="H21" s="104"/>
+      <c r="I21" s="104"/>
+      <c r="J21" s="104"/>
+    </row>
+    <row r="22" spans="2:17">
+      <c r="C22" s="105" t="s">
+        <v>284</v>
+      </c>
+      <c r="D22" s="104"/>
+      <c r="E22" s="104"/>
+      <c r="F22" s="104"/>
+      <c r="G22" s="104"/>
+      <c r="H22" s="104"/>
+      <c r="I22" s="104"/>
+      <c r="J22" s="104"/>
+    </row>
+    <row r="23" spans="2:17">
+      <c r="C23" s="104"/>
+      <c r="D23" s="104"/>
+      <c r="E23" s="104"/>
+      <c r="F23" s="104"/>
+      <c r="G23" s="104"/>
+      <c r="H23" s="104"/>
+      <c r="I23" s="104"/>
+      <c r="J23" s="104"/>
+    </row>
+    <row r="26" spans="2:17">
+      <c r="B26" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17">
+      <c r="C27" s="109" t="s">
+        <v>735</v>
+      </c>
+      <c r="D27" s="104"/>
+      <c r="E27" s="104"/>
+      <c r="F27" s="104"/>
+      <c r="G27" s="104"/>
+      <c r="H27" s="104"/>
+      <c r="I27" s="104"/>
+      <c r="J27" s="104"/>
+      <c r="K27" s="104"/>
+      <c r="L27" s="104"/>
+      <c r="M27" s="104"/>
+      <c r="N27" s="104"/>
+      <c r="O27" s="104"/>
+      <c r="P27" s="104"/>
+      <c r="Q27" s="104"/>
+    </row>
+    <row r="28" spans="2:17">
+      <c r="C28" s="109" t="s">
+        <v>736</v>
+      </c>
+      <c r="D28" s="104"/>
+      <c r="E28" s="104"/>
+      <c r="F28" s="104"/>
+      <c r="G28" s="104"/>
+      <c r="H28" s="104"/>
+      <c r="I28" s="104"/>
+      <c r="J28" s="104"/>
+      <c r="K28" s="104"/>
+      <c r="L28" s="104"/>
+      <c r="M28" s="104"/>
+      <c r="N28" s="104"/>
+      <c r="O28" s="104"/>
+      <c r="P28" s="104"/>
+      <c r="Q28" s="104"/>
+    </row>
+    <row r="29" spans="2:17">
+      <c r="C29" s="109" t="s">
+        <v>737</v>
+      </c>
+      <c r="D29" s="104"/>
+      <c r="E29" s="104"/>
+      <c r="F29" s="104"/>
+      <c r="G29" s="104"/>
+      <c r="H29" s="104"/>
+      <c r="I29" s="104"/>
+      <c r="J29" s="104"/>
+      <c r="K29" s="104"/>
+      <c r="L29" s="104"/>
+      <c r="M29" s="104"/>
+      <c r="N29" s="104"/>
+      <c r="O29" s="104"/>
+      <c r="P29" s="104"/>
+      <c r="Q29" s="104"/>
+    </row>
+    <row r="30" spans="2:17">
+      <c r="C30" s="109" t="s">
+        <v>738</v>
+      </c>
+      <c r="D30" s="104"/>
+      <c r="E30" s="104"/>
+      <c r="F30" s="104"/>
+      <c r="G30" s="104"/>
+      <c r="H30" s="104"/>
+      <c r="I30" s="104"/>
+      <c r="J30" s="104"/>
+      <c r="K30" s="104"/>
+      <c r="L30" s="104"/>
+      <c r="M30" s="104"/>
+      <c r="N30" s="104"/>
+      <c r="O30" s="104"/>
+      <c r="P30" s="104"/>
+      <c r="Q30" s="104"/>
+    </row>
+    <row r="31" spans="2:17">
+      <c r="C31" s="108"/>
+      <c r="D31" s="104"/>
+      <c r="E31" s="104"/>
+      <c r="F31" s="104"/>
+      <c r="G31" s="104"/>
+      <c r="H31" s="104"/>
+      <c r="I31" s="104"/>
+      <c r="J31" s="104"/>
+      <c r="K31" s="104"/>
+      <c r="L31" s="104"/>
+      <c r="M31" s="104"/>
+      <c r="N31" s="104"/>
+      <c r="O31" s="104"/>
+      <c r="P31" s="104"/>
+      <c r="Q31" s="104"/>
+    </row>
+    <row r="32" spans="2:17">
+      <c r="C32" s="103" t="s">
+        <v>739</v>
+      </c>
+      <c r="D32" s="104"/>
+      <c r="E32" s="104"/>
+      <c r="F32" s="104"/>
+      <c r="G32" s="104"/>
+      <c r="H32" s="104"/>
+      <c r="I32" s="104"/>
+      <c r="J32" s="104"/>
+      <c r="K32" s="104"/>
+      <c r="L32" s="104"/>
+      <c r="M32" s="104"/>
+      <c r="N32" s="104"/>
+      <c r="O32" s="104"/>
+      <c r="P32" s="104"/>
+      <c r="Q32" s="104"/>
+    </row>
+    <row r="33" spans="3:17">
+      <c r="C33" s="105" t="s">
+        <v>511</v>
+      </c>
+      <c r="D33" s="104"/>
+      <c r="E33" s="104"/>
+      <c r="F33" s="104"/>
+      <c r="G33" s="104"/>
+      <c r="H33" s="104"/>
+      <c r="I33" s="104"/>
+      <c r="J33" s="104"/>
+      <c r="K33" s="104"/>
+      <c r="L33" s="104"/>
+      <c r="M33" s="104"/>
+      <c r="N33" s="104"/>
+      <c r="O33" s="104"/>
+      <c r="P33" s="104"/>
+      <c r="Q33" s="104"/>
+    </row>
+    <row r="34" spans="3:17">
+      <c r="C34" s="103" t="s">
+        <v>628</v>
+      </c>
+      <c r="D34" s="104"/>
+      <c r="E34" s="104"/>
+      <c r="F34" s="104"/>
+      <c r="G34" s="104"/>
+      <c r="H34" s="104"/>
+      <c r="I34" s="104"/>
+      <c r="J34" s="104"/>
+      <c r="K34" s="104"/>
+      <c r="L34" s="104"/>
+      <c r="M34" s="104"/>
+      <c r="N34" s="104"/>
+      <c r="O34" s="104"/>
+      <c r="P34" s="104"/>
+      <c r="Q34" s="104"/>
+    </row>
+    <row r="35" spans="3:17">
+      <c r="C35" s="106" t="s">
+        <v>740</v>
+      </c>
+      <c r="D35" s="104"/>
+      <c r="E35" s="104"/>
+      <c r="F35" s="104"/>
+      <c r="G35" s="104"/>
+      <c r="H35" s="104"/>
+      <c r="I35" s="104"/>
+      <c r="J35" s="104"/>
+      <c r="K35" s="104"/>
+      <c r="L35" s="104"/>
+      <c r="M35" s="104"/>
+      <c r="N35" s="104"/>
+      <c r="O35" s="104"/>
+      <c r="P35" s="104"/>
+      <c r="Q35" s="104"/>
+    </row>
+    <row r="36" spans="3:17">
+      <c r="C36" s="103" t="s">
+        <v>741</v>
+      </c>
+      <c r="D36" s="104"/>
+      <c r="E36" s="104"/>
+      <c r="F36" s="104"/>
+      <c r="G36" s="104"/>
+      <c r="H36" s="104"/>
+      <c r="I36" s="104"/>
+      <c r="J36" s="104"/>
+      <c r="K36" s="104"/>
+      <c r="L36" s="104"/>
+      <c r="M36" s="104"/>
+      <c r="N36" s="104"/>
+      <c r="O36" s="104"/>
+      <c r="P36" s="104"/>
+      <c r="Q36" s="104"/>
+    </row>
+    <row r="37" spans="3:17">
+      <c r="C37" s="103" t="s">
+        <v>742</v>
+      </c>
+      <c r="D37" s="104"/>
+      <c r="E37" s="104"/>
+      <c r="F37" s="104"/>
+      <c r="G37" s="104"/>
+      <c r="H37" s="104"/>
+      <c r="I37" s="104"/>
+      <c r="J37" s="104"/>
+      <c r="K37" s="104"/>
+      <c r="L37" s="104"/>
+      <c r="M37" s="104"/>
+      <c r="N37" s="104"/>
+      <c r="O37" s="104"/>
+      <c r="P37" s="104"/>
+      <c r="Q37" s="104"/>
+    </row>
+    <row r="38" spans="3:17">
+      <c r="C38" s="105" t="s">
+        <v>610</v>
+      </c>
+      <c r="D38" s="104"/>
+      <c r="E38" s="104"/>
+      <c r="F38" s="104"/>
+      <c r="G38" s="104"/>
+      <c r="H38" s="104"/>
+      <c r="I38" s="104"/>
+      <c r="J38" s="104"/>
+      <c r="K38" s="104"/>
+      <c r="L38" s="104"/>
+      <c r="M38" s="104"/>
+      <c r="N38" s="104"/>
+      <c r="O38" s="104"/>
+      <c r="P38" s="104"/>
+      <c r="Q38" s="104"/>
+    </row>
+    <row r="39" spans="3:17">
+      <c r="C39" s="108"/>
+      <c r="D39" s="104"/>
+      <c r="E39" s="104"/>
+      <c r="F39" s="104"/>
+      <c r="G39" s="104"/>
+      <c r="H39" s="104"/>
+      <c r="I39" s="104"/>
+      <c r="J39" s="104"/>
+      <c r="K39" s="104"/>
+      <c r="L39" s="104"/>
+      <c r="M39" s="104"/>
+      <c r="N39" s="104"/>
+      <c r="O39" s="104"/>
+      <c r="P39" s="104"/>
+      <c r="Q39" s="104"/>
+    </row>
+    <row r="40" spans="3:17">
+      <c r="C40" s="103" t="s">
+        <v>743</v>
+      </c>
+      <c r="D40" s="104"/>
+      <c r="E40" s="104"/>
+      <c r="F40" s="104"/>
+      <c r="G40" s="104"/>
+      <c r="H40" s="104"/>
+      <c r="I40" s="104"/>
+      <c r="J40" s="104"/>
+      <c r="K40" s="104"/>
+      <c r="L40" s="104"/>
+      <c r="M40" s="104"/>
+      <c r="N40" s="104"/>
+      <c r="O40" s="104"/>
+      <c r="P40" s="104"/>
+      <c r="Q40" s="104"/>
+    </row>
+    <row r="41" spans="3:17">
+      <c r="C41" s="105" t="s">
+        <v>511</v>
+      </c>
+      <c r="D41" s="104"/>
+      <c r="E41" s="104"/>
+      <c r="F41" s="104"/>
+      <c r="G41" s="104"/>
+      <c r="H41" s="104"/>
+      <c r="I41" s="104"/>
+      <c r="J41" s="104"/>
+      <c r="K41" s="104"/>
+      <c r="L41" s="104"/>
+      <c r="M41" s="104"/>
+      <c r="N41" s="104"/>
+      <c r="O41" s="104"/>
+      <c r="P41" s="104"/>
+      <c r="Q41" s="104"/>
+    </row>
+    <row r="42" spans="3:17">
+      <c r="C42" s="103" t="s">
+        <v>725</v>
+      </c>
+      <c r="D42" s="104"/>
+      <c r="E42" s="104"/>
+      <c r="F42" s="104"/>
+      <c r="G42" s="104"/>
+      <c r="H42" s="104"/>
+      <c r="I42" s="104"/>
+      <c r="J42" s="104"/>
+      <c r="K42" s="104"/>
+      <c r="L42" s="104"/>
+      <c r="M42" s="104"/>
+      <c r="N42" s="104"/>
+      <c r="O42" s="104"/>
+      <c r="P42" s="104"/>
+      <c r="Q42" s="104"/>
+    </row>
+    <row r="43" spans="3:17">
+      <c r="C43" s="107" t="s">
+        <v>744</v>
+      </c>
+      <c r="D43" s="104"/>
+      <c r="E43" s="104"/>
+      <c r="F43" s="104"/>
+      <c r="G43" s="104"/>
+      <c r="H43" s="104"/>
+      <c r="I43" s="104"/>
+      <c r="J43" s="104"/>
+      <c r="K43" s="104"/>
+      <c r="L43" s="104"/>
+      <c r="M43" s="104"/>
+      <c r="N43" s="104"/>
+      <c r="O43" s="104"/>
+      <c r="P43" s="104"/>
+      <c r="Q43" s="104"/>
+    </row>
+    <row r="44" spans="3:17">
+      <c r="C44" s="107" t="s">
+        <v>745</v>
+      </c>
+      <c r="D44" s="104"/>
+      <c r="E44" s="104"/>
+      <c r="F44" s="104"/>
+      <c r="G44" s="104"/>
+      <c r="H44" s="104"/>
+      <c r="I44" s="104"/>
+      <c r="J44" s="104"/>
+      <c r="K44" s="104"/>
+      <c r="L44" s="104"/>
+      <c r="M44" s="104"/>
+      <c r="N44" s="104"/>
+      <c r="O44" s="104"/>
+      <c r="P44" s="104"/>
+      <c r="Q44" s="104"/>
+    </row>
+    <row r="45" spans="3:17">
+      <c r="C45" s="103" t="s">
+        <v>628</v>
+      </c>
+      <c r="D45" s="104"/>
+      <c r="E45" s="104"/>
+      <c r="F45" s="104"/>
+      <c r="G45" s="104"/>
+      <c r="H45" s="104"/>
+      <c r="I45" s="104"/>
+      <c r="J45" s="104"/>
+      <c r="K45" s="104"/>
+      <c r="L45" s="104"/>
+      <c r="M45" s="104"/>
+      <c r="N45" s="104"/>
+      <c r="O45" s="104"/>
+      <c r="P45" s="104"/>
+      <c r="Q45" s="104"/>
+    </row>
+    <row r="46" spans="3:17">
+      <c r="C46" s="103" t="s">
+        <v>746</v>
+      </c>
+      <c r="D46" s="104"/>
+      <c r="E46" s="104"/>
+      <c r="F46" s="104"/>
+      <c r="G46" s="104"/>
+      <c r="H46" s="104"/>
+      <c r="I46" s="104"/>
+      <c r="J46" s="104"/>
+      <c r="K46" s="104"/>
+      <c r="L46" s="104"/>
+      <c r="M46" s="104"/>
+      <c r="N46" s="104"/>
+      <c r="O46" s="104"/>
+      <c r="P46" s="104"/>
+      <c r="Q46" s="104"/>
+    </row>
+    <row r="47" spans="3:17">
+      <c r="C47" s="105" t="s">
+        <v>511</v>
+      </c>
+      <c r="D47" s="104"/>
+      <c r="E47" s="104"/>
+      <c r="F47" s="104"/>
+      <c r="G47" s="104"/>
+      <c r="H47" s="104"/>
+      <c r="I47" s="104"/>
+      <c r="J47" s="104"/>
+      <c r="K47" s="104"/>
+      <c r="L47" s="104"/>
+      <c r="M47" s="104"/>
+      <c r="N47" s="104"/>
+      <c r="O47" s="104"/>
+      <c r="P47" s="104"/>
+      <c r="Q47" s="104"/>
+    </row>
+    <row r="48" spans="3:17">
+      <c r="C48" s="110" t="s">
+        <v>747</v>
+      </c>
+      <c r="D48" s="104"/>
+      <c r="E48" s="104"/>
+      <c r="F48" s="104"/>
+      <c r="G48" s="104"/>
+      <c r="H48" s="104"/>
+      <c r="I48" s="104"/>
+      <c r="J48" s="104"/>
+      <c r="K48" s="104"/>
+      <c r="L48" s="104"/>
+      <c r="M48" s="104"/>
+      <c r="N48" s="104"/>
+      <c r="O48" s="104"/>
+      <c r="P48" s="104"/>
+      <c r="Q48" s="104"/>
+    </row>
+    <row r="49" spans="3:17">
+      <c r="C49" s="105" t="s">
+        <v>284</v>
+      </c>
+      <c r="D49" s="104"/>
+      <c r="E49" s="104"/>
+      <c r="F49" s="104"/>
+      <c r="G49" s="104"/>
+      <c r="H49" s="104"/>
+      <c r="I49" s="104"/>
+      <c r="J49" s="104"/>
+      <c r="K49" s="104"/>
+      <c r="L49" s="104"/>
+      <c r="M49" s="104"/>
+      <c r="N49" s="104"/>
+      <c r="O49" s="104"/>
+      <c r="P49" s="104"/>
+      <c r="Q49" s="104"/>
+    </row>
+    <row r="50" spans="3:17">
+      <c r="C50" s="103" t="s">
+        <v>748</v>
+      </c>
+      <c r="D50" s="104"/>
+      <c r="E50" s="104"/>
+      <c r="F50" s="104"/>
+      <c r="G50" s="104"/>
+      <c r="H50" s="104"/>
+      <c r="I50" s="104"/>
+      <c r="J50" s="104"/>
+      <c r="K50" s="104"/>
+      <c r="L50" s="104"/>
+      <c r="M50" s="104"/>
+      <c r="N50" s="104"/>
+      <c r="O50" s="104"/>
+      <c r="P50" s="104"/>
+      <c r="Q50" s="104"/>
+    </row>
+    <row r="51" spans="3:17">
+      <c r="C51" s="105" t="s">
+        <v>511</v>
+      </c>
+      <c r="D51" s="104"/>
+      <c r="E51" s="104"/>
+      <c r="F51" s="104"/>
+      <c r="G51" s="104"/>
+      <c r="H51" s="104"/>
+      <c r="I51" s="104"/>
+      <c r="J51" s="104"/>
+      <c r="K51" s="104"/>
+      <c r="L51" s="104"/>
+      <c r="M51" s="104"/>
+      <c r="N51" s="104"/>
+      <c r="O51" s="104"/>
+      <c r="P51" s="104"/>
+      <c r="Q51" s="104"/>
+    </row>
+    <row r="52" spans="3:17">
+      <c r="C52" s="110" t="s">
+        <v>749</v>
+      </c>
+      <c r="D52" s="104"/>
+      <c r="E52" s="104"/>
+      <c r="F52" s="104"/>
+      <c r="G52" s="104"/>
+      <c r="H52" s="104"/>
+      <c r="I52" s="104"/>
+      <c r="J52" s="104"/>
+      <c r="K52" s="104"/>
+      <c r="L52" s="104"/>
+      <c r="M52" s="104"/>
+      <c r="N52" s="104"/>
+      <c r="O52" s="104"/>
+      <c r="P52" s="104"/>
+      <c r="Q52" s="104"/>
+    </row>
+    <row r="53" spans="3:17">
+      <c r="C53" s="105" t="s">
+        <v>284</v>
+      </c>
+      <c r="D53" s="104"/>
+      <c r="E53" s="104"/>
+      <c r="F53" s="104"/>
+      <c r="G53" s="104"/>
+      <c r="H53" s="104"/>
+      <c r="I53" s="104"/>
+      <c r="J53" s="104"/>
+      <c r="K53" s="104"/>
+      <c r="L53" s="104"/>
+      <c r="M53" s="104"/>
+      <c r="N53" s="104"/>
+      <c r="O53" s="104"/>
+      <c r="P53" s="104"/>
+      <c r="Q53" s="104"/>
+    </row>
+    <row r="54" spans="3:17">
+      <c r="C54" s="103" t="s">
+        <v>750</v>
+      </c>
+      <c r="D54" s="104"/>
+      <c r="E54" s="104"/>
+      <c r="F54" s="104"/>
+      <c r="G54" s="104"/>
+      <c r="H54" s="104"/>
+      <c r="I54" s="104"/>
+      <c r="J54" s="104"/>
+      <c r="K54" s="104"/>
+      <c r="L54" s="104"/>
+      <c r="M54" s="104"/>
+      <c r="N54" s="104"/>
+      <c r="O54" s="104"/>
+      <c r="P54" s="104"/>
+      <c r="Q54" s="104"/>
+    </row>
+    <row r="55" spans="3:17">
+      <c r="C55" s="105" t="s">
+        <v>511</v>
+      </c>
+      <c r="D55" s="104"/>
+      <c r="E55" s="104"/>
+      <c r="F55" s="104"/>
+      <c r="G55" s="104"/>
+      <c r="H55" s="104"/>
+      <c r="I55" s="104"/>
+      <c r="J55" s="104"/>
+      <c r="K55" s="104"/>
+      <c r="L55" s="104"/>
+      <c r="M55" s="104"/>
+      <c r="N55" s="104"/>
+      <c r="O55" s="104"/>
+      <c r="P55" s="104"/>
+      <c r="Q55" s="104"/>
+    </row>
+    <row r="56" spans="3:17">
+      <c r="C56" s="105" t="s">
+        <v>751</v>
+      </c>
+      <c r="D56" s="104"/>
+      <c r="E56" s="104"/>
+      <c r="F56" s="104"/>
+      <c r="G56" s="104"/>
+      <c r="H56" s="104"/>
+      <c r="I56" s="104"/>
+      <c r="J56" s="104"/>
+      <c r="K56" s="104"/>
+      <c r="L56" s="104"/>
+      <c r="M56" s="104"/>
+      <c r="N56" s="104"/>
+      <c r="O56" s="104"/>
+      <c r="P56" s="104"/>
+      <c r="Q56" s="104"/>
+    </row>
+    <row r="57" spans="3:17">
+      <c r="C57" s="105" t="s">
+        <v>752</v>
+      </c>
+      <c r="D57" s="104"/>
+      <c r="E57" s="104"/>
+      <c r="F57" s="104"/>
+      <c r="G57" s="104"/>
+      <c r="H57" s="104"/>
+      <c r="I57" s="104"/>
+      <c r="J57" s="104"/>
+      <c r="K57" s="104"/>
+      <c r="L57" s="104"/>
+      <c r="M57" s="104"/>
+      <c r="N57" s="104"/>
+      <c r="O57" s="104"/>
+      <c r="P57" s="104"/>
+      <c r="Q57" s="104"/>
+    </row>
+    <row r="58" spans="3:17">
+      <c r="C58" s="105" t="s">
+        <v>753</v>
+      </c>
+      <c r="D58" s="104"/>
+      <c r="E58" s="104"/>
+      <c r="F58" s="104"/>
+      <c r="G58" s="104"/>
+      <c r="H58" s="104"/>
+      <c r="I58" s="104"/>
+      <c r="J58" s="104"/>
+      <c r="K58" s="104"/>
+      <c r="L58" s="104"/>
+      <c r="M58" s="104"/>
+      <c r="N58" s="104"/>
+      <c r="O58" s="104"/>
+      <c r="P58" s="104"/>
+      <c r="Q58" s="104"/>
+    </row>
+    <row r="59" spans="3:17">
+      <c r="C59" s="105" t="s">
+        <v>754</v>
+      </c>
+      <c r="D59" s="104"/>
+      <c r="E59" s="104"/>
+      <c r="F59" s="104"/>
+      <c r="G59" s="104"/>
+      <c r="H59" s="104"/>
+      <c r="I59" s="104"/>
+      <c r="J59" s="104"/>
+      <c r="K59" s="104"/>
+      <c r="L59" s="104"/>
+      <c r="M59" s="104"/>
+      <c r="N59" s="104"/>
+      <c r="O59" s="104"/>
+      <c r="P59" s="104"/>
+      <c r="Q59" s="104"/>
+    </row>
+    <row r="60" spans="3:17">
+      <c r="C60" s="105" t="s">
+        <v>284</v>
+      </c>
+      <c r="D60" s="104"/>
+      <c r="E60" s="104"/>
+      <c r="F60" s="104"/>
+      <c r="G60" s="104"/>
+      <c r="H60" s="104"/>
+      <c r="I60" s="104"/>
+      <c r="J60" s="104"/>
+      <c r="K60" s="104"/>
+      <c r="L60" s="104"/>
+      <c r="M60" s="104"/>
+      <c r="N60" s="104"/>
+      <c r="O60" s="104"/>
+      <c r="P60" s="104"/>
+      <c r="Q60" s="104"/>
+    </row>
+    <row r="61" spans="3:17">
+      <c r="C61" s="103" t="s">
+        <v>755</v>
+      </c>
+      <c r="D61" s="104"/>
+      <c r="E61" s="104"/>
+      <c r="F61" s="104"/>
+      <c r="G61" s="104"/>
+      <c r="H61" s="104"/>
+      <c r="I61" s="104"/>
+      <c r="J61" s="104"/>
+      <c r="K61" s="104"/>
+      <c r="L61" s="104"/>
+      <c r="M61" s="104"/>
+      <c r="N61" s="104"/>
+      <c r="O61" s="104"/>
+      <c r="P61" s="104"/>
+      <c r="Q61" s="104"/>
+    </row>
+    <row r="62" spans="3:17">
+      <c r="C62" s="105" t="s">
+        <v>511</v>
+      </c>
+      <c r="D62" s="104"/>
+      <c r="E62" s="104"/>
+      <c r="F62" s="104"/>
+      <c r="G62" s="104"/>
+      <c r="H62" s="104"/>
+      <c r="I62" s="104"/>
+      <c r="J62" s="104"/>
+      <c r="K62" s="104"/>
+      <c r="L62" s="104"/>
+      <c r="M62" s="104"/>
+      <c r="N62" s="104"/>
+      <c r="O62" s="104"/>
+      <c r="P62" s="104"/>
+      <c r="Q62" s="104"/>
+    </row>
+    <row r="63" spans="3:17">
+      <c r="C63" s="110" t="s">
+        <v>756</v>
+      </c>
+      <c r="D63" s="104"/>
+      <c r="E63" s="104"/>
+      <c r="F63" s="104"/>
+      <c r="G63" s="104"/>
+      <c r="H63" s="104"/>
+      <c r="I63" s="104"/>
+      <c r="J63" s="104"/>
+      <c r="K63" s="104"/>
+      <c r="L63" s="104"/>
+      <c r="M63" s="104"/>
+      <c r="N63" s="104"/>
+      <c r="O63" s="104"/>
+      <c r="P63" s="104"/>
+      <c r="Q63" s="104"/>
+    </row>
+    <row r="64" spans="3:17">
+      <c r="C64" s="106" t="s">
+        <v>757</v>
+      </c>
+      <c r="D64" s="104"/>
+      <c r="E64" s="104"/>
+      <c r="F64" s="104"/>
+      <c r="G64" s="104"/>
+      <c r="H64" s="104"/>
+      <c r="I64" s="104"/>
+      <c r="J64" s="104"/>
+      <c r="K64" s="104"/>
+      <c r="L64" s="104"/>
+      <c r="M64" s="104"/>
+      <c r="N64" s="104"/>
+      <c r="O64" s="104"/>
+      <c r="P64" s="104"/>
+      <c r="Q64" s="104"/>
+    </row>
+    <row r="65" spans="3:17">
+      <c r="C65" s="105" t="s">
+        <v>284</v>
+      </c>
+      <c r="D65" s="104"/>
+      <c r="E65" s="104"/>
+      <c r="F65" s="104"/>
+      <c r="G65" s="104"/>
+      <c r="H65" s="104"/>
+      <c r="I65" s="104"/>
+      <c r="J65" s="104"/>
+      <c r="K65" s="104"/>
+      <c r="L65" s="104"/>
+      <c r="M65" s="104"/>
+      <c r="N65" s="104"/>
+      <c r="O65" s="104"/>
+      <c r="P65" s="104"/>
+      <c r="Q65" s="104"/>
+    </row>
+    <row r="66" spans="3:17">
+      <c r="C66" s="105" t="s">
+        <v>610</v>
+      </c>
+      <c r="D66" s="104"/>
+      <c r="E66" s="104"/>
+      <c r="F66" s="104"/>
+      <c r="G66" s="104"/>
+      <c r="H66" s="104"/>
+      <c r="I66" s="104"/>
+      <c r="J66" s="104"/>
+      <c r="K66" s="104"/>
+      <c r="L66" s="104"/>
+      <c r="M66" s="104"/>
+      <c r="N66" s="104"/>
+      <c r="O66" s="104"/>
+      <c r="P66" s="104"/>
+      <c r="Q66" s="104"/>
+    </row>
+    <row r="67" spans="3:17">
+      <c r="C67" s="108"/>
+      <c r="D67" s="104"/>
+      <c r="E67" s="104"/>
+      <c r="F67" s="104"/>
+      <c r="G67" s="104"/>
+      <c r="H67" s="104"/>
+      <c r="I67" s="104"/>
+      <c r="J67" s="104"/>
+      <c r="K67" s="104"/>
+      <c r="L67" s="104"/>
+      <c r="M67" s="104"/>
+      <c r="N67" s="104"/>
+      <c r="O67" s="104"/>
+      <c r="P67" s="104"/>
+      <c r="Q67" s="104"/>
+    </row>
+    <row r="68" spans="3:17">
+      <c r="C68" s="103" t="s">
+        <v>758</v>
+      </c>
+      <c r="D68" s="104"/>
+      <c r="E68" s="104"/>
+      <c r="F68" s="104"/>
+      <c r="G68" s="104"/>
+      <c r="H68" s="104"/>
+      <c r="I68" s="104"/>
+      <c r="J68" s="104"/>
+      <c r="K68" s="104"/>
+      <c r="L68" s="104"/>
+      <c r="M68" s="104"/>
+      <c r="N68" s="104"/>
+      <c r="O68" s="104"/>
+      <c r="P68" s="104"/>
+      <c r="Q68" s="104"/>
+    </row>
+    <row r="69" spans="3:17">
+      <c r="C69" s="105" t="s">
+        <v>511</v>
+      </c>
+      <c r="D69" s="104"/>
+      <c r="E69" s="104"/>
+      <c r="F69" s="104"/>
+      <c r="G69" s="104"/>
+      <c r="H69" s="104"/>
+      <c r="I69" s="104"/>
+      <c r="J69" s="104"/>
+      <c r="K69" s="104"/>
+      <c r="L69" s="104"/>
+      <c r="M69" s="104"/>
+      <c r="N69" s="104"/>
+      <c r="O69" s="104"/>
+      <c r="P69" s="104"/>
+      <c r="Q69" s="104"/>
+    </row>
+    <row r="70" spans="3:17">
+      <c r="C70" s="103" t="s">
+        <v>725</v>
+      </c>
+      <c r="D70" s="104"/>
+      <c r="E70" s="104"/>
+      <c r="F70" s="104"/>
+      <c r="G70" s="104"/>
+      <c r="H70" s="104"/>
+      <c r="I70" s="104"/>
+      <c r="J70" s="104"/>
+      <c r="K70" s="104"/>
+      <c r="L70" s="104"/>
+      <c r="M70" s="104"/>
+      <c r="N70" s="104"/>
+      <c r="O70" s="104"/>
+      <c r="P70" s="104"/>
+      <c r="Q70" s="104"/>
+    </row>
+    <row r="71" spans="3:17">
+      <c r="C71" s="107" t="s">
+        <v>759</v>
+      </c>
+      <c r="D71" s="104"/>
+      <c r="E71" s="104"/>
+      <c r="F71" s="104"/>
+      <c r="G71" s="104"/>
+      <c r="H71" s="104"/>
+      <c r="I71" s="104"/>
+      <c r="J71" s="104"/>
+      <c r="K71" s="104"/>
+      <c r="L71" s="104"/>
+      <c r="M71" s="104"/>
+      <c r="N71" s="104"/>
+      <c r="O71" s="104"/>
+      <c r="P71" s="104"/>
+      <c r="Q71" s="104"/>
+    </row>
+    <row r="72" spans="3:17">
+      <c r="C72" s="107" t="s">
+        <v>760</v>
+      </c>
+      <c r="D72" s="104"/>
+      <c r="E72" s="104"/>
+      <c r="F72" s="104"/>
+      <c r="G72" s="104"/>
+      <c r="H72" s="104"/>
+      <c r="I72" s="104"/>
+      <c r="J72" s="104"/>
+      <c r="K72" s="104"/>
+      <c r="L72" s="104"/>
+      <c r="M72" s="104"/>
+      <c r="N72" s="104"/>
+      <c r="O72" s="104"/>
+      <c r="P72" s="104"/>
+      <c r="Q72" s="104"/>
+    </row>
+    <row r="73" spans="3:17">
+      <c r="C73" s="103" t="s">
+        <v>628</v>
+      </c>
+      <c r="D73" s="104"/>
+      <c r="E73" s="104"/>
+      <c r="F73" s="104"/>
+      <c r="G73" s="104"/>
+      <c r="H73" s="104"/>
+      <c r="I73" s="104"/>
+      <c r="J73" s="104"/>
+      <c r="K73" s="104"/>
+      <c r="L73" s="104"/>
+      <c r="M73" s="104"/>
+      <c r="N73" s="104"/>
+      <c r="O73" s="104"/>
+      <c r="P73" s="104"/>
+      <c r="Q73" s="104"/>
+    </row>
+    <row r="74" spans="3:17">
+      <c r="C74" s="106" t="s">
+        <v>761</v>
+      </c>
+      <c r="D74" s="104"/>
+      <c r="E74" s="104"/>
+      <c r="F74" s="104"/>
+      <c r="G74" s="104"/>
+      <c r="H74" s="104"/>
+      <c r="I74" s="104"/>
+      <c r="J74" s="104"/>
+      <c r="K74" s="104"/>
+      <c r="L74" s="104"/>
+      <c r="M74" s="104"/>
+      <c r="N74" s="104"/>
+      <c r="O74" s="104"/>
+      <c r="P74" s="104"/>
+      <c r="Q74" s="104"/>
+    </row>
+    <row r="75" spans="3:17">
+      <c r="C75" s="105" t="s">
+        <v>511</v>
+      </c>
+      <c r="D75" s="104"/>
+      <c r="E75" s="104"/>
+      <c r="F75" s="104"/>
+      <c r="G75" s="104"/>
+      <c r="H75" s="104"/>
+      <c r="I75" s="104"/>
+      <c r="J75" s="104"/>
+      <c r="K75" s="104"/>
+      <c r="L75" s="104"/>
+      <c r="M75" s="104"/>
+      <c r="N75" s="104"/>
+      <c r="O75" s="104"/>
+      <c r="P75" s="104"/>
+      <c r="Q75" s="104"/>
+    </row>
+    <row r="76" spans="3:17">
+      <c r="C76" s="110" t="s">
+        <v>762</v>
+      </c>
+      <c r="D76" s="104"/>
+      <c r="E76" s="104"/>
+      <c r="F76" s="104"/>
+      <c r="G76" s="104"/>
+      <c r="H76" s="104"/>
+      <c r="I76" s="104"/>
+      <c r="J76" s="104"/>
+      <c r="K76" s="104"/>
+      <c r="L76" s="104"/>
+      <c r="M76" s="104"/>
+      <c r="N76" s="104"/>
+      <c r="O76" s="104"/>
+      <c r="P76" s="104"/>
+      <c r="Q76" s="104"/>
+    </row>
+    <row r="77" spans="3:17">
+      <c r="C77" s="105" t="s">
+        <v>284</v>
+      </c>
+      <c r="D77" s="104"/>
+      <c r="E77" s="104"/>
+      <c r="F77" s="104"/>
+      <c r="G77" s="104"/>
+      <c r="H77" s="104"/>
+      <c r="I77" s="104"/>
+      <c r="J77" s="104"/>
+      <c r="K77" s="104"/>
+      <c r="L77" s="104"/>
+      <c r="M77" s="104"/>
+      <c r="N77" s="104"/>
+      <c r="O77" s="104"/>
+      <c r="P77" s="104"/>
+      <c r="Q77" s="104"/>
+    </row>
+    <row r="78" spans="3:17">
+      <c r="C78" s="108"/>
+      <c r="D78" s="104"/>
+      <c r="E78" s="104"/>
+      <c r="F78" s="104"/>
+      <c r="G78" s="104"/>
+      <c r="H78" s="104"/>
+      <c r="I78" s="104"/>
+      <c r="J78" s="104"/>
+      <c r="K78" s="104"/>
+      <c r="L78" s="104"/>
+      <c r="M78" s="104"/>
+      <c r="N78" s="104"/>
+      <c r="O78" s="104"/>
+      <c r="P78" s="104"/>
+      <c r="Q78" s="104"/>
+    </row>
+    <row r="79" spans="3:17">
+      <c r="C79" s="103" t="s">
+        <v>763</v>
+      </c>
+      <c r="D79" s="104"/>
+      <c r="E79" s="104"/>
+      <c r="F79" s="104"/>
+      <c r="G79" s="104"/>
+      <c r="H79" s="104"/>
+      <c r="I79" s="104"/>
+      <c r="J79" s="104"/>
+      <c r="K79" s="104"/>
+      <c r="L79" s="104"/>
+      <c r="M79" s="104"/>
+      <c r="N79" s="104"/>
+      <c r="O79" s="104"/>
+      <c r="P79" s="104"/>
+      <c r="Q79" s="104"/>
+    </row>
+    <row r="80" spans="3:17">
+      <c r="C80" s="105" t="s">
+        <v>511</v>
+      </c>
+      <c r="D80" s="104"/>
+      <c r="E80" s="104"/>
+      <c r="F80" s="104"/>
+      <c r="G80" s="104"/>
+      <c r="H80" s="104"/>
+      <c r="I80" s="104"/>
+      <c r="J80" s="104"/>
+      <c r="K80" s="104"/>
+      <c r="L80" s="104"/>
+      <c r="M80" s="104"/>
+      <c r="N80" s="104"/>
+      <c r="O80" s="104"/>
+      <c r="P80" s="104"/>
+      <c r="Q80" s="104"/>
+    </row>
+    <row r="81" spans="3:17">
+      <c r="C81" s="110" t="s">
+        <v>764</v>
+      </c>
+      <c r="D81" s="104"/>
+      <c r="E81" s="104"/>
+      <c r="F81" s="104"/>
+      <c r="G81" s="104"/>
+      <c r="H81" s="104"/>
+      <c r="I81" s="104"/>
+      <c r="J81" s="104"/>
+      <c r="K81" s="104"/>
+      <c r="L81" s="104"/>
+      <c r="M81" s="104"/>
+      <c r="N81" s="104"/>
+      <c r="O81" s="104"/>
+      <c r="P81" s="104"/>
+      <c r="Q81" s="104"/>
+    </row>
+    <row r="82" spans="3:17">
+      <c r="C82" s="107" t="s">
+        <v>765</v>
+      </c>
+      <c r="D82" s="104"/>
+      <c r="E82" s="104"/>
+      <c r="F82" s="104"/>
+      <c r="G82" s="104"/>
+      <c r="H82" s="104"/>
+      <c r="I82" s="104"/>
+      <c r="J82" s="104"/>
+      <c r="K82" s="104"/>
+      <c r="L82" s="104"/>
+      <c r="M82" s="104"/>
+      <c r="N82" s="104"/>
+      <c r="O82" s="104"/>
+      <c r="P82" s="104"/>
+      <c r="Q82" s="104"/>
+    </row>
+    <row r="83" spans="3:17">
+      <c r="C83" s="105" t="s">
+        <v>284</v>
+      </c>
+      <c r="D83" s="104"/>
+      <c r="E83" s="104"/>
+      <c r="F83" s="104"/>
+      <c r="G83" s="104"/>
+      <c r="H83" s="104"/>
+      <c r="I83" s="104"/>
+      <c r="J83" s="104"/>
+      <c r="K83" s="104"/>
+      <c r="L83" s="104"/>
+      <c r="M83" s="104"/>
+      <c r="N83" s="104"/>
+      <c r="O83" s="104"/>
+      <c r="P83" s="104"/>
+      <c r="Q83" s="104"/>
+    </row>
+    <row r="84" spans="3:17">
+      <c r="C84" s="108"/>
+      <c r="D84" s="104"/>
+      <c r="E84" s="104"/>
+      <c r="F84" s="104"/>
+      <c r="G84" s="104"/>
+      <c r="H84" s="104"/>
+      <c r="I84" s="104"/>
+      <c r="J84" s="104"/>
+      <c r="K84" s="104"/>
+      <c r="L84" s="104"/>
+      <c r="M84" s="104"/>
+      <c r="N84" s="104"/>
+      <c r="O84" s="104"/>
+      <c r="P84" s="104"/>
+      <c r="Q84" s="104"/>
+    </row>
+    <row r="85" spans="3:17">
+      <c r="C85" s="103" t="s">
+        <v>766</v>
+      </c>
+      <c r="D85" s="104"/>
+      <c r="E85" s="104"/>
+      <c r="F85" s="104"/>
+      <c r="G85" s="104"/>
+      <c r="H85" s="104"/>
+      <c r="I85" s="104"/>
+      <c r="J85" s="104"/>
+      <c r="K85" s="104"/>
+      <c r="L85" s="104"/>
+      <c r="M85" s="104"/>
+      <c r="N85" s="104"/>
+      <c r="O85" s="104"/>
+      <c r="P85" s="104"/>
+      <c r="Q85" s="104"/>
+    </row>
+    <row r="86" spans="3:17">
+      <c r="C86" s="105" t="s">
+        <v>511</v>
+      </c>
+      <c r="D86" s="104"/>
+      <c r="E86" s="104"/>
+      <c r="F86" s="104"/>
+      <c r="G86" s="104"/>
+      <c r="H86" s="104"/>
+      <c r="I86" s="104"/>
+      <c r="J86" s="104"/>
+      <c r="K86" s="104"/>
+      <c r="L86" s="104"/>
+      <c r="M86" s="104"/>
+      <c r="N86" s="104"/>
+      <c r="O86" s="104"/>
+      <c r="P86" s="104"/>
+      <c r="Q86" s="104"/>
+    </row>
+    <row r="87" spans="3:17">
+      <c r="C87" s="107" t="s">
+        <v>767</v>
+      </c>
+      <c r="D87" s="104"/>
+      <c r="E87" s="104"/>
+      <c r="F87" s="104"/>
+      <c r="G87" s="104"/>
+      <c r="H87" s="104"/>
+      <c r="I87" s="104"/>
+      <c r="J87" s="104"/>
+      <c r="K87" s="104"/>
+      <c r="L87" s="104"/>
+      <c r="M87" s="104"/>
+      <c r="N87" s="104"/>
+      <c r="O87" s="104"/>
+      <c r="P87" s="104"/>
+      <c r="Q87" s="104"/>
+    </row>
+    <row r="88" spans="3:17">
+      <c r="C88" s="105" t="s">
+        <v>284</v>
+      </c>
+      <c r="D88" s="104"/>
+      <c r="E88" s="104"/>
+      <c r="F88" s="104"/>
+      <c r="G88" s="104"/>
+      <c r="H88" s="104"/>
+      <c r="I88" s="104"/>
+      <c r="J88" s="104"/>
+      <c r="K88" s="104"/>
+      <c r="L88" s="104"/>
+      <c r="M88" s="104"/>
+      <c r="N88" s="104"/>
+      <c r="O88" s="104"/>
+      <c r="P88" s="104"/>
+      <c r="Q88" s="104"/>
+    </row>
+    <row r="89" spans="3:17">
+      <c r="C89" s="108"/>
+      <c r="D89" s="104"/>
+      <c r="E89" s="104"/>
+      <c r="F89" s="104"/>
+      <c r="G89" s="104"/>
+      <c r="H89" s="104"/>
+      <c r="I89" s="104"/>
+      <c r="J89" s="104"/>
+      <c r="K89" s="104"/>
+      <c r="L89" s="104"/>
+      <c r="M89" s="104"/>
+      <c r="N89" s="104"/>
+      <c r="O89" s="104"/>
+      <c r="P89" s="104"/>
+      <c r="Q89" s="104"/>
+    </row>
+    <row r="90" spans="3:17">
+      <c r="C90" s="105" t="s">
+        <v>610</v>
+      </c>
+      <c r="D90" s="104"/>
+      <c r="E90" s="104"/>
+      <c r="F90" s="104"/>
+      <c r="G90" s="104"/>
+      <c r="H90" s="104"/>
+      <c r="I90" s="104"/>
+      <c r="J90" s="104"/>
+      <c r="K90" s="104"/>
+      <c r="L90" s="104"/>
+      <c r="M90" s="104"/>
+      <c r="N90" s="104"/>
+      <c r="O90" s="104"/>
+      <c r="P90" s="104"/>
+      <c r="Q90" s="104"/>
+    </row>
+    <row r="91" spans="3:17">
+      <c r="C91" s="108"/>
+      <c r="D91" s="104"/>
+      <c r="E91" s="104"/>
+      <c r="F91" s="104"/>
+      <c r="G91" s="104"/>
+      <c r="H91" s="104"/>
+      <c r="I91" s="104"/>
+      <c r="J91" s="104"/>
+      <c r="K91" s="104"/>
+      <c r="L91" s="104"/>
+      <c r="M91" s="104"/>
+      <c r="N91" s="104"/>
+      <c r="O91" s="104"/>
+      <c r="P91" s="104"/>
+      <c r="Q91" s="104"/>
+    </row>
+    <row r="92" spans="3:17">
+      <c r="C92" s="103" t="s">
+        <v>729</v>
+      </c>
+      <c r="D92" s="104"/>
+      <c r="E92" s="104"/>
+      <c r="F92" s="104"/>
+      <c r="G92" s="104"/>
+      <c r="H92" s="104"/>
+      <c r="I92" s="104"/>
+      <c r="J92" s="104"/>
+      <c r="K92" s="104"/>
+      <c r="L92" s="104"/>
+      <c r="M92" s="104"/>
+      <c r="N92" s="104"/>
+      <c r="O92" s="104"/>
+      <c r="P92" s="104"/>
+      <c r="Q92" s="104"/>
+    </row>
+    <row r="93" spans="3:17">
+      <c r="C93" s="105" t="s">
+        <v>511</v>
+      </c>
+      <c r="D93" s="104"/>
+      <c r="E93" s="104"/>
+      <c r="F93" s="104"/>
+      <c r="G93" s="104"/>
+      <c r="H93" s="104"/>
+      <c r="I93" s="104"/>
+      <c r="J93" s="104"/>
+      <c r="K93" s="104"/>
+      <c r="L93" s="104"/>
+      <c r="M93" s="104"/>
+      <c r="N93" s="104"/>
+      <c r="O93" s="104"/>
+      <c r="P93" s="104"/>
+      <c r="Q93" s="104"/>
+    </row>
+    <row r="94" spans="3:17">
+      <c r="C94" s="107" t="s">
+        <v>768</v>
+      </c>
+      <c r="D94" s="104"/>
+      <c r="E94" s="104"/>
+      <c r="F94" s="104"/>
+      <c r="G94" s="104"/>
+      <c r="H94" s="104"/>
+      <c r="I94" s="104"/>
+      <c r="J94" s="104"/>
+      <c r="K94" s="104"/>
+      <c r="L94" s="104"/>
+      <c r="M94" s="104"/>
+      <c r="N94" s="104"/>
+      <c r="O94" s="104"/>
+      <c r="P94" s="104"/>
+      <c r="Q94" s="104"/>
+    </row>
+    <row r="95" spans="3:17">
+      <c r="C95" s="107" t="s">
+        <v>769</v>
+      </c>
+      <c r="D95" s="104"/>
+      <c r="E95" s="104"/>
+      <c r="F95" s="104"/>
+      <c r="G95" s="104"/>
+      <c r="H95" s="104"/>
+      <c r="I95" s="104"/>
+      <c r="J95" s="104"/>
+      <c r="K95" s="104"/>
+      <c r="L95" s="104"/>
+      <c r="M95" s="104"/>
+      <c r="N95" s="104"/>
+      <c r="O95" s="104"/>
+      <c r="P95" s="104"/>
+      <c r="Q95" s="104"/>
+    </row>
+    <row r="96" spans="3:17">
+      <c r="C96" s="107" t="s">
+        <v>770</v>
+      </c>
+      <c r="D96" s="104"/>
+      <c r="E96" s="104"/>
+      <c r="F96" s="104"/>
+      <c r="G96" s="104"/>
+      <c r="H96" s="104"/>
+      <c r="I96" s="104"/>
+      <c r="J96" s="104"/>
+      <c r="K96" s="104"/>
+      <c r="L96" s="104"/>
+      <c r="M96" s="104"/>
+      <c r="N96" s="104"/>
+      <c r="O96" s="104"/>
+      <c r="P96" s="104"/>
+      <c r="Q96" s="104"/>
+    </row>
+    <row r="97" spans="3:17">
+      <c r="C97" s="107" t="s">
+        <v>771</v>
+      </c>
+      <c r="D97" s="104"/>
+      <c r="E97" s="104"/>
+      <c r="F97" s="104"/>
+      <c r="G97" s="104"/>
+      <c r="H97" s="104"/>
+      <c r="I97" s="104"/>
+      <c r="J97" s="104"/>
+      <c r="K97" s="104"/>
+      <c r="L97" s="104"/>
+      <c r="M97" s="104"/>
+      <c r="N97" s="104"/>
+      <c r="O97" s="104"/>
+      <c r="P97" s="104"/>
+      <c r="Q97" s="104"/>
+    </row>
+    <row r="98" spans="3:17">
+      <c r="C98" s="108"/>
+      <c r="D98" s="104"/>
+      <c r="E98" s="104"/>
+      <c r="F98" s="104"/>
+      <c r="G98" s="104"/>
+      <c r="H98" s="104"/>
+      <c r="I98" s="104"/>
+      <c r="J98" s="104"/>
+      <c r="K98" s="104"/>
+      <c r="L98" s="104"/>
+      <c r="M98" s="104"/>
+      <c r="N98" s="104"/>
+      <c r="O98" s="104"/>
+      <c r="P98" s="104"/>
+      <c r="Q98" s="104"/>
+    </row>
+    <row r="99" spans="3:17">
+      <c r="C99" s="110" t="s">
+        <v>772</v>
+      </c>
+      <c r="D99" s="104"/>
+      <c r="E99" s="104"/>
+      <c r="F99" s="104"/>
+      <c r="G99" s="104"/>
+      <c r="H99" s="104"/>
+      <c r="I99" s="104"/>
+      <c r="J99" s="104"/>
+      <c r="K99" s="104"/>
+      <c r="L99" s="104"/>
+      <c r="M99" s="104"/>
+      <c r="N99" s="104"/>
+      <c r="O99" s="104"/>
+      <c r="P99" s="104"/>
+      <c r="Q99" s="104"/>
+    </row>
+    <row r="100" spans="3:17">
+      <c r="C100" s="110" t="s">
+        <v>773</v>
+      </c>
+      <c r="D100" s="104"/>
+      <c r="E100" s="104"/>
+      <c r="F100" s="104"/>
+      <c r="G100" s="104"/>
+      <c r="H100" s="104"/>
+      <c r="I100" s="104"/>
+      <c r="J100" s="104"/>
+      <c r="K100" s="104"/>
+      <c r="L100" s="104"/>
+      <c r="M100" s="104"/>
+      <c r="N100" s="104"/>
+      <c r="O100" s="104"/>
+      <c r="P100" s="104"/>
+      <c r="Q100" s="104"/>
+    </row>
+    <row r="101" spans="3:17">
+      <c r="C101" s="108"/>
+      <c r="D101" s="104"/>
+      <c r="E101" s="104"/>
+      <c r="F101" s="104"/>
+      <c r="G101" s="104"/>
+      <c r="H101" s="104"/>
+      <c r="I101" s="104"/>
+      <c r="J101" s="104"/>
+      <c r="K101" s="104"/>
+      <c r="L101" s="104"/>
+      <c r="M101" s="104"/>
+      <c r="N101" s="104"/>
+      <c r="O101" s="104"/>
+      <c r="P101" s="104"/>
+      <c r="Q101" s="104"/>
+    </row>
+    <row r="102" spans="3:17">
+      <c r="C102" s="110" t="s">
+        <v>774</v>
+      </c>
+      <c r="D102" s="104"/>
+      <c r="E102" s="104"/>
+      <c r="F102" s="104"/>
+      <c r="G102" s="104"/>
+      <c r="H102" s="104"/>
+      <c r="I102" s="104"/>
+      <c r="J102" s="104"/>
+      <c r="K102" s="104"/>
+      <c r="L102" s="104"/>
+      <c r="M102" s="104"/>
+      <c r="N102" s="104"/>
+      <c r="O102" s="104"/>
+      <c r="P102" s="104"/>
+      <c r="Q102" s="104"/>
+    </row>
+    <row r="103" spans="3:17">
+      <c r="C103" s="110" t="s">
+        <v>775</v>
+      </c>
+      <c r="D103" s="104"/>
+      <c r="E103" s="104"/>
+      <c r="F103" s="104"/>
+      <c r="G103" s="104"/>
+      <c r="H103" s="104"/>
+      <c r="I103" s="104"/>
+      <c r="J103" s="104"/>
+      <c r="K103" s="104"/>
+      <c r="L103" s="104"/>
+      <c r="M103" s="104"/>
+      <c r="N103" s="104"/>
+      <c r="O103" s="104"/>
+      <c r="P103" s="104"/>
+      <c r="Q103" s="104"/>
+    </row>
+    <row r="104" spans="3:17">
+      <c r="C104" s="108"/>
+      <c r="D104" s="104"/>
+      <c r="E104" s="104"/>
+      <c r="F104" s="104"/>
+      <c r="G104" s="104"/>
+      <c r="H104" s="104"/>
+      <c r="I104" s="104"/>
+      <c r="J104" s="104"/>
+      <c r="K104" s="104"/>
+      <c r="L104" s="104"/>
+      <c r="M104" s="104"/>
+      <c r="N104" s="104"/>
+      <c r="O104" s="104"/>
+      <c r="P104" s="104"/>
+      <c r="Q104" s="104"/>
+    </row>
+    <row r="105" spans="3:17">
+      <c r="C105" s="110" t="s">
+        <v>776</v>
+      </c>
+      <c r="D105" s="104"/>
+      <c r="E105" s="104"/>
+      <c r="F105" s="104"/>
+      <c r="G105" s="104"/>
+      <c r="H105" s="104"/>
+      <c r="I105" s="104"/>
+      <c r="J105" s="104"/>
+      <c r="K105" s="104"/>
+      <c r="L105" s="104"/>
+      <c r="M105" s="104"/>
+      <c r="N105" s="104"/>
+      <c r="O105" s="104"/>
+      <c r="P105" s="104"/>
+      <c r="Q105" s="104"/>
+    </row>
+    <row r="106" spans="3:17">
+      <c r="C106" s="108"/>
+      <c r="D106" s="104"/>
+      <c r="E106" s="104"/>
+      <c r="F106" s="104"/>
+      <c r="G106" s="104"/>
+      <c r="H106" s="104"/>
+      <c r="I106" s="104"/>
+      <c r="J106" s="104"/>
+      <c r="K106" s="104"/>
+      <c r="L106" s="104"/>
+      <c r="M106" s="104"/>
+      <c r="N106" s="104"/>
+      <c r="O106" s="104"/>
+      <c r="P106" s="104"/>
+      <c r="Q106" s="104"/>
+    </row>
+    <row r="107" spans="3:17">
+      <c r="C107" s="109" t="s">
+        <v>732</v>
+      </c>
+      <c r="D107" s="104"/>
+      <c r="E107" s="104"/>
+      <c r="F107" s="104"/>
+      <c r="G107" s="104"/>
+      <c r="H107" s="104"/>
+      <c r="I107" s="104"/>
+      <c r="J107" s="104"/>
+      <c r="K107" s="104"/>
+      <c r="L107" s="104"/>
+      <c r="M107" s="104"/>
+      <c r="N107" s="104"/>
+      <c r="O107" s="104"/>
+      <c r="P107" s="104"/>
+      <c r="Q107" s="104"/>
+    </row>
+    <row r="108" spans="3:17">
+      <c r="C108" s="105" t="s">
+        <v>284</v>
+      </c>
+      <c r="D108" s="104"/>
+      <c r="E108" s="104"/>
+      <c r="F108" s="104"/>
+      <c r="G108" s="104"/>
+      <c r="H108" s="104"/>
+      <c r="I108" s="104"/>
+      <c r="J108" s="104"/>
+      <c r="K108" s="104"/>
+      <c r="L108" s="104"/>
+      <c r="M108" s="104"/>
+      <c r="N108" s="104"/>
+      <c r="O108" s="104"/>
+      <c r="P108" s="104"/>
+      <c r="Q108" s="104"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:E27"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2" spans="2:5">
+      <c r="B2" s="6" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5">
+      <c r="C3" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5">
+      <c r="D4" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5">
+      <c r="D6" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5">
+      <c r="E7" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
+      <c r="E8" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5">
+      <c r="E9" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5">
+      <c r="E10" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5">
+      <c r="C12" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5">
+      <c r="D13" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5">
+      <c r="D15" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5">
+      <c r="E16" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="E17" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
+      <c r="B19" s="17" t="s">
+        <v>787</v>
+      </c>
+      <c r="C19" s="17"/>
+    </row>
+    <row r="20" spans="2:5">
+      <c r="B20" s="17" t="s">
+        <v>786</v>
+      </c>
+      <c r="C20" s="17"/>
+    </row>
+    <row r="21" spans="2:5">
+      <c r="C21" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5">
+      <c r="D22" t="s">
+        <v>790</v>
+      </c>
+      <c r="E22" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5">
+      <c r="D23" t="s">
+        <v>792</v>
+      </c>
+      <c r="E23" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5">
+      <c r="D24" t="s">
+        <v>794</v>
+      </c>
+      <c r="E24" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5">
+      <c r="C25" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5">
+      <c r="C26" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5">
+      <c r="B27" s="17" t="s">
+        <v>788</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2">
+      <c r="B2" s="7" t="s">
+        <v>811</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:O20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:15">
       <c r="B2" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="4" spans="2:15">
       <c r="C4" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
     </row>
     <row r="5" spans="2:15">
       <c r="C5" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
     </row>
     <row r="6" spans="2:15">
       <c r="C6" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
     </row>
     <row r="8" spans="2:15">
       <c r="F8" s="99" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="L8" s="100" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="M8" s="101"/>
       <c r="N8" s="101"/>
@@ -21008,13 +21352,13 @@
     </row>
     <row r="9" spans="2:15">
       <c r="F9" s="95" t="s">
+        <v>709</v>
+      </c>
+      <c r="G9" t="s">
+        <v>711</v>
+      </c>
+      <c r="L9" s="96" t="s">
         <v>712</v>
-      </c>
-      <c r="G9" t="s">
-        <v>714</v>
-      </c>
-      <c r="L9" s="96" t="s">
-        <v>715</v>
       </c>
       <c r="M9" s="97"/>
       <c r="N9" s="97"/>
@@ -21022,40 +21366,40 @@
     </row>
     <row r="11" spans="2:15">
       <c r="E11" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="L11" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
     </row>
     <row r="16" spans="2:15">
       <c r="D16" t="s">
-        <v>719</v>
-      </c>
-      <c r="I16" s="115" t="s">
-        <v>723</v>
-      </c>
-      <c r="J16" s="116"/>
+        <v>716</v>
+      </c>
+      <c r="I16" s="116" t="s">
+        <v>720</v>
+      </c>
+      <c r="J16" s="117"/>
     </row>
     <row r="17" spans="3:10" ht="15" customHeight="1">
-      <c r="I17" s="117"/>
-      <c r="J17" s="118"/>
+      <c r="I17" s="118"/>
+      <c r="J17" s="119"/>
     </row>
     <row r="18" spans="3:10">
       <c r="D18" t="s">
-        <v>720</v>
-      </c>
-      <c r="I18" s="119"/>
-      <c r="J18" s="120"/>
+        <v>717</v>
+      </c>
+      <c r="I18" s="120"/>
+      <c r="J18" s="121"/>
     </row>
     <row r="19" spans="3:10">
       <c r="C19" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
     </row>
     <row r="20" spans="3:10">
       <c r="D20" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
     </row>
   </sheetData>
@@ -21069,10 +21413,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:G92"/>
+  <dimension ref="B1:G96"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="50.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="54.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="68.5703125" customWidth="1"/>
     <col min="6" max="6" width="9.7109375" customWidth="1"/>
@@ -21804,7 +22148,7 @@
         <v>287</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D49" s="51">
         <v>0.9</v>
@@ -21819,7 +22163,7 @@
         <v>319</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="D50" s="42">
         <v>1</v>
@@ -21834,7 +22178,7 @@
         <v>320</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="16" t="s">
@@ -21847,7 +22191,7 @@
         <v>321</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D52" s="42">
         <v>1</v>
@@ -21892,7 +22236,7 @@
         <v>447</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="D55" s="42">
         <v>1</v>
@@ -21913,7 +22257,7 @@
         <v>1</v>
       </c>
       <c r="E56" s="16" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F56" s="6"/>
     </row>
@@ -21922,7 +22266,7 @@
         <v>16.100000000000001</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D57" s="42">
         <v>1</v>
@@ -21967,7 +22311,7 @@
         <v>16.399999999999999</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="D60" s="42">
         <v>1</v>
@@ -21982,7 +22326,7 @@
         <v>16.5</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="D61" s="42">
         <v>1</v>
@@ -21997,7 +22341,7 @@
         <v>16.600000000000001</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="D62" s="42">
         <v>1</v>
@@ -22018,7 +22362,7 @@
         <v>1</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="F63" s="16" t="s">
         <v>14</v>
@@ -22040,7 +22384,7 @@
         <v>17.100000000000001</v>
       </c>
       <c r="C65" s="78" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D65" s="6"/>
       <c r="E65" s="6"/>
@@ -22062,11 +22406,11 @@
         <v>17.3</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D67" s="6"/>
       <c r="E67" s="16" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F67" s="6"/>
     </row>
@@ -22130,7 +22474,7 @@
         <v>18.3</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D73" s="6"/>
       <c r="E73" s="6"/>
@@ -22141,7 +22485,7 @@
         <v>18.399999999999999</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D74" s="6"/>
       <c r="E74" s="6"/>
@@ -22152,26 +22496,34 @@
         <v>462</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>463</v>
-      </c>
-      <c r="D75" s="6"/>
+        <v>814</v>
+      </c>
+      <c r="D75" s="51">
+        <v>0.9</v>
+      </c>
       <c r="E75" s="6"/>
-      <c r="F75" s="6"/>
+      <c r="F75" s="43" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="5">
         <v>19.100000000000001</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>481</v>
-      </c>
-      <c r="D76" s="6"/>
+        <v>480</v>
+      </c>
+      <c r="D76" s="51">
+        <v>0.9</v>
+      </c>
       <c r="E76" s="6"/>
-      <c r="F76" s="6"/>
+      <c r="F76" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="5" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>437</v>
@@ -22182,7 +22534,7 @@
     </row>
     <row r="78" spans="2:6">
       <c r="B78" s="5" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>288</v>
@@ -22207,7 +22559,7 @@
         <v>21.2</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D80" s="6"/>
       <c r="E80" s="6"/>
@@ -22215,29 +22567,29 @@
     </row>
     <row r="81" spans="2:7">
       <c r="B81" s="5" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>323</v>
       </c>
       <c r="D81" s="6"/>
       <c r="E81" s="16" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F81" s="6"/>
     </row>
     <row r="82" spans="2:7" ht="30">
       <c r="B82" s="5" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D82" s="42">
         <v>1</v>
       </c>
       <c r="E82" s="16" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F82" s="16"/>
     </row>
@@ -22246,7 +22598,7 @@
         <v>24.1</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="D83" s="42">
         <v>1</v>
@@ -22261,7 +22613,7 @@
         <v>24.2</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="D84" s="42">
         <v>1</v>
@@ -22274,21 +22626,25 @@
     </row>
     <row r="85" spans="2:7">
       <c r="B85" s="5" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D85" s="6"/>
+        <v>478</v>
+      </c>
+      <c r="D85" s="42">
+        <v>1</v>
+      </c>
       <c r="E85" s="16"/>
-      <c r="F85" s="6"/>
+      <c r="F85" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="86" spans="2:7">
       <c r="B86" s="5" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D86" s="6"/>
       <c r="E86" s="16"/>
@@ -22296,23 +22652,23 @@
     </row>
     <row r="87" spans="2:7" ht="60">
       <c r="B87" s="5" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C87" s="79" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D87" s="6"/>
       <c r="E87" s="16" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F87" s="6"/>
     </row>
-    <row r="88" spans="2:7" ht="30">
+    <row r="88" spans="2:7" ht="45">
       <c r="B88" s="5" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>485</v>
+        <v>781</v>
       </c>
       <c r="D88" s="6"/>
       <c r="E88" s="16"/>
@@ -22320,53 +22676,103 @@
     </row>
     <row r="89" spans="2:7">
       <c r="B89" s="5" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="D89" s="6"/>
+        <v>484</v>
+      </c>
+      <c r="D89" s="51">
+        <v>0</v>
+      </c>
       <c r="E89" s="16"/>
       <c r="F89" s="6"/>
     </row>
-    <row r="90" spans="2:7" ht="60">
+    <row r="90" spans="2:7">
       <c r="B90" s="5" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>489</v>
-      </c>
-      <c r="D90" s="6"/>
+        <v>815</v>
+      </c>
+      <c r="D90" s="51">
+        <v>0</v>
+      </c>
       <c r="E90" s="16"/>
       <c r="F90" s="6"/>
     </row>
-    <row r="91" spans="2:7" ht="30">
-      <c r="B91" s="5" t="s">
-        <v>494</v>
+    <row r="91" spans="2:7">
+      <c r="B91" s="5">
+        <v>30.1</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>477</v>
-      </c>
-      <c r="D91" s="42">
-        <v>0</v>
-      </c>
+        <v>811</v>
+      </c>
+      <c r="D91" s="51"/>
       <c r="E91" s="16"/>
       <c r="F91" s="16" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="92" spans="2:7">
-      <c r="B92" s="77" t="s">
-        <v>474</v>
-      </c>
-      <c r="C92" s="57" t="s">
+      <c r="B92" s="5">
+        <v>30.2</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="D92" s="51"/>
+      <c r="E92" s="16"/>
+      <c r="F92" s="6"/>
+    </row>
+    <row r="93" spans="2:7">
+      <c r="B93" s="5">
+        <v>30.3</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>813</v>
+      </c>
+      <c r="D93" s="51"/>
+      <c r="E93" s="16"/>
+      <c r="F93" s="6"/>
+    </row>
+    <row r="94" spans="2:7" ht="30">
+      <c r="B94" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="D94" s="51">
+        <v>0</v>
+      </c>
+      <c r="E94" s="16"/>
+      <c r="F94" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="95" spans="2:7">
+      <c r="B95" s="5" t="s">
+        <v>779</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>780</v>
+      </c>
+      <c r="D95" s="42"/>
+      <c r="E95" s="16"/>
+      <c r="F95" s="16"/>
+    </row>
+    <row r="96" spans="2:7">
+      <c r="B96" s="77" t="s">
         <v>473</v>
       </c>
-      <c r="D92" s="1"/>
-      <c r="E92" s="49" t="s">
+      <c r="C96" s="57" t="s">
         <v>472</v>
       </c>
-      <c r="F92" s="1"/>
+      <c r="D96" s="1"/>
+      <c r="E96" s="49" t="s">
+        <v>471</v>
+      </c>
+      <c r="F96" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -22420,7 +22826,7 @@
     <hyperlink ref="E67" r:id="rId8"/>
     <hyperlink ref="E81" r:id="rId9"/>
     <hyperlink ref="E82" r:id="rId10"/>
-    <hyperlink ref="E92" r:id="rId11"/>
+    <hyperlink ref="E96" r:id="rId11"/>
     <hyperlink ref="F49" location="'#9'!B2" display="Link"/>
     <hyperlink ref="F52" location="'#12'!B2" display="Link"/>
     <hyperlink ref="F57" location="'#16'!B2" display="Link"/>
@@ -22433,10 +22839,13 @@
     <hyperlink ref="F55" location="'#15'!B2" display="Link"/>
     <hyperlink ref="F62" location="'#16'!B89" display="Link"/>
     <hyperlink ref="F63" location="'#16'!B10" display="Link"/>
-    <hyperlink ref="F91" location="'#31'!B2" display="Link"/>
+    <hyperlink ref="F94" location="'#31'!B2" display="Link"/>
     <hyperlink ref="F83" location="'#24'!B2" display="Link"/>
     <hyperlink ref="F84" location="'#24'!B2" display="Link"/>
     <hyperlink ref="F84:G84" location="'#24'!B26" display="Link"/>
+    <hyperlink ref="F85" location="'#25'!B2" display="Link"/>
+    <hyperlink ref="F76" location="'#19'!B2" display="Link"/>
+    <hyperlink ref="F91" location="'#30'!B2" display="Link"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId12"/>
@@ -22754,7 +23163,7 @@
       <c r="D12" s="11"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" thickBot="1">
-      <c r="C13" s="110" t="s">
+      <c r="C13" s="111" t="s">
         <v>78</v>
       </c>
       <c r="D13" s="26" t="s">
@@ -22771,7 +23180,7 @@
       <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:10" ht="15.75" thickBot="1">
-      <c r="C14" s="111"/>
+      <c r="C14" s="112"/>
       <c r="D14" s="23" t="s">
         <v>65</v>
       </c>
@@ -22787,7 +23196,7 @@
       <c r="J14" s="25"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="C15" s="111"/>
+      <c r="C15" s="112"/>
       <c r="D15" s="26" t="s">
         <v>66</v>
       </c>
@@ -22802,7 +23211,7 @@
       <c r="I15" s="28"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="C16" s="111"/>
+      <c r="C16" s="112"/>
       <c r="D16" s="29"/>
       <c r="E16" s="30" t="s">
         <v>74</v>
@@ -22813,7 +23222,7 @@
       <c r="I16" s="31"/>
     </row>
     <row r="17" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C17" s="112"/>
+      <c r="C17" s="113"/>
       <c r="D17" s="32"/>
       <c r="E17" s="33" t="s">
         <v>75</v>
@@ -22844,7 +23253,7 @@
       <c r="L18" s="25"/>
     </row>
     <row r="19" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C19" s="110" t="s">
+      <c r="C19" s="111" t="s">
         <v>78</v>
       </c>
       <c r="D19" s="23" t="s">
@@ -22855,7 +23264,7 @@
       </c>
     </row>
     <row r="20" spans="3:12">
-      <c r="C20" s="111"/>
+      <c r="C20" s="112"/>
       <c r="D20" s="26" t="s">
         <v>82</v>
       </c>
@@ -22864,7 +23273,7 @@
       </c>
     </row>
     <row r="21" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C21" s="112"/>
+      <c r="C21" s="113"/>
       <c r="D21" s="32"/>
       <c r="E21" s="40" t="s">
         <v>84</v>

--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Knowhow" sheetId="1" r:id="rId1"/>
@@ -31,6 +31,7 @@
     <sheet name="#29" sheetId="23" r:id="rId22"/>
     <sheet name="#30" sheetId="24" r:id="rId23"/>
     <sheet name="#31" sheetId="19" r:id="rId24"/>
+    <sheet name="#32" sheetId="25" r:id="rId25"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="816">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="855">
   <si>
     <t>No.</t>
   </si>
@@ -3853,9 +3854,6 @@
     <t>File anh Thư</t>
   </si>
   <si>
-    <t>How do vectors differ from arrays in C++?</t>
-  </si>
-  <si>
     <t>Unordered_map, map, set, priority_queue, list, …</t>
   </si>
   <si>
@@ -6954,205 +6952,6 @@
   </si>
   <si>
     <r>
-      <t>singleton</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFCCCCCC"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF4EC9B0"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>singleton</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF569CD6"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>&amp;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFCCCCCC"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF9CDCFE"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>ins</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFCCCCCC"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFD4D4D4"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF569CD6"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>delete</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFCCCCCC"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>singleton</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF569CD6"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>&amp;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFCCCCCC"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFDCDCAA"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>operator=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFCCCCCC"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF4EC9B0"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>singleton</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF569CD6"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>&amp;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFCCCCCC"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF9CDCFE"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>ins</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFCCCCCC"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFD4D4D4"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF569CD6"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>delete</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFCCCCCC"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>;</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>int</t>
     </r>
     <r>
@@ -10283,6 +10082,663 @@
   </si>
   <si>
     <t xml:space="preserve"> Casting in cpp</t>
+  </si>
+  <si>
+    <r>
+      <t>singleton</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">(const </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>singleton</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&amp;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ins</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>delete</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>singleton</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&amp;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>operator=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> (const </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>singleton</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&amp;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ins</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>delete</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <t>Trong C++ thì Vector và Array khác nhau như thế nào</t>
+  </si>
+  <si>
+    <t>array</t>
+  </si>
+  <si>
+    <t>là một biến dạng con trỏ, trỏ đến phần tử đầu tiên của 1 vùng nhớ các phần tử liền kề nhau</t>
+  </si>
+  <si>
+    <t>vector</t>
+  </si>
+  <si>
+    <t>Cũng giống vector, nhưng có thể điều chỉnh kích thước các phần tử dễ dàng. Không cần tạo vùng chứa mới và gán lại toàn bộ (trừ khi vượt size trong vùng nhớ)</t>
+  </si>
+  <si>
+    <t>vector gồm 1 con trỏ quản lý và 1 biến data chứa các phần tử liền kề.</t>
+  </si>
+  <si>
+    <t>khi mới khởi tạo, size của data trong vùng nhớ thường mặc định là x2 so với khai báo thực tế</t>
+  </si>
+  <si>
+    <t>vector có dung lượng là 24 byte, gồm 3 con trỏ :</t>
+  </si>
+  <si>
+    <t>|10|20|30|  |  |</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ^       ^    ^</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> |       |    |</t>
+  </si>
+  <si>
+    <t>start  finish  end_of_storage</t>
+  </si>
+  <si>
+    <t>_M_start trỏ vào 10</t>
+  </si>
+  <si>
+    <t>_M_finish trỏ vào ô sau 30</t>
+  </si>
+  <si>
+    <t>_M_end_of_storage trỏ vào cuối vùng capacity</t>
+  </si>
+  <si>
+    <t>các phương thức của vector :</t>
+  </si>
+  <si>
+    <t>vector&lt;int&gt; vec;</t>
+  </si>
+  <si>
+    <t>Thêm 1 phần tử vào cuối</t>
+  </si>
+  <si>
+    <t>Xóa 1 phần tử ở cuối</t>
+  </si>
+  <si>
+    <t>Truy cập phần tử và kiểm tra xem có hợp lệ không, nếu truy cập ngoài phạm vi thì tránh được Undefined Behavior và sẽ ném ra ngoại lệ</t>
+  </si>
+  <si>
+    <r>
+      <t>vec.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>at(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>vec.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pop_back()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>vec.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>push_back(8)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <t>Hãy cung cấp capibility &gt;=10 cho vector, để giới hạn 1 khoảng trên cho vec</t>
+  </si>
+  <si>
+    <r>
+      <t>vec.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>reverse</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(10);</t>
+    </r>
+  </si>
+  <si>
+    <t>erase()</t>
+  </si>
+  <si>
+    <t>là hàm của vector, thuộc thư viện #include&lt;vector&gt;</t>
+  </si>
+  <si>
+    <t>// xóa phần tử từ thứ 2 đến thứ 5</t>
+  </si>
+  <si>
+    <r>
+      <t>vec.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>erase(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>vec</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.begin()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+1,vec.begin()+5);</t>
+    </r>
+  </si>
+  <si>
+    <t>tác dụng là xóa 1 đoạn của vector, khi cung cấp interior bắt đầu xóa và interior kết thúc xóa</t>
+  </si>
+  <si>
+    <t>remove()</t>
+  </si>
+  <si>
+    <t>là hàm của thư viện #include&lt;algorithm&gt;</t>
+  </si>
+  <si>
+    <r>
+      <t>tác dụng là đẩy các phần tử được đưa ra xuống cuối mảng, vector : Ví dụ : {1,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2,2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,3,7,7} =&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>đối số truyền vào cũng cần là interior</t>
+  </si>
+  <si>
+    <r>
+      <t>remove(vec.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>begin()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+1,vec.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>end()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>8798</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>remove(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>arr+1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>arr+5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>8798</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>// Đẩy hết 8798 về cuối của vector</t>
+  </si>
+  <si>
+    <t>// Đẩy hết 8798 về cuối của array</t>
+  </si>
+  <si>
+    <t>return ra interior trỏ vào phần tử không hợp lệ đầu tiên</t>
+  </si>
+  <si>
+    <r>
+      <t>Nếu gọi remove giá trị 2 -&gt; {1,3,7,7,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2,2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">}, sau đó return vào interior ở vị trí số </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> đầu tiên</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -15310,19 +15766,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:K22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="5.7109375" customWidth="1"/>
-    <col min="3" max="3" width="37.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.42578125" customWidth="1"/>
+    <col min="2" max="2" width="5.7265625" customWidth="1"/>
+    <col min="3" max="3" width="37.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.453125" customWidth="1"/>
     <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7265625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="18.75">
+    <row r="2" spans="2:11" ht="18.5">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -15348,7 +15804,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:11" ht="45">
+    <row r="3" spans="2:11" ht="43.5">
       <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
@@ -15702,9 +16158,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Q30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="11" max="11" width="3.7109375" customWidth="1"/>
+    <col min="11" max="11" width="3.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:17">
@@ -16034,12 +16490,12 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E76"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="4.42578125" customWidth="1"/>
-    <col min="3" max="3" width="39.7109375" customWidth="1"/>
-    <col min="4" max="4" width="50.85546875" customWidth="1"/>
-    <col min="5" max="5" width="75.42578125" customWidth="1"/>
+    <col min="2" max="2" width="4.453125" customWidth="1"/>
+    <col min="3" max="3" width="39.7265625" customWidth="1"/>
+    <col min="4" max="4" width="50.81640625" customWidth="1"/>
+    <col min="5" max="5" width="75.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.5">
@@ -16047,7 +16503,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="23.25">
+    <row r="2" spans="1:5" ht="23.5">
       <c r="B2" s="63" t="s">
         <v>420</v>
       </c>
@@ -16066,7 +16522,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="45">
+    <row r="5" spans="1:5" ht="43.5">
       <c r="B5" s="69">
         <v>1</v>
       </c>
@@ -16094,7 +16550,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5" ht="29">
       <c r="B7" s="69">
         <v>3</v>
       </c>
@@ -16108,7 +16564,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="23.25">
+    <row r="10" spans="1:5" ht="23.5">
       <c r="B10" s="63" t="s">
         <v>344</v>
       </c>
@@ -16127,7 +16583,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="30">
+    <row r="13" spans="1:5">
       <c r="B13" s="69">
         <v>1</v>
       </c>
@@ -16141,7 +16597,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="30">
+    <row r="14" spans="1:5" ht="29">
       <c r="B14" s="69">
         <v>2</v>
       </c>
@@ -16155,7 +16611,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="30">
+    <row r="15" spans="1:5" ht="29">
       <c r="B15" s="69">
         <v>3</v>
       </c>
@@ -16169,7 +16625,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30">
+    <row r="16" spans="1:5" ht="29">
       <c r="B16" s="69">
         <v>4</v>
       </c>
@@ -16183,7 +16639,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="165">
+    <row r="17" spans="2:5" ht="145">
       <c r="B17" s="69">
         <v>5</v>
       </c>
@@ -16197,7 +16653,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="180">
+    <row r="18" spans="2:5" ht="159.5">
       <c r="B18" s="69">
         <v>6</v>
       </c>
@@ -16211,7 +16667,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="135">
+    <row r="19" spans="2:5" ht="130.5">
       <c r="B19" s="69">
         <v>7</v>
       </c>
@@ -16225,7 +16681,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="135">
+    <row r="20" spans="2:5" ht="130.5">
       <c r="B20" s="69">
         <v>8</v>
       </c>
@@ -16239,7 +16695,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="23" spans="2:5" ht="23.25">
+    <row r="23" spans="2:5" ht="23.5">
       <c r="B23" s="63" t="s">
         <v>419</v>
       </c>
@@ -16306,7 +16762,7 @@
       </c>
       <c r="E29" s="1"/>
     </row>
-    <row r="32" spans="2:5" ht="23.25">
+    <row r="32" spans="2:5" ht="23.5">
       <c r="B32" s="63" t="s">
         <v>418</v>
       </c>
@@ -16322,7 +16778,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="35" spans="2:4" ht="30">
+    <row r="35" spans="2:4" ht="29">
       <c r="B35" s="65">
         <v>1</v>
       </c>
@@ -16344,7 +16800,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="37" spans="2:4" ht="30">
+    <row r="37" spans="2:4">
       <c r="B37" s="65">
         <v>3</v>
       </c>
@@ -16366,7 +16822,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="41" spans="2:4" ht="23.25">
+    <row r="41" spans="2:4" ht="23.5">
       <c r="B41" s="63" t="s">
         <v>417</v>
       </c>
@@ -16382,7 +16838,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="44" spans="2:4" ht="30">
+    <row r="44" spans="2:4">
       <c r="B44" s="65">
         <v>1</v>
       </c>
@@ -16426,7 +16882,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="50" spans="2:4" ht="23.25">
+    <row r="50" spans="2:4" ht="23.5">
       <c r="B50" s="63" t="s">
         <v>416</v>
       </c>
@@ -16478,7 +16934,7 @@
     <row r="56" spans="2:4">
       <c r="B56" s="65"/>
     </row>
-    <row r="58" spans="2:4" ht="23.25">
+    <row r="58" spans="2:4" ht="23.5">
       <c r="B58" s="63" t="s">
         <v>415</v>
       </c>
@@ -16505,7 +16961,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="62" spans="2:4" ht="45">
+    <row r="62" spans="2:4" ht="29">
       <c r="B62" s="65">
         <v>2</v>
       </c>
@@ -16516,7 +16972,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="63" spans="2:4" ht="30">
+    <row r="63" spans="2:4" ht="29">
       <c r="B63" s="65">
         <v>3</v>
       </c>
@@ -16549,7 +17005,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="68" spans="2:4" ht="23.25">
+    <row r="68" spans="2:4" ht="23.5">
       <c r="B68" s="63" t="s">
         <v>400</v>
       </c>
@@ -16640,7 +17096,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:S38"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -16649,72 +17105,72 @@
     </row>
     <row r="3" spans="2:5">
       <c r="C3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="5" spans="2:5">
       <c r="C5" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="D6" t="s">
+        <v>493</v>
+      </c>
+      <c r="E6" t="s">
         <v>494</v>
-      </c>
-      <c r="E6" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="D7" t="s">
+        <v>495</v>
+      </c>
+      <c r="E7" t="s">
         <v>496</v>
-      </c>
-      <c r="E7" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="C9" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="C11" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="D12" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="C15" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="17" spans="3:19">
       <c r="D17" s="83" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E17" s="87"/>
       <c r="F17" s="87"/>
       <c r="G17" s="87"/>
       <c r="H17" s="87"/>
       <c r="I17" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="18" spans="3:19">
       <c r="D18" s="83" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E18" s="87"/>
       <c r="F18" s="87"/>
       <c r="G18" s="87"/>
       <c r="H18" s="87"/>
       <c r="I18" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="19" spans="3:19">
@@ -16726,31 +17182,31 @@
     </row>
     <row r="20" spans="3:19">
       <c r="D20" s="85" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E20" s="87"/>
       <c r="F20" s="87"/>
       <c r="G20" s="87"/>
       <c r="H20" s="87"/>
       <c r="I20" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="21" spans="3:19">
       <c r="D21" s="86" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E21" s="87"/>
       <c r="F21" s="87"/>
       <c r="G21" s="87"/>
       <c r="H21" s="87"/>
       <c r="I21" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="22" spans="3:19">
       <c r="D22" s="86" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E22" s="87"/>
       <c r="F22" s="87"/>
@@ -16775,7 +17231,7 @@
     </row>
     <row r="25" spans="3:19">
       <c r="D25" s="85" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E25" s="87"/>
       <c r="F25" s="87"/>
@@ -16784,7 +17240,7 @@
     </row>
     <row r="26" spans="3:19">
       <c r="D26" s="86" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E26" s="87"/>
       <c r="F26" s="87"/>
@@ -16793,7 +17249,7 @@
     </row>
     <row r="27" spans="3:19">
       <c r="D27" s="86" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E27" s="87"/>
       <c r="F27" s="87"/>
@@ -16811,7 +17267,7 @@
     </row>
     <row r="31" spans="3:19">
       <c r="C31" s="88" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D31" s="88"/>
       <c r="E31" s="88"/>
@@ -16823,7 +17279,7 @@
       <c r="K31" s="88"/>
       <c r="L31" s="88"/>
       <c r="M31" s="89" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="N31" s="89"/>
       <c r="O31" s="89"/>
@@ -16854,7 +17310,7 @@
     <row r="33" spans="3:19">
       <c r="C33" s="88"/>
       <c r="D33" s="88" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="E33" s="88"/>
       <c r="F33" s="88"/>
@@ -16865,7 +17321,7 @@
       <c r="K33" s="88"/>
       <c r="L33" s="88"/>
       <c r="M33" s="89" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="N33" s="89"/>
       <c r="O33" s="89"/>
@@ -16886,7 +17342,7 @@
       <c r="K34" s="88"/>
       <c r="L34" s="88"/>
       <c r="M34" s="89" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="N34" s="89"/>
       <c r="O34" s="89"/>
@@ -16919,7 +17375,7 @@
     <row r="36" spans="3:19">
       <c r="C36" s="88"/>
       <c r="D36" s="88" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E36" s="88"/>
       <c r="F36" s="88"/>
@@ -16933,7 +17389,7 @@
     <row r="37" spans="3:19">
       <c r="C37" s="88"/>
       <c r="D37" s="88" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E37" s="88"/>
       <c r="F37" s="88"/>
@@ -16967,105 +17423,105 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:M57"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="C4" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="D6" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="D7" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="D8" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E8" s="80"/>
     </row>
     <row r="9" spans="2:5">
       <c r="D9" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="D10" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="D11" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="D12" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="D13" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="D14" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="D15" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="D16" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="17" spans="3:12">
       <c r="D17" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="18" spans="3:12">
       <c r="D18" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="19" spans="3:12">
       <c r="D19" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="22" spans="3:12">
       <c r="C22" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="23" spans="3:12">
       <c r="D23" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="L23" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="24" spans="3:12">
       <c r="D24" s="81" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E24" s="90"/>
       <c r="F24" s="90"/>
@@ -17076,7 +17532,7 @@
     </row>
     <row r="25" spans="3:12">
       <c r="D25" s="81" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E25" s="90"/>
       <c r="F25" s="90"/>
@@ -17087,12 +17543,12 @@
     </row>
     <row r="27" spans="3:12">
       <c r="D27" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="28" spans="3:12">
       <c r="D28" s="81" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E28" s="90"/>
       <c r="F28" s="90"/>
@@ -17103,7 +17559,7 @@
     </row>
     <row r="29" spans="3:12">
       <c r="D29" s="81" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E29" s="90"/>
       <c r="F29" s="90"/>
@@ -17114,7 +17570,7 @@
     </row>
     <row r="30" spans="3:12">
       <c r="D30" s="82" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E30" s="90"/>
       <c r="F30" s="90"/>
@@ -17125,42 +17581,42 @@
     </row>
     <row r="33" spans="3:13">
       <c r="D33" s="91" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="34" spans="3:13">
       <c r="E34" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="35" spans="3:13">
       <c r="F35" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="36" spans="3:13">
       <c r="F36" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="39" spans="3:13">
       <c r="C39" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="41" spans="3:13">
       <c r="D41" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="43" spans="3:13">
       <c r="D43" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="44" spans="3:13">
       <c r="E44" s="81" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F44" s="90"/>
       <c r="G44" s="90"/>
@@ -17184,7 +17640,7 @@
     </row>
     <row r="46" spans="3:13">
       <c r="E46" s="81" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="F46" s="90"/>
       <c r="G46" s="90"/>
@@ -17197,7 +17653,7 @@
     </row>
     <row r="47" spans="3:13">
       <c r="E47" s="81" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="F47" s="90"/>
       <c r="G47" s="90"/>
@@ -17210,7 +17666,7 @@
     </row>
     <row r="48" spans="3:13">
       <c r="E48" s="81" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="F48" s="90"/>
       <c r="G48" s="90"/>
@@ -17223,7 +17679,7 @@
     </row>
     <row r="49" spans="4:13">
       <c r="E49" s="82" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F49" s="90"/>
       <c r="G49" s="90"/>
@@ -17236,7 +17692,7 @@
     </row>
     <row r="50" spans="4:13">
       <c r="E50" s="81" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="F50" s="90"/>
       <c r="G50" s="90"/>
@@ -17249,27 +17705,27 @@
     </row>
     <row r="53" spans="4:13">
       <c r="D53" s="91" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="54" spans="4:13">
       <c r="E54" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="55" spans="4:13">
       <c r="E55" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="56" spans="4:13">
       <c r="E56" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="57" spans="4:13">
       <c r="E57" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
   </sheetData>
@@ -17281,93 +17737,93 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3" spans="2:5">
       <c r="C3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D3" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E3" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="C4" s="80" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D4" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="C7" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="C8" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="C10" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="C11" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="C12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="C13" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="C14" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="C15" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="C16" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="17" spans="3:3">
       <c r="C17" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="18" spans="3:3">
       <c r="C18" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="20" spans="3:3">
       <c r="C20" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="21" spans="3:3">
@@ -17377,17 +17833,17 @@
     </row>
     <row r="23" spans="3:3">
       <c r="C23" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="24" spans="3:3">
       <c r="C24" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="25" spans="3:3">
       <c r="C25" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
@@ -17398,74 +17854,74 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="3" spans="2:5">
       <c r="C3" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="C4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="C6" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="D7" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="D8" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="C10" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="C11" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="D12" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="C13" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="D14" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E14" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="C15" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="D16" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
   </sheetData>
@@ -17476,7 +17932,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
@@ -17523,234 +17979,234 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I48"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" ht="18.75">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" ht="18.5">
       <c r="C3" s="93" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D3" s="94"/>
     </row>
     <row r="5" spans="2:4">
       <c r="C5" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D5" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="6" spans="2:4">
       <c r="D6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="7" spans="2:4">
       <c r="D7" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="8" spans="2:4">
       <c r="D8" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="9" spans="2:4">
       <c r="D9" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="11" spans="2:4">
       <c r="C11" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D11" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="12" spans="2:4">
       <c r="D12" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="13" spans="2:4">
       <c r="D13" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="14" spans="2:4">
       <c r="D14" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="15" spans="2:4">
       <c r="D15" s="92" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="16" spans="2:4">
       <c r="D16" s="76" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="17" spans="3:5">
       <c r="C17" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D17" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="18" spans="3:5">
       <c r="D18" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="19" spans="3:5">
       <c r="E19" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="20" spans="3:5">
       <c r="E20" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="21" spans="3:5">
       <c r="D21" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="22" spans="3:5">
       <c r="D22" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="23" spans="3:5">
       <c r="D23" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="24" spans="3:5">
       <c r="D24" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="26" spans="3:5">
       <c r="C26" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D26" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="27" spans="3:5">
       <c r="D27" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="28" spans="3:5">
       <c r="E28" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="29" spans="3:5">
       <c r="E29" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" ht="18.75">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" ht="18.5">
       <c r="C33" s="93" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D33" s="94"/>
     </row>
     <row r="35" spans="3:9">
       <c r="C35" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="36" spans="3:9">
       <c r="D36" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="38" spans="3:9">
       <c r="D38" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="39" spans="3:9">
       <c r="E39" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="40" spans="3:9">
       <c r="E40" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G40" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="I40" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="41" spans="3:9">
       <c r="E41" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="G41" t="s">
+        <v>685</v>
+      </c>
+      <c r="I41" t="s">
         <v>686</v>
-      </c>
-      <c r="I41" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="42" spans="3:9">
       <c r="E42" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="G42" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="44" spans="3:9">
       <c r="D44" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="45" spans="3:9">
       <c r="E45" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="46" spans="3:9">
       <c r="E46" t="s">
+        <v>690</v>
+      </c>
+      <c r="G46" t="s">
         <v>691</v>
-      </c>
-      <c r="G46" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="47" spans="3:9">
       <c r="E47" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="G47" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="48" spans="3:9">
       <c r="E48" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="G48" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
   </sheetData>
@@ -17762,7 +18218,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I101"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
@@ -17771,26 +18227,26 @@
     </row>
     <row r="3" spans="2:4">
       <c r="C3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D3" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="C4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="5" spans="2:4">
       <c r="C5" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D5" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="10" spans="2:4">
@@ -17800,62 +18256,62 @@
     </row>
     <row r="11" spans="2:4">
       <c r="C11" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="12" spans="2:4">
       <c r="C12" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="13" spans="2:4">
       <c r="C13" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="14" spans="2:4">
       <c r="C14" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="16" spans="2:4">
       <c r="C16" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="17" spans="2:5">
       <c r="C17" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="18" spans="2:5">
       <c r="C18" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="19" spans="2:5">
       <c r="C19" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="20" spans="2:5">
       <c r="C20" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="22" spans="2:5">
       <c r="D22" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="23" spans="2:5">
       <c r="E23" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="24" spans="2:5">
       <c r="E24" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="25" spans="2:5">
@@ -17870,162 +18326,162 @@
     </row>
     <row r="29" spans="2:5">
       <c r="C29" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="30" spans="2:5">
       <c r="D30" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="31" spans="2:5">
       <c r="D31" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="32" spans="2:5">
       <c r="D32" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="34" spans="3:5">
       <c r="D34" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="36" spans="3:5">
       <c r="D36" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="37" spans="3:5">
       <c r="E37" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="38" spans="3:5">
       <c r="E38" s="17" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="39" spans="3:5">
       <c r="E39" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="41" spans="3:5">
       <c r="E41" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="42" spans="3:5">
       <c r="E42" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="43" spans="3:5">
       <c r="E43" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="45" spans="3:5">
       <c r="C45" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="46" spans="3:5">
       <c r="D46" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="47" spans="3:5">
       <c r="D47" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="49" spans="2:5">
       <c r="D49" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="50" spans="2:5">
       <c r="E50" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="51" spans="2:5">
       <c r="E51" s="17" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="52" spans="2:5">
       <c r="E52" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="54" spans="2:5">
       <c r="E54" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="55" spans="2:5">
       <c r="E55" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="56" spans="2:5">
       <c r="E56" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="58" spans="2:5">
       <c r="D58" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="59" spans="2:5">
       <c r="D59" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="62" spans="2:5">
       <c r="B62" s="6" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="63" spans="2:5">
       <c r="C63" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="64" spans="2:5">
       <c r="C64" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="65" spans="3:4">
       <c r="C65" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="67" spans="3:4">
       <c r="C67" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="69" spans="3:4">
       <c r="D69" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="70" spans="3:4">
       <c r="D70" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="71" spans="3:4">
       <c r="D71" s="17" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="72" spans="3:4">
@@ -18035,22 +18491,22 @@
     </row>
     <row r="73" spans="3:4">
       <c r="D73" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="75" spans="3:4">
       <c r="D75" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="76" spans="3:4">
       <c r="D76" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="77" spans="3:4">
       <c r="D77" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="78" spans="3:4">
@@ -18060,32 +18516,32 @@
     </row>
     <row r="79" spans="3:4">
       <c r="D79" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="82" spans="2:9">
       <c r="B82" s="6" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="83" spans="2:9">
       <c r="C83" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="84" spans="2:9">
       <c r="C84" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="85" spans="2:9">
       <c r="C85" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="89" spans="2:9" ht="54" customHeight="1">
       <c r="B89" s="114" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C89" s="115"/>
       <c r="D89" s="115"/>
@@ -18097,52 +18553,52 @@
     </row>
     <row r="91" spans="2:9">
       <c r="B91" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="92" spans="2:9">
       <c r="C92" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="93" spans="2:9">
       <c r="C93" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="94" spans="2:9">
       <c r="D94" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="95" spans="2:9">
       <c r="D95" s="17" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="96" spans="2:9">
       <c r="C96" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="97" spans="3:4">
       <c r="D97" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="99" spans="3:4">
       <c r="C99" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="100" spans="3:4">
       <c r="C100" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="101" spans="3:4">
       <c r="C101" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
   </sheetData>
@@ -18157,7 +18613,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
@@ -18166,32 +18622,32 @@
     </row>
     <row r="3" spans="2:4">
       <c r="C3" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="C4" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
     </row>
     <row r="6" spans="2:4">
       <c r="C6" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
     </row>
     <row r="7" spans="2:4">
       <c r="C7" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
     </row>
     <row r="8" spans="2:4">
       <c r="D8" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
     </row>
     <row r="9" spans="2:4">
       <c r="D9" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
     </row>
   </sheetData>
@@ -18202,15 +18658,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:F103"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="3" max="3" width="12.28515625" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.26953125" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" customWidth="1"/>
+    <col min="5" max="5" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="18.75">
+    <row r="2" spans="2:6" ht="18.5">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -19353,16 +19809,16 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Q108"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:10">
       <c r="B2" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
     </row>
     <row r="3" spans="2:10">
       <c r="C3" s="103" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D3" s="104"/>
       <c r="E3" s="104"/>
@@ -19374,7 +19830,7 @@
     </row>
     <row r="4" spans="2:10">
       <c r="C4" s="105" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D4" s="104"/>
       <c r="E4" s="104"/>
@@ -19386,7 +19842,7 @@
     </row>
     <row r="5" spans="2:10">
       <c r="C5" s="103" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D5" s="104"/>
       <c r="E5" s="104"/>
@@ -19398,7 +19854,7 @@
     </row>
     <row r="6" spans="2:10">
       <c r="C6" s="103" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D6" s="104"/>
       <c r="E6" s="104"/>
@@ -19410,7 +19866,7 @@
     </row>
     <row r="7" spans="2:10">
       <c r="C7" s="105" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D7" s="104"/>
       <c r="E7" s="104"/>
@@ -19422,7 +19878,7 @@
     </row>
     <row r="8" spans="2:10">
       <c r="C8" s="105" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D8" s="104"/>
       <c r="E8" s="104"/>
@@ -19434,7 +19890,7 @@
     </row>
     <row r="9" spans="2:10">
       <c r="C9" s="105" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D9" s="104"/>
       <c r="E9" s="104"/>
@@ -19458,7 +19914,7 @@
     </row>
     <row r="11" spans="2:10">
       <c r="C11" s="103" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D11" s="104"/>
       <c r="E11" s="104"/>
@@ -19470,7 +19926,7 @@
     </row>
     <row r="12" spans="2:10">
       <c r="C12" s="106" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D12" s="104"/>
       <c r="E12" s="104"/>
@@ -19482,7 +19938,7 @@
     </row>
     <row r="13" spans="2:10">
       <c r="C13" s="106" t="s">
-        <v>727</v>
+        <v>813</v>
       </c>
       <c r="D13" s="104"/>
       <c r="E13" s="104"/>
@@ -19494,7 +19950,7 @@
     </row>
     <row r="14" spans="2:10">
       <c r="C14" s="107" t="s">
-        <v>728</v>
+        <v>814</v>
       </c>
       <c r="D14" s="104"/>
       <c r="E14" s="104"/>
@@ -19506,7 +19962,7 @@
     </row>
     <row r="15" spans="2:10">
       <c r="C15" s="105" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D15" s="104"/>
       <c r="E15" s="104"/>
@@ -19528,7 +19984,7 @@
     </row>
     <row r="17" spans="2:17">
       <c r="C17" s="103" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="D17" s="104"/>
       <c r="E17" s="104"/>
@@ -19540,7 +19996,7 @@
     </row>
     <row r="18" spans="2:17">
       <c r="C18" s="105" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D18" s="104"/>
       <c r="E18" s="104"/>
@@ -19552,7 +20008,7 @@
     </row>
     <row r="19" spans="2:17">
       <c r="C19" s="107" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="D19" s="104"/>
       <c r="E19" s="104"/>
@@ -19564,7 +20020,7 @@
     </row>
     <row r="20" spans="2:17">
       <c r="C20" s="107" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="D20" s="104"/>
       <c r="E20" s="104"/>
@@ -19576,7 +20032,7 @@
     </row>
     <row r="21" spans="2:17">
       <c r="C21" s="109" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="D21" s="104"/>
       <c r="E21" s="104"/>
@@ -19610,12 +20066,12 @@
     </row>
     <row r="26" spans="2:17">
       <c r="B26" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
     </row>
     <row r="27" spans="2:17">
       <c r="C27" s="109" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="D27" s="104"/>
       <c r="E27" s="104"/>
@@ -19634,7 +20090,7 @@
     </row>
     <row r="28" spans="2:17">
       <c r="C28" s="109" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D28" s="104"/>
       <c r="E28" s="104"/>
@@ -19653,7 +20109,7 @@
     </row>
     <row r="29" spans="2:17">
       <c r="C29" s="109" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="D29" s="104"/>
       <c r="E29" s="104"/>
@@ -19672,7 +20128,7 @@
     </row>
     <row r="30" spans="2:17">
       <c r="C30" s="109" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="D30" s="104"/>
       <c r="E30" s="104"/>
@@ -19708,7 +20164,7 @@
     </row>
     <row r="32" spans="2:17">
       <c r="C32" s="103" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="D32" s="104"/>
       <c r="E32" s="104"/>
@@ -19727,7 +20183,7 @@
     </row>
     <row r="33" spans="3:17">
       <c r="C33" s="105" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D33" s="104"/>
       <c r="E33" s="104"/>
@@ -19746,7 +20202,7 @@
     </row>
     <row r="34" spans="3:17">
       <c r="C34" s="103" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D34" s="104"/>
       <c r="E34" s="104"/>
@@ -19765,7 +20221,7 @@
     </row>
     <row r="35" spans="3:17">
       <c r="C35" s="106" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="D35" s="104"/>
       <c r="E35" s="104"/>
@@ -19784,7 +20240,7 @@
     </row>
     <row r="36" spans="3:17">
       <c r="C36" s="103" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="D36" s="104"/>
       <c r="E36" s="104"/>
@@ -19803,7 +20259,7 @@
     </row>
     <row r="37" spans="3:17">
       <c r="C37" s="103" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="D37" s="104"/>
       <c r="E37" s="104"/>
@@ -19822,7 +20278,7 @@
     </row>
     <row r="38" spans="3:17">
       <c r="C38" s="105" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D38" s="104"/>
       <c r="E38" s="104"/>
@@ -19858,7 +20314,7 @@
     </row>
     <row r="40" spans="3:17">
       <c r="C40" s="103" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="D40" s="104"/>
       <c r="E40" s="104"/>
@@ -19877,7 +20333,7 @@
     </row>
     <row r="41" spans="3:17">
       <c r="C41" s="105" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D41" s="104"/>
       <c r="E41" s="104"/>
@@ -19896,7 +20352,7 @@
     </row>
     <row r="42" spans="3:17">
       <c r="C42" s="103" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D42" s="104"/>
       <c r="E42" s="104"/>
@@ -19915,7 +20371,7 @@
     </row>
     <row r="43" spans="3:17">
       <c r="C43" s="107" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="D43" s="104"/>
       <c r="E43" s="104"/>
@@ -19934,7 +20390,7 @@
     </row>
     <row r="44" spans="3:17">
       <c r="C44" s="107" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="D44" s="104"/>
       <c r="E44" s="104"/>
@@ -19953,7 +20409,7 @@
     </row>
     <row r="45" spans="3:17">
       <c r="C45" s="103" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D45" s="104"/>
       <c r="E45" s="104"/>
@@ -19972,7 +20428,7 @@
     </row>
     <row r="46" spans="3:17">
       <c r="C46" s="103" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="D46" s="104"/>
       <c r="E46" s="104"/>
@@ -19991,7 +20447,7 @@
     </row>
     <row r="47" spans="3:17">
       <c r="C47" s="105" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D47" s="104"/>
       <c r="E47" s="104"/>
@@ -20010,7 +20466,7 @@
     </row>
     <row r="48" spans="3:17">
       <c r="C48" s="110" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="D48" s="104"/>
       <c r="E48" s="104"/>
@@ -20048,7 +20504,7 @@
     </row>
     <row r="50" spans="3:17">
       <c r="C50" s="103" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="D50" s="104"/>
       <c r="E50" s="104"/>
@@ -20067,7 +20523,7 @@
     </row>
     <row r="51" spans="3:17">
       <c r="C51" s="105" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D51" s="104"/>
       <c r="E51" s="104"/>
@@ -20086,7 +20542,7 @@
     </row>
     <row r="52" spans="3:17">
       <c r="C52" s="110" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="D52" s="104"/>
       <c r="E52" s="104"/>
@@ -20124,7 +20580,7 @@
     </row>
     <row r="54" spans="3:17">
       <c r="C54" s="103" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="D54" s="104"/>
       <c r="E54" s="104"/>
@@ -20143,7 +20599,7 @@
     </row>
     <row r="55" spans="3:17">
       <c r="C55" s="105" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D55" s="104"/>
       <c r="E55" s="104"/>
@@ -20162,7 +20618,7 @@
     </row>
     <row r="56" spans="3:17">
       <c r="C56" s="105" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="D56" s="104"/>
       <c r="E56" s="104"/>
@@ -20181,7 +20637,7 @@
     </row>
     <row r="57" spans="3:17">
       <c r="C57" s="105" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="D57" s="104"/>
       <c r="E57" s="104"/>
@@ -20200,7 +20656,7 @@
     </row>
     <row r="58" spans="3:17">
       <c r="C58" s="105" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="D58" s="104"/>
       <c r="E58" s="104"/>
@@ -20219,7 +20675,7 @@
     </row>
     <row r="59" spans="3:17">
       <c r="C59" s="105" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="D59" s="104"/>
       <c r="E59" s="104"/>
@@ -20257,7 +20713,7 @@
     </row>
     <row r="61" spans="3:17">
       <c r="C61" s="103" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="D61" s="104"/>
       <c r="E61" s="104"/>
@@ -20276,7 +20732,7 @@
     </row>
     <row r="62" spans="3:17">
       <c r="C62" s="105" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D62" s="104"/>
       <c r="E62" s="104"/>
@@ -20295,7 +20751,7 @@
     </row>
     <row r="63" spans="3:17">
       <c r="C63" s="110" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="D63" s="104"/>
       <c r="E63" s="104"/>
@@ -20314,7 +20770,7 @@
     </row>
     <row r="64" spans="3:17">
       <c r="C64" s="106" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="D64" s="104"/>
       <c r="E64" s="104"/>
@@ -20352,7 +20808,7 @@
     </row>
     <row r="66" spans="3:17">
       <c r="C66" s="105" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D66" s="104"/>
       <c r="E66" s="104"/>
@@ -20388,7 +20844,7 @@
     </row>
     <row r="68" spans="3:17">
       <c r="C68" s="103" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="D68" s="104"/>
       <c r="E68" s="104"/>
@@ -20407,7 +20863,7 @@
     </row>
     <row r="69" spans="3:17">
       <c r="C69" s="105" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D69" s="104"/>
       <c r="E69" s="104"/>
@@ -20426,7 +20882,7 @@
     </row>
     <row r="70" spans="3:17">
       <c r="C70" s="103" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D70" s="104"/>
       <c r="E70" s="104"/>
@@ -20445,7 +20901,7 @@
     </row>
     <row r="71" spans="3:17">
       <c r="C71" s="107" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="D71" s="104"/>
       <c r="E71" s="104"/>
@@ -20464,7 +20920,7 @@
     </row>
     <row r="72" spans="3:17">
       <c r="C72" s="107" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="D72" s="104"/>
       <c r="E72" s="104"/>
@@ -20483,7 +20939,7 @@
     </row>
     <row r="73" spans="3:17">
       <c r="C73" s="103" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D73" s="104"/>
       <c r="E73" s="104"/>
@@ -20502,7 +20958,7 @@
     </row>
     <row r="74" spans="3:17">
       <c r="C74" s="106" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="D74" s="104"/>
       <c r="E74" s="104"/>
@@ -20521,7 +20977,7 @@
     </row>
     <row r="75" spans="3:17">
       <c r="C75" s="105" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D75" s="104"/>
       <c r="E75" s="104"/>
@@ -20540,7 +20996,7 @@
     </row>
     <row r="76" spans="3:17">
       <c r="C76" s="110" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="D76" s="104"/>
       <c r="E76" s="104"/>
@@ -20595,7 +21051,7 @@
     </row>
     <row r="79" spans="3:17">
       <c r="C79" s="103" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="D79" s="104"/>
       <c r="E79" s="104"/>
@@ -20614,7 +21070,7 @@
     </row>
     <row r="80" spans="3:17">
       <c r="C80" s="105" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D80" s="104"/>
       <c r="E80" s="104"/>
@@ -20633,7 +21089,7 @@
     </row>
     <row r="81" spans="3:17">
       <c r="C81" s="110" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="D81" s="104"/>
       <c r="E81" s="104"/>
@@ -20652,7 +21108,7 @@
     </row>
     <row r="82" spans="3:17">
       <c r="C82" s="107" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="D82" s="104"/>
       <c r="E82" s="104"/>
@@ -20707,7 +21163,7 @@
     </row>
     <row r="85" spans="3:17">
       <c r="C85" s="103" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="D85" s="104"/>
       <c r="E85" s="104"/>
@@ -20726,7 +21182,7 @@
     </row>
     <row r="86" spans="3:17">
       <c r="C86" s="105" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D86" s="104"/>
       <c r="E86" s="104"/>
@@ -20745,7 +21201,7 @@
     </row>
     <row r="87" spans="3:17">
       <c r="C87" s="107" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="D87" s="104"/>
       <c r="E87" s="104"/>
@@ -20800,7 +21256,7 @@
     </row>
     <row r="90" spans="3:17">
       <c r="C90" s="105" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D90" s="104"/>
       <c r="E90" s="104"/>
@@ -20836,7 +21292,7 @@
     </row>
     <row r="92" spans="3:17">
       <c r="C92" s="103" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="D92" s="104"/>
       <c r="E92" s="104"/>
@@ -20855,7 +21311,7 @@
     </row>
     <row r="93" spans="3:17">
       <c r="C93" s="105" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D93" s="104"/>
       <c r="E93" s="104"/>
@@ -20874,7 +21330,7 @@
     </row>
     <row r="94" spans="3:17">
       <c r="C94" s="107" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="D94" s="104"/>
       <c r="E94" s="104"/>
@@ -20893,7 +21349,7 @@
     </row>
     <row r="95" spans="3:17">
       <c r="C95" s="107" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="D95" s="104"/>
       <c r="E95" s="104"/>
@@ -20912,7 +21368,7 @@
     </row>
     <row r="96" spans="3:17">
       <c r="C96" s="107" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="D96" s="104"/>
       <c r="E96" s="104"/>
@@ -20931,7 +21387,7 @@
     </row>
     <row r="97" spans="3:17">
       <c r="C97" s="107" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="D97" s="104"/>
       <c r="E97" s="104"/>
@@ -20967,7 +21423,7 @@
     </row>
     <row r="99" spans="3:17">
       <c r="C99" s="110" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="D99" s="104"/>
       <c r="E99" s="104"/>
@@ -20986,7 +21442,7 @@
     </row>
     <row r="100" spans="3:17">
       <c r="C100" s="110" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="D100" s="104"/>
       <c r="E100" s="104"/>
@@ -21022,7 +21478,7 @@
     </row>
     <row r="102" spans="3:17">
       <c r="C102" s="110" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="D102" s="104"/>
       <c r="E102" s="104"/>
@@ -21041,7 +21497,7 @@
     </row>
     <row r="103" spans="3:17">
       <c r="C103" s="110" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="D103" s="104"/>
       <c r="E103" s="104"/>
@@ -21077,7 +21533,7 @@
     </row>
     <row r="105" spans="3:17">
       <c r="C105" s="110" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="D105" s="104"/>
       <c r="E105" s="104"/>
@@ -21113,7 +21569,7 @@
     </row>
     <row r="107" spans="3:17">
       <c r="C107" s="109" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="D107" s="104"/>
       <c r="E107" s="104"/>
@@ -21158,7 +21614,7 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -21167,118 +21623,118 @@
     </row>
     <row r="3" spans="2:5">
       <c r="C3" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="D4" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="D6" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="E7" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="E8" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="E9" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="E10" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="C12" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="D13" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="D15" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="E16" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
     </row>
     <row r="17" spans="2:5">
       <c r="E17" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="17" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="C19" s="17"/>
     </row>
     <row r="20" spans="2:5">
       <c r="B20" s="17" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="C20" s="17"/>
     </row>
     <row r="21" spans="2:5">
       <c r="C21" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
     </row>
     <row r="22" spans="2:5">
       <c r="D22" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="E22" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="23" spans="2:5">
       <c r="D23" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="E23" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
     </row>
     <row r="24" spans="2:5">
       <c r="D24" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="E24" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
     </row>
     <row r="25" spans="2:5">
       <c r="C25" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
     </row>
     <row r="26" spans="2:5">
       <c r="C26" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
     </row>
     <row r="27" spans="2:5">
       <c r="B27" s="17" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
     </row>
   </sheetData>
@@ -21289,24 +21745,143 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <dimension ref="B2:F27"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="2" spans="2:4">
+      <c r="B2" s="6" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4">
+      <c r="C3" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="D4" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
+      <c r="C5" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
+      <c r="D6" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4">
+      <c r="D7" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="D8" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
+      <c r="D10" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4">
+      <c r="D12" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4">
+      <c r="D13" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4">
+      <c r="D14" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4">
+      <c r="D15" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4">
+      <c r="D16" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="18" spans="3:6">
+      <c r="D18" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="20" spans="3:6">
+      <c r="D20" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="22" spans="3:6">
+      <c r="C22" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="23" spans="3:6">
+      <c r="D23" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="24" spans="3:6">
+      <c r="D24" t="s">
+        <v>837</v>
+      </c>
+      <c r="F24" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="25" spans="3:6">
+      <c r="D25" t="s">
+        <v>836</v>
+      </c>
+      <c r="F25" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="26" spans="3:6">
+      <c r="D26" t="s">
+        <v>835</v>
+      </c>
+      <c r="E26" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="27" spans="3:6">
+      <c r="D27" t="s">
+        <v>839</v>
+      </c>
+      <c r="F27" t="s">
+        <v>838</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="22.140625" customWidth="1"/>
+    <col min="2" max="2" width="22.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:2">
       <c r="B2" s="7" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
     </row>
   </sheetData>
@@ -21317,7 +21892,7 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:O20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:15">
       <c r="B2" s="6" t="s">
@@ -21326,25 +21901,25 @@
     </row>
     <row r="4" spans="2:15">
       <c r="C4" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="5" spans="2:15">
       <c r="C5" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="6" spans="2:15">
       <c r="C6" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="8" spans="2:15">
       <c r="F8" s="99" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="L8" s="100" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="M8" s="101"/>
       <c r="N8" s="101"/>
@@ -21352,13 +21927,13 @@
     </row>
     <row r="9" spans="2:15">
       <c r="F9" s="95" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="G9" t="s">
+        <v>710</v>
+      </c>
+      <c r="L9" s="96" t="s">
         <v>711</v>
-      </c>
-      <c r="L9" s="96" t="s">
-        <v>712</v>
       </c>
       <c r="M9" s="97"/>
       <c r="N9" s="97"/>
@@ -21366,18 +21941,18 @@
     </row>
     <row r="11" spans="2:15">
       <c r="E11" t="s">
+        <v>713</v>
+      </c>
+      <c r="L11" t="s">
         <v>714</v>
-      </c>
-      <c r="L11" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="16" spans="2:15">
       <c r="D16" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="I16" s="116" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="J16" s="117"/>
     </row>
@@ -21387,19 +21962,19 @@
     </row>
     <row r="18" spans="3:10">
       <c r="D18" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="I18" s="120"/>
       <c r="J18" s="121"/>
     </row>
     <row r="19" spans="3:10">
       <c r="C19" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="20" spans="3:10">
       <c r="D20" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
   </sheetData>
@@ -21411,15 +21986,102 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:K18"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="2" spans="2:11">
+      <c r="B2" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11">
+      <c r="B3" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11">
+      <c r="B4" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11">
+      <c r="B6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11">
+      <c r="B7" t="s">
+        <v>843</v>
+      </c>
+      <c r="F7" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11">
+      <c r="B10" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11">
+      <c r="B11" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11">
+      <c r="B12" t="s">
+        <v>847</v>
+      </c>
+      <c r="K12" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11">
+      <c r="B13" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11">
+      <c r="B14" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11">
+      <c r="B16" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" t="s">
+        <v>849</v>
+      </c>
+      <c r="F17" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18" t="s">
+        <v>850</v>
+      </c>
+      <c r="F18" t="s">
+        <v>852</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:G96"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="3" max="3" width="54.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="68.5703125" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" customWidth="1"/>
+    <col min="3" max="3" width="54.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.54296875" customWidth="1"/>
+    <col min="6" max="6" width="9.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6">
@@ -21427,7 +22089,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="2:6" ht="18.75">
+    <row r="2" spans="2:6" ht="18.5">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -22148,7 +22810,7 @@
         <v>287</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D49" s="51">
         <v>0.9</v>
@@ -22163,7 +22825,7 @@
         <v>319</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D50" s="42">
         <v>1</v>
@@ -22173,12 +22835,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="2:6" ht="30">
+    <row r="51" spans="2:6">
       <c r="B51" s="5" t="s">
         <v>320</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="16" t="s">
@@ -22191,7 +22853,7 @@
         <v>321</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D52" s="42">
         <v>1</v>
@@ -22231,12 +22893,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="2:6" ht="45">
+    <row r="55" spans="2:6" ht="43.5">
       <c r="B55" s="5" t="s">
         <v>447</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D55" s="42">
         <v>1</v>
@@ -22306,12 +22968,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="2:6" ht="30">
+    <row r="60" spans="2:6" ht="29">
       <c r="B60" s="5">
         <v>16.399999999999999</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D60" s="42">
         <v>1</v>
@@ -22326,7 +22988,7 @@
         <v>16.5</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D61" s="42">
         <v>1</v>
@@ -22336,12 +22998,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="60">
+    <row r="62" spans="2:6" ht="58">
       <c r="B62" s="5">
         <v>16.600000000000001</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D62" s="42">
         <v>1</v>
@@ -22362,7 +23024,7 @@
         <v>1</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="F63" s="16" t="s">
         <v>14</v>
@@ -22379,7 +23041,7 @@
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>
     </row>
-    <row r="65" spans="2:6" ht="30">
+    <row r="65" spans="2:6" ht="29">
       <c r="B65" s="5">
         <v>17.100000000000001</v>
       </c>
@@ -22390,7 +23052,7 @@
       <c r="E65" s="6"/>
       <c r="F65" s="6"/>
     </row>
-    <row r="66" spans="2:6" ht="30">
+    <row r="66" spans="2:6" ht="29">
       <c r="B66" s="5">
         <v>17.2</v>
       </c>
@@ -22414,7 +23076,7 @@
       </c>
       <c r="F67" s="6"/>
     </row>
-    <row r="68" spans="2:6" ht="30">
+    <row r="68" spans="2:6" ht="29">
       <c r="B68" s="5">
         <v>17.399999999999999</v>
       </c>
@@ -22474,7 +23136,7 @@
         <v>18.3</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D73" s="6"/>
       <c r="E73" s="6"/>
@@ -22485,7 +23147,7 @@
         <v>18.399999999999999</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D74" s="6"/>
       <c r="E74" s="6"/>
@@ -22496,7 +23158,7 @@
         <v>462</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="D75" s="51">
         <v>0.9</v>
@@ -22554,7 +23216,7 @@
       <c r="E79" s="6"/>
       <c r="F79" s="6"/>
     </row>
-    <row r="80" spans="2:6" ht="30">
+    <row r="80" spans="2:6" ht="29">
       <c r="B80" s="5">
         <v>21.2</v>
       </c>
@@ -22578,12 +23240,12 @@
       </c>
       <c r="F81" s="6"/>
     </row>
-    <row r="82" spans="2:7" ht="30">
+    <row r="82" spans="2:7" ht="29">
       <c r="B82" s="5" t="s">
         <v>468</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="D82" s="42">
         <v>1</v>
@@ -22598,7 +23260,7 @@
         <v>24.1</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="D83" s="42">
         <v>1</v>
@@ -22613,7 +23275,7 @@
         <v>24.2</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="D84" s="42">
         <v>1</v>
@@ -22650,9 +23312,9 @@
       <c r="E86" s="16"/>
       <c r="F86" s="6"/>
     </row>
-    <row r="87" spans="2:7" ht="60">
+    <row r="87" spans="2:7" ht="58">
       <c r="B87" s="5" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C87" s="79" t="s">
         <v>482</v>
@@ -22663,12 +23325,12 @@
       </c>
       <c r="F87" s="6"/>
     </row>
-    <row r="88" spans="2:7" ht="45">
+    <row r="88" spans="2:7" ht="43.5">
       <c r="B88" s="5" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="D88" s="6"/>
       <c r="E88" s="16"/>
@@ -22676,23 +23338,25 @@
     </row>
     <row r="89" spans="2:7">
       <c r="B89" s="5" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>484</v>
-      </c>
-      <c r="D89" s="51">
-        <v>0</v>
+        <v>815</v>
+      </c>
+      <c r="D89" s="42">
+        <v>1</v>
       </c>
       <c r="E89" s="16"/>
-      <c r="F89" s="6"/>
+      <c r="F89" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="90" spans="2:7">
       <c r="B90" s="5" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="D90" s="51">
         <v>0</v>
@@ -22705,7 +23369,7 @@
         <v>30.1</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="D91" s="51"/>
       <c r="E91" s="16"/>
@@ -22718,7 +23382,7 @@
         <v>30.2</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="D92" s="51"/>
       <c r="E92" s="16"/>
@@ -22729,21 +23393,21 @@
         <v>30.3</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="D93" s="51"/>
       <c r="E93" s="16"/>
       <c r="F93" s="6"/>
     </row>
-    <row r="94" spans="2:7" ht="30">
+    <row r="94" spans="2:7" ht="29">
       <c r="B94" s="5" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C94" s="7" t="s">
         <v>476</v>
       </c>
       <c r="D94" s="51">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E94" s="16"/>
       <c r="F94" s="16" t="s">
@@ -22752,14 +23416,18 @@
     </row>
     <row r="95" spans="2:7">
       <c r="B95" s="5" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>780</v>
-      </c>
-      <c r="D95" s="42"/>
+        <v>777</v>
+      </c>
+      <c r="D95" s="42">
+        <v>1</v>
+      </c>
       <c r="E95" s="16"/>
-      <c r="F95" s="16"/>
+      <c r="F95" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="96" spans="2:7">
       <c r="B96" s="77" t="s">
@@ -22846,6 +23514,8 @@
     <hyperlink ref="F85" location="'#25'!B2" display="Link"/>
     <hyperlink ref="F76" location="'#19'!B2" display="Link"/>
     <hyperlink ref="F91" location="'#30'!B2" display="Link"/>
+    <hyperlink ref="F89" location="'#29'!B2" display="Link"/>
+    <hyperlink ref="F95" location="'#32'!B2" display="Link"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId12"/>
@@ -22855,13 +23525,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J164"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" customWidth="1"/>
+    <col min="1" max="1" width="4.26953125" customWidth="1"/>
+    <col min="2" max="2" width="6.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75">
+    <row r="1" spans="1:3" ht="18.5">
       <c r="C1" s="41" t="s">
         <v>15</v>
       </c>
@@ -23118,14 +23788,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L61"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="3" max="3" width="10.42578125" customWidth="1"/>
-    <col min="4" max="4" width="5.28515625" customWidth="1"/>
-    <col min="5" max="5" width="48.85546875" customWidth="1"/>
+    <col min="3" max="3" width="10.453125" customWidth="1"/>
+    <col min="4" max="4" width="5.26953125" customWidth="1"/>
+    <col min="5" max="5" width="48.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75">
+    <row r="1" spans="1:10" ht="18.5">
       <c r="C1" s="41" t="s">
         <v>57</v>
       </c>
@@ -23156,13 +23826,13 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15.75" thickBot="1">
+    <row r="12" spans="1:10" ht="15" thickBot="1">
       <c r="C12" s="11" t="s">
         <v>63</v>
       </c>
       <c r="D12" s="11"/>
     </row>
-    <row r="13" spans="1:10" ht="15.75" thickBot="1">
+    <row r="13" spans="1:10" ht="15" thickBot="1">
       <c r="C13" s="111" t="s">
         <v>78</v>
       </c>
@@ -23179,7 +23849,7 @@
       <c r="H13" s="24"/>
       <c r="I13" s="25"/>
     </row>
-    <row r="14" spans="1:10" ht="15.75" thickBot="1">
+    <row r="14" spans="1:10" ht="15" thickBot="1">
       <c r="C14" s="112"/>
       <c r="D14" s="23" t="s">
         <v>65</v>
@@ -23221,7 +23891,7 @@
       <c r="H16" s="30"/>
       <c r="I16" s="31"/>
     </row>
-    <row r="17" spans="3:12" ht="15.75" thickBot="1">
+    <row r="17" spans="3:12" ht="15" thickBot="1">
       <c r="C17" s="113"/>
       <c r="D17" s="32"/>
       <c r="E17" s="33" t="s">
@@ -23232,7 +23902,7 @@
       <c r="H17" s="30"/>
       <c r="I17" s="31"/>
     </row>
-    <row r="18" spans="3:12" ht="15.75" thickBot="1">
+    <row r="18" spans="3:12" ht="15" thickBot="1">
       <c r="C18" s="37" t="s">
         <v>79</v>
       </c>
@@ -23252,7 +23922,7 @@
       <c r="K18" s="24"/>
       <c r="L18" s="25"/>
     </row>
-    <row r="19" spans="3:12" ht="15.75" thickBot="1">
+    <row r="19" spans="3:12" ht="15" thickBot="1">
       <c r="C19" s="111" t="s">
         <v>78</v>
       </c>
@@ -23272,7 +23942,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="3:12" ht="15.75" thickBot="1">
+    <row r="21" spans="3:12" ht="15" thickBot="1">
       <c r="C21" s="113"/>
       <c r="D21" s="32"/>
       <c r="E21" s="40" t="s">
@@ -23386,10 +24056,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:V102"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="13" max="13" width="4.85546875" customWidth="1"/>
+    <col min="13" max="13" width="4.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
@@ -23904,7 +24574,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D32"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" s="6" t="s">
@@ -24027,10 +24697,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:H90"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="4" max="4" width="13.5703125" customWidth="1"/>
-    <col min="7" max="7" width="9.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" customWidth="1"/>
+    <col min="7" max="7" width="9.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4">
@@ -24396,9 +25066,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Z40"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="4" max="4" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:26">

--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" firstSheet="1" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="Knowhow" sheetId="1" r:id="rId1"/>
@@ -20,18 +20,19 @@
     <sheet name="#8" sheetId="11" r:id="rId11"/>
     <sheet name="#9" sheetId="13" r:id="rId12"/>
     <sheet name="#10" sheetId="16" r:id="rId13"/>
-    <sheet name="#12" sheetId="14" r:id="rId14"/>
-    <sheet name="#13" sheetId="17" r:id="rId15"/>
-    <sheet name="#14" sheetId="12" r:id="rId16"/>
-    <sheet name="#15" sheetId="18" r:id="rId17"/>
-    <sheet name="#16" sheetId="15" r:id="rId18"/>
-    <sheet name="#19" sheetId="22" r:id="rId19"/>
-    <sheet name="#24" sheetId="20" r:id="rId20"/>
-    <sheet name="#25" sheetId="21" r:id="rId21"/>
-    <sheet name="#29" sheetId="23" r:id="rId22"/>
-    <sheet name="#30" sheetId="24" r:id="rId23"/>
-    <sheet name="#31" sheetId="19" r:id="rId24"/>
-    <sheet name="#32" sheetId="25" r:id="rId25"/>
+    <sheet name="#11" sheetId="26" r:id="rId14"/>
+    <sheet name="#12" sheetId="14" r:id="rId15"/>
+    <sheet name="#13" sheetId="17" r:id="rId16"/>
+    <sheet name="#14" sheetId="12" r:id="rId17"/>
+    <sheet name="#15" sheetId="18" r:id="rId18"/>
+    <sheet name="#16" sheetId="15" r:id="rId19"/>
+    <sheet name="#19" sheetId="22" r:id="rId20"/>
+    <sheet name="#24" sheetId="20" r:id="rId21"/>
+    <sheet name="#25" sheetId="21" r:id="rId22"/>
+    <sheet name="#29" sheetId="23" r:id="rId23"/>
+    <sheet name="#30" sheetId="24" r:id="rId24"/>
+    <sheet name="#31" sheetId="19" r:id="rId25"/>
+    <sheet name="#32" sheetId="25" r:id="rId26"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="855">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="888">
   <si>
     <t>No.</t>
   </si>
@@ -10078,9 +10079,6 @@
     <t>reinterpret_cast</t>
   </si>
   <si>
-    <t>Làm thế nào để tránh Memory leak ( và tool tránh Valgrind)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Casting in cpp</t>
   </si>
   <si>
@@ -10739,6 +10737,381 @@
       </rPr>
       <t xml:space="preserve"> đầu tiên</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t>static_cast</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → "Ép kiểu hợp lý, compiler kiểm tra."</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>dynamic_cast</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → "Ép kiểu trong class, có kiểm tra runtime."</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>reinterpret_cast</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → "Ép kiểu thô, không kiểm tra, dễ lỗi."</t>
+    </r>
+  </si>
+  <si>
+    <t>Casting in C++</t>
+  </si>
+  <si>
+    <t>static_cast là cách ép kiểu mà compiler có thể kiểm tra được ngay lúc biên dịch (compile-time).
+Nếu việc chuyển đổi có ý nghĩa thì compiler cho phép.</t>
+  </si>
+  <si>
+    <t>Dùng khi :</t>
+  </si>
+  <si>
+    <t>- Ép kiểu cho các biến đơn giản như int, float, double,…</t>
+  </si>
+  <si>
+    <t>- Ép kiểu lớp dẫn xuất -&gt; lớp cơ sở (upcast)</t>
+  </si>
+  <si>
+    <t>- Chuyển đổi con trỏ void* thành kiểu cụ thể</t>
+  </si>
+  <si>
+    <t>int a = 10;</t>
+  </si>
+  <si>
+    <t>dynamic_cast dùng để ép kiểu trong hệ thống kế thừa (class), đặc biệt là từ Base → Derived, và có kiểm tra an toàn trong lúc chạy chương trình.</t>
+  </si>
+  <si>
+    <t>deliveried* a = new deliveried();</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">base* b = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>static_cast&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>base*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&gt;(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">double b = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>static_cast&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>double</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&gt; (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <t>- Ép kiểu lớp cơ sở -&gt; lớp dẫn xuất (downcast), nhưng vẫn muốn an toàn. Nếu không hợp lệ, class gán sẽ thành nullptr</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>base *A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = new base();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">deliveried* B = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dynamic_cast&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>deliveried*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&gt; (A)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">; //-&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>chặn tạo ra B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, B biến thành </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nullptr</t>
+    </r>
+  </si>
+  <si>
+    <t>-&gt; Ta có thể dễ dàng kiểm tra B trước khi gọi 1 phương thức mới trong B</t>
+  </si>
+  <si>
+    <t>Không kiểm tra dữ liệu có hợp lệ không</t>
+  </si>
+  <si>
+    <t>Nó sẽ làm compiler hiểu rằng hãy xem vùng nhớ đó là kiểu được ép.</t>
+  </si>
+  <si>
+    <t>-&gt; Đây là ép kiểu thô, rất nguy hiểm</t>
+  </si>
+  <si>
+    <t>Khi khai báo 1 biến con trỏ D được cast theo kiểu A. dữ liệu được cast không hợp lệ có thể phá hỏng dữ liệu của A.</t>
+  </si>
+  <si>
+    <r>
+      <t>Làm thế nào để tránh Memory leak ( và tool tránh Valgrind,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Klockwork</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Các thuật toán sort trong C++</t>
+  </si>
+  <si>
+    <t>Bubble sort</t>
+  </si>
+  <si>
+    <t>Mô tả :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chạy 2 vòng lặp lồng nhau đi qua các phần tử của mảng, vector. Vòng lặp 1 bằng số phần tử mảng, vòng lặp bằng số phần tử mảng </t>
+  </si>
+  <si>
+    <t>và kiểm tra xem phần tử nào lớn/nhỏ hơn thì đẩy ra sau ( giống như việc nổi bọt)</t>
+  </si>
+  <si>
+    <t>int arr = {3, 5, 6 , 9, 14};</t>
+  </si>
+  <si>
+    <t>for (int i = 0; i &lt; n-1; i++) {          // vòng ngoài</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    for (int j = 0; j &lt; n-i-1; j++) {    // vòng trong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        if (arr[j] &lt; arr[j+1]) {         // giảm dần</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            swap(arr[j], arr[j+1]);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        }</t>
   </si>
 </sst>
 </file>
@@ -11332,7 +11705,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -11580,6 +11953,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -17736,114 +18113,77 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:E25"/>
+  <dimension ref="B2:C18"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="2" spans="2:5">
-      <c r="B2" s="6" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5">
-      <c r="C3" t="s">
-        <v>503</v>
-      </c>
-      <c r="D3" t="s">
-        <v>502</v>
-      </c>
-      <c r="E3" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5">
-      <c r="C4" s="80" t="s">
-        <v>504</v>
-      </c>
-      <c r="D4" t="s">
-        <v>501</v>
-      </c>
-      <c r="E4" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5">
+    <row r="2" spans="2:3">
+      <c r="B2" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3">
+      <c r="B4" s="6" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3">
+      <c r="C5" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3">
+      <c r="C6" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3">
       <c r="C7" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5">
-      <c r="C8" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5">
-      <c r="C10" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3">
+      <c r="C9" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3">
       <c r="C11" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3">
       <c r="C12" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3">
       <c r="C13" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3">
       <c r="C14" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3">
       <c r="C15" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3">
       <c r="C16" t="s">
-        <v>515</v>
+        <v>887</v>
       </c>
     </row>
     <row r="17" spans="3:3">
       <c r="C17" t="s">
-        <v>516</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="3:3">
       <c r="C18" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="20" spans="3:3">
-      <c r="C20" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="21" spans="3:3">
-      <c r="C21" t="s">
         <v>284</v>
-      </c>
-    </row>
-    <row r="23" spans="3:3">
-      <c r="C23" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="24" spans="3:3">
-      <c r="C24" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="25" spans="3:3">
-      <c r="C25" t="s">
-        <v>521</v>
       </c>
     </row>
   </sheetData>
@@ -17853,75 +18193,114 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:E16"/>
+  <dimension ref="B2:E25"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
-        <v>637</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3" spans="2:5">
       <c r="C3" t="s">
-        <v>647</v>
+        <v>503</v>
+      </c>
+      <c r="D3" t="s">
+        <v>502</v>
+      </c>
+      <c r="E3" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="4" spans="2:5">
-      <c r="C4" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5">
-      <c r="C6" t="s">
-        <v>635</v>
+      <c r="C4" s="80" t="s">
+        <v>504</v>
+      </c>
+      <c r="D4" t="s">
+        <v>501</v>
+      </c>
+      <c r="E4" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="7" spans="2:5">
-      <c r="D7" t="s">
-        <v>636</v>
+      <c r="C7" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="8" spans="2:5">
-      <c r="D8" t="s">
-        <v>638</v>
+      <c r="C8" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="C10" t="s">
-        <v>639</v>
+        <v>509</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="C11" t="s">
-        <v>640</v>
+        <v>510</v>
       </c>
     </row>
     <row r="12" spans="2:5">
-      <c r="D12" t="s">
-        <v>645</v>
+      <c r="C12" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="C13" t="s">
-        <v>641</v>
+        <v>512</v>
       </c>
     </row>
     <row r="14" spans="2:5">
-      <c r="D14" t="s">
-        <v>644</v>
-      </c>
-      <c r="E14" t="s">
-        <v>642</v>
+      <c r="C14" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="C15" t="s">
-        <v>643</v>
+        <v>514</v>
       </c>
     </row>
     <row r="16" spans="2:5">
-      <c r="D16" t="s">
-        <v>646</v>
+      <c r="C16" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3">
+      <c r="C20" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3">
+      <c r="C21" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="23" spans="3:3">
+      <c r="C23" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3">
+      <c r="C24" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="25" spans="3:3">
+      <c r="C25" t="s">
+        <v>521</v>
       </c>
     </row>
   </sheetData>
@@ -17931,6 +18310,84 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:E16"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="2" spans="2:5">
+      <c r="B2" s="6" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5">
+      <c r="C3" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5">
+      <c r="C4" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5">
+      <c r="C6" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5">
+      <c r="D7" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
+      <c r="D8" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5">
+      <c r="C10" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5">
+      <c r="C11" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5">
+      <c r="D12" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5">
+      <c r="C13" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5">
+      <c r="D14" t="s">
+        <v>644</v>
+      </c>
+      <c r="E14" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5">
+      <c r="C15" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5">
+      <c r="D16" t="s">
+        <v>646</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D7"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
@@ -17976,7 +18433,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I48"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -18215,7 +18672,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I101"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -18607,51 +19064,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:D9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <sheetData>
-    <row r="2" spans="2:4">
-      <c r="B2" s="6" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4">
-      <c r="C3" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4">
-      <c r="C4" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4">
-      <c r="C6" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4">
-      <c r="C7" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4">
-      <c r="D8" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4">
-      <c r="D9" t="s">
-        <v>805</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -19808,6 +20220,51 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:D9"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="2" spans="2:4">
+      <c r="B2" s="6" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4">
+      <c r="C3" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="C4" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
+      <c r="C6" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4">
+      <c r="C7" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="D8" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4">
+      <c r="D9" t="s">
+        <v>805</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Q108"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
@@ -19938,7 +20395,7 @@
     </row>
     <row r="13" spans="2:10">
       <c r="C13" s="106" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="D13" s="104"/>
       <c r="E13" s="104"/>
@@ -19950,7 +20407,7 @@
     </row>
     <row r="14" spans="2:10">
       <c r="C14" s="107" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="D14" s="104"/>
       <c r="E14" s="104"/>
@@ -21611,7 +22068,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E27"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -21743,126 +22200,126 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:F27"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="3" spans="2:4">
       <c r="C3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="D4" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="5" spans="2:4">
       <c r="C5" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="6" spans="2:4">
       <c r="D6" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="7" spans="2:4">
       <c r="D7" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="8" spans="2:4">
       <c r="D8" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="10" spans="2:4">
       <c r="D10" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="12" spans="2:4">
       <c r="D12" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="13" spans="2:4">
       <c r="D13" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="14" spans="2:4">
       <c r="D14" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="15" spans="2:4">
       <c r="D15" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="16" spans="2:4">
       <c r="D16" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="18" spans="3:6">
       <c r="D18" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="20" spans="3:6">
       <c r="D20" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="22" spans="3:6">
       <c r="C22" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="23" spans="3:6">
       <c r="D23" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="24" spans="3:6">
       <c r="D24" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="F24" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="25" spans="3:6">
       <c r="D25" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="F25" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="26" spans="3:6">
       <c r="D26" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="E26" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="27" spans="3:6">
       <c r="D27" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="F27" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
   </sheetData>
@@ -21871,25 +22328,164 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2"/>
+  <dimension ref="B2:B39"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="22.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:2">
-      <c r="B2" s="7" t="s">
+      <c r="B2" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
+      <c r="B3" s="11" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" s="11" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" s="11" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" s="11" t="s">
         <v>808</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" s="12" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2">
+      <c r="B11" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" s="80" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" s="80" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" s="80" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2">
+      <c r="B16" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" s="11" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" s="80" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" s="11"/>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="122" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="11" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="80" t="s">
+        <v>874</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:O20"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -21986,24 +22582,24 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:K18"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:11">
       <c r="B2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="3" spans="2:11">
       <c r="B3" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="4" spans="2:11">
       <c r="B4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="6" spans="2:11">
@@ -22013,38 +22609,38 @@
     </row>
     <row r="7" spans="2:11">
       <c r="B7" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="F7" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="10" spans="2:11">
       <c r="B10" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="11" spans="2:11">
       <c r="B11" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="12" spans="2:11">
       <c r="B12" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="K12" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="13" spans="2:11">
       <c r="B13" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="14" spans="2:11">
       <c r="B14" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="16" spans="2:11">
@@ -22054,18 +22650,18 @@
     </row>
     <row r="17" spans="2:6">
       <c r="B17" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="F17" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F18" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
   </sheetData>
@@ -22075,10 +22671,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:G96"/>
+  <dimension ref="B1:G99"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="3" max="3" width="54.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="60.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="68.54296875" customWidth="1"/>
     <col min="6" max="6" width="9.7265625" customWidth="1"/>
@@ -22842,63 +23438,51 @@
       <c r="C51" s="7" t="s">
         <v>712</v>
       </c>
-      <c r="D51" s="6"/>
+      <c r="D51" s="51">
+        <v>0</v>
+      </c>
       <c r="E51" s="16" t="s">
         <v>436</v>
       </c>
-      <c r="F51" s="6"/>
+      <c r="F51" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>500</v>
+      <c r="B52" s="5">
+        <v>11.1</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>878</v>
       </c>
       <c r="D52" s="42">
         <v>1</v>
       </c>
-      <c r="E52" s="6"/>
+      <c r="E52" s="16"/>
       <c r="F52" s="16" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="53" spans="2:6">
-      <c r="B53" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>438</v>
-      </c>
-      <c r="D53" s="42">
-        <v>1</v>
-      </c>
-      <c r="E53" s="6"/>
-      <c r="F53" s="16" t="s">
-        <v>14</v>
-      </c>
+      <c r="B53" s="5"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="51"/>
+      <c r="E53" s="16"/>
+      <c r="F53" s="16"/>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>439</v>
-      </c>
-      <c r="D54" s="42">
-        <v>1</v>
-      </c>
-      <c r="E54" s="6"/>
-      <c r="F54" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="55" spans="2:6" ht="43.5">
+      <c r="B54" s="5"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="51"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="16"/>
+    </row>
+    <row r="55" spans="2:6">
       <c r="B55" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>649</v>
+        <v>321</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>500</v>
       </c>
       <c r="D55" s="42">
         <v>1</v>
@@ -22910,40 +23494,40 @@
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="5" t="s">
-        <v>448</v>
+        <v>322</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="D56" s="42">
         <v>1</v>
       </c>
-      <c r="E56" s="16" t="s">
-        <v>463</v>
-      </c>
-      <c r="F56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="5">
-        <v>16.100000000000001</v>
+      <c r="B57" s="5" t="s">
+        <v>435</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>474</v>
+        <v>439</v>
       </c>
       <c r="D57" s="42">
         <v>1</v>
       </c>
-      <c r="E57" s="16"/>
+      <c r="E57" s="6"/>
       <c r="F57" s="16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="5">
-        <v>16.2</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>461</v>
+    <row r="58" spans="2:6" ht="43.5">
+      <c r="B58" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>649</v>
       </c>
       <c r="D58" s="42">
         <v>1</v>
@@ -22954,41 +23538,41 @@
       </c>
     </row>
     <row r="59" spans="2:6">
-      <c r="B59" s="5">
-        <v>16.3</v>
+      <c r="B59" s="5" t="s">
+        <v>448</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D59" s="42">
         <v>1</v>
       </c>
-      <c r="E59" s="6"/>
-      <c r="F59" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="60" spans="2:6" ht="29">
+      <c r="E59" s="16" t="s">
+        <v>463</v>
+      </c>
+      <c r="F59" s="6"/>
+    </row>
+    <row r="60" spans="2:6">
       <c r="B60" s="5">
-        <v>16.399999999999999</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>620</v>
+        <v>16.100000000000001</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>474</v>
       </c>
       <c r="D60" s="42">
         <v>1</v>
       </c>
-      <c r="E60" s="6"/>
+      <c r="E60" s="16"/>
       <c r="F60" s="16" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="5">
-        <v>16.5</v>
+        <v>16.2</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>619</v>
+        <v>461</v>
       </c>
       <c r="D61" s="42">
         <v>1</v>
@@ -22998,12 +23582,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="58">
+    <row r="62" spans="2:6">
       <c r="B62" s="5">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>621</v>
+        <v>16.3</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>450</v>
       </c>
       <c r="D62" s="42">
         <v>1</v>
@@ -23013,108 +23597,120 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="2:6" ht="43.5" customHeight="1">
+    <row r="63" spans="2:6" ht="29">
       <c r="B63" s="5">
-        <v>16.7</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>460</v>
+        <v>620</v>
       </c>
       <c r="D63" s="42">
         <v>1</v>
       </c>
-      <c r="E63" s="7" t="s">
-        <v>700</v>
-      </c>
+      <c r="E63" s="6"/>
       <c r="F63" s="16" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="5" t="s">
+      <c r="B64" s="5">
+        <v>16.5</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="D64" s="42">
+        <v>1</v>
+      </c>
+      <c r="E64" s="6"/>
+      <c r="F64" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6" ht="58">
+      <c r="B65" s="5">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>621</v>
+      </c>
+      <c r="D65" s="42">
+        <v>1</v>
+      </c>
+      <c r="E65" s="6"/>
+      <c r="F65" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6" ht="43.5" customHeight="1">
+      <c r="B66" s="5">
+        <v>16.7</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D66" s="42">
+        <v>1</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="F66" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6">
+      <c r="B67" s="5" t="s">
         <v>451</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C67" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="D64" s="6"/>
-      <c r="E64" s="6"/>
-      <c r="F64" s="6"/>
-    </row>
-    <row r="65" spans="2:6" ht="29">
-      <c r="B65" s="5">
-        <v>17.100000000000001</v>
-      </c>
-      <c r="C65" s="78" t="s">
-        <v>481</v>
-      </c>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6"/>
-      <c r="F65" s="6"/>
-    </row>
-    <row r="66" spans="2:6" ht="29">
-      <c r="B66" s="5">
-        <v>17.2</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>453</v>
-      </c>
-      <c r="D66" s="6"/>
-      <c r="E66" s="6"/>
-      <c r="F66" s="6"/>
-    </row>
-    <row r="67" spans="2:6" ht="50.25" customHeight="1">
-      <c r="B67" s="5">
-        <v>17.3</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>469</v>
-      </c>
       <c r="D67" s="6"/>
-      <c r="E67" s="16" t="s">
-        <v>463</v>
-      </c>
+      <c r="E67" s="6"/>
       <c r="F67" s="6"/>
     </row>
     <row r="68" spans="2:6" ht="29">
       <c r="B68" s="5">
-        <v>17.399999999999999</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>454</v>
+        <v>17.100000000000001</v>
+      </c>
+      <c r="C68" s="78" t="s">
+        <v>481</v>
       </c>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
       <c r="F68" s="6"/>
     </row>
-    <row r="69" spans="2:6">
+    <row r="69" spans="2:6" ht="29">
       <c r="B69" s="5">
-        <v>17.5</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>455</v>
+        <v>17.2</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>453</v>
       </c>
       <c r="D69" s="6"/>
       <c r="E69" s="6"/>
       <c r="F69" s="6"/>
     </row>
-    <row r="70" spans="2:6">
-      <c r="B70" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="C70" s="6" t="s">
-        <v>459</v>
+    <row r="70" spans="2:6" ht="50.25" customHeight="1">
+      <c r="B70" s="5">
+        <v>17.3</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>469</v>
       </c>
       <c r="D70" s="6"/>
-      <c r="E70" s="6"/>
+      <c r="E70" s="16" t="s">
+        <v>463</v>
+      </c>
       <c r="F70" s="6"/>
     </row>
-    <row r="71" spans="2:6">
+    <row r="71" spans="2:6" ht="29">
       <c r="B71" s="5">
-        <v>18.100000000000001</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>457</v>
+        <v>17.399999999999999</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>454</v>
       </c>
       <c r="D71" s="6"/>
       <c r="E71" s="6"/>
@@ -23122,21 +23718,21 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="5">
-        <v>18.2</v>
+        <v>17.5</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D72" s="6"/>
       <c r="E72" s="6"/>
       <c r="F72" s="6"/>
     </row>
     <row r="73" spans="2:6">
-      <c r="B73" s="5">
-        <v>18.3</v>
+      <c r="B73" s="5" t="s">
+        <v>456</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>484</v>
+        <v>459</v>
       </c>
       <c r="D73" s="6"/>
       <c r="E73" s="6"/>
@@ -23144,51 +23740,43 @@
     </row>
     <row r="74" spans="2:6">
       <c r="B74" s="5">
-        <v>18.399999999999999</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>485</v>
+        <v>457</v>
       </c>
       <c r="D74" s="6"/>
       <c r="E74" s="6"/>
       <c r="F74" s="6"/>
     </row>
     <row r="75" spans="2:6">
-      <c r="B75" s="5" t="s">
-        <v>462</v>
+      <c r="B75" s="5">
+        <v>18.2</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>811</v>
-      </c>
-      <c r="D75" s="51">
-        <v>0.9</v>
-      </c>
+        <v>458</v>
+      </c>
+      <c r="D75" s="6"/>
       <c r="E75" s="6"/>
-      <c r="F75" s="43" t="s">
-        <v>121</v>
-      </c>
+      <c r="F75" s="6"/>
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="5">
-        <v>19.100000000000001</v>
+        <v>18.3</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>480</v>
-      </c>
-      <c r="D76" s="51">
-        <v>0.9</v>
-      </c>
+        <v>484</v>
+      </c>
+      <c r="D76" s="6"/>
       <c r="E76" s="6"/>
-      <c r="F76" s="16" t="s">
-        <v>14</v>
-      </c>
+      <c r="F76" s="6"/>
     </row>
     <row r="77" spans="2:6">
-      <c r="B77" s="5" t="s">
-        <v>464</v>
+      <c r="B77" s="5">
+        <v>18.399999999999999</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>437</v>
+        <v>485</v>
       </c>
       <c r="D77" s="6"/>
       <c r="E77" s="6"/>
@@ -23196,32 +23784,40 @@
     </row>
     <row r="78" spans="2:6">
       <c r="B78" s="5" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="D78" s="6"/>
+        <v>876</v>
+      </c>
+      <c r="D78" s="123">
+        <v>0.9</v>
+      </c>
       <c r="E78" s="6"/>
-      <c r="F78" s="6"/>
+      <c r="F78" s="43" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="79" spans="2:6">
       <c r="B79" s="5">
-        <v>21.1</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>432</v>
-      </c>
-      <c r="D79" s="6"/>
+        <v>480</v>
+      </c>
+      <c r="D79" s="51">
+        <v>0.9</v>
+      </c>
       <c r="E79" s="6"/>
-      <c r="F79" s="6"/>
-    </row>
-    <row r="80" spans="2:6" ht="29">
-      <c r="B80" s="5">
-        <v>21.2</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>470</v>
+      <c r="F79" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="80" spans="2:6">
+      <c r="B80" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>437</v>
       </c>
       <c r="D80" s="6"/>
       <c r="E80" s="6"/>
@@ -23229,185 +23825,185 @@
     </row>
     <row r="81" spans="2:7">
       <c r="B81" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="D81" s="6"/>
+      <c r="E81" s="6"/>
+      <c r="F81" s="6"/>
+    </row>
+    <row r="82" spans="2:7">
+      <c r="B82" s="5">
+        <v>21.1</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="D82" s="6"/>
+      <c r="E82" s="6"/>
+      <c r="F82" s="6"/>
+    </row>
+    <row r="83" spans="2:7" ht="29">
+      <c r="B83" s="5">
+        <v>21.2</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="D83" s="6"/>
+      <c r="E83" s="6"/>
+      <c r="F83" s="6"/>
+    </row>
+    <row r="84" spans="2:7">
+      <c r="B84" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="C81" s="6" t="s">
+      <c r="C84" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="D81" s="6"/>
-      <c r="E81" s="16" t="s">
+      <c r="D84" s="6"/>
+      <c r="E84" s="16" t="s">
         <v>467</v>
       </c>
-      <c r="F81" s="6"/>
-    </row>
-    <row r="82" spans="2:7" ht="29">
-      <c r="B82" s="5" t="s">
+      <c r="F84" s="6"/>
+    </row>
+    <row r="85" spans="2:7" ht="29">
+      <c r="B85" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="C82" s="7" t="s">
+      <c r="C85" s="7" t="s">
         <v>730</v>
-      </c>
-      <c r="D82" s="42">
-        <v>1</v>
-      </c>
-      <c r="E82" s="16" t="s">
-        <v>467</v>
-      </c>
-      <c r="F82" s="16"/>
-    </row>
-    <row r="83" spans="2:7">
-      <c r="B83" s="5">
-        <v>24.1</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>731</v>
-      </c>
-      <c r="D83" s="42">
-        <v>1</v>
-      </c>
-      <c r="E83" s="16"/>
-      <c r="F83" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="84" spans="2:7">
-      <c r="B84" s="5">
-        <v>24.2</v>
-      </c>
-      <c r="C84" s="7" t="s">
-        <v>775</v>
-      </c>
-      <c r="D84" s="42">
-        <v>1</v>
-      </c>
-      <c r="E84" s="16"/>
-      <c r="F84" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G84" s="48"/>
-    </row>
-    <row r="85" spans="2:7">
-      <c r="B85" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>478</v>
       </c>
       <c r="D85" s="42">
         <v>1</v>
       </c>
-      <c r="E85" s="16"/>
-      <c r="F85" s="16" t="s">
+      <c r="E85" s="16" t="s">
+        <v>467</v>
+      </c>
+      <c r="F85" s="16"/>
+    </row>
+    <row r="86" spans="2:7">
+      <c r="B86" s="5">
+        <v>24.1</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>731</v>
+      </c>
+      <c r="D86" s="42">
+        <v>1</v>
+      </c>
+      <c r="E86" s="16"/>
+      <c r="F86" s="16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="86" spans="2:7">
-      <c r="B86" s="5" t="s">
-        <v>477</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D86" s="6"/>
-      <c r="E86" s="16"/>
-      <c r="F86" s="6"/>
-    </row>
-    <row r="87" spans="2:7" ht="58">
-      <c r="B87" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="C87" s="79" t="s">
-        <v>482</v>
-      </c>
-      <c r="D87" s="6"/>
-      <c r="E87" s="16" t="s">
-        <v>483</v>
-      </c>
-      <c r="F87" s="6"/>
-    </row>
-    <row r="88" spans="2:7" ht="43.5">
+    <row r="87" spans="2:7">
+      <c r="B87" s="5">
+        <v>24.2</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>775</v>
+      </c>
+      <c r="D87" s="42">
+        <v>1</v>
+      </c>
+      <c r="E87" s="16"/>
+      <c r="F87" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G87" s="48"/>
+    </row>
+    <row r="88" spans="2:7">
       <c r="B88" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>778</v>
-      </c>
-      <c r="D88" s="6"/>
+        <v>475</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="D88" s="42">
+        <v>1</v>
+      </c>
       <c r="E88" s="16"/>
-      <c r="F88" s="6"/>
+      <c r="F88" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="89" spans="2:7">
       <c r="B89" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D89" s="6"/>
+      <c r="E89" s="16"/>
+      <c r="F89" s="6"/>
+    </row>
+    <row r="90" spans="2:7" ht="58">
+      <c r="B90" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="C90" s="79" t="s">
+        <v>482</v>
+      </c>
+      <c r="D90" s="6"/>
+      <c r="E90" s="16" t="s">
+        <v>483</v>
+      </c>
+      <c r="F90" s="6"/>
+    </row>
+    <row r="91" spans="2:7" ht="43.5">
+      <c r="B91" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>778</v>
+      </c>
+      <c r="D91" s="6"/>
+      <c r="E91" s="16"/>
+      <c r="F91" s="6"/>
+    </row>
+    <row r="92" spans="2:7">
+      <c r="B92" s="5" t="s">
         <v>488</v>
       </c>
-      <c r="C89" s="6" t="s">
-        <v>815</v>
-      </c>
-      <c r="D89" s="42">
+      <c r="C92" s="6" t="s">
+        <v>814</v>
+      </c>
+      <c r="D92" s="42">
         <v>1</v>
       </c>
-      <c r="E89" s="16"/>
-      <c r="F89" s="16" t="s">
+      <c r="E92" s="16"/>
+      <c r="F92" s="16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="90" spans="2:7">
-      <c r="B90" s="5" t="s">
+    <row r="93" spans="2:7">
+      <c r="B93" s="5" t="s">
         <v>489</v>
       </c>
-      <c r="C90" s="7" t="s">
-        <v>812</v>
-      </c>
-      <c r="D90" s="51">
-        <v>0</v>
-      </c>
-      <c r="E90" s="16"/>
-      <c r="F90" s="6"/>
-    </row>
-    <row r="91" spans="2:7">
-      <c r="B91" s="5">
+      <c r="C93" s="7" t="s">
+        <v>811</v>
+      </c>
+      <c r="D93" s="42">
+        <v>1</v>
+      </c>
+      <c r="E93" s="16"/>
+      <c r="F93" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="94" spans="2:7">
+      <c r="B94" s="5">
         <v>30.1</v>
       </c>
-      <c r="C91" s="7" t="s">
+      <c r="C94" s="7" t="s">
         <v>808</v>
       </c>
-      <c r="D91" s="51"/>
-      <c r="E91" s="16"/>
-      <c r="F91" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="92" spans="2:7">
-      <c r="B92" s="5">
-        <v>30.2</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>809</v>
-      </c>
-      <c r="D92" s="51"/>
-      <c r="E92" s="16"/>
-      <c r="F92" s="6"/>
-    </row>
-    <row r="93" spans="2:7">
-      <c r="B93" s="5">
-        <v>30.3</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>810</v>
-      </c>
-      <c r="D93" s="51"/>
-      <c r="E93" s="16"/>
-      <c r="F93" s="6"/>
-    </row>
-    <row r="94" spans="2:7" ht="29">
-      <c r="B94" s="5" t="s">
-        <v>490</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>476</v>
-      </c>
-      <c r="D94" s="51">
-        <v>0.05</v>
+      <c r="D94" s="42">
+        <v>1</v>
       </c>
       <c r="E94" s="16"/>
       <c r="F94" s="16" t="s">
@@ -23415,11 +24011,11 @@
       </c>
     </row>
     <row r="95" spans="2:7">
-      <c r="B95" s="5" t="s">
-        <v>776</v>
+      <c r="B95" s="5">
+        <v>30.2</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>777</v>
+        <v>809</v>
       </c>
       <c r="D95" s="42">
         <v>1</v>
@@ -23428,19 +24024,65 @@
       <c r="F95" s="16" t="s">
         <v>14</v>
       </c>
+      <c r="G95" s="48"/>
     </row>
     <row r="96" spans="2:7">
-      <c r="B96" s="77" t="s">
+      <c r="B96" s="5">
+        <v>30.3</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>810</v>
+      </c>
+      <c r="D96" s="42">
+        <v>1</v>
+      </c>
+      <c r="E96" s="16"/>
+      <c r="F96" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="97" spans="2:6" ht="29">
+      <c r="B97" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="D97" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="E97" s="16"/>
+      <c r="F97" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="98" spans="2:6">
+      <c r="B98" s="5" t="s">
+        <v>776</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>777</v>
+      </c>
+      <c r="D98" s="42">
+        <v>1</v>
+      </c>
+      <c r="E98" s="16"/>
+      <c r="F98" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="99" spans="2:6">
+      <c r="B99" s="77" t="s">
         <v>473</v>
       </c>
-      <c r="C96" s="57" t="s">
+      <c r="C99" s="57" t="s">
         <v>472</v>
       </c>
-      <c r="D96" s="1"/>
-      <c r="E96" s="49" t="s">
+      <c r="D99" s="1"/>
+      <c r="E99" s="49" t="s">
         <v>471</v>
       </c>
-      <c r="F96" s="1"/>
+      <c r="F99" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -23489,33 +24131,39 @@
     <hyperlink ref="F47" location="'#7'!B2" display="Link"/>
     <hyperlink ref="F48" location="'#8'!A1" display="Link"/>
     <hyperlink ref="E51" r:id="rId6"/>
-    <hyperlink ref="F54" location="'#14'!B2" display="Link"/>
-    <hyperlink ref="E56" r:id="rId7"/>
-    <hyperlink ref="E67" r:id="rId8"/>
-    <hyperlink ref="E81" r:id="rId9"/>
-    <hyperlink ref="E82" r:id="rId10"/>
-    <hyperlink ref="E96" r:id="rId11"/>
+    <hyperlink ref="F57" location="'#14'!B2" display="Link"/>
+    <hyperlink ref="E59" r:id="rId7"/>
+    <hyperlink ref="E70" r:id="rId8"/>
+    <hyperlink ref="E84" r:id="rId9"/>
+    <hyperlink ref="E85" r:id="rId10"/>
+    <hyperlink ref="E99" r:id="rId11"/>
     <hyperlink ref="F49" location="'#9'!B2" display="Link"/>
-    <hyperlink ref="F52" location="'#12'!B2" display="Link"/>
-    <hyperlink ref="F57" location="'#16'!B2" display="Link"/>
+    <hyperlink ref="F55" location="'#12'!B2" display="Link"/>
+    <hyperlink ref="F60" location="'#16'!B2" display="Link"/>
     <hyperlink ref="F50" location="'#10'!B2" display="Link"/>
-    <hyperlink ref="F53" location="'#13'!B2" display="Link"/>
-    <hyperlink ref="F58" location="'#16'!B10" display="Link"/>
-    <hyperlink ref="F59" location="'#16'!B28" display="Link"/>
-    <hyperlink ref="F60" location="'#16'!B62" display="Link"/>
-    <hyperlink ref="F61" location="'#16'!B82" display="Link"/>
-    <hyperlink ref="F55" location="'#15'!B2" display="Link"/>
-    <hyperlink ref="F62" location="'#16'!B89" display="Link"/>
-    <hyperlink ref="F63" location="'#16'!B10" display="Link"/>
-    <hyperlink ref="F94" location="'#31'!B2" display="Link"/>
-    <hyperlink ref="F83" location="'#24'!B2" display="Link"/>
-    <hyperlink ref="F84" location="'#24'!B2" display="Link"/>
-    <hyperlink ref="F84:G84" location="'#24'!B26" display="Link"/>
-    <hyperlink ref="F85" location="'#25'!B2" display="Link"/>
-    <hyperlink ref="F76" location="'#19'!B2" display="Link"/>
-    <hyperlink ref="F91" location="'#30'!B2" display="Link"/>
-    <hyperlink ref="F89" location="'#29'!B2" display="Link"/>
-    <hyperlink ref="F95" location="'#32'!B2" display="Link"/>
+    <hyperlink ref="F56" location="'#13'!B2" display="Link"/>
+    <hyperlink ref="F61" location="'#16'!B10" display="Link"/>
+    <hyperlink ref="F62" location="'#16'!B28" display="Link"/>
+    <hyperlink ref="F63" location="'#16'!B62" display="Link"/>
+    <hyperlink ref="F64" location="'#16'!B82" display="Link"/>
+    <hyperlink ref="F58" location="'#15'!B2" display="Link"/>
+    <hyperlink ref="F65" location="'#16'!B89" display="Link"/>
+    <hyperlink ref="F66" location="'#16'!B10" display="Link"/>
+    <hyperlink ref="F97" location="'#31'!B2" display="Link"/>
+    <hyperlink ref="F86" location="'#24'!B2" display="Link"/>
+    <hyperlink ref="F87" location="'#24'!B2" display="Link"/>
+    <hyperlink ref="F87:G87" location="'#24'!B26" display="Link"/>
+    <hyperlink ref="F88" location="'#25'!B2" display="Link"/>
+    <hyperlink ref="F79" location="'#19'!B2" display="Link"/>
+    <hyperlink ref="F94" location="'#30'!B8" display="Link"/>
+    <hyperlink ref="F92" location="'#29'!B2" display="Link"/>
+    <hyperlink ref="F98" location="'#32'!B2" display="Link"/>
+    <hyperlink ref="F93" location="'#30'!B2" display="Link"/>
+    <hyperlink ref="F95" location="'#30'!B8" display="Link"/>
+    <hyperlink ref="F95:G95" location="'#30'!B24" display="Link"/>
+    <hyperlink ref="F96" location="'#30'!B35" display="Link"/>
+    <hyperlink ref="F51" location="'#11'!B2" display="Link"/>
+    <hyperlink ref="F52" location="'#11'!B4" display="Link"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId12"/>

--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" firstSheet="1" activeTab="13"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Knowhow" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="888">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1189" uniqueCount="902">
   <si>
     <t>No.</t>
   </si>
@@ -11090,12 +11090,6 @@
     <t>Mô tả :</t>
   </si>
   <si>
-    <t xml:space="preserve">Chạy 2 vòng lặp lồng nhau đi qua các phần tử của mảng, vector. Vòng lặp 1 bằng số phần tử mảng, vòng lặp bằng số phần tử mảng </t>
-  </si>
-  <si>
-    <t>và kiểm tra xem phần tử nào lớn/nhỏ hơn thì đẩy ra sau ( giống như việc nổi bọt)</t>
-  </si>
-  <si>
     <t>int arr = {3, 5, 6 , 9, 14};</t>
   </si>
   <si>
@@ -11112,13 +11106,1139 @@
   </si>
   <si>
     <t xml:space="preserve">        }</t>
+  </si>
+  <si>
+    <t>Selection sort</t>
+  </si>
+  <si>
+    <r>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>};</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>sizeof</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>sizeof</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>]);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>minIdx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>for</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>++</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>minIdx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>for</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>++</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCE92A4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>if</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>minIdx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>])</t>
+    </r>
+  </si>
+  <si>
+    <t> {</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>swap</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>j</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>],</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>minIdx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>]);</t>
+    </r>
+  </si>
+  <si>
+    <t> }</t>
+  </si>
+  <si>
+    <t>và kiểm tra xem trong 2 phần tử liền kề, phần tử nào lớn/nhỏ hơn thì đẩy ra sau ( giống như việc nổi bọt)</t>
+  </si>
+  <si>
+    <t>Chạy 2 vòng lặp lồng nhau đi qua các phần tử của mảng, vector. Vòng lặp 1 bằng số phần tử mảng - 1. Lặp tiếp bằng số phần tử mảng -1</t>
+  </si>
+  <si>
+    <t>Chạy 2 vòng lặp lồng nhau đi qua các phần tử của mảng, vector. Vòng lặp 1 bằng số phần tử mảng, chọn ra index ở lần lặp đó. Lặp tiếp bằng số phần tử mảng - 1</t>
+  </si>
+  <si>
+    <t>và kiểm tra xem index ở vòng trên với các phần tử còn lại thì cái nào lớn hơn ? Nhỏ hơn thì được swap về đầu chuỗi</t>
+  </si>
+  <si>
+    <t>Insertion Sort</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -11292,6 +12412,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF4EC9B0"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFCE92A4"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -11705,7 +12831,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -11921,6 +13047,10 @@
     <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -11954,8 +13084,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -16143,19 +17272,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:K22"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="5.7265625" customWidth="1"/>
-    <col min="3" max="3" width="37.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.453125" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" customWidth="1"/>
+    <col min="3" max="3" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.42578125" customWidth="1"/>
     <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="18.5">
+    <row r="2" spans="2:11" ht="18.75">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -16181,7 +17310,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:11" ht="43.5">
+    <row r="3" spans="2:11" ht="45">
       <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
@@ -16535,9 +17664,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Q30"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="11" max="11" width="3.7265625" customWidth="1"/>
+    <col min="11" max="11" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:17">
@@ -16867,12 +17996,12 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E76"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="4.453125" customWidth="1"/>
-    <col min="3" max="3" width="39.7265625" customWidth="1"/>
-    <col min="4" max="4" width="50.81640625" customWidth="1"/>
-    <col min="5" max="5" width="75.453125" customWidth="1"/>
+    <col min="2" max="2" width="4.42578125" customWidth="1"/>
+    <col min="3" max="3" width="39.7109375" customWidth="1"/>
+    <col min="4" max="4" width="50.85546875" customWidth="1"/>
+    <col min="5" max="5" width="75.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.5">
@@ -16880,7 +18009,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="23.5">
+    <row r="2" spans="1:5" ht="23.25">
       <c r="B2" s="63" t="s">
         <v>420</v>
       </c>
@@ -16899,7 +18028,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="43.5">
+    <row r="5" spans="1:5" ht="45">
       <c r="B5" s="69">
         <v>1</v>
       </c>
@@ -16927,7 +18056,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="29">
+    <row r="7" spans="1:5" ht="30">
       <c r="B7" s="69">
         <v>3</v>
       </c>
@@ -16941,7 +18070,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="23.5">
+    <row r="10" spans="1:5" ht="23.25">
       <c r="B10" s="63" t="s">
         <v>344</v>
       </c>
@@ -16960,7 +18089,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" ht="30">
       <c r="B13" s="69">
         <v>1</v>
       </c>
@@ -16974,7 +18103,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="29">
+    <row r="14" spans="1:5" ht="30">
       <c r="B14" s="69">
         <v>2</v>
       </c>
@@ -16988,7 +18117,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="29">
+    <row r="15" spans="1:5" ht="30">
       <c r="B15" s="69">
         <v>3</v>
       </c>
@@ -17002,7 +18131,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="29">
+    <row r="16" spans="1:5" ht="30">
       <c r="B16" s="69">
         <v>4</v>
       </c>
@@ -17016,7 +18145,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="145">
+    <row r="17" spans="2:5" ht="165">
       <c r="B17" s="69">
         <v>5</v>
       </c>
@@ -17030,7 +18159,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="159.5">
+    <row r="18" spans="2:5" ht="180">
       <c r="B18" s="69">
         <v>6</v>
       </c>
@@ -17044,7 +18173,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="130.5">
+    <row r="19" spans="2:5" ht="135">
       <c r="B19" s="69">
         <v>7</v>
       </c>
@@ -17058,7 +18187,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="130.5">
+    <row r="20" spans="2:5" ht="135">
       <c r="B20" s="69">
         <v>8</v>
       </c>
@@ -17072,7 +18201,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="23" spans="2:5" ht="23.5">
+    <row r="23" spans="2:5" ht="23.25">
       <c r="B23" s="63" t="s">
         <v>419</v>
       </c>
@@ -17139,7 +18268,7 @@
       </c>
       <c r="E29" s="1"/>
     </row>
-    <row r="32" spans="2:5" ht="23.5">
+    <row r="32" spans="2:5" ht="23.25">
       <c r="B32" s="63" t="s">
         <v>418</v>
       </c>
@@ -17155,7 +18284,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="35" spans="2:4" ht="29">
+    <row r="35" spans="2:4" ht="30">
       <c r="B35" s="65">
         <v>1</v>
       </c>
@@ -17177,7 +18306,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="37" spans="2:4">
+    <row r="37" spans="2:4" ht="30">
       <c r="B37" s="65">
         <v>3</v>
       </c>
@@ -17199,7 +18328,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="41" spans="2:4" ht="23.5">
+    <row r="41" spans="2:4" ht="23.25">
       <c r="B41" s="63" t="s">
         <v>417</v>
       </c>
@@ -17215,7 +18344,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="44" spans="2:4">
+    <row r="44" spans="2:4" ht="30">
       <c r="B44" s="65">
         <v>1</v>
       </c>
@@ -17259,7 +18388,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="50" spans="2:4" ht="23.5">
+    <row r="50" spans="2:4" ht="23.25">
       <c r="B50" s="63" t="s">
         <v>416</v>
       </c>
@@ -17311,7 +18440,7 @@
     <row r="56" spans="2:4">
       <c r="B56" s="65"/>
     </row>
-    <row r="58" spans="2:4" ht="23.5">
+    <row r="58" spans="2:4" ht="23.25">
       <c r="B58" s="63" t="s">
         <v>415</v>
       </c>
@@ -17338,7 +18467,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="62" spans="2:4" ht="29">
+    <row r="62" spans="2:4" ht="45">
       <c r="B62" s="65">
         <v>2</v>
       </c>
@@ -17349,7 +18478,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="63" spans="2:4" ht="29">
+    <row r="63" spans="2:4" ht="30">
       <c r="B63" s="65">
         <v>3</v>
       </c>
@@ -17382,7 +18511,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="68" spans="2:4" ht="23.5">
+    <row r="68" spans="2:4" ht="23.25">
       <c r="B68" s="63" t="s">
         <v>400</v>
       </c>
@@ -17473,7 +18602,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:S38"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -17800,7 +18929,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:M57"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -18113,8 +19242,8 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:C18"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="B2:G44"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" t="s">
@@ -18133,12 +19262,12 @@
     </row>
     <row r="6" spans="2:3">
       <c r="C6" t="s">
-        <v>880</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="C7" t="s">
-        <v>881</v>
+        <v>897</v>
       </c>
     </row>
     <row r="9" spans="2:3">
@@ -18148,53 +19277,210 @@
     </row>
     <row r="11" spans="2:3">
       <c r="C11" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
     </row>
     <row r="12" spans="2:3">
       <c r="C12" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
     </row>
     <row r="13" spans="2:3">
       <c r="C13" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
     </row>
     <row r="14" spans="2:3">
       <c r="C14" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
     </row>
     <row r="15" spans="2:3">
       <c r="C15" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
     </row>
     <row r="16" spans="2:3">
       <c r="C16" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="17" spans="3:3">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7">
       <c r="C17" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="18" spans="3:3">
+    <row r="18" spans="2:7">
       <c r="C18" t="s">
         <v>284</v>
       </c>
     </row>
+    <row r="21" spans="2:7">
+      <c r="B21" s="6" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7">
+      <c r="C22" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7">
+      <c r="C23" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7">
+      <c r="C24" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7">
+      <c r="C26" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7">
+      <c r="C28" s="103" t="s">
+        <v>887</v>
+      </c>
+      <c r="D28" s="104"/>
+      <c r="E28" s="104"/>
+      <c r="F28" s="104"/>
+      <c r="G28" s="104"/>
+    </row>
+    <row r="29" spans="2:7">
+      <c r="C29" s="103" t="s">
+        <v>888</v>
+      </c>
+      <c r="D29" s="104"/>
+      <c r="E29" s="104"/>
+      <c r="F29" s="104"/>
+      <c r="G29" s="104"/>
+    </row>
+    <row r="30" spans="2:7">
+      <c r="C30" s="103" t="s">
+        <v>889</v>
+      </c>
+      <c r="D30" s="104"/>
+      <c r="E30" s="104"/>
+      <c r="F30" s="104"/>
+      <c r="G30" s="104"/>
+    </row>
+    <row r="31" spans="2:7">
+      <c r="C31" s="124" t="s">
+        <v>890</v>
+      </c>
+      <c r="D31" s="104"/>
+      <c r="E31" s="104"/>
+      <c r="F31" s="104"/>
+      <c r="G31" s="104"/>
+    </row>
+    <row r="32" spans="2:7">
+      <c r="C32" s="105" t="s">
+        <v>510</v>
+      </c>
+      <c r="D32" s="104"/>
+      <c r="E32" s="104"/>
+      <c r="F32" s="104"/>
+      <c r="G32" s="104"/>
+    </row>
+    <row r="33" spans="2:7">
+      <c r="C33" s="110" t="s">
+        <v>891</v>
+      </c>
+      <c r="D33" s="104"/>
+      <c r="E33" s="104"/>
+      <c r="F33" s="104"/>
+      <c r="G33" s="104"/>
+    </row>
+    <row r="34" spans="2:7">
+      <c r="C34" s="124" t="s">
+        <v>892</v>
+      </c>
+      <c r="D34" s="104"/>
+      <c r="E34" s="104"/>
+      <c r="F34" s="104"/>
+      <c r="G34" s="104"/>
+    </row>
+    <row r="35" spans="2:7">
+      <c r="C35" s="105" t="s">
+        <v>510</v>
+      </c>
+      <c r="D35" s="104"/>
+      <c r="E35" s="104"/>
+      <c r="F35" s="104"/>
+      <c r="G35" s="104"/>
+    </row>
+    <row r="36" spans="2:7">
+      <c r="C36" s="105" t="s">
+        <v>893</v>
+      </c>
+      <c r="D36" s="104"/>
+      <c r="E36" s="104"/>
+      <c r="F36" s="104"/>
+      <c r="G36" s="104"/>
+    </row>
+    <row r="37" spans="2:7">
+      <c r="C37" s="105" t="s">
+        <v>894</v>
+      </c>
+      <c r="D37" s="104"/>
+      <c r="E37" s="104"/>
+      <c r="F37" s="104"/>
+      <c r="G37" s="104"/>
+    </row>
+    <row r="38" spans="2:7">
+      <c r="C38" s="105" t="s">
+        <v>895</v>
+      </c>
+      <c r="D38" s="104"/>
+      <c r="E38" s="104"/>
+      <c r="F38" s="104"/>
+      <c r="G38" s="104"/>
+    </row>
+    <row r="39" spans="2:7">
+      <c r="C39" s="105" t="s">
+        <v>896</v>
+      </c>
+      <c r="D39" s="104"/>
+      <c r="E39" s="104"/>
+      <c r="F39" s="104"/>
+      <c r="G39" s="104"/>
+    </row>
+    <row r="40" spans="2:7">
+      <c r="C40" s="105" t="s">
+        <v>284</v>
+      </c>
+      <c r="D40" s="104"/>
+      <c r="E40" s="104"/>
+      <c r="F40" s="104"/>
+      <c r="G40" s="104"/>
+    </row>
+    <row r="41" spans="2:7">
+      <c r="C41" s="105" t="s">
+        <v>284</v>
+      </c>
+      <c r="D41" s="104"/>
+      <c r="E41" s="104"/>
+      <c r="F41" s="104"/>
+      <c r="G41" s="104"/>
+    </row>
+    <row r="44" spans="2:7">
+      <c r="B44" s="6" t="s">
+        <v>901</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E25"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -18311,7 +19597,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E16"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -18389,7 +19675,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
@@ -18436,14 +19722,14 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I48"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="18.5">
+    <row r="3" spans="2:4" ht="18.75">
       <c r="C3" s="93" t="s">
         <v>650</v>
       </c>
@@ -18576,7 +19862,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="33" spans="3:9" ht="18.5">
+    <row r="33" spans="3:9" ht="18.75">
       <c r="C33" s="93" t="s">
         <v>676</v>
       </c>
@@ -18675,7 +19961,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I101"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
@@ -18997,16 +20283,16 @@
       </c>
     </row>
     <row r="89" spans="2:9" ht="54" customHeight="1">
-      <c r="B89" s="114" t="s">
+      <c r="B89" s="116" t="s">
         <v>621</v>
       </c>
-      <c r="C89" s="115"/>
-      <c r="D89" s="115"/>
-      <c r="E89" s="115"/>
-      <c r="F89" s="115"/>
-      <c r="G89" s="115"/>
-      <c r="H89" s="115"/>
-      <c r="I89" s="115"/>
+      <c r="C89" s="117"/>
+      <c r="D89" s="117"/>
+      <c r="E89" s="117"/>
+      <c r="F89" s="117"/>
+      <c r="G89" s="117"/>
+      <c r="H89" s="117"/>
+      <c r="I89" s="117"/>
     </row>
     <row r="91" spans="2:9">
       <c r="B91" t="s">
@@ -19070,15 +20356,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:F103"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="12.26953125" customWidth="1"/>
-    <col min="4" max="4" width="13.54296875" customWidth="1"/>
-    <col min="5" max="5" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.1796875" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="18.5">
+    <row r="2" spans="2:6" ht="18.75">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -20221,7 +21507,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
@@ -20266,7 +21552,7 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Q108"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:10">
       <c r="B2" t="s">
@@ -22071,7 +23357,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E27"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -22203,7 +23489,7 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:F27"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
@@ -22331,9 +23617,9 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:B39"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="22.1796875" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:2">
@@ -22450,7 +23736,7 @@
       </c>
     </row>
     <row r="33" spans="2:2">
-      <c r="B33" s="122" t="s">
+      <c r="B33" s="111" t="s">
         <v>871</v>
       </c>
     </row>
@@ -22488,7 +23774,7 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:O20"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:15">
       <c r="B2" s="6" t="s">
@@ -22547,21 +23833,21 @@
       <c r="D16" t="s">
         <v>715</v>
       </c>
-      <c r="I16" s="116" t="s">
+      <c r="I16" s="118" t="s">
         <v>719</v>
       </c>
-      <c r="J16" s="117"/>
+      <c r="J16" s="119"/>
     </row>
     <row r="17" spans="3:10" ht="15" customHeight="1">
-      <c r="I17" s="118"/>
-      <c r="J17" s="119"/>
+      <c r="I17" s="120"/>
+      <c r="J17" s="121"/>
     </row>
     <row r="18" spans="3:10">
       <c r="D18" t="s">
         <v>716</v>
       </c>
-      <c r="I18" s="120"/>
-      <c r="J18" s="121"/>
+      <c r="I18" s="122"/>
+      <c r="J18" s="123"/>
     </row>
     <row r="19" spans="3:10">
       <c r="C19" t="s">
@@ -22585,7 +23871,7 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:K18"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:11">
       <c r="B2" t="s">
@@ -22671,13 +23957,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:G99"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="B1:G104"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="60.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="68.54296875" customWidth="1"/>
-    <col min="6" max="6" width="9.7265625" customWidth="1"/>
+    <col min="3" max="3" width="60.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6">
@@ -22685,7 +23971,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="2:6" ht="18.5">
+    <row r="2" spans="2:6" ht="18.75">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -23439,7 +24725,7 @@
         <v>712</v>
       </c>
       <c r="D51" s="51">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E51" s="16" t="s">
         <v>436</v>
@@ -23464,115 +24750,91 @@
       </c>
     </row>
     <row r="53" spans="2:6">
-      <c r="B53" s="5"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="51"/>
+      <c r="B53" s="5">
+        <v>11.2</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>886</v>
+      </c>
+      <c r="D53" s="42">
+        <v>1</v>
+      </c>
       <c r="E53" s="16"/>
-      <c r="F53" s="16"/>
+      <c r="F53" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="5"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="51"/>
+      <c r="B54" s="5">
+        <v>11.3</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>901</v>
+      </c>
+      <c r="D54" s="51">
+        <v>0</v>
+      </c>
       <c r="E54" s="16"/>
-      <c r="F54" s="16"/>
+      <c r="F54" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="5"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="51"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="16"/>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="5"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="51"/>
+      <c r="E56" s="16"/>
+      <c r="F56" s="16"/>
+    </row>
+    <row r="57" spans="2:6">
+      <c r="B57" s="5"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="51"/>
+      <c r="E57" s="16"/>
+      <c r="F57" s="16"/>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="5"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="51"/>
+      <c r="E58" s="16"/>
+      <c r="F58" s="16"/>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="5"/>
+      <c r="C59" s="7"/>
+      <c r="D59" s="51"/>
+      <c r="E59" s="16"/>
+      <c r="F59" s="16"/>
+    </row>
+    <row r="60" spans="2:6">
+      <c r="B60" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C60" s="6" t="s">
         <v>500</v>
-      </c>
-      <c r="D55" s="42">
-        <v>1</v>
-      </c>
-      <c r="E55" s="6"/>
-      <c r="F55" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="56" spans="2:6">
-      <c r="B56" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>438</v>
-      </c>
-      <c r="D56" s="42">
-        <v>1</v>
-      </c>
-      <c r="E56" s="6"/>
-      <c r="F56" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="57" spans="2:6">
-      <c r="B57" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>439</v>
-      </c>
-      <c r="D57" s="42">
-        <v>1</v>
-      </c>
-      <c r="E57" s="6"/>
-      <c r="F57" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="58" spans="2:6" ht="43.5">
-      <c r="B58" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>649</v>
-      </c>
-      <c r="D58" s="42">
-        <v>1</v>
-      </c>
-      <c r="E58" s="6"/>
-      <c r="F58" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="59" spans="2:6">
-      <c r="B59" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>449</v>
-      </c>
-      <c r="D59" s="42">
-        <v>1</v>
-      </c>
-      <c r="E59" s="16" t="s">
-        <v>463</v>
-      </c>
-      <c r="F59" s="6"/>
-    </row>
-    <row r="60" spans="2:6">
-      <c r="B60" s="5">
-        <v>16.100000000000001</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>474</v>
       </c>
       <c r="D60" s="42">
         <v>1</v>
       </c>
-      <c r="E60" s="16"/>
+      <c r="E60" s="6"/>
       <c r="F60" s="16" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="5">
-        <v>16.2</v>
+      <c r="B61" s="5" t="s">
+        <v>322</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>461</v>
+        <v>438</v>
       </c>
       <c r="D61" s="42">
         <v>1</v>
@@ -23583,11 +24845,11 @@
       </c>
     </row>
     <row r="62" spans="2:6">
-      <c r="B62" s="5">
-        <v>16.3</v>
+      <c r="B62" s="5" t="s">
+        <v>435</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="D62" s="42">
         <v>1</v>
@@ -23597,12 +24859,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="2:6" ht="29">
-      <c r="B63" s="5">
-        <v>16.399999999999999</v>
+    <row r="63" spans="2:6" ht="45">
+      <c r="B63" s="5" t="s">
+        <v>447</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>620</v>
+        <v>649</v>
       </c>
       <c r="D63" s="42">
         <v>1</v>
@@ -23613,159 +24875,179 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="5">
-        <v>16.5</v>
+      <c r="B64" s="5" t="s">
+        <v>448</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>619</v>
+        <v>449</v>
       </c>
       <c r="D64" s="42">
         <v>1</v>
       </c>
-      <c r="E64" s="6"/>
-      <c r="F64" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="65" spans="2:6" ht="58">
+      <c r="E64" s="16" t="s">
+        <v>463</v>
+      </c>
+      <c r="F64" s="6"/>
+    </row>
+    <row r="65" spans="2:6">
       <c r="B65" s="5">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>621</v>
+        <v>16.100000000000001</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>474</v>
       </c>
       <c r="D65" s="42">
         <v>1</v>
       </c>
-      <c r="E65" s="6"/>
+      <c r="E65" s="16"/>
       <c r="F65" s="16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="43.5" customHeight="1">
+    <row r="66" spans="2:6">
       <c r="B66" s="5">
-        <v>16.7</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>460</v>
+        <v>16.2</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>461</v>
       </c>
       <c r="D66" s="42">
         <v>1</v>
       </c>
-      <c r="E66" s="7" t="s">
-        <v>700</v>
-      </c>
+      <c r="E66" s="6"/>
       <c r="F66" s="16" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="67" spans="2:6">
-      <c r="B67" s="5" t="s">
+      <c r="B67" s="5">
+        <v>16.3</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="D67" s="42">
+        <v>1</v>
+      </c>
+      <c r="E67" s="6"/>
+      <c r="F67" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6" ht="30">
+      <c r="B68" s="5">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>620</v>
+      </c>
+      <c r="D68" s="42">
+        <v>1</v>
+      </c>
+      <c r="E68" s="6"/>
+      <c r="F68" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="69" spans="2:6">
+      <c r="B69" s="5">
+        <v>16.5</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="D69" s="42">
+        <v>1</v>
+      </c>
+      <c r="E69" s="6"/>
+      <c r="F69" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="70" spans="2:6" ht="60">
+      <c r="B70" s="5">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>621</v>
+      </c>
+      <c r="D70" s="42">
+        <v>1</v>
+      </c>
+      <c r="E70" s="6"/>
+      <c r="F70" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6" ht="43.5" customHeight="1">
+      <c r="B71" s="5">
+        <v>16.7</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D71" s="42">
+        <v>1</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="F71" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72" spans="2:6">
+      <c r="B72" s="5" t="s">
         <v>451</v>
       </c>
-      <c r="C67" s="6" t="s">
+      <c r="C72" s="6" t="s">
         <v>452</v>
-      </c>
-      <c r="D67" s="6"/>
-      <c r="E67" s="6"/>
-      <c r="F67" s="6"/>
-    </row>
-    <row r="68" spans="2:6" ht="29">
-      <c r="B68" s="5">
-        <v>17.100000000000001</v>
-      </c>
-      <c r="C68" s="78" t="s">
-        <v>481</v>
-      </c>
-      <c r="D68" s="6"/>
-      <c r="E68" s="6"/>
-      <c r="F68" s="6"/>
-    </row>
-    <row r="69" spans="2:6" ht="29">
-      <c r="B69" s="5">
-        <v>17.2</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>453</v>
-      </c>
-      <c r="D69" s="6"/>
-      <c r="E69" s="6"/>
-      <c r="F69" s="6"/>
-    </row>
-    <row r="70" spans="2:6" ht="50.25" customHeight="1">
-      <c r="B70" s="5">
-        <v>17.3</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>469</v>
-      </c>
-      <c r="D70" s="6"/>
-      <c r="E70" s="16" t="s">
-        <v>463</v>
-      </c>
-      <c r="F70" s="6"/>
-    </row>
-    <row r="71" spans="2:6" ht="29">
-      <c r="B71" s="5">
-        <v>17.399999999999999</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>454</v>
-      </c>
-      <c r="D71" s="6"/>
-      <c r="E71" s="6"/>
-      <c r="F71" s="6"/>
-    </row>
-    <row r="72" spans="2:6">
-      <c r="B72" s="5">
-        <v>17.5</v>
-      </c>
-      <c r="C72" s="6" t="s">
-        <v>455</v>
       </c>
       <c r="D72" s="6"/>
       <c r="E72" s="6"/>
       <c r="F72" s="6"/>
     </row>
-    <row r="73" spans="2:6">
-      <c r="B73" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="C73" s="6" t="s">
-        <v>459</v>
+    <row r="73" spans="2:6" ht="30">
+      <c r="B73" s="5">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="C73" s="78" t="s">
+        <v>481</v>
       </c>
       <c r="D73" s="6"/>
       <c r="E73" s="6"/>
       <c r="F73" s="6"/>
     </row>
-    <row r="74" spans="2:6">
+    <row r="74" spans="2:6" ht="30">
       <c r="B74" s="5">
-        <v>18.100000000000001</v>
-      </c>
-      <c r="C74" s="6" t="s">
-        <v>457</v>
+        <v>17.2</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>453</v>
       </c>
       <c r="D74" s="6"/>
       <c r="E74" s="6"/>
       <c r="F74" s="6"/>
     </row>
-    <row r="75" spans="2:6">
+    <row r="75" spans="2:6" ht="50.25" customHeight="1">
       <c r="B75" s="5">
-        <v>18.2</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>458</v>
+        <v>17.3</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>469</v>
       </c>
       <c r="D75" s="6"/>
-      <c r="E75" s="6"/>
+      <c r="E75" s="16" t="s">
+        <v>463</v>
+      </c>
       <c r="F75" s="6"/>
     </row>
-    <row r="76" spans="2:6">
+    <row r="76" spans="2:6" ht="30">
       <c r="B76" s="5">
-        <v>18.3</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>484</v>
+        <v>17.399999999999999</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>454</v>
       </c>
       <c r="D76" s="6"/>
       <c r="E76" s="6"/>
@@ -23773,10 +25055,10 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="5">
-        <v>18.399999999999999</v>
+        <v>17.5</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>485</v>
+        <v>455</v>
       </c>
       <c r="D77" s="6"/>
       <c r="E77" s="6"/>
@@ -23784,51 +25066,43 @@
     </row>
     <row r="78" spans="2:6">
       <c r="B78" s="5" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>876</v>
-      </c>
-      <c r="D78" s="123">
-        <v>0.9</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="D78" s="6"/>
       <c r="E78" s="6"/>
-      <c r="F78" s="43" t="s">
-        <v>121</v>
-      </c>
+      <c r="F78" s="6"/>
     </row>
     <row r="79" spans="2:6">
       <c r="B79" s="5">
-        <v>19.100000000000001</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>480</v>
-      </c>
-      <c r="D79" s="51">
-        <v>0.9</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="D79" s="6"/>
       <c r="E79" s="6"/>
-      <c r="F79" s="16" t="s">
-        <v>14</v>
-      </c>
+      <c r="F79" s="6"/>
     </row>
     <row r="80" spans="2:6">
-      <c r="B80" s="5" t="s">
-        <v>464</v>
+      <c r="B80" s="5">
+        <v>18.2</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>437</v>
+        <v>458</v>
       </c>
       <c r="D80" s="6"/>
       <c r="E80" s="6"/>
       <c r="F80" s="6"/>
     </row>
     <row r="81" spans="2:7">
-      <c r="B81" s="5" t="s">
-        <v>465</v>
+      <c r="B81" s="5">
+        <v>18.3</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>288</v>
+        <v>484</v>
       </c>
       <c r="D81" s="6"/>
       <c r="E81" s="6"/>
@@ -23836,141 +25110,138 @@
     </row>
     <row r="82" spans="2:7">
       <c r="B82" s="5">
-        <v>21.1</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>432</v>
+        <v>485</v>
       </c>
       <c r="D82" s="6"/>
       <c r="E82" s="6"/>
       <c r="F82" s="6"/>
     </row>
-    <row r="83" spans="2:7" ht="29">
-      <c r="B83" s="5">
-        <v>21.2</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>470</v>
-      </c>
-      <c r="D83" s="6"/>
+    <row r="83" spans="2:7">
+      <c r="B83" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>876</v>
+      </c>
+      <c r="D83" s="112">
+        <v>0.9</v>
+      </c>
       <c r="E83" s="6"/>
-      <c r="F83" s="6"/>
+      <c r="F83" s="43" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="84" spans="2:7">
-      <c r="B84" s="5" t="s">
-        <v>466</v>
+      <c r="B84" s="5">
+        <v>19.100000000000001</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="D84" s="6"/>
-      <c r="E84" s="16" t="s">
-        <v>467</v>
-      </c>
-      <c r="F84" s="6"/>
-    </row>
-    <row r="85" spans="2:7" ht="29">
+        <v>480</v>
+      </c>
+      <c r="D84" s="51">
+        <v>0.9</v>
+      </c>
+      <c r="E84" s="6"/>
+      <c r="F84" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="85" spans="2:7">
       <c r="B85" s="5" t="s">
-        <v>468</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>730</v>
-      </c>
-      <c r="D85" s="42">
-        <v>1</v>
-      </c>
-      <c r="E85" s="16" t="s">
-        <v>467</v>
-      </c>
-      <c r="F85" s="16"/>
+        <v>464</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="D85" s="6"/>
+      <c r="E85" s="6"/>
+      <c r="F85" s="6"/>
     </row>
     <row r="86" spans="2:7">
-      <c r="B86" s="5">
-        <v>24.1</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>731</v>
-      </c>
-      <c r="D86" s="42">
-        <v>1</v>
-      </c>
-      <c r="E86" s="16"/>
-      <c r="F86" s="16" t="s">
-        <v>14</v>
-      </c>
+      <c r="B86" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="D86" s="6"/>
+      <c r="E86" s="6"/>
+      <c r="F86" s="6"/>
     </row>
     <row r="87" spans="2:7">
       <c r="B87" s="5">
-        <v>24.2</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>775</v>
-      </c>
-      <c r="D87" s="42">
-        <v>1</v>
-      </c>
-      <c r="E87" s="16"/>
-      <c r="F87" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G87" s="48"/>
-    </row>
-    <row r="88" spans="2:7">
-      <c r="B88" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>478</v>
-      </c>
-      <c r="D88" s="42">
-        <v>1</v>
-      </c>
-      <c r="E88" s="16"/>
-      <c r="F88" s="16" t="s">
-        <v>14</v>
-      </c>
+        <v>21.1</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="D87" s="6"/>
+      <c r="E87" s="6"/>
+      <c r="F87" s="6"/>
+    </row>
+    <row r="88" spans="2:7" ht="30">
+      <c r="B88" s="5">
+        <v>21.2</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="D88" s="6"/>
+      <c r="E88" s="6"/>
+      <c r="F88" s="6"/>
     </row>
     <row r="89" spans="2:7">
       <c r="B89" s="5" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>479</v>
+        <v>323</v>
       </c>
       <c r="D89" s="6"/>
-      <c r="E89" s="16"/>
+      <c r="E89" s="16" t="s">
+        <v>467</v>
+      </c>
       <c r="F89" s="6"/>
     </row>
-    <row r="90" spans="2:7" ht="58">
+    <row r="90" spans="2:7" ht="30">
       <c r="B90" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="C90" s="79" t="s">
-        <v>482</v>
-      </c>
-      <c r="D90" s="6"/>
+        <v>468</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>730</v>
+      </c>
+      <c r="D90" s="42">
+        <v>1</v>
+      </c>
       <c r="E90" s="16" t="s">
-        <v>483</v>
-      </c>
-      <c r="F90" s="6"/>
-    </row>
-    <row r="91" spans="2:7" ht="43.5">
-      <c r="B91" s="5" t="s">
-        <v>487</v>
+        <v>467</v>
+      </c>
+      <c r="F90" s="16"/>
+    </row>
+    <row r="91" spans="2:7">
+      <c r="B91" s="5">
+        <v>24.1</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>778</v>
-      </c>
-      <c r="D91" s="6"/>
+        <v>731</v>
+      </c>
+      <c r="D91" s="42">
+        <v>1</v>
+      </c>
       <c r="E91" s="16"/>
-      <c r="F91" s="6"/>
+      <c r="F91" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="92" spans="2:7">
-      <c r="B92" s="5" t="s">
-        <v>488</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>814</v>
+      <c r="B92" s="5">
+        <v>24.2</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>775</v>
       </c>
       <c r="D92" s="42">
         <v>1</v>
@@ -23979,13 +25250,14 @@
       <c r="F92" s="16" t="s">
         <v>14</v>
       </c>
+      <c r="G92" s="48"/>
     </row>
     <row r="93" spans="2:7">
       <c r="B93" s="5" t="s">
-        <v>489</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>811</v>
+        <v>475</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>478</v>
       </c>
       <c r="D93" s="42">
         <v>1</v>
@@ -23996,72 +25268,61 @@
       </c>
     </row>
     <row r="94" spans="2:7">
-      <c r="B94" s="5">
-        <v>30.1</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>808</v>
-      </c>
-      <c r="D94" s="42">
+      <c r="B94" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D94" s="6"/>
+      <c r="E94" s="16"/>
+      <c r="F94" s="6"/>
+    </row>
+    <row r="95" spans="2:7" ht="60">
+      <c r="B95" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="C95" s="79" t="s">
+        <v>482</v>
+      </c>
+      <c r="D95" s="6"/>
+      <c r="E95" s="16" t="s">
+        <v>483</v>
+      </c>
+      <c r="F95" s="6"/>
+    </row>
+    <row r="96" spans="2:7" ht="45">
+      <c r="B96" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>778</v>
+      </c>
+      <c r="D96" s="6"/>
+      <c r="E96" s="16"/>
+      <c r="F96" s="6"/>
+    </row>
+    <row r="97" spans="2:7">
+      <c r="B97" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>814</v>
+      </c>
+      <c r="D97" s="42">
         <v>1</v>
-      </c>
-      <c r="E94" s="16"/>
-      <c r="F94" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="95" spans="2:7">
-      <c r="B95" s="5">
-        <v>30.2</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>809</v>
-      </c>
-      <c r="D95" s="42">
-        <v>1</v>
-      </c>
-      <c r="E95" s="16"/>
-      <c r="F95" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G95" s="48"/>
-    </row>
-    <row r="96" spans="2:7">
-      <c r="B96" s="5">
-        <v>30.3</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>810</v>
-      </c>
-      <c r="D96" s="42">
-        <v>1</v>
-      </c>
-      <c r="E96" s="16"/>
-      <c r="F96" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="97" spans="2:6" ht="29">
-      <c r="B97" s="5" t="s">
-        <v>490</v>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>476</v>
-      </c>
-      <c r="D97" s="51">
-        <v>0.05</v>
       </c>
       <c r="E97" s="16"/>
       <c r="F97" s="16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="98" spans="2:6">
+    <row r="98" spans="2:7">
       <c r="B98" s="5" t="s">
-        <v>776</v>
+        <v>489</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>777</v>
+        <v>811</v>
       </c>
       <c r="D98" s="42">
         <v>1</v>
@@ -24071,18 +25332,94 @@
         <v>14</v>
       </c>
     </row>
-    <row r="99" spans="2:6">
-      <c r="B99" s="77" t="s">
+    <row r="99" spans="2:7">
+      <c r="B99" s="5">
+        <v>30.1</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>808</v>
+      </c>
+      <c r="D99" s="42">
+        <v>1</v>
+      </c>
+      <c r="E99" s="16"/>
+      <c r="F99" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="100" spans="2:7">
+      <c r="B100" s="5">
+        <v>30.2</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>809</v>
+      </c>
+      <c r="D100" s="42">
+        <v>1</v>
+      </c>
+      <c r="E100" s="16"/>
+      <c r="F100" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G100" s="48"/>
+    </row>
+    <row r="101" spans="2:7">
+      <c r="B101" s="5">
+        <v>30.3</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>810</v>
+      </c>
+      <c r="D101" s="42">
+        <v>1</v>
+      </c>
+      <c r="E101" s="16"/>
+      <c r="F101" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="102" spans="2:7" ht="30">
+      <c r="B102" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="D102" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="E102" s="16"/>
+      <c r="F102" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="103" spans="2:7">
+      <c r="B103" s="5" t="s">
+        <v>776</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>777</v>
+      </c>
+      <c r="D103" s="42">
+        <v>1</v>
+      </c>
+      <c r="E103" s="16"/>
+      <c r="F103" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7">
+      <c r="B104" s="77" t="s">
         <v>473</v>
       </c>
-      <c r="C99" s="57" t="s">
+      <c r="C104" s="57" t="s">
         <v>472</v>
       </c>
-      <c r="D99" s="1"/>
-      <c r="E99" s="49" t="s">
+      <c r="D104" s="1"/>
+      <c r="E104" s="49" t="s">
         <v>471</v>
       </c>
-      <c r="F99" s="1"/>
+      <c r="F104" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -24131,39 +25468,41 @@
     <hyperlink ref="F47" location="'#7'!B2" display="Link"/>
     <hyperlink ref="F48" location="'#8'!A1" display="Link"/>
     <hyperlink ref="E51" r:id="rId6"/>
-    <hyperlink ref="F57" location="'#14'!B2" display="Link"/>
-    <hyperlink ref="E59" r:id="rId7"/>
-    <hyperlink ref="E70" r:id="rId8"/>
-    <hyperlink ref="E84" r:id="rId9"/>
-    <hyperlink ref="E85" r:id="rId10"/>
-    <hyperlink ref="E99" r:id="rId11"/>
+    <hyperlink ref="F62" location="'#14'!B2" display="Link"/>
+    <hyperlink ref="E64" r:id="rId7"/>
+    <hyperlink ref="E75" r:id="rId8"/>
+    <hyperlink ref="E89" r:id="rId9"/>
+    <hyperlink ref="E90" r:id="rId10"/>
+    <hyperlink ref="E104" r:id="rId11"/>
     <hyperlink ref="F49" location="'#9'!B2" display="Link"/>
-    <hyperlink ref="F55" location="'#12'!B2" display="Link"/>
-    <hyperlink ref="F60" location="'#16'!B2" display="Link"/>
+    <hyperlink ref="F60" location="'#12'!B2" display="Link"/>
+    <hyperlink ref="F65" location="'#16'!B2" display="Link"/>
     <hyperlink ref="F50" location="'#10'!B2" display="Link"/>
-    <hyperlink ref="F56" location="'#13'!B2" display="Link"/>
-    <hyperlink ref="F61" location="'#16'!B10" display="Link"/>
-    <hyperlink ref="F62" location="'#16'!B28" display="Link"/>
-    <hyperlink ref="F63" location="'#16'!B62" display="Link"/>
-    <hyperlink ref="F64" location="'#16'!B82" display="Link"/>
-    <hyperlink ref="F58" location="'#15'!B2" display="Link"/>
-    <hyperlink ref="F65" location="'#16'!B89" display="Link"/>
+    <hyperlink ref="F61" location="'#13'!B2" display="Link"/>
     <hyperlink ref="F66" location="'#16'!B10" display="Link"/>
-    <hyperlink ref="F97" location="'#31'!B2" display="Link"/>
-    <hyperlink ref="F86" location="'#24'!B2" display="Link"/>
-    <hyperlink ref="F87" location="'#24'!B2" display="Link"/>
-    <hyperlink ref="F87:G87" location="'#24'!B26" display="Link"/>
-    <hyperlink ref="F88" location="'#25'!B2" display="Link"/>
-    <hyperlink ref="F79" location="'#19'!B2" display="Link"/>
-    <hyperlink ref="F94" location="'#30'!B8" display="Link"/>
-    <hyperlink ref="F92" location="'#29'!B2" display="Link"/>
-    <hyperlink ref="F98" location="'#32'!B2" display="Link"/>
-    <hyperlink ref="F93" location="'#30'!B2" display="Link"/>
-    <hyperlink ref="F95" location="'#30'!B8" display="Link"/>
-    <hyperlink ref="F95:G95" location="'#30'!B24" display="Link"/>
-    <hyperlink ref="F96" location="'#30'!B35" display="Link"/>
+    <hyperlink ref="F67" location="'#16'!B28" display="Link"/>
+    <hyperlink ref="F68" location="'#16'!B62" display="Link"/>
+    <hyperlink ref="F69" location="'#16'!B82" display="Link"/>
+    <hyperlink ref="F63" location="'#15'!B2" display="Link"/>
+    <hyperlink ref="F70" location="'#16'!B89" display="Link"/>
+    <hyperlink ref="F71" location="'#16'!B10" display="Link"/>
+    <hyperlink ref="F102" location="'#31'!B2" display="Link"/>
+    <hyperlink ref="F91" location="'#24'!B2" display="Link"/>
+    <hyperlink ref="F92" location="'#24'!B2" display="Link"/>
+    <hyperlink ref="F92:G92" location="'#24'!B26" display="Link"/>
+    <hyperlink ref="F93" location="'#25'!B2" display="Link"/>
+    <hyperlink ref="F84" location="'#19'!B2" display="Link"/>
+    <hyperlink ref="F99" location="'#30'!B8" display="Link"/>
+    <hyperlink ref="F97" location="'#29'!B2" display="Link"/>
+    <hyperlink ref="F103" location="'#32'!B2" display="Link"/>
+    <hyperlink ref="F98" location="'#30'!B2" display="Link"/>
+    <hyperlink ref="F100" location="'#30'!B8" display="Link"/>
+    <hyperlink ref="F100:G100" location="'#30'!B24" display="Link"/>
+    <hyperlink ref="F101" location="'#30'!B35" display="Link"/>
     <hyperlink ref="F51" location="'#11'!B2" display="Link"/>
     <hyperlink ref="F52" location="'#11'!B4" display="Link"/>
+    <hyperlink ref="F53" location="'#11'!B21" display="Link"/>
+    <hyperlink ref="F54" location="'#11'!B44" display="Link"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId12"/>
@@ -24173,13 +25512,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J164"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.26953125" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.5">
+    <row r="1" spans="1:3" ht="18.75">
       <c r="C1" s="41" t="s">
         <v>15</v>
       </c>
@@ -24436,14 +25775,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L61"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="10.453125" customWidth="1"/>
-    <col min="4" max="4" width="5.26953125" customWidth="1"/>
-    <col min="5" max="5" width="48.81640625" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" customWidth="1"/>
+    <col min="4" max="4" width="5.28515625" customWidth="1"/>
+    <col min="5" max="5" width="48.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.5">
+    <row r="1" spans="1:10" ht="18.75">
       <c r="C1" s="41" t="s">
         <v>57</v>
       </c>
@@ -24474,14 +25813,14 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15" thickBot="1">
+    <row r="12" spans="1:10" ht="15.75" thickBot="1">
       <c r="C12" s="11" t="s">
         <v>63</v>
       </c>
       <c r="D12" s="11"/>
     </row>
-    <row r="13" spans="1:10" ht="15" thickBot="1">
-      <c r="C13" s="111" t="s">
+    <row r="13" spans="1:10" ht="15.75" thickBot="1">
+      <c r="C13" s="113" t="s">
         <v>78</v>
       </c>
       <c r="D13" s="26" t="s">
@@ -24497,8 +25836,8 @@
       <c r="H13" s="24"/>
       <c r="I13" s="25"/>
     </row>
-    <row r="14" spans="1:10" ht="15" thickBot="1">
-      <c r="C14" s="112"/>
+    <row r="14" spans="1:10" ht="15.75" thickBot="1">
+      <c r="C14" s="114"/>
       <c r="D14" s="23" t="s">
         <v>65</v>
       </c>
@@ -24514,7 +25853,7 @@
       <c r="J14" s="25"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="C15" s="112"/>
+      <c r="C15" s="114"/>
       <c r="D15" s="26" t="s">
         <v>66</v>
       </c>
@@ -24529,7 +25868,7 @@
       <c r="I15" s="28"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="C16" s="112"/>
+      <c r="C16" s="114"/>
       <c r="D16" s="29"/>
       <c r="E16" s="30" t="s">
         <v>74</v>
@@ -24539,8 +25878,8 @@
       <c r="H16" s="30"/>
       <c r="I16" s="31"/>
     </row>
-    <row r="17" spans="3:12" ht="15" thickBot="1">
-      <c r="C17" s="113"/>
+    <row r="17" spans="3:12" ht="15.75" thickBot="1">
+      <c r="C17" s="115"/>
       <c r="D17" s="32"/>
       <c r="E17" s="33" t="s">
         <v>75</v>
@@ -24550,7 +25889,7 @@
       <c r="H17" s="30"/>
       <c r="I17" s="31"/>
     </row>
-    <row r="18" spans="3:12" ht="15" thickBot="1">
+    <row r="18" spans="3:12" ht="15.75" thickBot="1">
       <c r="C18" s="37" t="s">
         <v>79</v>
       </c>
@@ -24570,8 +25909,8 @@
       <c r="K18" s="24"/>
       <c r="L18" s="25"/>
     </row>
-    <row r="19" spans="3:12" ht="15" thickBot="1">
-      <c r="C19" s="111" t="s">
+    <row r="19" spans="3:12" ht="15.75" thickBot="1">
+      <c r="C19" s="113" t="s">
         <v>78</v>
       </c>
       <c r="D19" s="23" t="s">
@@ -24582,7 +25921,7 @@
       </c>
     </row>
     <row r="20" spans="3:12">
-      <c r="C20" s="112"/>
+      <c r="C20" s="114"/>
       <c r="D20" s="26" t="s">
         <v>82</v>
       </c>
@@ -24590,8 +25929,8 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="3:12" ht="15" thickBot="1">
-      <c r="C21" s="113"/>
+    <row r="21" spans="3:12" ht="15.75" thickBot="1">
+      <c r="C21" s="115"/>
       <c r="D21" s="32"/>
       <c r="E21" s="40" t="s">
         <v>84</v>
@@ -24704,10 +26043,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:V102"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="13" max="13" width="4.81640625" customWidth="1"/>
+    <col min="13" max="13" width="4.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
@@ -25222,7 +26561,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D32"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" s="6" t="s">
@@ -25345,10 +26684,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:H90"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="13.54296875" customWidth="1"/>
-    <col min="7" max="7" width="9.453125" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4">
@@ -25714,9 +27053,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Z40"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="17.1796875" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:26">

--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="1" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="6" activeTab="20"/>
   </bookViews>
   <sheets>
     <sheet name="Knowhow" sheetId="1" r:id="rId1"/>
@@ -27,12 +27,13 @@
     <sheet name="#15" sheetId="18" r:id="rId18"/>
     <sheet name="#16" sheetId="15" r:id="rId19"/>
     <sheet name="#19" sheetId="22" r:id="rId20"/>
-    <sheet name="#24" sheetId="20" r:id="rId21"/>
-    <sheet name="#25" sheetId="21" r:id="rId22"/>
-    <sheet name="#29" sheetId="23" r:id="rId23"/>
-    <sheet name="#30" sheetId="24" r:id="rId24"/>
-    <sheet name="#31" sheetId="19" r:id="rId25"/>
-    <sheet name="#32" sheetId="25" r:id="rId26"/>
+    <sheet name="#20" sheetId="27" r:id="rId21"/>
+    <sheet name="#24" sheetId="20" r:id="rId22"/>
+    <sheet name="#25" sheetId="21" r:id="rId23"/>
+    <sheet name="#29" sheetId="23" r:id="rId24"/>
+    <sheet name="#30" sheetId="24" r:id="rId25"/>
+    <sheet name="#31" sheetId="19" r:id="rId26"/>
+    <sheet name="#32" sheetId="25" r:id="rId27"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1189" uniqueCount="902">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="919">
   <si>
     <t>No.</t>
   </si>
@@ -3649,9 +3650,6 @@
     <t>https://chatgpt.com/share/690b291c-d088-8002-b37a-10bb5da410ce</t>
   </si>
   <si>
-    <t>Các Segment trong C++ ( Data Segment)</t>
-  </si>
-  <si>
     <t>RAII là gì (Resource Acquisition Is Initialization)</t>
   </si>
   <si>
@@ -12232,6 +12230,271 @@
   </si>
   <si>
     <t>Insertion Sort</t>
+  </si>
+  <si>
+    <t>RVO, move class</t>
+  </si>
+  <si>
+    <t>Copy constructor, deep copy, shallow copy</t>
+  </si>
+  <si>
+    <t>Copy constructor</t>
+  </si>
+  <si>
+    <t>Là hàm tạo ra 1 đối tượng được copy thuộc tính của đối tượng chỉ định</t>
+  </si>
+  <si>
+    <t>trong đó</t>
+  </si>
+  <si>
+    <t>shallow copy</t>
+  </si>
+  <si>
+    <t>Copy nông : copy mọi biến trong class, copy cả địa chỉ của con trỏ trong class dẫn đến 2 class dùng chung biến con trỏ</t>
+  </si>
+  <si>
+    <t>deep copy</t>
+  </si>
+  <si>
+    <t>Copy sâu : copy nhưng tạo mới các biến con trỏ trong class, để copy class sử dụng tài nguyên khác biệt so với class gốc</t>
+  </si>
+  <si>
+    <t>Phải code bằng notepad được</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Giá trị</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> mà con trỏ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>trỏ đến</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>là hằng</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> trong hàm → không được sửa!</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nhưng con trỏ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>có thể trỏ sang chỗ khác</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>void func(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>const int*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> p);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>void func(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>int const*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> p);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Con trỏ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>không được đổi nơi trỏ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tới (hằng).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Nhưng</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> giá trị nơi nó trỏ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tới </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>có thể thay đổi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>void func(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>int* const</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> p);</t>
+    </r>
+  </si>
+  <si>
+    <t>Memory Layout - Các Segment trong C++</t>
   </si>
 </sst>
 </file>
@@ -13051,6 +13314,9 @@
     <xf numFmtId="9" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -13083,9 +13349,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -18611,72 +18874,72 @@
     </row>
     <row r="3" spans="2:5">
       <c r="C3" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="5" spans="2:5">
       <c r="C5" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="D6" t="s">
+        <v>492</v>
+      </c>
+      <c r="E6" t="s">
         <v>493</v>
-      </c>
-      <c r="E6" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="D7" t="s">
+        <v>494</v>
+      </c>
+      <c r="E7" t="s">
         <v>495</v>
-      </c>
-      <c r="E7" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="C9" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="C11" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="D12" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="C15" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="17" spans="3:19">
       <c r="D17" s="83" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E17" s="87"/>
       <c r="F17" s="87"/>
       <c r="G17" s="87"/>
       <c r="H17" s="87"/>
       <c r="I17" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="18" spans="3:19">
       <c r="D18" s="83" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E18" s="87"/>
       <c r="F18" s="87"/>
       <c r="G18" s="87"/>
       <c r="H18" s="87"/>
       <c r="I18" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="19" spans="3:19">
@@ -18688,31 +18951,31 @@
     </row>
     <row r="20" spans="3:19">
       <c r="D20" s="85" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E20" s="87"/>
       <c r="F20" s="87"/>
       <c r="G20" s="87"/>
       <c r="H20" s="87"/>
       <c r="I20" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="21" spans="3:19">
       <c r="D21" s="86" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E21" s="87"/>
       <c r="F21" s="87"/>
       <c r="G21" s="87"/>
       <c r="H21" s="87"/>
       <c r="I21" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="22" spans="3:19">
       <c r="D22" s="86" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E22" s="87"/>
       <c r="F22" s="87"/>
@@ -18737,7 +19000,7 @@
     </row>
     <row r="25" spans="3:19">
       <c r="D25" s="85" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E25" s="87"/>
       <c r="F25" s="87"/>
@@ -18746,7 +19009,7 @@
     </row>
     <row r="26" spans="3:19">
       <c r="D26" s="86" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E26" s="87"/>
       <c r="F26" s="87"/>
@@ -18755,7 +19018,7 @@
     </row>
     <row r="27" spans="3:19">
       <c r="D27" s="86" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E27" s="87"/>
       <c r="F27" s="87"/>
@@ -18773,7 +19036,7 @@
     </row>
     <row r="31" spans="3:19">
       <c r="C31" s="88" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D31" s="88"/>
       <c r="E31" s="88"/>
@@ -18785,7 +19048,7 @@
       <c r="K31" s="88"/>
       <c r="L31" s="88"/>
       <c r="M31" s="89" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="N31" s="89"/>
       <c r="O31" s="89"/>
@@ -18816,7 +19079,7 @@
     <row r="33" spans="3:19">
       <c r="C33" s="88"/>
       <c r="D33" s="88" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E33" s="88"/>
       <c r="F33" s="88"/>
@@ -18827,7 +19090,7 @@
       <c r="K33" s="88"/>
       <c r="L33" s="88"/>
       <c r="M33" s="89" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="N33" s="89"/>
       <c r="O33" s="89"/>
@@ -18848,7 +19111,7 @@
       <c r="K34" s="88"/>
       <c r="L34" s="88"/>
       <c r="M34" s="89" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="N34" s="89"/>
       <c r="O34" s="89"/>
@@ -18881,7 +19144,7 @@
     <row r="36" spans="3:19">
       <c r="C36" s="88"/>
       <c r="D36" s="88" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="E36" s="88"/>
       <c r="F36" s="88"/>
@@ -18895,7 +19158,7 @@
     <row r="37" spans="3:19">
       <c r="C37" s="88"/>
       <c r="D37" s="88" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E37" s="88"/>
       <c r="F37" s="88"/>
@@ -18933,101 +19196,101 @@
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="C4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="D6" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="D7" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="D8" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E8" s="80"/>
     </row>
     <row r="9" spans="2:5">
       <c r="D9" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="D10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="D11" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="D12" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="D13" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="D14" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="D15" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="D16" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="17" spans="3:12">
       <c r="D17" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="18" spans="3:12">
       <c r="D18" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="19" spans="3:12">
       <c r="D19" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="22" spans="3:12">
       <c r="C22" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="23" spans="3:12">
       <c r="D23" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="L23" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="24" spans="3:12">
       <c r="D24" s="81" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E24" s="90"/>
       <c r="F24" s="90"/>
@@ -19038,7 +19301,7 @@
     </row>
     <row r="25" spans="3:12">
       <c r="D25" s="81" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E25" s="90"/>
       <c r="F25" s="90"/>
@@ -19049,12 +19312,12 @@
     </row>
     <row r="27" spans="3:12">
       <c r="D27" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="28" spans="3:12">
       <c r="D28" s="81" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E28" s="90"/>
       <c r="F28" s="90"/>
@@ -19065,7 +19328,7 @@
     </row>
     <row r="29" spans="3:12">
       <c r="D29" s="81" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E29" s="90"/>
       <c r="F29" s="90"/>
@@ -19076,7 +19339,7 @@
     </row>
     <row r="30" spans="3:12">
       <c r="D30" s="82" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E30" s="90"/>
       <c r="F30" s="90"/>
@@ -19087,42 +19350,42 @@
     </row>
     <row r="33" spans="3:13">
       <c r="D33" s="91" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="34" spans="3:13">
       <c r="E34" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="35" spans="3:13">
       <c r="F35" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="36" spans="3:13">
       <c r="F36" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="39" spans="3:13">
       <c r="C39" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="41" spans="3:13">
       <c r="D41" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="43" spans="3:13">
       <c r="D43" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="44" spans="3:13">
       <c r="E44" s="81" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F44" s="90"/>
       <c r="G44" s="90"/>
@@ -19146,7 +19409,7 @@
     </row>
     <row r="46" spans="3:13">
       <c r="E46" s="81" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F46" s="90"/>
       <c r="G46" s="90"/>
@@ -19159,7 +19422,7 @@
     </row>
     <row r="47" spans="3:13">
       <c r="E47" s="81" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="F47" s="90"/>
       <c r="G47" s="90"/>
@@ -19172,7 +19435,7 @@
     </row>
     <row r="48" spans="3:13">
       <c r="E48" s="81" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="F48" s="90"/>
       <c r="G48" s="90"/>
@@ -19185,7 +19448,7 @@
     </row>
     <row r="49" spans="4:13">
       <c r="E49" s="82" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="F49" s="90"/>
       <c r="G49" s="90"/>
@@ -19198,7 +19461,7 @@
     </row>
     <row r="50" spans="4:13">
       <c r="E50" s="81" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F50" s="90"/>
       <c r="G50" s="90"/>
@@ -19211,27 +19474,27 @@
     </row>
     <row r="53" spans="4:13">
       <c r="D53" s="91" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="54" spans="4:13">
       <c r="E54" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="55" spans="4:13">
       <c r="E55" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="56" spans="4:13">
       <c r="E56" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="57" spans="4:13">
       <c r="E57" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
   </sheetData>
@@ -19247,27 +19510,27 @@
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" s="6" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="C5" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="6" spans="2:3">
       <c r="C6" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="C7" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="9" spans="2:3">
@@ -19277,32 +19540,32 @@
     </row>
     <row r="11" spans="2:3">
       <c r="C11" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="12" spans="2:3">
       <c r="C12" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="13" spans="2:3">
       <c r="C13" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="14" spans="2:3">
       <c r="C14" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="15" spans="2:3">
       <c r="C15" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="16" spans="2:3">
       <c r="C16" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="17" spans="2:7">
@@ -19317,22 +19580,22 @@
     </row>
     <row r="21" spans="2:7">
       <c r="B21" s="6" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="22" spans="2:7">
       <c r="C22" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="23" spans="2:7">
       <c r="C23" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="24" spans="2:7">
       <c r="C24" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="26" spans="2:7">
@@ -19342,7 +19605,7 @@
     </row>
     <row r="28" spans="2:7">
       <c r="C28" s="103" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="D28" s="104"/>
       <c r="E28" s="104"/>
@@ -19351,7 +19614,7 @@
     </row>
     <row r="29" spans="2:7">
       <c r="C29" s="103" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="D29" s="104"/>
       <c r="E29" s="104"/>
@@ -19360,7 +19623,7 @@
     </row>
     <row r="30" spans="2:7">
       <c r="C30" s="103" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="D30" s="104"/>
       <c r="E30" s="104"/>
@@ -19368,8 +19631,8 @@
       <c r="G30" s="104"/>
     </row>
     <row r="31" spans="2:7">
-      <c r="C31" s="124" t="s">
-        <v>890</v>
+      <c r="C31" s="113" t="s">
+        <v>889</v>
       </c>
       <c r="D31" s="104"/>
       <c r="E31" s="104"/>
@@ -19378,7 +19641,7 @@
     </row>
     <row r="32" spans="2:7">
       <c r="C32" s="105" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D32" s="104"/>
       <c r="E32" s="104"/>
@@ -19387,7 +19650,7 @@
     </row>
     <row r="33" spans="2:7">
       <c r="C33" s="110" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="D33" s="104"/>
       <c r="E33" s="104"/>
@@ -19395,8 +19658,8 @@
       <c r="G33" s="104"/>
     </row>
     <row r="34" spans="2:7">
-      <c r="C34" s="124" t="s">
-        <v>892</v>
+      <c r="C34" s="113" t="s">
+        <v>891</v>
       </c>
       <c r="D34" s="104"/>
       <c r="E34" s="104"/>
@@ -19405,7 +19668,7 @@
     </row>
     <row r="35" spans="2:7">
       <c r="C35" s="105" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D35" s="104"/>
       <c r="E35" s="104"/>
@@ -19414,7 +19677,7 @@
     </row>
     <row r="36" spans="2:7">
       <c r="C36" s="105" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="D36" s="104"/>
       <c r="E36" s="104"/>
@@ -19423,7 +19686,7 @@
     </row>
     <row r="37" spans="2:7">
       <c r="C37" s="105" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="D37" s="104"/>
       <c r="E37" s="104"/>
@@ -19432,7 +19695,7 @@
     </row>
     <row r="38" spans="2:7">
       <c r="C38" s="105" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="D38" s="104"/>
       <c r="E38" s="104"/>
@@ -19441,7 +19704,7 @@
     </row>
     <row r="39" spans="2:7">
       <c r="C39" s="105" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="D39" s="104"/>
       <c r="E39" s="104"/>
@@ -19468,7 +19731,7 @@
     </row>
     <row r="44" spans="2:7">
       <c r="B44" s="6" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
   </sheetData>
@@ -19484,89 +19747,89 @@
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="3" spans="2:5">
       <c r="C3" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="C4" s="80" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="C7" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="C8" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="C10" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="C11" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="C12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="C13" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="C14" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="C15" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="C16" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="17" spans="3:3">
       <c r="C17" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="18" spans="3:3">
       <c r="C18" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="20" spans="3:3">
       <c r="C20" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="21" spans="3:3">
@@ -19576,17 +19839,17 @@
     </row>
     <row r="23" spans="3:3">
       <c r="C23" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="24" spans="3:3">
       <c r="C24" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="25" spans="3:3">
       <c r="C25" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
@@ -19601,70 +19864,70 @@
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="3" spans="2:5">
       <c r="C3" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="C4" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="C6" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="D7" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="D8" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="C10" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="C11" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="D12" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="C13" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="D14" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="E14" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="C15" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="D16" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
   </sheetData>
@@ -19679,38 +19942,38 @@
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="3" spans="2:4">
       <c r="C3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="C4" s="76" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="5" spans="2:4">
       <c r="B5" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="6" spans="2:4">
       <c r="C6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D6" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="7" spans="2:4">
       <c r="C7" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
   </sheetData>
@@ -19726,230 +19989,230 @@
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="3" spans="2:4" ht="18.75">
       <c r="C3" s="93" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D3" s="94"/>
     </row>
     <row r="5" spans="2:4">
       <c r="C5" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D5" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="6" spans="2:4">
       <c r="D6" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="7" spans="2:4">
       <c r="D7" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="8" spans="2:4">
       <c r="D8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="9" spans="2:4">
       <c r="D9" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="11" spans="2:4">
       <c r="C11" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D11" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="12" spans="2:4">
       <c r="D12" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="13" spans="2:4">
       <c r="D13" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="14" spans="2:4">
       <c r="D14" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="15" spans="2:4">
       <c r="D15" s="92" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="16" spans="2:4">
       <c r="D16" s="76" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="17" spans="3:5">
       <c r="C17" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D17" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="18" spans="3:5">
       <c r="D18" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="19" spans="3:5">
       <c r="E19" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="20" spans="3:5">
       <c r="E20" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="21" spans="3:5">
       <c r="D21" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="22" spans="3:5">
       <c r="D22" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="23" spans="3:5">
       <c r="D23" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="24" spans="3:5">
       <c r="D24" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="26" spans="3:5">
       <c r="C26" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D26" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="27" spans="3:5">
       <c r="D27" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="28" spans="3:5">
       <c r="E28" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="29" spans="3:5">
       <c r="E29" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="33" spans="3:9" ht="18.75">
       <c r="C33" s="93" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D33" s="94"/>
     </row>
     <row r="35" spans="3:9">
       <c r="C35" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="36" spans="3:9">
       <c r="D36" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="38" spans="3:9">
       <c r="D38" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="39" spans="3:9">
       <c r="E39" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="40" spans="3:9">
       <c r="E40" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G40" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="I40" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="41" spans="3:9">
       <c r="E41" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G41" t="s">
+        <v>684</v>
+      </c>
+      <c r="I41" t="s">
         <v>685</v>
-      </c>
-      <c r="I41" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="42" spans="3:9">
       <c r="E42" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="G42" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="44" spans="3:9">
       <c r="D44" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="45" spans="3:9">
       <c r="E45" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="46" spans="3:9">
       <c r="E46" t="s">
+        <v>689</v>
+      </c>
+      <c r="G46" t="s">
         <v>690</v>
-      </c>
-      <c r="G46" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="47" spans="3:9">
       <c r="E47" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G47" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="48" spans="3:9">
       <c r="E48" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="G48" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
   </sheetData>
@@ -19960,101 +20223,101 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:I101"/>
+  <dimension ref="B2:I113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="3" spans="2:4">
       <c r="C3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D3" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="C4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="5" spans="2:4">
       <c r="C5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D5" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="10" spans="2:4">
       <c r="B10" s="6" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="11" spans="2:4">
       <c r="C11" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="12" spans="2:4">
       <c r="C12" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="13" spans="2:4">
       <c r="C13" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="14" spans="2:4">
       <c r="C14" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="16" spans="2:4">
       <c r="C16" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="17" spans="2:5">
       <c r="C17" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="18" spans="2:5">
       <c r="C18" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="19" spans="2:5">
       <c r="C19" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="20" spans="2:5">
       <c r="C20" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="22" spans="2:5">
       <c r="D22" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="23" spans="2:5">
       <c r="E23" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="24" spans="2:5">
       <c r="E24" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="25" spans="2:5">
@@ -20064,167 +20327,167 @@
     </row>
     <row r="28" spans="2:5">
       <c r="B28" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="29" spans="2:5">
       <c r="C29" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="30" spans="2:5">
       <c r="D30" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="31" spans="2:5">
       <c r="D31" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="32" spans="2:5">
       <c r="D32" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="34" spans="3:5">
       <c r="D34" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="36" spans="3:5">
       <c r="D36" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="37" spans="3:5">
       <c r="E37" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="38" spans="3:5">
       <c r="E38" s="17" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="39" spans="3:5">
       <c r="E39" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="41" spans="3:5">
       <c r="E41" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="42" spans="3:5">
       <c r="E42" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="43" spans="3:5">
       <c r="E43" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="45" spans="3:5">
       <c r="C45" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="46" spans="3:5">
       <c r="D46" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="47" spans="3:5">
       <c r="D47" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="49" spans="2:5">
       <c r="D49" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="50" spans="2:5">
       <c r="E50" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="51" spans="2:5">
       <c r="E51" s="17" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="52" spans="2:5">
       <c r="E52" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="54" spans="2:5">
       <c r="E54" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="55" spans="2:5">
       <c r="E55" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="56" spans="2:5">
       <c r="E56" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="58" spans="2:5">
       <c r="D58" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="59" spans="2:5">
       <c r="D59" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="62" spans="2:5">
       <c r="B62" s="6" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="63" spans="2:5">
       <c r="C63" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="64" spans="2:5">
       <c r="C64" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="65" spans="3:4">
       <c r="C65" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="67" spans="3:4">
       <c r="C67" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="69" spans="3:4">
       <c r="D69" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="70" spans="3:4">
       <c r="D70" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="71" spans="3:4">
       <c r="D71" s="17" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="72" spans="3:4">
@@ -20234,22 +20497,22 @@
     </row>
     <row r="73" spans="3:4">
       <c r="D73" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="75" spans="3:4">
       <c r="D75" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="76" spans="3:4">
       <c r="D76" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="77" spans="3:4">
       <c r="D77" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="78" spans="3:4">
@@ -20259,89 +20522,129 @@
     </row>
     <row r="79" spans="3:4">
       <c r="D79" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="82" spans="2:9">
       <c r="B82" s="6" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="83" spans="2:9">
       <c r="C83" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="84" spans="2:9">
       <c r="C84" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="85" spans="2:9">
       <c r="C85" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="89" spans="2:9" ht="54" customHeight="1">
-      <c r="B89" s="116" t="s">
-        <v>621</v>
-      </c>
-      <c r="C89" s="117"/>
-      <c r="D89" s="117"/>
-      <c r="E89" s="117"/>
-      <c r="F89" s="117"/>
-      <c r="G89" s="117"/>
-      <c r="H89" s="117"/>
-      <c r="I89" s="117"/>
+      <c r="B89" s="117" t="s">
+        <v>620</v>
+      </c>
+      <c r="C89" s="118"/>
+      <c r="D89" s="118"/>
+      <c r="E89" s="118"/>
+      <c r="F89" s="118"/>
+      <c r="G89" s="118"/>
+      <c r="H89" s="118"/>
+      <c r="I89" s="118"/>
     </row>
     <row r="91" spans="2:9">
       <c r="B91" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="92" spans="2:9">
       <c r="C92" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="93" spans="2:9">
       <c r="C93" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="94" spans="2:9">
       <c r="D94" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="95" spans="2:9">
       <c r="D95" s="17" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="96" spans="2:9">
       <c r="C96" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="97" spans="2:4">
+      <c r="D97" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="97" spans="3:4">
-      <c r="D97" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="99" spans="3:4">
+    <row r="99" spans="2:4">
       <c r="C99" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="100" spans="2:4">
+      <c r="C100" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="100" spans="3:4">
-      <c r="C100" t="s">
+    <row r="101" spans="2:4">
+      <c r="C101" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="101" spans="3:4">
-      <c r="C101" t="s">
-        <v>703</v>
+    <row r="103" spans="2:4">
+      <c r="B103" s="6" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="105" spans="2:4">
+      <c r="C105" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="106" spans="2:4">
+      <c r="D106" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="108" spans="2:4">
+      <c r="C108" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="109" spans="2:4">
+      <c r="D109" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="110" spans="2:4">
+      <c r="D110" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="112" spans="2:4">
+      <c r="D112" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="113" spans="4:4">
+      <c r="D113" t="s">
+        <v>909</v>
       </c>
     </row>
   </sheetData>
@@ -21511,37 +21814,37 @@
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="3" spans="2:4">
       <c r="C3" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="C4" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="6" spans="2:4">
       <c r="C6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="7" spans="2:4">
       <c r="C7" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="8" spans="2:4">
       <c r="D8" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="9" spans="2:4">
       <c r="D9" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -21551,17 +21854,32 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2" spans="2:2">
+      <c r="B2" s="6" t="s">
+        <v>918</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Q108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:10">
       <c r="B2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="3" spans="2:10">
       <c r="C3" s="103" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D3" s="104"/>
       <c r="E3" s="104"/>
@@ -21573,7 +21891,7 @@
     </row>
     <row r="4" spans="2:10">
       <c r="C4" s="105" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D4" s="104"/>
       <c r="E4" s="104"/>
@@ -21585,7 +21903,7 @@
     </row>
     <row r="5" spans="2:10">
       <c r="C5" s="103" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D5" s="104"/>
       <c r="E5" s="104"/>
@@ -21597,7 +21915,7 @@
     </row>
     <row r="6" spans="2:10">
       <c r="C6" s="103" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D6" s="104"/>
       <c r="E6" s="104"/>
@@ -21609,7 +21927,7 @@
     </row>
     <row r="7" spans="2:10">
       <c r="C7" s="105" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D7" s="104"/>
       <c r="E7" s="104"/>
@@ -21621,7 +21939,7 @@
     </row>
     <row r="8" spans="2:10">
       <c r="C8" s="105" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D8" s="104"/>
       <c r="E8" s="104"/>
@@ -21633,7 +21951,7 @@
     </row>
     <row r="9" spans="2:10">
       <c r="C9" s="105" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D9" s="104"/>
       <c r="E9" s="104"/>
@@ -21657,7 +21975,7 @@
     </row>
     <row r="11" spans="2:10">
       <c r="C11" s="103" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D11" s="104"/>
       <c r="E11" s="104"/>
@@ -21669,7 +21987,7 @@
     </row>
     <row r="12" spans="2:10">
       <c r="C12" s="106" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D12" s="104"/>
       <c r="E12" s="104"/>
@@ -21681,7 +21999,7 @@
     </row>
     <row r="13" spans="2:10">
       <c r="C13" s="106" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D13" s="104"/>
       <c r="E13" s="104"/>
@@ -21693,7 +22011,7 @@
     </row>
     <row r="14" spans="2:10">
       <c r="C14" s="107" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="D14" s="104"/>
       <c r="E14" s="104"/>
@@ -21705,7 +22023,7 @@
     </row>
     <row r="15" spans="2:10">
       <c r="C15" s="105" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D15" s="104"/>
       <c r="E15" s="104"/>
@@ -21727,7 +22045,7 @@
     </row>
     <row r="17" spans="2:17">
       <c r="C17" s="103" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D17" s="104"/>
       <c r="E17" s="104"/>
@@ -21739,7 +22057,7 @@
     </row>
     <row r="18" spans="2:17">
       <c r="C18" s="105" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D18" s="104"/>
       <c r="E18" s="104"/>
@@ -21751,7 +22069,7 @@
     </row>
     <row r="19" spans="2:17">
       <c r="C19" s="107" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D19" s="104"/>
       <c r="E19" s="104"/>
@@ -21763,7 +22081,7 @@
     </row>
     <row r="20" spans="2:17">
       <c r="C20" s="107" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D20" s="104"/>
       <c r="E20" s="104"/>
@@ -21775,7 +22093,7 @@
     </row>
     <row r="21" spans="2:17">
       <c r="C21" s="109" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D21" s="104"/>
       <c r="E21" s="104"/>
@@ -21809,12 +22127,12 @@
     </row>
     <row r="26" spans="2:17">
       <c r="B26" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="27" spans="2:17">
       <c r="C27" s="109" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D27" s="104"/>
       <c r="E27" s="104"/>
@@ -21833,7 +22151,7 @@
     </row>
     <row r="28" spans="2:17">
       <c r="C28" s="109" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D28" s="104"/>
       <c r="E28" s="104"/>
@@ -21852,7 +22170,7 @@
     </row>
     <row r="29" spans="2:17">
       <c r="C29" s="109" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D29" s="104"/>
       <c r="E29" s="104"/>
@@ -21871,7 +22189,7 @@
     </row>
     <row r="30" spans="2:17">
       <c r="C30" s="109" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D30" s="104"/>
       <c r="E30" s="104"/>
@@ -21907,7 +22225,7 @@
     </row>
     <row r="32" spans="2:17">
       <c r="C32" s="103" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D32" s="104"/>
       <c r="E32" s="104"/>
@@ -21926,7 +22244,7 @@
     </row>
     <row r="33" spans="3:17">
       <c r="C33" s="105" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D33" s="104"/>
       <c r="E33" s="104"/>
@@ -21945,7 +22263,7 @@
     </row>
     <row r="34" spans="3:17">
       <c r="C34" s="103" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D34" s="104"/>
       <c r="E34" s="104"/>
@@ -21964,7 +22282,7 @@
     </row>
     <row r="35" spans="3:17">
       <c r="C35" s="106" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D35" s="104"/>
       <c r="E35" s="104"/>
@@ -21983,7 +22301,7 @@
     </row>
     <row r="36" spans="3:17">
       <c r="C36" s="103" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D36" s="104"/>
       <c r="E36" s="104"/>
@@ -22002,7 +22320,7 @@
     </row>
     <row r="37" spans="3:17">
       <c r="C37" s="103" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D37" s="104"/>
       <c r="E37" s="104"/>
@@ -22021,7 +22339,7 @@
     </row>
     <row r="38" spans="3:17">
       <c r="C38" s="105" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D38" s="104"/>
       <c r="E38" s="104"/>
@@ -22057,7 +22375,7 @@
     </row>
     <row r="40" spans="3:17">
       <c r="C40" s="103" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D40" s="104"/>
       <c r="E40" s="104"/>
@@ -22076,7 +22394,7 @@
     </row>
     <row r="41" spans="3:17">
       <c r="C41" s="105" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D41" s="104"/>
       <c r="E41" s="104"/>
@@ -22095,7 +22413,7 @@
     </row>
     <row r="42" spans="3:17">
       <c r="C42" s="103" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D42" s="104"/>
       <c r="E42" s="104"/>
@@ -22114,7 +22432,7 @@
     </row>
     <row r="43" spans="3:17">
       <c r="C43" s="107" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D43" s="104"/>
       <c r="E43" s="104"/>
@@ -22133,7 +22451,7 @@
     </row>
     <row r="44" spans="3:17">
       <c r="C44" s="107" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D44" s="104"/>
       <c r="E44" s="104"/>
@@ -22152,7 +22470,7 @@
     </row>
     <row r="45" spans="3:17">
       <c r="C45" s="103" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D45" s="104"/>
       <c r="E45" s="104"/>
@@ -22171,7 +22489,7 @@
     </row>
     <row r="46" spans="3:17">
       <c r="C46" s="103" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D46" s="104"/>
       <c r="E46" s="104"/>
@@ -22190,7 +22508,7 @@
     </row>
     <row r="47" spans="3:17">
       <c r="C47" s="105" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D47" s="104"/>
       <c r="E47" s="104"/>
@@ -22209,7 +22527,7 @@
     </row>
     <row r="48" spans="3:17">
       <c r="C48" s="110" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D48" s="104"/>
       <c r="E48" s="104"/>
@@ -22247,7 +22565,7 @@
     </row>
     <row r="50" spans="3:17">
       <c r="C50" s="103" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D50" s="104"/>
       <c r="E50" s="104"/>
@@ -22266,7 +22584,7 @@
     </row>
     <row r="51" spans="3:17">
       <c r="C51" s="105" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D51" s="104"/>
       <c r="E51" s="104"/>
@@ -22285,7 +22603,7 @@
     </row>
     <row r="52" spans="3:17">
       <c r="C52" s="110" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D52" s="104"/>
       <c r="E52" s="104"/>
@@ -22323,7 +22641,7 @@
     </row>
     <row r="54" spans="3:17">
       <c r="C54" s="103" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D54" s="104"/>
       <c r="E54" s="104"/>
@@ -22342,7 +22660,7 @@
     </row>
     <row r="55" spans="3:17">
       <c r="C55" s="105" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D55" s="104"/>
       <c r="E55" s="104"/>
@@ -22361,7 +22679,7 @@
     </row>
     <row r="56" spans="3:17">
       <c r="C56" s="105" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D56" s="104"/>
       <c r="E56" s="104"/>
@@ -22380,7 +22698,7 @@
     </row>
     <row r="57" spans="3:17">
       <c r="C57" s="105" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D57" s="104"/>
       <c r="E57" s="104"/>
@@ -22399,7 +22717,7 @@
     </row>
     <row r="58" spans="3:17">
       <c r="C58" s="105" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D58" s="104"/>
       <c r="E58" s="104"/>
@@ -22418,7 +22736,7 @@
     </row>
     <row r="59" spans="3:17">
       <c r="C59" s="105" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D59" s="104"/>
       <c r="E59" s="104"/>
@@ -22456,7 +22774,7 @@
     </row>
     <row r="61" spans="3:17">
       <c r="C61" s="103" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D61" s="104"/>
       <c r="E61" s="104"/>
@@ -22475,7 +22793,7 @@
     </row>
     <row r="62" spans="3:17">
       <c r="C62" s="105" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D62" s="104"/>
       <c r="E62" s="104"/>
@@ -22494,7 +22812,7 @@
     </row>
     <row r="63" spans="3:17">
       <c r="C63" s="110" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D63" s="104"/>
       <c r="E63" s="104"/>
@@ -22513,7 +22831,7 @@
     </row>
     <row r="64" spans="3:17">
       <c r="C64" s="106" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D64" s="104"/>
       <c r="E64" s="104"/>
@@ -22551,7 +22869,7 @@
     </row>
     <row r="66" spans="3:17">
       <c r="C66" s="105" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D66" s="104"/>
       <c r="E66" s="104"/>
@@ -22587,7 +22905,7 @@
     </row>
     <row r="68" spans="3:17">
       <c r="C68" s="103" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D68" s="104"/>
       <c r="E68" s="104"/>
@@ -22606,7 +22924,7 @@
     </row>
     <row r="69" spans="3:17">
       <c r="C69" s="105" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D69" s="104"/>
       <c r="E69" s="104"/>
@@ -22625,7 +22943,7 @@
     </row>
     <row r="70" spans="3:17">
       <c r="C70" s="103" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D70" s="104"/>
       <c r="E70" s="104"/>
@@ -22644,7 +22962,7 @@
     </row>
     <row r="71" spans="3:17">
       <c r="C71" s="107" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="D71" s="104"/>
       <c r="E71" s="104"/>
@@ -22663,7 +22981,7 @@
     </row>
     <row r="72" spans="3:17">
       <c r="C72" s="107" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D72" s="104"/>
       <c r="E72" s="104"/>
@@ -22682,7 +23000,7 @@
     </row>
     <row r="73" spans="3:17">
       <c r="C73" s="103" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D73" s="104"/>
       <c r="E73" s="104"/>
@@ -22701,7 +23019,7 @@
     </row>
     <row r="74" spans="3:17">
       <c r="C74" s="106" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D74" s="104"/>
       <c r="E74" s="104"/>
@@ -22720,7 +23038,7 @@
     </row>
     <row r="75" spans="3:17">
       <c r="C75" s="105" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D75" s="104"/>
       <c r="E75" s="104"/>
@@ -22739,7 +23057,7 @@
     </row>
     <row r="76" spans="3:17">
       <c r="C76" s="110" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D76" s="104"/>
       <c r="E76" s="104"/>
@@ -22794,7 +23112,7 @@
     </row>
     <row r="79" spans="3:17">
       <c r="C79" s="103" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D79" s="104"/>
       <c r="E79" s="104"/>
@@ -22813,7 +23131,7 @@
     </row>
     <row r="80" spans="3:17">
       <c r="C80" s="105" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D80" s="104"/>
       <c r="E80" s="104"/>
@@ -22832,7 +23150,7 @@
     </row>
     <row r="81" spans="3:17">
       <c r="C81" s="110" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D81" s="104"/>
       <c r="E81" s="104"/>
@@ -22851,7 +23169,7 @@
     </row>
     <row r="82" spans="3:17">
       <c r="C82" s="107" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D82" s="104"/>
       <c r="E82" s="104"/>
@@ -22906,7 +23224,7 @@
     </row>
     <row r="85" spans="3:17">
       <c r="C85" s="103" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D85" s="104"/>
       <c r="E85" s="104"/>
@@ -22925,7 +23243,7 @@
     </row>
     <row r="86" spans="3:17">
       <c r="C86" s="105" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D86" s="104"/>
       <c r="E86" s="104"/>
@@ -22944,7 +23262,7 @@
     </row>
     <row r="87" spans="3:17">
       <c r="C87" s="107" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D87" s="104"/>
       <c r="E87" s="104"/>
@@ -22999,7 +23317,7 @@
     </row>
     <row r="90" spans="3:17">
       <c r="C90" s="105" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D90" s="104"/>
       <c r="E90" s="104"/>
@@ -23035,7 +23353,7 @@
     </row>
     <row r="92" spans="3:17">
       <c r="C92" s="103" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D92" s="104"/>
       <c r="E92" s="104"/>
@@ -23054,7 +23372,7 @@
     </row>
     <row r="93" spans="3:17">
       <c r="C93" s="105" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D93" s="104"/>
       <c r="E93" s="104"/>
@@ -23073,7 +23391,7 @@
     </row>
     <row r="94" spans="3:17">
       <c r="C94" s="107" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D94" s="104"/>
       <c r="E94" s="104"/>
@@ -23092,7 +23410,7 @@
     </row>
     <row r="95" spans="3:17">
       <c r="C95" s="107" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D95" s="104"/>
       <c r="E95" s="104"/>
@@ -23111,7 +23429,7 @@
     </row>
     <row r="96" spans="3:17">
       <c r="C96" s="107" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D96" s="104"/>
       <c r="E96" s="104"/>
@@ -23130,7 +23448,7 @@
     </row>
     <row r="97" spans="3:17">
       <c r="C97" s="107" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="D97" s="104"/>
       <c r="E97" s="104"/>
@@ -23166,7 +23484,7 @@
     </row>
     <row r="99" spans="3:17">
       <c r="C99" s="110" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D99" s="104"/>
       <c r="E99" s="104"/>
@@ -23185,7 +23503,7 @@
     </row>
     <row r="100" spans="3:17">
       <c r="C100" s="110" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D100" s="104"/>
       <c r="E100" s="104"/>
@@ -23221,7 +23539,7 @@
     </row>
     <row r="102" spans="3:17">
       <c r="C102" s="110" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="D102" s="104"/>
       <c r="E102" s="104"/>
@@ -23240,7 +23558,7 @@
     </row>
     <row r="103" spans="3:17">
       <c r="C103" s="110" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="D103" s="104"/>
       <c r="E103" s="104"/>
@@ -23276,7 +23594,7 @@
     </row>
     <row r="105" spans="3:17">
       <c r="C105" s="110" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="D105" s="104"/>
       <c r="E105" s="104"/>
@@ -23312,7 +23630,7 @@
     </row>
     <row r="107" spans="3:17">
       <c r="C107" s="109" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D107" s="104"/>
       <c r="E107" s="104"/>
@@ -23354,130 +23672,130 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="3" spans="2:5">
       <c r="C3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="D4" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="D6" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="E7" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="E8" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="E9" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="E10" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="C12" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="D13" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="D15" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="E16" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="17" spans="2:5">
       <c r="E17" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="17" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C19" s="17"/>
     </row>
     <row r="20" spans="2:5">
       <c r="B20" s="17" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C20" s="17"/>
     </row>
     <row r="21" spans="2:5">
       <c r="C21" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="22" spans="2:5">
       <c r="D22" t="s">
+        <v>786</v>
+      </c>
+      <c r="E22" t="s">
         <v>787</v>
-      </c>
-      <c r="E22" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="23" spans="2:5">
       <c r="D23" t="s">
+        <v>788</v>
+      </c>
+      <c r="E23" t="s">
         <v>789</v>
-      </c>
-      <c r="E23" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="24" spans="2:5">
       <c r="D24" t="s">
+        <v>790</v>
+      </c>
+      <c r="E24" t="s">
         <v>791</v>
-      </c>
-      <c r="E24" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="25" spans="2:5">
       <c r="C25" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="26" spans="2:5">
       <c r="C26" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="27" spans="2:5">
       <c r="B27" s="17" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
   </sheetData>
@@ -23486,126 +23804,126 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:F27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="3" spans="2:4">
       <c r="C3" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="D4" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="5" spans="2:4">
       <c r="C5" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="6" spans="2:4">
       <c r="D6" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="7" spans="2:4">
       <c r="D7" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="8" spans="2:4">
       <c r="D8" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="10" spans="2:4">
       <c r="D10" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="12" spans="2:4">
       <c r="D12" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="13" spans="2:4">
       <c r="D13" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="14" spans="2:4">
       <c r="D14" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="15" spans="2:4">
       <c r="D15" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="16" spans="2:4">
       <c r="D16" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="18" spans="3:6">
       <c r="D18" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="20" spans="3:6">
       <c r="D20" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="22" spans="3:6">
       <c r="C22" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="23" spans="3:6">
       <c r="D23" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="24" spans="3:6">
       <c r="D24" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="F24" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="25" spans="3:6">
       <c r="D25" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="F25" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="26" spans="3:6">
       <c r="D26" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E26" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="27" spans="3:6">
       <c r="D27" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="F27" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
   </sheetData>
@@ -23614,7 +23932,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:B39"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -23624,97 +23942,97 @@
   <sheetData>
     <row r="2" spans="2:2">
       <c r="B2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="3" spans="2:2">
       <c r="B3" s="11" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" s="11" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" s="11" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="8" spans="2:2">
       <c r="B8" s="11" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" s="12" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="11" spans="2:2">
       <c r="B11" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" s="80" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" s="80" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" s="80" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="16" spans="2:2">
       <c r="B16" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" s="11" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" s="80" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="29" spans="2:2">
@@ -23722,47 +24040,47 @@
     </row>
     <row r="30" spans="2:2">
       <c r="B30" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="31" spans="2:2">
       <c r="B31" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" s="111" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" s="11" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="39" spans="2:2">
       <c r="B39" s="80" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
   </sheetData>
@@ -23771,37 +24089,37 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:O20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:15">
       <c r="B2" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="4" spans="2:15">
       <c r="C4" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="5" spans="2:15">
       <c r="C5" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="6" spans="2:15">
       <c r="C6" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="8" spans="2:15">
       <c r="F8" s="99" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="L8" s="100" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="M8" s="101"/>
       <c r="N8" s="101"/>
@@ -23809,13 +24127,13 @@
     </row>
     <row r="9" spans="2:15">
       <c r="F9" s="95" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="G9" t="s">
+        <v>709</v>
+      </c>
+      <c r="L9" s="96" t="s">
         <v>710</v>
-      </c>
-      <c r="L9" s="96" t="s">
-        <v>711</v>
       </c>
       <c r="M9" s="97"/>
       <c r="N9" s="97"/>
@@ -23823,40 +24141,40 @@
     </row>
     <row r="11" spans="2:15">
       <c r="E11" t="s">
+        <v>712</v>
+      </c>
+      <c r="L11" t="s">
         <v>713</v>
-      </c>
-      <c r="L11" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="16" spans="2:15">
       <c r="D16" t="s">
-        <v>715</v>
-      </c>
-      <c r="I16" s="118" t="s">
-        <v>719</v>
-      </c>
-      <c r="J16" s="119"/>
+        <v>714</v>
+      </c>
+      <c r="I16" s="119" t="s">
+        <v>718</v>
+      </c>
+      <c r="J16" s="120"/>
     </row>
     <row r="17" spans="3:10" ht="15" customHeight="1">
-      <c r="I17" s="120"/>
-      <c r="J17" s="121"/>
+      <c r="I17" s="121"/>
+      <c r="J17" s="122"/>
     </row>
     <row r="18" spans="3:10">
       <c r="D18" t="s">
-        <v>716</v>
-      </c>
-      <c r="I18" s="122"/>
-      <c r="J18" s="123"/>
+        <v>715</v>
+      </c>
+      <c r="I18" s="123"/>
+      <c r="J18" s="124"/>
     </row>
     <row r="19" spans="3:10">
       <c r="C19" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="20" spans="3:10">
       <c r="D20" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
   </sheetData>
@@ -23868,24 +24186,24 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:K18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:11">
       <c r="B2" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="3" spans="2:11">
       <c r="B3" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="4" spans="2:11">
       <c r="B4" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="6" spans="2:11">
@@ -23895,38 +24213,38 @@
     </row>
     <row r="7" spans="2:11">
       <c r="B7" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="F7" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="10" spans="2:11">
       <c r="B10" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="11" spans="2:11">
       <c r="B11" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="12" spans="2:11">
       <c r="B12" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="K12" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="13" spans="2:11">
       <c r="B13" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="14" spans="2:11">
       <c r="B14" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="16" spans="2:11">
@@ -23936,18 +24254,18 @@
     </row>
     <row r="17" spans="2:6">
       <c r="B17" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="F17" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="F18" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
   </sheetData>
@@ -23957,10 +24275,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:G104"/>
+  <dimension ref="B1:G108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="60.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="62.85546875" customWidth="1"/>
     <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="68.5703125" customWidth="1"/>
     <col min="6" max="6" width="9.7109375" customWidth="1"/>
@@ -24379,11 +24697,13 @@
       <c r="C28" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="D28" s="51">
-        <v>0</v>
+      <c r="D28" s="42">
+        <v>1</v>
       </c>
       <c r="E28" s="6"/>
-      <c r="F28" s="16"/>
+      <c r="F28" s="49" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="29" spans="2:7">
       <c r="B29" s="5">
@@ -24392,11 +24712,13 @@
       <c r="C29" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="D29" s="51">
-        <v>0</v>
+      <c r="D29" s="42">
+        <v>1</v>
       </c>
       <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
+      <c r="F29" s="49" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="30" spans="2:7">
       <c r="B30" s="5" t="s">
@@ -24692,7 +25014,7 @@
         <v>287</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D49" s="51">
         <v>0.9</v>
@@ -24707,7 +25029,7 @@
         <v>319</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D50" s="42">
         <v>1</v>
@@ -24722,7 +25044,7 @@
         <v>320</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D51" s="51">
         <v>0.2</v>
@@ -24739,7 +25061,7 @@
         <v>11.1</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="D52" s="42">
         <v>1</v>
@@ -24754,7 +25076,7 @@
         <v>11.2</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="D53" s="42">
         <v>1</v>
@@ -24769,7 +25091,7 @@
         <v>11.3</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D54" s="51">
         <v>0</v>
@@ -24819,7 +25141,7 @@
         <v>321</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D60" s="42">
         <v>1</v>
@@ -24834,7 +25156,7 @@
         <v>322</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D61" s="42">
         <v>1</v>
@@ -24849,7 +25171,7 @@
         <v>435</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D62" s="42">
         <v>1</v>
@@ -24861,10 +25183,10 @@
     </row>
     <row r="63" spans="2:6" ht="45">
       <c r="B63" s="5" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D63" s="42">
         <v>1</v>
@@ -24876,16 +25198,16 @@
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="C64" s="6" t="s">
         <v>448</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>449</v>
       </c>
       <c r="D64" s="42">
         <v>1</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F64" s="6"/>
     </row>
@@ -24894,7 +25216,7 @@
         <v>16.100000000000001</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D65" s="42">
         <v>1</v>
@@ -24909,7 +25231,7 @@
         <v>16.2</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D66" s="42">
         <v>1</v>
@@ -24924,7 +25246,7 @@
         <v>16.3</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D67" s="42">
         <v>1</v>
@@ -24939,7 +25261,7 @@
         <v>16.399999999999999</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D68" s="42">
         <v>1</v>
@@ -24954,7 +25276,7 @@
         <v>16.5</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D69" s="42">
         <v>1</v>
@@ -24969,7 +25291,7 @@
         <v>16.600000000000001</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D70" s="42">
         <v>1</v>
@@ -24984,92 +25306,100 @@
         <v>16.7</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D71" s="42">
         <v>1</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F71" s="16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="72" spans="2:6">
-      <c r="B72" s="5" t="s">
+    <row r="72" spans="2:6" ht="43.5" customHeight="1">
+      <c r="B72" s="5">
+        <v>16.8</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>902</v>
+      </c>
+      <c r="D72" s="42">
+        <v>1</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>910</v>
+      </c>
+      <c r="F72" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="73" spans="2:6" ht="43.5" customHeight="1">
+      <c r="B73" s="5">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>901</v>
+      </c>
+      <c r="D73" s="51">
+        <v>0</v>
+      </c>
+      <c r="E73" s="7"/>
+      <c r="F73" s="16"/>
+    </row>
+    <row r="74" spans="2:6">
+      <c r="B74" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="C74" s="6" t="s">
         <v>451</v>
-      </c>
-      <c r="C72" s="6" t="s">
-        <v>452</v>
-      </c>
-      <c r="D72" s="6"/>
-      <c r="E72" s="6"/>
-      <c r="F72" s="6"/>
-    </row>
-    <row r="73" spans="2:6" ht="30">
-      <c r="B73" s="5">
-        <v>17.100000000000001</v>
-      </c>
-      <c r="C73" s="78" t="s">
-        <v>481</v>
-      </c>
-      <c r="D73" s="6"/>
-      <c r="E73" s="6"/>
-      <c r="F73" s="6"/>
-    </row>
-    <row r="74" spans="2:6" ht="30">
-      <c r="B74" s="5">
-        <v>17.2</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>453</v>
       </c>
       <c r="D74" s="6"/>
       <c r="E74" s="6"/>
       <c r="F74" s="6"/>
     </row>
-    <row r="75" spans="2:6" ht="50.25" customHeight="1">
+    <row r="75" spans="2:6" ht="30">
       <c r="B75" s="5">
-        <v>17.3</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>469</v>
+        <v>17.100000000000001</v>
+      </c>
+      <c r="C75" s="78" t="s">
+        <v>480</v>
       </c>
       <c r="D75" s="6"/>
-      <c r="E75" s="16" t="s">
-        <v>463</v>
-      </c>
+      <c r="E75" s="6"/>
       <c r="F75" s="6"/>
     </row>
     <row r="76" spans="2:6" ht="30">
       <c r="B76" s="5">
-        <v>17.399999999999999</v>
+        <v>17.2</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D76" s="6"/>
       <c r="E76" s="6"/>
       <c r="F76" s="6"/>
     </row>
-    <row r="77" spans="2:6">
+    <row r="77" spans="2:6" ht="50.25" customHeight="1">
       <c r="B77" s="5">
-        <v>17.5</v>
-      </c>
-      <c r="C77" s="6" t="s">
-        <v>455</v>
+        <v>17.3</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>468</v>
       </c>
       <c r="D77" s="6"/>
-      <c r="E77" s="6"/>
+      <c r="E77" s="16" t="s">
+        <v>462</v>
+      </c>
       <c r="F77" s="6"/>
     </row>
     <row r="78" spans="2:6">
-      <c r="B78" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>459</v>
+      <c r="B78" s="5">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>453</v>
       </c>
       <c r="D78" s="6"/>
       <c r="E78" s="6"/>
@@ -25077,18 +25407,18 @@
     </row>
     <row r="79" spans="2:6">
       <c r="B79" s="5">
-        <v>18.100000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D79" s="6"/>
       <c r="E79" s="6"/>
       <c r="F79" s="6"/>
     </row>
     <row r="80" spans="2:6">
-      <c r="B80" s="5">
-        <v>18.2</v>
+      <c r="B80" s="5" t="s">
+        <v>455</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>458</v>
@@ -25099,10 +25429,10 @@
     </row>
     <row r="81" spans="2:7">
       <c r="B81" s="5">
-        <v>18.3</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>484</v>
+        <v>456</v>
       </c>
       <c r="D81" s="6"/>
       <c r="E81" s="6"/>
@@ -25110,204 +25440,194 @@
     </row>
     <row r="82" spans="2:7">
       <c r="B82" s="5">
-        <v>18.399999999999999</v>
+        <v>18.2</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>485</v>
+        <v>457</v>
       </c>
       <c r="D82" s="6"/>
       <c r="E82" s="6"/>
       <c r="F82" s="6"/>
     </row>
     <row r="83" spans="2:7">
-      <c r="B83" s="5" t="s">
-        <v>462</v>
+      <c r="B83" s="5">
+        <v>18.3</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>876</v>
-      </c>
-      <c r="D83" s="112">
-        <v>0.9</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="D83" s="6"/>
       <c r="E83" s="6"/>
-      <c r="F83" s="43" t="s">
-        <v>121</v>
-      </c>
+      <c r="F83" s="6"/>
     </row>
     <row r="84" spans="2:7">
       <c r="B84" s="5">
-        <v>19.100000000000001</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>480</v>
-      </c>
-      <c r="D84" s="51">
-        <v>0.9</v>
-      </c>
+        <v>484</v>
+      </c>
+      <c r="D84" s="6"/>
       <c r="E84" s="6"/>
-      <c r="F84" s="16" t="s">
-        <v>14</v>
-      </c>
+      <c r="F84" s="6"/>
     </row>
     <row r="85" spans="2:7">
       <c r="B85" s="5" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>437</v>
-      </c>
-      <c r="D85" s="6"/>
+        <v>875</v>
+      </c>
+      <c r="D85" s="112">
+        <v>0.9</v>
+      </c>
       <c r="E85" s="6"/>
-      <c r="F85" s="6"/>
+      <c r="F85" s="43" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="86" spans="2:7">
-      <c r="B86" s="5" t="s">
-        <v>465</v>
+      <c r="B86" s="5">
+        <v>19.100000000000001</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="D86" s="6"/>
+        <v>479</v>
+      </c>
+      <c r="D86" s="42">
+        <v>1</v>
+      </c>
       <c r="E86" s="6"/>
-      <c r="F86" s="6"/>
+      <c r="F86" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="87" spans="2:7">
-      <c r="B87" s="5">
-        <v>21.1</v>
+      <c r="B87" s="5" t="s">
+        <v>463</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>432</v>
-      </c>
-      <c r="D87" s="6"/>
+        <v>918</v>
+      </c>
+      <c r="D87" s="51">
+        <v>0.05</v>
+      </c>
       <c r="E87" s="6"/>
-      <c r="F87" s="6"/>
-    </row>
-    <row r="88" spans="2:7" ht="30">
-      <c r="B88" s="5">
-        <v>21.2</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>470</v>
-      </c>
-      <c r="D88" s="6"/>
+      <c r="F87" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7">
+      <c r="B88" s="5"/>
+      <c r="C88" s="6"/>
+      <c r="D88" s="51"/>
       <c r="E88" s="6"/>
       <c r="F88" s="6"/>
     </row>
     <row r="89" spans="2:7">
-      <c r="B89" s="5" t="s">
-        <v>466</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="D89" s="6"/>
-      <c r="E89" s="16" t="s">
-        <v>467</v>
-      </c>
+      <c r="B89" s="5"/>
+      <c r="C89" s="6"/>
+      <c r="D89" s="51"/>
+      <c r="E89" s="6"/>
       <c r="F89" s="6"/>
     </row>
-    <row r="90" spans="2:7" ht="30">
+    <row r="90" spans="2:7">
       <c r="B90" s="5" t="s">
-        <v>468</v>
-      </c>
-      <c r="C90" s="7" t="s">
-        <v>730</v>
-      </c>
-      <c r="D90" s="42">
-        <v>1</v>
-      </c>
-      <c r="E90" s="16" t="s">
-        <v>467</v>
-      </c>
-      <c r="F90" s="16"/>
+        <v>464</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="D90" s="6"/>
+      <c r="E90" s="6"/>
+      <c r="F90" s="6"/>
     </row>
     <row r="91" spans="2:7">
       <c r="B91" s="5">
-        <v>24.1</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>731</v>
-      </c>
-      <c r="D91" s="42">
-        <v>1</v>
-      </c>
-      <c r="E91" s="16"/>
-      <c r="F91" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="92" spans="2:7">
+        <v>21.1</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="D91" s="6"/>
+      <c r="E91" s="6"/>
+      <c r="F91" s="6"/>
+    </row>
+    <row r="92" spans="2:7" ht="30">
       <c r="B92" s="5">
-        <v>24.2</v>
+        <v>21.2</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>775</v>
-      </c>
-      <c r="D92" s="42">
-        <v>1</v>
-      </c>
-      <c r="E92" s="16"/>
-      <c r="F92" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G92" s="48"/>
+        <v>469</v>
+      </c>
+      <c r="D92" s="6"/>
+      <c r="E92" s="6"/>
+      <c r="F92" s="6"/>
     </row>
     <row r="93" spans="2:7">
       <c r="B93" s="5" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>478</v>
-      </c>
-      <c r="D93" s="42">
+        <v>323</v>
+      </c>
+      <c r="D93" s="6"/>
+      <c r="E93" s="16" t="s">
+        <v>466</v>
+      </c>
+      <c r="F93" s="6"/>
+    </row>
+    <row r="94" spans="2:7" ht="30">
+      <c r="B94" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>729</v>
+      </c>
+      <c r="D94" s="42">
         <v>1</v>
       </c>
-      <c r="E93" s="16"/>
-      <c r="F93" s="16" t="s">
+      <c r="E94" s="16" t="s">
+        <v>466</v>
+      </c>
+      <c r="F94" s="16"/>
+    </row>
+    <row r="95" spans="2:7">
+      <c r="B95" s="5">
+        <v>24.1</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>730</v>
+      </c>
+      <c r="D95" s="42">
+        <v>1</v>
+      </c>
+      <c r="E95" s="16"/>
+      <c r="F95" s="16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="94" spans="2:7">
-      <c r="B94" s="5" t="s">
-        <v>477</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D94" s="6"/>
-      <c r="E94" s="16"/>
-      <c r="F94" s="6"/>
-    </row>
-    <row r="95" spans="2:7" ht="60">
-      <c r="B95" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="C95" s="79" t="s">
-        <v>482</v>
-      </c>
-      <c r="D95" s="6"/>
-      <c r="E95" s="16" t="s">
-        <v>483</v>
-      </c>
-      <c r="F95" s="6"/>
-    </row>
-    <row r="96" spans="2:7" ht="45">
-      <c r="B96" s="5" t="s">
-        <v>487</v>
+    <row r="96" spans="2:7">
+      <c r="B96" s="5">
+        <v>24.2</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>778</v>
-      </c>
-      <c r="D96" s="6"/>
+        <v>774</v>
+      </c>
+      <c r="D96" s="42">
+        <v>1</v>
+      </c>
       <c r="E96" s="16"/>
-      <c r="F96" s="6"/>
+      <c r="F96" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G96" s="48"/>
     </row>
     <row r="97" spans="2:7">
       <c r="B97" s="5" t="s">
-        <v>488</v>
+        <v>474</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>814</v>
+        <v>477</v>
       </c>
       <c r="D97" s="42">
         <v>1</v>
@@ -25319,56 +25639,45 @@
     </row>
     <row r="98" spans="2:7">
       <c r="B98" s="5" t="s">
-        <v>489</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>811</v>
-      </c>
-      <c r="D98" s="42">
-        <v>1</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="D98" s="6"/>
       <c r="E98" s="16"/>
-      <c r="F98" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="99" spans="2:7">
-      <c r="B99" s="5">
-        <v>30.1</v>
-      </c>
-      <c r="C99" s="7" t="s">
-        <v>808</v>
-      </c>
-      <c r="D99" s="42">
-        <v>1</v>
-      </c>
-      <c r="E99" s="16"/>
-      <c r="F99" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="100" spans="2:7">
-      <c r="B100" s="5">
-        <v>30.2</v>
+      <c r="F98" s="6"/>
+    </row>
+    <row r="99" spans="2:7" ht="60">
+      <c r="B99" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="C99" s="79" t="s">
+        <v>481</v>
+      </c>
+      <c r="D99" s="6"/>
+      <c r="E99" s="16" t="s">
+        <v>482</v>
+      </c>
+      <c r="F99" s="6"/>
+    </row>
+    <row r="100" spans="2:7" ht="45">
+      <c r="B100" s="5" t="s">
+        <v>486</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>809</v>
-      </c>
-      <c r="D100" s="42">
-        <v>1</v>
-      </c>
+        <v>777</v>
+      </c>
+      <c r="D100" s="6"/>
       <c r="E100" s="16"/>
-      <c r="F100" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G100" s="48"/>
+      <c r="F100" s="6"/>
     </row>
     <row r="101" spans="2:7">
-      <c r="B101" s="5">
-        <v>30.3</v>
-      </c>
-      <c r="C101" s="7" t="s">
-        <v>810</v>
+      <c r="B101" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>813</v>
       </c>
       <c r="D101" s="42">
         <v>1</v>
@@ -25378,15 +25687,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="102" spans="2:7" ht="30">
+    <row r="102" spans="2:7">
       <c r="B102" s="5" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>476</v>
-      </c>
-      <c r="D102" s="51">
-        <v>0.05</v>
+        <v>810</v>
+      </c>
+      <c r="D102" s="42">
+        <v>1</v>
       </c>
       <c r="E102" s="16"/>
       <c r="F102" s="16" t="s">
@@ -25394,11 +25703,11 @@
       </c>
     </row>
     <row r="103" spans="2:7">
-      <c r="B103" s="5" t="s">
-        <v>776</v>
+      <c r="B103" s="5">
+        <v>30.1</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>777</v>
+        <v>807</v>
       </c>
       <c r="D103" s="42">
         <v>1</v>
@@ -25409,17 +25718,78 @@
       </c>
     </row>
     <row r="104" spans="2:7">
-      <c r="B104" s="77" t="s">
-        <v>473</v>
-      </c>
-      <c r="C104" s="57" t="s">
+      <c r="B104" s="5">
+        <v>30.2</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>808</v>
+      </c>
+      <c r="D104" s="42">
+        <v>1</v>
+      </c>
+      <c r="E104" s="16"/>
+      <c r="F104" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G104" s="48"/>
+    </row>
+    <row r="105" spans="2:7">
+      <c r="B105" s="5">
+        <v>30.3</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>809</v>
+      </c>
+      <c r="D105" s="42">
+        <v>1</v>
+      </c>
+      <c r="E105" s="16"/>
+      <c r="F105" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="106" spans="2:7" ht="30">
+      <c r="B106" s="5" t="s">
+        <v>489</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="D106" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="E106" s="16"/>
+      <c r="F106" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="107" spans="2:7">
+      <c r="B107" s="5" t="s">
+        <v>775</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>776</v>
+      </c>
+      <c r="D107" s="42">
+        <v>1</v>
+      </c>
+      <c r="E107" s="16"/>
+      <c r="F107" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="108" spans="2:7">
+      <c r="B108" s="77" t="s">
         <v>472</v>
       </c>
-      <c r="D104" s="1"/>
-      <c r="E104" s="49" t="s">
+      <c r="C108" s="57" t="s">
         <v>471</v>
       </c>
-      <c r="F104" s="1"/>
+      <c r="D108" s="1"/>
+      <c r="E108" s="49" t="s">
+        <v>470</v>
+      </c>
+      <c r="F108" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -25470,10 +25840,10 @@
     <hyperlink ref="E51" r:id="rId6"/>
     <hyperlink ref="F62" location="'#14'!B2" display="Link"/>
     <hyperlink ref="E64" r:id="rId7"/>
-    <hyperlink ref="E75" r:id="rId8"/>
-    <hyperlink ref="E89" r:id="rId9"/>
-    <hyperlink ref="E90" r:id="rId10"/>
-    <hyperlink ref="E104" r:id="rId11"/>
+    <hyperlink ref="E77" r:id="rId8"/>
+    <hyperlink ref="E93" r:id="rId9"/>
+    <hyperlink ref="E94" r:id="rId10"/>
+    <hyperlink ref="E108" r:id="rId11"/>
     <hyperlink ref="F49" location="'#9'!B2" display="Link"/>
     <hyperlink ref="F60" location="'#12'!B2" display="Link"/>
     <hyperlink ref="F65" location="'#16'!B2" display="Link"/>
@@ -25486,23 +25856,27 @@
     <hyperlink ref="F63" location="'#15'!B2" display="Link"/>
     <hyperlink ref="F70" location="'#16'!B89" display="Link"/>
     <hyperlink ref="F71" location="'#16'!B10" display="Link"/>
-    <hyperlink ref="F102" location="'#31'!B2" display="Link"/>
-    <hyperlink ref="F91" location="'#24'!B2" display="Link"/>
-    <hyperlink ref="F92" location="'#24'!B2" display="Link"/>
-    <hyperlink ref="F92:G92" location="'#24'!B26" display="Link"/>
-    <hyperlink ref="F93" location="'#25'!B2" display="Link"/>
-    <hyperlink ref="F84" location="'#19'!B2" display="Link"/>
-    <hyperlink ref="F99" location="'#30'!B8" display="Link"/>
-    <hyperlink ref="F97" location="'#29'!B2" display="Link"/>
-    <hyperlink ref="F103" location="'#32'!B2" display="Link"/>
-    <hyperlink ref="F98" location="'#30'!B2" display="Link"/>
-    <hyperlink ref="F100" location="'#30'!B8" display="Link"/>
-    <hyperlink ref="F100:G100" location="'#30'!B24" display="Link"/>
-    <hyperlink ref="F101" location="'#30'!B35" display="Link"/>
+    <hyperlink ref="F106" location="'#31'!B2" display="Link"/>
+    <hyperlink ref="F95" location="'#24'!B2" display="Link"/>
+    <hyperlink ref="F96" location="'#24'!B2" display="Link"/>
+    <hyperlink ref="F96:G96" location="'#24'!B26" display="Link"/>
+    <hyperlink ref="F97" location="'#25'!B2" display="Link"/>
+    <hyperlink ref="F86" location="'#19'!B2" display="Link"/>
+    <hyperlink ref="F103" location="'#30'!B8" display="Link"/>
+    <hyperlink ref="F101" location="'#29'!B2" display="Link"/>
+    <hyperlink ref="F107" location="'#32'!B2" display="Link"/>
+    <hyperlink ref="F102" location="'#30'!B2" display="Link"/>
+    <hyperlink ref="F104" location="'#30'!B8" display="Link"/>
+    <hyperlink ref="F104:G104" location="'#30'!B24" display="Link"/>
+    <hyperlink ref="F105" location="'#30'!B35" display="Link"/>
     <hyperlink ref="F51" location="'#11'!B2" display="Link"/>
     <hyperlink ref="F52" location="'#11'!B4" display="Link"/>
     <hyperlink ref="F53" location="'#11'!B21" display="Link"/>
     <hyperlink ref="F54" location="'#11'!B44" display="Link"/>
+    <hyperlink ref="F72" location="'#16'!B103" display="Link"/>
+    <hyperlink ref="F28" location="'#4'!B35" display="Link"/>
+    <hyperlink ref="F29" location="'#4'!B43" display="Link"/>
+    <hyperlink ref="F87" location="'#20'!B2" display="Link"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId12"/>
@@ -25820,7 +26194,7 @@
       <c r="D12" s="11"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" thickBot="1">
-      <c r="C13" s="113" t="s">
+      <c r="C13" s="114" t="s">
         <v>78</v>
       </c>
       <c r="D13" s="26" t="s">
@@ -25837,7 +26211,7 @@
       <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:10" ht="15.75" thickBot="1">
-      <c r="C14" s="114"/>
+      <c r="C14" s="115"/>
       <c r="D14" s="23" t="s">
         <v>65</v>
       </c>
@@ -25853,7 +26227,7 @@
       <c r="J14" s="25"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="C15" s="114"/>
+      <c r="C15" s="115"/>
       <c r="D15" s="26" t="s">
         <v>66</v>
       </c>
@@ -25868,7 +26242,7 @@
       <c r="I15" s="28"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="C16" s="114"/>
+      <c r="C16" s="115"/>
       <c r="D16" s="29"/>
       <c r="E16" s="30" t="s">
         <v>74</v>
@@ -25879,7 +26253,7 @@
       <c r="I16" s="31"/>
     </row>
     <row r="17" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C17" s="115"/>
+      <c r="C17" s="116"/>
       <c r="D17" s="32"/>
       <c r="E17" s="33" t="s">
         <v>75</v>
@@ -25910,7 +26284,7 @@
       <c r="L18" s="25"/>
     </row>
     <row r="19" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C19" s="113" t="s">
+      <c r="C19" s="114" t="s">
         <v>78</v>
       </c>
       <c r="D19" s="23" t="s">
@@ -25921,7 +26295,7 @@
       </c>
     </row>
     <row r="20" spans="3:12">
-      <c r="C20" s="114"/>
+      <c r="C20" s="115"/>
       <c r="D20" s="26" t="s">
         <v>82</v>
       </c>
@@ -25930,7 +26304,7 @@
       </c>
     </row>
     <row r="21" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C21" s="115"/>
+      <c r="C21" s="116"/>
       <c r="D21" s="32"/>
       <c r="E21" s="40" t="s">
         <v>84</v>
@@ -26560,7 +26934,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:D32"/>
+  <dimension ref="B2:D48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:3">
@@ -26673,6 +27047,61 @@
     <row r="32" spans="2:4">
       <c r="C32" t="s">
         <v>184</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3">
+      <c r="B35" s="6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3">
+      <c r="C36" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3">
+      <c r="C37" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3">
+      <c r="B39" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3">
+      <c r="B40" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3">
+      <c r="B41" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3">
+      <c r="B43" s="6" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3">
+      <c r="C44" s="50" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3">
+      <c r="C45" s="50" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3">
+      <c r="B47" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3">
+      <c r="B48" t="s">
+        <v>917</v>
       </c>
     </row>
   </sheetData>

--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="6" activeTab="20"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Knowhow" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="919">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="932">
   <si>
     <t>No.</t>
   </si>
@@ -12495,6 +12495,45 @@
   </si>
   <si>
     <t>Memory Layout - Các Segment trong C++</t>
+  </si>
+  <si>
+    <t>Code/Text Segment</t>
+  </si>
+  <si>
+    <t>Data Segment</t>
+  </si>
+  <si>
+    <t>Heap</t>
+  </si>
+  <si>
+    <t>Stack</t>
+  </si>
+  <si>
+    <t>Chức năng :</t>
+  </si>
+  <si>
+    <t>Lưu trữ mã máy của chương trình</t>
+  </si>
+  <si>
+    <t>Thời gian tồn tại :</t>
+  </si>
+  <si>
+    <t>Suốt vòng đời chương trình</t>
+  </si>
+  <si>
+    <t>Lưu trữ các biến global và static của chương trình</t>
+  </si>
+  <si>
+    <t>Vùng nhớ động, lưu trữ các biến được cấp phát động tại runtime</t>
+  </si>
+  <si>
+    <t>Vùng nhớ tĩnh, lưu trữ các biến local được khai báo bên trong 1 hàm</t>
+  </si>
+  <si>
+    <t>Cấp phát tài nguyên và giải phóng phụ thuộc vào quyết định của lập trình viên</t>
+  </si>
+  <si>
+    <t>Tồn tại trong phạm vi của nó và tự động thoát khi ra khỏi phạm vi</t>
   </si>
 </sst>
 </file>
@@ -13094,7 +13133,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -13349,6 +13388,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -17535,19 +17592,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:K22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="5.7109375" customWidth="1"/>
-    <col min="3" max="3" width="37.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.42578125" customWidth="1"/>
+    <col min="2" max="2" width="5.7265625" customWidth="1"/>
+    <col min="3" max="3" width="37.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.453125" customWidth="1"/>
     <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7265625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="18.75">
+    <row r="2" spans="2:11" ht="18.5">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -17573,7 +17630,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:11" ht="45">
+    <row r="3" spans="2:11" ht="43.5">
       <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
@@ -17927,9 +17984,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Q30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="11" max="11" width="3.7109375" customWidth="1"/>
+    <col min="11" max="11" width="3.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:17">
@@ -18259,12 +18316,12 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E76"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="4.42578125" customWidth="1"/>
-    <col min="3" max="3" width="39.7109375" customWidth="1"/>
-    <col min="4" max="4" width="50.85546875" customWidth="1"/>
-    <col min="5" max="5" width="75.42578125" customWidth="1"/>
+    <col min="2" max="2" width="4.453125" customWidth="1"/>
+    <col min="3" max="3" width="39.7265625" customWidth="1"/>
+    <col min="4" max="4" width="50.81640625" customWidth="1"/>
+    <col min="5" max="5" width="75.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.5">
@@ -18272,7 +18329,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="23.25">
+    <row r="2" spans="1:5" ht="23.5">
       <c r="B2" s="63" t="s">
         <v>420</v>
       </c>
@@ -18291,7 +18348,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="45">
+    <row r="5" spans="1:5" ht="43.5">
       <c r="B5" s="69">
         <v>1</v>
       </c>
@@ -18319,7 +18376,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5" ht="29">
       <c r="B7" s="69">
         <v>3</v>
       </c>
@@ -18333,7 +18390,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="23.25">
+    <row r="10" spans="1:5" ht="23.5">
       <c r="B10" s="63" t="s">
         <v>344</v>
       </c>
@@ -18352,7 +18409,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="30">
+    <row r="13" spans="1:5">
       <c r="B13" s="69">
         <v>1</v>
       </c>
@@ -18366,7 +18423,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="30">
+    <row r="14" spans="1:5" ht="29">
       <c r="B14" s="69">
         <v>2</v>
       </c>
@@ -18380,7 +18437,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="30">
+    <row r="15" spans="1:5" ht="29">
       <c r="B15" s="69">
         <v>3</v>
       </c>
@@ -18394,7 +18451,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30">
+    <row r="16" spans="1:5" ht="29">
       <c r="B16" s="69">
         <v>4</v>
       </c>
@@ -18408,7 +18465,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="165">
+    <row r="17" spans="2:5" ht="145">
       <c r="B17" s="69">
         <v>5</v>
       </c>
@@ -18422,7 +18479,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="180">
+    <row r="18" spans="2:5" ht="159.5">
       <c r="B18" s="69">
         <v>6</v>
       </c>
@@ -18436,7 +18493,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="135">
+    <row r="19" spans="2:5" ht="130.5">
       <c r="B19" s="69">
         <v>7</v>
       </c>
@@ -18450,7 +18507,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="135">
+    <row r="20" spans="2:5" ht="130.5">
       <c r="B20" s="69">
         <v>8</v>
       </c>
@@ -18464,7 +18521,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="23" spans="2:5" ht="23.25">
+    <row r="23" spans="2:5" ht="23.5">
       <c r="B23" s="63" t="s">
         <v>419</v>
       </c>
@@ -18531,7 +18588,7 @@
       </c>
       <c r="E29" s="1"/>
     </row>
-    <row r="32" spans="2:5" ht="23.25">
+    <row r="32" spans="2:5" ht="23.5">
       <c r="B32" s="63" t="s">
         <v>418</v>
       </c>
@@ -18547,7 +18604,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="35" spans="2:4" ht="30">
+    <row r="35" spans="2:4" ht="29">
       <c r="B35" s="65">
         <v>1</v>
       </c>
@@ -18569,7 +18626,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="37" spans="2:4" ht="30">
+    <row r="37" spans="2:4">
       <c r="B37" s="65">
         <v>3</v>
       </c>
@@ -18591,7 +18648,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="41" spans="2:4" ht="23.25">
+    <row r="41" spans="2:4" ht="23.5">
       <c r="B41" s="63" t="s">
         <v>417</v>
       </c>
@@ -18607,7 +18664,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="44" spans="2:4" ht="30">
+    <row r="44" spans="2:4">
       <c r="B44" s="65">
         <v>1</v>
       </c>
@@ -18651,7 +18708,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="50" spans="2:4" ht="23.25">
+    <row r="50" spans="2:4" ht="23.5">
       <c r="B50" s="63" t="s">
         <v>416</v>
       </c>
@@ -18703,7 +18760,7 @@
     <row r="56" spans="2:4">
       <c r="B56" s="65"/>
     </row>
-    <row r="58" spans="2:4" ht="23.25">
+    <row r="58" spans="2:4" ht="23.5">
       <c r="B58" s="63" t="s">
         <v>415</v>
       </c>
@@ -18730,7 +18787,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="62" spans="2:4" ht="45">
+    <row r="62" spans="2:4" ht="29">
       <c r="B62" s="65">
         <v>2</v>
       </c>
@@ -18741,7 +18798,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="63" spans="2:4" ht="30">
+    <row r="63" spans="2:4" ht="29">
       <c r="B63" s="65">
         <v>3</v>
       </c>
@@ -18774,7 +18831,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="68" spans="2:4" ht="23.25">
+    <row r="68" spans="2:4" ht="23.5">
       <c r="B68" s="63" t="s">
         <v>400</v>
       </c>
@@ -18865,7 +18922,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:S38"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -19192,7 +19249,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:M57"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -19506,7 +19563,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:G44"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" t="s">
@@ -19743,7 +19800,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -19860,7 +19917,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -19938,7 +19995,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
@@ -19985,14 +20042,14 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I48"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="18.75">
+    <row r="3" spans="2:4" ht="18.5">
       <c r="C3" s="93" t="s">
         <v>649</v>
       </c>
@@ -20125,7 +20182,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="33" spans="3:9" ht="18.75">
+    <row r="33" spans="3:9" ht="18.5">
       <c r="C33" s="93" t="s">
         <v>675</v>
       </c>
@@ -20224,7 +20281,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I113"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
@@ -20659,15 +20716,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:F103"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="3" max="3" width="12.28515625" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.26953125" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" customWidth="1"/>
+    <col min="5" max="5" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="18.75">
+    <row r="2" spans="2:6" ht="18.5">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -21810,7 +21867,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
@@ -21854,15 +21911,121 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="B2:G11"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="6" max="6" width="15.36328125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="2:2">
+    <row r="2" spans="2:7">
       <c r="B2" s="6" t="s">
         <v>918</v>
       </c>
     </row>
+    <row r="3" spans="2:7" ht="15" thickBot="1"/>
+    <row r="4" spans="2:7">
+      <c r="C4" s="125" t="s">
+        <v>919</v>
+      </c>
+      <c r="D4" s="126"/>
+      <c r="E4" s="127"/>
+      <c r="F4" t="s">
+        <v>923</v>
+      </c>
+      <c r="G4" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="15" thickBot="1">
+      <c r="C5" s="128"/>
+      <c r="D5" s="129"/>
+      <c r="E5" s="130"/>
+      <c r="F5" t="s">
+        <v>925</v>
+      </c>
+      <c r="G5" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7">
+      <c r="C6" s="125" t="s">
+        <v>920</v>
+      </c>
+      <c r="D6" s="126"/>
+      <c r="E6" s="127"/>
+      <c r="F6" t="s">
+        <v>923</v>
+      </c>
+      <c r="G6" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" ht="15" thickBot="1">
+      <c r="C7" s="128"/>
+      <c r="D7" s="129"/>
+      <c r="E7" s="130"/>
+      <c r="F7" t="s">
+        <v>925</v>
+      </c>
+      <c r="G7" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7">
+      <c r="C8" s="125" t="s">
+        <v>921</v>
+      </c>
+      <c r="D8" s="126"/>
+      <c r="E8" s="127"/>
+      <c r="F8" t="s">
+        <v>923</v>
+      </c>
+      <c r="G8" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="15" thickBot="1">
+      <c r="C9" s="128"/>
+      <c r="D9" s="129"/>
+      <c r="E9" s="130"/>
+      <c r="F9" t="s">
+        <v>925</v>
+      </c>
+      <c r="G9" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7">
+      <c r="C10" s="125" t="s">
+        <v>922</v>
+      </c>
+      <c r="D10" s="126"/>
+      <c r="E10" s="127"/>
+      <c r="F10" t="s">
+        <v>923</v>
+      </c>
+      <c r="G10" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="15" thickBot="1">
+      <c r="C11" s="128"/>
+      <c r="D11" s="129"/>
+      <c r="E11" s="130"/>
+      <c r="F11" t="s">
+        <v>925</v>
+      </c>
+      <c r="G11" t="s">
+        <v>931</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C4:E5"/>
+    <mergeCell ref="C6:E7"/>
+    <mergeCell ref="C8:E9"/>
+    <mergeCell ref="C10:E11"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -21870,7 +22033,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Q108"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:10">
       <c r="B2" t="s">
@@ -23675,7 +23838,7 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -23807,7 +23970,7 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:F27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
@@ -23935,9 +24098,9 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:B39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="22.140625" customWidth="1"/>
+    <col min="2" max="2" width="22.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:2">
@@ -24092,7 +24255,7 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:O20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:15">
       <c r="B2" s="6" t="s">
@@ -24189,7 +24352,7 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:K18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:11">
       <c r="B2" t="s">
@@ -24275,13 +24438,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:G108"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="B1:G106"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="3" max="3" width="62.85546875" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="68.5703125" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" customWidth="1"/>
+    <col min="3" max="3" width="62.81640625" customWidth="1"/>
+    <col min="4" max="4" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.54296875" customWidth="1"/>
+    <col min="6" max="6" width="9.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6">
@@ -24289,7 +24452,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="2:6" ht="18.75">
+    <row r="2" spans="2:6" ht="18.5">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -25181,7 +25344,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="2:6" ht="45">
+    <row r="63" spans="2:6" ht="43.5">
       <c r="B63" s="5" t="s">
         <v>446</v>
       </c>
@@ -25256,7 +25419,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="68" spans="2:6" ht="30">
+    <row r="68" spans="2:6" ht="29">
       <c r="B68" s="5">
         <v>16.399999999999999</v>
       </c>
@@ -25286,7 +25449,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="70" spans="2:6" ht="60">
+    <row r="70" spans="2:6" ht="43.5">
       <c r="B70" s="5">
         <v>16.600000000000001</v>
       </c>
@@ -25359,7 +25522,7 @@
       <c r="E74" s="6"/>
       <c r="F74" s="6"/>
     </row>
-    <row r="75" spans="2:6" ht="30">
+    <row r="75" spans="2:6" ht="29">
       <c r="B75" s="5">
         <v>17.100000000000001</v>
       </c>
@@ -25370,7 +25533,7 @@
       <c r="E75" s="6"/>
       <c r="F75" s="6"/>
     </row>
-    <row r="76" spans="2:6" ht="30">
+    <row r="76" spans="2:6">
       <c r="B76" s="5">
         <v>17.2</v>
       </c>
@@ -25508,8 +25671,8 @@
       <c r="C87" s="6" t="s">
         <v>918</v>
       </c>
-      <c r="D87" s="51">
-        <v>0.05</v>
+      <c r="D87" s="42">
+        <v>1</v>
       </c>
       <c r="E87" s="6"/>
       <c r="F87" s="16" t="s">
@@ -25517,86 +25680,103 @@
       </c>
     </row>
     <row r="88" spans="2:7">
-      <c r="B88" s="5"/>
-      <c r="C88" s="6"/>
-      <c r="D88" s="51"/>
+      <c r="B88" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="D88" s="6"/>
       <c r="E88" s="6"/>
       <c r="F88" s="6"/>
     </row>
     <row r="89" spans="2:7">
-      <c r="B89" s="5"/>
-      <c r="C89" s="6"/>
-      <c r="D89" s="51"/>
+      <c r="B89" s="5">
+        <v>21.1</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="D89" s="6"/>
       <c r="E89" s="6"/>
       <c r="F89" s="6"/>
     </row>
-    <row r="90" spans="2:7">
-      <c r="B90" s="5" t="s">
-        <v>464</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>288</v>
+    <row r="90" spans="2:7" ht="29">
+      <c r="B90" s="5">
+        <v>21.2</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>469</v>
       </c>
       <c r="D90" s="6"/>
       <c r="E90" s="6"/>
       <c r="F90" s="6"/>
     </row>
     <row r="91" spans="2:7">
-      <c r="B91" s="5">
-        <v>21.1</v>
+      <c r="B91" s="5" t="s">
+        <v>465</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>432</v>
+        <v>323</v>
       </c>
       <c r="D91" s="6"/>
-      <c r="E91" s="6"/>
+      <c r="E91" s="16" t="s">
+        <v>466</v>
+      </c>
       <c r="F91" s="6"/>
     </row>
-    <row r="92" spans="2:7" ht="30">
-      <c r="B92" s="5">
-        <v>21.2</v>
+    <row r="92" spans="2:7" ht="29">
+      <c r="B92" s="5" t="s">
+        <v>467</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>469</v>
-      </c>
-      <c r="D92" s="6"/>
-      <c r="E92" s="6"/>
-      <c r="F92" s="6"/>
+        <v>729</v>
+      </c>
+      <c r="D92" s="42">
+        <v>1</v>
+      </c>
+      <c r="E92" s="16" t="s">
+        <v>466</v>
+      </c>
+      <c r="F92" s="16"/>
     </row>
     <row r="93" spans="2:7">
-      <c r="B93" s="5" t="s">
-        <v>465</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="D93" s="6"/>
-      <c r="E93" s="16" t="s">
-        <v>466</v>
-      </c>
-      <c r="F93" s="6"/>
-    </row>
-    <row r="94" spans="2:7" ht="30">
-      <c r="B94" s="5" t="s">
-        <v>467</v>
+      <c r="B93" s="5">
+        <v>24.1</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>730</v>
+      </c>
+      <c r="D93" s="42">
+        <v>1</v>
+      </c>
+      <c r="E93" s="16"/>
+      <c r="F93" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="94" spans="2:7">
+      <c r="B94" s="5">
+        <v>24.2</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>729</v>
+        <v>774</v>
       </c>
       <c r="D94" s="42">
         <v>1</v>
       </c>
-      <c r="E94" s="16" t="s">
-        <v>466</v>
-      </c>
-      <c r="F94" s="16"/>
+      <c r="E94" s="16"/>
+      <c r="F94" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G94" s="48"/>
     </row>
     <row r="95" spans="2:7">
-      <c r="B95" s="5">
-        <v>24.1</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>730</v>
+      <c r="B95" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>477</v>
       </c>
       <c r="D95" s="42">
         <v>1</v>
@@ -25607,77 +25787,76 @@
       </c>
     </row>
     <row r="96" spans="2:7">
-      <c r="B96" s="5">
-        <v>24.2</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>774</v>
-      </c>
-      <c r="D96" s="42">
-        <v>1</v>
-      </c>
+      <c r="B96" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="D96" s="6"/>
       <c r="E96" s="16"/>
-      <c r="F96" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G96" s="48"/>
-    </row>
-    <row r="97" spans="2:7">
+      <c r="F96" s="6"/>
+    </row>
+    <row r="97" spans="2:7" ht="58">
       <c r="B97" s="5" t="s">
-        <v>474</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>477</v>
-      </c>
-      <c r="D97" s="42">
-        <v>1</v>
-      </c>
-      <c r="E97" s="16"/>
-      <c r="F97" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="98" spans="2:7">
+        <v>485</v>
+      </c>
+      <c r="C97" s="79" t="s">
+        <v>481</v>
+      </c>
+      <c r="D97" s="6"/>
+      <c r="E97" s="16" t="s">
+        <v>482</v>
+      </c>
+      <c r="F97" s="6"/>
+    </row>
+    <row r="98" spans="2:7" ht="43.5">
       <c r="B98" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>478</v>
+        <v>486</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>777</v>
       </c>
       <c r="D98" s="6"/>
       <c r="E98" s="16"/>
       <c r="F98" s="6"/>
     </row>
-    <row r="99" spans="2:7" ht="60">
+    <row r="99" spans="2:7">
       <c r="B99" s="5" t="s">
-        <v>485</v>
-      </c>
-      <c r="C99" s="79" t="s">
-        <v>481</v>
-      </c>
-      <c r="D99" s="6"/>
-      <c r="E99" s="16" t="s">
-        <v>482</v>
-      </c>
-      <c r="F99" s="6"/>
-    </row>
-    <row r="100" spans="2:7" ht="45">
+        <v>487</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>813</v>
+      </c>
+      <c r="D99" s="42">
+        <v>1</v>
+      </c>
+      <c r="E99" s="16"/>
+      <c r="F99" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="100" spans="2:7">
       <c r="B100" s="5" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>777</v>
-      </c>
-      <c r="D100" s="6"/>
+        <v>810</v>
+      </c>
+      <c r="D100" s="42">
+        <v>1</v>
+      </c>
       <c r="E100" s="16"/>
-      <c r="F100" s="6"/>
+      <c r="F100" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="101" spans="2:7">
-      <c r="B101" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>813</v>
+      <c r="B101" s="5">
+        <v>30.1</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>807</v>
       </c>
       <c r="D101" s="42">
         <v>1</v>
@@ -25688,11 +25867,11 @@
       </c>
     </row>
     <row r="102" spans="2:7">
-      <c r="B102" s="5" t="s">
-        <v>488</v>
+      <c r="B102" s="5">
+        <v>30.2</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="D102" s="42">
         <v>1</v>
@@ -25701,13 +25880,14 @@
       <c r="F102" s="16" t="s">
         <v>14</v>
       </c>
+      <c r="G102" s="48"/>
     </row>
     <row r="103" spans="2:7">
       <c r="B103" s="5">
-        <v>30.1</v>
+        <v>30.3</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="D103" s="42">
         <v>1</v>
@@ -25717,28 +25897,27 @@
         <v>14</v>
       </c>
     </row>
-    <row r="104" spans="2:7">
-      <c r="B104" s="5">
-        <v>30.2</v>
+    <row r="104" spans="2:7" ht="29">
+      <c r="B104" s="5" t="s">
+        <v>489</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>808</v>
-      </c>
-      <c r="D104" s="42">
-        <v>1</v>
+        <v>475</v>
+      </c>
+      <c r="D104" s="51">
+        <v>0.05</v>
       </c>
       <c r="E104" s="16"/>
       <c r="F104" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G104" s="48"/>
     </row>
     <row r="105" spans="2:7">
-      <c r="B105" s="5">
-        <v>30.3</v>
+      <c r="B105" s="5" t="s">
+        <v>775</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>809</v>
+        <v>776</v>
       </c>
       <c r="D105" s="42">
         <v>1</v>
@@ -25748,48 +25927,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="106" spans="2:7" ht="30">
-      <c r="B106" s="5" t="s">
-        <v>489</v>
-      </c>
-      <c r="C106" s="7" t="s">
-        <v>475</v>
-      </c>
-      <c r="D106" s="51">
-        <v>0.05</v>
-      </c>
-      <c r="E106" s="16"/>
-      <c r="F106" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="107" spans="2:7">
-      <c r="B107" s="5" t="s">
-        <v>775</v>
-      </c>
-      <c r="C107" s="7" t="s">
-        <v>776</v>
-      </c>
-      <c r="D107" s="42">
-        <v>1</v>
-      </c>
-      <c r="E107" s="16"/>
-      <c r="F107" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="108" spans="2:7">
-      <c r="B108" s="77" t="s">
+    <row r="106" spans="2:7">
+      <c r="B106" s="77" t="s">
         <v>472</v>
       </c>
-      <c r="C108" s="57" t="s">
+      <c r="C106" s="57" t="s">
         <v>471</v>
       </c>
-      <c r="D108" s="1"/>
-      <c r="E108" s="49" t="s">
+      <c r="D106" s="1"/>
+      <c r="E106" s="49" t="s">
         <v>470</v>
       </c>
-      <c r="F108" s="1"/>
+      <c r="F106" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -25841,9 +25990,9 @@
     <hyperlink ref="F62" location="'#14'!B2" display="Link"/>
     <hyperlink ref="E64" r:id="rId7"/>
     <hyperlink ref="E77" r:id="rId8"/>
-    <hyperlink ref="E93" r:id="rId9"/>
-    <hyperlink ref="E94" r:id="rId10"/>
-    <hyperlink ref="E108" r:id="rId11"/>
+    <hyperlink ref="E91" r:id="rId9"/>
+    <hyperlink ref="E92" r:id="rId10"/>
+    <hyperlink ref="E106" r:id="rId11"/>
     <hyperlink ref="F49" location="'#9'!B2" display="Link"/>
     <hyperlink ref="F60" location="'#12'!B2" display="Link"/>
     <hyperlink ref="F65" location="'#16'!B2" display="Link"/>
@@ -25856,19 +26005,19 @@
     <hyperlink ref="F63" location="'#15'!B2" display="Link"/>
     <hyperlink ref="F70" location="'#16'!B89" display="Link"/>
     <hyperlink ref="F71" location="'#16'!B10" display="Link"/>
-    <hyperlink ref="F106" location="'#31'!B2" display="Link"/>
-    <hyperlink ref="F95" location="'#24'!B2" display="Link"/>
-    <hyperlink ref="F96" location="'#24'!B2" display="Link"/>
-    <hyperlink ref="F96:G96" location="'#24'!B26" display="Link"/>
-    <hyperlink ref="F97" location="'#25'!B2" display="Link"/>
+    <hyperlink ref="F104" location="'#31'!B2" display="Link"/>
+    <hyperlink ref="F93" location="'#24'!B2" display="Link"/>
+    <hyperlink ref="F94" location="'#24'!B2" display="Link"/>
+    <hyperlink ref="F94:G94" location="'#24'!B26" display="Link"/>
+    <hyperlink ref="F95" location="'#25'!B2" display="Link"/>
     <hyperlink ref="F86" location="'#19'!B2" display="Link"/>
-    <hyperlink ref="F103" location="'#30'!B8" display="Link"/>
-    <hyperlink ref="F101" location="'#29'!B2" display="Link"/>
-    <hyperlink ref="F107" location="'#32'!B2" display="Link"/>
-    <hyperlink ref="F102" location="'#30'!B2" display="Link"/>
-    <hyperlink ref="F104" location="'#30'!B8" display="Link"/>
-    <hyperlink ref="F104:G104" location="'#30'!B24" display="Link"/>
-    <hyperlink ref="F105" location="'#30'!B35" display="Link"/>
+    <hyperlink ref="F101" location="'#30'!B8" display="Link"/>
+    <hyperlink ref="F99" location="'#29'!B2" display="Link"/>
+    <hyperlink ref="F105" location="'#32'!B2" display="Link"/>
+    <hyperlink ref="F100" location="'#30'!B2" display="Link"/>
+    <hyperlink ref="F102" location="'#30'!B8" display="Link"/>
+    <hyperlink ref="F102:G102" location="'#30'!B24" display="Link"/>
+    <hyperlink ref="F103" location="'#30'!B35" display="Link"/>
     <hyperlink ref="F51" location="'#11'!B2" display="Link"/>
     <hyperlink ref="F52" location="'#11'!B4" display="Link"/>
     <hyperlink ref="F53" location="'#11'!B21" display="Link"/>
@@ -25886,13 +26035,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J164"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" customWidth="1"/>
+    <col min="1" max="1" width="4.26953125" customWidth="1"/>
+    <col min="2" max="2" width="6.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75">
+    <row r="1" spans="1:3" ht="18.5">
       <c r="C1" s="41" t="s">
         <v>15</v>
       </c>
@@ -26149,14 +26298,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L61"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="3" max="3" width="10.42578125" customWidth="1"/>
-    <col min="4" max="4" width="5.28515625" customWidth="1"/>
-    <col min="5" max="5" width="48.85546875" customWidth="1"/>
+    <col min="3" max="3" width="10.453125" customWidth="1"/>
+    <col min="4" max="4" width="5.26953125" customWidth="1"/>
+    <col min="5" max="5" width="48.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75">
+    <row r="1" spans="1:10" ht="18.5">
       <c r="C1" s="41" t="s">
         <v>57</v>
       </c>
@@ -26187,13 +26336,13 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15.75" thickBot="1">
+    <row r="12" spans="1:10" ht="15" thickBot="1">
       <c r="C12" s="11" t="s">
         <v>63</v>
       </c>
       <c r="D12" s="11"/>
     </row>
-    <row r="13" spans="1:10" ht="15.75" thickBot="1">
+    <row r="13" spans="1:10" ht="15" thickBot="1">
       <c r="C13" s="114" t="s">
         <v>78</v>
       </c>
@@ -26210,7 +26359,7 @@
       <c r="H13" s="24"/>
       <c r="I13" s="25"/>
     </row>
-    <row r="14" spans="1:10" ht="15.75" thickBot="1">
+    <row r="14" spans="1:10" ht="15" thickBot="1">
       <c r="C14" s="115"/>
       <c r="D14" s="23" t="s">
         <v>65</v>
@@ -26252,7 +26401,7 @@
       <c r="H16" s="30"/>
       <c r="I16" s="31"/>
     </row>
-    <row r="17" spans="3:12" ht="15.75" thickBot="1">
+    <row r="17" spans="3:12" ht="15" thickBot="1">
       <c r="C17" s="116"/>
       <c r="D17" s="32"/>
       <c r="E17" s="33" t="s">
@@ -26263,7 +26412,7 @@
       <c r="H17" s="30"/>
       <c r="I17" s="31"/>
     </row>
-    <row r="18" spans="3:12" ht="15.75" thickBot="1">
+    <row r="18" spans="3:12" ht="15" thickBot="1">
       <c r="C18" s="37" t="s">
         <v>79</v>
       </c>
@@ -26283,7 +26432,7 @@
       <c r="K18" s="24"/>
       <c r="L18" s="25"/>
     </row>
-    <row r="19" spans="3:12" ht="15.75" thickBot="1">
+    <row r="19" spans="3:12" ht="15" thickBot="1">
       <c r="C19" s="114" t="s">
         <v>78</v>
       </c>
@@ -26303,7 +26452,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="3:12" ht="15.75" thickBot="1">
+    <row r="21" spans="3:12" ht="15" thickBot="1">
       <c r="C21" s="116"/>
       <c r="D21" s="32"/>
       <c r="E21" s="40" t="s">
@@ -26417,10 +26566,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:V102"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="13" max="13" width="4.85546875" customWidth="1"/>
+    <col min="13" max="13" width="4.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
@@ -26935,7 +27084,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D48"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" s="6" t="s">
@@ -27113,10 +27262,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:H90"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="4" max="4" width="13.5703125" customWidth="1"/>
-    <col min="7" max="7" width="9.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" customWidth="1"/>
+    <col min="7" max="7" width="9.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4">
@@ -27482,9 +27631,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Z40"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="4" max="4" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:26">

--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Knowhow" sheetId="1" r:id="rId1"/>
@@ -30,10 +30,12 @@
     <sheet name="#20" sheetId="27" r:id="rId21"/>
     <sheet name="#24" sheetId="20" r:id="rId22"/>
     <sheet name="#25" sheetId="21" r:id="rId23"/>
-    <sheet name="#29" sheetId="23" r:id="rId24"/>
-    <sheet name="#30" sheetId="24" r:id="rId25"/>
-    <sheet name="#31" sheetId="19" r:id="rId26"/>
-    <sheet name="#32" sheetId="25" r:id="rId27"/>
+    <sheet name="#26" sheetId="28" r:id="rId24"/>
+    <sheet name="#28" sheetId="29" r:id="rId25"/>
+    <sheet name="#29" sheetId="23" r:id="rId26"/>
+    <sheet name="#30" sheetId="24" r:id="rId27"/>
+    <sheet name="#31" sheetId="19" r:id="rId28"/>
+    <sheet name="#32" sheetId="25" r:id="rId29"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -45,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="932">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="975">
   <si>
     <t>No.</t>
   </si>
@@ -3769,9 +3771,6 @@
     <t>#18</t>
   </si>
   <si>
-    <t>Containers (vector, list, map, set, queue, stack, …)</t>
-  </si>
-  <si>
     <t>Algorithms (sort(), find(), count(), max_element(), …)</t>
   </si>
   <si>
@@ -9940,11 +9939,6 @@
     <t>Cách sử dụng erase, remove</t>
   </si>
   <si>
-    <t>What is a template in C++? 
-- class template khác class thường ntn khi compile
-- function template</t>
-  </si>
-  <si>
     <t>Struct :</t>
   </si>
   <si>
@@ -9984,9 +9978,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>alignment = 32</t>
-  </si>
-  <si>
     <t>Vì sao phải dùng quy tắc alignment : vì CPU đọc dữ liệu theo từng word (word là đơn vị dữ liệu mà CPU có thể xử lý trong 1 lần)</t>
   </si>
   <si>
@@ -10435,31 +10426,6 @@
   </si>
   <si>
     <t>Hãy cung cấp capibility &gt;=10 cho vector, để giới hạn 1 khoảng trên cho vec</t>
-  </si>
-  <si>
-    <r>
-      <t>vec.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>reverse</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(10);</t>
-    </r>
   </si>
   <si>
     <t>erase()</t>
@@ -12534,13 +12500,492 @@
   </si>
   <si>
     <t>Tồn tại trong phạm vi của nó và tự động thoát khi ra khỏi phạm vi</t>
+  </si>
+  <si>
+    <t>Là con trỏ trỏ tới hàm</t>
+  </si>
+  <si>
+    <t>tác dụng là có thể gọi hàm thông qua 1 biến con trỏ, hoặc truyền hàm như một đối số cho hàm khác</t>
+  </si>
+  <si>
+    <t>void run()</t>
+  </si>
+  <si>
+    <t>{}</t>
+  </si>
+  <si>
+    <t>int sum(int a, int b)</t>
+  </si>
+  <si>
+    <t>return 0;</t>
+  </si>
+  <si>
+    <r>
+      <t>void(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>runptr)() = run;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>int(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sumptr)(int, int) = sum;</t>
+    </r>
+  </si>
+  <si>
+    <t>Struct vs Union (Đá thêm chút data alignment)</t>
+  </si>
+  <si>
+    <t>lệnh reverse() : đảo chiều các phần tử trong array/vector</t>
+  </si>
+  <si>
+    <r>
+      <t>vec.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>reserve</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(10);</t>
+    </r>
+  </si>
+  <si>
+    <t>reverse()</t>
+  </si>
+  <si>
+    <t>reverse(vec.begin(), vec.end()); // Đảo chiều vector</t>
+  </si>
+  <si>
+    <r>
+      <t>reverse(arr, arr+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>); // Đảo chiều array có n phần tử , arr+n là phần tử không tồn tại đầu tiên</t>
+    </r>
+  </si>
+  <si>
+    <t>Hàm có tác dụng đảo ngược các phần tử trong vector, array</t>
+  </si>
+  <si>
+    <t>Function template</t>
+  </si>
+  <si>
+    <t>What is a template in C++? 
+- class template khác class thường ntn khi compile</t>
+  </si>
+  <si>
+    <t>Containers (vector, list, map, unordered_map, tree, pair, set, queue, stack, deque)</t>
+  </si>
+  <si>
+    <t>Class Template là một khuôn mẫu (template) để tạo ra nhiều class khác nhau dựa trên kiểu dữ liệu mà bạn truyền vào.</t>
+  </si>
+  <si>
+    <t>class B{</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>template</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>typename</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a, b;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    Compare(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> x, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> y) : a(x), b(y) {}</t>
+    </r>
+  </si>
+  <si>
+    <t>//&lt;- Dòng này biến class thường thành class template</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khi nào dùng : </t>
+  </si>
+  <si>
+    <t>Khi muốn code một lần nhưng dùng cho nhiều kiểu khác nhau</t>
+  </si>
+  <si>
+    <t>Khái niệm :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return a + b;</t>
+  </si>
+  <si>
+    <t>Là 1 template chung có thể dùng cho nhiều hàm tương đồng nhau về xử lý, chỉ khác kiểu dữ liệu truyền vào</t>
+  </si>
+  <si>
+    <t>Muốn code 1 lần nhưng gọi được ở nhiều hàm</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> add(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> b) {</t>
+    </r>
+  </si>
+  <si>
+    <t>class template là gì ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Class template khác class thường ntn khi compile ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khi compile thì </t>
+  </si>
+  <si>
+    <t>Function template khác function thường như thế nào ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khi compile thì function thường sẽ được định nghĩa và lưu trong binary. Khi gọi tới hàm thì sẽ nhảy vào vùng đó để thực thi </t>
+  </si>
+  <si>
+    <t>Function thường :</t>
+  </si>
+  <si>
+    <t>Function template :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compiler không tạo code, chỉ lưu lại khuôn mẫu, khi gọi hàm với 1 phiên bản nhất định thì chương trình mới tạo ra phiên bản đó và để vào trong binary </t>
+  </si>
+  <si>
+    <t>(n cách gọi thì sẽ có n phiên bản của function trong binary)</t>
+  </si>
+  <si>
+    <t>alignment = 8</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">➡ Compiler </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tạo ra cấu trúc class ngay lập tức</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">➡ Bất kỳ object </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>A obj;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> nào cũng dùng </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>chỉ một phiên bản duy nhất</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> trong binary.</t>
+    </r>
+  </si>
+  <si>
+    <t>Class thường :</t>
+  </si>
+  <si>
+    <t>Class template :</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">➡ Compiler </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>chưa tạo ra cấu trúc class, mà chờ được định nghĩa cụ thể</t>
+    </r>
+  </si>
+  <si>
+    <t>➡ Sẽ có n phiên bản cho n kiểu khác nhau. Mỗi lần khai báo 1 phiên bản là trong binary được định nghĩa thêm phiên bản đó</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -12722,6 +13167,13 @@
       <color rgb="FFCE92A4"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="19">
@@ -13133,7 +13585,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -13371,6 +13823,24 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -13389,23 +13859,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -17592,19 +18050,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:K22"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="5.7265625" customWidth="1"/>
-    <col min="3" max="3" width="37.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.453125" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" customWidth="1"/>
+    <col min="3" max="3" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.42578125" customWidth="1"/>
     <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="18.5">
+    <row r="2" spans="2:11" ht="18.75">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -17630,7 +18088,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:11" ht="43.5">
+    <row r="3" spans="2:11" ht="45">
       <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
@@ -17984,9 +18442,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Q30"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="11" max="11" width="3.7265625" customWidth="1"/>
+    <col min="11" max="11" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:17">
@@ -18316,12 +18774,12 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E76"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="4.453125" customWidth="1"/>
-    <col min="3" max="3" width="39.7265625" customWidth="1"/>
-    <col min="4" max="4" width="50.81640625" customWidth="1"/>
-    <col min="5" max="5" width="75.453125" customWidth="1"/>
+    <col min="2" max="2" width="4.42578125" customWidth="1"/>
+    <col min="3" max="3" width="39.7109375" customWidth="1"/>
+    <col min="4" max="4" width="50.85546875" customWidth="1"/>
+    <col min="5" max="5" width="75.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.5">
@@ -18329,7 +18787,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="23.5">
+    <row r="2" spans="1:5" ht="23.25">
       <c r="B2" s="63" t="s">
         <v>420</v>
       </c>
@@ -18348,7 +18806,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="43.5">
+    <row r="5" spans="1:5" ht="45">
       <c r="B5" s="69">
         <v>1</v>
       </c>
@@ -18376,7 +18834,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="29">
+    <row r="7" spans="1:5" ht="30">
       <c r="B7" s="69">
         <v>3</v>
       </c>
@@ -18390,7 +18848,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="23.5">
+    <row r="10" spans="1:5" ht="23.25">
       <c r="B10" s="63" t="s">
         <v>344</v>
       </c>
@@ -18409,7 +18867,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" ht="30">
       <c r="B13" s="69">
         <v>1</v>
       </c>
@@ -18423,7 +18881,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="29">
+    <row r="14" spans="1:5" ht="30">
       <c r="B14" s="69">
         <v>2</v>
       </c>
@@ -18437,7 +18895,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="29">
+    <row r="15" spans="1:5" ht="30">
       <c r="B15" s="69">
         <v>3</v>
       </c>
@@ -18451,7 +18909,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="29">
+    <row r="16" spans="1:5" ht="30">
       <c r="B16" s="69">
         <v>4</v>
       </c>
@@ -18465,7 +18923,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="145">
+    <row r="17" spans="2:5" ht="165">
       <c r="B17" s="69">
         <v>5</v>
       </c>
@@ -18479,7 +18937,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="159.5">
+    <row r="18" spans="2:5" ht="180">
       <c r="B18" s="69">
         <v>6</v>
       </c>
@@ -18493,7 +18951,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="130.5">
+    <row r="19" spans="2:5" ht="135">
       <c r="B19" s="69">
         <v>7</v>
       </c>
@@ -18507,7 +18965,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="130.5">
+    <row r="20" spans="2:5" ht="135">
       <c r="B20" s="69">
         <v>8</v>
       </c>
@@ -18521,7 +18979,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="23" spans="2:5" ht="23.5">
+    <row r="23" spans="2:5" ht="23.25">
       <c r="B23" s="63" t="s">
         <v>419</v>
       </c>
@@ -18588,7 +19046,7 @@
       </c>
       <c r="E29" s="1"/>
     </row>
-    <row r="32" spans="2:5" ht="23.5">
+    <row r="32" spans="2:5" ht="23.25">
       <c r="B32" s="63" t="s">
         <v>418</v>
       </c>
@@ -18604,7 +19062,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="35" spans="2:4" ht="29">
+    <row r="35" spans="2:4" ht="30">
       <c r="B35" s="65">
         <v>1</v>
       </c>
@@ -18626,7 +19084,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="37" spans="2:4">
+    <row r="37" spans="2:4" ht="30">
       <c r="B37" s="65">
         <v>3</v>
       </c>
@@ -18648,7 +19106,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="41" spans="2:4" ht="23.5">
+    <row r="41" spans="2:4" ht="23.25">
       <c r="B41" s="63" t="s">
         <v>417</v>
       </c>
@@ -18664,7 +19122,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="44" spans="2:4">
+    <row r="44" spans="2:4" ht="30">
       <c r="B44" s="65">
         <v>1</v>
       </c>
@@ -18708,7 +19166,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="50" spans="2:4" ht="23.5">
+    <row r="50" spans="2:4" ht="23.25">
       <c r="B50" s="63" t="s">
         <v>416</v>
       </c>
@@ -18760,7 +19218,7 @@
     <row r="56" spans="2:4">
       <c r="B56" s="65"/>
     </row>
-    <row r="58" spans="2:4" ht="23.5">
+    <row r="58" spans="2:4" ht="23.25">
       <c r="B58" s="63" t="s">
         <v>415</v>
       </c>
@@ -18787,7 +19245,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="62" spans="2:4" ht="29">
+    <row r="62" spans="2:4" ht="45">
       <c r="B62" s="65">
         <v>2</v>
       </c>
@@ -18798,7 +19256,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="63" spans="2:4" ht="29">
+    <row r="63" spans="2:4" ht="30">
       <c r="B63" s="65">
         <v>3</v>
       </c>
@@ -18831,7 +19289,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="68" spans="2:4" ht="23.5">
+    <row r="68" spans="2:4" ht="23.25">
       <c r="B68" s="63" t="s">
         <v>400</v>
       </c>
@@ -18922,7 +19380,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:S38"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -18931,72 +19389,72 @@
     </row>
     <row r="3" spans="2:5">
       <c r="C3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="5" spans="2:5">
       <c r="C5" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="D6" t="s">
+        <v>491</v>
+      </c>
+      <c r="E6" t="s">
         <v>492</v>
-      </c>
-      <c r="E6" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="D7" t="s">
+        <v>493</v>
+      </c>
+      <c r="E7" t="s">
         <v>494</v>
-      </c>
-      <c r="E7" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="C9" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="C11" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="D12" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="C15" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="17" spans="3:19">
       <c r="D17" s="83" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E17" s="87"/>
       <c r="F17" s="87"/>
       <c r="G17" s="87"/>
       <c r="H17" s="87"/>
       <c r="I17" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="18" spans="3:19">
       <c r="D18" s="83" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E18" s="87"/>
       <c r="F18" s="87"/>
       <c r="G18" s="87"/>
       <c r="H18" s="87"/>
       <c r="I18" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="19" spans="3:19">
@@ -19008,31 +19466,31 @@
     </row>
     <row r="20" spans="3:19">
       <c r="D20" s="85" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E20" s="87"/>
       <c r="F20" s="87"/>
       <c r="G20" s="87"/>
       <c r="H20" s="87"/>
       <c r="I20" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="21" spans="3:19">
       <c r="D21" s="86" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E21" s="87"/>
       <c r="F21" s="87"/>
       <c r="G21" s="87"/>
       <c r="H21" s="87"/>
       <c r="I21" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="22" spans="3:19">
       <c r="D22" s="86" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E22" s="87"/>
       <c r="F22" s="87"/>
@@ -19057,7 +19515,7 @@
     </row>
     <row r="25" spans="3:19">
       <c r="D25" s="85" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E25" s="87"/>
       <c r="F25" s="87"/>
@@ -19066,7 +19524,7 @@
     </row>
     <row r="26" spans="3:19">
       <c r="D26" s="86" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E26" s="87"/>
       <c r="F26" s="87"/>
@@ -19075,7 +19533,7 @@
     </row>
     <row r="27" spans="3:19">
       <c r="D27" s="86" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E27" s="87"/>
       <c r="F27" s="87"/>
@@ -19093,7 +19551,7 @@
     </row>
     <row r="31" spans="3:19">
       <c r="C31" s="88" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D31" s="88"/>
       <c r="E31" s="88"/>
@@ -19105,7 +19563,7 @@
       <c r="K31" s="88"/>
       <c r="L31" s="88"/>
       <c r="M31" s="89" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="N31" s="89"/>
       <c r="O31" s="89"/>
@@ -19136,7 +19594,7 @@
     <row r="33" spans="3:19">
       <c r="C33" s="88"/>
       <c r="D33" s="88" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E33" s="88"/>
       <c r="F33" s="88"/>
@@ -19147,7 +19605,7 @@
       <c r="K33" s="88"/>
       <c r="L33" s="88"/>
       <c r="M33" s="89" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="N33" s="89"/>
       <c r="O33" s="89"/>
@@ -19168,7 +19626,7 @@
       <c r="K34" s="88"/>
       <c r="L34" s="88"/>
       <c r="M34" s="89" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="N34" s="89"/>
       <c r="O34" s="89"/>
@@ -19201,7 +19659,7 @@
     <row r="36" spans="3:19">
       <c r="C36" s="88"/>
       <c r="D36" s="88" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E36" s="88"/>
       <c r="F36" s="88"/>
@@ -19215,7 +19673,7 @@
     <row r="37" spans="3:19">
       <c r="C37" s="88"/>
       <c r="D37" s="88" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="E37" s="88"/>
       <c r="F37" s="88"/>
@@ -19249,105 +19707,105 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:M57"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="C4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="D6" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="D7" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="D8" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E8" s="80"/>
     </row>
     <row r="9" spans="2:5">
       <c r="D9" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="D10" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="D11" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="D12" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="D13" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="D14" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="D15" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="D16" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="17" spans="3:12">
       <c r="D17" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="18" spans="3:12">
       <c r="D18" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="19" spans="3:12">
       <c r="D19" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="22" spans="3:12">
       <c r="C22" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="23" spans="3:12">
       <c r="D23" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="L23" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="24" spans="3:12">
       <c r="D24" s="81" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E24" s="90"/>
       <c r="F24" s="90"/>
@@ -19358,7 +19816,7 @@
     </row>
     <row r="25" spans="3:12">
       <c r="D25" s="81" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E25" s="90"/>
       <c r="F25" s="90"/>
@@ -19369,12 +19827,12 @@
     </row>
     <row r="27" spans="3:12">
       <c r="D27" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="28" spans="3:12">
       <c r="D28" s="81" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E28" s="90"/>
       <c r="F28" s="90"/>
@@ -19385,7 +19843,7 @@
     </row>
     <row r="29" spans="3:12">
       <c r="D29" s="81" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E29" s="90"/>
       <c r="F29" s="90"/>
@@ -19396,7 +19854,7 @@
     </row>
     <row r="30" spans="3:12">
       <c r="D30" s="82" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E30" s="90"/>
       <c r="F30" s="90"/>
@@ -19407,42 +19865,42 @@
     </row>
     <row r="33" spans="3:13">
       <c r="D33" s="91" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="34" spans="3:13">
       <c r="E34" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="35" spans="3:13">
       <c r="F35" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="36" spans="3:13">
       <c r="F36" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="39" spans="3:13">
       <c r="C39" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="41" spans="3:13">
       <c r="D41" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="43" spans="3:13">
       <c r="D43" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="44" spans="3:13">
       <c r="E44" s="81" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F44" s="90"/>
       <c r="G44" s="90"/>
@@ -19466,7 +19924,7 @@
     </row>
     <row r="46" spans="3:13">
       <c r="E46" s="81" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F46" s="90"/>
       <c r="G46" s="90"/>
@@ -19479,7 +19937,7 @@
     </row>
     <row r="47" spans="3:13">
       <c r="E47" s="81" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F47" s="90"/>
       <c r="G47" s="90"/>
@@ -19492,7 +19950,7 @@
     </row>
     <row r="48" spans="3:13">
       <c r="E48" s="81" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="F48" s="90"/>
       <c r="G48" s="90"/>
@@ -19505,7 +19963,7 @@
     </row>
     <row r="49" spans="4:13">
       <c r="E49" s="82" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="F49" s="90"/>
       <c r="G49" s="90"/>
@@ -19518,7 +19976,7 @@
     </row>
     <row r="50" spans="4:13">
       <c r="E50" s="81" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="F50" s="90"/>
       <c r="G50" s="90"/>
@@ -19531,27 +19989,27 @@
     </row>
     <row r="53" spans="4:13">
       <c r="D53" s="91" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="54" spans="4:13">
       <c r="E54" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="55" spans="4:13">
       <c r="E55" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="56" spans="4:13">
       <c r="E56" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="57" spans="4:13">
       <c r="E57" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
   </sheetData>
@@ -19563,31 +20021,31 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:G44"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" s="6" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="C5" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
     </row>
     <row r="6" spans="2:3">
       <c r="C6" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="C7" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
     </row>
     <row r="9" spans="2:3">
@@ -19597,32 +20055,32 @@
     </row>
     <row r="11" spans="2:3">
       <c r="C11" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
     </row>
     <row r="12" spans="2:3">
       <c r="C12" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
     </row>
     <row r="13" spans="2:3">
       <c r="C13" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
     </row>
     <row r="14" spans="2:3">
       <c r="C14" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
     </row>
     <row r="15" spans="2:3">
       <c r="C15" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="16" spans="2:3">
       <c r="C16" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="17" spans="2:7">
@@ -19637,22 +20095,22 @@
     </row>
     <row r="21" spans="2:7">
       <c r="B21" s="6" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
     </row>
     <row r="22" spans="2:7">
       <c r="C22" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
     </row>
     <row r="23" spans="2:7">
       <c r="C23" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
     </row>
     <row r="24" spans="2:7">
       <c r="C24" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
     </row>
     <row r="26" spans="2:7">
@@ -19662,7 +20120,7 @@
     </row>
     <row r="28" spans="2:7">
       <c r="C28" s="103" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="D28" s="104"/>
       <c r="E28" s="104"/>
@@ -19671,7 +20129,7 @@
     </row>
     <row r="29" spans="2:7">
       <c r="C29" s="103" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="D29" s="104"/>
       <c r="E29" s="104"/>
@@ -19680,7 +20138,7 @@
     </row>
     <row r="30" spans="2:7">
       <c r="C30" s="103" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="D30" s="104"/>
       <c r="E30" s="104"/>
@@ -19689,7 +20147,7 @@
     </row>
     <row r="31" spans="2:7">
       <c r="C31" s="113" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="D31" s="104"/>
       <c r="E31" s="104"/>
@@ -19698,7 +20156,7 @@
     </row>
     <row r="32" spans="2:7">
       <c r="C32" s="105" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D32" s="104"/>
       <c r="E32" s="104"/>
@@ -19707,7 +20165,7 @@
     </row>
     <row r="33" spans="2:7">
       <c r="C33" s="110" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="D33" s="104"/>
       <c r="E33" s="104"/>
@@ -19716,7 +20174,7 @@
     </row>
     <row r="34" spans="2:7">
       <c r="C34" s="113" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="D34" s="104"/>
       <c r="E34" s="104"/>
@@ -19725,7 +20183,7 @@
     </row>
     <row r="35" spans="2:7">
       <c r="C35" s="105" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D35" s="104"/>
       <c r="E35" s="104"/>
@@ -19734,7 +20192,7 @@
     </row>
     <row r="36" spans="2:7">
       <c r="C36" s="105" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="D36" s="104"/>
       <c r="E36" s="104"/>
@@ -19743,7 +20201,7 @@
     </row>
     <row r="37" spans="2:7">
       <c r="C37" s="105" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="D37" s="104"/>
       <c r="E37" s="104"/>
@@ -19752,7 +20210,7 @@
     </row>
     <row r="38" spans="2:7">
       <c r="C38" s="105" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="D38" s="104"/>
       <c r="E38" s="104"/>
@@ -19761,7 +20219,7 @@
     </row>
     <row r="39" spans="2:7">
       <c r="C39" s="105" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="D39" s="104"/>
       <c r="E39" s="104"/>
@@ -19788,7 +20246,7 @@
     </row>
     <row r="44" spans="2:7">
       <c r="B44" s="6" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
     </row>
   </sheetData>
@@ -19800,93 +20258,93 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E25"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="3" spans="2:5">
       <c r="C3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D3" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="C4" s="80" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D4" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="C7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="C8" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="C10" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="C11" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="C12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="C13" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="C14" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="C15" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="C16" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="17" spans="3:3">
       <c r="C17" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="18" spans="3:3">
       <c r="C18" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="20" spans="3:3">
       <c r="C20" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="21" spans="3:3">
@@ -19896,17 +20354,17 @@
     </row>
     <row r="23" spans="3:3">
       <c r="C23" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="24" spans="3:3">
       <c r="C24" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="25" spans="3:3">
       <c r="C25" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
@@ -19917,74 +20375,74 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E16"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="3" spans="2:5">
       <c r="C3" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="C4" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="C6" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="D7" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="D8" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="C10" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="C11" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="D12" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="C13" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="D14" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E14" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="C15" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="D16" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
   </sheetData>
@@ -19995,7 +20453,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
@@ -20042,234 +20500,234 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I48"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" ht="18.5">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" ht="18.75">
       <c r="C3" s="93" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D3" s="94"/>
     </row>
     <row r="5" spans="2:4">
       <c r="C5" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D5" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="6" spans="2:4">
       <c r="D6" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="7" spans="2:4">
       <c r="D7" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="8" spans="2:4">
       <c r="D8" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="9" spans="2:4">
       <c r="D9" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="11" spans="2:4">
       <c r="C11" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D11" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="12" spans="2:4">
       <c r="D12" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="13" spans="2:4">
       <c r="D13" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="14" spans="2:4">
       <c r="D14" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="15" spans="2:4">
       <c r="D15" s="92" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="16" spans="2:4">
       <c r="D16" s="76" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="17" spans="3:5">
       <c r="C17" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D17" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="18" spans="3:5">
       <c r="D18" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="19" spans="3:5">
       <c r="E19" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="20" spans="3:5">
       <c r="E20" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="21" spans="3:5">
       <c r="D21" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="22" spans="3:5">
       <c r="D22" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="23" spans="3:5">
       <c r="D23" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="24" spans="3:5">
       <c r="D24" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="26" spans="3:5">
       <c r="C26" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D26" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="27" spans="3:5">
       <c r="D27" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="28" spans="3:5">
       <c r="E28" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="29" spans="3:5">
       <c r="E29" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="33" spans="3:9" ht="18.5">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" ht="18.75">
       <c r="C33" s="93" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D33" s="94"/>
     </row>
     <row r="35" spans="3:9">
       <c r="C35" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="36" spans="3:9">
       <c r="D36" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="38" spans="3:9">
       <c r="D38" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="39" spans="3:9">
       <c r="E39" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="40" spans="3:9">
       <c r="E40" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="G40" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="I40" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="41" spans="3:9">
       <c r="E41" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G41" t="s">
+        <v>683</v>
+      </c>
+      <c r="I41" t="s">
         <v>684</v>
-      </c>
-      <c r="I41" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="42" spans="3:9">
       <c r="E42" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G42" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="44" spans="3:9">
       <c r="D44" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="45" spans="3:9">
       <c r="E45" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="46" spans="3:9">
       <c r="E46" t="s">
+        <v>688</v>
+      </c>
+      <c r="G46" t="s">
         <v>689</v>
-      </c>
-      <c r="G46" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="47" spans="3:9">
       <c r="E47" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G47" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="48" spans="3:9">
       <c r="E48" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G48" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
   </sheetData>
@@ -20281,100 +20739,100 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I113"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="3" spans="2:4">
       <c r="C3" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="C4" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="5" spans="2:4">
       <c r="C5" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D5" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="10" spans="2:4">
       <c r="B10" s="6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="11" spans="2:4">
       <c r="C11" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="12" spans="2:4">
       <c r="C12" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="13" spans="2:4">
       <c r="C13" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="14" spans="2:4">
       <c r="C14" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="16" spans="2:4">
       <c r="C16" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="17" spans="2:5">
       <c r="C17" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="18" spans="2:5">
       <c r="C18" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="19" spans="2:5">
       <c r="C19" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="20" spans="2:5">
       <c r="C20" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="22" spans="2:5">
       <c r="D22" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="23" spans="2:5">
       <c r="E23" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="24" spans="2:5">
       <c r="E24" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="25" spans="2:5">
@@ -20389,162 +20847,162 @@
     </row>
     <row r="29" spans="2:5">
       <c r="C29" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="30" spans="2:5">
       <c r="D30" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="31" spans="2:5">
       <c r="D31" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="32" spans="2:5">
       <c r="D32" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="34" spans="3:5">
       <c r="D34" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="36" spans="3:5">
       <c r="D36" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="37" spans="3:5">
       <c r="E37" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="38" spans="3:5">
       <c r="E38" s="17" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="39" spans="3:5">
       <c r="E39" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="41" spans="3:5">
       <c r="E41" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="42" spans="3:5">
       <c r="E42" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="43" spans="3:5">
       <c r="E43" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="45" spans="3:5">
       <c r="C45" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="46" spans="3:5">
       <c r="D46" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="47" spans="3:5">
       <c r="D47" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="49" spans="2:5">
       <c r="D49" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="50" spans="2:5">
       <c r="E50" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="51" spans="2:5">
       <c r="E51" s="17" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="52" spans="2:5">
       <c r="E52" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="54" spans="2:5">
       <c r="E54" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="55" spans="2:5">
       <c r="E55" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="56" spans="2:5">
       <c r="E56" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="58" spans="2:5">
       <c r="D58" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="59" spans="2:5">
       <c r="D59" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="62" spans="2:5">
       <c r="B62" s="6" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="63" spans="2:5">
       <c r="C63" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="64" spans="2:5">
       <c r="C64" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="65" spans="3:4">
       <c r="C65" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="67" spans="3:4">
       <c r="C67" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="69" spans="3:4">
       <c r="D69" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="70" spans="3:4">
       <c r="D70" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="71" spans="3:4">
       <c r="D71" s="17" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="72" spans="3:4">
@@ -20554,22 +21012,22 @@
     </row>
     <row r="73" spans="3:4">
       <c r="D73" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="75" spans="3:4">
       <c r="D75" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="76" spans="3:4">
       <c r="D76" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="77" spans="3:4">
       <c r="D77" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="78" spans="3:4">
@@ -20579,32 +21037,32 @@
     </row>
     <row r="79" spans="3:4">
       <c r="D79" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="82" spans="2:9">
       <c r="B82" s="6" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="83" spans="2:9">
       <c r="C83" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="84" spans="2:9">
       <c r="C84" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="85" spans="2:9">
       <c r="C85" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="89" spans="2:9" ht="54" customHeight="1">
       <c r="B89" s="117" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C89" s="118"/>
       <c r="D89" s="118"/>
@@ -20616,92 +21074,92 @@
     </row>
     <row r="91" spans="2:9">
       <c r="B91" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="92" spans="2:9">
       <c r="C92" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="93" spans="2:9">
       <c r="C93" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="94" spans="2:9">
       <c r="D94" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="95" spans="2:9">
       <c r="D95" s="17" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="96" spans="2:9">
       <c r="C96" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="97" spans="2:4">
       <c r="D97" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="99" spans="2:4">
       <c r="C99" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="100" spans="2:4">
       <c r="C100" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="101" spans="2:4">
       <c r="C101" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="103" spans="2:4">
       <c r="B103" s="6" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
     </row>
     <row r="105" spans="2:4">
       <c r="C105" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
     </row>
     <row r="106" spans="2:4">
       <c r="D106" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
     </row>
     <row r="108" spans="2:4">
       <c r="C108" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
     </row>
     <row r="109" spans="2:4">
       <c r="D109" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
     </row>
     <row r="110" spans="2:4">
       <c r="D110" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
     </row>
     <row r="112" spans="2:4">
       <c r="D112" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
     </row>
     <row r="113" spans="4:4">
       <c r="D113" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
     </row>
   </sheetData>
@@ -20716,15 +21174,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:F103"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="12.26953125" customWidth="1"/>
-    <col min="4" max="4" width="13.54296875" customWidth="1"/>
-    <col min="5" max="5" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.1796875" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="18.5">
+    <row r="2" spans="2:6" ht="18.75">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -21867,41 +22325,41 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="3" spans="2:4">
       <c r="C3" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="C4" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
     </row>
     <row r="6" spans="2:4">
       <c r="C6" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
     </row>
     <row r="7" spans="2:4">
       <c r="C7" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
     </row>
     <row r="8" spans="2:4">
       <c r="D8" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
     </row>
     <row r="9" spans="2:4">
       <c r="D9" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -21912,111 +22370,111 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:G11"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="6" max="6" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7">
       <c r="B2" s="6" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="15.75" thickBot="1"/>
+    <row r="4" spans="2:7">
+      <c r="C4" s="119" t="s">
+        <v>915</v>
+      </c>
+      <c r="D4" s="120"/>
+      <c r="E4" s="121"/>
+      <c r="F4" t="s">
+        <v>919</v>
+      </c>
+      <c r="G4" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="15.75" thickBot="1">
+      <c r="C5" s="122"/>
+      <c r="D5" s="123"/>
+      <c r="E5" s="124"/>
+      <c r="F5" t="s">
+        <v>921</v>
+      </c>
+      <c r="G5" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7">
+      <c r="C6" s="119" t="s">
+        <v>916</v>
+      </c>
+      <c r="D6" s="120"/>
+      <c r="E6" s="121"/>
+      <c r="F6" t="s">
+        <v>919</v>
+      </c>
+      <c r="G6" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" ht="15.75" thickBot="1">
+      <c r="C7" s="122"/>
+      <c r="D7" s="123"/>
+      <c r="E7" s="124"/>
+      <c r="F7" t="s">
+        <v>921</v>
+      </c>
+      <c r="G7" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7">
+      <c r="C8" s="119" t="s">
+        <v>917</v>
+      </c>
+      <c r="D8" s="120"/>
+      <c r="E8" s="121"/>
+      <c r="F8" t="s">
+        <v>919</v>
+      </c>
+      <c r="G8" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="15.75" thickBot="1">
+      <c r="C9" s="122"/>
+      <c r="D9" s="123"/>
+      <c r="E9" s="124"/>
+      <c r="F9" t="s">
+        <v>921</v>
+      </c>
+      <c r="G9" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7">
+      <c r="C10" s="119" t="s">
         <v>918</v>
       </c>
-    </row>
-    <row r="3" spans="2:7" ht="15" thickBot="1"/>
-    <row r="4" spans="2:7">
-      <c r="C4" s="125" t="s">
+      <c r="D10" s="120"/>
+      <c r="E10" s="121"/>
+      <c r="F10" t="s">
         <v>919</v>
       </c>
-      <c r="D4" s="126"/>
-      <c r="E4" s="127"/>
-      <c r="F4" t="s">
-        <v>923</v>
-      </c>
-      <c r="G4" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="15" thickBot="1">
-      <c r="C5" s="128"/>
-      <c r="D5" s="129"/>
-      <c r="E5" s="130"/>
-      <c r="F5" t="s">
+      <c r="G10" t="s">
         <v>925</v>
       </c>
-      <c r="G5" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7">
-      <c r="C6" s="125" t="s">
-        <v>920</v>
-      </c>
-      <c r="D6" s="126"/>
-      <c r="E6" s="127"/>
-      <c r="F6" t="s">
-        <v>923</v>
-      </c>
-      <c r="G6" t="s">
+    </row>
+    <row r="11" spans="2:7" ht="15.75" thickBot="1">
+      <c r="C11" s="122"/>
+      <c r="D11" s="123"/>
+      <c r="E11" s="124"/>
+      <c r="F11" t="s">
+        <v>921</v>
+      </c>
+      <c r="G11" t="s">
         <v>927</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" ht="15" thickBot="1">
-      <c r="C7" s="128"/>
-      <c r="D7" s="129"/>
-      <c r="E7" s="130"/>
-      <c r="F7" t="s">
-        <v>925</v>
-      </c>
-      <c r="G7" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7">
-      <c r="C8" s="125" t="s">
-        <v>921</v>
-      </c>
-      <c r="D8" s="126"/>
-      <c r="E8" s="127"/>
-      <c r="F8" t="s">
-        <v>923</v>
-      </c>
-      <c r="G8" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" ht="15" thickBot="1">
-      <c r="C9" s="128"/>
-      <c r="D9" s="129"/>
-      <c r="E9" s="130"/>
-      <c r="F9" t="s">
-        <v>925</v>
-      </c>
-      <c r="G9" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7">
-      <c r="C10" s="125" t="s">
-        <v>922</v>
-      </c>
-      <c r="D10" s="126"/>
-      <c r="E10" s="127"/>
-      <c r="F10" t="s">
-        <v>923</v>
-      </c>
-      <c r="G10" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" ht="15" thickBot="1">
-      <c r="C11" s="128"/>
-      <c r="D11" s="129"/>
-      <c r="E11" s="130"/>
-      <c r="F11" t="s">
-        <v>925</v>
-      </c>
-      <c r="G11" t="s">
-        <v>931</v>
       </c>
     </row>
   </sheetData>
@@ -22033,16 +22491,16 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Q108"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:10">
       <c r="B2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="3" spans="2:10">
       <c r="C3" s="103" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D3" s="104"/>
       <c r="E3" s="104"/>
@@ -22054,7 +22512,7 @@
     </row>
     <row r="4" spans="2:10">
       <c r="C4" s="105" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D4" s="104"/>
       <c r="E4" s="104"/>
@@ -22066,7 +22524,7 @@
     </row>
     <row r="5" spans="2:10">
       <c r="C5" s="103" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D5" s="104"/>
       <c r="E5" s="104"/>
@@ -22078,7 +22536,7 @@
     </row>
     <row r="6" spans="2:10">
       <c r="C6" s="103" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D6" s="104"/>
       <c r="E6" s="104"/>
@@ -22090,7 +22548,7 @@
     </row>
     <row r="7" spans="2:10">
       <c r="C7" s="105" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D7" s="104"/>
       <c r="E7" s="104"/>
@@ -22102,7 +22560,7 @@
     </row>
     <row r="8" spans="2:10">
       <c r="C8" s="105" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D8" s="104"/>
       <c r="E8" s="104"/>
@@ -22114,7 +22572,7 @@
     </row>
     <row r="9" spans="2:10">
       <c r="C9" s="105" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D9" s="104"/>
       <c r="E9" s="104"/>
@@ -22138,7 +22596,7 @@
     </row>
     <row r="11" spans="2:10">
       <c r="C11" s="103" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D11" s="104"/>
       <c r="E11" s="104"/>
@@ -22150,7 +22608,7 @@
     </row>
     <row r="12" spans="2:10">
       <c r="C12" s="106" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D12" s="104"/>
       <c r="E12" s="104"/>
@@ -22162,7 +22620,7 @@
     </row>
     <row r="13" spans="2:10">
       <c r="C13" s="106" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="D13" s="104"/>
       <c r="E13" s="104"/>
@@ -22174,7 +22632,7 @@
     </row>
     <row r="14" spans="2:10">
       <c r="C14" s="107" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="D14" s="104"/>
       <c r="E14" s="104"/>
@@ -22186,7 +22644,7 @@
     </row>
     <row r="15" spans="2:10">
       <c r="C15" s="105" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D15" s="104"/>
       <c r="E15" s="104"/>
@@ -22208,7 +22666,7 @@
     </row>
     <row r="17" spans="2:17">
       <c r="C17" s="103" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D17" s="104"/>
       <c r="E17" s="104"/>
@@ -22220,7 +22678,7 @@
     </row>
     <row r="18" spans="2:17">
       <c r="C18" s="105" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D18" s="104"/>
       <c r="E18" s="104"/>
@@ -22232,7 +22690,7 @@
     </row>
     <row r="19" spans="2:17">
       <c r="C19" s="107" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D19" s="104"/>
       <c r="E19" s="104"/>
@@ -22244,7 +22702,7 @@
     </row>
     <row r="20" spans="2:17">
       <c r="C20" s="107" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D20" s="104"/>
       <c r="E20" s="104"/>
@@ -22256,7 +22714,7 @@
     </row>
     <row r="21" spans="2:17">
       <c r="C21" s="109" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D21" s="104"/>
       <c r="E21" s="104"/>
@@ -22290,12 +22748,12 @@
     </row>
     <row r="26" spans="2:17">
       <c r="B26" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="27" spans="2:17">
       <c r="C27" s="109" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D27" s="104"/>
       <c r="E27" s="104"/>
@@ -22314,7 +22772,7 @@
     </row>
     <row r="28" spans="2:17">
       <c r="C28" s="109" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D28" s="104"/>
       <c r="E28" s="104"/>
@@ -22333,7 +22791,7 @@
     </row>
     <row r="29" spans="2:17">
       <c r="C29" s="109" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D29" s="104"/>
       <c r="E29" s="104"/>
@@ -22352,7 +22810,7 @@
     </row>
     <row r="30" spans="2:17">
       <c r="C30" s="109" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D30" s="104"/>
       <c r="E30" s="104"/>
@@ -22388,7 +22846,7 @@
     </row>
     <row r="32" spans="2:17">
       <c r="C32" s="103" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D32" s="104"/>
       <c r="E32" s="104"/>
@@ -22407,7 +22865,7 @@
     </row>
     <row r="33" spans="3:17">
       <c r="C33" s="105" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D33" s="104"/>
       <c r="E33" s="104"/>
@@ -22426,7 +22884,7 @@
     </row>
     <row r="34" spans="3:17">
       <c r="C34" s="103" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D34" s="104"/>
       <c r="E34" s="104"/>
@@ -22445,7 +22903,7 @@
     </row>
     <row r="35" spans="3:17">
       <c r="C35" s="106" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D35" s="104"/>
       <c r="E35" s="104"/>
@@ -22464,7 +22922,7 @@
     </row>
     <row r="36" spans="3:17">
       <c r="C36" s="103" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D36" s="104"/>
       <c r="E36" s="104"/>
@@ -22483,7 +22941,7 @@
     </row>
     <row r="37" spans="3:17">
       <c r="C37" s="103" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D37" s="104"/>
       <c r="E37" s="104"/>
@@ -22502,7 +22960,7 @@
     </row>
     <row r="38" spans="3:17">
       <c r="C38" s="105" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D38" s="104"/>
       <c r="E38" s="104"/>
@@ -22538,7 +22996,7 @@
     </row>
     <row r="40" spans="3:17">
       <c r="C40" s="103" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D40" s="104"/>
       <c r="E40" s="104"/>
@@ -22557,7 +23015,7 @@
     </row>
     <row r="41" spans="3:17">
       <c r="C41" s="105" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D41" s="104"/>
       <c r="E41" s="104"/>
@@ -22576,7 +23034,7 @@
     </row>
     <row r="42" spans="3:17">
       <c r="C42" s="103" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D42" s="104"/>
       <c r="E42" s="104"/>
@@ -22595,7 +23053,7 @@
     </row>
     <row r="43" spans="3:17">
       <c r="C43" s="107" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D43" s="104"/>
       <c r="E43" s="104"/>
@@ -22614,7 +23072,7 @@
     </row>
     <row r="44" spans="3:17">
       <c r="C44" s="107" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D44" s="104"/>
       <c r="E44" s="104"/>
@@ -22633,7 +23091,7 @@
     </row>
     <row r="45" spans="3:17">
       <c r="C45" s="103" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D45" s="104"/>
       <c r="E45" s="104"/>
@@ -22652,7 +23110,7 @@
     </row>
     <row r="46" spans="3:17">
       <c r="C46" s="103" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D46" s="104"/>
       <c r="E46" s="104"/>
@@ -22671,7 +23129,7 @@
     </row>
     <row r="47" spans="3:17">
       <c r="C47" s="105" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D47" s="104"/>
       <c r="E47" s="104"/>
@@ -22690,7 +23148,7 @@
     </row>
     <row r="48" spans="3:17">
       <c r="C48" s="110" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D48" s="104"/>
       <c r="E48" s="104"/>
@@ -22728,7 +23186,7 @@
     </row>
     <row r="50" spans="3:17">
       <c r="C50" s="103" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D50" s="104"/>
       <c r="E50" s="104"/>
@@ -22747,7 +23205,7 @@
     </row>
     <row r="51" spans="3:17">
       <c r="C51" s="105" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D51" s="104"/>
       <c r="E51" s="104"/>
@@ -22766,7 +23224,7 @@
     </row>
     <row r="52" spans="3:17">
       <c r="C52" s="110" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D52" s="104"/>
       <c r="E52" s="104"/>
@@ -22804,7 +23262,7 @@
     </row>
     <row r="54" spans="3:17">
       <c r="C54" s="103" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D54" s="104"/>
       <c r="E54" s="104"/>
@@ -22823,7 +23281,7 @@
     </row>
     <row r="55" spans="3:17">
       <c r="C55" s="105" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D55" s="104"/>
       <c r="E55" s="104"/>
@@ -22842,7 +23300,7 @@
     </row>
     <row r="56" spans="3:17">
       <c r="C56" s="105" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D56" s="104"/>
       <c r="E56" s="104"/>
@@ -22861,7 +23319,7 @@
     </row>
     <row r="57" spans="3:17">
       <c r="C57" s="105" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D57" s="104"/>
       <c r="E57" s="104"/>
@@ -22880,7 +23338,7 @@
     </row>
     <row r="58" spans="3:17">
       <c r="C58" s="105" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D58" s="104"/>
       <c r="E58" s="104"/>
@@ -22899,7 +23357,7 @@
     </row>
     <row r="59" spans="3:17">
       <c r="C59" s="105" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D59" s="104"/>
       <c r="E59" s="104"/>
@@ -22937,7 +23395,7 @@
     </row>
     <row r="61" spans="3:17">
       <c r="C61" s="103" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D61" s="104"/>
       <c r="E61" s="104"/>
@@ -22956,7 +23414,7 @@
     </row>
     <row r="62" spans="3:17">
       <c r="C62" s="105" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D62" s="104"/>
       <c r="E62" s="104"/>
@@ -22975,7 +23433,7 @@
     </row>
     <row r="63" spans="3:17">
       <c r="C63" s="110" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D63" s="104"/>
       <c r="E63" s="104"/>
@@ -22994,7 +23452,7 @@
     </row>
     <row r="64" spans="3:17">
       <c r="C64" s="106" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D64" s="104"/>
       <c r="E64" s="104"/>
@@ -23032,7 +23490,7 @@
     </row>
     <row r="66" spans="3:17">
       <c r="C66" s="105" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D66" s="104"/>
       <c r="E66" s="104"/>
@@ -23068,7 +23526,7 @@
     </row>
     <row r="68" spans="3:17">
       <c r="C68" s="103" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D68" s="104"/>
       <c r="E68" s="104"/>
@@ -23087,7 +23545,7 @@
     </row>
     <row r="69" spans="3:17">
       <c r="C69" s="105" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D69" s="104"/>
       <c r="E69" s="104"/>
@@ -23106,7 +23564,7 @@
     </row>
     <row r="70" spans="3:17">
       <c r="C70" s="103" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D70" s="104"/>
       <c r="E70" s="104"/>
@@ -23125,7 +23583,7 @@
     </row>
     <row r="71" spans="3:17">
       <c r="C71" s="107" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D71" s="104"/>
       <c r="E71" s="104"/>
@@ -23144,7 +23602,7 @@
     </row>
     <row r="72" spans="3:17">
       <c r="C72" s="107" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="D72" s="104"/>
       <c r="E72" s="104"/>
@@ -23163,7 +23621,7 @@
     </row>
     <row r="73" spans="3:17">
       <c r="C73" s="103" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D73" s="104"/>
       <c r="E73" s="104"/>
@@ -23182,7 +23640,7 @@
     </row>
     <row r="74" spans="3:17">
       <c r="C74" s="106" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D74" s="104"/>
       <c r="E74" s="104"/>
@@ -23201,7 +23659,7 @@
     </row>
     <row r="75" spans="3:17">
       <c r="C75" s="105" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D75" s="104"/>
       <c r="E75" s="104"/>
@@ -23220,7 +23678,7 @@
     </row>
     <row r="76" spans="3:17">
       <c r="C76" s="110" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D76" s="104"/>
       <c r="E76" s="104"/>
@@ -23275,7 +23733,7 @@
     </row>
     <row r="79" spans="3:17">
       <c r="C79" s="103" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D79" s="104"/>
       <c r="E79" s="104"/>
@@ -23294,7 +23752,7 @@
     </row>
     <row r="80" spans="3:17">
       <c r="C80" s="105" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D80" s="104"/>
       <c r="E80" s="104"/>
@@ -23313,7 +23771,7 @@
     </row>
     <row r="81" spans="3:17">
       <c r="C81" s="110" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D81" s="104"/>
       <c r="E81" s="104"/>
@@ -23332,7 +23790,7 @@
     </row>
     <row r="82" spans="3:17">
       <c r="C82" s="107" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D82" s="104"/>
       <c r="E82" s="104"/>
@@ -23387,7 +23845,7 @@
     </row>
     <row r="85" spans="3:17">
       <c r="C85" s="103" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D85" s="104"/>
       <c r="E85" s="104"/>
@@ -23406,7 +23864,7 @@
     </row>
     <row r="86" spans="3:17">
       <c r="C86" s="105" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D86" s="104"/>
       <c r="E86" s="104"/>
@@ -23425,7 +23883,7 @@
     </row>
     <row r="87" spans="3:17">
       <c r="C87" s="107" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D87" s="104"/>
       <c r="E87" s="104"/>
@@ -23480,7 +23938,7 @@
     </row>
     <row r="90" spans="3:17">
       <c r="C90" s="105" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D90" s="104"/>
       <c r="E90" s="104"/>
@@ -23516,7 +23974,7 @@
     </row>
     <row r="92" spans="3:17">
       <c r="C92" s="103" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D92" s="104"/>
       <c r="E92" s="104"/>
@@ -23535,7 +23993,7 @@
     </row>
     <row r="93" spans="3:17">
       <c r="C93" s="105" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D93" s="104"/>
       <c r="E93" s="104"/>
@@ -23554,7 +24012,7 @@
     </row>
     <row r="94" spans="3:17">
       <c r="C94" s="107" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D94" s="104"/>
       <c r="E94" s="104"/>
@@ -23573,7 +24031,7 @@
     </row>
     <row r="95" spans="3:17">
       <c r="C95" s="107" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D95" s="104"/>
       <c r="E95" s="104"/>
@@ -23592,7 +24050,7 @@
     </row>
     <row r="96" spans="3:17">
       <c r="C96" s="107" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D96" s="104"/>
       <c r="E96" s="104"/>
@@ -23611,7 +24069,7 @@
     </row>
     <row r="97" spans="3:17">
       <c r="C97" s="107" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D97" s="104"/>
       <c r="E97" s="104"/>
@@ -23647,7 +24105,7 @@
     </row>
     <row r="99" spans="3:17">
       <c r="C99" s="110" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="D99" s="104"/>
       <c r="E99" s="104"/>
@@ -23666,7 +24124,7 @@
     </row>
     <row r="100" spans="3:17">
       <c r="C100" s="110" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D100" s="104"/>
       <c r="E100" s="104"/>
@@ -23702,7 +24160,7 @@
     </row>
     <row r="102" spans="3:17">
       <c r="C102" s="110" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D102" s="104"/>
       <c r="E102" s="104"/>
@@ -23721,7 +24179,7 @@
     </row>
     <row r="103" spans="3:17">
       <c r="C103" s="110" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="D103" s="104"/>
       <c r="E103" s="104"/>
@@ -23757,7 +24215,7 @@
     </row>
     <row r="105" spans="3:17">
       <c r="C105" s="110" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="D105" s="104"/>
       <c r="E105" s="104"/>
@@ -23793,7 +24251,7 @@
     </row>
     <row r="107" spans="3:17">
       <c r="C107" s="109" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D107" s="104"/>
       <c r="E107" s="104"/>
@@ -23838,127 +24296,127 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E27"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="3" spans="2:5">
       <c r="C3" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="D4" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="D6" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="E7" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="E8" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="E9" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="E10" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="C12" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="D13" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="D15" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="E16" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
     </row>
     <row r="17" spans="2:5">
       <c r="E17" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="17" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C19" s="17"/>
     </row>
     <row r="20" spans="2:5">
       <c r="B20" s="17" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C20" s="17"/>
     </row>
     <row r="21" spans="2:5">
       <c r="C21" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="22" spans="2:5">
       <c r="D22" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="E22" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="23" spans="2:5">
       <c r="D23" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="E23" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="24" spans="2:5">
       <c r="D24" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="E24" t="s">
-        <v>791</v>
+        <v>968</v>
       </c>
     </row>
     <row r="25" spans="2:5">
       <c r="C25" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
     </row>
     <row r="26" spans="2:5">
       <c r="C26" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
     </row>
     <row r="27" spans="2:5">
       <c r="B27" s="17" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
   </sheetData>
@@ -23969,124 +24427,437 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:F27"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="B2:E37"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="4" max="4" width="19" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3">
+      <c r="B2" s="6" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3">
+      <c r="C3" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3">
+      <c r="C4" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3">
+      <c r="C6" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3">
+      <c r="C8" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3">
+      <c r="C9" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3">
+      <c r="C11" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3">
+      <c r="C12" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3">
+      <c r="C14" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3">
+      <c r="C15" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3">
+      <c r="C16" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
+      <c r="C17" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="C18" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="C19" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4">
+      <c r="B22" s="6" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4">
+      <c r="C23" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4">
+      <c r="D24" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4">
+      <c r="C25" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4">
+      <c r="D26" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4">
+      <c r="C28" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4">
+      <c r="C29" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4">
+      <c r="C30" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4">
+      <c r="C31" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4">
+      <c r="C32" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="34" spans="3:5">
+      <c r="C34" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="35" spans="3:5">
+      <c r="D35" t="s">
+        <v>964</v>
+      </c>
+      <c r="E35" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="36" spans="3:5">
+      <c r="D36" t="s">
+        <v>965</v>
+      </c>
+      <c r="E36" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="37" spans="3:5">
+      <c r="E37" t="s">
+        <v>967</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:F28"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="4" max="4" width="16.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6">
+      <c r="B2" s="6" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6">
+      <c r="C3" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6">
+      <c r="D4" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6">
+      <c r="C5" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6">
+      <c r="D6" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6">
+      <c r="C8" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6">
+      <c r="C9" t="s">
+        <v>948</v>
+      </c>
+      <c r="F9" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6">
+      <c r="C10" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6">
+      <c r="C11" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6">
+      <c r="C12" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6">
+      <c r="C13" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6">
+      <c r="C14" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6">
+      <c r="C15" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5">
+      <c r="C18" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
+      <c r="D19" t="s">
+        <v>971</v>
+      </c>
+      <c r="E19" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5">
+      <c r="E20" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5">
+      <c r="D22" t="s">
+        <v>972</v>
+      </c>
+      <c r="E22" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5">
+      <c r="E23" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5">
+      <c r="E24" s="131"/>
+    </row>
+    <row r="25" spans="2:5">
+      <c r="E25" s="131"/>
+    </row>
+    <row r="26" spans="2:5">
+      <c r="E26" s="131"/>
+    </row>
+    <row r="27" spans="2:5">
+      <c r="E27" s="131"/>
+    </row>
+    <row r="28" spans="2:5">
+      <c r="E28" s="131"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:F33"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
     </row>
     <row r="3" spans="2:4">
       <c r="C3" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="D4" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
     </row>
     <row r="5" spans="2:4">
       <c r="C5" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
     </row>
     <row r="6" spans="2:4">
       <c r="D6" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
     </row>
     <row r="7" spans="2:4">
       <c r="D7" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
     </row>
     <row r="8" spans="2:4">
       <c r="D8" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
     </row>
     <row r="10" spans="2:4">
       <c r="D10" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
     </row>
     <row r="12" spans="2:4">
       <c r="D12" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
     </row>
     <row r="13" spans="2:4">
       <c r="D13" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
     </row>
     <row r="14" spans="2:4">
       <c r="D14" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
     </row>
     <row r="15" spans="2:4">
       <c r="D15" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
     </row>
     <row r="16" spans="2:4">
       <c r="D16" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="D18" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="D20" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="C22" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="18" spans="3:6">
-      <c r="D18" t="s">
+    <row r="23" spans="2:6">
+      <c r="D23" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="20" spans="3:6">
-      <c r="D20" t="s">
+    <row r="24" spans="2:6">
+      <c r="D24" t="s">
+        <v>832</v>
+      </c>
+      <c r="F24" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="22" spans="3:6">
-      <c r="C22" t="s">
+    <row r="25" spans="2:6">
+      <c r="D25" t="s">
+        <v>831</v>
+      </c>
+      <c r="F25" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="23" spans="3:6">
-      <c r="D23" t="s">
+    <row r="26" spans="2:6">
+      <c r="D26" t="s">
+        <v>830</v>
+      </c>
+      <c r="E26" t="s">
         <v>829</v>
       </c>
     </row>
-    <row r="24" spans="3:6">
-      <c r="D24" t="s">
-        <v>835</v>
-      </c>
-      <c r="F24" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="25" spans="3:6">
-      <c r="D25" t="s">
-        <v>834</v>
-      </c>
-      <c r="F25" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="26" spans="3:6">
-      <c r="D26" t="s">
+    <row r="27" spans="2:6">
+      <c r="D27" t="s">
+        <v>938</v>
+      </c>
+      <c r="F27" t="s">
         <v>833</v>
       </c>
-      <c r="E26" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="27" spans="3:6">
-      <c r="D27" t="s">
-        <v>837</v>
-      </c>
-      <c r="F27" t="s">
-        <v>836</v>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="C31" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="C32" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3">
+      <c r="C33" t="s">
+        <v>941</v>
       </c>
     </row>
   </sheetData>
@@ -24095,107 +24866,107 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:B39"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="22.1796875" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:2">
       <c r="B2" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
     </row>
     <row r="3" spans="2:2">
       <c r="B3" s="11" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" s="11" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" s="11" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
     </row>
     <row r="8" spans="2:2">
       <c r="B8" s="11" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" s="12" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
     </row>
     <row r="11" spans="2:2">
       <c r="B11" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" s="80" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" s="80" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" s="80" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
     </row>
     <row r="16" spans="2:2">
       <c r="B16" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" s="11" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" s="80" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
     </row>
     <row r="29" spans="2:2">
@@ -24203,47 +24974,47 @@
     </row>
     <row r="30" spans="2:2">
       <c r="B30" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="31" spans="2:2">
       <c r="B31" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" s="111" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" s="11" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
     </row>
     <row r="39" spans="2:2">
       <c r="B39" s="80" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
     </row>
   </sheetData>
@@ -24252,37 +25023,37 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:O20"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:15">
       <c r="B2" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="4" spans="2:15">
       <c r="C4" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="5" spans="2:15">
       <c r="C5" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="6" spans="2:15">
       <c r="C6" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="8" spans="2:15">
       <c r="F8" s="99" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="L8" s="100" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="M8" s="101"/>
       <c r="N8" s="101"/>
@@ -24290,13 +25061,13 @@
     </row>
     <row r="9" spans="2:15">
       <c r="F9" s="95" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="G9" t="s">
+        <v>708</v>
+      </c>
+      <c r="L9" s="96" t="s">
         <v>709</v>
-      </c>
-      <c r="L9" s="96" t="s">
-        <v>710</v>
       </c>
       <c r="M9" s="97"/>
       <c r="N9" s="97"/>
@@ -24304,40 +25075,40 @@
     </row>
     <row r="11" spans="2:15">
       <c r="E11" t="s">
+        <v>711</v>
+      </c>
+      <c r="L11" t="s">
         <v>712</v>
-      </c>
-      <c r="L11" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="16" spans="2:15">
       <c r="D16" t="s">
-        <v>714</v>
-      </c>
-      <c r="I16" s="119" t="s">
-        <v>718</v>
-      </c>
-      <c r="J16" s="120"/>
+        <v>713</v>
+      </c>
+      <c r="I16" s="125" t="s">
+        <v>717</v>
+      </c>
+      <c r="J16" s="126"/>
     </row>
     <row r="17" spans="3:10" ht="15" customHeight="1">
-      <c r="I17" s="121"/>
-      <c r="J17" s="122"/>
+      <c r="I17" s="127"/>
+      <c r="J17" s="128"/>
     </row>
     <row r="18" spans="3:10">
       <c r="D18" t="s">
-        <v>715</v>
-      </c>
-      <c r="I18" s="123"/>
-      <c r="J18" s="124"/>
+        <v>714</v>
+      </c>
+      <c r="I18" s="129"/>
+      <c r="J18" s="130"/>
     </row>
     <row r="19" spans="3:10">
       <c r="C19" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="20" spans="3:10">
       <c r="D20" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
   </sheetData>
@@ -24349,24 +25120,24 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:K18"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:11">
       <c r="B2" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
     </row>
     <row r="3" spans="2:11">
       <c r="B3" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
     </row>
     <row r="4" spans="2:11">
       <c r="B4" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
     </row>
     <row r="6" spans="2:11">
@@ -24376,38 +25147,38 @@
     </row>
     <row r="7" spans="2:11">
       <c r="B7" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="F7" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
     </row>
     <row r="10" spans="2:11">
       <c r="B10" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
     </row>
     <row r="11" spans="2:11">
       <c r="B11" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
     </row>
     <row r="12" spans="2:11">
       <c r="B12" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="K12" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
     </row>
     <row r="13" spans="2:11">
       <c r="B13" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
     </row>
     <row r="14" spans="2:11">
       <c r="B14" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
     </row>
     <row r="16" spans="2:11">
@@ -24417,18 +25188,18 @@
     </row>
     <row r="17" spans="2:6">
       <c r="B17" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="F17" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="F18" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
     </row>
   </sheetData>
@@ -24438,13 +25209,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:G106"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="B1:G108"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="62.81640625" customWidth="1"/>
-    <col min="4" max="4" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="68.54296875" customWidth="1"/>
-    <col min="6" max="6" width="9.7265625" customWidth="1"/>
+    <col min="3" max="3" width="62.85546875" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6">
@@ -24452,7 +25223,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="2:6" ht="18.5">
+    <row r="2" spans="2:6" ht="18.75">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -25177,7 +25948,7 @@
         <v>287</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D49" s="51">
         <v>0.9</v>
@@ -25192,7 +25963,7 @@
         <v>319</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D50" s="42">
         <v>1</v>
@@ -25207,9 +25978,9 @@
         <v>320</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>711</v>
-      </c>
-      <c r="D51" s="51">
+        <v>710</v>
+      </c>
+      <c r="D51" s="132">
         <v>0.2</v>
       </c>
       <c r="E51" s="16" t="s">
@@ -25224,7 +25995,7 @@
         <v>11.1</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="D52" s="42">
         <v>1</v>
@@ -25239,7 +26010,7 @@
         <v>11.2</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="D53" s="42">
         <v>1</v>
@@ -25254,11 +26025,9 @@
         <v>11.3</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>900</v>
-      </c>
-      <c r="D54" s="51">
-        <v>0</v>
-      </c>
+        <v>896</v>
+      </c>
+      <c r="D54" s="132"/>
       <c r="E54" s="16"/>
       <c r="F54" s="16" t="s">
         <v>14</v>
@@ -25267,35 +26036,35 @@
     <row r="55" spans="2:6">
       <c r="B55" s="5"/>
       <c r="C55" s="7"/>
-      <c r="D55" s="51"/>
+      <c r="D55" s="132"/>
       <c r="E55" s="16"/>
       <c r="F55" s="16"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="5"/>
       <c r="C56" s="7"/>
-      <c r="D56" s="51"/>
+      <c r="D56" s="132"/>
       <c r="E56" s="16"/>
       <c r="F56" s="16"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="5"/>
       <c r="C57" s="7"/>
-      <c r="D57" s="51"/>
+      <c r="D57" s="132"/>
       <c r="E57" s="16"/>
       <c r="F57" s="16"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="5"/>
       <c r="C58" s="7"/>
-      <c r="D58" s="51"/>
+      <c r="D58" s="132"/>
       <c r="E58" s="16"/>
       <c r="F58" s="16"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="5"/>
       <c r="C59" s="7"/>
-      <c r="D59" s="51"/>
+      <c r="D59" s="132"/>
       <c r="E59" s="16"/>
       <c r="F59" s="16"/>
     </row>
@@ -25304,7 +26073,7 @@
         <v>321</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D60" s="42">
         <v>1</v>
@@ -25344,12 +26113,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="2:6" ht="43.5">
+    <row r="63" spans="2:6" ht="45">
       <c r="B63" s="5" t="s">
         <v>446</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D63" s="42">
         <v>1</v>
@@ -25370,7 +26139,7 @@
         <v>1</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F64" s="6"/>
     </row>
@@ -25379,7 +26148,7 @@
         <v>16.100000000000001</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D65" s="42">
         <v>1</v>
@@ -25394,7 +26163,7 @@
         <v>16.2</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D66" s="42">
         <v>1</v>
@@ -25419,12 +26188,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="68" spans="2:6" ht="29">
+    <row r="68" spans="2:6" ht="30">
       <c r="B68" s="5">
         <v>16.399999999999999</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D68" s="42">
         <v>1</v>
@@ -25439,7 +26208,7 @@
         <v>16.5</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D69" s="42">
         <v>1</v>
@@ -25449,12 +26218,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="70" spans="2:6" ht="43.5">
+    <row r="70" spans="2:6" ht="60">
       <c r="B70" s="5">
         <v>16.600000000000001</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="D70" s="42">
         <v>1</v>
@@ -25469,13 +26238,13 @@
         <v>16.7</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D71" s="42">
         <v>1</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="F71" s="16" t="s">
         <v>14</v>
@@ -25486,13 +26255,13 @@
         <v>16.8</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="D72" s="42">
         <v>1</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="F72" s="16" t="s">
         <v>14</v>
@@ -25503,9 +26272,9 @@
         <v>16.899999999999999</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>901</v>
-      </c>
-      <c r="D73" s="51">
+        <v>897</v>
+      </c>
+      <c r="D73" s="132">
         <v>0</v>
       </c>
       <c r="E73" s="7"/>
@@ -25522,18 +26291,18 @@
       <c r="E74" s="6"/>
       <c r="F74" s="6"/>
     </row>
-    <row r="75" spans="2:6" ht="29">
+    <row r="75" spans="2:6" ht="30">
       <c r="B75" s="5">
         <v>17.100000000000001</v>
       </c>
       <c r="C75" s="78" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D75" s="6"/>
       <c r="E75" s="6"/>
       <c r="F75" s="6"/>
     </row>
-    <row r="76" spans="2:6">
+    <row r="76" spans="2:6" ht="30">
       <c r="B76" s="5">
         <v>17.2</v>
       </c>
@@ -25549,11 +26318,11 @@
         <v>17.3</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D77" s="6"/>
       <c r="E77" s="16" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F77" s="6"/>
     </row>
@@ -25584,20 +26353,22 @@
         <v>455</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D80" s="6"/>
       <c r="E80" s="6"/>
       <c r="F80" s="6"/>
     </row>
-    <row r="81" spans="2:7">
+    <row r="81" spans="2:7" ht="30">
       <c r="B81" s="5">
         <v>18.100000000000001</v>
       </c>
-      <c r="C81" s="6" t="s">
-        <v>456</v>
-      </c>
-      <c r="D81" s="6"/>
+      <c r="C81" s="7" t="s">
+        <v>945</v>
+      </c>
+      <c r="D81" s="51">
+        <v>0</v>
+      </c>
       <c r="E81" s="6"/>
       <c r="F81" s="6"/>
     </row>
@@ -25606,7 +26377,7 @@
         <v>18.2</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D82" s="6"/>
       <c r="E82" s="6"/>
@@ -25617,7 +26388,7 @@
         <v>18.3</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D83" s="6"/>
       <c r="E83" s="6"/>
@@ -25628,7 +26399,7 @@
         <v>18.399999999999999</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D84" s="6"/>
       <c r="E84" s="6"/>
@@ -25636,10 +26407,10 @@
     </row>
     <row r="85" spans="2:7">
       <c r="B85" s="5" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D85" s="112">
         <v>0.9</v>
@@ -25654,7 +26425,7 @@
         <v>19.100000000000001</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D86" s="42">
         <v>1</v>
@@ -25666,10 +26437,10 @@
     </row>
     <row r="87" spans="2:7">
       <c r="B87" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="D87" s="42">
         <v>1</v>
@@ -25681,12 +26452,14 @@
     </row>
     <row r="88" spans="2:7">
       <c r="B88" s="5" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="D88" s="6"/>
+      <c r="D88" s="51">
+        <v>0</v>
+      </c>
       <c r="E88" s="6"/>
       <c r="F88" s="6"/>
     </row>
@@ -25701,12 +26474,12 @@
       <c r="E89" s="6"/>
       <c r="F89" s="6"/>
     </row>
-    <row r="90" spans="2:7" ht="29">
+    <row r="90" spans="2:7" ht="30">
       <c r="B90" s="5">
         <v>21.2</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D90" s="6"/>
       <c r="E90" s="6"/>
@@ -25714,29 +26487,31 @@
     </row>
     <row r="91" spans="2:7">
       <c r="B91" s="5" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="D91" s="6"/>
+      <c r="D91" s="51">
+        <v>0.01</v>
+      </c>
       <c r="E91" s="16" t="s">
+        <v>465</v>
+      </c>
+      <c r="F91" s="6"/>
+    </row>
+    <row r="92" spans="2:7" ht="30">
+      <c r="B92" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="F91" s="6"/>
-    </row>
-    <row r="92" spans="2:7" ht="29">
-      <c r="B92" s="5" t="s">
-        <v>467</v>
-      </c>
       <c r="C92" s="7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D92" s="42">
         <v>1</v>
       </c>
       <c r="E92" s="16" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F92" s="16"/>
     </row>
@@ -25745,7 +26520,7 @@
         <v>24.1</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D93" s="42">
         <v>1</v>
@@ -25760,7 +26535,7 @@
         <v>24.2</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="D94" s="42">
         <v>1</v>
@@ -25773,10 +26548,10 @@
     </row>
     <row r="95" spans="2:7">
       <c r="B95" s="5" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>477</v>
+        <v>936</v>
       </c>
       <c r="D95" s="42">
         <v>1</v>
@@ -25788,45 +26563,53 @@
     </row>
     <row r="96" spans="2:7">
       <c r="B96" s="5" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>478</v>
-      </c>
-      <c r="D96" s="6"/>
+        <v>477</v>
+      </c>
+      <c r="D96" s="42">
+        <v>1</v>
+      </c>
       <c r="E96" s="16"/>
-      <c r="F96" s="6"/>
-    </row>
-    <row r="97" spans="2:7" ht="58">
-      <c r="B97" s="5" t="s">
+      <c r="F96" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="97" spans="2:7">
+      <c r="B97" s="5">
+        <v>26.1</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>943</v>
+      </c>
+      <c r="D97" s="42">
+        <v>1</v>
+      </c>
+      <c r="E97" s="16"/>
+      <c r="F97" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7" ht="60">
+      <c r="B98" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="C98" s="79" t="s">
+        <v>480</v>
+      </c>
+      <c r="D98" s="6"/>
+      <c r="E98" s="16" t="s">
+        <v>481</v>
+      </c>
+      <c r="F98" s="6"/>
+    </row>
+    <row r="99" spans="2:7" ht="30">
+      <c r="B99" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="C97" s="79" t="s">
-        <v>481</v>
-      </c>
-      <c r="D97" s="6"/>
-      <c r="E97" s="16" t="s">
-        <v>482</v>
-      </c>
-      <c r="F97" s="6"/>
-    </row>
-    <row r="98" spans="2:7" ht="43.5">
-      <c r="B98" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>777</v>
-      </c>
-      <c r="D98" s="6"/>
-      <c r="E98" s="16"/>
-      <c r="F98" s="6"/>
-    </row>
-    <row r="99" spans="2:7">
-      <c r="B99" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="C99" s="6" t="s">
-        <v>813</v>
+      <c r="C99" s="7" t="s">
+        <v>944</v>
       </c>
       <c r="D99" s="42">
         <v>1</v>
@@ -25838,9 +26621,9 @@
     </row>
     <row r="100" spans="2:7">
       <c r="B100" s="5" t="s">
-        <v>488</v>
-      </c>
-      <c r="C100" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="C100" s="6" t="s">
         <v>810</v>
       </c>
       <c r="D100" s="42">
@@ -25853,10 +26636,10 @@
     </row>
     <row r="101" spans="2:7">
       <c r="B101" s="5">
-        <v>30.1</v>
-      </c>
-      <c r="C101" s="7" t="s">
-        <v>807</v>
+        <v>29.1</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>937</v>
       </c>
       <c r="D101" s="42">
         <v>1</v>
@@ -25867,11 +26650,11 @@
       </c>
     </row>
     <row r="102" spans="2:7">
-      <c r="B102" s="5">
-        <v>30.2</v>
+      <c r="B102" s="5" t="s">
+        <v>487</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D102" s="42">
         <v>1</v>
@@ -25880,14 +26663,13 @@
       <c r="F102" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G102" s="48"/>
     </row>
     <row r="103" spans="2:7">
       <c r="B103" s="5">
-        <v>30.3</v>
+        <v>30.1</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="D103" s="42">
         <v>1</v>
@@ -25897,27 +26679,28 @@
         <v>14</v>
       </c>
     </row>
-    <row r="104" spans="2:7" ht="29">
-      <c r="B104" s="5" t="s">
-        <v>489</v>
+    <row r="104" spans="2:7">
+      <c r="B104" s="5">
+        <v>30.2</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>475</v>
-      </c>
-      <c r="D104" s="51">
-        <v>0.05</v>
+        <v>805</v>
+      </c>
+      <c r="D104" s="42">
+        <v>1</v>
       </c>
       <c r="E104" s="16"/>
       <c r="F104" s="16" t="s">
         <v>14</v>
       </c>
+      <c r="G104" s="48"/>
     </row>
     <row r="105" spans="2:7">
-      <c r="B105" s="5" t="s">
-        <v>775</v>
+      <c r="B105" s="5">
+        <v>30.3</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>776</v>
+        <v>806</v>
       </c>
       <c r="D105" s="42">
         <v>1</v>
@@ -25927,18 +26710,48 @@
         <v>14</v>
       </c>
     </row>
-    <row r="106" spans="2:7">
-      <c r="B106" s="77" t="s">
-        <v>472</v>
-      </c>
-      <c r="C106" s="57" t="s">
+    <row r="106" spans="2:7" ht="30">
+      <c r="B106" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="D106" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="E106" s="16"/>
+      <c r="F106" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="107" spans="2:7">
+      <c r="B107" s="5" t="s">
+        <v>774</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>775</v>
+      </c>
+      <c r="D107" s="42">
+        <v>1</v>
+      </c>
+      <c r="E107" s="16"/>
+      <c r="F107" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="108" spans="2:7">
+      <c r="B108" s="77" t="s">
         <v>471</v>
       </c>
-      <c r="D106" s="1"/>
-      <c r="E106" s="49" t="s">
+      <c r="C108" s="57" t="s">
         <v>470</v>
       </c>
-      <c r="F106" s="1"/>
+      <c r="D108" s="1"/>
+      <c r="E108" s="49" t="s">
+        <v>469</v>
+      </c>
+      <c r="F108" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -25992,7 +26805,7 @@
     <hyperlink ref="E77" r:id="rId8"/>
     <hyperlink ref="E91" r:id="rId9"/>
     <hyperlink ref="E92" r:id="rId10"/>
-    <hyperlink ref="E106" r:id="rId11"/>
+    <hyperlink ref="E108" r:id="rId11"/>
     <hyperlink ref="F49" location="'#9'!B2" display="Link"/>
     <hyperlink ref="F60" location="'#12'!B2" display="Link"/>
     <hyperlink ref="F65" location="'#16'!B2" display="Link"/>
@@ -26005,19 +26818,19 @@
     <hyperlink ref="F63" location="'#15'!B2" display="Link"/>
     <hyperlink ref="F70" location="'#16'!B89" display="Link"/>
     <hyperlink ref="F71" location="'#16'!B10" display="Link"/>
-    <hyperlink ref="F104" location="'#31'!B2" display="Link"/>
+    <hyperlink ref="F106" location="'#31'!B2" display="Link"/>
     <hyperlink ref="F93" location="'#24'!B2" display="Link"/>
     <hyperlink ref="F94" location="'#24'!B2" display="Link"/>
     <hyperlink ref="F94:G94" location="'#24'!B26" display="Link"/>
     <hyperlink ref="F95" location="'#25'!B2" display="Link"/>
     <hyperlink ref="F86" location="'#19'!B2" display="Link"/>
-    <hyperlink ref="F101" location="'#30'!B8" display="Link"/>
-    <hyperlink ref="F99" location="'#29'!B2" display="Link"/>
-    <hyperlink ref="F105" location="'#32'!B2" display="Link"/>
-    <hyperlink ref="F100" location="'#30'!B2" display="Link"/>
-    <hyperlink ref="F102" location="'#30'!B8" display="Link"/>
-    <hyperlink ref="F102:G102" location="'#30'!B24" display="Link"/>
-    <hyperlink ref="F103" location="'#30'!B35" display="Link"/>
+    <hyperlink ref="F103" location="'#30'!B8" display="Link"/>
+    <hyperlink ref="F100" location="'#29'!B2" display="Link"/>
+    <hyperlink ref="F107" location="'#32'!B2" display="Link"/>
+    <hyperlink ref="F102" location="'#30'!B2" display="Link"/>
+    <hyperlink ref="F104" location="'#30'!B8" display="Link"/>
+    <hyperlink ref="F104:G104" location="'#30'!B24" display="Link"/>
+    <hyperlink ref="F105" location="'#30'!B35" display="Link"/>
     <hyperlink ref="F51" location="'#11'!B2" display="Link"/>
     <hyperlink ref="F52" location="'#11'!B4" display="Link"/>
     <hyperlink ref="F53" location="'#11'!B21" display="Link"/>
@@ -26026,6 +26839,10 @@
     <hyperlink ref="F28" location="'#4'!B35" display="Link"/>
     <hyperlink ref="F29" location="'#4'!B43" display="Link"/>
     <hyperlink ref="F87" location="'#20'!B2" display="Link"/>
+    <hyperlink ref="F96" location="'#26'!B2" display="Link"/>
+    <hyperlink ref="F101" location="'#29'!B30" display="Link"/>
+    <hyperlink ref="F99" location="'#28'!B17" display="Link"/>
+    <hyperlink ref="F97" location="'#26'!B22" display="Link"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId12"/>
@@ -26035,13 +26852,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J164"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.26953125" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.5">
+    <row r="1" spans="1:3" ht="18.75">
       <c r="C1" s="41" t="s">
         <v>15</v>
       </c>
@@ -26298,14 +27115,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L61"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="10.453125" customWidth="1"/>
-    <col min="4" max="4" width="5.26953125" customWidth="1"/>
-    <col min="5" max="5" width="48.81640625" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" customWidth="1"/>
+    <col min="4" max="4" width="5.28515625" customWidth="1"/>
+    <col min="5" max="5" width="48.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.5">
+    <row r="1" spans="1:10" ht="18.75">
       <c r="C1" s="41" t="s">
         <v>57</v>
       </c>
@@ -26336,13 +27153,13 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15" thickBot="1">
+    <row r="12" spans="1:10" ht="15.75" thickBot="1">
       <c r="C12" s="11" t="s">
         <v>63</v>
       </c>
       <c r="D12" s="11"/>
     </row>
-    <row r="13" spans="1:10" ht="15" thickBot="1">
+    <row r="13" spans="1:10" ht="15.75" thickBot="1">
       <c r="C13" s="114" t="s">
         <v>78</v>
       </c>
@@ -26359,7 +27176,7 @@
       <c r="H13" s="24"/>
       <c r="I13" s="25"/>
     </row>
-    <row r="14" spans="1:10" ht="15" thickBot="1">
+    <row r="14" spans="1:10" ht="15.75" thickBot="1">
       <c r="C14" s="115"/>
       <c r="D14" s="23" t="s">
         <v>65</v>
@@ -26401,7 +27218,7 @@
       <c r="H16" s="30"/>
       <c r="I16" s="31"/>
     </row>
-    <row r="17" spans="3:12" ht="15" thickBot="1">
+    <row r="17" spans="3:12" ht="15.75" thickBot="1">
       <c r="C17" s="116"/>
       <c r="D17" s="32"/>
       <c r="E17" s="33" t="s">
@@ -26412,7 +27229,7 @@
       <c r="H17" s="30"/>
       <c r="I17" s="31"/>
     </row>
-    <row r="18" spans="3:12" ht="15" thickBot="1">
+    <row r="18" spans="3:12" ht="15.75" thickBot="1">
       <c r="C18" s="37" t="s">
         <v>79</v>
       </c>
@@ -26432,7 +27249,7 @@
       <c r="K18" s="24"/>
       <c r="L18" s="25"/>
     </row>
-    <row r="19" spans="3:12" ht="15" thickBot="1">
+    <row r="19" spans="3:12" ht="15.75" thickBot="1">
       <c r="C19" s="114" t="s">
         <v>78</v>
       </c>
@@ -26452,7 +27269,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="3:12" ht="15" thickBot="1">
+    <row r="21" spans="3:12" ht="15.75" thickBot="1">
       <c r="C21" s="116"/>
       <c r="D21" s="32"/>
       <c r="E21" s="40" t="s">
@@ -26566,10 +27383,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:V102"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="13" max="13" width="4.81640625" customWidth="1"/>
+    <col min="13" max="13" width="4.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
@@ -27084,7 +27901,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D48"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" s="6" t="s">
@@ -27205,27 +28022,27 @@
     </row>
     <row r="36" spans="2:3">
       <c r="C36" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
     </row>
     <row r="37" spans="2:3">
       <c r="C37" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
     </row>
     <row r="39" spans="2:3">
       <c r="B39" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="40" spans="2:3">
       <c r="B40" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
     </row>
     <row r="41" spans="2:3">
       <c r="B41" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
     </row>
     <row r="43" spans="2:3">
@@ -27235,22 +28052,22 @@
     </row>
     <row r="44" spans="2:3">
       <c r="C44" s="50" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
     </row>
     <row r="45" spans="2:3">
       <c r="C45" s="50" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
     </row>
     <row r="47" spans="2:3">
       <c r="B47" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="48" spans="2:3">
       <c r="B48" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
     </row>
   </sheetData>
@@ -27262,10 +28079,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:H90"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="13.54296875" customWidth="1"/>
-    <col min="7" max="7" width="9.453125" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4">
@@ -27631,9 +28448,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Z40"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="17.1796875" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:26">

--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -26,16 +26,19 @@
     <sheet name="#14" sheetId="12" r:id="rId17"/>
     <sheet name="#15" sheetId="18" r:id="rId18"/>
     <sheet name="#16" sheetId="15" r:id="rId19"/>
-    <sheet name="#19" sheetId="22" r:id="rId20"/>
-    <sheet name="#20" sheetId="27" r:id="rId21"/>
-    <sheet name="#24" sheetId="20" r:id="rId22"/>
-    <sheet name="#25" sheetId="21" r:id="rId23"/>
-    <sheet name="#26" sheetId="28" r:id="rId24"/>
-    <sheet name="#28" sheetId="29" r:id="rId25"/>
-    <sheet name="#29" sheetId="23" r:id="rId26"/>
-    <sheet name="#30" sheetId="24" r:id="rId27"/>
-    <sheet name="#31" sheetId="19" r:id="rId28"/>
-    <sheet name="#32" sheetId="25" r:id="rId29"/>
+    <sheet name="#17" sheetId="32" r:id="rId20"/>
+    <sheet name="#19" sheetId="22" r:id="rId21"/>
+    <sheet name="#20" sheetId="27" r:id="rId22"/>
+    <sheet name="#23" sheetId="30" r:id="rId23"/>
+    <sheet name="#24" sheetId="20" r:id="rId24"/>
+    <sheet name="#25" sheetId="21" r:id="rId25"/>
+    <sheet name="#26" sheetId="28" r:id="rId26"/>
+    <sheet name="#27" sheetId="31" r:id="rId27"/>
+    <sheet name="#28" sheetId="29" r:id="rId28"/>
+    <sheet name="#29" sheetId="23" r:id="rId29"/>
+    <sheet name="#30" sheetId="24" r:id="rId30"/>
+    <sheet name="#31" sheetId="19" r:id="rId31"/>
+    <sheet name="#32" sheetId="25" r:id="rId32"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -47,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="1017">
   <si>
     <t>No.</t>
   </si>
@@ -3843,12 +3846,6 @@
     <t>Khác nhau giữa C và C++, Data alignment and padding of struct/class in cpp</t>
   </si>
   <si>
-    <t>-dangerous of using gets()
-- char src[] = ""Sample Test"";
-char dst[10];
-strcpy(dst, src)</t>
-  </si>
-  <si>
     <t>File anh Thư</t>
   </si>
   <si>
@@ -12979,6 +12976,159 @@
   </si>
   <si>
     <t>➡ Sẽ có n phiên bản cho n kiểu khác nhau. Mỗi lần khai báo 1 phiên bản là trong binary được định nghĩa thêm phiên bản đó</t>
+  </si>
+  <si>
+    <t>std::unique_ptr&lt;int&gt;a</t>
+  </si>
+  <si>
+    <t>Cách dùng :</t>
+  </si>
+  <si>
+    <t>Mục đích sử dụng :</t>
+  </si>
+  <si>
+    <t>std::unique_ptr&lt;int&gt; ptr = std::make_unique&lt;int&gt;(10);</t>
+  </si>
+  <si>
+    <t>// khi constructor yêu cầu truyền vào đối số thì viết như vậy</t>
+  </si>
+  <si>
+    <r>
+      <t>std::unique_ptr&lt;MyClass&gt; d = std::make_unique&lt;MyClass&gt;(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MyClass(145)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <t>Để tạo ra 1 con trỏ có cơ chế RAII và trỏ đến 1 đối tượng duy nhất ( không được copy, chỉ được move)</t>
+  </si>
+  <si>
+    <t>std::share_ptr&lt;int&gt;a</t>
+  </si>
+  <si>
+    <t>shared_ptr&lt;int&gt; p = make_shared&lt;int&gt;(p);</t>
+  </si>
+  <si>
+    <t>shared_ptr&lt;int&gt; p1 = p;</t>
+  </si>
+  <si>
+    <t>Khi nhiều đối tượng cùng sử dụng 1 object nhưng không nắm được đối tượng nào sẽ dùng xong cuối cùng để giải phóng</t>
+  </si>
+  <si>
+    <t>shared_ptr&lt;int&gt; p2 = p;</t>
+  </si>
+  <si>
+    <t>p.use_count();</t>
+  </si>
+  <si>
+    <t>//kiểm tra xem số lượng con trỏ đang trỏ vào object là bao nhiêu</t>
+  </si>
+  <si>
+    <t>p.reset();</t>
+  </si>
+  <si>
+    <t>//hủy ngay đối tượng p ra khỏi hệ thống shared_ptr, nếu vẫn còn những thằng khác trỏ vào thì object được trỏ chưa clean</t>
+  </si>
+  <si>
+    <t>int *raw = p.get();</t>
+  </si>
+  <si>
+    <t>// gán 1 raw pointer giữ địa chỉ của shared_ptr, rủi ro là nếu dùng xong hết shared_ptr thì con trỏ raw này trở thành dangling pointer</t>
+  </si>
+  <si>
+    <t>std::weak_ptr&lt;int&gt;a</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> =&gt; 1 trong 2 là weak_ptr để quan sát biến còn lại thì sẽ an toàn</t>
+  </si>
+  <si>
+    <t>Khi 2 đối tượng A và B đều giữ shared_ptr trỏ đến nhau, sẽ dẫn đến vòng lặp không thể clear được object khi thoát ra khỏi phạm vi =&gt; Memory Leak</t>
+  </si>
+  <si>
+    <t>std::weak_ptr&lt;A&gt; a;</t>
+  </si>
+  <si>
+    <t>strcpy(dst, src)</t>
+  </si>
+  <si>
+    <t>memcpy(dst, src, size)</t>
+  </si>
+  <si>
+    <t>-dangerous of using gets()
+- char src[] = ""Sample Test"";
+char dst[10];</t>
+  </si>
+  <si>
+    <t>Mục đích :</t>
+  </si>
+  <si>
+    <t>dùng để copy chuỗi kiểu C ( có ký tự \0 ở cuối)</t>
+  </si>
+  <si>
+    <t>Rủi ro : không kiểm tra kích thước, dễ bị buffer overflow khi size của src quá lớn</t>
+  </si>
+  <si>
+    <t>char src[] = "Hello";</t>
+  </si>
+  <si>
+    <t xml:space="preserve">char dest[10];  </t>
+  </si>
+  <si>
+    <t>#include&lt;cstring&gt;</t>
+  </si>
+  <si>
+    <t>strcpy(dest,src);</t>
+  </si>
+  <si>
+    <t>dùng để copy vùng nhớ của 1 đối tượng</t>
+  </si>
+  <si>
+    <t>#include &lt;cstring&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int a[4] = {1, 2, 3, 4};</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int b[4];</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    memcpy(b, a, sizeof(a));</t>
+  </si>
+  <si>
+    <t>rvalue và lvalue</t>
+  </si>
+  <si>
+    <t>rvalue :</t>
+  </si>
+  <si>
+    <t>lvalue :</t>
+  </si>
+  <si>
+    <t>là 1 giá trị tạm thời, không có địa chỉ cố định, thường nằm ở bên phải của phép gán "="</t>
+  </si>
+  <si>
+    <t>là 1 đại diện cho 1 địa chỉ nhớ cố định, đại diện cho biến, object,.. Thường nằm bên trái của phép gán "="</t>
+  </si>
+  <si>
+    <t>#include &lt;algorithm&gt;</t>
   </si>
 </sst>
 </file>
@@ -13585,7 +13735,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -13808,6 +13958,12 @@
     <xf numFmtId="0" fontId="26" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -13859,10 +14015,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -19389,72 +19542,72 @@
     </row>
     <row r="3" spans="2:5">
       <c r="C3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="5" spans="2:5">
       <c r="C5" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="D6" t="s">
+        <v>490</v>
+      </c>
+      <c r="E6" t="s">
         <v>491</v>
-      </c>
-      <c r="E6" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="D7" t="s">
+        <v>492</v>
+      </c>
+      <c r="E7" t="s">
         <v>493</v>
-      </c>
-      <c r="E7" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="C9" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="C11" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="D12" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="C15" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="17" spans="3:19">
       <c r="D17" s="83" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E17" s="87"/>
       <c r="F17" s="87"/>
       <c r="G17" s="87"/>
       <c r="H17" s="87"/>
       <c r="I17" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="18" spans="3:19">
       <c r="D18" s="83" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E18" s="87"/>
       <c r="F18" s="87"/>
       <c r="G18" s="87"/>
       <c r="H18" s="87"/>
       <c r="I18" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="19" spans="3:19">
@@ -19466,31 +19619,31 @@
     </row>
     <row r="20" spans="3:19">
       <c r="D20" s="85" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E20" s="87"/>
       <c r="F20" s="87"/>
       <c r="G20" s="87"/>
       <c r="H20" s="87"/>
       <c r="I20" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="21" spans="3:19">
       <c r="D21" s="86" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E21" s="87"/>
       <c r="F21" s="87"/>
       <c r="G21" s="87"/>
       <c r="H21" s="87"/>
       <c r="I21" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="22" spans="3:19">
       <c r="D22" s="86" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E22" s="87"/>
       <c r="F22" s="87"/>
@@ -19515,7 +19668,7 @@
     </row>
     <row r="25" spans="3:19">
       <c r="D25" s="85" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E25" s="87"/>
       <c r="F25" s="87"/>
@@ -19524,7 +19677,7 @@
     </row>
     <row r="26" spans="3:19">
       <c r="D26" s="86" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E26" s="87"/>
       <c r="F26" s="87"/>
@@ -19533,7 +19686,7 @@
     </row>
     <row r="27" spans="3:19">
       <c r="D27" s="86" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="E27" s="87"/>
       <c r="F27" s="87"/>
@@ -19551,7 +19704,7 @@
     </row>
     <row r="31" spans="3:19">
       <c r="C31" s="88" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D31" s="88"/>
       <c r="E31" s="88"/>
@@ -19563,7 +19716,7 @@
       <c r="K31" s="88"/>
       <c r="L31" s="88"/>
       <c r="M31" s="89" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="N31" s="89"/>
       <c r="O31" s="89"/>
@@ -19594,7 +19747,7 @@
     <row r="33" spans="3:19">
       <c r="C33" s="88"/>
       <c r="D33" s="88" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="E33" s="88"/>
       <c r="F33" s="88"/>
@@ -19605,7 +19758,7 @@
       <c r="K33" s="88"/>
       <c r="L33" s="88"/>
       <c r="M33" s="89" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="N33" s="89"/>
       <c r="O33" s="89"/>
@@ -19626,7 +19779,7 @@
       <c r="K34" s="88"/>
       <c r="L34" s="88"/>
       <c r="M34" s="89" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="N34" s="89"/>
       <c r="O34" s="89"/>
@@ -19659,7 +19812,7 @@
     <row r="36" spans="3:19">
       <c r="C36" s="88"/>
       <c r="D36" s="88" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E36" s="88"/>
       <c r="F36" s="88"/>
@@ -19673,7 +19826,7 @@
     <row r="37" spans="3:19">
       <c r="C37" s="88"/>
       <c r="D37" s="88" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E37" s="88"/>
       <c r="F37" s="88"/>
@@ -19711,101 +19864,101 @@
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="C4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="D6" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="D7" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="D8" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E8" s="80"/>
     </row>
     <row r="9" spans="2:5">
       <c r="D9" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="D10" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="D11" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="D12" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="D13" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="D14" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="D15" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="D16" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="17" spans="3:12">
       <c r="D17" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="18" spans="3:12">
       <c r="D18" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="19" spans="3:12">
       <c r="D19" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="22" spans="3:12">
       <c r="C22" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="23" spans="3:12">
       <c r="D23" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="L23" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="24" spans="3:12">
       <c r="D24" s="81" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E24" s="90"/>
       <c r="F24" s="90"/>
@@ -19816,7 +19969,7 @@
     </row>
     <row r="25" spans="3:12">
       <c r="D25" s="81" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E25" s="90"/>
       <c r="F25" s="90"/>
@@ -19827,12 +19980,12 @@
     </row>
     <row r="27" spans="3:12">
       <c r="D27" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="28" spans="3:12">
       <c r="D28" s="81" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E28" s="90"/>
       <c r="F28" s="90"/>
@@ -19843,7 +19996,7 @@
     </row>
     <row r="29" spans="3:12">
       <c r="D29" s="81" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E29" s="90"/>
       <c r="F29" s="90"/>
@@ -19854,7 +20007,7 @@
     </row>
     <row r="30" spans="3:12">
       <c r="D30" s="82" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E30" s="90"/>
       <c r="F30" s="90"/>
@@ -19865,42 +20018,42 @@
     </row>
     <row r="33" spans="3:13">
       <c r="D33" s="91" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="34" spans="3:13">
       <c r="E34" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="35" spans="3:13">
       <c r="F35" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="36" spans="3:13">
       <c r="F36" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="39" spans="3:13">
       <c r="C39" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="41" spans="3:13">
       <c r="D41" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="43" spans="3:13">
       <c r="D43" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="44" spans="3:13">
       <c r="E44" s="81" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="F44" s="90"/>
       <c r="G44" s="90"/>
@@ -19924,7 +20077,7 @@
     </row>
     <row r="46" spans="3:13">
       <c r="E46" s="81" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F46" s="90"/>
       <c r="G46" s="90"/>
@@ -19937,7 +20090,7 @@
     </row>
     <row r="47" spans="3:13">
       <c r="E47" s="81" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F47" s="90"/>
       <c r="G47" s="90"/>
@@ -19950,7 +20103,7 @@
     </row>
     <row r="48" spans="3:13">
       <c r="E48" s="81" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F48" s="90"/>
       <c r="G48" s="90"/>
@@ -19963,7 +20116,7 @@
     </row>
     <row r="49" spans="4:13">
       <c r="E49" s="82" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="F49" s="90"/>
       <c r="G49" s="90"/>
@@ -19976,7 +20129,7 @@
     </row>
     <row r="50" spans="4:13">
       <c r="E50" s="81" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="F50" s="90"/>
       <c r="G50" s="90"/>
@@ -19989,27 +20142,27 @@
     </row>
     <row r="53" spans="4:13">
       <c r="D53" s="91" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="54" spans="4:13">
       <c r="E54" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="55" spans="4:13">
       <c r="E55" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="56" spans="4:13">
       <c r="E56" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="57" spans="4:13">
       <c r="E57" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
   </sheetData>
@@ -20025,27 +20178,27 @@
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" s="6" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="C5" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="6" spans="2:3">
       <c r="C6" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="C7" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="9" spans="2:3">
@@ -20055,32 +20208,32 @@
     </row>
     <row r="11" spans="2:3">
       <c r="C11" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="12" spans="2:3">
       <c r="C12" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="13" spans="2:3">
       <c r="C13" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="14" spans="2:3">
       <c r="C14" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="15" spans="2:3">
       <c r="C15" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="16" spans="2:3">
       <c r="C16" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="17" spans="2:7">
@@ -20095,22 +20248,22 @@
     </row>
     <row r="21" spans="2:7">
       <c r="B21" s="6" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="22" spans="2:7">
       <c r="C22" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="23" spans="2:7">
       <c r="C23" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="24" spans="2:7">
       <c r="C24" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="26" spans="2:7">
@@ -20120,7 +20273,7 @@
     </row>
     <row r="28" spans="2:7">
       <c r="C28" s="103" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="D28" s="104"/>
       <c r="E28" s="104"/>
@@ -20129,7 +20282,7 @@
     </row>
     <row r="29" spans="2:7">
       <c r="C29" s="103" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="D29" s="104"/>
       <c r="E29" s="104"/>
@@ -20138,7 +20291,7 @@
     </row>
     <row r="30" spans="2:7">
       <c r="C30" s="103" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="D30" s="104"/>
       <c r="E30" s="104"/>
@@ -20147,7 +20300,7 @@
     </row>
     <row r="31" spans="2:7">
       <c r="C31" s="113" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="D31" s="104"/>
       <c r="E31" s="104"/>
@@ -20156,7 +20309,7 @@
     </row>
     <row r="32" spans="2:7">
       <c r="C32" s="105" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D32" s="104"/>
       <c r="E32" s="104"/>
@@ -20165,7 +20318,7 @@
     </row>
     <row r="33" spans="2:7">
       <c r="C33" s="110" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="D33" s="104"/>
       <c r="E33" s="104"/>
@@ -20174,7 +20327,7 @@
     </row>
     <row r="34" spans="2:7">
       <c r="C34" s="113" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="D34" s="104"/>
       <c r="E34" s="104"/>
@@ -20183,7 +20336,7 @@
     </row>
     <row r="35" spans="2:7">
       <c r="C35" s="105" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D35" s="104"/>
       <c r="E35" s="104"/>
@@ -20192,7 +20345,7 @@
     </row>
     <row r="36" spans="2:7">
       <c r="C36" s="105" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="D36" s="104"/>
       <c r="E36" s="104"/>
@@ -20201,7 +20354,7 @@
     </row>
     <row r="37" spans="2:7">
       <c r="C37" s="105" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="D37" s="104"/>
       <c r="E37" s="104"/>
@@ -20210,7 +20363,7 @@
     </row>
     <row r="38" spans="2:7">
       <c r="C38" s="105" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="D38" s="104"/>
       <c r="E38" s="104"/>
@@ -20219,7 +20372,7 @@
     </row>
     <row r="39" spans="2:7">
       <c r="C39" s="105" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="D39" s="104"/>
       <c r="E39" s="104"/>
@@ -20246,7 +20399,7 @@
     </row>
     <row r="44" spans="2:7">
       <c r="B44" s="6" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
   </sheetData>
@@ -20262,89 +20415,89 @@
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="3" spans="2:5">
       <c r="C3" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E3" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="C4" s="80" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D4" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="C7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="C8" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="C10" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="C11" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="C12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="C13" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="C14" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="C15" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="C16" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="17" spans="3:3">
       <c r="C17" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="18" spans="3:3">
       <c r="C18" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="20" spans="3:3">
       <c r="C20" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="21" spans="3:3">
@@ -20354,17 +20507,17 @@
     </row>
     <row r="23" spans="3:3">
       <c r="C23" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="24" spans="3:3">
       <c r="C24" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="25" spans="3:3">
       <c r="C25" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
   </sheetData>
@@ -20379,70 +20532,70 @@
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="3" spans="2:5">
       <c r="C3" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="C4" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="C6" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="D7" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="D8" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="C10" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="11" spans="2:5">
       <c r="C11" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="D12" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="C13" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="D14" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E14" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="C15" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="D16" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
   </sheetData>
@@ -20504,230 +20657,230 @@
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="3" spans="2:4" ht="18.75">
       <c r="C3" s="93" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D3" s="94"/>
     </row>
     <row r="5" spans="2:4">
       <c r="C5" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D5" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="6" spans="2:4">
       <c r="D6" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="7" spans="2:4">
       <c r="D7" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="8" spans="2:4">
       <c r="D8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="9" spans="2:4">
       <c r="D9" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="11" spans="2:4">
       <c r="C11" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D11" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="12" spans="2:4">
       <c r="D12" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="13" spans="2:4">
       <c r="D13" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="14" spans="2:4">
       <c r="D14" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="15" spans="2:4">
       <c r="D15" s="92" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="16" spans="2:4">
       <c r="D16" s="76" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="17" spans="3:5">
       <c r="C17" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D17" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="18" spans="3:5">
       <c r="D18" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="19" spans="3:5">
       <c r="E19" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="20" spans="3:5">
       <c r="E20" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="21" spans="3:5">
       <c r="D21" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="22" spans="3:5">
       <c r="D22" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="23" spans="3:5">
       <c r="D23" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="24" spans="3:5">
       <c r="D24" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="26" spans="3:5">
       <c r="C26" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D26" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="27" spans="3:5">
       <c r="D27" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="28" spans="3:5">
       <c r="E28" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="29" spans="3:5">
       <c r="E29" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="33" spans="3:9" ht="18.75">
       <c r="C33" s="93" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D33" s="94"/>
     </row>
     <row r="35" spans="3:9">
       <c r="C35" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="36" spans="3:9">
       <c r="D36" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="38" spans="3:9">
       <c r="D38" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="39" spans="3:9">
       <c r="E39" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="40" spans="3:9">
       <c r="E40" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="G40" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="I40" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="41" spans="3:9">
       <c r="E41" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="G41" t="s">
+        <v>682</v>
+      </c>
+      <c r="I41" t="s">
         <v>683</v>
-      </c>
-      <c r="I41" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="42" spans="3:9">
       <c r="E42" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G42" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="44" spans="3:9">
       <c r="D44" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="45" spans="3:9">
       <c r="E45" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="46" spans="3:9">
       <c r="E46" t="s">
+        <v>687</v>
+      </c>
+      <c r="G46" t="s">
         <v>688</v>
-      </c>
-      <c r="G46" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="47" spans="3:9">
       <c r="E47" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="G47" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="48" spans="3:9">
       <c r="E48" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G48" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
   </sheetData>
@@ -20748,26 +20901,26 @@
     </row>
     <row r="3" spans="2:4">
       <c r="C3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="C4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="5" spans="2:4">
       <c r="C5" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D5" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="10" spans="2:4">
@@ -20777,62 +20930,62 @@
     </row>
     <row r="11" spans="2:4">
       <c r="C11" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="12" spans="2:4">
       <c r="C12" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="13" spans="2:4">
       <c r="C13" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="14" spans="2:4">
       <c r="C14" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="16" spans="2:4">
       <c r="C16" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="17" spans="2:5">
       <c r="C17" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="18" spans="2:5">
       <c r="C18" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="19" spans="2:5">
       <c r="C19" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="20" spans="2:5">
       <c r="C20" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="22" spans="2:5">
       <c r="D22" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="23" spans="2:5">
       <c r="E23" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="24" spans="2:5">
       <c r="E24" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="25" spans="2:5">
@@ -20847,162 +21000,162 @@
     </row>
     <row r="29" spans="2:5">
       <c r="C29" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="30" spans="2:5">
       <c r="D30" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="31" spans="2:5">
       <c r="D31" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="32" spans="2:5">
       <c r="D32" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="34" spans="3:5">
       <c r="D34" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="36" spans="3:5">
       <c r="D36" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="37" spans="3:5">
       <c r="E37" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="38" spans="3:5">
       <c r="E38" s="17" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="39" spans="3:5">
       <c r="E39" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="41" spans="3:5">
       <c r="E41" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="42" spans="3:5">
       <c r="E42" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="43" spans="3:5">
       <c r="E43" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="45" spans="3:5">
       <c r="C45" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="46" spans="3:5">
       <c r="D46" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="47" spans="3:5">
       <c r="D47" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="49" spans="2:5">
       <c r="D49" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="50" spans="2:5">
       <c r="E50" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="51" spans="2:5">
       <c r="E51" s="17" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="52" spans="2:5">
       <c r="E52" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="54" spans="2:5">
       <c r="E54" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="55" spans="2:5">
       <c r="E55" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="56" spans="2:5">
       <c r="E56" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="58" spans="2:5">
       <c r="D58" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="59" spans="2:5">
       <c r="D59" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="62" spans="2:5">
       <c r="B62" s="6" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="63" spans="2:5">
       <c r="C63" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="64" spans="2:5">
       <c r="C64" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="65" spans="3:4">
       <c r="C65" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="67" spans="3:4">
       <c r="C67" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="69" spans="3:4">
       <c r="D69" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="70" spans="3:4">
       <c r="D70" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="71" spans="3:4">
       <c r="D71" s="17" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="72" spans="3:4">
@@ -21012,22 +21165,22 @@
     </row>
     <row r="73" spans="3:4">
       <c r="D73" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="75" spans="3:4">
       <c r="D75" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="76" spans="3:4">
       <c r="D76" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="77" spans="3:4">
       <c r="D77" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="78" spans="3:4">
@@ -21037,129 +21190,129 @@
     </row>
     <row r="79" spans="3:4">
       <c r="D79" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="82" spans="2:9">
       <c r="B82" s="6" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="83" spans="2:9">
       <c r="C83" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="84" spans="2:9">
       <c r="C84" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="85" spans="2:9">
       <c r="C85" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="89" spans="2:9" ht="54" customHeight="1">
-      <c r="B89" s="117" t="s">
-        <v>619</v>
-      </c>
-      <c r="C89" s="118"/>
-      <c r="D89" s="118"/>
-      <c r="E89" s="118"/>
-      <c r="F89" s="118"/>
-      <c r="G89" s="118"/>
-      <c r="H89" s="118"/>
-      <c r="I89" s="118"/>
+      <c r="B89" s="119" t="s">
+        <v>618</v>
+      </c>
+      <c r="C89" s="120"/>
+      <c r="D89" s="120"/>
+      <c r="E89" s="120"/>
+      <c r="F89" s="120"/>
+      <c r="G89" s="120"/>
+      <c r="H89" s="120"/>
+      <c r="I89" s="120"/>
     </row>
     <row r="91" spans="2:9">
       <c r="B91" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="92" spans="2:9">
       <c r="C92" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="93" spans="2:9">
       <c r="C93" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="94" spans="2:9">
       <c r="D94" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="95" spans="2:9">
       <c r="D95" s="17" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="96" spans="2:9">
       <c r="C96" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="97" spans="2:4">
       <c r="D97" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="99" spans="2:4">
       <c r="C99" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="100" spans="2:4">
       <c r="C100" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="101" spans="2:4">
       <c r="C101" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="103" spans="2:4">
       <c r="B103" s="6" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="105" spans="2:4">
       <c r="C105" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="106" spans="2:4">
       <c r="D106" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="108" spans="2:4">
       <c r="C108" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="109" spans="2:4">
       <c r="D109" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="110" spans="2:4">
       <c r="D110" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="112" spans="2:4">
       <c r="D112" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="113" spans="4:4">
       <c r="D113" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
   </sheetData>
@@ -22324,6 +22477,37 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B17:D19"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="17" spans="2:4">
+      <c r="B17" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4">
+      <c r="C18" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4">
+      <c r="C19" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
@@ -22334,32 +22518,32 @@
     </row>
     <row r="3" spans="2:4">
       <c r="C3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="C4" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="6" spans="2:4">
       <c r="C6" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7" spans="2:4">
       <c r="C7" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="8" spans="2:4">
       <c r="D8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="9" spans="2:4">
       <c r="D9" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -22367,7 +22551,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -22377,104 +22561,104 @@
   <sheetData>
     <row r="2" spans="2:7">
       <c r="B2" s="6" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="3" spans="2:7" ht="15.75" thickBot="1"/>
     <row r="4" spans="2:7">
-      <c r="C4" s="119" t="s">
+      <c r="C4" s="121" t="s">
+        <v>914</v>
+      </c>
+      <c r="D4" s="122"/>
+      <c r="E4" s="123"/>
+      <c r="F4" t="s">
+        <v>918</v>
+      </c>
+      <c r="G4" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="15.75" thickBot="1">
+      <c r="C5" s="124"/>
+      <c r="D5" s="125"/>
+      <c r="E5" s="126"/>
+      <c r="F5" t="s">
+        <v>920</v>
+      </c>
+      <c r="G5" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7">
+      <c r="C6" s="121" t="s">
         <v>915</v>
       </c>
-      <c r="D4" s="120"/>
-      <c r="E4" s="121"/>
-      <c r="F4" t="s">
-        <v>919</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="D6" s="122"/>
+      <c r="E6" s="123"/>
+      <c r="F6" t="s">
+        <v>918</v>
+      </c>
+      <c r="G6" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" ht="15.75" thickBot="1">
+      <c r="C7" s="124"/>
+      <c r="D7" s="125"/>
+      <c r="E7" s="126"/>
+      <c r="F7" t="s">
         <v>920</v>
       </c>
-    </row>
-    <row r="5" spans="2:7" ht="15.75" thickBot="1">
-      <c r="C5" s="122"/>
-      <c r="D5" s="123"/>
-      <c r="E5" s="124"/>
-      <c r="F5" t="s">
+      <c r="G7" t="s">
         <v>921</v>
       </c>
-      <c r="G5" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7">
-      <c r="C6" s="119" t="s">
+    </row>
+    <row r="8" spans="2:7">
+      <c r="C8" s="121" t="s">
         <v>916</v>
       </c>
-      <c r="D6" s="120"/>
-      <c r="E6" s="121"/>
-      <c r="F6" t="s">
-        <v>919</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="D8" s="122"/>
+      <c r="E8" s="123"/>
+      <c r="F8" t="s">
+        <v>918</v>
+      </c>
+      <c r="G8" t="s">
         <v>923</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="15.75" thickBot="1">
-      <c r="C7" s="122"/>
-      <c r="D7" s="123"/>
-      <c r="E7" s="124"/>
-      <c r="F7" t="s">
-        <v>921</v>
-      </c>
-      <c r="G7" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7">
-      <c r="C8" s="119" t="s">
+    <row r="9" spans="2:7" ht="15.75" thickBot="1">
+      <c r="C9" s="124"/>
+      <c r="D9" s="125"/>
+      <c r="E9" s="126"/>
+      <c r="F9" t="s">
+        <v>920</v>
+      </c>
+      <c r="G9" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7">
+      <c r="C10" s="121" t="s">
         <v>917</v>
       </c>
-      <c r="D8" s="120"/>
-      <c r="E8" s="121"/>
-      <c r="F8" t="s">
-        <v>919</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="D10" s="122"/>
+      <c r="E10" s="123"/>
+      <c r="F10" t="s">
+        <v>918</v>
+      </c>
+      <c r="G10" t="s">
         <v>924</v>
       </c>
     </row>
-    <row r="9" spans="2:7" ht="15.75" thickBot="1">
-      <c r="C9" s="122"/>
-      <c r="D9" s="123"/>
-      <c r="E9" s="124"/>
-      <c r="F9" t="s">
-        <v>921</v>
-      </c>
-      <c r="G9" t="s">
+    <row r="11" spans="2:7" ht="15.75" thickBot="1">
+      <c r="C11" s="124"/>
+      <c r="D11" s="125"/>
+      <c r="E11" s="126"/>
+      <c r="F11" t="s">
+        <v>920</v>
+      </c>
+      <c r="G11" t="s">
         <v>926</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7">
-      <c r="C10" s="119" t="s">
-        <v>918</v>
-      </c>
-      <c r="D10" s="120"/>
-      <c r="E10" s="121"/>
-      <c r="F10" t="s">
-        <v>919</v>
-      </c>
-      <c r="G10" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" ht="15.75" thickBot="1">
-      <c r="C11" s="122"/>
-      <c r="D11" s="123"/>
-      <c r="E11" s="124"/>
-      <c r="F11" t="s">
-        <v>921</v>
-      </c>
-      <c r="G11" t="s">
-        <v>927</v>
       </c>
     </row>
   </sheetData>
@@ -22488,19 +22672,152 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:L30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2" spans="2:12">
+      <c r="B2" s="6" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12">
+      <c r="C3" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12">
+      <c r="D4" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12">
+      <c r="C6" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12">
+      <c r="D7" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12">
+      <c r="D8" t="s">
+        <v>979</v>
+      </c>
+      <c r="L8" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12">
+      <c r="B10" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12">
+      <c r="C11" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12">
+      <c r="D12" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12">
+      <c r="C14" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12">
+      <c r="D15" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12">
+      <c r="D16" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="D17" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6">
+      <c r="D19" t="s">
+        <v>986</v>
+      </c>
+      <c r="F19" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="D20" t="s">
+        <v>988</v>
+      </c>
+      <c r="F20" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="D21" t="s">
+        <v>990</v>
+      </c>
+      <c r="F21" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="C25" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="D26" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="D27" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="C29" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="D30" t="s">
+        <v>995</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Q108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:10">
       <c r="B2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="3" spans="2:10">
       <c r="C3" s="103" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D3" s="104"/>
       <c r="E3" s="104"/>
@@ -22512,7 +22829,7 @@
     </row>
     <row r="4" spans="2:10">
       <c r="C4" s="105" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D4" s="104"/>
       <c r="E4" s="104"/>
@@ -22524,7 +22841,7 @@
     </row>
     <row r="5" spans="2:10">
       <c r="C5" s="103" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D5" s="104"/>
       <c r="E5" s="104"/>
@@ -22536,7 +22853,7 @@
     </row>
     <row r="6" spans="2:10">
       <c r="C6" s="103" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D6" s="104"/>
       <c r="E6" s="104"/>
@@ -22548,7 +22865,7 @@
     </row>
     <row r="7" spans="2:10">
       <c r="C7" s="105" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D7" s="104"/>
       <c r="E7" s="104"/>
@@ -22560,7 +22877,7 @@
     </row>
     <row r="8" spans="2:10">
       <c r="C8" s="105" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D8" s="104"/>
       <c r="E8" s="104"/>
@@ -22572,7 +22889,7 @@
     </row>
     <row r="9" spans="2:10">
       <c r="C9" s="105" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D9" s="104"/>
       <c r="E9" s="104"/>
@@ -22596,7 +22913,7 @@
     </row>
     <row r="11" spans="2:10">
       <c r="C11" s="103" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D11" s="104"/>
       <c r="E11" s="104"/>
@@ -22608,7 +22925,7 @@
     </row>
     <row r="12" spans="2:10">
       <c r="C12" s="106" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D12" s="104"/>
       <c r="E12" s="104"/>
@@ -22620,7 +22937,7 @@
     </row>
     <row r="13" spans="2:10">
       <c r="C13" s="106" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D13" s="104"/>
       <c r="E13" s="104"/>
@@ -22632,7 +22949,7 @@
     </row>
     <row r="14" spans="2:10">
       <c r="C14" s="107" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="D14" s="104"/>
       <c r="E14" s="104"/>
@@ -22644,7 +22961,7 @@
     </row>
     <row r="15" spans="2:10">
       <c r="C15" s="105" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D15" s="104"/>
       <c r="E15" s="104"/>
@@ -22666,7 +22983,7 @@
     </row>
     <row r="17" spans="2:17">
       <c r="C17" s="103" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D17" s="104"/>
       <c r="E17" s="104"/>
@@ -22678,7 +22995,7 @@
     </row>
     <row r="18" spans="2:17">
       <c r="C18" s="105" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D18" s="104"/>
       <c r="E18" s="104"/>
@@ -22690,7 +23007,7 @@
     </row>
     <row r="19" spans="2:17">
       <c r="C19" s="107" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D19" s="104"/>
       <c r="E19" s="104"/>
@@ -22702,7 +23019,7 @@
     </row>
     <row r="20" spans="2:17">
       <c r="C20" s="107" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D20" s="104"/>
       <c r="E20" s="104"/>
@@ -22714,7 +23031,7 @@
     </row>
     <row r="21" spans="2:17">
       <c r="C21" s="109" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D21" s="104"/>
       <c r="E21" s="104"/>
@@ -22748,12 +23065,12 @@
     </row>
     <row r="26" spans="2:17">
       <c r="B26" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="27" spans="2:17">
       <c r="C27" s="109" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D27" s="104"/>
       <c r="E27" s="104"/>
@@ -22772,7 +23089,7 @@
     </row>
     <row r="28" spans="2:17">
       <c r="C28" s="109" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D28" s="104"/>
       <c r="E28" s="104"/>
@@ -22791,7 +23108,7 @@
     </row>
     <row r="29" spans="2:17">
       <c r="C29" s="109" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D29" s="104"/>
       <c r="E29" s="104"/>
@@ -22810,7 +23127,7 @@
     </row>
     <row r="30" spans="2:17">
       <c r="C30" s="109" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D30" s="104"/>
       <c r="E30" s="104"/>
@@ -22846,7 +23163,7 @@
     </row>
     <row r="32" spans="2:17">
       <c r="C32" s="103" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D32" s="104"/>
       <c r="E32" s="104"/>
@@ -22865,7 +23182,7 @@
     </row>
     <row r="33" spans="3:17">
       <c r="C33" s="105" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D33" s="104"/>
       <c r="E33" s="104"/>
@@ -22884,7 +23201,7 @@
     </row>
     <row r="34" spans="3:17">
       <c r="C34" s="103" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D34" s="104"/>
       <c r="E34" s="104"/>
@@ -22903,7 +23220,7 @@
     </row>
     <row r="35" spans="3:17">
       <c r="C35" s="106" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D35" s="104"/>
       <c r="E35" s="104"/>
@@ -22922,7 +23239,7 @@
     </row>
     <row r="36" spans="3:17">
       <c r="C36" s="103" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D36" s="104"/>
       <c r="E36" s="104"/>
@@ -22941,7 +23258,7 @@
     </row>
     <row r="37" spans="3:17">
       <c r="C37" s="103" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D37" s="104"/>
       <c r="E37" s="104"/>
@@ -22960,7 +23277,7 @@
     </row>
     <row r="38" spans="3:17">
       <c r="C38" s="105" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D38" s="104"/>
       <c r="E38" s="104"/>
@@ -22996,7 +23313,7 @@
     </row>
     <row r="40" spans="3:17">
       <c r="C40" s="103" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D40" s="104"/>
       <c r="E40" s="104"/>
@@ -23015,7 +23332,7 @@
     </row>
     <row r="41" spans="3:17">
       <c r="C41" s="105" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D41" s="104"/>
       <c r="E41" s="104"/>
@@ -23034,7 +23351,7 @@
     </row>
     <row r="42" spans="3:17">
       <c r="C42" s="103" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D42" s="104"/>
       <c r="E42" s="104"/>
@@ -23053,7 +23370,7 @@
     </row>
     <row r="43" spans="3:17">
       <c r="C43" s="107" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D43" s="104"/>
       <c r="E43" s="104"/>
@@ -23072,7 +23389,7 @@
     </row>
     <row r="44" spans="3:17">
       <c r="C44" s="107" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D44" s="104"/>
       <c r="E44" s="104"/>
@@ -23091,7 +23408,7 @@
     </row>
     <row r="45" spans="3:17">
       <c r="C45" s="103" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D45" s="104"/>
       <c r="E45" s="104"/>
@@ -23110,7 +23427,7 @@
     </row>
     <row r="46" spans="3:17">
       <c r="C46" s="103" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D46" s="104"/>
       <c r="E46" s="104"/>
@@ -23129,7 +23446,7 @@
     </row>
     <row r="47" spans="3:17">
       <c r="C47" s="105" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D47" s="104"/>
       <c r="E47" s="104"/>
@@ -23148,7 +23465,7 @@
     </row>
     <row r="48" spans="3:17">
       <c r="C48" s="110" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D48" s="104"/>
       <c r="E48" s="104"/>
@@ -23186,7 +23503,7 @@
     </row>
     <row r="50" spans="3:17">
       <c r="C50" s="103" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D50" s="104"/>
       <c r="E50" s="104"/>
@@ -23205,7 +23522,7 @@
     </row>
     <row r="51" spans="3:17">
       <c r="C51" s="105" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D51" s="104"/>
       <c r="E51" s="104"/>
@@ -23224,7 +23541,7 @@
     </row>
     <row r="52" spans="3:17">
       <c r="C52" s="110" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D52" s="104"/>
       <c r="E52" s="104"/>
@@ -23262,7 +23579,7 @@
     </row>
     <row r="54" spans="3:17">
       <c r="C54" s="103" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D54" s="104"/>
       <c r="E54" s="104"/>
@@ -23281,7 +23598,7 @@
     </row>
     <row r="55" spans="3:17">
       <c r="C55" s="105" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D55" s="104"/>
       <c r="E55" s="104"/>
@@ -23300,7 +23617,7 @@
     </row>
     <row r="56" spans="3:17">
       <c r="C56" s="105" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D56" s="104"/>
       <c r="E56" s="104"/>
@@ -23319,7 +23636,7 @@
     </row>
     <row r="57" spans="3:17">
       <c r="C57" s="105" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D57" s="104"/>
       <c r="E57" s="104"/>
@@ -23338,7 +23655,7 @@
     </row>
     <row r="58" spans="3:17">
       <c r="C58" s="105" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D58" s="104"/>
       <c r="E58" s="104"/>
@@ -23357,7 +23674,7 @@
     </row>
     <row r="59" spans="3:17">
       <c r="C59" s="105" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D59" s="104"/>
       <c r="E59" s="104"/>
@@ -23395,7 +23712,7 @@
     </row>
     <row r="61" spans="3:17">
       <c r="C61" s="103" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D61" s="104"/>
       <c r="E61" s="104"/>
@@ -23414,7 +23731,7 @@
     </row>
     <row r="62" spans="3:17">
       <c r="C62" s="105" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D62" s="104"/>
       <c r="E62" s="104"/>
@@ -23433,7 +23750,7 @@
     </row>
     <row r="63" spans="3:17">
       <c r="C63" s="110" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D63" s="104"/>
       <c r="E63" s="104"/>
@@ -23452,7 +23769,7 @@
     </row>
     <row r="64" spans="3:17">
       <c r="C64" s="106" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D64" s="104"/>
       <c r="E64" s="104"/>
@@ -23490,7 +23807,7 @@
     </row>
     <row r="66" spans="3:17">
       <c r="C66" s="105" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D66" s="104"/>
       <c r="E66" s="104"/>
@@ -23526,7 +23843,7 @@
     </row>
     <row r="68" spans="3:17">
       <c r="C68" s="103" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D68" s="104"/>
       <c r="E68" s="104"/>
@@ -23545,7 +23862,7 @@
     </row>
     <row r="69" spans="3:17">
       <c r="C69" s="105" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D69" s="104"/>
       <c r="E69" s="104"/>
@@ -23564,7 +23881,7 @@
     </row>
     <row r="70" spans="3:17">
       <c r="C70" s="103" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D70" s="104"/>
       <c r="E70" s="104"/>
@@ -23583,7 +23900,7 @@
     </row>
     <row r="71" spans="3:17">
       <c r="C71" s="107" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D71" s="104"/>
       <c r="E71" s="104"/>
@@ -23602,7 +23919,7 @@
     </row>
     <row r="72" spans="3:17">
       <c r="C72" s="107" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D72" s="104"/>
       <c r="E72" s="104"/>
@@ -23621,7 +23938,7 @@
     </row>
     <row r="73" spans="3:17">
       <c r="C73" s="103" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D73" s="104"/>
       <c r="E73" s="104"/>
@@ -23640,7 +23957,7 @@
     </row>
     <row r="74" spans="3:17">
       <c r="C74" s="106" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="D74" s="104"/>
       <c r="E74" s="104"/>
@@ -23659,7 +23976,7 @@
     </row>
     <row r="75" spans="3:17">
       <c r="C75" s="105" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D75" s="104"/>
       <c r="E75" s="104"/>
@@ -23678,7 +23995,7 @@
     </row>
     <row r="76" spans="3:17">
       <c r="C76" s="110" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D76" s="104"/>
       <c r="E76" s="104"/>
@@ -23733,7 +24050,7 @@
     </row>
     <row r="79" spans="3:17">
       <c r="C79" s="103" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D79" s="104"/>
       <c r="E79" s="104"/>
@@ -23752,7 +24069,7 @@
     </row>
     <row r="80" spans="3:17">
       <c r="C80" s="105" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D80" s="104"/>
       <c r="E80" s="104"/>
@@ -23771,7 +24088,7 @@
     </row>
     <row r="81" spans="3:17">
       <c r="C81" s="110" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D81" s="104"/>
       <c r="E81" s="104"/>
@@ -23790,7 +24107,7 @@
     </row>
     <row r="82" spans="3:17">
       <c r="C82" s="107" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D82" s="104"/>
       <c r="E82" s="104"/>
@@ -23845,7 +24162,7 @@
     </row>
     <row r="85" spans="3:17">
       <c r="C85" s="103" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D85" s="104"/>
       <c r="E85" s="104"/>
@@ -23864,7 +24181,7 @@
     </row>
     <row r="86" spans="3:17">
       <c r="C86" s="105" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D86" s="104"/>
       <c r="E86" s="104"/>
@@ -23883,7 +24200,7 @@
     </row>
     <row r="87" spans="3:17">
       <c r="C87" s="107" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D87" s="104"/>
       <c r="E87" s="104"/>
@@ -23938,7 +24255,7 @@
     </row>
     <row r="90" spans="3:17">
       <c r="C90" s="105" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D90" s="104"/>
       <c r="E90" s="104"/>
@@ -23974,7 +24291,7 @@
     </row>
     <row r="92" spans="3:17">
       <c r="C92" s="103" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D92" s="104"/>
       <c r="E92" s="104"/>
@@ -23993,7 +24310,7 @@
     </row>
     <row r="93" spans="3:17">
       <c r="C93" s="105" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D93" s="104"/>
       <c r="E93" s="104"/>
@@ -24012,7 +24329,7 @@
     </row>
     <row r="94" spans="3:17">
       <c r="C94" s="107" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D94" s="104"/>
       <c r="E94" s="104"/>
@@ -24031,7 +24348,7 @@
     </row>
     <row r="95" spans="3:17">
       <c r="C95" s="107" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D95" s="104"/>
       <c r="E95" s="104"/>
@@ -24050,7 +24367,7 @@
     </row>
     <row r="96" spans="3:17">
       <c r="C96" s="107" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D96" s="104"/>
       <c r="E96" s="104"/>
@@ -24069,7 +24386,7 @@
     </row>
     <row r="97" spans="3:17">
       <c r="C97" s="107" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D97" s="104"/>
       <c r="E97" s="104"/>
@@ -24105,7 +24422,7 @@
     </row>
     <row r="99" spans="3:17">
       <c r="C99" s="110" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D99" s="104"/>
       <c r="E99" s="104"/>
@@ -24124,7 +24441,7 @@
     </row>
     <row r="100" spans="3:17">
       <c r="C100" s="110" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="D100" s="104"/>
       <c r="E100" s="104"/>
@@ -24160,7 +24477,7 @@
     </row>
     <row r="102" spans="3:17">
       <c r="C102" s="110" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D102" s="104"/>
       <c r="E102" s="104"/>
@@ -24179,7 +24496,7 @@
     </row>
     <row r="103" spans="3:17">
       <c r="C103" s="110" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D103" s="104"/>
       <c r="E103" s="104"/>
@@ -24215,7 +24532,7 @@
     </row>
     <row r="105" spans="3:17">
       <c r="C105" s="110" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="D105" s="104"/>
       <c r="E105" s="104"/>
@@ -24251,7 +24568,7 @@
     </row>
     <row r="107" spans="3:17">
       <c r="C107" s="109" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D107" s="104"/>
       <c r="E107" s="104"/>
@@ -24293,7 +24610,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E27"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -24305,118 +24622,118 @@
     </row>
     <row r="3" spans="2:5">
       <c r="C3" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="4" spans="2:5">
       <c r="D4" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="6" spans="2:5">
       <c r="D6" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="7" spans="2:5">
       <c r="E7" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="8" spans="2:5">
       <c r="E8" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="9" spans="2:5">
       <c r="E9" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="E10" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="C12" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="D13" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="D15" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="16" spans="2:5">
       <c r="E16" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="17" spans="2:5">
       <c r="E17" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="17" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C19" s="17"/>
     </row>
     <row r="20" spans="2:5">
       <c r="B20" s="17" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C20" s="17"/>
     </row>
     <row r="21" spans="2:5">
       <c r="C21" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="22" spans="2:5">
       <c r="D22" t="s">
+        <v>783</v>
+      </c>
+      <c r="E22" t="s">
         <v>784</v>
-      </c>
-      <c r="E22" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="23" spans="2:5">
       <c r="D23" t="s">
+        <v>785</v>
+      </c>
+      <c r="E23" t="s">
         <v>786</v>
-      </c>
-      <c r="E23" t="s">
-        <v>787</v>
       </c>
     </row>
     <row r="24" spans="2:5">
       <c r="D24" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E24" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="25" spans="2:5">
       <c r="C25" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="26" spans="2:5">
       <c r="C26" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="27" spans="2:5">
       <c r="B27" s="17" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
   </sheetData>
@@ -24425,7 +24742,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E37"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -24440,62 +24757,62 @@
     </row>
     <row r="3" spans="2:3">
       <c r="C3" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="C4" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="6" spans="2:3">
       <c r="C6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="8" spans="2:3">
       <c r="C8" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="9" spans="2:3">
       <c r="C9" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="11" spans="2:3">
       <c r="C11" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="12" spans="2:3">
       <c r="C12" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="14" spans="2:3">
       <c r="C14" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="15" spans="2:3">
       <c r="C15" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="16" spans="2:3">
       <c r="C16" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="17" spans="2:4">
       <c r="C17" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="18" spans="2:4">
       <c r="C18" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="19" spans="2:4">
@@ -24505,7 +24822,7 @@
     </row>
     <row r="22" spans="2:4">
       <c r="B22" s="6" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="23" spans="2:4">
@@ -24515,7 +24832,7 @@
     </row>
     <row r="24" spans="2:4">
       <c r="D24" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="25" spans="2:4">
@@ -24525,27 +24842,27 @@
     </row>
     <row r="26" spans="2:4">
       <c r="D26" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="28" spans="2:4">
       <c r="C28" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="29" spans="2:4">
       <c r="C29" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="30" spans="2:4">
       <c r="C30" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="31" spans="2:4">
       <c r="C31" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="32" spans="2:4">
@@ -24555,28 +24872,28 @@
     </row>
     <row r="34" spans="3:5">
       <c r="C34" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="35" spans="3:5">
       <c r="D35" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="E35" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="36" spans="3:5">
       <c r="D36" t="s">
+        <v>964</v>
+      </c>
+      <c r="E36" t="s">
         <v>965</v>
-      </c>
-      <c r="E36" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="37" spans="3:5">
       <c r="E37" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
   </sheetData>
@@ -24585,7 +24902,115 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:C31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="17.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3">
+      <c r="B2" s="79" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3">
+      <c r="C3" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3">
+      <c r="C4" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3">
+      <c r="C6" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3">
+      <c r="C8" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3">
+      <c r="C9" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3">
+      <c r="C11" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3">
+      <c r="C12" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3">
+      <c r="C13" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18" s="43" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="C19" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="C20" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="C22" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3">
+      <c r="C24" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3">
+      <c r="C25" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3">
+      <c r="C27" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3">
+      <c r="C28" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3">
+      <c r="C29" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3">
+      <c r="C31" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:F28"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -24595,122 +25020,122 @@
   <sheetData>
     <row r="2" spans="2:6">
       <c r="B2" s="6" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="3" spans="2:6">
       <c r="C3" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="4" spans="2:6">
       <c r="D4" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="5" spans="2:6">
       <c r="C5" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="6" spans="2:6">
       <c r="D6" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="8" spans="2:6">
       <c r="C8" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="9" spans="2:6">
       <c r="C9" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="F9" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="10" spans="2:6">
       <c r="C10" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="11" spans="2:6">
       <c r="C11" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="12" spans="2:6">
       <c r="C12" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="13" spans="2:6">
       <c r="C13" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="14" spans="2:6">
       <c r="C14" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="15" spans="2:6">
       <c r="C15" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="17" spans="2:5">
       <c r="B17" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="18" spans="2:5">
       <c r="C18" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="19" spans="2:5">
       <c r="D19" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E19" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="20" spans="2:5">
       <c r="E20" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="22" spans="2:5">
       <c r="D22" t="s">
+        <v>971</v>
+      </c>
+      <c r="E22" t="s">
         <v>972</v>
-      </c>
-      <c r="E22" t="s">
-        <v>973</v>
       </c>
     </row>
     <row r="23" spans="2:5">
       <c r="E23" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="24" spans="2:5">
-      <c r="E24" s="131"/>
+      <c r="E24" s="114"/>
     </row>
     <row r="25" spans="2:5">
-      <c r="E25" s="131"/>
+      <c r="E25" s="114"/>
     </row>
     <row r="26" spans="2:5">
-      <c r="E26" s="131"/>
+      <c r="E26" s="114"/>
     </row>
     <row r="27" spans="2:5">
-      <c r="E27" s="131"/>
+      <c r="E27" s="114"/>
     </row>
     <row r="28" spans="2:5">
-      <c r="E28" s="131"/>
+      <c r="E28" s="114"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -24718,146 +25143,151 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:F33"/>
+  <dimension ref="B2:F36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="3" spans="2:4">
       <c r="C3" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="D4" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="5" spans="2:4">
       <c r="C5" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="6" spans="2:4">
       <c r="D6" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="7" spans="2:4">
       <c r="D7" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="8" spans="2:4">
       <c r="D8" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="10" spans="2:4">
       <c r="D10" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="12" spans="2:4">
       <c r="D12" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="13" spans="2:4">
       <c r="D13" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="14" spans="2:4">
       <c r="D14" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="15" spans="2:4">
       <c r="D15" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="16" spans="2:4">
       <c r="D16" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="D18" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="20" spans="2:6">
       <c r="D20" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="22" spans="2:6">
       <c r="C22" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="23" spans="2:6">
       <c r="D23" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="D24" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F24" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="D25" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="F25" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="26" spans="2:6">
       <c r="D26" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E26" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="27" spans="2:6">
       <c r="D27" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="F27" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="31" spans="2:6">
       <c r="C31" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6">
-      <c r="C32" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3">
+      <c r="C34" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="35" spans="3:3">
+      <c r="C35" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="36" spans="3:3">
+      <c r="C36" t="s">
         <v>940</v>
-      </c>
-    </row>
-    <row r="33" spans="3:3">
-      <c r="C33" t="s">
-        <v>941</v>
       </c>
     </row>
   </sheetData>
@@ -24866,350 +25296,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:B39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="22.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:2">
-      <c r="B2" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2">
-      <c r="B3" s="11" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2">
-      <c r="B4" s="11" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2">
-      <c r="B5" s="11" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2">
-      <c r="B8" s="11" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2">
-      <c r="B9" s="12" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2">
-      <c r="B11" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2">
-      <c r="B12" s="80" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2">
-      <c r="B13" s="80" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2">
-      <c r="B14" s="80" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="16" spans="2:2">
-      <c r="B16" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2">
-      <c r="B17" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2">
-      <c r="B18" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2">
-      <c r="B20" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2">
-      <c r="B21" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2">
-      <c r="B24" s="11" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2">
-      <c r="B25" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2">
-      <c r="B27" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2">
-      <c r="B28" s="80" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2">
-      <c r="B29" s="11"/>
-    </row>
-    <row r="30" spans="2:2">
-      <c r="B30" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2">
-      <c r="B31" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2">
-      <c r="B32" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2">
-      <c r="B33" s="111" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2">
-      <c r="B35" s="11" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2">
-      <c r="B36" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2">
-      <c r="B37" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2">
-      <c r="B38" t="s">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2">
-      <c r="B39" s="80" t="s">
-        <v>869</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:O20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="2" spans="2:15">
-      <c r="B2" s="6" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="4" spans="2:15">
-      <c r="C4" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="5" spans="2:15">
-      <c r="C5" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15">
-      <c r="C6" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="8" spans="2:15">
-      <c r="F8" s="99" t="s">
-        <v>705</v>
-      </c>
-      <c r="L8" s="100" t="s">
-        <v>707</v>
-      </c>
-      <c r="M8" s="101"/>
-      <c r="N8" s="101"/>
-      <c r="O8" s="102"/>
-    </row>
-    <row r="9" spans="2:15">
-      <c r="F9" s="95" t="s">
-        <v>706</v>
-      </c>
-      <c r="G9" t="s">
-        <v>708</v>
-      </c>
-      <c r="L9" s="96" t="s">
-        <v>709</v>
-      </c>
-      <c r="M9" s="97"/>
-      <c r="N9" s="97"/>
-      <c r="O9" s="98"/>
-    </row>
-    <row r="11" spans="2:15">
-      <c r="E11" t="s">
-        <v>711</v>
-      </c>
-      <c r="L11" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="16" spans="2:15">
-      <c r="D16" t="s">
-        <v>713</v>
-      </c>
-      <c r="I16" s="125" t="s">
-        <v>717</v>
-      </c>
-      <c r="J16" s="126"/>
-    </row>
-    <row r="17" spans="3:10" ht="15" customHeight="1">
-      <c r="I17" s="127"/>
-      <c r="J17" s="128"/>
-    </row>
-    <row r="18" spans="3:10">
-      <c r="D18" t="s">
-        <v>714</v>
-      </c>
-      <c r="I18" s="129"/>
-      <c r="J18" s="130"/>
-    </row>
-    <row r="19" spans="3:10">
-      <c r="C19" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="20" spans="3:10">
-      <c r="D20" t="s">
-        <v>716</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="I16:J18"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:K18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="2" spans="2:11">
-      <c r="B2" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="3" spans="2:11">
-      <c r="B3" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11">
-      <c r="B4" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11">
-      <c r="B6" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11">
-      <c r="B7" t="s">
-        <v>837</v>
-      </c>
-      <c r="F7" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11">
-      <c r="B10" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11">
-      <c r="B11" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11">
-      <c r="B12" t="s">
-        <v>841</v>
-      </c>
-      <c r="K12" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11">
-      <c r="B13" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11">
-      <c r="B14" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="16" spans="2:11">
-      <c r="B16" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6">
-      <c r="B17" t="s">
-        <v>843</v>
-      </c>
-      <c r="F17" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6">
-      <c r="B18" t="s">
-        <v>844</v>
-      </c>
-      <c r="F18" t="s">
-        <v>846</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:G108"/>
+  <dimension ref="B1:G113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="62.85546875" customWidth="1"/>
@@ -25948,7 +26037,7 @@
         <v>287</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D49" s="51">
         <v>0.9</v>
@@ -25963,7 +26052,7 @@
         <v>319</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D50" s="42">
         <v>1</v>
@@ -25978,9 +26067,9 @@
         <v>320</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>710</v>
-      </c>
-      <c r="D51" s="132">
+        <v>709</v>
+      </c>
+      <c r="D51" s="115">
         <v>0.2</v>
       </c>
       <c r="E51" s="16" t="s">
@@ -25995,7 +26084,7 @@
         <v>11.1</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="D52" s="42">
         <v>1</v>
@@ -26010,7 +26099,7 @@
         <v>11.2</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="D53" s="42">
         <v>1</v>
@@ -26025,9 +26114,9 @@
         <v>11.3</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>896</v>
-      </c>
-      <c r="D54" s="132"/>
+        <v>895</v>
+      </c>
+      <c r="D54" s="115"/>
       <c r="E54" s="16"/>
       <c r="F54" s="16" t="s">
         <v>14</v>
@@ -26036,35 +26125,35 @@
     <row r="55" spans="2:6">
       <c r="B55" s="5"/>
       <c r="C55" s="7"/>
-      <c r="D55" s="132"/>
+      <c r="D55" s="115"/>
       <c r="E55" s="16"/>
       <c r="F55" s="16"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="5"/>
       <c r="C56" s="7"/>
-      <c r="D56" s="132"/>
+      <c r="D56" s="115"/>
       <c r="E56" s="16"/>
       <c r="F56" s="16"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="5"/>
       <c r="C57" s="7"/>
-      <c r="D57" s="132"/>
+      <c r="D57" s="115"/>
       <c r="E57" s="16"/>
       <c r="F57" s="16"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="5"/>
       <c r="C58" s="7"/>
-      <c r="D58" s="132"/>
+      <c r="D58" s="115"/>
       <c r="E58" s="16"/>
       <c r="F58" s="16"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="5"/>
       <c r="C59" s="7"/>
-      <c r="D59" s="132"/>
+      <c r="D59" s="115"/>
       <c r="E59" s="16"/>
       <c r="F59" s="16"/>
     </row>
@@ -26073,7 +26162,7 @@
         <v>321</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D60" s="42">
         <v>1</v>
@@ -26118,7 +26207,7 @@
         <v>446</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D63" s="42">
         <v>1</v>
@@ -26193,7 +26282,7 @@
         <v>16.399999999999999</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D68" s="42">
         <v>1</v>
@@ -26208,7 +26297,7 @@
         <v>16.5</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D69" s="42">
         <v>1</v>
@@ -26223,7 +26312,7 @@
         <v>16.600000000000001</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D70" s="42">
         <v>1</v>
@@ -26244,7 +26333,7 @@
         <v>1</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="F71" s="16" t="s">
         <v>14</v>
@@ -26255,13 +26344,13 @@
         <v>16.8</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="D72" s="42">
         <v>1</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="F72" s="16" t="s">
         <v>14</v>
@@ -26272,9 +26361,9 @@
         <v>16.899999999999999</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>897</v>
-      </c>
-      <c r="D73" s="132">
+        <v>896</v>
+      </c>
+      <c r="D73" s="115">
         <v>0</v>
       </c>
       <c r="E73" s="7"/>
@@ -26311,7 +26400,9 @@
       </c>
       <c r="D76" s="6"/>
       <c r="E76" s="6"/>
-      <c r="F76" s="6"/>
+      <c r="F76" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="77" spans="2:6" ht="50.25" customHeight="1">
       <c r="B77" s="5">
@@ -26341,7 +26432,7 @@
       <c r="B79" s="5">
         <v>17.5</v>
       </c>
-      <c r="C79" s="6" t="s">
+      <c r="C79" s="133" t="s">
         <v>454</v>
       </c>
       <c r="D79" s="6"/>
@@ -26359,12 +26450,12 @@
       <c r="E80" s="6"/>
       <c r="F80" s="6"/>
     </row>
-    <row r="81" spans="2:7" ht="30">
+    <row r="81" spans="2:6" ht="30">
       <c r="B81" s="5">
         <v>18.100000000000001</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="D81" s="51">
         <v>0</v>
@@ -26372,7 +26463,7 @@
       <c r="E81" s="6"/>
       <c r="F81" s="6"/>
     </row>
-    <row r="82" spans="2:7">
+    <row r="82" spans="2:6">
       <c r="B82" s="5">
         <v>18.2</v>
       </c>
@@ -26383,34 +26474,34 @@
       <c r="E82" s="6"/>
       <c r="F82" s="6"/>
     </row>
-    <row r="83" spans="2:7">
+    <row r="83" spans="2:6">
       <c r="B83" s="5">
         <v>18.3</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D83" s="6"/>
       <c r="E83" s="6"/>
       <c r="F83" s="6"/>
     </row>
-    <row r="84" spans="2:7">
+    <row r="84" spans="2:6">
       <c r="B84" s="5">
         <v>18.399999999999999</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D84" s="6"/>
       <c r="E84" s="6"/>
       <c r="F84" s="6"/>
     </row>
-    <row r="85" spans="2:7">
+    <row r="85" spans="2:6">
       <c r="B85" s="5" t="s">
         <v>460</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="D85" s="112">
         <v>0.9</v>
@@ -26420,7 +26511,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="86" spans="2:7">
+    <row r="86" spans="2:6">
       <c r="B86" s="5">
         <v>19.100000000000001</v>
       </c>
@@ -26435,12 +26526,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="87" spans="2:7">
+    <row r="87" spans="2:6">
       <c r="B87" s="5" t="s">
         <v>462</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="D87" s="42">
         <v>1</v>
@@ -26450,7 +26541,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="88" spans="2:7">
+    <row r="88" spans="2:6">
       <c r="B88" s="5" t="s">
         <v>463</v>
       </c>
@@ -26463,7 +26554,7 @@
       <c r="E88" s="6"/>
       <c r="F88" s="6"/>
     </row>
-    <row r="89" spans="2:7">
+    <row r="89" spans="2:6">
       <c r="B89" s="5">
         <v>21.1</v>
       </c>
@@ -26474,7 +26565,7 @@
       <c r="E89" s="6"/>
       <c r="F89" s="6"/>
     </row>
-    <row r="90" spans="2:7" ht="30">
+    <row r="90" spans="2:6" ht="30">
       <c r="B90" s="5">
         <v>21.2</v>
       </c>
@@ -26485,42 +26576,44 @@
       <c r="E90" s="6"/>
       <c r="F90" s="6"/>
     </row>
-    <row r="91" spans="2:7">
+    <row r="91" spans="2:6">
       <c r="B91" s="5" t="s">
         <v>464</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="D91" s="51">
-        <v>0.01</v>
+      <c r="D91" s="42">
+        <v>1</v>
       </c>
       <c r="E91" s="16" t="s">
         <v>465</v>
       </c>
-      <c r="F91" s="6"/>
-    </row>
-    <row r="92" spans="2:7" ht="30">
-      <c r="B92" s="5" t="s">
-        <v>466</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>728</v>
+      <c r="F91" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="92" spans="2:6">
+      <c r="B92" s="5">
+        <v>23.1</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>974</v>
       </c>
       <c r="D92" s="42">
         <v>1</v>
       </c>
-      <c r="E92" s="16" t="s">
-        <v>465</v>
-      </c>
-      <c r="F92" s="16"/>
-    </row>
-    <row r="93" spans="2:7">
+      <c r="E92" s="16"/>
+      <c r="F92" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="93" spans="2:6">
       <c r="B93" s="5">
-        <v>24.1</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>729</v>
+        <v>23.2</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>981</v>
       </c>
       <c r="D93" s="42">
         <v>1</v>
@@ -26530,43 +26623,42 @@
         <v>14</v>
       </c>
     </row>
-    <row r="94" spans="2:7">
+    <row r="94" spans="2:6">
       <c r="B94" s="5">
-        <v>24.2</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>773</v>
-      </c>
-      <c r="D94" s="42">
-        <v>1</v>
+        <v>23.3</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="D94" s="51">
+        <v>0.99</v>
       </c>
       <c r="E94" s="16"/>
       <c r="F94" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G94" s="48"/>
-    </row>
-    <row r="95" spans="2:7">
+    </row>
+    <row r="95" spans="2:6" ht="30">
       <c r="B95" s="5" t="s">
-        <v>473</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>936</v>
+        <v>466</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>727</v>
       </c>
       <c r="D95" s="42">
         <v>1</v>
       </c>
-      <c r="E95" s="16"/>
-      <c r="F95" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="96" spans="2:7">
-      <c r="B96" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>477</v>
+      <c r="E95" s="16" t="s">
+        <v>465</v>
+      </c>
+      <c r="F95" s="16"/>
+    </row>
+    <row r="96" spans="2:6">
+      <c r="B96" s="5">
+        <v>24.1</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>728</v>
       </c>
       <c r="D96" s="42">
         <v>1</v>
@@ -26578,10 +26670,10 @@
     </row>
     <row r="97" spans="2:7">
       <c r="B97" s="5">
-        <v>26.1</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>943</v>
+        <v>24.2</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>772</v>
       </c>
       <c r="D97" s="42">
         <v>1</v>
@@ -26590,26 +26682,29 @@
       <c r="F97" s="16" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="98" spans="2:7" ht="60">
+      <c r="G97" s="48"/>
+    </row>
+    <row r="98" spans="2:7">
       <c r="B98" s="5" t="s">
-        <v>484</v>
-      </c>
-      <c r="C98" s="79" t="s">
-        <v>480</v>
-      </c>
-      <c r="D98" s="6"/>
-      <c r="E98" s="16" t="s">
-        <v>481</v>
-      </c>
-      <c r="F98" s="6"/>
-    </row>
-    <row r="99" spans="2:7" ht="30">
+        <v>473</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="D98" s="42">
+        <v>1</v>
+      </c>
+      <c r="E98" s="16"/>
+      <c r="F98" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="99" spans="2:7">
       <c r="B99" s="5" t="s">
-        <v>485</v>
-      </c>
-      <c r="C99" s="7" t="s">
-        <v>944</v>
+        <v>475</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>477</v>
       </c>
       <c r="D99" s="42">
         <v>1</v>
@@ -26620,11 +26715,11 @@
       </c>
     </row>
     <row r="100" spans="2:7">
-      <c r="B100" s="5" t="s">
-        <v>486</v>
+      <c r="B100" s="5">
+        <v>26.1</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>810</v>
+        <v>942</v>
       </c>
       <c r="D100" s="42">
         <v>1</v>
@@ -26634,30 +26729,32 @@
         <v>14</v>
       </c>
     </row>
-    <row r="101" spans="2:7">
-      <c r="B101" s="5">
-        <v>29.1</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>937</v>
-      </c>
-      <c r="D101" s="42">
-        <v>1</v>
-      </c>
-      <c r="E101" s="16"/>
-      <c r="F101" s="16" t="s">
-        <v>14</v>
+    <row r="101" spans="2:7" ht="45">
+      <c r="B101" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="C101" s="79" t="s">
+        <v>998</v>
+      </c>
+      <c r="D101" s="51">
+        <v>0.5</v>
+      </c>
+      <c r="E101" s="16" t="s">
+        <v>480</v>
+      </c>
+      <c r="F101" s="6" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="102" spans="2:7">
-      <c r="B102" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="C102" s="7" t="s">
-        <v>807</v>
-      </c>
-      <c r="D102" s="42">
-        <v>1</v>
+      <c r="B102" s="5">
+        <v>27.1</v>
+      </c>
+      <c r="C102" s="79" t="s">
+        <v>996</v>
+      </c>
+      <c r="D102" s="51">
+        <v>0.99</v>
       </c>
       <c r="E102" s="16"/>
       <c r="F102" s="16" t="s">
@@ -26666,25 +26763,25 @@
     </row>
     <row r="103" spans="2:7">
       <c r="B103" s="5">
-        <v>30.1</v>
-      </c>
-      <c r="C103" s="7" t="s">
-        <v>804</v>
-      </c>
-      <c r="D103" s="42">
-        <v>1</v>
+        <v>27.2</v>
+      </c>
+      <c r="C103" s="79" t="s">
+        <v>997</v>
+      </c>
+      <c r="D103" s="51">
+        <v>0.99</v>
       </c>
       <c r="E103" s="16"/>
-      <c r="F103" s="16" t="s">
+      <c r="F103" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="104" spans="2:7">
-      <c r="B104" s="5">
-        <v>30.2</v>
+    <row r="104" spans="2:7" ht="30">
+      <c r="B104" s="5" t="s">
+        <v>484</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>805</v>
+        <v>943</v>
       </c>
       <c r="D104" s="42">
         <v>1</v>
@@ -26693,14 +26790,13 @@
       <c r="F104" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G104" s="48"/>
     </row>
     <row r="105" spans="2:7">
-      <c r="B105" s="5">
-        <v>30.3</v>
-      </c>
-      <c r="C105" s="7" t="s">
-        <v>806</v>
+      <c r="B105" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>809</v>
       </c>
       <c r="D105" s="42">
         <v>1</v>
@@ -26710,15 +26806,15 @@
         <v>14</v>
       </c>
     </row>
-    <row r="106" spans="2:7" ht="30">
-      <c r="B106" s="5" t="s">
-        <v>488</v>
-      </c>
-      <c r="C106" s="7" t="s">
-        <v>474</v>
-      </c>
-      <c r="D106" s="51">
-        <v>0.05</v>
+    <row r="106" spans="2:7">
+      <c r="B106" s="5">
+        <v>29.1</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>936</v>
+      </c>
+      <c r="D106" s="42">
+        <v>1</v>
       </c>
       <c r="E106" s="16"/>
       <c r="F106" s="16" t="s">
@@ -26727,10 +26823,10 @@
     </row>
     <row r="107" spans="2:7">
       <c r="B107" s="5" t="s">
-        <v>774</v>
+        <v>486</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>775</v>
+        <v>806</v>
       </c>
       <c r="D107" s="42">
         <v>1</v>
@@ -26741,17 +26837,93 @@
       </c>
     </row>
     <row r="108" spans="2:7">
-      <c r="B108" s="77" t="s">
+      <c r="B108" s="5">
+        <v>30.1</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>803</v>
+      </c>
+      <c r="D108" s="42">
+        <v>1</v>
+      </c>
+      <c r="E108" s="16"/>
+      <c r="F108" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="109" spans="2:7">
+      <c r="B109" s="5">
+        <v>30.2</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>804</v>
+      </c>
+      <c r="D109" s="42">
+        <v>1</v>
+      </c>
+      <c r="E109" s="16"/>
+      <c r="F109" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G109" s="48"/>
+    </row>
+    <row r="110" spans="2:7">
+      <c r="B110" s="5">
+        <v>30.3</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>805</v>
+      </c>
+      <c r="D110" s="42">
+        <v>1</v>
+      </c>
+      <c r="E110" s="16"/>
+      <c r="F110" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="111" spans="2:7" ht="30">
+      <c r="B111" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="D111" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="E111" s="16"/>
+      <c r="F111" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="112" spans="2:7">
+      <c r="B112" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>774</v>
+      </c>
+      <c r="D112" s="42">
+        <v>1</v>
+      </c>
+      <c r="E112" s="16"/>
+      <c r="F112" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="113" spans="2:6">
+      <c r="B113" s="77" t="s">
         <v>471</v>
       </c>
-      <c r="C108" s="57" t="s">
+      <c r="C113" s="57" t="s">
         <v>470</v>
       </c>
-      <c r="D108" s="1"/>
-      <c r="E108" s="49" t="s">
+      <c r="D113" s="1"/>
+      <c r="E113" s="49" t="s">
         <v>469</v>
       </c>
-      <c r="F108" s="1"/>
+      <c r="F113" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -26804,8 +26976,8 @@
     <hyperlink ref="E64" r:id="rId7"/>
     <hyperlink ref="E77" r:id="rId8"/>
     <hyperlink ref="E91" r:id="rId9"/>
-    <hyperlink ref="E92" r:id="rId10"/>
-    <hyperlink ref="E108" r:id="rId11"/>
+    <hyperlink ref="E95" r:id="rId10"/>
+    <hyperlink ref="E113" r:id="rId11"/>
     <hyperlink ref="F49" location="'#9'!B2" display="Link"/>
     <hyperlink ref="F60" location="'#12'!B2" display="Link"/>
     <hyperlink ref="F65" location="'#16'!B2" display="Link"/>
@@ -26818,19 +26990,19 @@
     <hyperlink ref="F63" location="'#15'!B2" display="Link"/>
     <hyperlink ref="F70" location="'#16'!B89" display="Link"/>
     <hyperlink ref="F71" location="'#16'!B10" display="Link"/>
-    <hyperlink ref="F106" location="'#31'!B2" display="Link"/>
-    <hyperlink ref="F93" location="'#24'!B2" display="Link"/>
-    <hyperlink ref="F94" location="'#24'!B2" display="Link"/>
-    <hyperlink ref="F94:G94" location="'#24'!B26" display="Link"/>
-    <hyperlink ref="F95" location="'#25'!B2" display="Link"/>
+    <hyperlink ref="F111" location="'#31'!B2" display="Link"/>
+    <hyperlink ref="F96" location="'#24'!B2" display="Link"/>
+    <hyperlink ref="F97" location="'#24'!B2" display="Link"/>
+    <hyperlink ref="F97:G97" location="'#24'!B26" display="Link"/>
+    <hyperlink ref="F98" location="'#25'!B2" display="Link"/>
     <hyperlink ref="F86" location="'#19'!B2" display="Link"/>
-    <hyperlink ref="F103" location="'#30'!B8" display="Link"/>
-    <hyperlink ref="F100" location="'#29'!B2" display="Link"/>
-    <hyperlink ref="F107" location="'#32'!B2" display="Link"/>
-    <hyperlink ref="F102" location="'#30'!B2" display="Link"/>
-    <hyperlink ref="F104" location="'#30'!B8" display="Link"/>
-    <hyperlink ref="F104:G104" location="'#30'!B24" display="Link"/>
-    <hyperlink ref="F105" location="'#30'!B35" display="Link"/>
+    <hyperlink ref="F108" location="'#30'!B8" display="Link"/>
+    <hyperlink ref="F105" location="'#29'!B2" display="Link"/>
+    <hyperlink ref="F112" location="'#32'!B2" display="Link"/>
+    <hyperlink ref="F107" location="'#30'!B2" display="Link"/>
+    <hyperlink ref="F109" location="'#30'!B8" display="Link"/>
+    <hyperlink ref="F109:G109" location="'#30'!B24" display="Link"/>
+    <hyperlink ref="F110" location="'#30'!B35" display="Link"/>
     <hyperlink ref="F51" location="'#11'!B2" display="Link"/>
     <hyperlink ref="F52" location="'#11'!B4" display="Link"/>
     <hyperlink ref="F53" location="'#11'!B21" display="Link"/>
@@ -26839,13 +27011,358 @@
     <hyperlink ref="F28" location="'#4'!B35" display="Link"/>
     <hyperlink ref="F29" location="'#4'!B43" display="Link"/>
     <hyperlink ref="F87" location="'#20'!B2" display="Link"/>
-    <hyperlink ref="F96" location="'#26'!B2" display="Link"/>
-    <hyperlink ref="F101" location="'#29'!B30" display="Link"/>
-    <hyperlink ref="F99" location="'#28'!B17" display="Link"/>
-    <hyperlink ref="F97" location="'#26'!B22" display="Link"/>
+    <hyperlink ref="F99" location="'#26'!B2" display="Link"/>
+    <hyperlink ref="F106" location="'#29'!B30" display="Link"/>
+    <hyperlink ref="F104" location="'#28'!B17" display="Link"/>
+    <hyperlink ref="F100" location="'#26'!B22" display="Link"/>
+    <hyperlink ref="F92" location="'#23'!B2" display="Link"/>
+    <hyperlink ref="F93" location="'#23'!B10" display="Link"/>
+    <hyperlink ref="F94" location="'#23'!B24" display="Link"/>
+    <hyperlink ref="F102" location="'#27'!B2" display="Link"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId12"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:B39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2">
+      <c r="B2" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
+      <c r="B3" s="11" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" s="11" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" s="11" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" s="11" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" s="12" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2">
+      <c r="B11" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" s="80" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2">
+      <c r="B13" s="80" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" s="80" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2">
+      <c r="B16" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" s="11" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" s="80" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" s="11"/>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="111" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="11" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="80" t="s">
+        <v>868</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:O20"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2" spans="2:15">
+      <c r="B2" s="6" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15">
+      <c r="C4" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15">
+      <c r="C5" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15">
+      <c r="C6" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15">
+      <c r="F8" s="99" t="s">
+        <v>704</v>
+      </c>
+      <c r="L8" s="100" t="s">
+        <v>706</v>
+      </c>
+      <c r="M8" s="101"/>
+      <c r="N8" s="101"/>
+      <c r="O8" s="102"/>
+    </row>
+    <row r="9" spans="2:15">
+      <c r="F9" s="95" t="s">
+        <v>705</v>
+      </c>
+      <c r="G9" t="s">
+        <v>707</v>
+      </c>
+      <c r="L9" s="96" t="s">
+        <v>708</v>
+      </c>
+      <c r="M9" s="97"/>
+      <c r="N9" s="97"/>
+      <c r="O9" s="98"/>
+    </row>
+    <row r="11" spans="2:15">
+      <c r="E11" t="s">
+        <v>710</v>
+      </c>
+      <c r="L11" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15">
+      <c r="D16" t="s">
+        <v>712</v>
+      </c>
+      <c r="I16" s="127" t="s">
+        <v>716</v>
+      </c>
+      <c r="J16" s="128"/>
+    </row>
+    <row r="17" spans="3:10" ht="15" customHeight="1">
+      <c r="I17" s="129"/>
+      <c r="J17" s="130"/>
+    </row>
+    <row r="18" spans="3:10">
+      <c r="D18" t="s">
+        <v>713</v>
+      </c>
+      <c r="I18" s="131"/>
+      <c r="J18" s="132"/>
+    </row>
+    <row r="19" spans="3:10">
+      <c r="C19" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="20" spans="3:10">
+      <c r="D20" t="s">
+        <v>715</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="I16:J18"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:K18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2" spans="2:11">
+      <c r="B2" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11">
+      <c r="B3" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11">
+      <c r="B4" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11">
+      <c r="B6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11">
+      <c r="B7" t="s">
+        <v>836</v>
+      </c>
+      <c r="F7" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11">
+      <c r="B10" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11">
+      <c r="B11" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11">
+      <c r="B12" t="s">
+        <v>840</v>
+      </c>
+      <c r="K12" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11">
+      <c r="B13" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11">
+      <c r="B14" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11">
+      <c r="B16" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" t="s">
+        <v>842</v>
+      </c>
+      <c r="F17" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18" t="s">
+        <v>843</v>
+      </c>
+      <c r="F18" t="s">
+        <v>845</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -27160,7 +27677,7 @@
       <c r="D12" s="11"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" thickBot="1">
-      <c r="C13" s="114" t="s">
+      <c r="C13" s="116" t="s">
         <v>78</v>
       </c>
       <c r="D13" s="26" t="s">
@@ -27177,7 +27694,7 @@
       <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:10" ht="15.75" thickBot="1">
-      <c r="C14" s="115"/>
+      <c r="C14" s="117"/>
       <c r="D14" s="23" t="s">
         <v>65</v>
       </c>
@@ -27193,7 +27710,7 @@
       <c r="J14" s="25"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="C15" s="115"/>
+      <c r="C15" s="117"/>
       <c r="D15" s="26" t="s">
         <v>66</v>
       </c>
@@ -27208,7 +27725,7 @@
       <c r="I15" s="28"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="C16" s="115"/>
+      <c r="C16" s="117"/>
       <c r="D16" s="29"/>
       <c r="E16" s="30" t="s">
         <v>74</v>
@@ -27219,7 +27736,7 @@
       <c r="I16" s="31"/>
     </row>
     <row r="17" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C17" s="116"/>
+      <c r="C17" s="118"/>
       <c r="D17" s="32"/>
       <c r="E17" s="33" t="s">
         <v>75</v>
@@ -27250,7 +27767,7 @@
       <c r="L18" s="25"/>
     </row>
     <row r="19" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C19" s="114" t="s">
+      <c r="C19" s="116" t="s">
         <v>78</v>
       </c>
       <c r="D19" s="23" t="s">
@@ -27261,7 +27778,7 @@
       </c>
     </row>
     <row r="20" spans="3:12">
-      <c r="C20" s="115"/>
+      <c r="C20" s="117"/>
       <c r="D20" s="26" t="s">
         <v>82</v>
       </c>
@@ -27270,7 +27787,7 @@
       </c>
     </row>
     <row r="21" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C21" s="116"/>
+      <c r="C21" s="118"/>
       <c r="D21" s="32"/>
       <c r="E21" s="40" t="s">
         <v>84</v>
@@ -28022,27 +28539,27 @@
     </row>
     <row r="36" spans="2:3">
       <c r="C36" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="37" spans="2:3">
       <c r="C37" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="39" spans="2:3">
       <c r="B39" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="40" spans="2:3">
       <c r="B40" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="41" spans="2:3">
       <c r="B41" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="43" spans="2:3">
@@ -28052,22 +28569,22 @@
     </row>
     <row r="44" spans="2:3">
       <c r="C44" s="50" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="45" spans="2:3">
       <c r="C45" s="50" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="47" spans="2:3">
       <c r="B47" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="48" spans="2:3">
       <c r="B48" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
   </sheetData>

--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -29,16 +29,17 @@
     <sheet name="#17" sheetId="32" r:id="rId20"/>
     <sheet name="#19" sheetId="22" r:id="rId21"/>
     <sheet name="#20" sheetId="27" r:id="rId22"/>
-    <sheet name="#23" sheetId="30" r:id="rId23"/>
-    <sheet name="#24" sheetId="20" r:id="rId24"/>
-    <sheet name="#25" sheetId="21" r:id="rId25"/>
-    <sheet name="#26" sheetId="28" r:id="rId26"/>
-    <sheet name="#27" sheetId="31" r:id="rId27"/>
-    <sheet name="#28" sheetId="29" r:id="rId28"/>
-    <sheet name="#29" sheetId="23" r:id="rId29"/>
-    <sheet name="#30" sheetId="24" r:id="rId30"/>
-    <sheet name="#31" sheetId="19" r:id="rId31"/>
-    <sheet name="#32" sheetId="25" r:id="rId32"/>
+    <sheet name="#21" sheetId="33" r:id="rId23"/>
+    <sheet name="#23" sheetId="30" r:id="rId24"/>
+    <sheet name="#24" sheetId="20" r:id="rId25"/>
+    <sheet name="#25" sheetId="21" r:id="rId26"/>
+    <sheet name="#26" sheetId="28" r:id="rId27"/>
+    <sheet name="#27" sheetId="31" r:id="rId28"/>
+    <sheet name="#28" sheetId="29" r:id="rId29"/>
+    <sheet name="#29" sheetId="23" r:id="rId30"/>
+    <sheet name="#30" sheetId="24" r:id="rId31"/>
+    <sheet name="#31" sheetId="19" r:id="rId32"/>
+    <sheet name="#32" sheetId="25" r:id="rId33"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="1017">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="1044">
   <si>
     <t>No.</t>
   </si>
@@ -13129,13 +13130,152 @@
   </si>
   <si>
     <t>#include &lt;algorithm&gt;</t>
+  </si>
+  <si>
+    <t>21.10</t>
+  </si>
+  <si>
+    <t>21.11</t>
+  </si>
+  <si>
+    <t>21.12</t>
+  </si>
+  <si>
+    <t>#33</t>
+  </si>
+  <si>
+    <t>Các loại thư viện</t>
+  </si>
+  <si>
+    <t>Shared Library</t>
+  </si>
+  <si>
+    <t>Static Library</t>
+  </si>
+  <si>
+    <t>Header-only Library</t>
+  </si>
+  <si>
+    <t>std::mutex mtx;</t>
+  </si>
+  <si>
+    <t>Khóa mutex</t>
+  </si>
+  <si>
+    <t>std::mutex mtx;  // Sẽ ra sao nếu chỉ lock mutex mà quên không unlock</t>
+  </si>
+  <si>
+    <t>Khái niệm : là một cơ chế giúp đảm bảo chỉ một thread được truy cập tài nguyên chung tại cùng một thời điểm.</t>
+  </si>
+  <si>
+    <t>// khai báo thư viện</t>
+  </si>
+  <si>
+    <t>// khai báo biến mutex là mtx</t>
+  </si>
+  <si>
+    <t>………</t>
+  </si>
+  <si>
+    <t>mtx.lock();</t>
+  </si>
+  <si>
+    <t>mtx.unlock();</t>
+  </si>
+  <si>
+    <t>// tài nguyên chung cần sửa</t>
+  </si>
+  <si>
+    <t>// dùng mutex để khóa</t>
+  </si>
+  <si>
+    <t>// dùng mutex để mở khóa</t>
+  </si>
+  <si>
+    <t>Sẽ ra sao nếu chỉ lock mutex mà quên không unlock</t>
+  </si>
+  <si>
+    <r>
+      <t>#include</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;mutex&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nếu hoạt động với nhiều thread, thread khác sẽ chờ đợi và không thể giữ được khóa mutex -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Deadlock</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">hoặc nếu gọi lần 2 về chính thread khóa mà lần 1 chưa unlock() -&gt; tự </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Deadlock</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mục đích sử dụng : để </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tránh race condition</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> khi có quá nhiều thread tranh nhau sửa tài nguyên dẫn đến hoạt động sai</t>
+    </r>
+  </si>
+  <si>
+    <t>race condition là gì</t>
+  </si>
+  <si>
+    <t>deadlock là gì ?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -13321,6 +13461,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -13735,7 +13883,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -13964,6 +14112,9 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -14015,9 +14166,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -21214,16 +21363,16 @@
       </c>
     </row>
     <row r="89" spans="2:9" ht="54" customHeight="1">
-      <c r="B89" s="119" t="s">
+      <c r="B89" s="120" t="s">
         <v>618</v>
       </c>
-      <c r="C89" s="120"/>
-      <c r="D89" s="120"/>
-      <c r="E89" s="120"/>
-      <c r="F89" s="120"/>
-      <c r="G89" s="120"/>
-      <c r="H89" s="120"/>
-      <c r="I89" s="120"/>
+      <c r="C89" s="121"/>
+      <c r="D89" s="121"/>
+      <c r="E89" s="121"/>
+      <c r="F89" s="121"/>
+      <c r="G89" s="121"/>
+      <c r="H89" s="121"/>
+      <c r="I89" s="121"/>
     </row>
     <row r="91" spans="2:9">
       <c r="B91" t="s">
@@ -22566,11 +22715,11 @@
     </row>
     <row r="3" spans="2:7" ht="15.75" thickBot="1"/>
     <row r="4" spans="2:7">
-      <c r="C4" s="121" t="s">
+      <c r="C4" s="122" t="s">
         <v>914</v>
       </c>
-      <c r="D4" s="122"/>
-      <c r="E4" s="123"/>
+      <c r="D4" s="123"/>
+      <c r="E4" s="124"/>
       <c r="F4" t="s">
         <v>918</v>
       </c>
@@ -22579,9 +22728,9 @@
       </c>
     </row>
     <row r="5" spans="2:7" ht="15.75" thickBot="1">
-      <c r="C5" s="124"/>
-      <c r="D5" s="125"/>
-      <c r="E5" s="126"/>
+      <c r="C5" s="125"/>
+      <c r="D5" s="126"/>
+      <c r="E5" s="127"/>
       <c r="F5" t="s">
         <v>920</v>
       </c>
@@ -22590,11 +22739,11 @@
       </c>
     </row>
     <row r="6" spans="2:7">
-      <c r="C6" s="121" t="s">
+      <c r="C6" s="122" t="s">
         <v>915</v>
       </c>
-      <c r="D6" s="122"/>
-      <c r="E6" s="123"/>
+      <c r="D6" s="123"/>
+      <c r="E6" s="124"/>
       <c r="F6" t="s">
         <v>918</v>
       </c>
@@ -22603,9 +22752,9 @@
       </c>
     </row>
     <row r="7" spans="2:7" ht="15.75" thickBot="1">
-      <c r="C7" s="124"/>
-      <c r="D7" s="125"/>
-      <c r="E7" s="126"/>
+      <c r="C7" s="125"/>
+      <c r="D7" s="126"/>
+      <c r="E7" s="127"/>
       <c r="F7" t="s">
         <v>920</v>
       </c>
@@ -22614,11 +22763,11 @@
       </c>
     </row>
     <row r="8" spans="2:7">
-      <c r="C8" s="121" t="s">
+      <c r="C8" s="122" t="s">
         <v>916</v>
       </c>
-      <c r="D8" s="122"/>
-      <c r="E8" s="123"/>
+      <c r="D8" s="123"/>
+      <c r="E8" s="124"/>
       <c r="F8" t="s">
         <v>918</v>
       </c>
@@ -22627,9 +22776,9 @@
       </c>
     </row>
     <row r="9" spans="2:7" ht="15.75" thickBot="1">
-      <c r="C9" s="124"/>
-      <c r="D9" s="125"/>
-      <c r="E9" s="126"/>
+      <c r="C9" s="125"/>
+      <c r="D9" s="126"/>
+      <c r="E9" s="127"/>
       <c r="F9" t="s">
         <v>920</v>
       </c>
@@ -22638,11 +22787,11 @@
       </c>
     </row>
     <row r="10" spans="2:7">
-      <c r="C10" s="121" t="s">
+      <c r="C10" s="122" t="s">
         <v>917</v>
       </c>
-      <c r="D10" s="122"/>
-      <c r="E10" s="123"/>
+      <c r="D10" s="123"/>
+      <c r="E10" s="124"/>
       <c r="F10" t="s">
         <v>918</v>
       </c>
@@ -22651,9 +22800,9 @@
       </c>
     </row>
     <row r="11" spans="2:7" ht="15.75" thickBot="1">
-      <c r="C11" s="124"/>
-      <c r="D11" s="125"/>
-      <c r="E11" s="126"/>
+      <c r="C11" s="125"/>
+      <c r="D11" s="126"/>
+      <c r="E11" s="127"/>
       <c r="F11" t="s">
         <v>920</v>
       </c>
@@ -22674,129 +22823,84 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:L30"/>
+  <dimension ref="B2:E20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="2" spans="2:12">
-      <c r="B2" s="6" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12">
+    <row r="2" spans="2:5">
+      <c r="B2" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5">
       <c r="C3" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12">
-      <c r="D4" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12">
-      <c r="C6" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12">
-      <c r="D7" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12">
-      <c r="D8" t="s">
-        <v>979</v>
-      </c>
-      <c r="L8" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12">
-      <c r="B10" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12">
-      <c r="C11" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12">
-      <c r="D12" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5">
+      <c r="C5" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5">
+      <c r="C7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
+      <c r="C8" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5">
+      <c r="C10" s="17" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5">
+      <c r="C12" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5">
+      <c r="C13" s="17" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5">
       <c r="C14" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12">
-      <c r="D15" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12">
-      <c r="D16" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6">
-      <c r="D17" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6">
-      <c r="D19" t="s">
-        <v>986</v>
-      </c>
-      <c r="F19" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6">
-      <c r="D20" t="s">
-        <v>988</v>
-      </c>
-      <c r="F20" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6">
-      <c r="D21" t="s">
-        <v>990</v>
-      </c>
-      <c r="F21" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6">
-      <c r="B24" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6">
-      <c r="C25" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6">
-      <c r="D26" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6">
-      <c r="D27" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6">
-      <c r="C29" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6">
-      <c r="D30" t="s">
-        <v>995</v>
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5">
+      <c r="C15" s="17" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18" s="134" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="C19" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="C20" t="s">
+        <v>1040</v>
       </c>
     </row>
   </sheetData>
@@ -22806,6 +22910,139 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:L30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2" spans="2:12">
+      <c r="B2" s="6" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12">
+      <c r="C3" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12">
+      <c r="D4" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12">
+      <c r="C6" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12">
+      <c r="D7" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12">
+      <c r="D8" t="s">
+        <v>979</v>
+      </c>
+      <c r="L8" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12">
+      <c r="B10" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12">
+      <c r="C11" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12">
+      <c r="D12" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12">
+      <c r="C14" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12">
+      <c r="D15" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12">
+      <c r="D16" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="D17" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6">
+      <c r="D19" t="s">
+        <v>986</v>
+      </c>
+      <c r="F19" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="D20" t="s">
+        <v>988</v>
+      </c>
+      <c r="F20" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="D21" t="s">
+        <v>990</v>
+      </c>
+      <c r="F21" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="C25" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="D26" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="D27" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="C29" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="D30" t="s">
+        <v>995</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Q108"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -24610,7 +24847,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E27"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -24742,7 +24979,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E37"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -24902,7 +25139,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:C31"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -25010,7 +25247,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:F28"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -25143,162 +25380,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:F36"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="2" spans="2:4">
-      <c r="B2" s="6" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4">
-      <c r="C3" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4">
-      <c r="D4" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4">
-      <c r="C5" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4">
-      <c r="D6" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4">
-      <c r="D7" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4">
-      <c r="D8" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4">
-      <c r="D10" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4">
-      <c r="D12" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4">
-      <c r="D13" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4">
-      <c r="D14" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4">
-      <c r="D15" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4">
-      <c r="D16" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6">
-      <c r="D18" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6">
-      <c r="D20" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6">
-      <c r="C22" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6">
-      <c r="D23" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6">
-      <c r="D24" t="s">
-        <v>831</v>
-      </c>
-      <c r="F24" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6">
-      <c r="D25" t="s">
-        <v>830</v>
-      </c>
-      <c r="F25" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6">
-      <c r="D26" t="s">
-        <v>829</v>
-      </c>
-      <c r="E26" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6">
-      <c r="D27" t="s">
-        <v>937</v>
-      </c>
-      <c r="F27" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6">
-      <c r="B30" t="s">
-        <v>938</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6">
-      <c r="C31" t="s">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="34" spans="3:3">
-      <c r="C34" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="35" spans="3:3">
-      <c r="C35" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="36" spans="3:3">
-      <c r="C36" t="s">
-        <v>940</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:G113"/>
+  <dimension ref="B1:G128"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="62.85546875" customWidth="1"/>
@@ -26432,7 +26516,7 @@
       <c r="B79" s="5">
         <v>17.5</v>
       </c>
-      <c r="C79" s="133" t="s">
+      <c r="C79" s="116" t="s">
         <v>454</v>
       </c>
       <c r="D79" s="6"/>
@@ -26552,195 +26636,144 @@
         <v>0</v>
       </c>
       <c r="E88" s="6"/>
-      <c r="F88" s="6"/>
+      <c r="F88" s="43" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="89" spans="2:6">
       <c r="B89" s="5">
         <v>21.1</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>432</v>
-      </c>
-      <c r="D89" s="6"/>
+        <v>1027</v>
+      </c>
+      <c r="D89" s="51">
+        <v>0</v>
+      </c>
       <c r="E89" s="6"/>
-      <c r="F89" s="6"/>
-    </row>
-    <row r="90" spans="2:6" ht="30">
+      <c r="F89" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6">
       <c r="B90" s="5">
         <v>21.2</v>
       </c>
-      <c r="C90" s="7" t="s">
-        <v>468</v>
-      </c>
-      <c r="D90" s="6"/>
+      <c r="C90" s="6" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D90" s="51"/>
       <c r="E90" s="6"/>
       <c r="F90" s="6"/>
     </row>
     <row r="91" spans="2:6">
-      <c r="B91" s="5" t="s">
-        <v>464</v>
+      <c r="B91" s="5">
+        <v>21.3</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="D91" s="42">
-        <v>1</v>
-      </c>
-      <c r="E91" s="16" t="s">
-        <v>465</v>
-      </c>
-      <c r="F91" s="6" t="s">
-        <v>121</v>
-      </c>
+        <v>1043</v>
+      </c>
+      <c r="D91" s="51"/>
+      <c r="E91" s="6"/>
+      <c r="F91" s="6"/>
     </row>
     <row r="92" spans="2:6">
       <c r="B92" s="5">
-        <v>23.1</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>974</v>
-      </c>
-      <c r="D92" s="42">
-        <v>1</v>
-      </c>
-      <c r="E92" s="16"/>
-      <c r="F92" s="16" t="s">
-        <v>14</v>
-      </c>
+        <v>21.4</v>
+      </c>
+      <c r="C92" s="6"/>
+      <c r="D92" s="51"/>
+      <c r="E92" s="6"/>
+      <c r="F92" s="6"/>
     </row>
     <row r="93" spans="2:6">
       <c r="B93" s="5">
-        <v>23.2</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>981</v>
-      </c>
-      <c r="D93" s="42">
-        <v>1</v>
-      </c>
-      <c r="E93" s="16"/>
-      <c r="F93" s="16" t="s">
-        <v>14</v>
-      </c>
+        <v>21.5</v>
+      </c>
+      <c r="C93" s="6"/>
+      <c r="D93" s="51"/>
+      <c r="E93" s="6"/>
+      <c r="F93" s="6"/>
     </row>
     <row r="94" spans="2:6">
       <c r="B94" s="5">
-        <v>23.3</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>992</v>
-      </c>
-      <c r="D94" s="51">
-        <v>0.99</v>
-      </c>
-      <c r="E94" s="16"/>
-      <c r="F94" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="95" spans="2:6" ht="30">
-      <c r="B95" s="5" t="s">
-        <v>466</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>727</v>
-      </c>
-      <c r="D95" s="42">
-        <v>1</v>
-      </c>
-      <c r="E95" s="16" t="s">
-        <v>465</v>
-      </c>
-      <c r="F95" s="16"/>
+        <v>21.6</v>
+      </c>
+      <c r="C94" s="6"/>
+      <c r="D94" s="51"/>
+      <c r="E94" s="6"/>
+      <c r="F94" s="6"/>
+    </row>
+    <row r="95" spans="2:6">
+      <c r="B95" s="5">
+        <v>21.7</v>
+      </c>
+      <c r="C95" s="6"/>
+      <c r="D95" s="51"/>
+      <c r="E95" s="6"/>
+      <c r="F95" s="6"/>
     </row>
     <row r="96" spans="2:6">
       <c r="B96" s="5">
-        <v>24.1</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>728</v>
-      </c>
-      <c r="D96" s="42">
-        <v>1</v>
-      </c>
-      <c r="E96" s="16"/>
-      <c r="F96" s="16" t="s">
-        <v>14</v>
-      </c>
+        <v>21.8</v>
+      </c>
+      <c r="C96" s="6"/>
+      <c r="D96" s="51"/>
+      <c r="E96" s="6"/>
+      <c r="F96" s="6"/>
     </row>
     <row r="97" spans="2:7">
       <c r="B97" s="5">
-        <v>24.2</v>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>772</v>
-      </c>
-      <c r="D97" s="42">
+        <v>21.9</v>
+      </c>
+      <c r="C97" s="6"/>
+      <c r="D97" s="51"/>
+      <c r="E97" s="6"/>
+      <c r="F97" s="6"/>
+    </row>
+    <row r="98" spans="2:7">
+      <c r="B98" s="52" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C98" s="6"/>
+      <c r="D98" s="51"/>
+      <c r="E98" s="6"/>
+      <c r="F98" s="6"/>
+    </row>
+    <row r="99" spans="2:7">
+      <c r="B99" s="52" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="D99" s="6"/>
+      <c r="E99" s="6"/>
+      <c r="F99" s="6"/>
+    </row>
+    <row r="100" spans="2:7" ht="30">
+      <c r="B100" s="52" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="D100" s="6"/>
+      <c r="E100" s="6"/>
+      <c r="F100" s="6"/>
+    </row>
+    <row r="101" spans="2:7">
+      <c r="B101" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="D101" s="42">
         <v>1</v>
       </c>
-      <c r="E97" s="16"/>
-      <c r="F97" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G97" s="48"/>
-    </row>
-    <row r="98" spans="2:7">
-      <c r="B98" s="5" t="s">
-        <v>473</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>935</v>
-      </c>
-      <c r="D98" s="42">
-        <v>1</v>
-      </c>
-      <c r="E98" s="16"/>
-      <c r="F98" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="99" spans="2:7">
-      <c r="B99" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="C99" s="6" t="s">
-        <v>477</v>
-      </c>
-      <c r="D99" s="42">
-        <v>1</v>
-      </c>
-      <c r="E99" s="16"/>
-      <c r="F99" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="100" spans="2:7">
-      <c r="B100" s="5">
-        <v>26.1</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>942</v>
-      </c>
-      <c r="D100" s="42">
-        <v>1</v>
-      </c>
-      <c r="E100" s="16"/>
-      <c r="F100" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="101" spans="2:7" ht="45">
-      <c r="B101" s="5" t="s">
-        <v>483</v>
-      </c>
-      <c r="C101" s="79" t="s">
-        <v>998</v>
-      </c>
-      <c r="D101" s="51">
-        <v>0.5</v>
-      </c>
       <c r="E101" s="16" t="s">
-        <v>480</v>
+        <v>465</v>
       </c>
       <c r="F101" s="6" t="s">
         <v>121</v>
@@ -26748,13 +26781,13 @@
     </row>
     <row r="102" spans="2:7">
       <c r="B102" s="5">
-        <v>27.1</v>
-      </c>
-      <c r="C102" s="79" t="s">
-        <v>996</v>
-      </c>
-      <c r="D102" s="51">
-        <v>0.99</v>
+        <v>23.1</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>974</v>
+      </c>
+      <c r="D102" s="42">
+        <v>1</v>
       </c>
       <c r="E102" s="16"/>
       <c r="F102" s="16" t="s">
@@ -26763,55 +26796,55 @@
     </row>
     <row r="103" spans="2:7">
       <c r="B103" s="5">
-        <v>27.2</v>
-      </c>
-      <c r="C103" s="79" t="s">
-        <v>997</v>
-      </c>
-      <c r="D103" s="51">
+        <v>23.2</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="D103" s="42">
+        <v>1</v>
+      </c>
+      <c r="E103" s="16"/>
+      <c r="F103" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7">
+      <c r="B104" s="5">
+        <v>23.3</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="D104" s="51">
         <v>0.99</v>
-      </c>
-      <c r="E103" s="16"/>
-      <c r="F103" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="104" spans="2:7" ht="30">
-      <c r="B104" s="5" t="s">
-        <v>484</v>
-      </c>
-      <c r="C104" s="7" t="s">
-        <v>943</v>
-      </c>
-      <c r="D104" s="42">
-        <v>1</v>
       </c>
       <c r="E104" s="16"/>
       <c r="F104" s="16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="105" spans="2:7">
+    <row r="105" spans="2:7" ht="30">
       <c r="B105" s="5" t="s">
-        <v>485</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>809</v>
+        <v>466</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>727</v>
       </c>
       <c r="D105" s="42">
         <v>1</v>
       </c>
-      <c r="E105" s="16"/>
-      <c r="F105" s="16" t="s">
-        <v>14</v>
-      </c>
+      <c r="E105" s="16" t="s">
+        <v>465</v>
+      </c>
+      <c r="F105" s="16"/>
     </row>
     <row r="106" spans="2:7">
       <c r="B106" s="5">
-        <v>29.1</v>
-      </c>
-      <c r="C106" s="6" t="s">
-        <v>936</v>
+        <v>24.1</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>728</v>
       </c>
       <c r="D106" s="42">
         <v>1</v>
@@ -26822,11 +26855,11 @@
       </c>
     </row>
     <row r="107" spans="2:7">
-      <c r="B107" s="5" t="s">
-        <v>486</v>
+      <c r="B107" s="5">
+        <v>24.2</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>806</v>
+        <v>772</v>
       </c>
       <c r="D107" s="42">
         <v>1</v>
@@ -26835,13 +26868,14 @@
       <c r="F107" s="16" t="s">
         <v>14</v>
       </c>
+      <c r="G107" s="48"/>
     </row>
     <row r="108" spans="2:7">
-      <c r="B108" s="5">
-        <v>30.1</v>
-      </c>
-      <c r="C108" s="7" t="s">
-        <v>803</v>
+      <c r="B108" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>935</v>
       </c>
       <c r="D108" s="42">
         <v>1</v>
@@ -26852,11 +26886,11 @@
       </c>
     </row>
     <row r="109" spans="2:7">
-      <c r="B109" s="5">
-        <v>30.2</v>
-      </c>
-      <c r="C109" s="7" t="s">
-        <v>804</v>
+      <c r="B109" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>477</v>
       </c>
       <c r="D109" s="42">
         <v>1</v>
@@ -26865,14 +26899,13 @@
       <c r="F109" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G109" s="48"/>
     </row>
     <row r="110" spans="2:7">
       <c r="B110" s="5">
-        <v>30.3</v>
-      </c>
-      <c r="C110" s="7" t="s">
-        <v>805</v>
+        <v>26.1</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>942</v>
       </c>
       <c r="D110" s="42">
         <v>1</v>
@@ -26882,48 +26915,246 @@
         <v>14</v>
       </c>
     </row>
-    <row r="111" spans="2:7" ht="30">
+    <row r="111" spans="2:7" ht="45">
       <c r="B111" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="C111" s="7" t="s">
-        <v>474</v>
+        <v>483</v>
+      </c>
+      <c r="C111" s="79" t="s">
+        <v>998</v>
       </c>
       <c r="D111" s="51">
-        <v>0.05</v>
-      </c>
-      <c r="E111" s="16"/>
-      <c r="F111" s="16" t="s">
-        <v>14</v>
+        <v>0.5</v>
+      </c>
+      <c r="E111" s="16" t="s">
+        <v>480</v>
+      </c>
+      <c r="F111" s="6" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="112" spans="2:7">
-      <c r="B112" s="5" t="s">
-        <v>773</v>
-      </c>
-      <c r="C112" s="7" t="s">
-        <v>774</v>
-      </c>
-      <c r="D112" s="42">
-        <v>1</v>
+      <c r="B112" s="5">
+        <v>27.1</v>
+      </c>
+      <c r="C112" s="79" t="s">
+        <v>996</v>
+      </c>
+      <c r="D112" s="51">
+        <v>0.99</v>
       </c>
       <c r="E112" s="16"/>
       <c r="F112" s="16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="113" spans="2:6">
-      <c r="B113" s="77" t="s">
+    <row r="113" spans="2:7">
+      <c r="B113" s="5">
+        <v>27.2</v>
+      </c>
+      <c r="C113" s="79" t="s">
+        <v>997</v>
+      </c>
+      <c r="D113" s="51">
+        <v>0.99</v>
+      </c>
+      <c r="E113" s="16"/>
+      <c r="F113" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="114" spans="2:7" ht="30">
+      <c r="B114" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>943</v>
+      </c>
+      <c r="D114" s="42">
+        <v>1</v>
+      </c>
+      <c r="E114" s="16"/>
+      <c r="F114" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="115" spans="2:7">
+      <c r="B115" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>809</v>
+      </c>
+      <c r="D115" s="42">
+        <v>1</v>
+      </c>
+      <c r="E115" s="16"/>
+      <c r="F115" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="116" spans="2:7">
+      <c r="B116" s="5">
+        <v>29.1</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>936</v>
+      </c>
+      <c r="D116" s="42">
+        <v>1</v>
+      </c>
+      <c r="E116" s="16"/>
+      <c r="F116" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="117" spans="2:7">
+      <c r="B117" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>806</v>
+      </c>
+      <c r="D117" s="42">
+        <v>1</v>
+      </c>
+      <c r="E117" s="16"/>
+      <c r="F117" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="118" spans="2:7">
+      <c r="B118" s="5">
+        <v>30.1</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>803</v>
+      </c>
+      <c r="D118" s="42">
+        <v>1</v>
+      </c>
+      <c r="E118" s="16"/>
+      <c r="F118" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="119" spans="2:7">
+      <c r="B119" s="5">
+        <v>30.2</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>804</v>
+      </c>
+      <c r="D119" s="42">
+        <v>1</v>
+      </c>
+      <c r="E119" s="16"/>
+      <c r="F119" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G119" s="48"/>
+    </row>
+    <row r="120" spans="2:7">
+      <c r="B120" s="5">
+        <v>30.3</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>805</v>
+      </c>
+      <c r="D120" s="42">
+        <v>1</v>
+      </c>
+      <c r="E120" s="16"/>
+      <c r="F120" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="121" spans="2:7" ht="30">
+      <c r="B121" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="C121" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="D121" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="E121" s="16"/>
+      <c r="F121" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="122" spans="2:7">
+      <c r="B122" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>774</v>
+      </c>
+      <c r="D122" s="42">
+        <v>1</v>
+      </c>
+      <c r="E122" s="16"/>
+      <c r="F122" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="123" spans="2:7">
+      <c r="B123" s="5" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C123" s="7" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D123" s="42"/>
+      <c r="E123" s="16"/>
+      <c r="F123" s="16"/>
+    </row>
+    <row r="124" spans="2:7">
+      <c r="B124" s="5"/>
+      <c r="C124" s="7" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D124" s="42"/>
+      <c r="E124" s="16"/>
+      <c r="F124" s="16"/>
+    </row>
+    <row r="125" spans="2:7">
+      <c r="B125" s="5"/>
+      <c r="C125" s="7" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D125" s="42"/>
+      <c r="E125" s="16"/>
+      <c r="F125" s="16"/>
+    </row>
+    <row r="126" spans="2:7">
+      <c r="B126" s="5"/>
+      <c r="C126" s="7" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D126" s="42"/>
+      <c r="E126" s="16"/>
+      <c r="F126" s="16"/>
+    </row>
+    <row r="127" spans="2:7">
+      <c r="B127" s="5"/>
+      <c r="C127" s="7"/>
+      <c r="D127" s="42"/>
+      <c r="E127" s="16"/>
+      <c r="F127" s="16"/>
+    </row>
+    <row r="128" spans="2:7">
+      <c r="B128" s="77" t="s">
         <v>471</v>
       </c>
-      <c r="C113" s="57" t="s">
+      <c r="C128" s="57" t="s">
         <v>470</v>
       </c>
-      <c r="D113" s="1"/>
-      <c r="E113" s="49" t="s">
+      <c r="D128" s="1"/>
+      <c r="E128" s="49" t="s">
         <v>469</v>
       </c>
-      <c r="F113" s="1"/>
+      <c r="F128" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -26975,9 +27206,9 @@
     <hyperlink ref="F62" location="'#14'!B2" display="Link"/>
     <hyperlink ref="E64" r:id="rId7"/>
     <hyperlink ref="E77" r:id="rId8"/>
-    <hyperlink ref="E91" r:id="rId9"/>
-    <hyperlink ref="E95" r:id="rId10"/>
-    <hyperlink ref="E113" r:id="rId11"/>
+    <hyperlink ref="E101" r:id="rId9"/>
+    <hyperlink ref="E105" r:id="rId10"/>
+    <hyperlink ref="E128" r:id="rId11"/>
     <hyperlink ref="F49" location="'#9'!B2" display="Link"/>
     <hyperlink ref="F60" location="'#12'!B2" display="Link"/>
     <hyperlink ref="F65" location="'#16'!B2" display="Link"/>
@@ -26990,19 +27221,19 @@
     <hyperlink ref="F63" location="'#15'!B2" display="Link"/>
     <hyperlink ref="F70" location="'#16'!B89" display="Link"/>
     <hyperlink ref="F71" location="'#16'!B10" display="Link"/>
-    <hyperlink ref="F111" location="'#31'!B2" display="Link"/>
-    <hyperlink ref="F96" location="'#24'!B2" display="Link"/>
-    <hyperlink ref="F97" location="'#24'!B2" display="Link"/>
-    <hyperlink ref="F97:G97" location="'#24'!B26" display="Link"/>
-    <hyperlink ref="F98" location="'#25'!B2" display="Link"/>
+    <hyperlink ref="F121" location="'#31'!B2" display="Link"/>
+    <hyperlink ref="F106" location="'#24'!B2" display="Link"/>
+    <hyperlink ref="F107" location="'#24'!B2" display="Link"/>
+    <hyperlink ref="F107:G107" location="'#24'!B26" display="Link"/>
+    <hyperlink ref="F108" location="'#25'!B2" display="Link"/>
     <hyperlink ref="F86" location="'#19'!B2" display="Link"/>
-    <hyperlink ref="F108" location="'#30'!B8" display="Link"/>
-    <hyperlink ref="F105" location="'#29'!B2" display="Link"/>
-    <hyperlink ref="F112" location="'#32'!B2" display="Link"/>
-    <hyperlink ref="F107" location="'#30'!B2" display="Link"/>
-    <hyperlink ref="F109" location="'#30'!B8" display="Link"/>
-    <hyperlink ref="F109:G109" location="'#30'!B24" display="Link"/>
-    <hyperlink ref="F110" location="'#30'!B35" display="Link"/>
+    <hyperlink ref="F118" location="'#30'!B8" display="Link"/>
+    <hyperlink ref="F115" location="'#29'!B2" display="Link"/>
+    <hyperlink ref="F122" location="'#32'!B2" display="Link"/>
+    <hyperlink ref="F117" location="'#30'!B2" display="Link"/>
+    <hyperlink ref="F119" location="'#30'!B8" display="Link"/>
+    <hyperlink ref="F119:G119" location="'#30'!B24" display="Link"/>
+    <hyperlink ref="F120" location="'#30'!B35" display="Link"/>
     <hyperlink ref="F51" location="'#11'!B2" display="Link"/>
     <hyperlink ref="F52" location="'#11'!B4" display="Link"/>
     <hyperlink ref="F53" location="'#11'!B21" display="Link"/>
@@ -27011,14 +27242,16 @@
     <hyperlink ref="F28" location="'#4'!B35" display="Link"/>
     <hyperlink ref="F29" location="'#4'!B43" display="Link"/>
     <hyperlink ref="F87" location="'#20'!B2" display="Link"/>
-    <hyperlink ref="F99" location="'#26'!B2" display="Link"/>
-    <hyperlink ref="F106" location="'#29'!B30" display="Link"/>
-    <hyperlink ref="F104" location="'#28'!B17" display="Link"/>
-    <hyperlink ref="F100" location="'#26'!B22" display="Link"/>
-    <hyperlink ref="F92" location="'#23'!B2" display="Link"/>
-    <hyperlink ref="F93" location="'#23'!B10" display="Link"/>
-    <hyperlink ref="F94" location="'#23'!B24" display="Link"/>
-    <hyperlink ref="F102" location="'#27'!B2" display="Link"/>
+    <hyperlink ref="F109" location="'#26'!B2" display="Link"/>
+    <hyperlink ref="F116" location="'#29'!B30" display="Link"/>
+    <hyperlink ref="F114" location="'#28'!B17" display="Link"/>
+    <hyperlink ref="F110" location="'#26'!B22" display="Link"/>
+    <hyperlink ref="F102" location="'#23'!B2" display="Link"/>
+    <hyperlink ref="F103" location="'#23'!B10" display="Link"/>
+    <hyperlink ref="F104" location="'#23'!B24" display="Link"/>
+    <hyperlink ref="F112" location="'#27'!B2" display="Link"/>
+    <hyperlink ref="F113" location="'#27'!B18" display="Link"/>
+    <hyperlink ref="F89" location="'#21'!B2" display="Link"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId12"/>
@@ -27026,6 +27259,159 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:F36"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2" spans="2:4">
+      <c r="B2" s="6" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4">
+      <c r="C3" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="D4" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
+      <c r="C5" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
+      <c r="D6" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4">
+      <c r="D7" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="D8" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
+      <c r="D10" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4">
+      <c r="D12" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4">
+      <c r="D13" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4">
+      <c r="D14" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4">
+      <c r="D15" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4">
+      <c r="D16" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="D18" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="D20" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="C22" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="D23" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="D24" t="s">
+        <v>831</v>
+      </c>
+      <c r="F24" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="D25" t="s">
+        <v>830</v>
+      </c>
+      <c r="F25" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="D26" t="s">
+        <v>829</v>
+      </c>
+      <c r="E26" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="D27" t="s">
+        <v>937</v>
+      </c>
+      <c r="F27" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="C31" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3">
+      <c r="C34" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="35" spans="3:3">
+      <c r="C35" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="36" spans="3:3">
+      <c r="C36" t="s">
+        <v>940</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:B39"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -27182,7 +27568,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:O20"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -27244,21 +27630,21 @@
       <c r="D16" t="s">
         <v>712</v>
       </c>
-      <c r="I16" s="127" t="s">
+      <c r="I16" s="128" t="s">
         <v>716</v>
       </c>
-      <c r="J16" s="128"/>
+      <c r="J16" s="129"/>
     </row>
     <row r="17" spans="3:10" ht="15" customHeight="1">
-      <c r="I17" s="129"/>
-      <c r="J17" s="130"/>
+      <c r="I17" s="130"/>
+      <c r="J17" s="131"/>
     </row>
     <row r="18" spans="3:10">
       <c r="D18" t="s">
         <v>713</v>
       </c>
-      <c r="I18" s="131"/>
-      <c r="J18" s="132"/>
+      <c r="I18" s="132"/>
+      <c r="J18" s="133"/>
     </row>
     <row r="19" spans="3:10">
       <c r="C19" t="s">
@@ -27279,7 +27665,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:K18"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -27677,7 +28063,7 @@
       <c r="D12" s="11"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" thickBot="1">
-      <c r="C13" s="116" t="s">
+      <c r="C13" s="117" t="s">
         <v>78</v>
       </c>
       <c r="D13" s="26" t="s">
@@ -27694,7 +28080,7 @@
       <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:10" ht="15.75" thickBot="1">
-      <c r="C14" s="117"/>
+      <c r="C14" s="118"/>
       <c r="D14" s="23" t="s">
         <v>65</v>
       </c>
@@ -27710,7 +28096,7 @@
       <c r="J14" s="25"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="C15" s="117"/>
+      <c r="C15" s="118"/>
       <c r="D15" s="26" t="s">
         <v>66</v>
       </c>
@@ -27725,7 +28111,7 @@
       <c r="I15" s="28"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="C16" s="117"/>
+      <c r="C16" s="118"/>
       <c r="D16" s="29"/>
       <c r="E16" s="30" t="s">
         <v>74</v>
@@ -27736,7 +28122,7 @@
       <c r="I16" s="31"/>
     </row>
     <row r="17" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C17" s="118"/>
+      <c r="C17" s="119"/>
       <c r="D17" s="32"/>
       <c r="E17" s="33" t="s">
         <v>75</v>
@@ -27767,7 +28153,7 @@
       <c r="L18" s="25"/>
     </row>
     <row r="19" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C19" s="116" t="s">
+      <c r="C19" s="117" t="s">
         <v>78</v>
       </c>
       <c r="D19" s="23" t="s">
@@ -27778,7 +28164,7 @@
       </c>
     </row>
     <row r="20" spans="3:12">
-      <c r="C20" s="117"/>
+      <c r="C20" s="118"/>
       <c r="D20" s="26" t="s">
         <v>82</v>
       </c>
@@ -27787,7 +28173,7 @@
       </c>
     </row>
     <row r="21" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C21" s="118"/>
+      <c r="C21" s="119"/>
       <c r="D21" s="32"/>
       <c r="E21" s="40" t="s">
         <v>84</v>

--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="9" activeTab="22"/>
   </bookViews>
   <sheets>
     <sheet name="Knowhow" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="1106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1636" uniqueCount="1178">
   <si>
     <t>No.</t>
   </si>
@@ -15842,11 +15842,871 @@
     <t>Học về độ phức tạp O(n) , O(1) các thứ</t>
   </si>
   <si>
-    <t>std::thead, std::ref() , join(), dettach(), làm thế nào để nhận biết dettach()
-chạy xong ?</t>
-  </si>
-  <si>
     <t>std::chrono::microseconds(1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deadlock là trạng thái trong đó hai hoặc nhiều thread bị chặn vĩnh viễn vì mỗi thread đang giữ một tài nguyên </t>
+  </si>
+  <si>
+    <t>và đồng thời chờ tài nguyên khác mà thread khác đang giữ. Không thread nào tiếp tục để giải phóng tài nguyên, khiến hệ thống ngưng hoạt động.</t>
+  </si>
+  <si>
+    <t>Deadlock</t>
+  </si>
+  <si>
+    <t>- Lock Orderin : luôn phân cấp thứ tự cố định và lock theo thứ tự đó ở mọi luồng</t>
+  </si>
+  <si>
+    <t>- Dùng std::scoped_lock</t>
+  </si>
+  <si>
+    <t>std::scoped_lock</t>
+  </si>
+  <si>
+    <t>- Dùng std::lock</t>
+  </si>
+  <si>
+    <t>21.18</t>
+  </si>
+  <si>
+    <t>21.19</t>
+  </si>
+  <si>
+    <t>21.20</t>
+  </si>
+  <si>
+    <t>21.21</t>
+  </si>
+  <si>
+    <t>21.22</t>
+  </si>
+  <si>
+    <t>std::lock</t>
+  </si>
+  <si>
+    <t>try_lock()</t>
+  </si>
+  <si>
+    <t>- Dùng try_lock()</t>
+  </si>
+  <si>
+    <t>21.23</t>
+  </si>
+  <si>
+    <t>std::thead</t>
+  </si>
+  <si>
+    <t>Thư viện :</t>
+  </si>
+  <si>
+    <t>#include&lt;thread&gt;</t>
+  </si>
+  <si>
+    <t>cách dùng :</t>
+  </si>
+  <si>
+    <t>void run(int a, char b){}</t>
+  </si>
+  <si>
+    <t>std::thread thrd1(run, 6, 'k');</t>
+  </si>
+  <si>
+    <t>std::thread thrd2(run, 6, 'k');</t>
+  </si>
+  <si>
+    <t>thrd1.join();</t>
+  </si>
+  <si>
+    <t>// khai báo 1 thread để run hàm, đối số truyền vào cách nhau với tên hàm bằng dấu phẩy</t>
+  </si>
+  <si>
+    <t>// Khai báo rằng main thread sẽ đợi thrd1 chạy xong để chạy tiếp</t>
+  </si>
+  <si>
+    <t>std::thead, join(), dettach(), làm thế nào để nhận biết dettach()
+chạy xong ? Nếu quên không join() hoặc dettach() thì sao ?</t>
+  </si>
+  <si>
+    <t>thrd2.dettach();</t>
+  </si>
+  <si>
+    <t>.join()</t>
+  </si>
+  <si>
+    <t>.dettach()</t>
+  </si>
+  <si>
+    <t>(nếu muốn nắm rõ thì phải tự modify can thiệp ở hàm)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>thread gọi join</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sẽ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> đợi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>thread được gọi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hoàn thành. Sau đó nó mới tiếp tục chạy</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>thread được dettach</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sẽ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tách ra</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> chạy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>độc lập</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> với</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> thread gọi dettach</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Chương trình sẽ tự quản lý thread dettach và ta sẽ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>không nắm rõ được khi nào thread dettach chạy xong</t>
+    </r>
+  </si>
+  <si>
+    <t>Nếu quên không join() hoặc dettach() thì có thể xảy ra trường hợp :</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- chương trình </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>chính kết thúc trước</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : nhưng thread chưa chạy xong -&gt; OS diệt Process -&gt; Mọi thread chết theo -&gt; Không thấy ouput</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- chương trình </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>chính kết thúc sau</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : Destructor của std::thread thấy thread còn joinable</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">→ phá hủy 1 thread chưa được join() hoặc dettach() -&gt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>UB</t>
+    </r>
+  </si>
+  <si>
+    <t>std::ref(x)</t>
+  </si>
+  <si>
+    <t>Trong 1 số thư viện, C++ mặc định copy tham số ( ví dụ như thread). Thì lúc này cần dùng std::ref() để truyền tham chiếu vào</t>
+  </si>
+  <si>
+    <t>void increment(int&amp; x) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    x++;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int a = 5;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    t.join();</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   // std::thread t(increment, a); // LỖI: Không truyền được int&amp; qua copy</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    std::thread t(increment,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> std::ref(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>); // OK</t>
+    </r>
+  </si>
+  <si>
+    <t>std::cref(x)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tạo tham chiếu </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hằng</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tới biến x</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Để</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tạo ra 1 đối tượng tham chiếu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tới biến x</t>
+    </r>
+  </si>
+  <si>
+    <t>std::ref(), std::cref()</t>
+  </si>
+  <si>
+    <r>
+      <t>Có tác dụng là lock và</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tự động giải phóng 1 mutex</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> khi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>out ra khỏi scope</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> của nó ( không phải thread, mà là </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> )</t>
+    </r>
+  </si>
+  <si>
+    <t>#include &lt;functional&gt; // thư viện của std::ref()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thư viện </t>
+  </si>
+  <si>
+    <r>
+      <t>#include &lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>functional</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>Muốn giải phóng mutex một cách tự động</t>
+  </si>
+  <si>
+    <t>#include &lt;mutex&gt;</t>
+  </si>
+  <si>
+    <t>std::lock_guard&lt;std::mutex&gt; lock(mtx);</t>
+  </si>
+  <si>
+    <t>….</t>
+  </si>
+  <si>
+    <r>
+      <t>#include &lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mutex</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>Có tác dụng là lock/unlock được nhiều lần trong 1 scope và có thể dùng với condition_variable</t>
+  </si>
+  <si>
+    <t>Muốn giải phóng mutex một cách tự động, muốn làm việc vơi condition_variable, muốn unlock linh hoạt trong scope</t>
+  </si>
+  <si>
+    <t>std::unique_lock&lt;std::mutex&gt; lock(mtx);</t>
+  </si>
+  <si>
+    <t>if(x==7)</t>
+  </si>
+  <si>
+    <t>if(x==10)</t>
+  </si>
+  <si>
+    <t>lock.lock();</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCC00FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>lock</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.unlock();</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">// Nếu gọi trực tiếp </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mtx.unlock()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> trong trường hợp này sẽ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> rất nguy hiểm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Gây ra </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>UB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vì</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> unique_lock</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vẫn </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>giữ quyền sở hữu mutex</t>
+    </r>
+  </si>
+  <si>
+    <t>std::condition_variable</t>
+  </si>
+  <si>
+    <t>Khi nào dùng</t>
+  </si>
+  <si>
+    <r>
+      <t>Là công cụ để đồng bộ dữ liệu giữa các thread. Khi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 1 thread đợi 1 điều kiện xảy ra</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>thread khác</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> thì </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>thông báo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> điều kiện đã </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>xảy ra rồi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">-&gt; condition_variable đóng vai trò là </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>biến notify trung gian</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Khi có 2 hoặc </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nhiều thread giao tiếp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> với nhau </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bằng cờ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Chú ý, CV luôn đi với s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>td::unique_lock</t>
+    </r>
+  </si>
+  <si>
+    <t>Thư viện</t>
+  </si>
+  <si>
+    <t>#include &lt;condition_variable&gt;</t>
   </si>
 </sst>
 </file>
@@ -16461,7 +17321,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -16745,6 +17605,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -27555,8 +28416,11 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:E32"/>
+  <dimension ref="B2:F157"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="10.140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" t="s">
@@ -27678,6 +28542,496 @@
     <row r="32" spans="2:5">
       <c r="E32" s="80" t="s">
         <v>1086</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5">
+      <c r="B34" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5">
+      <c r="C35" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5">
+      <c r="C36" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5">
+      <c r="C38" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5">
+      <c r="D39" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5">
+      <c r="E40" s="80" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5">
+      <c r="E41" s="80" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5">
+      <c r="E42" s="80" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5">
+      <c r="E43" s="80" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5">
+      <c r="B45" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5">
+      <c r="C46" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D46" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5">
+      <c r="C48" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6">
+      <c r="C49" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="C51" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="C52" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="C53" s="17" t="s">
+        <v>1126</v>
+      </c>
+      <c r="F53" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6">
+      <c r="C54" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="C56" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F56" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6">
+      <c r="C57" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="C59" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6">
+      <c r="C60" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="17" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C62" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6">
+      <c r="B63" s="17" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C63" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6">
+      <c r="C64" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4">
+      <c r="B67" s="17" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4">
+      <c r="C68" s="80" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4">
+      <c r="C69" s="135" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4">
+      <c r="C70" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4">
+      <c r="B73" s="7" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4">
+      <c r="C74" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4">
+      <c r="C76" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4">
+      <c r="D77" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4">
+      <c r="C79" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4">
+      <c r="D80" s="50" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4">
+      <c r="C82" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4">
+      <c r="D83" s="17" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4">
+      <c r="D85" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4">
+      <c r="D86" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4">
+      <c r="D87" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="89" spans="2:4">
+      <c r="D89" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4">
+      <c r="D90" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4">
+      <c r="D91" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4">
+      <c r="D92" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4">
+      <c r="D93" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="94" spans="2:4">
+      <c r="D94" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4">
+      <c r="B95" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4">
+      <c r="C96" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="99" spans="2:4">
+      <c r="B99" s="6" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="100" spans="2:4">
+      <c r="C100" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="102" spans="2:4">
+      <c r="C102" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="103" spans="2:4">
+      <c r="D103" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="104" spans="2:4">
+      <c r="C104" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="105" spans="2:4">
+      <c r="D105" s="50" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="107" spans="2:4">
+      <c r="C107" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="108" spans="2:4">
+      <c r="D108" s="17" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="109" spans="2:4">
+      <c r="D109" s="17"/>
+    </row>
+    <row r="110" spans="2:4">
+      <c r="D110" s="50" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="111" spans="2:4">
+      <c r="D111" s="17"/>
+    </row>
+    <row r="112" spans="2:4">
+      <c r="D112" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="113" spans="2:4">
+      <c r="D113" s="17" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4">
+      <c r="D114" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4">
+      <c r="D115" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4">
+      <c r="D116" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4">
+      <c r="B118" s="6" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4">
+      <c r="C119" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4">
+      <c r="C121" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4">
+      <c r="D122" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4">
+      <c r="C123" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4">
+      <c r="D124" s="50" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4">
+      <c r="C126" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4">
+      <c r="D127" s="17" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4">
+      <c r="D128" s="17"/>
+    </row>
+    <row r="129" spans="4:6">
+      <c r="D129" s="50" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="130" spans="4:6">
+      <c r="D130" s="17"/>
+    </row>
+    <row r="131" spans="4:6">
+      <c r="D131" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="132" spans="4:6">
+      <c r="D132" s="17" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="133" spans="4:6">
+      <c r="D133" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="134" spans="4:6">
+      <c r="D134" s="50" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="135" spans="4:6">
+      <c r="D135" s="50" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="136" spans="4:6">
+      <c r="D136" s="17" t="s">
+        <v>1169</v>
+      </c>
+      <c r="F136" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="137" spans="4:6">
+      <c r="D137" s="50" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="138" spans="4:6">
+      <c r="D138" s="50" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="139" spans="4:6">
+      <c r="D139" s="50" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="140" spans="4:6">
+      <c r="D140" s="17" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="141" spans="4:6">
+      <c r="D141" s="50" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="142" spans="4:6">
+      <c r="D142" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="143" spans="4:6">
+      <c r="D143" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4">
+      <c r="B146" s="56" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
+      <c r="C147" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
+      <c r="D148" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="D149" s="80" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
+      <c r="C151" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4">
+      <c r="D152" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4">
+      <c r="C154" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4">
+      <c r="D155" s="17" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="C157" t="s">
+        <v>611</v>
       </c>
     </row>
   </sheetData>
@@ -30159,7 +31513,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:G137"/>
+  <dimension ref="B1:G142"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col min="3" max="3" width="62.85546875" customWidth="1"/>
@@ -31495,77 +32849,99 @@
       <c r="C94" s="6" t="s">
         <v>1076</v>
       </c>
-      <c r="D94" s="51">
-        <v>0</v>
+      <c r="D94" s="42">
+        <v>1</v>
       </c>
       <c r="E94" s="6"/>
       <c r="F94" s="16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="95" spans="2:6" ht="45">
+    <row r="95" spans="2:6" ht="30">
       <c r="B95" s="5">
         <v>21.4</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>1104</v>
-      </c>
-      <c r="D95" s="51"/>
+        <v>1131</v>
+      </c>
+      <c r="D95" s="42">
+        <v>1</v>
+      </c>
       <c r="E95" s="6"/>
-      <c r="F95" s="6"/>
+      <c r="F95" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="96" spans="2:6">
       <c r="B96" s="5">
         <v>21.5</v>
       </c>
-      <c r="C96" s="6" t="s">
-        <v>1089</v>
-      </c>
-      <c r="D96" s="51"/>
+      <c r="C96" s="7" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D96" s="42">
+        <v>1</v>
+      </c>
       <c r="E96" s="6"/>
-      <c r="F96" s="6"/>
+      <c r="F96" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="97" spans="2:6">
       <c r="B97" s="5">
         <v>21.6</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>1090</v>
-      </c>
-      <c r="D97" s="51"/>
+        <v>1093</v>
+      </c>
+      <c r="D97" s="42">
+        <v>1</v>
+      </c>
       <c r="E97" s="6"/>
-      <c r="F97" s="6"/>
+      <c r="F97" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="5">
         <v>21.7</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>1091</v>
-      </c>
-      <c r="D98" s="51"/>
+        <v>1099</v>
+      </c>
+      <c r="D98" s="42">
+        <v>1</v>
+      </c>
       <c r="E98" s="6"/>
-      <c r="F98" s="6"/>
+      <c r="F98" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="99" spans="2:6">
       <c r="B99" s="5">
         <v>21.8</v>
       </c>
-      <c r="C99" s="6" t="s">
-        <v>1092</v>
-      </c>
-      <c r="D99" s="51"/>
+      <c r="C99" s="56" t="s">
+        <v>1171</v>
+      </c>
+      <c r="D99" s="51">
+        <v>0</v>
+      </c>
       <c r="E99" s="6"/>
-      <c r="F99" s="6"/>
+      <c r="F99" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="5">
         <v>21.9</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>1093</v>
-      </c>
-      <c r="D100" s="51"/>
+        <v>1092</v>
+      </c>
+      <c r="D100" s="51">
+        <v>0</v>
+      </c>
       <c r="E100" s="6"/>
       <c r="F100" s="6"/>
     </row>
@@ -31574,7 +32950,7 @@
         <v>1014</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>1099</v>
+        <v>1089</v>
       </c>
       <c r="D101" s="51"/>
       <c r="E101" s="6"/>
@@ -31585,7 +32961,7 @@
         <v>1015</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>1100</v>
+        <v>1090</v>
       </c>
       <c r="D102" s="51"/>
       <c r="E102" s="6"/>
@@ -31596,7 +32972,7 @@
         <v>1016</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>1101</v>
+        <v>1091</v>
       </c>
       <c r="D103" s="51"/>
       <c r="E103" s="6"/>
@@ -31607,7 +32983,7 @@
         <v>1094</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="D104" s="51"/>
       <c r="E104" s="6"/>
@@ -31618,7 +32994,7 @@
         <v>1095</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>1105</v>
+        <v>1101</v>
       </c>
       <c r="D105" s="51"/>
       <c r="E105" s="6"/>
@@ -31628,7 +33004,9 @@
       <c r="B106" s="52" t="s">
         <v>1096</v>
       </c>
-      <c r="C106" s="6"/>
+      <c r="C106" s="6" t="s">
+        <v>1102</v>
+      </c>
       <c r="D106" s="51"/>
       <c r="E106" s="6"/>
       <c r="F106" s="6"/>
@@ -31637,7 +33015,9 @@
       <c r="B107" s="52" t="s">
         <v>1097</v>
       </c>
-      <c r="C107" s="6"/>
+      <c r="C107" s="6" t="s">
+        <v>1104</v>
+      </c>
       <c r="D107" s="51"/>
       <c r="E107" s="6"/>
       <c r="F107" s="6"/>
@@ -31647,121 +33027,97 @@
         <v>1098</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>432</v>
-      </c>
-      <c r="D108" s="6"/>
+        <v>1110</v>
+      </c>
+      <c r="D108" s="51"/>
       <c r="E108" s="6"/>
       <c r="F108" s="6"/>
     </row>
-    <row r="109" spans="2:6" ht="30">
+    <row r="109" spans="2:6">
       <c r="B109" s="52" t="s">
-        <v>1016</v>
-      </c>
-      <c r="C109" s="7" t="s">
-        <v>466</v>
-      </c>
-      <c r="D109" s="6"/>
+        <v>1112</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D109" s="51"/>
       <c r="E109" s="6"/>
       <c r="F109" s="6"/>
     </row>
     <row r="110" spans="2:6">
-      <c r="B110" s="5" t="s">
+      <c r="B110" s="52" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D110" s="51"/>
+      <c r="E110" s="6"/>
+      <c r="F110" s="6"/>
+    </row>
+    <row r="111" spans="2:6">
+      <c r="B111" s="52" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C111" s="6"/>
+      <c r="D111" s="51"/>
+      <c r="E111" s="6"/>
+      <c r="F111" s="6"/>
+    </row>
+    <row r="112" spans="2:6">
+      <c r="B112" s="52" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C112" s="6"/>
+      <c r="D112" s="51"/>
+      <c r="E112" s="6"/>
+      <c r="F112" s="6"/>
+    </row>
+    <row r="113" spans="2:7">
+      <c r="B113" s="52" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="D113" s="6"/>
+      <c r="E113" s="6"/>
+      <c r="F113" s="6"/>
+    </row>
+    <row r="114" spans="2:7" ht="30">
+      <c r="B114" s="52" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="D114" s="6"/>
+      <c r="E114" s="6"/>
+      <c r="F114" s="6"/>
+    </row>
+    <row r="115" spans="2:7">
+      <c r="B115" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="C110" s="6" t="s">
+      <c r="C115" s="6" t="s">
         <v>323</v>
-      </c>
-      <c r="D110" s="42">
-        <v>1</v>
-      </c>
-      <c r="E110" s="16" t="s">
-        <v>463</v>
-      </c>
-      <c r="F110" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="111" spans="2:6">
-      <c r="B111" s="5">
-        <v>23.1</v>
-      </c>
-      <c r="C111" s="6" t="s">
-        <v>971</v>
-      </c>
-      <c r="D111" s="42">
-        <v>1</v>
-      </c>
-      <c r="E111" s="16"/>
-      <c r="F111" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="112" spans="2:6">
-      <c r="B112" s="5">
-        <v>23.2</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>978</v>
-      </c>
-      <c r="D112" s="42">
-        <v>1</v>
-      </c>
-      <c r="E112" s="16"/>
-      <c r="F112" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="113" spans="2:7">
-      <c r="B113" s="5">
-        <v>23.3</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>989</v>
-      </c>
-      <c r="D113" s="51">
-        <v>0.99</v>
-      </c>
-      <c r="E113" s="16"/>
-      <c r="F113" s="16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="114" spans="2:7" ht="30">
-      <c r="B114" s="5" t="s">
-        <v>464</v>
-      </c>
-      <c r="C114" s="7" t="s">
-        <v>725</v>
-      </c>
-      <c r="D114" s="42">
-        <v>1</v>
-      </c>
-      <c r="E114" s="16" t="s">
-        <v>463</v>
-      </c>
-      <c r="F114" s="16"/>
-    </row>
-    <row r="115" spans="2:7">
-      <c r="B115" s="5">
-        <v>24.1</v>
-      </c>
-      <c r="C115" s="7" t="s">
-        <v>726</v>
       </c>
       <c r="D115" s="42">
         <v>1</v>
       </c>
-      <c r="E115" s="16"/>
-      <c r="F115" s="16" t="s">
-        <v>14</v>
+      <c r="E115" s="16" t="s">
+        <v>463</v>
+      </c>
+      <c r="F115" s="6" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="116" spans="2:7">
       <c r="B116" s="5">
-        <v>24.2</v>
-      </c>
-      <c r="C116" s="7" t="s">
-        <v>770</v>
+        <v>23.1</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>971</v>
       </c>
       <c r="D116" s="42">
         <v>1</v>
@@ -31770,14 +33126,13 @@
       <c r="F116" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G116" s="48"/>
     </row>
     <row r="117" spans="2:7">
-      <c r="B117" s="5" t="s">
-        <v>471</v>
-      </c>
-      <c r="C117" s="6" t="s">
-        <v>932</v>
+      <c r="B117" s="5">
+        <v>23.2</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>978</v>
       </c>
       <c r="D117" s="42">
         <v>1</v>
@@ -31788,88 +33143,87 @@
       </c>
     </row>
     <row r="118" spans="2:7">
-      <c r="B118" s="5" t="s">
-        <v>473</v>
-      </c>
-      <c r="C118" s="6" t="s">
-        <v>475</v>
-      </c>
-      <c r="D118" s="42">
-        <v>1</v>
+      <c r="B118" s="5">
+        <v>23.3</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="D118" s="51">
+        <v>0.99</v>
       </c>
       <c r="E118" s="16"/>
       <c r="F118" s="16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="119" spans="2:7">
-      <c r="B119" s="5">
-        <v>26.1</v>
-      </c>
-      <c r="C119" s="6" t="s">
-        <v>939</v>
+    <row r="119" spans="2:7" ht="30">
+      <c r="B119" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>725</v>
       </c>
       <c r="D119" s="42">
         <v>1</v>
       </c>
-      <c r="E119" s="16"/>
-      <c r="F119" s="16" t="s">
+      <c r="E119" s="16" t="s">
+        <v>463</v>
+      </c>
+      <c r="F119" s="16"/>
+    </row>
+    <row r="120" spans="2:7">
+      <c r="B120" s="5">
+        <v>24.1</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>726</v>
+      </c>
+      <c r="D120" s="42">
+        <v>1</v>
+      </c>
+      <c r="E120" s="16"/>
+      <c r="F120" s="16" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="120" spans="2:7" ht="45">
-      <c r="B120" s="5" t="s">
-        <v>481</v>
-      </c>
-      <c r="C120" s="79" t="s">
-        <v>995</v>
-      </c>
-      <c r="D120" s="51">
-        <v>0.5</v>
-      </c>
-      <c r="E120" s="16" t="s">
-        <v>478</v>
-      </c>
-      <c r="F120" s="6" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="121" spans="2:7">
       <c r="B121" s="5">
-        <v>27.1</v>
-      </c>
-      <c r="C121" s="79" t="s">
-        <v>993</v>
-      </c>
-      <c r="D121" s="51">
-        <v>0.99</v>
+        <v>24.2</v>
+      </c>
+      <c r="C121" s="7" t="s">
+        <v>770</v>
+      </c>
+      <c r="D121" s="42">
+        <v>1</v>
       </c>
       <c r="E121" s="16"/>
       <c r="F121" s="16" t="s">
         <v>14</v>
       </c>
+      <c r="G121" s="48"/>
     </row>
     <row r="122" spans="2:7">
-      <c r="B122" s="5">
-        <v>27.2</v>
-      </c>
-      <c r="C122" s="79" t="s">
-        <v>994</v>
-      </c>
-      <c r="D122" s="51">
-        <v>0.99</v>
+      <c r="B122" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>932</v>
+      </c>
+      <c r="D122" s="42">
+        <v>1</v>
       </c>
       <c r="E122" s="16"/>
       <c r="F122" s="16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="123" spans="2:7" ht="30">
+    <row r="123" spans="2:7">
       <c r="B123" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="C123" s="7" t="s">
-        <v>940</v>
+        <v>473</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>475</v>
       </c>
       <c r="D123" s="42">
         <v>1</v>
@@ -31880,11 +33234,11 @@
       </c>
     </row>
     <row r="124" spans="2:7">
-      <c r="B124" s="5" t="s">
-        <v>483</v>
+      <c r="B124" s="5">
+        <v>26.1</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>807</v>
+        <v>939</v>
       </c>
       <c r="D124" s="42">
         <v>1</v>
@@ -31894,30 +33248,32 @@
         <v>14</v>
       </c>
     </row>
-    <row r="125" spans="2:7">
-      <c r="B125" s="5">
-        <v>29.1</v>
-      </c>
-      <c r="C125" s="6" t="s">
-        <v>933</v>
-      </c>
-      <c r="D125" s="42">
-        <v>1</v>
-      </c>
-      <c r="E125" s="16"/>
-      <c r="F125" s="16" t="s">
-        <v>14</v>
+    <row r="125" spans="2:7" ht="45">
+      <c r="B125" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="C125" s="79" t="s">
+        <v>995</v>
+      </c>
+      <c r="D125" s="51">
+        <v>0.5</v>
+      </c>
+      <c r="E125" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="F125" s="6" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="126" spans="2:7">
-      <c r="B126" s="5" t="s">
-        <v>484</v>
-      </c>
-      <c r="C126" s="7" t="s">
-        <v>804</v>
-      </c>
-      <c r="D126" s="42">
-        <v>1</v>
+      <c r="B126" s="5">
+        <v>27.1</v>
+      </c>
+      <c r="C126" s="79" t="s">
+        <v>993</v>
+      </c>
+      <c r="D126" s="51">
+        <v>0.99</v>
       </c>
       <c r="E126" s="16"/>
       <c r="F126" s="16" t="s">
@@ -31926,25 +33282,25 @@
     </row>
     <row r="127" spans="2:7">
       <c r="B127" s="5">
-        <v>30.1</v>
-      </c>
-      <c r="C127" s="7" t="s">
-        <v>801</v>
-      </c>
-      <c r="D127" s="42">
-        <v>1</v>
+        <v>27.2</v>
+      </c>
+      <c r="C127" s="79" t="s">
+        <v>994</v>
+      </c>
+      <c r="D127" s="51">
+        <v>0.99</v>
       </c>
       <c r="E127" s="16"/>
       <c r="F127" s="16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="128" spans="2:7">
-      <c r="B128" s="5">
-        <v>30.2</v>
+    <row r="128" spans="2:7" ht="30">
+      <c r="B128" s="5" t="s">
+        <v>482</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>802</v>
+        <v>940</v>
       </c>
       <c r="D128" s="42">
         <v>1</v>
@@ -31953,14 +33309,13 @@
       <c r="F128" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G128" s="48"/>
-    </row>
-    <row r="129" spans="2:6">
-      <c r="B129" s="5">
-        <v>30.3</v>
-      </c>
-      <c r="C129" s="7" t="s">
-        <v>803</v>
+    </row>
+    <row r="129" spans="2:7">
+      <c r="B129" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>807</v>
       </c>
       <c r="D129" s="42">
         <v>1</v>
@@ -31970,27 +33325,27 @@
         <v>14</v>
       </c>
     </row>
-    <row r="130" spans="2:6" ht="30">
-      <c r="B130" s="5" t="s">
-        <v>485</v>
-      </c>
-      <c r="C130" s="7" t="s">
-        <v>472</v>
-      </c>
-      <c r="D130" s="51">
-        <v>0.05</v>
+    <row r="130" spans="2:7">
+      <c r="B130" s="5">
+        <v>29.1</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>933</v>
+      </c>
+      <c r="D130" s="42">
+        <v>1</v>
       </c>
       <c r="E130" s="16"/>
       <c r="F130" s="16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="131" spans="2:6">
+    <row r="131" spans="2:7">
       <c r="B131" s="5" t="s">
-        <v>771</v>
+        <v>484</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>772</v>
+        <v>804</v>
       </c>
       <c r="D131" s="42">
         <v>1</v>
@@ -32000,63 +33355,139 @@
         <v>14</v>
       </c>
     </row>
-    <row r="132" spans="2:6">
-      <c r="B132" s="5" t="s">
+    <row r="132" spans="2:7">
+      <c r="B132" s="5">
+        <v>30.1</v>
+      </c>
+      <c r="C132" s="7" t="s">
+        <v>801</v>
+      </c>
+      <c r="D132" s="42">
+        <v>1</v>
+      </c>
+      <c r="E132" s="16"/>
+      <c r="F132" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="133" spans="2:7">
+      <c r="B133" s="5">
+        <v>30.2</v>
+      </c>
+      <c r="C133" s="7" t="s">
+        <v>802</v>
+      </c>
+      <c r="D133" s="42">
+        <v>1</v>
+      </c>
+      <c r="E133" s="16"/>
+      <c r="F133" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G133" s="48"/>
+    </row>
+    <row r="134" spans="2:7">
+      <c r="B134" s="5">
+        <v>30.3</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>803</v>
+      </c>
+      <c r="D134" s="42">
+        <v>1</v>
+      </c>
+      <c r="E134" s="16"/>
+      <c r="F134" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="135" spans="2:7" ht="30">
+      <c r="B135" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="C135" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="D135" s="51">
+        <v>0.05</v>
+      </c>
+      <c r="E135" s="16"/>
+      <c r="F135" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="136" spans="2:7">
+      <c r="B136" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="C136" s="7" t="s">
+        <v>772</v>
+      </c>
+      <c r="D136" s="42">
+        <v>1</v>
+      </c>
+      <c r="E136" s="16"/>
+      <c r="F136" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="137" spans="2:7">
+      <c r="B137" s="5" t="s">
         <v>1017</v>
       </c>
-      <c r="C132" s="7" t="s">
+      <c r="C137" s="7" t="s">
         <v>1018</v>
       </c>
-      <c r="D132" s="42"/>
-      <c r="E132" s="16"/>
-      <c r="F132" s="16"/>
-    </row>
-    <row r="133" spans="2:6">
-      <c r="B133" s="5"/>
-      <c r="C133" s="7" t="s">
+      <c r="D137" s="42"/>
+      <c r="E137" s="16"/>
+      <c r="F137" s="16"/>
+    </row>
+    <row r="138" spans="2:7">
+      <c r="B138" s="5"/>
+      <c r="C138" s="7" t="s">
         <v>1019</v>
       </c>
-      <c r="D133" s="42"/>
-      <c r="E133" s="16"/>
-      <c r="F133" s="16"/>
-    </row>
-    <row r="134" spans="2:6">
-      <c r="B134" s="5"/>
-      <c r="C134" s="7" t="s">
+      <c r="D138" s="42"/>
+      <c r="E138" s="16"/>
+      <c r="F138" s="16"/>
+    </row>
+    <row r="139" spans="2:7">
+      <c r="B139" s="5"/>
+      <c r="C139" s="7" t="s">
         <v>1020</v>
       </c>
-      <c r="D134" s="42"/>
-      <c r="E134" s="16"/>
-      <c r="F134" s="16"/>
-    </row>
-    <row r="135" spans="2:6">
-      <c r="B135" s="5"/>
-      <c r="C135" s="7" t="s">
+      <c r="D139" s="42"/>
+      <c r="E139" s="16"/>
+      <c r="F139" s="16"/>
+    </row>
+    <row r="140" spans="2:7">
+      <c r="B140" s="5"/>
+      <c r="C140" s="7" t="s">
         <v>1021</v>
       </c>
-      <c r="D135" s="42"/>
-      <c r="E135" s="16"/>
-      <c r="F135" s="16"/>
-    </row>
-    <row r="136" spans="2:6">
-      <c r="B136" s="5"/>
-      <c r="C136" s="7"/>
-      <c r="D136" s="42"/>
-      <c r="E136" s="16"/>
-      <c r="F136" s="16"/>
-    </row>
-    <row r="137" spans="2:6">
-      <c r="B137" s="77" t="s">
+      <c r="D140" s="42"/>
+      <c r="E140" s="16"/>
+      <c r="F140" s="16"/>
+    </row>
+    <row r="141" spans="2:7">
+      <c r="B141" s="5"/>
+      <c r="C141" s="7"/>
+      <c r="D141" s="42"/>
+      <c r="E141" s="16"/>
+      <c r="F141" s="16"/>
+    </row>
+    <row r="142" spans="2:7">
+      <c r="B142" s="77" t="s">
         <v>469</v>
       </c>
-      <c r="C137" s="57" t="s">
+      <c r="C142" s="57" t="s">
         <v>468</v>
       </c>
-      <c r="D137" s="1"/>
-      <c r="E137" s="49" t="s">
+      <c r="D142" s="1"/>
+      <c r="E142" s="49" t="s">
         <v>467</v>
       </c>
-      <c r="F137" s="1"/>
+      <c r="F142" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -32108,9 +33539,9 @@
     <hyperlink ref="F63" location="'#14'!B2" display="Link"/>
     <hyperlink ref="E65" r:id="rId7"/>
     <hyperlink ref="E80" r:id="rId8"/>
-    <hyperlink ref="E110" r:id="rId9"/>
-    <hyperlink ref="E114" r:id="rId10"/>
-    <hyperlink ref="E137" r:id="rId11"/>
+    <hyperlink ref="E115" r:id="rId9"/>
+    <hyperlink ref="E119" r:id="rId10"/>
+    <hyperlink ref="E142" r:id="rId11"/>
     <hyperlink ref="F49" location="'#9'!B2" display="Link"/>
     <hyperlink ref="F61" location="'#12'!B2" display="Link"/>
     <hyperlink ref="F66" location="'#16'!B2" display="Link"/>
@@ -32123,19 +33554,19 @@
     <hyperlink ref="F64" location="'#15'!B2" display="Link"/>
     <hyperlink ref="F71" location="'#16'!B89" display="Link"/>
     <hyperlink ref="F72" location="'#16'!B10" display="Link"/>
-    <hyperlink ref="F130" location="'#31'!B2" display="Link"/>
-    <hyperlink ref="F115" location="'#24'!B2" display="Link"/>
-    <hyperlink ref="F116" location="'#24'!B2" display="Link"/>
-    <hyperlink ref="F116:G116" location="'#24'!B26" display="Link"/>
-    <hyperlink ref="F117" location="'#25'!B2" display="Link"/>
+    <hyperlink ref="F135" location="'#31'!B2" display="Link"/>
+    <hyperlink ref="F120" location="'#24'!B2" display="Link"/>
+    <hyperlink ref="F121" location="'#24'!B2" display="Link"/>
+    <hyperlink ref="F121:G121" location="'#24'!B26" display="Link"/>
+    <hyperlink ref="F122" location="'#25'!B2" display="Link"/>
     <hyperlink ref="F89" location="'#19'!B2" display="Link"/>
-    <hyperlink ref="F127" location="'#30'!B8" display="Link"/>
-    <hyperlink ref="F124" location="'#29'!B2" display="Link"/>
-    <hyperlink ref="F131" location="'#32'!B2" display="Link"/>
-    <hyperlink ref="F126" location="'#30'!B2" display="Link"/>
-    <hyperlink ref="F128" location="'#30'!B8" display="Link"/>
-    <hyperlink ref="F128:G128" location="'#30'!B24" display="Link"/>
-    <hyperlink ref="F129" location="'#30'!B35" display="Link"/>
+    <hyperlink ref="F132" location="'#30'!B8" display="Link"/>
+    <hyperlink ref="F129" location="'#29'!B2" display="Link"/>
+    <hyperlink ref="F136" location="'#32'!B2" display="Link"/>
+    <hyperlink ref="F131" location="'#30'!B2" display="Link"/>
+    <hyperlink ref="F133" location="'#30'!B8" display="Link"/>
+    <hyperlink ref="F133:G133" location="'#30'!B24" display="Link"/>
+    <hyperlink ref="F134" location="'#30'!B35" display="Link"/>
     <hyperlink ref="F51" location="'#11'!B2" display="Link"/>
     <hyperlink ref="F53" location="'#11'!B4" display="Link"/>
     <hyperlink ref="F54" location="'#11'!B21" display="Link"/>
@@ -32144,20 +33575,25 @@
     <hyperlink ref="F28" location="'#4'!B35" display="Link"/>
     <hyperlink ref="F29" location="'#4'!B43" display="Link"/>
     <hyperlink ref="F90" location="'#20'!B2" display="Link"/>
-    <hyperlink ref="F118" location="'#26'!B2" display="Link"/>
-    <hyperlink ref="F125" location="'#29'!B30" display="Link"/>
-    <hyperlink ref="F123" location="'#28'!B17" display="Link"/>
-    <hyperlink ref="F119" location="'#26'!B22" display="Link"/>
-    <hyperlink ref="F111" location="'#23'!B2" display="Link"/>
-    <hyperlink ref="F112" location="'#23'!B10" display="Link"/>
-    <hyperlink ref="F113" location="'#23'!B24" display="Link"/>
-    <hyperlink ref="F121" location="'#27'!B2" display="Link"/>
-    <hyperlink ref="F122" location="'#27'!B18" display="Link"/>
+    <hyperlink ref="F123" location="'#26'!B2" display="Link"/>
+    <hyperlink ref="F130" location="'#29'!B30" display="Link"/>
+    <hyperlink ref="F128" location="'#28'!B17" display="Link"/>
+    <hyperlink ref="F124" location="'#26'!B22" display="Link"/>
+    <hyperlink ref="F116" location="'#23'!B2" display="Link"/>
+    <hyperlink ref="F117" location="'#23'!B10" display="Link"/>
+    <hyperlink ref="F118" location="'#23'!B24" display="Link"/>
+    <hyperlink ref="F126" location="'#27'!B2" display="Link"/>
+    <hyperlink ref="F127" location="'#27'!B18" display="Link"/>
     <hyperlink ref="F92" location="'#21'!B2" display="Link"/>
     <hyperlink ref="F74" location="'#16'!D109" display="Link"/>
     <hyperlink ref="F75" location="'#16'!D168" display="Link"/>
-    <hyperlink ref="F94" location="'#21'!B2" display="Link"/>
+    <hyperlink ref="F94" location="'#21'!B34" display="Link"/>
     <hyperlink ref="F93" location="'#21'!B23" display="Link"/>
+    <hyperlink ref="F95" location="'#21'!B45" display="Link"/>
+    <hyperlink ref="F96" location="'#21'!B73" display="Link"/>
+    <hyperlink ref="F97" location="'#21'!B99" display="Link"/>
+    <hyperlink ref="F98" location="'#21'!B118" display="Link"/>
+    <hyperlink ref="F99" location="'#21'!B146" display="Link"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId12"/>

--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="9" activeTab="22"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Knowhow" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1636" uniqueCount="1178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1675" uniqueCount="1210">
   <si>
     <t>No.</t>
   </si>
@@ -12979,9 +12979,6 @@
     <t>Mục đích sử dụng :</t>
   </si>
   <si>
-    <t>std::unique_ptr&lt;int&gt; ptr = std::make_unique&lt;int&gt;(10);</t>
-  </si>
-  <si>
     <t>// khi constructor yêu cầu truyền vào đối số thì viết như vậy</t>
   </si>
   <si>
@@ -13014,9 +13011,6 @@
   </si>
   <si>
     <t>std::share_ptr&lt;int&gt;a</t>
-  </si>
-  <si>
-    <t>shared_ptr&lt;int&gt; p = make_shared&lt;int&gt;(p);</t>
   </si>
   <si>
     <t>shared_ptr&lt;int&gt; p1 = p;</t>
@@ -15830,9 +15824,6 @@
     <t>std::unique_lock</t>
   </si>
   <si>
-    <t>spinlock</t>
-  </si>
-  <si>
     <t>memory pool</t>
   </si>
   <si>
@@ -16648,6 +16639,274 @@
     </r>
   </si>
   <si>
+    <t>Thư viện</t>
+  </si>
+  <si>
+    <t>#include &lt;condition_variable&gt;</t>
+  </si>
+  <si>
+    <t>Cách để tránh double singleton khi gọi trong 2 thread</t>
+  </si>
+  <si>
+    <t>21.24</t>
+  </si>
+  <si>
+    <t>std::condition_variable, spurious wake-up</t>
+  </si>
+  <si>
+    <t>Các hàm quan trọng của condition_variable cần nhớ</t>
+  </si>
+  <si>
+    <t>wait(unique_lock&lt;mutex&gt;&amp; lock)</t>
+  </si>
+  <si>
+    <t>wait(unique_lock&lt;mutex&gt;&amp; lock, Predicate pred)</t>
+  </si>
+  <si>
+    <t>// Nhả mutex, chờ đợi được đánh thức</t>
+  </si>
+  <si>
+    <t>// Nhả mutex, chờ đợi được đánh thức, chống spurious wake-up</t>
+  </si>
+  <si>
+    <t>wait_for(lock, duration, pred)</t>
+  </si>
+  <si>
+    <t>wait_until(lock, time_point, pred)</t>
+  </si>
+  <si>
+    <t>notify_one()</t>
+  </si>
+  <si>
+    <t>// Đánh thức 1 thread đang đợi, nhưng không biết thread nào được đánh thức</t>
+  </si>
+  <si>
+    <t>notify_all()</t>
+  </si>
+  <si>
+    <t>// Đánh thức tất cả các thread đang đợi</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">cv.wait(lock, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[] { return ready; }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">// Truyền vào lambda hoặc 1 hàm có </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>return</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">std::unique_ptr&lt;int&gt; ptr = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>std::make_unique&lt;int&gt;(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>std::unique_ptr&lt;int&gt; ptr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(new int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(10)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">std::shared_ptr&lt;int&gt; p = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>std::make_shared&lt;int&gt;(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>std::shared_ptr&lt;int&gt; p</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(new int(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Khi có 2 hoặc </t>
     </r>
@@ -16689,7 +16948,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>. Chú ý, CV luôn đi với s</t>
+      <t xml:space="preserve">. Chú ý, CV luôn đi với </t>
     </r>
     <r>
       <rPr>
@@ -16699,14 +16958,364 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>td::unique_lock</t>
-    </r>
-  </si>
-  <si>
-    <t>Thư viện</t>
-  </si>
-  <si>
-    <t>#include &lt;condition_variable&gt;</t>
+      <t>std::unique_lock</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hiện tượng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>spurious wake-up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> :</t>
+    </r>
+  </si>
+  <si>
+    <t>Thêm predicate cho wait</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Xảy ra khi sử dụng phương thức </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>wait()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> của condition_variable mà </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>không truyền vào prediacate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, dẫn đến rủi ro </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>thread</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bị </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>đánh thức</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ngẫu nhiên</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> mặc dù chưa có tín hiệu notify</t>
+    </r>
+  </si>
+  <si>
+    <t>spinlock, busy-waiting</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nếu </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sử dụng 1 biến global làm cờ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> thay vì condition_variable -&gt; Biến global sẽ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>không có</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> phương thức </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>wait</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> cho thread ngủ giống như condition_variable</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">-&gt; Sẽ cần </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dùng 1 vòng while</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> check</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> điều kiện của biến global </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>liên tục</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -&gt; tiên tốn công suất để kiểm tra liên tục, nếu điều kiện trong while không xảy ra, và buộc cần nó để tiếp tục</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>-&gt; dẫn đến chương trình bị</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> treo ở trong vòng lặp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -&gt; spinlock, busy-waiting</t>
+    </r>
+  </si>
+  <si>
+    <t>Cách khắc phục</t>
+  </si>
+  <si>
+    <t>Cách 1 :</t>
+  </si>
+  <si>
+    <t>và gọi 2 thread khởi tạo singleton -&gt; Xảy ra hiện tượng double singleton</t>
+  </si>
+  <si>
+    <t>Sử dụng 1 static mutex truyền vào hàm getInstance</t>
+  </si>
+  <si>
+    <t>Sử dụng Meyer Singleton (dùng tham chiếu thay vì con trỏ)</t>
+  </si>
+  <si>
+    <t>Cách 2 :</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Khi sử dụng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>singleton dưới dạng con trỏ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">check </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>điều kiện</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> null để getInstance</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -17321,7 +17930,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -17554,6 +18163,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -17605,7 +18215,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -25423,16 +26035,16 @@
       </c>
     </row>
     <row r="89" spans="2:9" ht="54" customHeight="1">
-      <c r="B89" s="121" t="s">
+      <c r="B89" s="122" t="s">
         <v>616</v>
       </c>
-      <c r="C89" s="122"/>
-      <c r="D89" s="122"/>
-      <c r="E89" s="122"/>
-      <c r="F89" s="122"/>
-      <c r="G89" s="122"/>
-      <c r="H89" s="122"/>
-      <c r="I89" s="122"/>
+      <c r="C89" s="123"/>
+      <c r="D89" s="123"/>
+      <c r="E89" s="123"/>
+      <c r="F89" s="123"/>
+      <c r="G89" s="123"/>
+      <c r="H89" s="123"/>
+      <c r="I89" s="123"/>
     </row>
     <row r="91" spans="2:9">
       <c r="B91" t="s">
@@ -25544,7 +26156,7 @@
     </row>
     <row r="114" spans="4:14">
       <c r="D114" s="113" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="E114" s="104"/>
       <c r="F114" s="104"/>
@@ -25572,7 +26184,7 @@
     </row>
     <row r="116" spans="4:14">
       <c r="D116" s="103" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="E116" s="104"/>
       <c r="F116" s="104"/>
@@ -25617,7 +26229,7 @@
     </row>
     <row r="119" spans="4:14">
       <c r="D119" s="106" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="E119" s="104"/>
       <c r="F119" s="104"/>
@@ -25647,7 +26259,7 @@
     </row>
     <row r="121" spans="4:14">
       <c r="D121" s="110" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="E121" s="104"/>
       <c r="F121" s="104"/>
@@ -25677,7 +26289,7 @@
     </row>
     <row r="123" spans="4:14">
       <c r="D123" s="106" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="E123" s="104"/>
       <c r="F123" s="104"/>
@@ -25707,7 +26319,7 @@
     </row>
     <row r="125" spans="4:14">
       <c r="D125" s="110" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="E125" s="104"/>
       <c r="F125" s="104"/>
@@ -25722,7 +26334,7 @@
     </row>
     <row r="126" spans="4:14">
       <c r="D126" s="110" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="E126" s="104"/>
       <c r="F126" s="104"/>
@@ -25737,7 +26349,7 @@
     </row>
     <row r="127" spans="4:14">
       <c r="D127" s="107" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="E127" s="104"/>
       <c r="F127" s="104"/>
@@ -25767,7 +26379,7 @@
     </row>
     <row r="129" spans="4:14">
       <c r="D129" s="103" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="E129" s="104"/>
       <c r="F129" s="104"/>
@@ -25797,7 +26409,7 @@
     </row>
     <row r="131" spans="4:14">
       <c r="D131" s="113" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="E131" s="104"/>
       <c r="F131" s="104"/>
@@ -25827,7 +26439,7 @@
     </row>
     <row r="133" spans="4:14">
       <c r="D133" s="103" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="E133" s="104"/>
       <c r="F133" s="104"/>
@@ -25857,7 +26469,7 @@
     </row>
     <row r="135" spans="4:14">
       <c r="D135" s="110" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="E135" s="104"/>
       <c r="F135" s="104"/>
@@ -25887,7 +26499,7 @@
     </row>
     <row r="137" spans="4:14">
       <c r="D137" s="103" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="E137" s="104"/>
       <c r="F137" s="104"/>
@@ -25917,7 +26529,7 @@
     </row>
     <row r="139" spans="4:14">
       <c r="D139" s="113" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="E139" s="104"/>
       <c r="F139" s="104"/>
@@ -25975,7 +26587,7 @@
     </row>
     <row r="143" spans="4:14">
       <c r="D143" s="103" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="E143" s="104"/>
       <c r="F143" s="104"/>
@@ -25990,7 +26602,7 @@
     </row>
     <row r="144" spans="4:14">
       <c r="D144" s="103" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="E144" s="104"/>
       <c r="F144" s="104"/>
@@ -26063,7 +26675,7 @@
     </row>
     <row r="149" spans="4:14">
       <c r="D149" s="107" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="E149" s="104"/>
       <c r="F149" s="104"/>
@@ -26078,7 +26690,7 @@
     </row>
     <row r="150" spans="4:14">
       <c r="D150" s="107" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="E150" s="104"/>
       <c r="F150" s="104"/>
@@ -26093,7 +26705,7 @@
     </row>
     <row r="151" spans="4:14">
       <c r="D151" s="107" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="E151" s="104"/>
       <c r="F151" s="104"/>
@@ -26121,7 +26733,7 @@
     </row>
     <row r="153" spans="4:14">
       <c r="D153" s="110" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="E153" s="104"/>
       <c r="F153" s="104"/>
@@ -26136,7 +26748,7 @@
     </row>
     <row r="154" spans="4:14">
       <c r="D154" s="110" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="E154" s="104"/>
       <c r="F154" s="104"/>
@@ -26164,7 +26776,7 @@
     </row>
     <row r="156" spans="4:14">
       <c r="D156" s="107" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="E156" s="104"/>
       <c r="F156" s="104"/>
@@ -26179,7 +26791,7 @@
     </row>
     <row r="157" spans="4:14">
       <c r="D157" s="107" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="E157" s="104"/>
       <c r="F157" s="104"/>
@@ -26194,7 +26806,7 @@
     </row>
     <row r="158" spans="4:14">
       <c r="D158" s="107" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="E158" s="104"/>
       <c r="F158" s="104"/>
@@ -26222,7 +26834,7 @@
     </row>
     <row r="160" spans="4:14">
       <c r="D160" s="107" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="E160" s="104"/>
       <c r="F160" s="104"/>
@@ -26237,7 +26849,7 @@
     </row>
     <row r="161" spans="4:14">
       <c r="D161" s="107" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="E161" s="104"/>
       <c r="F161" s="104"/>
@@ -26252,7 +26864,7 @@
     </row>
     <row r="162" spans="4:14">
       <c r="D162" s="107" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="E162" s="104"/>
       <c r="F162" s="104"/>
@@ -26344,7 +26956,7 @@
     </row>
     <row r="173" spans="4:14">
       <c r="D173" s="113" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="E173" s="104"/>
       <c r="F173" s="104"/>
@@ -26368,7 +26980,7 @@
     </row>
     <row r="175" spans="4:14">
       <c r="D175" s="103" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="E175" s="104"/>
       <c r="F175" s="104"/>
@@ -26407,7 +27019,7 @@
     </row>
     <row r="178" spans="4:12">
       <c r="D178" s="106" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="E178" s="104"/>
       <c r="F178" s="104"/>
@@ -26433,7 +27045,7 @@
     </row>
     <row r="180" spans="4:12">
       <c r="D180" s="110" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="E180" s="104"/>
       <c r="F180" s="104"/>
@@ -26459,7 +27071,7 @@
     </row>
     <row r="182" spans="4:12">
       <c r="D182" s="106" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="E182" s="104"/>
       <c r="F182" s="104"/>
@@ -26485,7 +27097,7 @@
     </row>
     <row r="184" spans="4:12">
       <c r="D184" s="110" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="E184" s="104"/>
       <c r="F184" s="104"/>
@@ -26498,7 +27110,7 @@
     </row>
     <row r="185" spans="4:12">
       <c r="D185" s="103" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="E185" s="104"/>
       <c r="F185" s="104"/>
@@ -26511,7 +27123,7 @@
     </row>
     <row r="186" spans="4:12">
       <c r="D186" s="113" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="E186" s="104"/>
       <c r="F186" s="104"/>
@@ -26537,7 +27149,7 @@
     </row>
     <row r="188" spans="4:12">
       <c r="D188" s="110" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="E188" s="104"/>
       <c r="F188" s="104"/>
@@ -26563,7 +27175,7 @@
     </row>
     <row r="190" spans="4:12">
       <c r="D190" s="110" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="E190" s="104"/>
       <c r="F190" s="104"/>
@@ -26589,7 +27201,7 @@
     </row>
     <row r="192" spans="4:12">
       <c r="D192" s="103" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="E192" s="104"/>
       <c r="F192" s="104"/>
@@ -26615,7 +27227,7 @@
     </row>
     <row r="194" spans="4:12">
       <c r="D194" s="113" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="E194" s="104"/>
       <c r="F194" s="104"/>
@@ -26641,7 +27253,7 @@
     </row>
     <row r="196" spans="4:12">
       <c r="D196" s="103" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="E196" s="104"/>
       <c r="F196" s="104"/>
@@ -26667,7 +27279,7 @@
     </row>
     <row r="198" spans="4:12">
       <c r="D198" s="110" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="E198" s="104"/>
       <c r="F198" s="104"/>
@@ -26693,7 +27305,7 @@
     </row>
     <row r="200" spans="4:12">
       <c r="D200" s="103" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="E200" s="104"/>
       <c r="F200" s="104"/>
@@ -26719,7 +27331,7 @@
     </row>
     <row r="202" spans="4:12">
       <c r="D202" s="113" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="E202" s="104"/>
       <c r="F202" s="104"/>
@@ -26769,7 +27381,7 @@
     </row>
     <row r="206" spans="4:12">
       <c r="D206" s="103" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="E206" s="104"/>
       <c r="F206" s="104"/>
@@ -26782,7 +27394,7 @@
     </row>
     <row r="207" spans="4:12">
       <c r="D207" s="103" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="E207" s="104"/>
       <c r="F207" s="104"/>
@@ -26845,7 +27457,7 @@
     </row>
     <row r="212" spans="4:12">
       <c r="D212" s="107" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="E212" s="104"/>
       <c r="F212" s="104"/>
@@ -26858,7 +27470,7 @@
     </row>
     <row r="213" spans="4:12">
       <c r="D213" s="107" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="E213" s="104"/>
       <c r="F213" s="104"/>
@@ -26871,7 +27483,7 @@
     </row>
     <row r="214" spans="4:12">
       <c r="D214" s="107" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="E214" s="104"/>
       <c r="F214" s="104"/>
@@ -26895,7 +27507,7 @@
     </row>
     <row r="216" spans="4:12">
       <c r="D216" s="110" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="E216" s="104"/>
       <c r="F216" s="104"/>
@@ -26908,7 +27520,7 @@
     </row>
     <row r="217" spans="4:12">
       <c r="D217" s="110" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="E217" s="104"/>
       <c r="F217" s="104"/>
@@ -26932,7 +27544,7 @@
     </row>
     <row r="219" spans="4:12">
       <c r="D219" s="107" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="E219" s="104"/>
       <c r="F219" s="104"/>
@@ -26945,7 +27557,7 @@
     </row>
     <row r="220" spans="4:12">
       <c r="D220" s="107" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="E220" s="104"/>
       <c r="F220" s="104"/>
@@ -26958,7 +27570,7 @@
     </row>
     <row r="221" spans="4:12">
       <c r="D221" s="107" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="E221" s="104"/>
       <c r="F221" s="104"/>
@@ -26982,7 +27594,7 @@
     </row>
     <row r="223" spans="4:12">
       <c r="D223" s="107" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="E223" s="104"/>
       <c r="F223" s="104"/>
@@ -26995,7 +27607,7 @@
     </row>
     <row r="224" spans="4:12">
       <c r="D224" s="107" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="E224" s="104"/>
       <c r="F224" s="104"/>
@@ -27008,7 +27620,7 @@
     </row>
     <row r="225" spans="4:12">
       <c r="D225" s="107" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="E225" s="104"/>
       <c r="F225" s="104"/>
@@ -28224,23 +28836,23 @@
   <sheetData>
     <row r="17" spans="2:4">
       <c r="B17" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="18" spans="2:4">
       <c r="C18" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D18" t="s">
         <v>1009</v>
-      </c>
-      <c r="D18" t="s">
-        <v>1011</v>
       </c>
     </row>
     <row r="19" spans="2:4">
       <c r="C19" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D19" t="s">
         <v>1010</v>
-      </c>
-      <c r="D19" t="s">
-        <v>1012</v>
       </c>
     </row>
   </sheetData>
@@ -28308,11 +28920,11 @@
     </row>
     <row r="3" spans="2:7" ht="15.75" thickBot="1"/>
     <row r="4" spans="2:7">
-      <c r="C4" s="123" t="s">
+      <c r="C4" s="124" t="s">
         <v>911</v>
       </c>
-      <c r="D4" s="124"/>
-      <c r="E4" s="125"/>
+      <c r="D4" s="125"/>
+      <c r="E4" s="126"/>
       <c r="F4" t="s">
         <v>915</v>
       </c>
@@ -28321,9 +28933,9 @@
       </c>
     </row>
     <row r="5" spans="2:7" ht="15.75" thickBot="1">
-      <c r="C5" s="126"/>
-      <c r="D5" s="127"/>
-      <c r="E5" s="128"/>
+      <c r="C5" s="127"/>
+      <c r="D5" s="128"/>
+      <c r="E5" s="129"/>
       <c r="F5" t="s">
         <v>917</v>
       </c>
@@ -28332,11 +28944,11 @@
       </c>
     </row>
     <row r="6" spans="2:7">
-      <c r="C6" s="123" t="s">
+      <c r="C6" s="124" t="s">
         <v>912</v>
       </c>
-      <c r="D6" s="124"/>
-      <c r="E6" s="125"/>
+      <c r="D6" s="125"/>
+      <c r="E6" s="126"/>
       <c r="F6" t="s">
         <v>915</v>
       </c>
@@ -28345,9 +28957,9 @@
       </c>
     </row>
     <row r="7" spans="2:7" ht="15.75" thickBot="1">
-      <c r="C7" s="126"/>
-      <c r="D7" s="127"/>
-      <c r="E7" s="128"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="128"/>
+      <c r="E7" s="129"/>
       <c r="F7" t="s">
         <v>917</v>
       </c>
@@ -28356,11 +28968,11 @@
       </c>
     </row>
     <row r="8" spans="2:7">
-      <c r="C8" s="123" t="s">
+      <c r="C8" s="124" t="s">
         <v>913</v>
       </c>
-      <c r="D8" s="124"/>
-      <c r="E8" s="125"/>
+      <c r="D8" s="125"/>
+      <c r="E8" s="126"/>
       <c r="F8" t="s">
         <v>915</v>
       </c>
@@ -28369,9 +28981,9 @@
       </c>
     </row>
     <row r="9" spans="2:7" ht="15.75" thickBot="1">
-      <c r="C9" s="126"/>
-      <c r="D9" s="127"/>
-      <c r="E9" s="128"/>
+      <c r="C9" s="127"/>
+      <c r="D9" s="128"/>
+      <c r="E9" s="129"/>
       <c r="F9" t="s">
         <v>917</v>
       </c>
@@ -28380,11 +28992,11 @@
       </c>
     </row>
     <row r="10" spans="2:7">
-      <c r="C10" s="123" t="s">
+      <c r="C10" s="124" t="s">
         <v>914</v>
       </c>
-      <c r="D10" s="124"/>
-      <c r="E10" s="125"/>
+      <c r="D10" s="125"/>
+      <c r="E10" s="126"/>
       <c r="F10" t="s">
         <v>915</v>
       </c>
@@ -28393,9 +29005,9 @@
       </c>
     </row>
     <row r="11" spans="2:7" ht="15.75" thickBot="1">
-      <c r="C11" s="126"/>
-      <c r="D11" s="127"/>
-      <c r="E11" s="128"/>
+      <c r="C11" s="127"/>
+      <c r="D11" s="128"/>
+      <c r="E11" s="129"/>
       <c r="F11" t="s">
         <v>917</v>
       </c>
@@ -28416,7 +29028,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:F157"/>
+  <dimension ref="B2:I188"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="10.140625" customWidth="1"/>
@@ -28424,17 +29036,17 @@
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="3" spans="2:5">
       <c r="C3" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="5" spans="2:5">
       <c r="C5" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="7" spans="2:5">
@@ -28444,172 +29056,172 @@
     </row>
     <row r="8" spans="2:5">
       <c r="C8" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="E8" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="10" spans="2:5">
       <c r="C10" s="17" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="E10" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="12" spans="2:5">
       <c r="C12" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="13" spans="2:5">
       <c r="C13" s="17" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="E13" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="14" spans="2:5">
       <c r="C14" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="15" spans="2:5">
       <c r="C15" s="17" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="E15" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="18" spans="2:5">
       <c r="B18" s="117" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="19" spans="2:5">
       <c r="C19" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="20" spans="2:5">
       <c r="C20" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="23" spans="2:5">
       <c r="B23" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="24" spans="2:5">
       <c r="C24" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="25" spans="2:5">
       <c r="C25" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="26" spans="2:5">
       <c r="C26" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="28" spans="2:5">
       <c r="C28" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="29" spans="2:5">
       <c r="D29" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="30" spans="2:5">
       <c r="E30" s="80" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="31" spans="2:5">
       <c r="E31" s="80" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="32" spans="2:5">
       <c r="E32" s="80" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="34" spans="2:5">
       <c r="B34" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="35" spans="2:5">
       <c r="C35" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="36" spans="2:5">
       <c r="C36" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="38" spans="2:5">
       <c r="C38" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="39" spans="2:5">
       <c r="D39" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="40" spans="2:5">
       <c r="E40" s="80" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="41" spans="2:5">
       <c r="E41" s="80" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="42" spans="2:5">
       <c r="E42" s="80" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="43" spans="2:5">
       <c r="E43" s="80" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="45" spans="2:5">
       <c r="B45" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="46" spans="2:5">
       <c r="C46" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
       <c r="D46" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="48" spans="2:5">
       <c r="C48" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="49" spans="2:6">
       <c r="C49" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="51" spans="2:6">
@@ -28624,28 +29236,28 @@
     </row>
     <row r="53" spans="2:6">
       <c r="C53" s="17" t="s">
+        <v>1123</v>
+      </c>
+      <c r="F53" t="s">
         <v>1126</v>
-      </c>
-      <c r="F53" t="s">
-        <v>1129</v>
       </c>
     </row>
     <row r="54" spans="2:6">
       <c r="C54" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="C56" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="F56" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="57" spans="2:6">
       <c r="C57" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="59" spans="2:6">
@@ -28660,53 +29272,53 @@
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="17" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C62" t="s">
         <v>1133</v>
-      </c>
-      <c r="C62" t="s">
-        <v>1136</v>
       </c>
     </row>
     <row r="63" spans="2:6">
       <c r="B63" s="17" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C63" t="s">
         <v>1134</v>
-      </c>
-      <c r="C63" t="s">
-        <v>1137</v>
       </c>
     </row>
     <row r="64" spans="2:6">
       <c r="C64" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="67" spans="2:4">
       <c r="B67" s="17" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="68" spans="2:4">
       <c r="C68" s="80" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="69" spans="2:4">
-      <c r="C69" s="135" t="s">
-        <v>1140</v>
+      <c r="C69" s="118" t="s">
+        <v>1137</v>
       </c>
     </row>
     <row r="70" spans="2:4">
       <c r="C70" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="73" spans="2:4">
       <c r="B73" s="7" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="74" spans="2:4">
       <c r="C74" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="76" spans="2:4">
@@ -28716,17 +29328,17 @@
     </row>
     <row r="77" spans="2:4">
       <c r="D77" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="79" spans="2:4">
       <c r="C79" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="80" spans="2:4">
       <c r="D80" s="50" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="82" spans="2:4">
@@ -28736,17 +29348,17 @@
     </row>
     <row r="83" spans="2:4">
       <c r="D83" s="17" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="85" spans="2:4">
       <c r="D85" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="86" spans="2:4">
       <c r="D86" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="87" spans="2:4">
@@ -28761,22 +29373,22 @@
     </row>
     <row r="90" spans="2:4">
       <c r="D90" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="91" spans="2:4">
       <c r="D91" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="92" spans="2:4">
       <c r="D92" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="93" spans="2:4">
       <c r="D93" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="94" spans="2:4">
@@ -28786,22 +29398,22 @@
     </row>
     <row r="95" spans="2:4">
       <c r="B95" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="96" spans="2:4">
       <c r="C96" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="99" spans="2:4">
       <c r="B99" s="6" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="100" spans="2:4">
       <c r="C100" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="102" spans="2:4">
@@ -28811,17 +29423,17 @@
     </row>
     <row r="103" spans="2:4">
       <c r="D103" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="104" spans="2:4">
       <c r="C104" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="105" spans="2:4">
       <c r="D105" s="50" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="107" spans="2:4">
@@ -28831,7 +29443,7 @@
     </row>
     <row r="108" spans="2:4">
       <c r="D108" s="17" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="109" spans="2:4">
@@ -28839,7 +29451,7 @@
     </row>
     <row r="110" spans="2:4">
       <c r="D110" s="50" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="111" spans="2:4">
@@ -28847,17 +29459,17 @@
     </row>
     <row r="112" spans="2:4">
       <c r="D112" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="113" spans="2:4">
       <c r="D113" s="17" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="114" spans="2:4">
       <c r="D114" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="115" spans="2:4">
@@ -28867,17 +29479,17 @@
     </row>
     <row r="116" spans="2:4">
       <c r="D116" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="118" spans="2:4">
       <c r="B118" s="6" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="119" spans="2:4">
       <c r="C119" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="121" spans="2:4">
@@ -28887,17 +29499,17 @@
     </row>
     <row r="122" spans="2:4">
       <c r="D122" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="123" spans="2:4">
       <c r="C123" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="124" spans="2:4">
       <c r="D124" s="50" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="126" spans="2:4">
@@ -28907,7 +29519,7 @@
     </row>
     <row r="127" spans="2:4">
       <c r="D127" s="17" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="128" spans="2:4">
@@ -28915,7 +29527,7 @@
     </row>
     <row r="129" spans="4:6">
       <c r="D129" s="50" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="130" spans="4:6">
@@ -28923,22 +29535,22 @@
     </row>
     <row r="131" spans="4:6">
       <c r="D131" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="132" spans="4:6">
       <c r="D132" s="17" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="133" spans="4:6">
       <c r="D133" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="134" spans="4:6">
       <c r="D134" s="50" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="135" spans="4:6">
@@ -28948,10 +29560,10 @@
     </row>
     <row r="136" spans="4:6">
       <c r="D136" s="17" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="F136" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="137" spans="4:6">
@@ -28961,7 +29573,7 @@
     </row>
     <row r="138" spans="4:6">
       <c r="D138" s="50" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="139" spans="4:6">
@@ -28971,7 +29583,7 @@
     </row>
     <row r="140" spans="4:6">
       <c r="D140" s="17" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="141" spans="4:6">
@@ -28986,52 +29598,183 @@
     </row>
     <row r="143" spans="4:6">
       <c r="D143" t="s">
-        <v>1161</v>
-      </c>
-    </row>
-    <row r="146" spans="2:4">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="146" spans="2:9">
       <c r="B146" s="56" t="s">
-        <v>1171</v>
-      </c>
-    </row>
-    <row r="147" spans="2:4">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="147" spans="2:9">
       <c r="C147" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="148" spans="2:4">
+    <row r="148" spans="2:9">
       <c r="D148" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="149" spans="2:9">
+      <c r="D149" s="80" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="151" spans="2:9">
+      <c r="C151" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="152" spans="2:9">
+      <c r="D152" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="154" spans="2:9">
+      <c r="C154" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="155" spans="2:9">
+      <c r="D155" s="17" t="s">
         <v>1173</v>
       </c>
     </row>
-    <row r="149" spans="2:4">
-      <c r="D149" s="80" t="s">
+    <row r="157" spans="2:9">
+      <c r="C157" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="158" spans="2:9">
+      <c r="D158" t="s">
+        <v>1178</v>
+      </c>
+      <c r="I158" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="159" spans="2:9">
+      <c r="D159" s="17" t="s">
+        <v>1179</v>
+      </c>
+      <c r="I159" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="160" spans="2:9">
+      <c r="E160" t="s">
+        <v>1188</v>
+      </c>
+      <c r="I160" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="161" spans="2:6">
+      <c r="D161" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="162" spans="2:6">
+      <c r="D162" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="164" spans="2:6">
+      <c r="D164" s="17" t="s">
+        <v>1184</v>
+      </c>
+      <c r="F164" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="165" spans="2:6">
+      <c r="D165" s="17" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F165" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="167" spans="2:6">
+      <c r="B167" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="168" spans="2:6">
+      <c r="C168" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="169" spans="2:6">
+      <c r="C169" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="171" spans="2:6">
+      <c r="C171" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="172" spans="2:6">
+      <c r="D172" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="176" spans="2:6">
+      <c r="B176" s="6" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="177" spans="2:5">
+      <c r="C177" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="178" spans="2:5">
+      <c r="C178" s="80" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="179" spans="2:5">
+      <c r="C179" s="80" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="182" spans="2:5">
+      <c r="B182" s="57" t="s">
         <v>1174</v>
       </c>
     </row>
-    <row r="151" spans="2:4">
-      <c r="C151" t="s">
-        <v>1172</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4">
-      <c r="D152" t="s">
-        <v>1175</v>
-      </c>
-    </row>
-    <row r="154" spans="2:4">
-      <c r="C154" t="s">
-        <v>1176</v>
-      </c>
-    </row>
-    <row r="155" spans="2:4">
-      <c r="D155" s="17" t="s">
-        <v>1177</v>
-      </c>
-    </row>
-    <row r="157" spans="2:4">
-      <c r="C157" t="s">
-        <v>611</v>
+    <row r="183" spans="2:5">
+      <c r="C183" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="184" spans="2:5">
+      <c r="C184" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="186" spans="2:5">
+      <c r="C186" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="187" spans="2:5">
+      <c r="D187" t="s">
+        <v>1204</v>
+      </c>
+      <c r="E187" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="188" spans="2:5">
+      <c r="D188" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E188" t="s">
+        <v>1207</v>
       </c>
     </row>
   </sheetData>
@@ -29042,7 +29785,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:L30"/>
+  <dimension ref="B2:L33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:12">
@@ -29057,7 +29800,7 @@
     </row>
     <row r="4" spans="2:12">
       <c r="D4" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="6" spans="2:12">
@@ -29066,105 +29809,127 @@
       </c>
     </row>
     <row r="7" spans="2:12">
+      <c r="C7" s="136" t="s">
+        <v>441</v>
+      </c>
       <c r="D7" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12">
+      <c r="C8" s="136" t="s">
+        <v>442</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12">
+      <c r="D9" t="s">
+        <v>975</v>
+      </c>
+      <c r="L9" t="s">
         <v>974</v>
       </c>
     </row>
-    <row r="8" spans="2:12">
-      <c r="D8" t="s">
-        <v>976</v>
-      </c>
-      <c r="L8" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12">
-      <c r="B10" t="s">
-        <v>978</v>
-      </c>
-    </row>
     <row r="11" spans="2:12">
-      <c r="C11" t="s">
+      <c r="B11" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12">
+      <c r="C12" t="s">
         <v>973</v>
       </c>
     </row>
-    <row r="12" spans="2:12">
-      <c r="D12" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12">
-      <c r="C14" t="s">
+    <row r="13" spans="2:12">
+      <c r="D13" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12">
+      <c r="C15" t="s">
         <v>972</v>
       </c>
     </row>
-    <row r="15" spans="2:12">
-      <c r="D15" t="s">
-        <v>979</v>
-      </c>
-    </row>
     <row r="16" spans="2:12">
+      <c r="C16" s="136" t="s">
+        <v>441</v>
+      </c>
       <c r="D16" t="s">
-        <v>980</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="17" spans="2:6">
       <c r="D17" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="D18" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6">
+      <c r="C19" s="136" t="s">
+        <v>442</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="D22" t="s">
+        <v>981</v>
+      </c>
+      <c r="F22" t="s">
         <v>982</v>
       </c>
     </row>
-    <row r="19" spans="2:6">
-      <c r="D19" t="s">
+    <row r="23" spans="2:6">
+      <c r="D23" t="s">
         <v>983</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F23" t="s">
         <v>984</v>
       </c>
     </row>
-    <row r="20" spans="2:6">
-      <c r="D20" t="s">
+    <row r="24" spans="2:6">
+      <c r="D24" t="s">
         <v>985</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F24" t="s">
         <v>986</v>
       </c>
     </row>
-    <row r="21" spans="2:6">
-      <c r="D21" t="s">
+    <row r="27" spans="2:6">
+      <c r="B27" t="s">
         <v>987</v>
       </c>
-      <c r="F21" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6">
-      <c r="B24" t="s">
+    </row>
+    <row r="28" spans="2:6">
+      <c r="C28" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="D29" t="s">
         <v>989</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6">
-      <c r="C25" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6">
-      <c r="D26" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6">
-      <c r="D27" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6">
-      <c r="C29" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="D30" t="s">
-        <v>992</v>
+        <v>988</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="C32" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="33" spans="4:4">
+      <c r="D33" t="s">
+        <v>990</v>
       </c>
     </row>
   </sheetData>
@@ -31280,22 +32045,22 @@
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" s="79" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
     </row>
     <row r="3" spans="2:3">
       <c r="C3" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="C4" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="6" spans="2:3">
       <c r="C6" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
     </row>
     <row r="8" spans="2:3">
@@ -31305,42 +32070,42 @@
     </row>
     <row r="9" spans="2:3">
       <c r="C9" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
     </row>
     <row r="11" spans="2:3">
       <c r="C11" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
     </row>
     <row r="12" spans="2:3">
       <c r="C12" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="13" spans="2:3">
       <c r="C13" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="18" spans="2:3">
       <c r="B18" s="43" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="19" spans="2:3">
       <c r="C19" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="20" spans="2:3">
       <c r="C20" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="22" spans="2:3">
       <c r="C22" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
     </row>
     <row r="24" spans="2:3">
@@ -31350,7 +32115,7 @@
     </row>
     <row r="25" spans="2:3">
       <c r="C25" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="27" spans="2:3">
@@ -31360,17 +32125,17 @@
     </row>
     <row r="28" spans="2:3">
       <c r="C28" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="29" spans="2:3">
       <c r="C29" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="31" spans="2:3">
       <c r="C31" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
     </row>
   </sheetData>
@@ -31513,7 +32278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:G142"/>
+  <dimension ref="B1:G143"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col min="3" max="3" width="62.85546875" customWidth="1"/>
@@ -32299,7 +33064,7 @@
         <v>11.1</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="D52" s="115"/>
       <c r="E52" s="16"/>
@@ -32553,7 +33318,7 @@
         <v>16.7</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="D72" s="42">
         <v>1</v>
@@ -32587,7 +33352,7 @@
         <v>16.899999999999999</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="D74" s="42">
         <v>1</v>
@@ -32599,10 +33364,10 @@
     </row>
     <row r="75" spans="2:6" hidden="1" outlineLevel="1">
       <c r="B75" s="52" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="D75" s="42">
         <v>1</v>
@@ -32614,10 +33379,10 @@
     </row>
     <row r="76" spans="2:6" ht="43.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="B76" s="52" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="D76" s="115">
         <v>0</v>
@@ -32689,7 +33454,7 @@
         <v>17.5</v>
       </c>
       <c r="C82" s="116" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="D82" s="6"/>
       <c r="E82" s="6"/>
@@ -32817,7 +33582,7 @@
         <v>21.1</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="D92" s="42">
         <v>1</v>
@@ -32832,7 +33597,7 @@
         <v>21.2</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="D93" s="51">
         <v>0.99</v>
@@ -32847,7 +33612,7 @@
         <v>21.3</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="D94" s="42">
         <v>1</v>
@@ -32862,7 +33627,7 @@
         <v>21.4</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="D95" s="42">
         <v>1</v>
@@ -32877,7 +33642,7 @@
         <v>21.5</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="D96" s="42">
         <v>1</v>
@@ -32892,7 +33657,7 @@
         <v>21.6</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="D97" s="42">
         <v>1</v>
@@ -32907,7 +33672,7 @@
         <v>21.7</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="D98" s="42">
         <v>1</v>
@@ -32921,11 +33686,11 @@
       <c r="B99" s="5">
         <v>21.8</v>
       </c>
-      <c r="C99" s="56" t="s">
-        <v>1171</v>
-      </c>
-      <c r="D99" s="51">
-        <v>0</v>
+      <c r="C99" s="57" t="s">
+        <v>1176</v>
+      </c>
+      <c r="D99" s="42">
+        <v>1</v>
       </c>
       <c r="E99" s="6"/>
       <c r="F99" s="16" t="s">
@@ -32937,28 +33702,34 @@
         <v>21.9</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>1092</v>
-      </c>
-      <c r="D100" s="51">
-        <v>0</v>
+        <v>1199</v>
+      </c>
+      <c r="D100" s="42">
+        <v>1</v>
       </c>
       <c r="E100" s="6"/>
-      <c r="F100" s="6"/>
+      <c r="F100" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="101" spans="2:6">
       <c r="B101" s="52" t="s">
-        <v>1014</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>1089</v>
-      </c>
-      <c r="D101" s="51"/>
+        <v>1012</v>
+      </c>
+      <c r="C101" s="57" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D101" s="42">
+        <v>1</v>
+      </c>
       <c r="E101" s="6"/>
-      <c r="F101" s="6"/>
+      <c r="F101" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="52" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>1090</v>
@@ -32969,10 +33740,10 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="52" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>1091</v>
+        <v>1087</v>
       </c>
       <c r="D103" s="51"/>
       <c r="E103" s="6"/>
@@ -32980,10 +33751,10 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="52" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>1100</v>
+        <v>1088</v>
       </c>
       <c r="D104" s="51"/>
       <c r="E104" s="6"/>
@@ -32991,10 +33762,10 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="52" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>1101</v>
+        <v>1089</v>
       </c>
       <c r="D105" s="51"/>
       <c r="E105" s="6"/>
@@ -33002,10 +33773,10 @@
     </row>
     <row r="106" spans="2:6">
       <c r="B106" s="52" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="D106" s="51"/>
       <c r="E106" s="6"/>
@@ -33013,10 +33784,10 @@
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="52" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>1104</v>
+        <v>1099</v>
       </c>
       <c r="D107" s="51"/>
       <c r="E107" s="6"/>
@@ -33024,10 +33795,10 @@
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="52" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>1110</v>
+        <v>1101</v>
       </c>
       <c r="D108" s="51"/>
       <c r="E108" s="6"/>
@@ -33035,10 +33806,10 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="52" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>1117</v>
+        <v>1107</v>
       </c>
       <c r="D109" s="51"/>
       <c r="E109" s="6"/>
@@ -33046,10 +33817,10 @@
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="52" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
       <c r="D110" s="51"/>
       <c r="E110" s="6"/>
@@ -33057,16 +33828,18 @@
     </row>
     <row r="111" spans="2:6">
       <c r="B111" s="52" t="s">
-        <v>1114</v>
-      </c>
-      <c r="C111" s="6"/>
+        <v>1111</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>1115</v>
+      </c>
       <c r="D111" s="51"/>
       <c r="E111" s="6"/>
       <c r="F111" s="6"/>
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="52" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="51"/>
@@ -33075,64 +33848,58 @@
     </row>
     <row r="113" spans="2:7">
       <c r="B113" s="52" t="s">
-        <v>1116</v>
-      </c>
-      <c r="C113" s="6" t="s">
-        <v>432</v>
-      </c>
-      <c r="D113" s="6"/>
+        <v>1113</v>
+      </c>
+      <c r="C113" s="6"/>
+      <c r="D113" s="51"/>
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
     </row>
-    <row r="114" spans="2:7" ht="30">
+    <row r="114" spans="2:7">
       <c r="B114" s="52" t="s">
-        <v>1120</v>
-      </c>
-      <c r="C114" s="7" t="s">
-        <v>466</v>
+        <v>1117</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>432</v>
       </c>
       <c r="D114" s="6"/>
       <c r="E114" s="6"/>
       <c r="F114" s="6"/>
     </row>
-    <row r="115" spans="2:7">
-      <c r="B115" s="5" t="s">
+    <row r="115" spans="2:7" ht="30">
+      <c r="B115" s="52" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="D115" s="6"/>
+      <c r="E115" s="6"/>
+      <c r="F115" s="6"/>
+    </row>
+    <row r="116" spans="2:7">
+      <c r="B116" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="C115" s="6" t="s">
+      <c r="C116" s="6" t="s">
         <v>323</v>
-      </c>
-      <c r="D115" s="42">
-        <v>1</v>
-      </c>
-      <c r="E115" s="16" t="s">
-        <v>463</v>
-      </c>
-      <c r="F115" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="116" spans="2:7">
-      <c r="B116" s="5">
-        <v>23.1</v>
-      </c>
-      <c r="C116" s="6" t="s">
-        <v>971</v>
       </c>
       <c r="D116" s="42">
         <v>1</v>
       </c>
-      <c r="E116" s="16"/>
-      <c r="F116" s="16" t="s">
-        <v>14</v>
+      <c r="E116" s="16" t="s">
+        <v>463</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="117" spans="2:7">
       <c r="B117" s="5">
-        <v>23.2</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>978</v>
+        <v>23.1</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>971</v>
       </c>
       <c r="D117" s="42">
         <v>1</v>
@@ -33144,55 +33911,55 @@
     </row>
     <row r="118" spans="2:7">
       <c r="B118" s="5">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>989</v>
-      </c>
-      <c r="D118" s="51">
-        <v>0.99</v>
+        <v>977</v>
+      </c>
+      <c r="D118" s="42">
+        <v>1</v>
       </c>
       <c r="E118" s="16"/>
       <c r="F118" s="16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="119" spans="2:7" ht="30">
-      <c r="B119" s="5" t="s">
+    <row r="119" spans="2:7">
+      <c r="B119" s="5">
+        <v>23.3</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="D119" s="51">
+        <v>0.99</v>
+      </c>
+      <c r="E119" s="16"/>
+      <c r="F119" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="120" spans="2:7" ht="30">
+      <c r="B120" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="C119" s="7" t="s">
+      <c r="C120" s="7" t="s">
         <v>725</v>
-      </c>
-      <c r="D119" s="42">
-        <v>1</v>
-      </c>
-      <c r="E119" s="16" t="s">
-        <v>463</v>
-      </c>
-      <c r="F119" s="16"/>
-    </row>
-    <row r="120" spans="2:7">
-      <c r="B120" s="5">
-        <v>24.1</v>
-      </c>
-      <c r="C120" s="7" t="s">
-        <v>726</v>
       </c>
       <c r="D120" s="42">
         <v>1</v>
       </c>
-      <c r="E120" s="16"/>
-      <c r="F120" s="16" t="s">
-        <v>14</v>
-      </c>
+      <c r="E120" s="16" t="s">
+        <v>463</v>
+      </c>
+      <c r="F120" s="16"/>
     </row>
     <row r="121" spans="2:7">
       <c r="B121" s="5">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>770</v>
+        <v>726</v>
       </c>
       <c r="D121" s="42">
         <v>1</v>
@@ -33201,14 +33968,13 @@
       <c r="F121" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G121" s="48"/>
     </row>
     <row r="122" spans="2:7">
-      <c r="B122" s="5" t="s">
-        <v>471</v>
-      </c>
-      <c r="C122" s="6" t="s">
-        <v>932</v>
+      <c r="B122" s="5">
+        <v>24.2</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>770</v>
       </c>
       <c r="D122" s="42">
         <v>1</v>
@@ -33217,13 +33983,14 @@
       <c r="F122" s="16" t="s">
         <v>14</v>
       </c>
+      <c r="G122" s="48"/>
     </row>
     <row r="123" spans="2:7">
       <c r="B123" s="5" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>475</v>
+        <v>932</v>
       </c>
       <c r="D123" s="42">
         <v>1</v>
@@ -33234,11 +34001,11 @@
       </c>
     </row>
     <row r="124" spans="2:7">
-      <c r="B124" s="5">
-        <v>26.1</v>
+      <c r="B124" s="5" t="s">
+        <v>473</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>939</v>
+        <v>475</v>
       </c>
       <c r="D124" s="42">
         <v>1</v>
@@ -33248,44 +34015,44 @@
         <v>14</v>
       </c>
     </row>
-    <row r="125" spans="2:7" ht="45">
-      <c r="B125" s="5" t="s">
+    <row r="125" spans="2:7">
+      <c r="B125" s="5">
+        <v>26.1</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>939</v>
+      </c>
+      <c r="D125" s="42">
+        <v>1</v>
+      </c>
+      <c r="E125" s="16"/>
+      <c r="F125" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="126" spans="2:7" ht="45">
+      <c r="B126" s="5" t="s">
         <v>481</v>
-      </c>
-      <c r="C125" s="79" t="s">
-        <v>995</v>
-      </c>
-      <c r="D125" s="51">
-        <v>0.5</v>
-      </c>
-      <c r="E125" s="16" t="s">
-        <v>478</v>
-      </c>
-      <c r="F125" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="126" spans="2:7">
-      <c r="B126" s="5">
-        <v>27.1</v>
       </c>
       <c r="C126" s="79" t="s">
         <v>993</v>
       </c>
       <c r="D126" s="51">
-        <v>0.99</v>
-      </c>
-      <c r="E126" s="16"/>
-      <c r="F126" s="16" t="s">
-        <v>14</v>
+        <v>0.5</v>
+      </c>
+      <c r="E126" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="F126" s="6" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="127" spans="2:7">
       <c r="B127" s="5">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="C127" s="79" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="D127" s="51">
         <v>0.99</v>
@@ -33295,27 +34062,27 @@
         <v>14</v>
       </c>
     </row>
-    <row r="128" spans="2:7" ht="30">
-      <c r="B128" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="C128" s="7" t="s">
-        <v>940</v>
-      </c>
-      <c r="D128" s="42">
-        <v>1</v>
+    <row r="128" spans="2:7">
+      <c r="B128" s="5">
+        <v>27.2</v>
+      </c>
+      <c r="C128" s="79" t="s">
+        <v>992</v>
+      </c>
+      <c r="D128" s="51">
+        <v>0.99</v>
       </c>
       <c r="E128" s="16"/>
       <c r="F128" s="16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="129" spans="2:7">
+    <row r="129" spans="2:7" ht="30">
       <c r="B129" s="5" t="s">
-        <v>483</v>
-      </c>
-      <c r="C129" s="6" t="s">
-        <v>807</v>
+        <v>482</v>
+      </c>
+      <c r="C129" s="7" t="s">
+        <v>940</v>
       </c>
       <c r="D129" s="42">
         <v>1</v>
@@ -33326,11 +34093,11 @@
       </c>
     </row>
     <row r="130" spans="2:7">
-      <c r="B130" s="5">
-        <v>29.1</v>
+      <c r="B130" s="5" t="s">
+        <v>483</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>933</v>
+        <v>807</v>
       </c>
       <c r="D130" s="42">
         <v>1</v>
@@ -33341,11 +34108,11 @@
       </c>
     </row>
     <row r="131" spans="2:7">
-      <c r="B131" s="5" t="s">
-        <v>484</v>
-      </c>
-      <c r="C131" s="7" t="s">
-        <v>804</v>
+      <c r="B131" s="5">
+        <v>29.1</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>933</v>
       </c>
       <c r="D131" s="42">
         <v>1</v>
@@ -33356,11 +34123,11 @@
       </c>
     </row>
     <row r="132" spans="2:7">
-      <c r="B132" s="5">
-        <v>30.1</v>
+      <c r="B132" s="5" t="s">
+        <v>484</v>
       </c>
       <c r="C132" s="7" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="D132" s="42">
         <v>1</v>
@@ -33372,10 +34139,10 @@
     </row>
     <row r="133" spans="2:7">
       <c r="B133" s="5">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="C133" s="7" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D133" s="42">
         <v>1</v>
@@ -33384,14 +34151,13 @@
       <c r="F133" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G133" s="48"/>
     </row>
     <row r="134" spans="2:7">
       <c r="B134" s="5">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="D134" s="42">
         <v>1</v>
@@ -33400,31 +34166,32 @@
       <c r="F134" s="16" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="135" spans="2:7" ht="30">
-      <c r="B135" s="5" t="s">
-        <v>485</v>
+      <c r="G134" s="48"/>
+    </row>
+    <row r="135" spans="2:7">
+      <c r="B135" s="5">
+        <v>30.3</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>472</v>
-      </c>
-      <c r="D135" s="51">
-        <v>0.05</v>
+        <v>803</v>
+      </c>
+      <c r="D135" s="42">
+        <v>1</v>
       </c>
       <c r="E135" s="16"/>
       <c r="F135" s="16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="136" spans="2:7">
+    <row r="136" spans="2:7" ht="30">
       <c r="B136" s="5" t="s">
-        <v>771</v>
+        <v>485</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>772</v>
-      </c>
-      <c r="D136" s="42">
-        <v>1</v>
+        <v>472</v>
+      </c>
+      <c r="D136" s="51">
+        <v>0.05</v>
       </c>
       <c r="E136" s="16"/>
       <c r="F136" s="16" t="s">
@@ -33433,19 +34200,25 @@
     </row>
     <row r="137" spans="2:7">
       <c r="B137" s="5" t="s">
-        <v>1017</v>
+        <v>771</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>1018</v>
-      </c>
-      <c r="D137" s="42"/>
+        <v>772</v>
+      </c>
+      <c r="D137" s="42">
+        <v>1</v>
+      </c>
       <c r="E137" s="16"/>
-      <c r="F137" s="16"/>
+      <c r="F137" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="138" spans="2:7">
-      <c r="B138" s="5"/>
+      <c r="B138" s="5" t="s">
+        <v>1015</v>
+      </c>
       <c r="C138" s="7" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="D138" s="42"/>
       <c r="E138" s="16"/>
@@ -33454,7 +34227,7 @@
     <row r="139" spans="2:7">
       <c r="B139" s="5"/>
       <c r="C139" s="7" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="D139" s="42"/>
       <c r="E139" s="16"/>
@@ -33463,7 +34236,7 @@
     <row r="140" spans="2:7">
       <c r="B140" s="5"/>
       <c r="C140" s="7" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="D140" s="42"/>
       <c r="E140" s="16"/>
@@ -33471,23 +34244,32 @@
     </row>
     <row r="141" spans="2:7">
       <c r="B141" s="5"/>
-      <c r="C141" s="7"/>
+      <c r="C141" s="7" t="s">
+        <v>1019</v>
+      </c>
       <c r="D141" s="42"/>
       <c r="E141" s="16"/>
       <c r="F141" s="16"/>
     </row>
     <row r="142" spans="2:7">
-      <c r="B142" s="77" t="s">
+      <c r="B142" s="5"/>
+      <c r="C142" s="7"/>
+      <c r="D142" s="42"/>
+      <c r="E142" s="16"/>
+      <c r="F142" s="16"/>
+    </row>
+    <row r="143" spans="2:7">
+      <c r="B143" s="77" t="s">
         <v>469</v>
       </c>
-      <c r="C142" s="57" t="s">
+      <c r="C143" s="57" t="s">
         <v>468</v>
       </c>
-      <c r="D142" s="1"/>
-      <c r="E142" s="49" t="s">
+      <c r="D143" s="1"/>
+      <c r="E143" s="49" t="s">
         <v>467</v>
       </c>
-      <c r="F142" s="1"/>
+      <c r="F143" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -33539,9 +34321,9 @@
     <hyperlink ref="F63" location="'#14'!B2" display="Link"/>
     <hyperlink ref="E65" r:id="rId7"/>
     <hyperlink ref="E80" r:id="rId8"/>
-    <hyperlink ref="E115" r:id="rId9"/>
-    <hyperlink ref="E119" r:id="rId10"/>
-    <hyperlink ref="E142" r:id="rId11"/>
+    <hyperlink ref="E116" r:id="rId9"/>
+    <hyperlink ref="E120" r:id="rId10"/>
+    <hyperlink ref="E143" r:id="rId11"/>
     <hyperlink ref="F49" location="'#9'!B2" display="Link"/>
     <hyperlink ref="F61" location="'#12'!B2" display="Link"/>
     <hyperlink ref="F66" location="'#16'!B2" display="Link"/>
@@ -33554,19 +34336,19 @@
     <hyperlink ref="F64" location="'#15'!B2" display="Link"/>
     <hyperlink ref="F71" location="'#16'!B89" display="Link"/>
     <hyperlink ref="F72" location="'#16'!B10" display="Link"/>
-    <hyperlink ref="F135" location="'#31'!B2" display="Link"/>
-    <hyperlink ref="F120" location="'#24'!B2" display="Link"/>
+    <hyperlink ref="F136" location="'#31'!B2" display="Link"/>
     <hyperlink ref="F121" location="'#24'!B2" display="Link"/>
-    <hyperlink ref="F121:G121" location="'#24'!B26" display="Link"/>
-    <hyperlink ref="F122" location="'#25'!B2" display="Link"/>
+    <hyperlink ref="F122" location="'#24'!B2" display="Link"/>
+    <hyperlink ref="F122:G122" location="'#24'!B26" display="Link"/>
+    <hyperlink ref="F123" location="'#25'!B2" display="Link"/>
     <hyperlink ref="F89" location="'#19'!B2" display="Link"/>
-    <hyperlink ref="F132" location="'#30'!B8" display="Link"/>
-    <hyperlink ref="F129" location="'#29'!B2" display="Link"/>
-    <hyperlink ref="F136" location="'#32'!B2" display="Link"/>
-    <hyperlink ref="F131" location="'#30'!B2" display="Link"/>
     <hyperlink ref="F133" location="'#30'!B8" display="Link"/>
-    <hyperlink ref="F133:G133" location="'#30'!B24" display="Link"/>
-    <hyperlink ref="F134" location="'#30'!B35" display="Link"/>
+    <hyperlink ref="F130" location="'#29'!B2" display="Link"/>
+    <hyperlink ref="F137" location="'#32'!B2" display="Link"/>
+    <hyperlink ref="F132" location="'#30'!B2" display="Link"/>
+    <hyperlink ref="F134" location="'#30'!B8" display="Link"/>
+    <hyperlink ref="F134:G134" location="'#30'!B24" display="Link"/>
+    <hyperlink ref="F135" location="'#30'!B35" display="Link"/>
     <hyperlink ref="F51" location="'#11'!B2" display="Link"/>
     <hyperlink ref="F53" location="'#11'!B4" display="Link"/>
     <hyperlink ref="F54" location="'#11'!B21" display="Link"/>
@@ -33575,15 +34357,15 @@
     <hyperlink ref="F28" location="'#4'!B35" display="Link"/>
     <hyperlink ref="F29" location="'#4'!B43" display="Link"/>
     <hyperlink ref="F90" location="'#20'!B2" display="Link"/>
-    <hyperlink ref="F123" location="'#26'!B2" display="Link"/>
-    <hyperlink ref="F130" location="'#29'!B30" display="Link"/>
-    <hyperlink ref="F128" location="'#28'!B17" display="Link"/>
-    <hyperlink ref="F124" location="'#26'!B22" display="Link"/>
-    <hyperlink ref="F116" location="'#23'!B2" display="Link"/>
-    <hyperlink ref="F117" location="'#23'!B10" display="Link"/>
-    <hyperlink ref="F118" location="'#23'!B24" display="Link"/>
-    <hyperlink ref="F126" location="'#27'!B2" display="Link"/>
-    <hyperlink ref="F127" location="'#27'!B18" display="Link"/>
+    <hyperlink ref="F124" location="'#26'!B2" display="Link"/>
+    <hyperlink ref="F131" location="'#29'!B30" display="Link"/>
+    <hyperlink ref="F129" location="'#28'!B17" display="Link"/>
+    <hyperlink ref="F125" location="'#26'!B22" display="Link"/>
+    <hyperlink ref="F117" location="'#23'!B2" display="Link"/>
+    <hyperlink ref="F118" location="'#23'!B10" display="Link"/>
+    <hyperlink ref="F119" location="'#23'!B24" display="Link"/>
+    <hyperlink ref="F127" location="'#27'!B2" display="Link"/>
+    <hyperlink ref="F128" location="'#27'!B18" display="Link"/>
     <hyperlink ref="F92" location="'#21'!B2" display="Link"/>
     <hyperlink ref="F74" location="'#16'!D109" display="Link"/>
     <hyperlink ref="F75" location="'#16'!D168" display="Link"/>
@@ -33594,6 +34376,8 @@
     <hyperlink ref="F97" location="'#21'!B99" display="Link"/>
     <hyperlink ref="F98" location="'#21'!B118" display="Link"/>
     <hyperlink ref="F99" location="'#21'!B146" display="Link"/>
+    <hyperlink ref="F100" location="'#21'!B176" display="Link"/>
+    <hyperlink ref="F101" location="'#21'!B182" display="Link"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId12"/>
@@ -33734,7 +34518,7 @@
     </row>
     <row r="34" spans="3:3">
       <c r="C34" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="35" spans="3:3">
@@ -33972,21 +34756,21 @@
       <c r="D16" t="s">
         <v>710</v>
       </c>
-      <c r="I16" s="129" t="s">
+      <c r="I16" s="130" t="s">
         <v>714</v>
       </c>
-      <c r="J16" s="130"/>
+      <c r="J16" s="131"/>
     </row>
     <row r="17" spans="3:10" ht="15" customHeight="1">
-      <c r="I17" s="131"/>
-      <c r="J17" s="132"/>
+      <c r="I17" s="132"/>
+      <c r="J17" s="133"/>
     </row>
     <row r="18" spans="3:10">
       <c r="D18" t="s">
         <v>711</v>
       </c>
-      <c r="I18" s="133"/>
-      <c r="J18" s="134"/>
+      <c r="I18" s="134"/>
+      <c r="J18" s="135"/>
     </row>
     <row r="19" spans="3:10">
       <c r="C19" t="s">
@@ -34405,7 +35189,7 @@
       <c r="D12" s="11"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" thickBot="1">
-      <c r="C13" s="118" t="s">
+      <c r="C13" s="119" t="s">
         <v>78</v>
       </c>
       <c r="D13" s="26" t="s">
@@ -34422,7 +35206,7 @@
       <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:10" ht="15.75" thickBot="1">
-      <c r="C14" s="119"/>
+      <c r="C14" s="120"/>
       <c r="D14" s="23" t="s">
         <v>65</v>
       </c>
@@ -34438,7 +35222,7 @@
       <c r="J14" s="25"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="C15" s="119"/>
+      <c r="C15" s="120"/>
       <c r="D15" s="26" t="s">
         <v>66</v>
       </c>
@@ -34453,7 +35237,7 @@
       <c r="I15" s="28"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="C16" s="119"/>
+      <c r="C16" s="120"/>
       <c r="D16" s="29"/>
       <c r="E16" s="30" t="s">
         <v>74</v>
@@ -34464,7 +35248,7 @@
       <c r="I16" s="31"/>
     </row>
     <row r="17" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C17" s="120"/>
+      <c r="C17" s="121"/>
       <c r="D17" s="32"/>
       <c r="E17" s="33" t="s">
         <v>75</v>
@@ -34495,7 +35279,7 @@
       <c r="L18" s="25"/>
     </row>
     <row r="19" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C19" s="118" t="s">
+      <c r="C19" s="119" t="s">
         <v>78</v>
       </c>
       <c r="D19" s="23" t="s">
@@ -34506,7 +35290,7 @@
       </c>
     </row>
     <row r="20" spans="3:12">
-      <c r="C20" s="119"/>
+      <c r="C20" s="120"/>
       <c r="D20" s="26" t="s">
         <v>82</v>
       </c>
@@ -34515,7 +35299,7 @@
       </c>
     </row>
     <row r="21" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C21" s="120"/>
+      <c r="C21" s="121"/>
       <c r="D21" s="32"/>
       <c r="E21" s="40" t="s">
         <v>84</v>

--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1675" uniqueCount="1210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1679" uniqueCount="1214">
   <si>
     <t>No.</t>
   </si>
@@ -17316,6 +17316,18 @@
       </rPr>
       <t xml:space="preserve"> null để getInstance</t>
     </r>
+  </si>
+  <si>
+    <t>https://github.com/HoangAnh-Dinh/C-_Learning/tree/main/21.10</t>
+  </si>
+  <si>
+    <t>#34</t>
+  </si>
+  <si>
+    <t>Khác biệt giữa Multi-thread(Multithread , Multi thread) và Multi-process (Multiprocess/ Multi process)</t>
+  </si>
+  <si>
+    <t>Các loại IPC phổ biến trong C++</t>
   </si>
 </sst>
 </file>
@@ -17930,7 +17942,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -18164,6 +18176,9 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -18215,8 +18230,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -26035,16 +26050,16 @@
       </c>
     </row>
     <row r="89" spans="2:9" ht="54" customHeight="1">
-      <c r="B89" s="122" t="s">
+      <c r="B89" s="123" t="s">
         <v>616</v>
       </c>
-      <c r="C89" s="123"/>
-      <c r="D89" s="123"/>
-      <c r="E89" s="123"/>
-      <c r="F89" s="123"/>
-      <c r="G89" s="123"/>
-      <c r="H89" s="123"/>
-      <c r="I89" s="123"/>
+      <c r="C89" s="124"/>
+      <c r="D89" s="124"/>
+      <c r="E89" s="124"/>
+      <c r="F89" s="124"/>
+      <c r="G89" s="124"/>
+      <c r="H89" s="124"/>
+      <c r="I89" s="124"/>
     </row>
     <row r="91" spans="2:9">
       <c r="B91" t="s">
@@ -28920,11 +28935,11 @@
     </row>
     <row r="3" spans="2:7" ht="15.75" thickBot="1"/>
     <row r="4" spans="2:7">
-      <c r="C4" s="124" t="s">
+      <c r="C4" s="125" t="s">
         <v>911</v>
       </c>
-      <c r="D4" s="125"/>
-      <c r="E4" s="126"/>
+      <c r="D4" s="126"/>
+      <c r="E4" s="127"/>
       <c r="F4" t="s">
         <v>915</v>
       </c>
@@ -28933,9 +28948,9 @@
       </c>
     </row>
     <row r="5" spans="2:7" ht="15.75" thickBot="1">
-      <c r="C5" s="127"/>
-      <c r="D5" s="128"/>
-      <c r="E5" s="129"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="129"/>
+      <c r="E5" s="130"/>
       <c r="F5" t="s">
         <v>917</v>
       </c>
@@ -28944,11 +28959,11 @@
       </c>
     </row>
     <row r="6" spans="2:7">
-      <c r="C6" s="124" t="s">
+      <c r="C6" s="125" t="s">
         <v>912</v>
       </c>
-      <c r="D6" s="125"/>
-      <c r="E6" s="126"/>
+      <c r="D6" s="126"/>
+      <c r="E6" s="127"/>
       <c r="F6" t="s">
         <v>915</v>
       </c>
@@ -28957,9 +28972,9 @@
       </c>
     </row>
     <row r="7" spans="2:7" ht="15.75" thickBot="1">
-      <c r="C7" s="127"/>
-      <c r="D7" s="128"/>
-      <c r="E7" s="129"/>
+      <c r="C7" s="128"/>
+      <c r="D7" s="129"/>
+      <c r="E7" s="130"/>
       <c r="F7" t="s">
         <v>917</v>
       </c>
@@ -28968,11 +28983,11 @@
       </c>
     </row>
     <row r="8" spans="2:7">
-      <c r="C8" s="124" t="s">
+      <c r="C8" s="125" t="s">
         <v>913</v>
       </c>
-      <c r="D8" s="125"/>
-      <c r="E8" s="126"/>
+      <c r="D8" s="126"/>
+      <c r="E8" s="127"/>
       <c r="F8" t="s">
         <v>915</v>
       </c>
@@ -28981,9 +28996,9 @@
       </c>
     </row>
     <row r="9" spans="2:7" ht="15.75" thickBot="1">
-      <c r="C9" s="127"/>
-      <c r="D9" s="128"/>
-      <c r="E9" s="129"/>
+      <c r="C9" s="128"/>
+      <c r="D9" s="129"/>
+      <c r="E9" s="130"/>
       <c r="F9" t="s">
         <v>917</v>
       </c>
@@ -28992,11 +29007,11 @@
       </c>
     </row>
     <row r="10" spans="2:7">
-      <c r="C10" s="124" t="s">
+      <c r="C10" s="125" t="s">
         <v>914</v>
       </c>
-      <c r="D10" s="125"/>
-      <c r="E10" s="126"/>
+      <c r="D10" s="126"/>
+      <c r="E10" s="127"/>
       <c r="F10" t="s">
         <v>915</v>
       </c>
@@ -29005,9 +29020,9 @@
       </c>
     </row>
     <row r="11" spans="2:7" ht="15.75" thickBot="1">
-      <c r="C11" s="127"/>
-      <c r="D11" s="128"/>
-      <c r="E11" s="129"/>
+      <c r="C11" s="128"/>
+      <c r="D11" s="129"/>
+      <c r="E11" s="130"/>
       <c r="F11" t="s">
         <v>917</v>
       </c>
@@ -29809,7 +29824,7 @@
       </c>
     </row>
     <row r="7" spans="2:12">
-      <c r="C7" s="136" t="s">
+      <c r="C7" s="119" t="s">
         <v>441</v>
       </c>
       <c r="D7" t="s">
@@ -29817,7 +29832,7 @@
       </c>
     </row>
     <row r="8" spans="2:12">
-      <c r="C8" s="136" t="s">
+      <c r="C8" s="119" t="s">
         <v>442</v>
       </c>
       <c r="D8" t="s">
@@ -29853,7 +29868,7 @@
       </c>
     </row>
     <row r="16" spans="2:12">
-      <c r="C16" s="136" t="s">
+      <c r="C16" s="119" t="s">
         <v>441</v>
       </c>
       <c r="D16" t="s">
@@ -29871,7 +29886,7 @@
       </c>
     </row>
     <row r="19" spans="2:6">
-      <c r="C19" s="136" t="s">
+      <c r="C19" s="119" t="s">
         <v>442</v>
       </c>
       <c r="D19" t="s">
@@ -32278,7 +32293,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:G143"/>
+  <dimension ref="B1:G144"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col min="3" max="3" width="62.85546875" customWidth="1"/>
@@ -33722,7 +33737,9 @@
       <c r="D101" s="42">
         <v>1</v>
       </c>
-      <c r="E101" s="6"/>
+      <c r="E101" s="16" t="s">
+        <v>1210</v>
+      </c>
       <c r="F101" s="16" t="s">
         <v>14</v>
       </c>
@@ -33931,7 +33948,7 @@
       <c r="C119" s="1" t="s">
         <v>987</v>
       </c>
-      <c r="D119" s="51">
+      <c r="D119" s="137">
         <v>0.99</v>
       </c>
       <c r="E119" s="16"/>
@@ -34251,25 +34268,38 @@
       <c r="E141" s="16"/>
       <c r="F141" s="16"/>
     </row>
-    <row r="142" spans="2:7">
-      <c r="B142" s="5"/>
-      <c r="C142" s="7"/>
+    <row r="142" spans="2:7" ht="30">
+      <c r="B142" s="5" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C142" s="7" t="s">
+        <v>1212</v>
+      </c>
       <c r="D142" s="42"/>
       <c r="E142" s="16"/>
       <c r="F142" s="16"/>
     </row>
     <row r="143" spans="2:7">
-      <c r="B143" s="77" t="s">
+      <c r="B143" s="5"/>
+      <c r="C143" s="7" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D143" s="42"/>
+      <c r="E143" s="16"/>
+      <c r="F143" s="16"/>
+    </row>
+    <row r="144" spans="2:7">
+      <c r="B144" s="77" t="s">
         <v>469</v>
       </c>
-      <c r="C143" s="57" t="s">
+      <c r="C144" s="57" t="s">
         <v>468</v>
       </c>
-      <c r="D143" s="1"/>
-      <c r="E143" s="49" t="s">
+      <c r="D144" s="1"/>
+      <c r="E144" s="49" t="s">
         <v>467</v>
       </c>
-      <c r="F143" s="1"/>
+      <c r="F144" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -34323,7 +34353,7 @@
     <hyperlink ref="E80" r:id="rId8"/>
     <hyperlink ref="E116" r:id="rId9"/>
     <hyperlink ref="E120" r:id="rId10"/>
-    <hyperlink ref="E143" r:id="rId11"/>
+    <hyperlink ref="E144" r:id="rId11"/>
     <hyperlink ref="F49" location="'#9'!B2" display="Link"/>
     <hyperlink ref="F61" location="'#12'!B2" display="Link"/>
     <hyperlink ref="F66" location="'#16'!B2" display="Link"/>
@@ -34378,9 +34408,10 @@
     <hyperlink ref="F99" location="'#21'!B146" display="Link"/>
     <hyperlink ref="F100" location="'#21'!B176" display="Link"/>
     <hyperlink ref="F101" location="'#21'!B182" display="Link"/>
+    <hyperlink ref="E101" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId12"/>
+  <pageSetup orientation="portrait" r:id="rId13"/>
 </worksheet>
 </file>
 
@@ -34756,21 +34787,21 @@
       <c r="D16" t="s">
         <v>710</v>
       </c>
-      <c r="I16" s="130" t="s">
+      <c r="I16" s="131" t="s">
         <v>714</v>
       </c>
-      <c r="J16" s="131"/>
+      <c r="J16" s="132"/>
     </row>
     <row r="17" spans="3:10" ht="15" customHeight="1">
-      <c r="I17" s="132"/>
-      <c r="J17" s="133"/>
+      <c r="I17" s="133"/>
+      <c r="J17" s="134"/>
     </row>
     <row r="18" spans="3:10">
       <c r="D18" t="s">
         <v>711</v>
       </c>
-      <c r="I18" s="134"/>
-      <c r="J18" s="135"/>
+      <c r="I18" s="135"/>
+      <c r="J18" s="136"/>
     </row>
     <row r="19" spans="3:10">
       <c r="C19" t="s">
@@ -35189,7 +35220,7 @@
       <c r="D12" s="11"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" thickBot="1">
-      <c r="C13" s="119" t="s">
+      <c r="C13" s="120" t="s">
         <v>78</v>
       </c>
       <c r="D13" s="26" t="s">
@@ -35206,7 +35237,7 @@
       <c r="I13" s="25"/>
     </row>
     <row r="14" spans="1:10" ht="15.75" thickBot="1">
-      <c r="C14" s="120"/>
+      <c r="C14" s="121"/>
       <c r="D14" s="23" t="s">
         <v>65</v>
       </c>
@@ -35222,7 +35253,7 @@
       <c r="J14" s="25"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="C15" s="120"/>
+      <c r="C15" s="121"/>
       <c r="D15" s="26" t="s">
         <v>66</v>
       </c>
@@ -35237,7 +35268,7 @@
       <c r="I15" s="28"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="C16" s="120"/>
+      <c r="C16" s="121"/>
       <c r="D16" s="29"/>
       <c r="E16" s="30" t="s">
         <v>74</v>
@@ -35248,7 +35279,7 @@
       <c r="I16" s="31"/>
     </row>
     <row r="17" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C17" s="121"/>
+      <c r="C17" s="122"/>
       <c r="D17" s="32"/>
       <c r="E17" s="33" t="s">
         <v>75</v>
@@ -35279,7 +35310,7 @@
       <c r="L18" s="25"/>
     </row>
     <row r="19" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C19" s="119" t="s">
+      <c r="C19" s="120" t="s">
         <v>78</v>
       </c>
       <c r="D19" s="23" t="s">
@@ -35290,7 +35321,7 @@
       </c>
     </row>
     <row r="20" spans="3:12">
-      <c r="C20" s="120"/>
+      <c r="C20" s="121"/>
       <c r="D20" s="26" t="s">
         <v>82</v>
       </c>
@@ -35299,7 +35330,7 @@
       </c>
     </row>
     <row r="21" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C21" s="121"/>
+      <c r="C21" s="122"/>
       <c r="D21" s="32"/>
       <c r="E21" s="40" t="s">
         <v>84</v>

--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="7" activeTab="22"/>
   </bookViews>
   <sheets>
     <sheet name="Knowhow" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="1266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1768" uniqueCount="1269">
   <si>
     <t>No.</t>
   </si>
@@ -19122,6 +19122,119 @@
   </si>
   <si>
     <t>deque</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Trong C++, future là một </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>đối tượng</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> dùng để </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nhận kết quả</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> của một </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tác vụ chạy bất đồng bộ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nó biểu diễn một </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>giá trị</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sẽ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>được tính toán trong tương lai</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+  </si>
+  <si>
+    <t>Future cho phép thread gọi hàm bất đồng bộ và sau đó đồng bộ lại bằng cách lấy kết quả thông qua get(), thay vì phải chia sẻ biến chung hay dùng mutex.</t>
   </si>
 </sst>
 </file>
@@ -25320,19 +25433,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:K22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="5.7109375" customWidth="1"/>
-    <col min="3" max="3" width="37.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.42578125" customWidth="1"/>
+    <col min="2" max="2" width="5.7265625" customWidth="1"/>
+    <col min="3" max="3" width="37.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.453125" customWidth="1"/>
     <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7265625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="18.75">
+    <row r="2" spans="2:11" ht="18.5">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -25358,7 +25471,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:11" ht="45">
+    <row r="3" spans="2:11" ht="43.5">
       <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
@@ -25712,9 +25825,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Q30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="11" max="11" width="3.7109375" customWidth="1"/>
+    <col min="11" max="11" width="3.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:17">
@@ -26044,12 +26157,12 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E76"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="4.42578125" customWidth="1"/>
-    <col min="3" max="3" width="39.7109375" customWidth="1"/>
-    <col min="4" max="4" width="50.85546875" customWidth="1"/>
-    <col min="5" max="5" width="75.42578125" customWidth="1"/>
+    <col min="2" max="2" width="4.453125" customWidth="1"/>
+    <col min="3" max="3" width="39.7265625" customWidth="1"/>
+    <col min="4" max="4" width="50.81640625" customWidth="1"/>
+    <col min="5" max="5" width="75.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.5">
@@ -26057,7 +26170,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="23.25">
+    <row r="2" spans="1:5" ht="23.5">
       <c r="B2" s="55" t="s">
         <v>420</v>
       </c>
@@ -26076,7 +26189,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="45">
+    <row r="5" spans="1:5" ht="43.5">
       <c r="B5" s="61">
         <v>1</v>
       </c>
@@ -26104,7 +26217,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30">
+    <row r="7" spans="1:5" ht="29">
       <c r="B7" s="61">
         <v>3</v>
       </c>
@@ -26118,7 +26231,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="23.25">
+    <row r="10" spans="1:5" ht="23.5">
       <c r="B10" s="55" t="s">
         <v>344</v>
       </c>
@@ -26137,7 +26250,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="30">
+    <row r="13" spans="1:5">
       <c r="B13" s="61">
         <v>1</v>
       </c>
@@ -26151,7 +26264,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="30">
+    <row r="14" spans="1:5" ht="29">
       <c r="B14" s="61">
         <v>2</v>
       </c>
@@ -26165,7 +26278,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="30">
+    <row r="15" spans="1:5" ht="29">
       <c r="B15" s="61">
         <v>3</v>
       </c>
@@ -26179,7 +26292,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30">
+    <row r="16" spans="1:5" ht="29">
       <c r="B16" s="61">
         <v>4</v>
       </c>
@@ -26193,7 +26306,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="165">
+    <row r="17" spans="2:5" ht="145">
       <c r="B17" s="61">
         <v>5</v>
       </c>
@@ -26207,7 +26320,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="180">
+    <row r="18" spans="2:5" ht="159.5">
       <c r="B18" s="61">
         <v>6</v>
       </c>
@@ -26221,7 +26334,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="135">
+    <row r="19" spans="2:5" ht="130.5">
       <c r="B19" s="61">
         <v>7</v>
       </c>
@@ -26235,7 +26348,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="135">
+    <row r="20" spans="2:5" ht="130.5">
       <c r="B20" s="61">
         <v>8</v>
       </c>
@@ -26249,7 +26362,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="23" spans="2:5" ht="23.25">
+    <row r="23" spans="2:5" ht="23.5">
       <c r="B23" s="55" t="s">
         <v>419</v>
       </c>
@@ -26316,7 +26429,7 @@
       </c>
       <c r="E29" s="1"/>
     </row>
-    <row r="32" spans="2:5" ht="23.25">
+    <row r="32" spans="2:5" ht="23.5">
       <c r="B32" s="55" t="s">
         <v>418</v>
       </c>
@@ -26332,7 +26445,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="35" spans="2:4" ht="30">
+    <row r="35" spans="2:4" ht="29">
       <c r="B35" s="57">
         <v>1</v>
       </c>
@@ -26354,7 +26467,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="37" spans="2:4" ht="30">
+    <row r="37" spans="2:4">
       <c r="B37" s="57">
         <v>3</v>
       </c>
@@ -26376,7 +26489,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="41" spans="2:4" ht="23.25">
+    <row r="41" spans="2:4" ht="23.5">
       <c r="B41" s="55" t="s">
         <v>417</v>
       </c>
@@ -26392,7 +26505,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="44" spans="2:4" ht="30">
+    <row r="44" spans="2:4">
       <c r="B44" s="57">
         <v>1</v>
       </c>
@@ -26436,7 +26549,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="50" spans="2:4" ht="23.25">
+    <row r="50" spans="2:4" ht="23.5">
       <c r="B50" s="55" t="s">
         <v>416</v>
       </c>
@@ -26488,7 +26601,7 @@
     <row r="56" spans="2:4">
       <c r="B56" s="57"/>
     </row>
-    <row r="58" spans="2:4" ht="23.25">
+    <row r="58" spans="2:4" ht="23.5">
       <c r="B58" s="55" t="s">
         <v>415</v>
       </c>
@@ -26515,7 +26628,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="62" spans="2:4" ht="45">
+    <row r="62" spans="2:4" ht="29">
       <c r="B62" s="57">
         <v>2</v>
       </c>
@@ -26526,7 +26639,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="63" spans="2:4" ht="30">
+    <row r="63" spans="2:4" ht="29">
       <c r="B63" s="57">
         <v>3</v>
       </c>
@@ -26559,7 +26672,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="68" spans="2:4" ht="23.25">
+    <row r="68" spans="2:4" ht="23.5">
       <c r="B68" s="55" t="s">
         <v>400</v>
       </c>
@@ -26650,7 +26763,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:S38"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -26977,7 +27090,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:M57"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -27291,7 +27404,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:G44"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" t="s">
@@ -27528,7 +27641,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -27645,7 +27758,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -27723,7 +27836,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
@@ -27770,14 +27883,14 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I48"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="18.75">
+    <row r="3" spans="2:4" ht="18.5">
       <c r="C3" s="84" t="s">
         <v>644</v>
       </c>
@@ -27910,7 +28023,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="33" spans="3:9" ht="18.75">
+    <row r="33" spans="3:9" ht="18.5">
       <c r="C33" s="84" t="s">
         <v>670</v>
       </c>
@@ -28009,7 +28122,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:N228"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
@@ -29977,15 +30090,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:F103"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="3" max="3" width="12.28515625" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.26953125" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" customWidth="1"/>
+    <col min="5" max="5" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="18.75">
+    <row r="2" spans="2:6" ht="18.5">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -31128,7 +31241,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B17:D19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="17" spans="2:4">
       <c r="B17" t="s">
@@ -31159,7 +31272,7 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
@@ -31204,9 +31317,9 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:G11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7">
@@ -31214,7 +31327,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="3" spans="2:7" ht="15.75" thickBot="1"/>
+    <row r="3" spans="2:7" ht="15" thickBot="1"/>
     <row r="4" spans="2:7">
       <c r="C4" s="118" t="s">
         <v>910</v>
@@ -31228,7 +31341,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="5" spans="2:7" ht="15.75" thickBot="1">
+    <row r="5" spans="2:7" ht="15" thickBot="1">
       <c r="C5" s="121"/>
       <c r="D5" s="122"/>
       <c r="E5" s="123"/>
@@ -31252,7 +31365,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="15.75" thickBot="1">
+    <row r="7" spans="2:7" ht="15" thickBot="1">
       <c r="C7" s="121"/>
       <c r="D7" s="122"/>
       <c r="E7" s="123"/>
@@ -31276,7 +31389,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="9" spans="2:7" ht="15.75" thickBot="1">
+    <row r="9" spans="2:7" ht="15" thickBot="1">
       <c r="C9" s="121"/>
       <c r="D9" s="122"/>
       <c r="E9" s="123"/>
@@ -31300,7 +31413,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="11" spans="2:7" ht="15.75" thickBot="1">
+    <row r="11" spans="2:7" ht="15" thickBot="1">
       <c r="C11" s="121"/>
       <c r="D11" s="122"/>
       <c r="E11" s="123"/>
@@ -31324,10 +31437,10 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:V256"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="B2:V263"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="10.140625" customWidth="1"/>
+    <col min="2" max="2" width="10.1796875" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -32788,6 +32901,31 @@
       <c r="K256" s="95"/>
       <c r="L256" s="95"/>
     </row>
+    <row r="259" spans="2:3">
+      <c r="B259" s="6" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="260" spans="2:3">
+      <c r="C260" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="261" spans="2:3">
+      <c r="C261" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="262" spans="2:3">
+      <c r="C262" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="263" spans="2:3">
+      <c r="C263" t="s">
+        <v>1268</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -32797,7 +32935,7 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:L33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:12">
       <c r="B2" s="6" t="s">
@@ -32952,7 +33090,7 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Q108"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:10">
       <c r="B2" t="s">
@@ -34757,7 +34895,7 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -34889,7 +35027,7 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E37"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="4" max="4" width="19" customWidth="1"/>
   </cols>
@@ -35049,9 +35187,9 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:C31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="17.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
@@ -35157,9 +35295,9 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:F28"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="4" max="4" width="16.28515625" customWidth="1"/>
+    <col min="4" max="4" width="16.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6">
@@ -35290,12 +35428,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:G156"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="1"/>
   <cols>
-    <col min="3" max="3" width="62.85546875" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="68.5703125" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" customWidth="1"/>
+    <col min="3" max="3" width="62.81640625" customWidth="1"/>
+    <col min="4" max="4" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.54296875" customWidth="1"/>
+    <col min="6" max="6" width="9.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6">
@@ -35303,7 +35441,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="2:6" ht="18.75">
+    <row r="2" spans="2:6" ht="18.5">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -36204,7 +36342,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="45" hidden="1" outlineLevel="1">
+    <row r="64" spans="2:6" ht="43.5" hidden="1" outlineLevel="1">
       <c r="B64" s="5" t="s">
         <v>446</v>
       </c>
@@ -36279,7 +36417,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="69" spans="2:6" ht="30" hidden="1" outlineLevel="1">
+    <row r="69" spans="2:6" ht="29" hidden="1" outlineLevel="1">
       <c r="B69" s="5">
         <v>16.399999999999999</v>
       </c>
@@ -36309,7 +36447,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="71" spans="2:6" ht="60" hidden="1" outlineLevel="1">
+    <row r="71" spans="2:6" ht="43.5" hidden="1" outlineLevel="1">
       <c r="B71" s="5">
         <v>16.600000000000001</v>
       </c>
@@ -36412,7 +36550,7 @@
       <c r="E77" s="6"/>
       <c r="F77" s="6"/>
     </row>
-    <row r="78" spans="2:6" ht="30" hidden="1" outlineLevel="1">
+    <row r="78" spans="2:6" ht="29" hidden="1" outlineLevel="1">
       <c r="B78" s="5">
         <v>17.100000000000001</v>
       </c>
@@ -36423,7 +36561,7 @@
       <c r="E78" s="6"/>
       <c r="F78" s="6"/>
     </row>
-    <row r="79" spans="2:6" ht="30" hidden="1" outlineLevel="1">
+    <row r="79" spans="2:6" hidden="1" outlineLevel="1">
       <c r="B79" s="5">
         <v>17.2</v>
       </c>
@@ -36482,7 +36620,7 @@
       <c r="E83" s="6"/>
       <c r="F83" s="6"/>
     </row>
-    <row r="84" spans="2:6" ht="30" hidden="1" outlineLevel="1">
+    <row r="84" spans="2:6" ht="29" hidden="1" outlineLevel="1">
       <c r="B84" s="5">
         <v>18.100000000000001</v>
       </c>
@@ -36691,7 +36829,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="103" spans="2:6" ht="45">
+    <row r="103" spans="2:6" ht="29">
       <c r="B103" s="5">
         <v>21.2</v>
       </c>
@@ -36721,7 +36859,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="105" spans="2:6" ht="30">
+    <row r="105" spans="2:6" ht="29">
       <c r="B105" s="5">
         <v>21.4</v>
       </c>
@@ -36865,9 +37003,13 @@
       <c r="C114" s="6" t="s">
         <v>1087</v>
       </c>
-      <c r="D114" s="44"/>
+      <c r="D114" s="44">
+        <v>0</v>
+      </c>
       <c r="E114" s="6"/>
-      <c r="F114" s="6"/>
+      <c r="F114" s="14" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="115" spans="2:6">
       <c r="B115" s="45" t="s">
@@ -36986,7 +37128,7 @@
       <c r="E125" s="6"/>
       <c r="F125" s="6"/>
     </row>
-    <row r="126" spans="2:6" ht="30">
+    <row r="126" spans="2:6" ht="29">
       <c r="B126" s="45" t="s">
         <v>1174</v>
       </c>
@@ -37059,7 +37201,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="131" spans="2:7" ht="30">
+    <row r="131" spans="2:7" ht="29">
       <c r="B131" s="5" t="s">
         <v>464</v>
       </c>
@@ -37150,7 +37292,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="137" spans="2:7" ht="45">
+    <row r="137" spans="2:7" ht="43.5">
       <c r="B137" s="5" t="s">
         <v>480</v>
       </c>
@@ -37197,7 +37339,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="140" spans="2:7" ht="30">
+    <row r="140" spans="2:7" ht="29">
       <c r="B140" s="5" t="s">
         <v>481</v>
       </c>
@@ -37303,7 +37445,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="147" spans="2:7" ht="30">
+    <row r="147" spans="2:7" ht="29">
       <c r="B147" s="5" t="s">
         <v>484</v>
       </c>
@@ -37371,7 +37513,7 @@
       <c r="E152" s="14"/>
       <c r="F152" s="14"/>
     </row>
-    <row r="153" spans="2:7" ht="30">
+    <row r="153" spans="2:7" ht="29">
       <c r="B153" s="5" t="s">
         <v>1210</v>
       </c>
@@ -37531,6 +37673,7 @@
     <hyperlink ref="F112" location="'#21'!B190" display="Link"/>
     <hyperlink ref="F113" location="'#21'!H246" display="Link"/>
     <hyperlink ref="F155" location="'#35'!B2" display="Link"/>
+    <hyperlink ref="F114" location="'#21'!B259" display="Link"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId13"/>
@@ -37540,7 +37683,7 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:F36"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
@@ -37693,9 +37836,9 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:B39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="22.140625" customWidth="1"/>
+    <col min="2" max="2" width="22.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:2">
@@ -37850,7 +37993,7 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:O20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:15">
       <c r="B2" s="6" t="s">
@@ -37947,7 +38090,7 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:K18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:11">
       <c r="B2" t="s">
@@ -38034,9 +38177,9 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
@@ -38067,13 +38210,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J164"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" customWidth="1"/>
+    <col min="1" max="1" width="4.26953125" customWidth="1"/>
+    <col min="2" max="2" width="6.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75">
+    <row r="1" spans="1:3" ht="18.5">
       <c r="C1" s="35" t="s">
         <v>15</v>
       </c>
@@ -38330,14 +38473,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L61"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="3" max="3" width="10.42578125" customWidth="1"/>
-    <col min="4" max="4" width="5.28515625" customWidth="1"/>
-    <col min="5" max="5" width="48.85546875" customWidth="1"/>
+    <col min="3" max="3" width="10.453125" customWidth="1"/>
+    <col min="4" max="4" width="5.26953125" customWidth="1"/>
+    <col min="5" max="5" width="48.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75">
+    <row r="1" spans="1:10" ht="18.5">
       <c r="C1" s="35" t="s">
         <v>57</v>
       </c>
@@ -38368,13 +38511,13 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15.75" thickBot="1">
+    <row r="12" spans="1:10" ht="15" thickBot="1">
       <c r="C12" s="11" t="s">
         <v>63</v>
       </c>
       <c r="D12" s="11"/>
     </row>
-    <row r="13" spans="1:10" ht="15.75" thickBot="1">
+    <row r="13" spans="1:10" ht="15" thickBot="1">
       <c r="C13" s="113" t="s">
         <v>78</v>
       </c>
@@ -38391,7 +38534,7 @@
       <c r="H13" s="22"/>
       <c r="I13" s="23"/>
     </row>
-    <row r="14" spans="1:10" ht="15.75" thickBot="1">
+    <row r="14" spans="1:10" ht="15" thickBot="1">
       <c r="C14" s="114"/>
       <c r="D14" s="21" t="s">
         <v>65</v>
@@ -38431,7 +38574,7 @@
       <c r="F16" s="27"/>
       <c r="I16" s="28"/>
     </row>
-    <row r="17" spans="3:12" ht="15.75" thickBot="1">
+    <row r="17" spans="3:12" ht="15" thickBot="1">
       <c r="C17" s="115"/>
       <c r="D17" s="29"/>
       <c r="E17" s="30" t="s">
@@ -38440,7 +38583,7 @@
       <c r="F17" s="27"/>
       <c r="I17" s="28"/>
     </row>
-    <row r="18" spans="3:12" ht="15.75" thickBot="1">
+    <row r="18" spans="3:12" ht="15" thickBot="1">
       <c r="C18" s="33" t="s">
         <v>79</v>
       </c>
@@ -38460,7 +38603,7 @@
       <c r="K18" s="22"/>
       <c r="L18" s="23"/>
     </row>
-    <row r="19" spans="3:12" ht="15.75" thickBot="1">
+    <row r="19" spans="3:12" ht="15" thickBot="1">
       <c r="C19" s="113" t="s">
         <v>78</v>
       </c>
@@ -38480,7 +38623,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="3:12" ht="15.75" thickBot="1">
+    <row r="21" spans="3:12" ht="15" thickBot="1">
       <c r="C21" s="115"/>
       <c r="D21" s="29"/>
       <c r="E21" s="34" t="s">
@@ -38594,10 +38737,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:V102"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="13" max="13" width="4.85546875" customWidth="1"/>
+    <col min="13" max="13" width="4.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
@@ -39112,7 +39255,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D48"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" s="6" t="s">
@@ -39290,10 +39433,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:H90"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="4" max="4" width="13.5703125" customWidth="1"/>
-    <col min="7" max="7" width="9.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" customWidth="1"/>
+    <col min="7" max="7" width="9.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4">
@@ -39659,9 +39802,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Z40"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="4" max="4" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:26">

--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="7" activeTab="22"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="9" activeTab="22"/>
   </bookViews>
   <sheets>
     <sheet name="Knowhow" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1768" uniqueCount="1269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="1272">
   <si>
     <t>No.</t>
   </si>
@@ -19235,6 +19235,107 @@
   </si>
   <si>
     <t>Future cho phép thread gọi hàm bất đồng bộ và sau đó đồng bộ lại bằng cách lấy kết quả thông qua get(), thay vì phải chia sẻ biến chung hay dùng mutex.</t>
+  </si>
+  <si>
+    <t>std::future / Bất đồng bộ / Asynchronous programming</t>
+  </si>
+  <si>
+    <t>Bất đồng bộ / Asynchronous programming</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Là một mô hình cho phép tác vụ khởi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>chạy độc lập</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> so với</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> luồng gọi nó</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Kết quả của tác vụ sẽ được </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>thu nhận</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>qua</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> cơ chế đồng bộ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>future</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -25110,6 +25211,136 @@
 
 <file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>263</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>296</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1371600" y="50225325"/>
+          <a:ext cx="5419725" cy="6191250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>304799</xdr:colOff>
+      <xdr:row>284</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>85724</xdr:colOff>
+      <xdr:row>289</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Rectangular Callout 5"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5981699" y="54102000"/>
+          <a:ext cx="2219325" cy="1019175"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -82459"/>
+            <a:gd name="adj2" fmla="val 44905"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>Tác</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> vụ chạy bất đồng bộ : A và B không biết chắc được là khi nào hàng về,chỉ biết là khi get() vào main thì A phải xếp trước B ( khi get là đồng bộ lại)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
@@ -25433,19 +25664,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:K22"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="5.7265625" customWidth="1"/>
-    <col min="3" max="3" width="37.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.453125" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" customWidth="1"/>
+    <col min="3" max="3" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.42578125" customWidth="1"/>
     <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="18.5">
+    <row r="2" spans="2:11" ht="18.75">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -25471,7 +25702,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:11" ht="43.5">
+    <row r="3" spans="2:11" ht="45">
       <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
@@ -25825,9 +26056,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Q30"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="11" max="11" width="3.7265625" customWidth="1"/>
+    <col min="11" max="11" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:17">
@@ -26157,12 +26388,12 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E76"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="4.453125" customWidth="1"/>
-    <col min="3" max="3" width="39.7265625" customWidth="1"/>
-    <col min="4" max="4" width="50.81640625" customWidth="1"/>
-    <col min="5" max="5" width="75.453125" customWidth="1"/>
+    <col min="2" max="2" width="4.42578125" customWidth="1"/>
+    <col min="3" max="3" width="39.7109375" customWidth="1"/>
+    <col min="4" max="4" width="50.85546875" customWidth="1"/>
+    <col min="5" max="5" width="75.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.5">
@@ -26170,7 +26401,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="23.5">
+    <row r="2" spans="1:5" ht="23.25">
       <c r="B2" s="55" t="s">
         <v>420</v>
       </c>
@@ -26189,7 +26420,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="43.5">
+    <row r="5" spans="1:5" ht="45">
       <c r="B5" s="61">
         <v>1</v>
       </c>
@@ -26217,7 +26448,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="29">
+    <row r="7" spans="1:5" ht="30">
       <c r="B7" s="61">
         <v>3</v>
       </c>
@@ -26231,7 +26462,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="23.5">
+    <row r="10" spans="1:5" ht="23.25">
       <c r="B10" s="55" t="s">
         <v>344</v>
       </c>
@@ -26250,7 +26481,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" ht="30">
       <c r="B13" s="61">
         <v>1</v>
       </c>
@@ -26264,7 +26495,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="29">
+    <row r="14" spans="1:5" ht="30">
       <c r="B14" s="61">
         <v>2</v>
       </c>
@@ -26278,7 +26509,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="29">
+    <row r="15" spans="1:5" ht="30">
       <c r="B15" s="61">
         <v>3</v>
       </c>
@@ -26292,7 +26523,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="29">
+    <row r="16" spans="1:5" ht="30">
       <c r="B16" s="61">
         <v>4</v>
       </c>
@@ -26306,7 +26537,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="145">
+    <row r="17" spans="2:5" ht="165">
       <c r="B17" s="61">
         <v>5</v>
       </c>
@@ -26320,7 +26551,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="159.5">
+    <row r="18" spans="2:5" ht="180">
       <c r="B18" s="61">
         <v>6</v>
       </c>
@@ -26334,7 +26565,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="130.5">
+    <row r="19" spans="2:5" ht="135">
       <c r="B19" s="61">
         <v>7</v>
       </c>
@@ -26348,7 +26579,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="130.5">
+    <row r="20" spans="2:5" ht="135">
       <c r="B20" s="61">
         <v>8</v>
       </c>
@@ -26362,7 +26593,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="23" spans="2:5" ht="23.5">
+    <row r="23" spans="2:5" ht="23.25">
       <c r="B23" s="55" t="s">
         <v>419</v>
       </c>
@@ -26429,7 +26660,7 @@
       </c>
       <c r="E29" s="1"/>
     </row>
-    <row r="32" spans="2:5" ht="23.5">
+    <row r="32" spans="2:5" ht="23.25">
       <c r="B32" s="55" t="s">
         <v>418</v>
       </c>
@@ -26445,7 +26676,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="35" spans="2:4" ht="29">
+    <row r="35" spans="2:4" ht="30">
       <c r="B35" s="57">
         <v>1</v>
       </c>
@@ -26467,7 +26698,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="37" spans="2:4">
+    <row r="37" spans="2:4" ht="30">
       <c r="B37" s="57">
         <v>3</v>
       </c>
@@ -26489,7 +26720,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="41" spans="2:4" ht="23.5">
+    <row r="41" spans="2:4" ht="23.25">
       <c r="B41" s="55" t="s">
         <v>417</v>
       </c>
@@ -26505,7 +26736,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="44" spans="2:4">
+    <row r="44" spans="2:4" ht="30">
       <c r="B44" s="57">
         <v>1</v>
       </c>
@@ -26549,7 +26780,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="50" spans="2:4" ht="23.5">
+    <row r="50" spans="2:4" ht="23.25">
       <c r="B50" s="55" t="s">
         <v>416</v>
       </c>
@@ -26601,7 +26832,7 @@
     <row r="56" spans="2:4">
       <c r="B56" s="57"/>
     </row>
-    <row r="58" spans="2:4" ht="23.5">
+    <row r="58" spans="2:4" ht="23.25">
       <c r="B58" s="55" t="s">
         <v>415</v>
       </c>
@@ -26628,7 +26859,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="62" spans="2:4" ht="29">
+    <row r="62" spans="2:4" ht="45">
       <c r="B62" s="57">
         <v>2</v>
       </c>
@@ -26639,7 +26870,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="63" spans="2:4" ht="29">
+    <row r="63" spans="2:4" ht="30">
       <c r="B63" s="57">
         <v>3</v>
       </c>
@@ -26672,7 +26903,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="68" spans="2:4" ht="23.5">
+    <row r="68" spans="2:4" ht="23.25">
       <c r="B68" s="55" t="s">
         <v>400</v>
       </c>
@@ -26763,7 +26994,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:S38"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -27090,7 +27321,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:M57"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -27404,7 +27635,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:G44"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" t="s">
@@ -27641,7 +27872,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E25"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -27758,7 +27989,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E16"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -27836,7 +28067,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
@@ -27883,14 +28114,14 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I48"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="18.5">
+    <row r="3" spans="2:4" ht="18.75">
       <c r="C3" s="84" t="s">
         <v>644</v>
       </c>
@@ -28023,7 +28254,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="33" spans="3:9" ht="18.5">
+    <row r="33" spans="3:9" ht="18.75">
       <c r="C33" s="84" t="s">
         <v>670</v>
       </c>
@@ -28122,7 +28353,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:N228"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
@@ -30090,15 +30321,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:F103"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="12.26953125" customWidth="1"/>
-    <col min="4" max="4" width="13.54296875" customWidth="1"/>
-    <col min="5" max="5" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.1796875" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" customWidth="1"/>
+    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="18.5">
+    <row r="2" spans="2:6" ht="18.75">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -31241,7 +31472,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B17:D19"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="17" spans="2:4">
       <c r="B17" t="s">
@@ -31272,7 +31503,7 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
@@ -31317,9 +31548,9 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:G11"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="6" max="6" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7">
@@ -31327,7 +31558,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="3" spans="2:7" ht="15" thickBot="1"/>
+    <row r="3" spans="2:7" ht="15.75" thickBot="1"/>
     <row r="4" spans="2:7">
       <c r="C4" s="118" t="s">
         <v>910</v>
@@ -31341,7 +31572,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="5" spans="2:7" ht="15" thickBot="1">
+    <row r="5" spans="2:7" ht="15.75" thickBot="1">
       <c r="C5" s="121"/>
       <c r="D5" s="122"/>
       <c r="E5" s="123"/>
@@ -31365,7 +31596,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="15" thickBot="1">
+    <row r="7" spans="2:7" ht="15.75" thickBot="1">
       <c r="C7" s="121"/>
       <c r="D7" s="122"/>
       <c r="E7" s="123"/>
@@ -31389,7 +31620,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="9" spans="2:7" ht="15" thickBot="1">
+    <row r="9" spans="2:7" ht="15.75" thickBot="1">
       <c r="C9" s="121"/>
       <c r="D9" s="122"/>
       <c r="E9" s="123"/>
@@ -31413,7 +31644,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="11" spans="2:7" ht="15" thickBot="1">
+    <row r="11" spans="2:7" ht="15.75" thickBot="1">
       <c r="C11" s="121"/>
       <c r="D11" s="122"/>
       <c r="E11" s="123"/>
@@ -31437,10 +31668,10 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:V263"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="B2:V301"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="10.1796875" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -32926,16 +33157,32 @@
         <v>1268</v>
       </c>
     </row>
+    <row r="299" spans="2:3">
+      <c r="B299" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="300" spans="2:3">
+      <c r="C300" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="301" spans="2:3">
+      <c r="C301" t="s">
+        <v>1271</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:L33"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:12">
       <c r="B2" s="6" t="s">
@@ -33090,7 +33337,7 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Q108"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:10">
       <c r="B2" t="s">
@@ -34895,7 +35142,7 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E27"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:5">
       <c r="B2" s="6" t="s">
@@ -35027,7 +35274,7 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E37"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="19" customWidth="1"/>
   </cols>
@@ -35187,9 +35434,9 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:C31"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="17.453125" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
@@ -35295,9 +35542,9 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:F28"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="16.26953125" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6">
@@ -35428,12 +35675,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:G156"/>
-  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
-    <col min="3" max="3" width="62.81640625" customWidth="1"/>
-    <col min="4" max="4" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="68.54296875" customWidth="1"/>
-    <col min="6" max="6" width="9.7265625" customWidth="1"/>
+    <col min="3" max="3" width="62.85546875" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="68.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6">
@@ -35441,7 +35688,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="2:6" ht="18.5">
+    <row r="2" spans="2:6" ht="18.75">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -36342,7 +36589,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="43.5" hidden="1" outlineLevel="1">
+    <row r="64" spans="2:6" ht="45" hidden="1" outlineLevel="1">
       <c r="B64" s="5" t="s">
         <v>446</v>
       </c>
@@ -36417,7 +36664,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="69" spans="2:6" ht="29" hidden="1" outlineLevel="1">
+    <row r="69" spans="2:6" ht="30" hidden="1" outlineLevel="1">
       <c r="B69" s="5">
         <v>16.399999999999999</v>
       </c>
@@ -36447,7 +36694,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="71" spans="2:6" ht="43.5" hidden="1" outlineLevel="1">
+    <row r="71" spans="2:6" ht="60" hidden="1" outlineLevel="1">
       <c r="B71" s="5">
         <v>16.600000000000001</v>
       </c>
@@ -36550,7 +36797,7 @@
       <c r="E77" s="6"/>
       <c r="F77" s="6"/>
     </row>
-    <row r="78" spans="2:6" ht="29" hidden="1" outlineLevel="1">
+    <row r="78" spans="2:6" ht="30" hidden="1" outlineLevel="1">
       <c r="B78" s="5">
         <v>17.100000000000001</v>
       </c>
@@ -36561,7 +36808,7 @@
       <c r="E78" s="6"/>
       <c r="F78" s="6"/>
     </row>
-    <row r="79" spans="2:6" hidden="1" outlineLevel="1">
+    <row r="79" spans="2:6" ht="30" hidden="1" outlineLevel="1">
       <c r="B79" s="5">
         <v>17.2</v>
       </c>
@@ -36620,7 +36867,7 @@
       <c r="E83" s="6"/>
       <c r="F83" s="6"/>
     </row>
-    <row r="84" spans="2:6" ht="29" hidden="1" outlineLevel="1">
+    <row r="84" spans="2:6" ht="30" hidden="1" outlineLevel="1">
       <c r="B84" s="5">
         <v>18.100000000000001</v>
       </c>
@@ -36829,7 +37076,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="103" spans="2:6" ht="29">
+    <row r="103" spans="2:6" ht="45">
       <c r="B103" s="5">
         <v>21.2</v>
       </c>
@@ -36859,7 +37106,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="105" spans="2:6" ht="29">
+    <row r="105" spans="2:6" ht="30">
       <c r="B105" s="5">
         <v>21.4</v>
       </c>
@@ -37001,7 +37248,7 @@
         <v>1091</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>1087</v>
+        <v>1269</v>
       </c>
       <c r="D114" s="44">
         <v>0</v>
@@ -37128,7 +37375,7 @@
       <c r="E125" s="6"/>
       <c r="F125" s="6"/>
     </row>
-    <row r="126" spans="2:6" ht="29">
+    <row r="126" spans="2:6" ht="30">
       <c r="B126" s="45" t="s">
         <v>1174</v>
       </c>
@@ -37201,7 +37448,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="131" spans="2:7" ht="29">
+    <row r="131" spans="2:7" ht="30">
       <c r="B131" s="5" t="s">
         <v>464</v>
       </c>
@@ -37292,7 +37539,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="137" spans="2:7" ht="43.5">
+    <row r="137" spans="2:7" ht="45">
       <c r="B137" s="5" t="s">
         <v>480</v>
       </c>
@@ -37339,7 +37586,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="140" spans="2:7" ht="29">
+    <row r="140" spans="2:7" ht="30">
       <c r="B140" s="5" t="s">
         <v>481</v>
       </c>
@@ -37445,7 +37692,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="147" spans="2:7" ht="29">
+    <row r="147" spans="2:7" ht="30">
       <c r="B147" s="5" t="s">
         <v>484</v>
       </c>
@@ -37513,7 +37760,7 @@
       <c r="E152" s="14"/>
       <c r="F152" s="14"/>
     </row>
-    <row r="153" spans="2:7" ht="29">
+    <row r="153" spans="2:7" ht="30">
       <c r="B153" s="5" t="s">
         <v>1210</v>
       </c>
@@ -37683,7 +37930,7 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:F36"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:4">
       <c r="B2" s="6" t="s">
@@ -37836,9 +38083,9 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:B39"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="22.1796875" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:2">
@@ -37993,7 +38240,7 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:O20"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:15">
       <c r="B2" s="6" t="s">
@@ -38090,7 +38337,7 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:K18"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:11">
       <c r="B2" t="s">
@@ -38177,9 +38424,9 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
@@ -38210,13 +38457,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J164"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.26953125" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.5">
+    <row r="1" spans="1:3" ht="18.75">
       <c r="C1" s="35" t="s">
         <v>15</v>
       </c>
@@ -38473,14 +38720,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L61"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="10.453125" customWidth="1"/>
-    <col min="4" max="4" width="5.26953125" customWidth="1"/>
-    <col min="5" max="5" width="48.81640625" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" customWidth="1"/>
+    <col min="4" max="4" width="5.28515625" customWidth="1"/>
+    <col min="5" max="5" width="48.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.5">
+    <row r="1" spans="1:10" ht="18.75">
       <c r="C1" s="35" t="s">
         <v>57</v>
       </c>
@@ -38511,13 +38758,13 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15" thickBot="1">
+    <row r="12" spans="1:10" ht="15.75" thickBot="1">
       <c r="C12" s="11" t="s">
         <v>63</v>
       </c>
       <c r="D12" s="11"/>
     </row>
-    <row r="13" spans="1:10" ht="15" thickBot="1">
+    <row r="13" spans="1:10" ht="15.75" thickBot="1">
       <c r="C13" s="113" t="s">
         <v>78</v>
       </c>
@@ -38534,7 +38781,7 @@
       <c r="H13" s="22"/>
       <c r="I13" s="23"/>
     </row>
-    <row r="14" spans="1:10" ht="15" thickBot="1">
+    <row r="14" spans="1:10" ht="15.75" thickBot="1">
       <c r="C14" s="114"/>
       <c r="D14" s="21" t="s">
         <v>65</v>
@@ -38574,7 +38821,7 @@
       <c r="F16" s="27"/>
       <c r="I16" s="28"/>
     </row>
-    <row r="17" spans="3:12" ht="15" thickBot="1">
+    <row r="17" spans="3:12" ht="15.75" thickBot="1">
       <c r="C17" s="115"/>
       <c r="D17" s="29"/>
       <c r="E17" s="30" t="s">
@@ -38583,7 +38830,7 @@
       <c r="F17" s="27"/>
       <c r="I17" s="28"/>
     </row>
-    <row r="18" spans="3:12" ht="15" thickBot="1">
+    <row r="18" spans="3:12" ht="15.75" thickBot="1">
       <c r="C18" s="33" t="s">
         <v>79</v>
       </c>
@@ -38603,7 +38850,7 @@
       <c r="K18" s="22"/>
       <c r="L18" s="23"/>
     </row>
-    <row r="19" spans="3:12" ht="15" thickBot="1">
+    <row r="19" spans="3:12" ht="15.75" thickBot="1">
       <c r="C19" s="113" t="s">
         <v>78</v>
       </c>
@@ -38623,7 +38870,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="3:12" ht="15" thickBot="1">
+    <row r="21" spans="3:12" ht="15.75" thickBot="1">
       <c r="C21" s="115"/>
       <c r="D21" s="29"/>
       <c r="E21" s="34" t="s">
@@ -38737,10 +38984,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:V102"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="13" max="13" width="4.81640625" customWidth="1"/>
+    <col min="13" max="13" width="4.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
@@ -39255,7 +39502,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D48"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" s="6" t="s">
@@ -39433,10 +39680,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:H90"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="13.54296875" customWidth="1"/>
-    <col min="7" max="7" width="9.453125" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4">
@@ -39802,9 +40049,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:Z40"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="17.1796875" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:26">

--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="1272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="1284">
   <si>
     <t>No.</t>
   </si>
@@ -19335,6 +19335,783 @@
         <scheme val="minor"/>
       </rPr>
       <t>future</t>
+    </r>
+  </si>
+  <si>
+    <t>Function callback</t>
+  </si>
+  <si>
+    <t>Khi truyền dưới dạng con trỏ hàm A vào hàm B. Sau đó thực hiện gọi hàm A trong B, thì gọi là function call back</t>
+  </si>
+  <si>
+    <r>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>) {</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC586C0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>return</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>y</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>void</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>func</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>))</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>std</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>cout</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Hello"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>std</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>endl</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>std</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>cout</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>func</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFB5CEA8"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>std</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>endl</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>std</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>cout</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Bye"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>&lt;&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF4EC9B0"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>std</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>endl</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>main</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(){</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>sumA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF569CD6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>int</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFD4D4D4"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFDCDCAA"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF9CDCFE"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>sumA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>);</t>
+    </r>
+  </si>
+  <si>
+    <t>#include&lt;future&gt;</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tham khảo phần </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>promise</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>async</t>
     </r>
   </si>
 </sst>
@@ -31668,7 +32445,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:V301"/>
+  <dimension ref="B2:V307"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="10.140625" customWidth="1"/>
@@ -33170,6 +33947,26 @@
     <row r="301" spans="2:3">
       <c r="C301" t="s">
         <v>1271</v>
+      </c>
+    </row>
+    <row r="303" spans="2:3">
+      <c r="B303" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="304" spans="2:3">
+      <c r="C304" s="15" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="306" spans="2:3">
+      <c r="B306" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="307" spans="2:3">
+      <c r="C307" t="s">
+        <v>1283</v>
       </c>
     </row>
   </sheetData>
@@ -35273,7 +36070,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:E37"/>
+  <dimension ref="B2:G54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="19" customWidth="1"/>
@@ -35334,94 +36131,211 @@
         <v>929</v>
       </c>
     </row>
-    <row r="17" spans="2:4">
+    <row r="17" spans="2:7">
       <c r="C17" t="s">
         <v>930</v>
       </c>
     </row>
-    <row r="18" spans="2:4">
+    <row r="18" spans="2:7">
       <c r="C18" t="s">
         <v>928</v>
       </c>
     </row>
-    <row r="19" spans="2:4">
+    <row r="19" spans="2:7">
       <c r="C19" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="22" spans="2:4">
+    <row r="22" spans="2:7">
       <c r="B22" s="6" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7">
+      <c r="C23" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7">
+      <c r="C24" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7">
+      <c r="D25" s="94" t="s">
+        <v>1274</v>
+      </c>
+      <c r="E25" s="95"/>
+      <c r="F25" s="95"/>
+      <c r="G25" s="95"/>
+    </row>
+    <row r="26" spans="2:7">
+      <c r="D26" s="94" t="s">
+        <v>1275</v>
+      </c>
+      <c r="E26" s="95"/>
+      <c r="F26" s="95"/>
+      <c r="G26" s="95"/>
+    </row>
+    <row r="27" spans="2:7">
+      <c r="D27" s="96" t="s">
+        <v>504</v>
+      </c>
+      <c r="E27" s="95"/>
+      <c r="F27" s="95"/>
+      <c r="G27" s="95"/>
+    </row>
+    <row r="28" spans="2:7">
+      <c r="D28" s="98" t="s">
+        <v>1276</v>
+      </c>
+      <c r="E28" s="95"/>
+      <c r="F28" s="95"/>
+      <c r="G28" s="95"/>
+    </row>
+    <row r="29" spans="2:7">
+      <c r="D29" s="98" t="s">
+        <v>1277</v>
+      </c>
+      <c r="E29" s="95"/>
+      <c r="F29" s="95"/>
+      <c r="G29" s="95"/>
+    </row>
+    <row r="30" spans="2:7">
+      <c r="D30" s="98" t="s">
+        <v>1278</v>
+      </c>
+      <c r="E30" s="95"/>
+      <c r="F30" s="95"/>
+      <c r="G30" s="95"/>
+    </row>
+    <row r="31" spans="2:7">
+      <c r="D31" s="96" t="s">
+        <v>284</v>
+      </c>
+      <c r="E31" s="95"/>
+      <c r="F31" s="95"/>
+      <c r="G31" s="95"/>
+    </row>
+    <row r="32" spans="2:7">
+      <c r="D32" s="99"/>
+      <c r="E32" s="95"/>
+      <c r="F32" s="95"/>
+      <c r="G32" s="95"/>
+    </row>
+    <row r="33" spans="2:7">
+      <c r="D33" s="94" t="s">
+        <v>1279</v>
+      </c>
+      <c r="E33" s="95"/>
+      <c r="F33" s="95"/>
+      <c r="G33" s="95"/>
+    </row>
+    <row r="34" spans="2:7">
+      <c r="D34" s="94" t="s">
+        <v>1280</v>
+      </c>
+      <c r="E34" s="95"/>
+      <c r="F34" s="95"/>
+      <c r="G34" s="95"/>
+    </row>
+    <row r="35" spans="2:7">
+      <c r="D35" s="97" t="s">
+        <v>1281</v>
+      </c>
+      <c r="E35" s="95"/>
+      <c r="F35" s="95"/>
+      <c r="G35" s="95"/>
+    </row>
+    <row r="36" spans="2:7">
+      <c r="D36" s="100" t="s">
+        <v>723</v>
+      </c>
+      <c r="E36" s="95"/>
+      <c r="F36" s="95"/>
+      <c r="G36" s="95"/>
+    </row>
+    <row r="37" spans="2:7">
+      <c r="D37" s="96" t="s">
+        <v>284</v>
+      </c>
+      <c r="E37" s="95"/>
+      <c r="F37" s="95"/>
+      <c r="G37" s="95"/>
+    </row>
+    <row r="39" spans="2:7">
+      <c r="B39" s="6" t="s">
         <v>938</v>
       </c>
     </row>
-    <row r="23" spans="2:4">
-      <c r="C23" t="s">
+    <row r="40" spans="2:7">
+      <c r="C40" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="2:4">
-      <c r="D24" t="s">
+    <row r="41" spans="2:7">
+      <c r="D41" t="s">
         <v>951</v>
       </c>
     </row>
-    <row r="25" spans="2:4">
-      <c r="C25" t="s">
+    <row r="42" spans="2:7">
+      <c r="C42" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="26" spans="2:4">
-      <c r="D26" t="s">
+    <row r="43" spans="2:7">
+      <c r="D43" t="s">
         <v>952</v>
       </c>
     </row>
-    <row r="28" spans="2:4">
-      <c r="C28" t="s">
+    <row r="45" spans="2:7">
+      <c r="C45" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="29" spans="2:4">
-      <c r="C29" t="s">
+    <row r="46" spans="2:7">
+      <c r="C46" t="s">
         <v>943</v>
       </c>
     </row>
-    <row r="30" spans="2:4">
-      <c r="C30" t="s">
+    <row r="47" spans="2:7">
+      <c r="C47" t="s">
         <v>953</v>
       </c>
     </row>
-    <row r="31" spans="2:4">
-      <c r="C31" t="s">
+    <row r="48" spans="2:7">
+      <c r="C48" t="s">
         <v>950</v>
       </c>
     </row>
-    <row r="32" spans="2:4">
-      <c r="C32" t="s">
+    <row r="49" spans="3:5">
+      <c r="C49" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="34" spans="3:5">
-      <c r="C34" t="s">
+    <row r="51" spans="3:5">
+      <c r="C51" t="s">
         <v>957</v>
       </c>
     </row>
-    <row r="35" spans="3:5">
-      <c r="D35" t="s">
+    <row r="52" spans="3:5">
+      <c r="D52" t="s">
         <v>959</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E52" t="s">
         <v>958</v>
       </c>
     </row>
-    <row r="36" spans="3:5">
-      <c r="D36" t="s">
+    <row r="53" spans="3:5">
+      <c r="D53" t="s">
         <v>960</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E53" t="s">
         <v>961</v>
       </c>
     </row>
-    <row r="37" spans="3:5">
-      <c r="E37" t="s">
+    <row r="54" spans="3:5">
+      <c r="E54" t="s">
         <v>962</v>
       </c>
     </row>
@@ -35674,7 +36588,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:G156"/>
+  <dimension ref="B1:G157"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col min="3" max="3" width="62.85546875" customWidth="1"/>
@@ -37054,7 +37968,7 @@
         <v>288</v>
       </c>
       <c r="D101" s="44">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E101" s="6"/>
       <c r="F101" s="37" t="s">
@@ -37529,7 +38443,7 @@
         <v>26.1</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>938</v>
+        <v>1272</v>
       </c>
       <c r="D136" s="36">
         <v>1</v>
@@ -37539,44 +38453,44 @@
         <v>14</v>
       </c>
     </row>
-    <row r="137" spans="2:7" ht="45">
-      <c r="B137" s="5" t="s">
+    <row r="137" spans="2:7">
+      <c r="B137" s="5">
+        <v>26.2</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>938</v>
+      </c>
+      <c r="D137" s="36">
+        <v>1</v>
+      </c>
+      <c r="E137" s="14"/>
+      <c r="F137" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="138" spans="2:7" ht="45">
+      <c r="B138" s="5" t="s">
         <v>480</v>
       </c>
-      <c r="C137" s="70" t="s">
+      <c r="C138" s="70" t="s">
         <v>992</v>
       </c>
-      <c r="D137" s="44">
+      <c r="D138" s="44">
         <v>0.5</v>
       </c>
-      <c r="E137" s="14" t="s">
+      <c r="E138" s="14" t="s">
         <v>478</v>
       </c>
-      <c r="F137" s="6" t="s">
+      <c r="F138" s="6" t="s">
         <v>121</v>
-      </c>
-    </row>
-    <row r="138" spans="2:7">
-      <c r="B138" s="5">
-        <v>27.1</v>
-      </c>
-      <c r="C138" s="70" t="s">
-        <v>990</v>
-      </c>
-      <c r="D138" s="44">
-        <v>0.99</v>
-      </c>
-      <c r="E138" s="14"/>
-      <c r="F138" s="14" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="139" spans="2:7">
       <c r="B139" s="5">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="C139" s="70" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="D139" s="44">
         <v>0.99</v>
@@ -37586,27 +38500,27 @@
         <v>14</v>
       </c>
     </row>
-    <row r="140" spans="2:7" ht="30">
-      <c r="B140" s="5" t="s">
-        <v>481</v>
-      </c>
-      <c r="C140" s="7" t="s">
-        <v>939</v>
-      </c>
-      <c r="D140" s="36">
-        <v>1</v>
+    <row r="140" spans="2:7">
+      <c r="B140" s="5">
+        <v>27.2</v>
+      </c>
+      <c r="C140" s="70" t="s">
+        <v>991</v>
+      </c>
+      <c r="D140" s="44">
+        <v>0.99</v>
       </c>
       <c r="E140" s="14"/>
       <c r="F140" s="14" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="141" spans="2:7">
+    <row r="141" spans="2:7" ht="30">
       <c r="B141" s="5" t="s">
-        <v>482</v>
-      </c>
-      <c r="C141" s="6" t="s">
-        <v>806</v>
+        <v>481</v>
+      </c>
+      <c r="C141" s="7" t="s">
+        <v>939</v>
       </c>
       <c r="D141" s="36">
         <v>1</v>
@@ -37617,11 +38531,11 @@
       </c>
     </row>
     <row r="142" spans="2:7">
-      <c r="B142" s="5">
-        <v>29.1</v>
+      <c r="B142" s="5" t="s">
+        <v>482</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>932</v>
+        <v>806</v>
       </c>
       <c r="D142" s="36">
         <v>1</v>
@@ -37632,11 +38546,11 @@
       </c>
     </row>
     <row r="143" spans="2:7">
-      <c r="B143" s="5" t="s">
-        <v>483</v>
-      </c>
-      <c r="C143" s="7" t="s">
-        <v>803</v>
+      <c r="B143" s="5">
+        <v>29.1</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>932</v>
       </c>
       <c r="D143" s="36">
         <v>1</v>
@@ -37647,11 +38561,11 @@
       </c>
     </row>
     <row r="144" spans="2:7">
-      <c r="B144" s="5">
-        <v>30.1</v>
+      <c r="B144" s="5" t="s">
+        <v>483</v>
       </c>
       <c r="C144" s="7" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="D144" s="36">
         <v>1</v>
@@ -37663,10 +38577,10 @@
     </row>
     <row r="145" spans="2:7">
       <c r="B145" s="5">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D145" s="36">
         <v>1</v>
@@ -37675,14 +38589,13 @@
       <c r="F145" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="G145" s="42"/>
     </row>
     <row r="146" spans="2:7">
       <c r="B146" s="5">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="C146" s="7" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D146" s="36">
         <v>1</v>
@@ -37691,31 +38604,32 @@
       <c r="F146" s="14" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="147" spans="2:7" ht="30">
-      <c r="B147" s="5" t="s">
-        <v>484</v>
+      <c r="G146" s="42"/>
+    </row>
+    <row r="147" spans="2:7">
+      <c r="B147" s="5">
+        <v>30.3</v>
       </c>
       <c r="C147" s="7" t="s">
-        <v>472</v>
-      </c>
-      <c r="D147" s="44">
-        <v>0.05</v>
+        <v>802</v>
+      </c>
+      <c r="D147" s="36">
+        <v>1</v>
       </c>
       <c r="E147" s="14"/>
       <c r="F147" s="14" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="148" spans="2:7">
+    <row r="148" spans="2:7" ht="30">
       <c r="B148" s="5" t="s">
-        <v>770</v>
+        <v>484</v>
       </c>
       <c r="C148" s="7" t="s">
-        <v>771</v>
-      </c>
-      <c r="D148" s="36">
-        <v>1</v>
+        <v>472</v>
+      </c>
+      <c r="D148" s="44">
+        <v>0.05</v>
       </c>
       <c r="E148" s="14"/>
       <c r="F148" s="14" t="s">
@@ -37724,19 +38638,25 @@
     </row>
     <row r="149" spans="2:7">
       <c r="B149" s="5" t="s">
+        <v>770</v>
+      </c>
+      <c r="C149" s="7" t="s">
+        <v>771</v>
+      </c>
+      <c r="D149" s="36">
+        <v>1</v>
+      </c>
+      <c r="E149" s="14"/>
+      <c r="F149" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="150" spans="2:7">
+      <c r="B150" s="5" t="s">
         <v>1014</v>
       </c>
-      <c r="C149" s="7" t="s">
+      <c r="C150" s="7" t="s">
         <v>1015</v>
-      </c>
-      <c r="D149" s="112"/>
-      <c r="E149" s="14"/>
-      <c r="F149" s="14"/>
-    </row>
-    <row r="150" spans="2:7">
-      <c r="B150" s="5"/>
-      <c r="C150" s="7" t="s">
-        <v>1016</v>
       </c>
       <c r="D150" s="112"/>
       <c r="E150" s="14"/>
@@ -37745,7 +38665,7 @@
     <row r="151" spans="2:7">
       <c r="B151" s="5"/>
       <c r="C151" s="7" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="D151" s="112"/>
       <c r="E151" s="14"/>
@@ -37754,59 +38674,68 @@
     <row r="152" spans="2:7">
       <c r="B152" s="5"/>
       <c r="C152" s="7" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="D152" s="112"/>
       <c r="E152" s="14"/>
       <c r="F152" s="14"/>
     </row>
-    <row r="153" spans="2:7" ht="30">
-      <c r="B153" s="5" t="s">
-        <v>1210</v>
-      </c>
+    <row r="153" spans="2:7">
+      <c r="B153" s="5"/>
       <c r="C153" s="7" t="s">
-        <v>1211</v>
+        <v>1018</v>
       </c>
       <c r="D153" s="112"/>
       <c r="E153" s="14"/>
       <c r="F153" s="14"/>
     </row>
-    <row r="154" spans="2:7">
-      <c r="B154" s="5"/>
+    <row r="154" spans="2:7" ht="30">
+      <c r="B154" s="5" t="s">
+        <v>1210</v>
+      </c>
       <c r="C154" s="7" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="D154" s="112"/>
       <c r="E154" s="14"/>
       <c r="F154" s="14"/>
     </row>
     <row r="155" spans="2:7">
-      <c r="B155" s="5" t="s">
-        <v>1250</v>
-      </c>
+      <c r="B155" s="5"/>
       <c r="C155" s="7" t="s">
-        <v>1251</v>
-      </c>
-      <c r="D155" s="36">
-        <v>1</v>
-      </c>
+        <v>1212</v>
+      </c>
+      <c r="D155" s="112"/>
       <c r="E155" s="14"/>
-      <c r="F155" s="14" t="s">
-        <v>14</v>
-      </c>
+      <c r="F155" s="14"/>
     </row>
     <row r="156" spans="2:7">
       <c r="B156" s="5" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C156" s="7" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D156" s="36">
+        <v>1</v>
+      </c>
+      <c r="E156" s="14"/>
+      <c r="F156" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="157" spans="2:7">
+      <c r="B157" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="C156" s="6" t="s">
+      <c r="C157" s="6" t="s">
         <v>468</v>
       </c>
-      <c r="D156" s="1"/>
-      <c r="E156" s="43" t="s">
+      <c r="D157" s="1"/>
+      <c r="E157" s="43" t="s">
         <v>467</v>
       </c>
-      <c r="F156" s="1"/>
+      <c r="F157" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="30" type="noConversion"/>
@@ -37861,7 +38790,7 @@
     <hyperlink ref="E80" r:id="rId8"/>
     <hyperlink ref="E127" r:id="rId9"/>
     <hyperlink ref="E131" r:id="rId10"/>
-    <hyperlink ref="E156" r:id="rId11"/>
+    <hyperlink ref="E157" r:id="rId11"/>
     <hyperlink ref="F49" location="'#9'!B2" display="Link"/>
     <hyperlink ref="F61" location="'#12'!B2" display="Link"/>
     <hyperlink ref="F66" location="'#16'!B2" display="Link"/>
@@ -37874,19 +38803,19 @@
     <hyperlink ref="F64" location="'#15'!B2" display="Link"/>
     <hyperlink ref="F71" location="'#16'!B89" display="Link"/>
     <hyperlink ref="F72" location="'#16'!B10" display="Link"/>
-    <hyperlink ref="F147" location="'#31'!B2" display="Link"/>
+    <hyperlink ref="F148" location="'#31'!B2" display="Link"/>
     <hyperlink ref="F132" location="'#24'!B2" display="Link"/>
     <hyperlink ref="F133" location="'#24'!B2" display="Link"/>
     <hyperlink ref="F133:G133" location="'#24'!B26" display="Link"/>
     <hyperlink ref="F134" location="'#25'!B2" display="Link"/>
     <hyperlink ref="F99" location="'#19'!B2" display="Link"/>
-    <hyperlink ref="F144" location="'#30'!B8" display="Link"/>
-    <hyperlink ref="F141" location="'#29'!B2" display="Link"/>
-    <hyperlink ref="F148" location="'#32'!B2" display="Link"/>
-    <hyperlink ref="F143" location="'#30'!B2" display="Link"/>
     <hyperlink ref="F145" location="'#30'!B8" display="Link"/>
-    <hyperlink ref="F145:G145" location="'#30'!B24" display="Link"/>
-    <hyperlink ref="F146" location="'#30'!B35" display="Link"/>
+    <hyperlink ref="F142" location="'#29'!B2" display="Link"/>
+    <hyperlink ref="F149" location="'#32'!B2" display="Link"/>
+    <hyperlink ref="F144" location="'#30'!B2" display="Link"/>
+    <hyperlink ref="F146" location="'#30'!B8" display="Link"/>
+    <hyperlink ref="F146:G146" location="'#30'!B24" display="Link"/>
+    <hyperlink ref="F147" location="'#30'!B35" display="Link"/>
     <hyperlink ref="F51" location="'#11'!B2" display="Link"/>
     <hyperlink ref="F53" location="'#11'!B4" display="Link"/>
     <hyperlink ref="F54" location="'#11'!B21" display="Link"/>
@@ -37896,14 +38825,14 @@
     <hyperlink ref="F29" location="'#4'!B43" display="Link"/>
     <hyperlink ref="F100" location="'#20'!B2" display="Link"/>
     <hyperlink ref="F135" location="'#26'!B2" display="Link"/>
-    <hyperlink ref="F142" location="'#29'!B30" display="Link"/>
-    <hyperlink ref="F140" location="'#28'!B17" display="Link"/>
-    <hyperlink ref="F136" location="'#26'!B22" display="Link"/>
+    <hyperlink ref="F143" location="'#29'!B30" display="Link"/>
+    <hyperlink ref="F141" location="'#28'!B17" display="Link"/>
+    <hyperlink ref="F137" location="'#26'!B39" display="Link"/>
     <hyperlink ref="F128" location="'#23'!B2" display="Link"/>
     <hyperlink ref="F129" location="'#23'!B10" display="Link"/>
     <hyperlink ref="F130" location="'#23'!B24" display="Link"/>
-    <hyperlink ref="F138" location="'#27'!B2" display="Link"/>
-    <hyperlink ref="F139" location="'#27'!B18" display="Link"/>
+    <hyperlink ref="F139" location="'#27'!B2" display="Link"/>
+    <hyperlink ref="F140" location="'#27'!B18" display="Link"/>
     <hyperlink ref="F102" location="'#21'!B2" display="Link"/>
     <hyperlink ref="F74" location="'#16'!D109" display="Link"/>
     <hyperlink ref="F75" location="'#16'!D168" display="Link"/>
@@ -37919,8 +38848,9 @@
     <hyperlink ref="E111" r:id="rId12"/>
     <hyperlink ref="F112" location="'#21'!B190" display="Link"/>
     <hyperlink ref="F113" location="'#21'!H246" display="Link"/>
-    <hyperlink ref="F155" location="'#35'!B2" display="Link"/>
+    <hyperlink ref="F156" location="'#35'!B2" display="Link"/>
     <hyperlink ref="F114" location="'#21'!B259" display="Link"/>
+    <hyperlink ref="F136" location="'#26'!B22" display="Link"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId13"/>

--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -47,12 +47,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="1284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1830" uniqueCount="1315">
   <si>
     <t>No.</t>
   </si>
@@ -20112,6 +20123,806 @@
         <scheme val="minor"/>
       </rPr>
       <t>async</t>
+    </r>
+  </si>
+  <si>
+    <t>*Hãy tưởng tượng promise là 1 cái hộp chứa kết quả, luồng phụ xử lý xong thì đặt kết quả vào promise. Luồng chính muốn lấy được kết quả thì dùng chìa khóa mở hộp là "future"</t>
+  </si>
+  <si>
+    <r>
+      <t>promise là một</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> cơ chế</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> trong C++ dùng để </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cung cấp một giá trị</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (hoặc </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>exception</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) cho một</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> std::future</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>liên kết với nó</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, thường được sử dụng để </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>giao tiếp kết quả giữa các thread</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Đặc điểm</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Một promise chỉ có thể </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>gửi dữ liệu một lần</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (one-shot synchronization).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Promise </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>không thể sao chép</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (non-copyable) nhưng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>có thể di chuyển</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (movable), do đó thường được </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>truyền vào thread bằng std::move</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Có thể truyền tham chiếu Promise vào thread nếu hàm trong thread là hàm lambda</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>#include</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;future&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>Phương thức set value cho future :</t>
+  </si>
+  <si>
+    <r>
+      <t>ins.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>set_value(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>56</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <t>std::promise&lt;int&gt; ins</t>
+  </si>
+  <si>
+    <t>Khai báo</t>
+  </si>
+  <si>
+    <t>std::promise&lt;int&gt; prom;</t>
+  </si>
+  <si>
+    <t>Phương thức get value từ future :</t>
+  </si>
+  <si>
+    <r>
+      <t>std::future&lt;int&gt; fu = prom.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>get_future()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <t>Phương thức get value từ promise cho future :</t>
+  </si>
+  <si>
+    <t>int result;</t>
+  </si>
+  <si>
+    <r>
+      <t>result = fu.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>get()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <t>Trình tự dùng :</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Truyền</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>std::promise</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vào </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hàm con</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, tại hàm con, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>set_value() cho future</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Tại main, khai báo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1 promise</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">, khai báo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1 future liên kết với promise</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> đó : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>promise.get_future()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Tạo 1 thread chạy hàm con có promise, </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">qua future, lệnh </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>future.get()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> gọi 1 lần</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>truyền promise</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> theo kiểu </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>std::move()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vào làm tham số. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Lấy kết quả</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tính toán xong của promise thông</t>
+    </r>
+  </si>
+  <si>
+    <t>copy1.set_value(10);</t>
+  </si>
+  <si>
+    <t>copy2.set_value(20);</t>
+  </si>
+  <si>
+    <t>copy3.set_value(30);</t>
+  </si>
+  <si>
+    <t>-&gt; Không xác định được cái nào sẽ được gửi tới future</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Khi muốn </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>tạo ra 1 thread xử lý</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> dữ liệu </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>riêng</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> biệt và</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> nhận 1 kết quả duy nhất -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Mô hình</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> One-shot communication</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (bởi vậy nên không thể truyền std::promise theo kiểu copy)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Khi cần </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>truyền exception</t>
+    </r>
+  </si>
+  <si>
+    <t>std::condition_variable cv;</t>
+  </si>
+  <si>
+    <r>
+      <t>cơ chế chờ, ngoài ra thì thread con cũng không biết chính xác dữ liệu đã sẵn sàng chưa (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>không one-shot</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> commu)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Khi cần</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> truyền dữ liệu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sau khi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>thread đã chạy được 1 lúc.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Nêu </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dùng thread thông thường</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> thì phải </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>thêm condition_variable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> phức tạp mới có</t>
     </r>
   </si>
 </sst>
@@ -20740,7 +21551,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -20965,9 +21776,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -26003,7 +26811,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4"/>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1600-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -26058,7 +26872,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="Rectangular Callout 5"/>
+        <xdr:cNvPr id="6" name="Rectangular Callout 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1600-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -29452,16 +30272,16 @@
       </c>
     </row>
     <row r="89" spans="2:9" ht="54" customHeight="1">
-      <c r="B89" s="116" t="s">
+      <c r="B89" s="115" t="s">
         <v>615</v>
       </c>
-      <c r="C89" s="117"/>
-      <c r="D89" s="117"/>
-      <c r="E89" s="117"/>
-      <c r="F89" s="117"/>
-      <c r="G89" s="117"/>
-      <c r="H89" s="117"/>
-      <c r="I89" s="117"/>
+      <c r="C89" s="116"/>
+      <c r="D89" s="116"/>
+      <c r="E89" s="116"/>
+      <c r="F89" s="116"/>
+      <c r="G89" s="116"/>
+      <c r="H89" s="116"/>
+      <c r="I89" s="116"/>
     </row>
     <row r="91" spans="2:9">
       <c r="B91" t="s">
@@ -32337,11 +33157,11 @@
     </row>
     <row r="3" spans="2:7" ht="15.75" thickBot="1"/>
     <row r="4" spans="2:7">
-      <c r="C4" s="118" t="s">
+      <c r="C4" s="117" t="s">
         <v>910</v>
       </c>
-      <c r="D4" s="119"/>
-      <c r="E4" s="120"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="119"/>
       <c r="F4" t="s">
         <v>914</v>
       </c>
@@ -32350,9 +33170,9 @@
       </c>
     </row>
     <row r="5" spans="2:7" ht="15.75" thickBot="1">
-      <c r="C5" s="121"/>
-      <c r="D5" s="122"/>
-      <c r="E5" s="123"/>
+      <c r="C5" s="120"/>
+      <c r="D5" s="121"/>
+      <c r="E5" s="122"/>
       <c r="F5" t="s">
         <v>916</v>
       </c>
@@ -32361,11 +33181,11 @@
       </c>
     </row>
     <row r="6" spans="2:7">
-      <c r="C6" s="118" t="s">
+      <c r="C6" s="117" t="s">
         <v>911</v>
       </c>
-      <c r="D6" s="119"/>
-      <c r="E6" s="120"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="119"/>
       <c r="F6" t="s">
         <v>914</v>
       </c>
@@ -32374,9 +33194,9 @@
       </c>
     </row>
     <row r="7" spans="2:7" ht="15.75" thickBot="1">
-      <c r="C7" s="121"/>
-      <c r="D7" s="122"/>
-      <c r="E7" s="123"/>
+      <c r="C7" s="120"/>
+      <c r="D7" s="121"/>
+      <c r="E7" s="122"/>
       <c r="F7" t="s">
         <v>916</v>
       </c>
@@ -32385,11 +33205,11 @@
       </c>
     </row>
     <row r="8" spans="2:7">
-      <c r="C8" s="118" t="s">
+      <c r="C8" s="117" t="s">
         <v>912</v>
       </c>
-      <c r="D8" s="119"/>
-      <c r="E8" s="120"/>
+      <c r="D8" s="118"/>
+      <c r="E8" s="119"/>
       <c r="F8" t="s">
         <v>914</v>
       </c>
@@ -32398,9 +33218,9 @@
       </c>
     </row>
     <row r="9" spans="2:7" ht="15.75" thickBot="1">
-      <c r="C9" s="121"/>
-      <c r="D9" s="122"/>
-      <c r="E9" s="123"/>
+      <c r="C9" s="120"/>
+      <c r="D9" s="121"/>
+      <c r="E9" s="122"/>
       <c r="F9" t="s">
         <v>916</v>
       </c>
@@ -32409,11 +33229,11 @@
       </c>
     </row>
     <row r="10" spans="2:7">
-      <c r="C10" s="118" t="s">
+      <c r="C10" s="117" t="s">
         <v>913</v>
       </c>
-      <c r="D10" s="119"/>
-      <c r="E10" s="120"/>
+      <c r="D10" s="118"/>
+      <c r="E10" s="119"/>
       <c r="F10" t="s">
         <v>914</v>
       </c>
@@ -32422,9 +33242,9 @@
       </c>
     </row>
     <row r="11" spans="2:7" ht="15.75" thickBot="1">
-      <c r="C11" s="121"/>
-      <c r="D11" s="122"/>
-      <c r="E11" s="123"/>
+      <c r="C11" s="120"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="122"/>
       <c r="F11" t="s">
         <v>916</v>
       </c>
@@ -32445,7 +33265,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:V307"/>
+  <dimension ref="B2:V348"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="10.140625" customWidth="1"/>
@@ -33057,6 +33877,14 @@
     <row r="155" spans="2:9">
       <c r="D155" s="15" t="s">
         <v>1172</v>
+      </c>
+    </row>
+    <row r="156" spans="2:9">
+      <c r="C156" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D156" s="15" t="s">
+        <v>1312</v>
       </c>
     </row>
     <row r="157" spans="2:9">
@@ -33959,14 +34787,195 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="306" spans="2:3">
+    <row r="306" spans="2:4">
       <c r="B306" t="s">
         <v>971</v>
       </c>
     </row>
-    <row r="307" spans="2:3">
+    <row r="307" spans="2:4">
       <c r="C307" t="s">
         <v>1283</v>
+      </c>
+    </row>
+    <row r="311" spans="2:4">
+      <c r="B311" s="6" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="312" spans="2:4">
+      <c r="C312" s="15" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="313" spans="2:4">
+      <c r="C313" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="314" spans="2:4">
+      <c r="D314" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="316" spans="2:4">
+      <c r="C316" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="317" spans="2:4">
+      <c r="D317" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="318" spans="2:4">
+      <c r="D318" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="319" spans="2:4">
+      <c r="D319" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="320" spans="2:4">
+      <c r="C320" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="321" spans="3:5">
+      <c r="D321" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="322" spans="3:5">
+      <c r="E322" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="323" spans="3:5">
+      <c r="E323" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="324" spans="3:5">
+      <c r="E324" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="325" spans="3:5">
+      <c r="E325" s="71" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="326" spans="3:5">
+      <c r="D326" t="s">
+        <v>1314</v>
+      </c>
+      <c r="E326" s="71"/>
+    </row>
+    <row r="327" spans="3:5">
+      <c r="E327" s="71" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="328" spans="3:5">
+      <c r="D328" t="s">
+        <v>1311</v>
+      </c>
+      <c r="E328" s="71"/>
+    </row>
+    <row r="329" spans="3:5">
+      <c r="E329" s="71"/>
+    </row>
+    <row r="331" spans="3:5">
+      <c r="C331" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="332" spans="3:5">
+      <c r="D332" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="333" spans="3:5">
+      <c r="E333" s="15" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="334" spans="3:5">
+      <c r="D334" t="s">
+        <v>1301</v>
+      </c>
+      <c r="E334" s="15"/>
+    </row>
+    <row r="335" spans="3:5" s="40" customFormat="1">
+      <c r="E335" s="40" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="336" spans="3:5" s="40" customFormat="1">
+      <c r="E336" s="40" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="337" spans="4:5" s="40" customFormat="1">
+      <c r="E337" s="40" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="338" spans="4:5" s="40" customFormat="1">
+      <c r="E338" s="40" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="339" spans="4:5">
+      <c r="D339" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="340" spans="4:5">
+      <c r="E340" s="15" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="341" spans="4:5">
+      <c r="D341" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="342" spans="4:5">
+      <c r="E342" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="343" spans="4:5">
+      <c r="D343" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="344" spans="4:5">
+      <c r="E344" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="345" spans="4:5">
+      <c r="E345" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="346" spans="4:5">
+      <c r="D346" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="347" spans="4:5">
+      <c r="E347" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="348" spans="4:5">
+      <c r="E348" t="s">
+        <v>1300</v>
       </c>
     </row>
   </sheetData>
@@ -38164,8 +39173,8 @@
       <c r="C114" s="6" t="s">
         <v>1269</v>
       </c>
-      <c r="D114" s="44">
-        <v>0</v>
+      <c r="D114" s="36">
+        <v>1</v>
       </c>
       <c r="E114" s="6"/>
       <c r="F114" s="14" t="s">
@@ -38177,18 +39186,22 @@
         <v>1092</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>1086</v>
-      </c>
-      <c r="D115" s="44"/>
+        <v>1088</v>
+      </c>
+      <c r="D115" s="36">
+        <v>1</v>
+      </c>
       <c r="E115" s="6"/>
-      <c r="F115" s="6"/>
+      <c r="F115" s="14" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="45" t="s">
         <v>1093</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="D116" s="44"/>
       <c r="E116" s="6"/>
@@ -38658,7 +39671,7 @@
       <c r="C150" s="7" t="s">
         <v>1015</v>
       </c>
-      <c r="D150" s="112"/>
+      <c r="D150" s="106"/>
       <c r="E150" s="14"/>
       <c r="F150" s="14"/>
     </row>
@@ -38667,7 +39680,7 @@
       <c r="C151" s="7" t="s">
         <v>1016</v>
       </c>
-      <c r="D151" s="112"/>
+      <c r="D151" s="106"/>
       <c r="E151" s="14"/>
       <c r="F151" s="14"/>
     </row>
@@ -38676,7 +39689,7 @@
       <c r="C152" s="7" t="s">
         <v>1017</v>
       </c>
-      <c r="D152" s="112"/>
+      <c r="D152" s="106"/>
       <c r="E152" s="14"/>
       <c r="F152" s="14"/>
     </row>
@@ -38685,7 +39698,7 @@
       <c r="C153" s="7" t="s">
         <v>1018</v>
       </c>
-      <c r="D153" s="112"/>
+      <c r="D153" s="106"/>
       <c r="E153" s="14"/>
       <c r="F153" s="14"/>
     </row>
@@ -38696,7 +39709,7 @@
       <c r="C154" s="7" t="s">
         <v>1211</v>
       </c>
-      <c r="D154" s="112"/>
+      <c r="D154" s="106"/>
       <c r="E154" s="14"/>
       <c r="F154" s="14"/>
     </row>
@@ -38705,7 +39718,7 @@
       <c r="C155" s="7" t="s">
         <v>1212</v>
       </c>
-      <c r="D155" s="112"/>
+      <c r="D155" s="106"/>
       <c r="E155" s="14"/>
       <c r="F155" s="14"/>
     </row>
@@ -38851,6 +39864,7 @@
     <hyperlink ref="F156" location="'#35'!B2" display="Link"/>
     <hyperlink ref="F114" location="'#21'!B259" display="Link"/>
     <hyperlink ref="F136" location="'#26'!B22" display="Link"/>
+    <hyperlink ref="F115" location="'#21'!B311" display="Link"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId13"/>
@@ -39229,21 +40243,21 @@
       <c r="D16" t="s">
         <v>709</v>
       </c>
-      <c r="I16" s="124" t="s">
+      <c r="I16" s="123" t="s">
         <v>713</v>
       </c>
-      <c r="J16" s="125"/>
+      <c r="J16" s="124"/>
     </row>
     <row r="17" spans="3:10" ht="15" customHeight="1">
-      <c r="I17" s="126"/>
-      <c r="J17" s="127"/>
+      <c r="I17" s="125"/>
+      <c r="J17" s="126"/>
     </row>
     <row r="18" spans="3:10">
       <c r="D18" t="s">
         <v>710</v>
       </c>
-      <c r="I18" s="128"/>
-      <c r="J18" s="129"/>
+      <c r="I18" s="127"/>
+      <c r="J18" s="128"/>
     </row>
     <row r="19" spans="3:10">
       <c r="C19" t="s">
@@ -39695,7 +40709,7 @@
       <c r="D12" s="11"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" thickBot="1">
-      <c r="C13" s="113" t="s">
+      <c r="C13" s="112" t="s">
         <v>78</v>
       </c>
       <c r="D13" s="24" t="s">
@@ -39712,7 +40726,7 @@
       <c r="I13" s="23"/>
     </row>
     <row r="14" spans="1:10" ht="15.75" thickBot="1">
-      <c r="C14" s="114"/>
+      <c r="C14" s="113"/>
       <c r="D14" s="21" t="s">
         <v>65</v>
       </c>
@@ -39728,7 +40742,7 @@
       <c r="J14" s="23"/>
     </row>
     <row r="15" spans="1:10">
-      <c r="C15" s="114"/>
+      <c r="C15" s="113"/>
       <c r="D15" s="24" t="s">
         <v>66</v>
       </c>
@@ -39743,7 +40757,7 @@
       <c r="I15" s="26"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="C16" s="114"/>
+      <c r="C16" s="113"/>
       <c r="D16" s="27"/>
       <c r="E16" t="s">
         <v>74</v>
@@ -39752,7 +40766,7 @@
       <c r="I16" s="28"/>
     </row>
     <row r="17" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C17" s="115"/>
+      <c r="C17" s="114"/>
       <c r="D17" s="29"/>
       <c r="E17" s="30" t="s">
         <v>75</v>
@@ -39781,7 +40795,7 @@
       <c r="L18" s="23"/>
     </row>
     <row r="19" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C19" s="113" t="s">
+      <c r="C19" s="112" t="s">
         <v>78</v>
       </c>
       <c r="D19" s="21" t="s">
@@ -39792,7 +40806,7 @@
       </c>
     </row>
     <row r="20" spans="3:12">
-      <c r="C20" s="114"/>
+      <c r="C20" s="113"/>
       <c r="D20" s="24" t="s">
         <v>82</v>
       </c>
@@ -39801,7 +40815,7 @@
       </c>
     </row>
     <row r="21" spans="3:12" ht="15.75" thickBot="1">
-      <c r="C21" s="115"/>
+      <c r="C21" s="114"/>
       <c r="D21" s="29"/>
       <c r="E21" s="34" t="s">
         <v>84</v>

--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="9" activeTab="22"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Knowhow" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1830" uniqueCount="1315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1851" uniqueCount="1327">
   <si>
     <t>No.</t>
   </si>
@@ -20923,6 +20923,304 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> phức tạp mới có</t>
+    </r>
+  </si>
+  <si>
+    <t>https://github.com/HoangAnh-Dinh/C-_Learning/tree/main/21.14</t>
+  </si>
+  <si>
+    <t>thread id</t>
+  </si>
+  <si>
+    <r>
+      <t>std::async là</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> khởi chạy một tác vụ bất đồng bộ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và trả kết quả cho future mà </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>không cần phải tạo thread thủ công</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Muốn chạy một tác vụ bất đồng bộ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>one-shot commu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nhanh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, và </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>dễ lấy kết quả</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (không muốn quản lý thread thủ công).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">std::future&lt;int&gt; fut = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>std::async(std::launch::async</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, heavy_work, 21);</t>
+    </r>
+  </si>
+  <si>
+    <t>int heavy_work(int x) {}</t>
+  </si>
+  <si>
+    <t>Cấu trúc</t>
+  </si>
+  <si>
+    <r>
+      <t>std::future&lt;int&gt; fut = std::async([</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Kiểu async</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>], [</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Tên hàm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>], [</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Tham số truyền vào hàm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]);</t>
+    </r>
+  </si>
+  <si>
+    <t>Khai báo 1 future có dùng async (chọn kiểu async thích hợp), rồi bao giờ cần lấy kêt quả thì future.get()</t>
+  </si>
+  <si>
+    <t>Kiểu async :</t>
+  </si>
+  <si>
+    <r>
+      <t>std::launch::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">async </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> // Tạo thread mới và </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>chạy ngay</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, chạy xong thì đợi được trả kết quả</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>std::launch::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>deferred</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> // </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Không chạy ngay</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, bao giờ có gọi get(), wait() thì mới chạy</t>
     </r>
   </si>
 </sst>
@@ -21551,7 +21849,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -21827,6 +22125,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -33265,7 +33564,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:V348"/>
+  <dimension ref="B2:V372"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="10.140625" customWidth="1"/>
@@ -34918,64 +35217,162 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="337" spans="4:5" s="40" customFormat="1">
+    <row r="337" spans="2:5" s="40" customFormat="1">
       <c r="E337" s="40" t="s">
         <v>1305</v>
       </c>
     </row>
-    <row r="338" spans="4:5" s="40" customFormat="1">
+    <row r="338" spans="2:5" s="40" customFormat="1">
       <c r="E338" s="40" t="s">
         <v>1304</v>
       </c>
     </row>
-    <row r="339" spans="4:5">
+    <row r="339" spans="2:5">
       <c r="D339" t="s">
         <v>1294</v>
       </c>
     </row>
-    <row r="340" spans="4:5">
+    <row r="340" spans="2:5">
       <c r="E340" s="15" t="s">
         <v>1293</v>
       </c>
     </row>
-    <row r="341" spans="4:5">
+    <row r="341" spans="2:5">
       <c r="D341" t="s">
         <v>1291</v>
       </c>
     </row>
-    <row r="342" spans="4:5">
+    <row r="342" spans="2:5">
       <c r="E342" t="s">
         <v>1292</v>
       </c>
     </row>
-    <row r="343" spans="4:5">
+    <row r="343" spans="2:5">
       <c r="D343" t="s">
         <v>1298</v>
       </c>
     </row>
-    <row r="344" spans="4:5">
+    <row r="344" spans="2:5">
       <c r="E344" t="s">
         <v>1295</v>
       </c>
     </row>
-    <row r="345" spans="4:5">
+    <row r="345" spans="2:5">
       <c r="E345" t="s">
         <v>1297</v>
       </c>
     </row>
-    <row r="346" spans="4:5">
+    <row r="346" spans="2:5">
       <c r="D346" t="s">
         <v>1296</v>
       </c>
     </row>
-    <row r="347" spans="4:5">
+    <row r="347" spans="2:5">
       <c r="E347" t="s">
         <v>1299</v>
       </c>
     </row>
-    <row r="348" spans="4:5">
+    <row r="348" spans="2:5">
       <c r="E348" t="s">
         <v>1300</v>
+      </c>
+    </row>
+    <row r="352" spans="2:5">
+      <c r="B352" s="6" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="353" spans="3:5">
+      <c r="C353" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="354" spans="3:5">
+      <c r="D354" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="356" spans="3:5">
+      <c r="C356" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="357" spans="3:5">
+      <c r="D357" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="359" spans="3:5">
+      <c r="C359" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="360" spans="3:5">
+      <c r="D360" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="361" spans="3:5">
+      <c r="E361" s="15" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="362" spans="3:5">
+      <c r="D362" t="s">
+        <v>1301</v>
+      </c>
+      <c r="E362" s="15"/>
+    </row>
+    <row r="363" spans="3:5">
+      <c r="C363" s="40"/>
+      <c r="D363" s="40"/>
+      <c r="E363" s="40" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="364" spans="3:5">
+      <c r="C364" s="40"/>
+      <c r="D364" s="40"/>
+      <c r="E364" s="40"/>
+    </row>
+    <row r="365" spans="3:5">
+      <c r="D365" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="366" spans="3:5">
+      <c r="E366" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="367" spans="3:5">
+      <c r="E367" s="129" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="368" spans="3:5">
+      <c r="D368" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="369" spans="5:7">
+      <c r="E369" s="129" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="370" spans="5:7">
+      <c r="F370" t="s">
+        <v>1324</v>
+      </c>
+    </row>
+    <row r="371" spans="5:7">
+      <c r="G371" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="372" spans="5:7">
+      <c r="G372" t="s">
+        <v>1326</v>
       </c>
     </row>
   </sheetData>
@@ -39191,7 +39588,9 @@
       <c r="D115" s="36">
         <v>1</v>
       </c>
-      <c r="E115" s="6"/>
+      <c r="E115" s="14" t="s">
+        <v>1315</v>
+      </c>
       <c r="F115" s="14" t="s">
         <v>14</v>
       </c>
@@ -39203,9 +39602,13 @@
       <c r="C116" s="6" t="s">
         <v>1086</v>
       </c>
-      <c r="D116" s="44"/>
+      <c r="D116" s="36">
+        <v>1</v>
+      </c>
       <c r="E116" s="6"/>
-      <c r="F116" s="6"/>
+      <c r="F116" s="14" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="117" spans="2:6">
       <c r="B117" s="45" t="s">
@@ -39277,7 +39680,9 @@
       <c r="B123" s="45" t="s">
         <v>1112</v>
       </c>
-      <c r="C123" s="6"/>
+      <c r="C123" s="6" t="s">
+        <v>1316</v>
+      </c>
       <c r="D123" s="44"/>
       <c r="E123" s="6"/>
       <c r="F123" s="6"/>
@@ -39865,9 +40270,11 @@
     <hyperlink ref="F114" location="'#21'!B259" display="Link"/>
     <hyperlink ref="F136" location="'#26'!B22" display="Link"/>
     <hyperlink ref="F115" location="'#21'!B311" display="Link"/>
+    <hyperlink ref="E115" r:id="rId13"/>
+    <hyperlink ref="F116" location="'#21'!B352" display="Link"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId13"/>
+  <pageSetup orientation="portrait" r:id="rId14"/>
 </worksheet>
 </file>
 

--- a/Study_CL.xlsx
+++ b/Study_CL.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1851" uniqueCount="1327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1857" uniqueCount="1333">
   <si>
     <t>No.</t>
   </si>
@@ -19248,9 +19248,6 @@
     <t>Future cho phép thread gọi hàm bất đồng bộ và sau đó đồng bộ lại bằng cách lấy kết quả thông qua get(), thay vì phải chia sẻ biến chung hay dùng mutex.</t>
   </si>
   <si>
-    <t>std::future / Bất đồng bộ / Asynchronous programming</t>
-  </si>
-  <si>
     <t>Bất đồng bộ / Asynchronous programming</t>
   </si>
   <si>
@@ -21222,6 +21219,183 @@
       </rPr>
       <t>, bao giờ có gọi get(), wait() thì mới chạy</t>
     </r>
+  </si>
+  <si>
+    <t>https://github.com/HoangAnh-Dinh/C-_Learning/tree/main/21.15</t>
+  </si>
+  <si>
+    <r>
+      <t>future.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>wait()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> // Có thể </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>gọi nhiều lần</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, tác dụng là </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>đợi kết quả</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tính toán từ future</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>future.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>get()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> // Chỉ được </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>gọi 1 lần</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>lấy kết quả</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tính toán cho future</t>
+    </r>
+  </si>
+  <si>
+    <t>std::future / Bất đồng bộ / Asynchronous programming/ future.wait() / future.get() / Nếu cố tình gọi get() 2 lần cho future thì sao</t>
+  </si>
+  <si>
+    <t>Nếu cố tình gọi get() 2 lần cho future thì sao ?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">-&gt; Chương trình sẽ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ném ra exception</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> : future_error::</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>no_state</t>
+    </r>
+  </si>
+  <si>
+    <t>std::shared_future</t>
   </si>
 </sst>
 </file>
@@ -22074,6 +22248,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -22125,7 +22300,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -30571,16 +30745,16 @@
       </c>
     </row>
     <row r="89" spans="2:9" ht="54" customHeight="1">
-      <c r="B89" s="115" t="s">
+      <c r="B89" s="116" t="s">
         <v>615</v>
       </c>
-      <c r="C89" s="116"/>
-      <c r="D89" s="116"/>
-      <c r="E89" s="116"/>
-      <c r="F89" s="116"/>
-      <c r="G89" s="116"/>
-      <c r="H89" s="116"/>
-      <c r="I89" s="116"/>
+      <c r="C89" s="117"/>
+      <c r="D89" s="117"/>
+      <c r="E89" s="117"/>
+      <c r="F89" s="117"/>
+      <c r="G89" s="117"/>
+      <c r="H89" s="117"/>
+      <c r="I89" s="117"/>
     </row>
     <row r="91" spans="2:9">
       <c r="B91" t="s">
@@ -33456,11 +33630,11 @@
     </row>
     <row r="3" spans="2:7" ht="15.75" thickBot="1"/>
     <row r="4" spans="2:7">
-      <c r="C4" s="117" t="s">
+      <c r="C4" s="118" t="s">
         <v>910</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="119"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="120"/>
       <c r="F4" t="s">
         <v>914</v>
       </c>
@@ -33469,9 +33643,9 @@
       </c>
     </row>
     <row r="5" spans="2:7" ht="15.75" thickBot="1">
-      <c r="C5" s="120"/>
-      <c r="D5" s="121"/>
-      <c r="E5" s="122"/>
+      <c r="C5" s="121"/>
+      <c r="D5" s="122"/>
+      <c r="E5" s="123"/>
       <c r="F5" t="s">
         <v>916</v>
       </c>
@@ -33480,11 +33654,11 @@
       </c>
     </row>
     <row r="6" spans="2:7">
-      <c r="C6" s="117" t="s">
+      <c r="C6" s="118" t="s">
         <v>911</v>
       </c>
-      <c r="D6" s="118"/>
-      <c r="E6" s="119"/>
+      <c r="D6" s="119"/>
+      <c r="E6" s="120"/>
       <c r="F6" t="s">
         <v>914</v>
       </c>
@@ -33493,9 +33667,9 @@
       </c>
     </row>
     <row r="7" spans="2:7" ht="15.75" thickBot="1">
-      <c r="C7" s="120"/>
-      <c r="D7" s="121"/>
-      <c r="E7" s="122"/>
+      <c r="C7" s="121"/>
+      <c r="D7" s="122"/>
+      <c r="E7" s="123"/>
       <c r="F7" t="s">
         <v>916</v>
       </c>
@@ -33504,11 +33678,11 @@
       </c>
     </row>
     <row r="8" spans="2:7">
-      <c r="C8" s="117" t="s">
+      <c r="C8" s="118" t="s">
         <v>912</v>
       </c>
-      <c r="D8" s="118"/>
-      <c r="E8" s="119"/>
+      <c r="D8" s="119"/>
+      <c r="E8" s="120"/>
       <c r="F8" t="s">
         <v>914</v>
       </c>
@@ -33517,9 +33691,9 @@
       </c>
     </row>
     <row r="9" spans="2:7" ht="15.75" thickBot="1">
-      <c r="C9" s="120"/>
-      <c r="D9" s="121"/>
-      <c r="E9" s="122"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="122"/>
+      <c r="E9" s="123"/>
       <c r="F9" t="s">
         <v>916</v>
       </c>
@@ -33528,11 +33702,11 @@
       </c>
     </row>
     <row r="10" spans="2:7">
-      <c r="C10" s="117" t="s">
+      <c r="C10" s="118" t="s">
         <v>913</v>
       </c>
-      <c r="D10" s="118"/>
-      <c r="E10" s="119"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="120"/>
       <c r="F10" t="s">
         <v>914</v>
       </c>
@@ -33541,9 +33715,9 @@
       </c>
     </row>
     <row r="11" spans="2:7" ht="15.75" thickBot="1">
-      <c r="C11" s="120"/>
-      <c r="D11" s="121"/>
-      <c r="E11" s="122"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="122"/>
+      <c r="E11" s="123"/>
       <c r="F11" t="s">
         <v>916</v>
       </c>
@@ -34180,10 +34354,10 @@
     </row>
     <row r="156" spans="2:9">
       <c r="C156" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="D156" s="15" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="157" spans="2:9">
@@ -35063,7 +35237,7 @@
     </row>
     <row r="299" spans="2:3">
       <c r="B299" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="300" spans="2:3">
@@ -35073,7 +35247,7 @@
     </row>
     <row r="301" spans="2:3">
       <c r="C301" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="303" spans="2:3">
@@ -35083,17 +35257,37 @@
     </row>
     <row r="304" spans="2:3">
       <c r="C304" s="15" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="305" spans="2:4">
+      <c r="B305" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="306" spans="2:4">
+      <c r="C306" t="s">
         <v>1282</v>
-      </c>
-    </row>
-    <row r="306" spans="2:4">
-      <c r="B306" t="s">
-        <v>971</v>
       </c>
     </row>
     <row r="307" spans="2:4">
       <c r="C307" t="s">
-        <v>1283</v>
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="308" spans="2:4">
+      <c r="C308" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="309" spans="2:4">
+      <c r="B309" s="15" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="310" spans="2:4">
+      <c r="D310" s="71" t="s">
+        <v>1331</v>
       </c>
     </row>
     <row r="311" spans="2:4">
@@ -35103,7 +35297,7 @@
     </row>
     <row r="312" spans="2:4">
       <c r="C312" s="15" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="313" spans="2:4">
@@ -35113,27 +35307,27 @@
     </row>
     <row r="314" spans="2:4">
       <c r="D314" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="316" spans="2:4">
       <c r="C316" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="317" spans="2:4">
       <c r="D317" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="318" spans="2:4">
       <c r="D318" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="319" spans="2:4">
       <c r="D319" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="320" spans="2:4">
@@ -35143,43 +35337,43 @@
     </row>
     <row r="321" spans="3:5">
       <c r="D321" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="322" spans="3:5">
       <c r="E322" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="323" spans="3:5">
       <c r="E323" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="324" spans="3:5">
       <c r="E324" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="325" spans="3:5">
       <c r="E325" s="71" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="326" spans="3:5">
       <c r="D326" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="E326" s="71"/>
     </row>
     <row r="327" spans="3:5">
       <c r="E327" s="71" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="328" spans="3:5">
       <c r="D328" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E328" s="71"/>
     </row>
@@ -35198,83 +35392,83 @@
     </row>
     <row r="333" spans="3:5">
       <c r="E333" s="15" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="334" spans="3:5">
       <c r="D334" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="E334" s="15"/>
     </row>
     <row r="335" spans="3:5" s="40" customFormat="1">
       <c r="E335" s="40" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="336" spans="3:5" s="40" customFormat="1">
       <c r="E336" s="40" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="337" spans="2:5" s="40" customFormat="1">
       <c r="E337" s="40" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="338" spans="2:5" s="40" customFormat="1">
       <c r="E338" s="40" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="339" spans="2:5">
       <c r="D339" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="340" spans="2:5">
       <c r="E340" s="15" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="341" spans="2:5">
       <c r="D341" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="342" spans="2:5">
       <c r="E342" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="343" spans="2:5">
       <c r="D343" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="344" spans="2:5">
       <c r="E344" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="345" spans="2:5">
       <c r="E345" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="346" spans="2:5">
       <c r="D346" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="347" spans="2:5">
       <c r="E347" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="348" spans="2:5">
       <c r="E348" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="352" spans="2:5">
@@ -35289,7 +35483,7 @@
     </row>
     <row r="354" spans="3:5">
       <c r="D354" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="356" spans="3:5">
@@ -35299,7 +35493,7 @@
     </row>
     <row r="357" spans="3:5">
       <c r="D357" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="359" spans="3:5">
@@ -35314,12 +35508,12 @@
     </row>
     <row r="361" spans="3:5">
       <c r="E361" s="15" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="362" spans="3:5">
       <c r="D362" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="E362" s="15"/>
     </row>
@@ -35327,7 +35521,7 @@
       <c r="C363" s="40"/>
       <c r="D363" s="40"/>
       <c r="E363" s="40" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="364" spans="3:5">
@@ -35337,42 +35531,42 @@
     </row>
     <row r="365" spans="3:5">
       <c r="D365" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="366" spans="3:5">
       <c r="E366" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="367" spans="3:5">
-      <c r="E367" s="129" t="s">
-        <v>1319</v>
+      <c r="E367" s="112" t="s">
+        <v>1318</v>
       </c>
     </row>
     <row r="368" spans="3:5">
       <c r="D368" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="369" spans="5:7">
+      <c r="E369" s="112" t="s">
         <v>1321</v>
-      </c>
-    </row>
-    <row r="369" spans="5:7">
-      <c r="E369" s="129" t="s">
-        <v>1322</v>
       </c>
     </row>
     <row r="370" spans="5:7">
       <c r="F370" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="371" spans="5:7">
       <c r="G371" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="372" spans="5:7">
       <c r="G372" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
   </sheetData>
@@ -37554,12 +37748,12 @@
     </row>
     <row r="22" spans="2:7">
       <c r="B22" s="6" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="23" spans="2:7">
       <c r="C23" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="24" spans="2:7">
@@ -37569,7 +37763,7 @@
     </row>
     <row r="25" spans="2:7">
       <c r="D25" s="94" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="E25" s="95"/>
       <c r="F25" s="95"/>
@@ -37577,7 +37771,7 @@
     </row>
     <row r="26" spans="2:7">
       <c r="D26" s="94" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="E26" s="95"/>
       <c r="F26" s="95"/>
@@ -37593,7 +37787,7 @@
     </row>
     <row r="28" spans="2:7">
       <c r="D28" s="98" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="E28" s="95"/>
       <c r="F28" s="95"/>
@@ -37601,7 +37795,7 @@
     </row>
     <row r="29" spans="2:7">
       <c r="D29" s="98" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="E29" s="95"/>
       <c r="F29" s="95"/>
@@ -37609,7 +37803,7 @@
     </row>
     <row r="30" spans="2:7">
       <c r="D30" s="98" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="E30" s="95"/>
       <c r="F30" s="95"/>
@@ -37631,7 +37825,7 @@
     </row>
     <row r="33" spans="2:7">
       <c r="D33" s="94" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="E33" s="95"/>
       <c r="F33" s="95"/>
@@ -37639,7 +37833,7 @@
     </row>
     <row r="34" spans="2:7">
       <c r="D34" s="94" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="E34" s="95"/>
       <c r="F34" s="95"/>
@@ -37647,7 +37841,7 @@
     </row>
     <row r="35" spans="2:7">
       <c r="D35" s="97" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="E35" s="95"/>
       <c r="F35" s="95"/>
@@ -39563,12 +39757,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="114" spans="2:6">
+    <row r="114" spans="2:6" ht="33" customHeight="1">
       <c r="B114" s="45" t="s">
         <v>1091</v>
       </c>
-      <c r="C114" s="6" t="s">
-        <v>1269</v>
+      <c r="C114" s="7" t="s">
+        <v>1329</v>
       </c>
       <c r="D114" s="36">
         <v>1</v>
@@ -39589,7 +39783,7 @@
         <v>1</v>
       </c>
       <c r="E115" s="14" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="F115" s="14" t="s">
         <v>14</v>
@@ -39605,7 +39799,9 @@
       <c r="D116" s="36">
         <v>1</v>
       </c>
-      <c r="E116" s="6"/>
+      <c r="E116" s="14" t="s">
+        <v>1326</v>
+      </c>
       <c r="F116" s="14" t="s">
         <v>14</v>
       </c>
@@ -39636,8 +39832,8 @@
       <c r="B119" s="45" t="s">
         <v>1108</v>
       </c>
-      <c r="C119" s="6" t="s">
-        <v>1100</v>
+      <c r="C119" s="1" t="s">
+        <v>1332</v>
       </c>
       <c r="D119" s="44"/>
       <c r="E119" s="6"/>
@@ -39648,7 +39844,7 @@
         